--- a/remote_jobs.xlsx
+++ b/remote_jobs.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Remote Jobs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remote Jobs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:K95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -523,281 +523,245 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Rust Consultant / Engineer (m/w/d)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Dry Ground AI</t>
+          <t>Hackstack GmbH</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Brazil, Colombia, Philippines</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>full_time</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence</t>
-        </is>
-      </c>
+          <t>berufserfahren</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>api, cloud, fullstack, python, AI/ML, automation, research, CI/CD, TensorFlow, spark, NLP, CMS, Pytorch, REST</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>$40- $60k</t>
-        </is>
-      </c>
+          <t>Remote, Consulting, Engineering</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Remotive</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>https://remotive.com/remote-jobs/artificial-intelligence/ai-engineer-2089958</t>
+          <t>https://www.arbeitnow.com/jobs/companies/hackstack-gmbh/senior-rust-consultant-engineer-munich-451602</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Senior Independent AI Engineer / Architect</t>
+          <t>Applied AI Engineer - Remote</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>A.Team</t>
+          <t>dexter health</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Americas, Europe, Israel</t>
+          <t>Cologne</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>contract</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Software Development</t>
-        </is>
-      </c>
+          <t>professional / experienced</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr"/>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>go, UI/UX, wordpress, chat, apple, testing, catalyst</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>$120 - $170 /hour</t>
-        </is>
-      </c>
+          <t>Remote, Development</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr"/>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>Remotive</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>https://remotive.com/remote-jobs/software-development/senior-independent-ai-engineer-architect-1919266</t>
+          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/applied-ai-engineer-remote-cologne-2870</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Senior Independent Software Developer</t>
+          <t>Python Backend Engineer - Remote</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>A.Team</t>
+          <t>dexter health</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Americas, Europe, Israel</t>
+          <t>Cologne</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>contract</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Software Development</t>
-        </is>
-      </c>
+          <t>professional / experienced</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>go, wordpress, chat, apple, testing, catalyst</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>$90 - $150 /hour</t>
-        </is>
-      </c>
+          <t>Remote, Development</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Remotive</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>https://remotive.com/remote-jobs/software-development/senior-independent-software-developer-1919265</t>
+          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/python-backend-engineer-remote-cologne-34228</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Senior Full-stack React Developer</t>
+          <t>AI Engineer (LLM Products) - Remote</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Lemon.io</t>
+          <t>dexter health</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Americas, Europe, Asia, Oceania</t>
+          <t>Cologne</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>contract</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Software Development</t>
-        </is>
-      </c>
+          <t>professional / experienced</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>.Net, android, AWS, azure, backend, C, C#, C++, data science, fullstack, golang, ios, java, javascript, node.js, php, python, react, react js, ruby/rails, shopify, video, blockchain, AI/ML, react native, rust, unity, spring, data analysis, laravel, solidity, flask, Typescript , angular , GCP, data engineering, Symfony, startup, marketplace, next.js</t>
+          <t>Remote, Development</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>Remotive</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>https://remotive.com/remote-jobs/software-development/senior-full-stack-react-developer-2088711</t>
+          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/ai-engineer-llm-products-remote-cologne-236027</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Tech Lead Full-Stack Rails Engineer</t>
+          <t>Backend Python Engineer (APIs, Databases &amp; Cloud) - Remote</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Mitre Media</t>
+          <t>dexter health</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>USA, Canada, USA timezones</t>
+          <t>Cologne</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>full_time</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Software Development</t>
-        </is>
-      </c>
+          <t>professional / experienced</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>api, CSS, docker, elasticsearch, fullstack, html, javascript, kubernetes, postgresql, react, ror, ruby/rails, AI/ML, CAD, advertising, Redis, ES6, web applications, MySQL, NLP, fintech, Micro services, github, system architecture</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>$170k - $200k</t>
-        </is>
-      </c>
+          <t>Remote, Development</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Remotive</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>https://remotive.com/remote-jobs/software-development/tech-lead-full-stack-rails-engineer-2069746</t>
+          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/backend-python-engineer-apis-databases-cloud-remote-cologne-274767</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -809,52 +773,32 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Senior Frontend Developer</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Sanctuary Computer</t>
-        </is>
-      </c>
+          <t>Toptal: QA Automation Engineer</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr"/>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>LATAM, Asia</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>contract</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Software Development</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>api, backend, CSS, ecommerce, frontend, fullstack, graphql, postgresql, redux, security, seo, shopify, open source, paas, product management, documentation, mentoring, Typescript , Redis, web applications, cypress, data visualization, firebase, IoT, engineering management, runtime, responsive, prismic, testing, next.js, CMS, jest, REST, web sockets, performance optimization</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>$80k - $120k</t>
-        </is>
-      </c>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr"/>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>Remotive</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>https://remotive.com/remote-jobs/software-development/senior-frontend-developer-2088707</t>
+          <t>https://weworkremotely.com/remote-jobs/toptal-qa-automation-engineer-1</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -866,48 +810,32 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Fullstack Developer (US - ET)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Chooose</t>
-        </is>
-      </c>
+          <t>Opensea: Staff Product Designer</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr"/>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>full_time</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Software Development</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>api, azure, fullstack, python, react, saas, AI/ML, project management, documentation, Typescript , computer science, diversity, insurance</t>
-        </is>
-      </c>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Remotive</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>https://remotive.com/remote-jobs/software-development/fullstack-developer-us-et-2088706</t>
+          <t>https://weworkremotely.com/remote-jobs/opensea-staff-product-designer</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -919,17 +847,13 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning Manager, Notifications Relevance</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Reddit</t>
-        </is>
-      </c>
+          <t>Mutt Data: Devops</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr"/>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr"/>
@@ -938,17 +862,17 @@
       <c r="H9" s="4" t="inlineStr"/>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7846885</t>
+          <t>https://weworkremotely.com/remote-jobs/mutt-data-devops</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -960,17 +884,13 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Senior Staff ML Engineer, Search &amp; Recommendation</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Reddit</t>
-        </is>
-      </c>
+          <t>Holywater: Full-Stack Developer</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -979,17 +899,17 @@
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7833622</t>
+          <t>https://weworkremotely.com/remote-jobs/holywater-full-stack-developer</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1001,17 +921,13 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Twilio</t>
-        </is>
-      </c>
+          <t>Qventus: DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr"/>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Remote - US</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr"/>
@@ -1020,17 +936,17 @@
       <c r="H11" s="4" t="inlineStr"/>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7059734</t>
+          <t>https://weworkremotely.com/remote-jobs/qventus-devops-engineer</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1042,17 +958,13 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Twilio</t>
-        </is>
-      </c>
+          <t>Visualis: Senior Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Remote - US</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
@@ -1061,17 +973,17 @@
       <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7702644</t>
+          <t>https://weworkremotely.com/remote-jobs/visualis-senior-full-stack-developer</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1083,17 +995,17 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Principal Machine Learning &amp; Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Remote - US</t>
+          <t>Remote, Bangalore</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr"/>
@@ -1107,12 +1019,12 @@
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7155492</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8517564002</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1036,17 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Principal, Product Manager - AI / LLM</t>
+          <t>Backend Engineer, Analytics Instrumentation (Golang)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Remote - US</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
@@ -1148,12 +1060,12 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7619420</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481922002</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1165,17 +1077,17 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Product Engineer (Backend)</t>
+          <t>Backend Engineer, Analytics Instrumentation (Golang)</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Remote - US</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr"/>
@@ -1189,12 +1101,12 @@
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7671815</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481929002</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1118,17 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Senior Manager, Machine Learning</t>
+          <t>Backend Engineer, Knowledge Graph (Rust)</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Remote - US</t>
+          <t>Remote, Canada; Remote, US</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -1230,12 +1142,12 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7066029</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8437754002</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1247,17 +1159,17 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Staff Data Scientist</t>
+          <t>Backend Engineer, Knowledge Graph (Rust)</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Remote - US</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr"/>
@@ -1271,12 +1183,12 @@
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7821458</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481958002</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1288,17 +1200,17 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Staff, Data Scientist (L4) GTM Data Science &amp; Analytics</t>
+          <t>Intermediate Backend Engineer (C), Tenant Scale: Git</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Remote - US</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
@@ -1312,12 +1224,12 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7851920</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8497793002</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1329,17 +1241,17 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer</t>
+          <t>Intermediate Backend Engineer, Gitlab Delivery: Upgrades</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Remote - US</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
@@ -1353,12 +1265,12 @@
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7061880</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8463951002</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1370,17 +1282,17 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer (L4)</t>
+          <t>Intermediate Backend Engineer, SRM: Security Platform Management</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Remote - India</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -1394,12 +1306,12 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7520997</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8443325002</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1411,44 +1323,36 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Senior Python Developer - Django (m/w/d)</t>
+          <t>Intermediate Backend Engineer, SSCS: AI Governance</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>sync.blue® GmbH</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Haltern am See</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>berufserfahren</t>
-        </is>
-      </c>
+          <t>Remote, India</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr"/>
       <c r="F21" s="4" t="inlineStr"/>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Software Development</t>
-        </is>
-      </c>
+      <c r="G21" s="4" t="inlineStr"/>
       <c r="H21" s="4" t="inlineStr"/>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/syncblue-gmbh/senior-python-developer-django-haltern-am-see-16238</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480551002</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1460,44 +1364,36 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Freelance Senior AI Product Manager</t>
+          <t>Intermediate Backend Engineer,  SSCS: Supply Chain</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>nexamind GmbH</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Freelance, professional / experienced</t>
-        </is>
-      </c>
+          <t>Remote, India</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr"/>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>Remote, Product Management</t>
-        </is>
-      </c>
+      <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/nexamind-gmbh/freelance-senior-ai-product-manager-berlin-73613</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480565002</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1509,44 +1405,36 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Senior Full-Stack-Entwickler:in React / TypeScript / .NET  100 % Remote, KI-First</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>yourMAIL GmbH</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>berufserfahren</t>
-        </is>
-      </c>
+          <t>Remote, EMEA</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr"/>
       <c r="F23" s="4" t="inlineStr"/>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Software Development</t>
-        </is>
-      </c>
+      <c r="G23" s="4" t="inlineStr"/>
       <c r="H23" s="4" t="inlineStr"/>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/yourmail-gmbh/senior-full-stack-entwicklerin-react-typescript-net-100-remote-ki-first-berlin-21152</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8464072002</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1558,44 +1446,36 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Senior Frontend-Entwickler:in React / TypeScript, 100 % Remote, KI-First</t>
+          <t>Senior Backend Engineer (AI), Pipeline Execution</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>yourMAIL GmbH</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>berufserfahren</t>
-        </is>
-      </c>
+          <t>Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US-Southeast</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>Remote, Software Development</t>
-        </is>
-      </c>
+      <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/yourmail-gmbh/senior-frontend-entwicklerin-react-typescript-100-remote-ki-first-berlin-288218</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8514945002</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1607,40 +1487,36 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Full-Stack Entwickler (m/w/d) - .NET 100% Remote</t>
+          <t>Senior Backend Engineer, Analytics Instrumentation (Golang)</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>FNTIO</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Frankfurt am Main</t>
+          <t>Remote, Canada; Remote, US</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr"/>
       <c r="F25" s="4" t="inlineStr"/>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Consulting, Engineering</t>
-        </is>
-      </c>
+      <c r="G25" s="4" t="inlineStr"/>
       <c r="H25" s="4" t="inlineStr"/>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/fntio/full-stack-entwickler-net-100-remote-frankfurt-am-main-122380</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8451512002</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1652,40 +1528,36 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Backend Engineer (C), Tenant Scale: Git</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Phantasma Labs</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="2" t="inlineStr"/>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Remote, Engineering</t>
-        </is>
-      </c>
+      <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/phantasma-labs/machine-learning-engineer-berlin-303955</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8497791002</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1697,44 +1569,36 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Technical Data Manager (m/w/d)</t>
+          <t>Senior Backend Engineer, Gitlab Delivery: Runway (Platform Engineering)</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>BMF Media Information Technology GmbH</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Augsburg</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>berufserfahren</t>
-        </is>
-      </c>
+          <t>Remote, Australia; Remote, India; Remote, Ireland; Remote, Japan; Remote, Netherlands; Remote, Singapore; Remote, United Kingdom</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr"/>
       <c r="F27" s="4" t="inlineStr"/>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Technical Documentation</t>
-        </is>
-      </c>
+      <c r="G27" s="4" t="inlineStr"/>
       <c r="H27" s="4" t="inlineStr"/>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/bmf-media-information-technology-gmbh/technical-data-manager-augsburg-42188</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8324132002</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1746,44 +1610,36 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Data Integration &amp; API Engineer m/w/d - Bi &amp; Data Automation</t>
+          <t>Senior Backend Engineer, Gitlab Delivery: Upgrades</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>loyos bi GmbH</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Hamburg</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>berufserfahren</t>
-        </is>
-      </c>
+          <t>Remote, India</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="2" t="inlineStr"/>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Remote, Software Development</t>
-        </is>
-      </c>
+      <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/loyos-bi-gmbh/data-integration-api-engineer-bi-data-automation-hamburg-66228</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8463933002</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1795,44 +1651,36 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Backend Engineer(Go), Continuous Delivery</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Coding Partners</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
+          <t>Remote, India</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr"/>
       <c r="F29" s="4" t="inlineStr"/>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Software Development</t>
-        </is>
-      </c>
+      <c r="G29" s="4" t="inlineStr"/>
       <c r="H29" s="4" t="inlineStr"/>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/coding-partners/senior-full-stack-engineer-berlin-391720</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8488966002</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1844,44 +1692,36 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Laravel Developer (m/w/d) - AI-First PropTech</t>
+          <t>Senior Backend Engineer(Golang),Software Supply Chain Security: Auth Infrastructure</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Immovara GmbH</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Korntal-Münchingen</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>berufserfahren</t>
-        </is>
-      </c>
+          <t>Remote, Americas; Remote, APAC; Remote, Canada</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>Remote, Software Development</t>
-        </is>
-      </c>
+      <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/immovara-gmbh/laravel-developer-ai-first-proptech-korntal-munchingen-471269</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8157520002</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1893,44 +1733,36 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Fullstack Softwareentwickler (m/w/d)</t>
+          <t>Senior Backend Engineer (RoR), AST: Secret Detection</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>TecFox GmbH</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Braunschweig</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>berufserfahren</t>
-        </is>
-      </c>
+          <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr"/>
       <c r="F31" s="4" t="inlineStr"/>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Software Development</t>
-        </is>
-      </c>
+      <c r="G31" s="4" t="inlineStr"/>
       <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/tecfox-gmbh/fullstack-softwareentwickler-braunschweig-405178</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8432262002</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1942,44 +1774,36 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Frontend Softwareentwickler (m/w/d)</t>
+          <t>Senior Backend Engineer (RoR/Go), SSCS: Pipeline Security</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>TecFox GmbH</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Braunschweig</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>berufserfahren</t>
-        </is>
-      </c>
+          <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr"/>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Remote, Software Development</t>
-        </is>
-      </c>
+      <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/tecfox-gmbh/frontend-softwareentwickler-braunschweig-341792</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8432221002</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1991,44 +1815,36 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Fullstack-Developer*in (m/w/d) Web &amp; AI Automation</t>
+          <t>Senior Backend Engineer (RoR), SSCS: Authorization</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>NeoBird Digital</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Nuremberg</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>berufserfahren</t>
-        </is>
-      </c>
+          <t>Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr"/>
       <c r="F33" s="4" t="inlineStr"/>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Software Development</t>
-        </is>
-      </c>
+      <c r="G33" s="4" t="inlineStr"/>
       <c r="H33" s="4" t="inlineStr"/>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/neobird-digital/fullstack-developerin-web-ai-automation-nuremberg-157752</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8457315002</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2040,40 +1856,36 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer / Backend &amp; Frontend - Bootstrapped SaaS Startup (m/w/d) remote in EU</t>
+          <t>Senior Backend Engineer (Ruby or Golang), Tenant Scale; Cells Infrastructure</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>DatAds</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Cologne</t>
+          <t>Remote, APAC; Remote, Canada; Remote, EMEA; Remote, US</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr"/>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>Remote, IT</t>
-        </is>
-      </c>
+      <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-bootstrapped-saas-startup-remote-in-eu-cologne-82307</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8437148002</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2085,40 +1897,36 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer / Rest APIs / Cloud / TailwindCSS / SaaS Startup (m/w/d) remote in EU</t>
+          <t>Senior Backend Engineer, SSCS: AI Governance</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>DatAds</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Cologne</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr"/>
       <c r="F35" s="4" t="inlineStr"/>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t>Remote, IT</t>
-        </is>
-      </c>
+      <c r="G35" s="4" t="inlineStr"/>
       <c r="H35" s="4" t="inlineStr"/>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-bootstrapped-saas-startup-remote-in-eu-cologne-38634</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480544002</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2130,40 +1938,36 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer / Node.js / TypeScript / React / Azure - AdTech SaaS Startup (m/w/d) remote</t>
+          <t>Senior Backend Engineer,  SSCS: Supply Chain</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>DatAds</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Cologne</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr"/>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>Remote, IT</t>
-        </is>
-      </c>
+      <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-adtech-saas-startup-remote-cologne-263746</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480580002</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2175,197 +1979,181 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Senior DevOps / Platform Engineer (f/m/x)</t>
+          <t>Senior Fullstack Engineer (TypeScript), AI Engineering: Editor Extensions</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>MAIA</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Leipzig</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
+          <t>Remote, APAC; Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US-Southeast</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr"/>
       <c r="F37" s="4" t="inlineStr"/>
-      <c r="G37" s="4" t="inlineStr">
-        <is>
-          <t>Remote, IT</t>
-        </is>
-      </c>
+      <c r="G37" s="4" t="inlineStr"/>
       <c r="H37" s="4" t="inlineStr"/>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/maia/senior-devops-platform-engineer-leipzig-388068</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8452278002</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer AI Infrastructure</t>
+          <t>Staff Backend Engineer, Analytics Instrumentation (Golang)</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Andromeda Cluster</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="2" t="inlineStr"/>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>design, training, technical, software, code, manager, financial, cloud, management, lead, senior, operations, reliability, go, health, engineer, engineering, linux, digital nomad</t>
-        </is>
-      </c>
+      <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-senior-site-reliability-engineer-ai-infrastructure-andromeda-cluster-1131375</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8508027002</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Senior Financial Analyst Digital Assets</t>
+          <t>Staff Backend Engineer, AST: Composition Analysis</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Exodus Movement Inc.</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote, Australia; Remote, Canada; Remote, India; Remote, Ireland; Remote, Israel; Remote, Japan; Remote, Netherlands; Remote, New Zealand; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr"/>
       <c r="F39" s="4" t="inlineStr"/>
-      <c r="G39" s="4" t="inlineStr">
-        <is>
-          <t>analyst, cryptocurrency, support, financial, investment, finance, senior, non tech</t>
-        </is>
-      </c>
+      <c r="G39" s="4" t="inlineStr"/>
       <c r="H39" s="4" t="inlineStr"/>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-senior-financial-analyst-digital-assets-exodus-movement-inc-1131374</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8478364002</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Front End Full Stack Developer</t>
+          <t>Staff Backend Engineer, Developer Experience</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Honor Foods</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Philadelphia, PA</t>
+          <t>Remote, Canada; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="2" t="inlineStr"/>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>developer, front-end, ui, code, web, operational, backend, digital nomad</t>
-        </is>
-      </c>
+      <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr"/>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-front-end-full-stack-developer-honor-foods-1131370</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8490477002</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Wing Assistant: Full-Stack Developer</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr"/>
+          <t>Staff Backend Engineer, Gitlab Delivery: Upgrades</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>GitLab</t>
+        </is>
+      </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr"/>
@@ -2374,35 +2162,39 @@
       <c r="H41" s="4" t="inlineStr"/>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/wing-assistant-full-stack-developer</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8463922002</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Qventus: Product Designer</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr"/>
+          <t>Staff Backend Engineer (Go), Continuous Delivery</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>GitLab</t>
+        </is>
+      </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr"/>
@@ -2411,35 +2203,39 @@
       <c r="H42" s="2" t="inlineStr"/>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/qventus-product-designer</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8488961002</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Socure: Senior Product Marketing Manager</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr"/>
+          <t>Staff Backend Engineer (Go), Software Supply Chain Security: Secrets Management</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>GitLab</t>
+        </is>
+      </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr"/>
@@ -2448,35 +2244,39 @@
       <c r="H43" s="4" t="inlineStr"/>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/socure-senior-product-marketing-manager</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8432235002</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Blueprint: Product Designer</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr"/>
+          <t>Staff Backend Engineer, Knowledge Graph (Rust)</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>GitLab</t>
+        </is>
+      </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
@@ -2485,35 +2285,39 @@
       <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/blueprint-product-designer</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481945002</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Interop Labs: Product Marketing Manager</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr"/>
+          <t>Staff Backend Engineer,  Software Supply Chain Security</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>GitLab</t>
+        </is>
+      </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr"/>
@@ -2522,39 +2326,39 @@
       <c r="H45" s="4" t="inlineStr"/>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/interop-labs-product-marketing-manager</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480559002</t>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Link</t>
+          <t>Staff Backend Engineer, SSCS: AI Governance</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Toronto, Remote in Canada</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
@@ -2568,34 +2372,34 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=6447175</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480531002</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Staff Backend (Python) Engineer, AI Engineering:Duo Chat</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Remote - Ontario, Canada</t>
+          <t>Remote, Americas; Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr"/>
@@ -2609,34 +2413,34 @@
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/6960833</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8450446002</t>
         </is>
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Full Stack Product Software Engineer</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Dropbox</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Remote - Poland</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr"/>
@@ -2650,10 +2454,2149 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>https://jobs.dropbox.com/listing/6449719?gh_jid=6449719</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Dry Ground AI</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Brazil, Colombia, Philippines</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>full_time</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>api, cloud, fullstack, python, AI/ML, automation, research, CI/CD, TensorFlow, spark, NLP, CMS, Pytorch, REST</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>$40- $60k</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Remotive</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/artificial-intelligence/ai-engineer-2089958</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Senior Independent AI Engineer / Architect</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>A.Team</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>Americas, Europe, Israel</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>contract</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>Software Development</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>go, UI/UX, wordpress, chat, apple, testing, catalyst</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>$120 - $170 /hour</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>Remotive</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/software-development/senior-independent-ai-engineer-architect-1919266</t>
+        </is>
+      </c>
+      <c r="K50" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Senior Independent Software Developer</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>A.Team</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Americas, Europe, Israel</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>contract</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Software Development</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>go, wordpress, chat, apple, testing, catalyst</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>$90 - $150 /hour</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Remotive</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/software-development/senior-independent-software-developer-1919265</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>Senior Full-stack React Developer</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>Lemon.io</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>Americas, Europe, Asia, Oceania</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>contract</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>Software Development</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>.Net, android, AWS, azure, backend, C, C#, C++, data science, fullstack, golang, ios, java, javascript, node.js, php, python, react, react js, ruby/rails, shopify, video, blockchain, AI/ML, react native, rust, unity, spring, data analysis, laravel, solidity, flask, Typescript , angular , GCP, data engineering, Symfony, startup, marketplace, next.js</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr"/>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>Remotive</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/software-development/senior-full-stack-react-developer-2088711</t>
+        </is>
+      </c>
+      <c r="K52" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Tech Lead Full-Stack Rails Engineer</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Mitre Media</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>USA, Canada, USA timezones</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>full_time</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Software Development</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>api, CSS, docker, elasticsearch, fullstack, html, javascript, kubernetes, postgresql, react, ror, ruby/rails, AI/ML, CAD, advertising, Redis, ES6, web applications, MySQL, NLP, fintech, Micro services, github, system architecture</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>$170k - $200k</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>Remotive</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/software-development/tech-lead-full-stack-rails-engineer-2069746</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>Senior Frontend Developer</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>Sanctuary Computer</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>LATAM, Asia</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>contract</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>Software Development</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>api, backend, CSS, ecommerce, frontend, fullstack, graphql, postgresql, redux, security, seo, shopify, open source, paas, product management, documentation, mentoring, Typescript , Redis, web applications, cypress, data visualization, firebase, IoT, engineering management, runtime, responsive, prismic, testing, next.js, CMS, jest, REST, web sockets, performance optimization</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>$80k - $120k</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>Remotive</t>
+        </is>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/software-development/senior-frontend-developer-2088707</t>
+        </is>
+      </c>
+      <c r="K54" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Fullstack Developer (US - ET)</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Chooose</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>full_time</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Software Development</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>api, azure, fullstack, python, react, saas, AI/ML, project management, documentation, Typescript , computer science, diversity, insurance</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>Remotive</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/software-development/fullstack-developer-us-et-2088706</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>Machine Learning Manager, Notifications Relevance</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr"/>
+      <c r="F56" s="4" t="inlineStr"/>
+      <c r="G56" s="4" t="inlineStr"/>
+      <c r="H56" s="4" t="inlineStr"/>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7846885</t>
+        </is>
+      </c>
+      <c r="K56" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Senior Staff ML Engineer, Search &amp; Recommendation</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr"/>
+      <c r="F57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr"/>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7833622</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>Remote - US</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr"/>
+      <c r="F58" s="4" t="inlineStr"/>
+      <c r="G58" s="4" t="inlineStr"/>
+      <c r="H58" s="4" t="inlineStr"/>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7059734</t>
+        </is>
+      </c>
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Remote - US</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr"/>
+      <c r="F59" s="2" t="inlineStr"/>
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7702644</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>Principal Machine Learning &amp; Data Engineer</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>Remote - US</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr"/>
+      <c r="F60" s="4" t="inlineStr"/>
+      <c r="G60" s="4" t="inlineStr"/>
+      <c r="H60" s="4" t="inlineStr"/>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7155492</t>
+        </is>
+      </c>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Principal, Product Manager - AI / LLM</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Remote - US</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr"/>
+      <c r="F61" s="2" t="inlineStr"/>
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr"/>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7619420</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>Product Engineer (Backend)</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>Remote - US</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr"/>
+      <c r="F62" s="4" t="inlineStr"/>
+      <c r="G62" s="4" t="inlineStr"/>
+      <c r="H62" s="4" t="inlineStr"/>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7671815</t>
+        </is>
+      </c>
+      <c r="K62" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Senior Manager, Machine Learning</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Remote - US</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr"/>
+      <c r="F63" s="2" t="inlineStr"/>
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr"/>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7066029</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>Staff Data Scientist</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>Remote - US</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr"/>
+      <c r="F64" s="4" t="inlineStr"/>
+      <c r="G64" s="4" t="inlineStr"/>
+      <c r="H64" s="4" t="inlineStr"/>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7821458</t>
+        </is>
+      </c>
+      <c r="K64" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Staff, Data Scientist (L4) GTM Data Science &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Remote - US</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr"/>
+      <c r="F65" s="2" t="inlineStr"/>
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr"/>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7851920</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>Staff Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>Remote - US</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr"/>
+      <c r="F66" s="4" t="inlineStr"/>
+      <c r="G66" s="4" t="inlineStr"/>
+      <c r="H66" s="4" t="inlineStr"/>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7061880</t>
+        </is>
+      </c>
+      <c r="K66" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Staff Machine Learning Engineer (L4)</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Remote - India</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr"/>
+      <c r="F67" s="2" t="inlineStr"/>
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr"/>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7520997</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>Senior Python Developer - Django (m/w/d)</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>sync.blue® GmbH</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>Haltern am See</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr"/>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Software Development</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr"/>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J68" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/syncblue-gmbh/senior-python-developer-django-haltern-am-see-16238</t>
+        </is>
+      </c>
+      <c r="K68" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Freelance Senior AI Product Manager</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>nexamind GmbH</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Freelance, professional / experienced</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr"/>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Remote, Product Management</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/nexamind-gmbh/freelance-senior-ai-product-manager-berlin-73613</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack-Entwickler:in React / TypeScript / .NET  100 % Remote, KI-First</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>yourMAIL GmbH</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr"/>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Software Development</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr"/>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/yourmail-gmbh/senior-full-stack-entwicklerin-react-typescript-net-100-remote-ki-first-berlin-21152</t>
+        </is>
+      </c>
+      <c r="K70" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Senior Frontend-Entwickler:in React / TypeScript, 100 % Remote, KI-First</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>yourMAIL GmbH</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr"/>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Remote, Software Development</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr"/>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/yourmail-gmbh/senior-frontend-entwicklerin-react-typescript-100-remote-ki-first-berlin-288218</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>Full-Stack Entwickler (m/w/d) - .NET 100% Remote</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>FNTIO</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>Frankfurt am Main</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr"/>
+      <c r="F72" s="4" t="inlineStr"/>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Consulting, Engineering</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr"/>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J72" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/fntio/full-stack-entwickler-net-100-remote-frankfurt-am-main-122380</t>
+        </is>
+      </c>
+      <c r="K72" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Phantasma Labs</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr"/>
+      <c r="F73" s="2" t="inlineStr"/>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Remote, Engineering</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr"/>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/phantasma-labs/machine-learning-engineer-berlin-303955</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>Technical Data Manager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>BMF Media Information Technology GmbH</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>Augsburg</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr"/>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Technical Documentation</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr"/>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J74" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/bmf-media-information-technology-gmbh/technical-data-manager-augsburg-42188</t>
+        </is>
+      </c>
+      <c r="K74" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Data Integration &amp; API Engineer m/w/d - Bi &amp; Data Automation</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>loyos bi GmbH</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Hamburg</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr"/>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Remote, Software Development</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr"/>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/loyos-bi-gmbh/data-integration-api-engineer-bi-data-automation-hamburg-66228</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>Coding Partners</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr"/>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Software Development</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr"/>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J76" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/coding-partners/senior-full-stack-engineer-berlin-391720</t>
+        </is>
+      </c>
+      <c r="K76" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Laravel Developer (m/w/d) - AI-First PropTech</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Immovara GmbH</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Korntal-Münchingen</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr"/>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>Remote, Software Development</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr"/>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/immovara-gmbh/laravel-developer-ai-first-proptech-korntal-munchingen-471269</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>Fullstack Softwareentwickler (m/w/d)</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>TecFox GmbH</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>Braunschweig</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr"/>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Software Development</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr"/>
+      <c r="I78" s="4" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J78" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/tecfox-gmbh/fullstack-softwareentwickler-braunschweig-405178</t>
+        </is>
+      </c>
+      <c r="K78" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Frontend Softwareentwickler (m/w/d)</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>TecFox GmbH</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Braunschweig</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr"/>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Remote, Software Development</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr"/>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/tecfox-gmbh/frontend-softwareentwickler-braunschweig-341792</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>Fullstack-Developer*in (m/w/d) Web &amp; AI Automation</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>NeoBird Digital</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>Nuremberg</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr"/>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Software Development</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr"/>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J80" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/neobird-digital/fullstack-developerin-web-ai-automation-nuremberg-157752</t>
+        </is>
+      </c>
+      <c r="K80" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Full-Stack Software Engineer / Backend &amp; Frontend - Bootstrapped SaaS Startup (m/w/d) remote in EU</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>DatAds</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Cologne</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr"/>
+      <c r="F81" s="2" t="inlineStr"/>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>Remote, IT</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr"/>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-bootstrapped-saas-startup-remote-in-eu-cologne-82307</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>Full-Stack Software Engineer / Rest APIs / Cloud / TailwindCSS / SaaS Startup (m/w/d) remote in EU</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>DatAds</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>Cologne</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr"/>
+      <c r="F82" s="4" t="inlineStr"/>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>Remote, IT</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr"/>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J82" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-bootstrapped-saas-startup-remote-in-eu-cologne-38634</t>
+        </is>
+      </c>
+      <c r="K82" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Full-Stack Software Engineer / Node.js / TypeScript / React / Azure - AdTech SaaS Startup (m/w/d) remote</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>DatAds</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Cologne</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr"/>
+      <c r="F83" s="2" t="inlineStr"/>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>Remote, IT</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr"/>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-adtech-saas-startup-remote-cologne-263746</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>Senior DevOps / Platform Engineer (f/m/x)</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>MAIA</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>Leipzig</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr"/>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>Remote, IT</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr"/>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J84" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/maia/senior-devops-platform-engineer-leipzig-388068</t>
+        </is>
+      </c>
+      <c r="K84" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer AI Infrastructure</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Andromeda Cluster</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr"/>
+      <c r="F85" s="2" t="inlineStr"/>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>design, training, technical, software, code, manager, financial, cloud, management, lead, senior, operations, reliability, go, health, engineer, engineering, linux, digital nomad</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr"/>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-senior-site-reliability-engineer-ai-infrastructure-andromeda-cluster-1131375</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>Senior Financial Analyst Digital Assets</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>Exodus Movement Inc.</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr"/>
+      <c r="F86" s="4" t="inlineStr"/>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t>analyst, cryptocurrency, support, financial, investment, finance, senior, non tech</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="inlineStr"/>
+      <c r="I86" s="4" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+      <c r="J86" s="5" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-senior-financial-analyst-digital-assets-exodus-movement-inc-1131374</t>
+        </is>
+      </c>
+      <c r="K86" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Front End Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Honor Foods</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr"/>
+      <c r="F87" s="2" t="inlineStr"/>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>developer, front-end, ui, code, web, operational, backend, digital nomad</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr"/>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-front-end-full-stack-developer-honor-foods-1131370</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>Wing Assistant: Full-Stack Developer</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr"/>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr"/>
+      <c r="F88" s="4" t="inlineStr"/>
+      <c r="G88" s="4" t="inlineStr"/>
+      <c r="H88" s="4" t="inlineStr"/>
+      <c r="I88" s="4" t="inlineStr">
+        <is>
+          <t>WeWorkRemotely</t>
+        </is>
+      </c>
+      <c r="J88" s="5" t="inlineStr">
+        <is>
+          <t>https://weworkremotely.com/remote-jobs/wing-assistant-full-stack-developer</t>
+        </is>
+      </c>
+      <c r="K88" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Qventus: Product Designer</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr"/>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr"/>
+      <c r="F89" s="2" t="inlineStr"/>
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr"/>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>WeWorkRemotely</t>
+        </is>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>https://weworkremotely.com/remote-jobs/qventus-product-designer</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>Socure: Senior Product Marketing Manager</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr"/>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr"/>
+      <c r="F90" s="4" t="inlineStr"/>
+      <c r="G90" s="4" t="inlineStr"/>
+      <c r="H90" s="4" t="inlineStr"/>
+      <c r="I90" s="4" t="inlineStr">
+        <is>
+          <t>WeWorkRemotely</t>
+        </is>
+      </c>
+      <c r="J90" s="5" t="inlineStr">
+        <is>
+          <t>https://weworkremotely.com/remote-jobs/socure-senior-product-marketing-manager</t>
+        </is>
+      </c>
+      <c r="K90" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Blueprint: Product Designer</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr"/>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr"/>
+      <c r="F91" s="2" t="inlineStr"/>
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr"/>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>WeWorkRemotely</t>
+        </is>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>https://weworkremotely.com/remote-jobs/blueprint-product-designer</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>Interop Labs: Product Marketing Manager</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr"/>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr"/>
+      <c r="F92" s="4" t="inlineStr"/>
+      <c r="G92" s="4" t="inlineStr"/>
+      <c r="H92" s="4" t="inlineStr"/>
+      <c r="I92" s="4" t="inlineStr">
+        <is>
+          <t>WeWorkRemotely</t>
+        </is>
+      </c>
+      <c r="J92" s="5" t="inlineStr">
+        <is>
+          <t>https://weworkremotely.com/remote-jobs/interop-labs-product-marketing-manager</t>
+        </is>
+      </c>
+      <c r="K92" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer, Link</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Remote in Canada</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr"/>
+      <c r="F93" s="2" t="inlineStr"/>
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr"/>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=6447175</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>Remote - Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr"/>
+      <c r="F94" s="4" t="inlineStr"/>
+      <c r="G94" s="4" t="inlineStr"/>
+      <c r="H94" s="4" t="inlineStr"/>
+      <c r="I94" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J94" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/6960833</t>
+        </is>
+      </c>
+      <c r="K94" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr"/>
+      <c r="F95" s="2" t="inlineStr"/>
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr"/>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
           <t>https://job-boards.greenhouse.io/reddit/jobs/6960831</t>
         </is>
       </c>
-      <c r="K48" s="2" t="inlineStr">
+      <c r="K95" s="2" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
@@ -2708,6 +4651,53 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId94"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/remote_jobs.xlsx
+++ b/remote_jobs.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K100"/>
+  <dimension ref="A1:K101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -523,215 +523,219 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Fullstack Developer (m/w/d) REMOTE //  UX / Python / Vue.js</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Lemon.io</t>
+          <t>Pont Connects e.K.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Americas, Europe, Asia, Oceania</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>full_time</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Devops</t>
-        </is>
-      </c>
+          <t>Düsseldorf</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>.Net, android, AWS, azure, C, C#, C++, data science, golang, ios, java, javascript, kubernetes, node.js, php, python, react, ruby/rails, shopify, sql, video, blockchain, AI/ML, automation, react native, rust, unity, spring, data analysis, laravel, solidity, flask, Typescript , terraform, angular , GCP, data engineering, Symfony, startup, marketplace, next.js</t>
+          <t>Remote, IT</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/pont-connects-ek/fullstack-developer-remote-ux-python-vuejs-dusseldorf-371903</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Lemon.io</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Americas, Europe, Asia, Oceania</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>full_time</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Devops</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>.Net, android, AWS, azure, C, C#, C++, data science, golang, ios, java, javascript, kubernetes, node.js, php, python, react, ruby/rails, shopify, sql, video, blockchain, AI/ML, automation, react native, rust, unity, spring, data analysis, laravel, solidity, flask, Typescript , terraform, angular , GCP, data engineering, Symfony, startup, marketplace, next.js</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
           <t>Remotive</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>https://remotive.com/remote-jobs/devops/senior-devops-engineer-2090002</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>2026-05-02</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>M&amp;A Research Analyst</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>EquiMatch GmbH</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>professional / experienced</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Remote, Mergers &amp; Acquisitions</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr"/>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>Arbeitnow</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>https://www.arbeitnow.com/jobs/companies/equimatch-gmbh/ma-research-analyst-berlin-498635</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>2026-05-02</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Xsolla: Full Stack Developer</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>WeWorkRemotely</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>https://weworkremotely.com/remote-jobs/xsolla-full-stack-developer</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>2026-05-02</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Dropbox: Staff Fullstack Product Software Engineer, Dash</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr"/>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr"/>
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>WeWorkRemotely</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>https://weworkremotely.com/remote-jobs/dropbox-staff-fullstack-product-software-engineer-dash</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Staff Machine Learning Engineer, Ranking and Personalization</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Reddit</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Remote - United States</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7848689</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>2026-05-02</t>
         </is>
@@ -745,1936 +749,1936 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Senior Rust Consultant / Engineer (m/w/d)</t>
+          <t>Staff Machine Learning Engineer, Ranking and Personalization</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Hackstack GmbH</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>berufserfahren</t>
-        </is>
-      </c>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Remote, Consulting, Engineering</t>
-        </is>
-      </c>
+      <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7848689</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Senior Rust Consultant / Engineer (m/w/d)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Hackstack GmbH</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Remote, Consulting, Engineering</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
           <t>Arbeitnow</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>https://www.arbeitnow.com/jobs/companies/hackstack-gmbh/senior-rust-consultant-engineer-munich-451602</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Applied AI Engineer - Remote</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>dexter health</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>Cologne</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>professional / experienced</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr"/>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>Remote, Development</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr"/>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr"/>
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>Arbeitnow</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>https://www.arbeitnow.com/jobs/companies/dexter-health/applied-ai-engineer-remote-cologne-2870</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Python Backend Engineer - Remote</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>dexter health</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Cologne</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>professional / experienced</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Remote, Development</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>Arbeitnow</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>https://www.arbeitnow.com/jobs/companies/dexter-health/python-backend-engineer-remote-cologne-34228</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>AI Engineer (LLM Products) - Remote</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>dexter health</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>Cologne</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>professional / experienced</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr"/>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr"/>
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>Remote, Development</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr"/>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>Arbeitnow</t>
         </is>
       </c>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>https://www.arbeitnow.com/jobs/companies/dexter-health/ai-engineer-llm-products-remote-cologne-236027</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Backend Python Engineer (APIs, Databases &amp; Cloud) - Remote</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>dexter health</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Cologne</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>professional / experienced</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Remote, Development</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>Arbeitnow</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>https://www.arbeitnow.com/jobs/companies/dexter-health/backend-python-engineer-apis-databases-cloud-remote-cologne-274767</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Toptal: QA Automation Engineer</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr"/>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr"/>
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr"/>
-      <c r="G12" s="4" t="inlineStr"/>
-      <c r="H12" s="4" t="inlineStr"/>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr"/>
+      <c r="G13" s="4" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr"/>
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>WeWorkRemotely</t>
         </is>
       </c>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>https://weworkremotely.com/remote-jobs/toptal-qa-automation-engineer-1</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Opensea: Staff Product Designer</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr"/>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="2" t="inlineStr"/>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>WeWorkRemotely</t>
         </is>
       </c>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>https://weworkremotely.com/remote-jobs/opensea-staff-product-designer</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Mutt Data: Devops</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr"/>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr"/>
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr"/>
-      <c r="G14" s="4" t="inlineStr"/>
-      <c r="H14" s="4" t="inlineStr"/>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr"/>
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>WeWorkRemotely</t>
         </is>
       </c>
-      <c r="J14" s="5" t="inlineStr">
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>https://weworkremotely.com/remote-jobs/mutt-data-devops</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Holywater: Full-Stack Developer</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr"/>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>WeWorkRemotely</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>https://weworkremotely.com/remote-jobs/holywater-full-stack-developer</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Qventus: DevOps Engineer</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr"/>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr"/>
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr"/>
-      <c r="G16" s="4" t="inlineStr"/>
-      <c r="H16" s="4" t="inlineStr"/>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr"/>
+      <c r="G17" s="4" t="inlineStr"/>
+      <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>WeWorkRemotely</t>
         </is>
       </c>
-      <c r="J16" s="5" t="inlineStr">
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>https://weworkremotely.com/remote-jobs/qventus-devops-engineer</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Visualis: Senior Full Stack Developer</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr"/>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr"/>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr"/>
-      <c r="F17" s="2" t="inlineStr"/>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr"/>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>WeWorkRemotely</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t>https://weworkremotely.com/remote-jobs/visualis-senior-full-stack-developer</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>AI Engineer</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Remote, Bangalore</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="4" t="inlineStr"/>
-      <c r="G18" s="4" t="inlineStr"/>
-      <c r="H18" s="4" t="inlineStr"/>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J18" s="5" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr"/>
+      <c r="G19" s="4" t="inlineStr"/>
+      <c r="H19" s="4" t="inlineStr"/>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8517564002</t>
         </is>
       </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Backend Engineer, Analytics Instrumentation (Golang)</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Remote, India</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr"/>
-      <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr"/>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8481922002</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Backend Engineer, Analytics Instrumentation (Golang)</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>Remote, India</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr"/>
-      <c r="F20" s="4" t="inlineStr"/>
-      <c r="G20" s="4" t="inlineStr"/>
-      <c r="H20" s="4" t="inlineStr"/>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J20" s="5" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr"/>
+      <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8481929002</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Backend Engineer, Knowledge Graph (Rust)</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Remote, Canada; Remote, US</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr"/>
-      <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8437754002</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Backend Engineer, Knowledge Graph (Rust)</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>Remote, India</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr"/>
-      <c r="F22" s="4" t="inlineStr"/>
-      <c r="G22" s="4" t="inlineStr"/>
-      <c r="H22" s="4" t="inlineStr"/>
-      <c r="I22" s="4" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J22" s="5" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr"/>
+      <c r="G23" s="4" t="inlineStr"/>
+      <c r="H23" s="4" t="inlineStr"/>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8481958002</t>
         </is>
       </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Intermediate Backend Engineer (C), Tenant Scale: Git</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Remote, India</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr"/>
-      <c r="F23" s="2" t="inlineStr"/>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr"/>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8497793002</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Intermediate Backend Engineer, Gitlab Delivery: Upgrades</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>Remote, India</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr"/>
-      <c r="F24" s="4" t="inlineStr"/>
-      <c r="G24" s="4" t="inlineStr"/>
-      <c r="H24" s="4" t="inlineStr"/>
-      <c r="I24" s="4" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J24" s="5" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr"/>
+      <c r="G25" s="4" t="inlineStr"/>
+      <c r="H25" s="4" t="inlineStr"/>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8463951002</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Intermediate Backend Engineer, SRM: Security Platform Management</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr"/>
-      <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr"/>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8443325002</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Intermediate Backend Engineer, SSCS: AI Governance</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>Remote, India</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr"/>
-      <c r="F26" s="4" t="inlineStr"/>
-      <c r="G26" s="4" t="inlineStr"/>
-      <c r="H26" s="4" t="inlineStr"/>
-      <c r="I26" s="4" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J26" s="5" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr"/>
+      <c r="G27" s="4" t="inlineStr"/>
+      <c r="H27" s="4" t="inlineStr"/>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8480551002</t>
         </is>
       </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Intermediate Backend Engineer,  SSCS: Supply Chain</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Remote, India</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr"/>
-      <c r="F27" s="2" t="inlineStr"/>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8480565002</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Senior AI Engineer</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>Remote, EMEA</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr"/>
-      <c r="F28" s="4" t="inlineStr"/>
-      <c r="G28" s="4" t="inlineStr"/>
-      <c r="H28" s="4" t="inlineStr"/>
-      <c r="I28" s="4" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J28" s="5" t="inlineStr">
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr"/>
+      <c r="G29" s="4" t="inlineStr"/>
+      <c r="H29" s="4" t="inlineStr"/>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8464072002</t>
         </is>
       </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Senior Backend Engineer (AI), Pipeline Execution</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US-Southeast</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr"/>
-      <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr"/>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8514945002</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Senior Backend Engineer, Analytics Instrumentation (Golang)</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>Remote, Canada; Remote, US</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr"/>
-      <c r="F30" s="4" t="inlineStr"/>
-      <c r="G30" s="4" t="inlineStr"/>
-      <c r="H30" s="4" t="inlineStr"/>
-      <c r="I30" s="4" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J30" s="5" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr"/>
+      <c r="G31" s="4" t="inlineStr"/>
+      <c r="H31" s="4" t="inlineStr"/>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8451512002</t>
         </is>
       </c>
-      <c r="K30" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Senior Backend Engineer (C), Tenant Scale: Git</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Remote, India</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr"/>
-      <c r="F31" s="2" t="inlineStr"/>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr"/>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8497791002</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>Senior Backend Engineer, Gitlab Delivery: Runway (Platform Engineering)</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>Remote, Australia; Remote, India; Remote, Ireland; Remote, Japan; Remote, Netherlands; Remote, Singapore; Remote, United Kingdom</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr"/>
-      <c r="F32" s="4" t="inlineStr"/>
-      <c r="G32" s="4" t="inlineStr"/>
-      <c r="H32" s="4" t="inlineStr"/>
-      <c r="I32" s="4" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J32" s="5" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr"/>
+      <c r="G33" s="4" t="inlineStr"/>
+      <c r="H33" s="4" t="inlineStr"/>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8324132002</t>
         </is>
       </c>
-      <c r="K32" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Senior Backend Engineer, Gitlab Delivery: Upgrades</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Remote, India</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr"/>
-      <c r="F33" s="2" t="inlineStr"/>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8463933002</t>
         </is>
       </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>Senior Backend Engineer(Go), Continuous Delivery</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>Remote, India</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr"/>
-      <c r="F34" s="4" t="inlineStr"/>
-      <c r="G34" s="4" t="inlineStr"/>
-      <c r="H34" s="4" t="inlineStr"/>
-      <c r="I34" s="4" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J34" s="5" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr"/>
+      <c r="G35" s="4" t="inlineStr"/>
+      <c r="H35" s="4" t="inlineStr"/>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8488966002</t>
         </is>
       </c>
-      <c r="K34" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>Senior Backend Engineer(Golang),Software Supply Chain Security: Auth Infrastructure</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Remote, Americas; Remote, APAC; Remote, Canada</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr"/>
-      <c r="F35" s="2" t="inlineStr"/>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr"/>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8157520002</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>Senior Backend Engineer (RoR), AST: Secret Detection</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr"/>
-      <c r="F36" s="4" t="inlineStr"/>
-      <c r="G36" s="4" t="inlineStr"/>
-      <c r="H36" s="4" t="inlineStr"/>
-      <c r="I36" s="4" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J36" s="5" t="inlineStr">
+      <c r="E37" s="4" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr"/>
+      <c r="G37" s="4" t="inlineStr"/>
+      <c r="H37" s="4" t="inlineStr"/>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8432262002</t>
         </is>
       </c>
-      <c r="K36" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>Senior Backend Engineer (RoR/Go), SSCS: Pipeline Security</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr"/>
-      <c r="F37" s="2" t="inlineStr"/>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr"/>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8432221002</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Senior Backend Engineer (RoR), SSCS: Authorization</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t>Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr"/>
-      <c r="F38" s="4" t="inlineStr"/>
-      <c r="G38" s="4" t="inlineStr"/>
-      <c r="H38" s="4" t="inlineStr"/>
-      <c r="I38" s="4" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J38" s="5" t="inlineStr">
+      <c r="E39" s="4" t="inlineStr"/>
+      <c r="F39" s="4" t="inlineStr"/>
+      <c r="G39" s="4" t="inlineStr"/>
+      <c r="H39" s="4" t="inlineStr"/>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8457315002</t>
         </is>
       </c>
-      <c r="K38" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>Senior Backend Engineer (Ruby or Golang), Tenant Scale; Cells Infrastructure</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Remote, APAC; Remote, Canada; Remote, EMEA; Remote, US</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr"/>
-      <c r="F39" s="2" t="inlineStr"/>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr"/>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr"/>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8437148002</t>
         </is>
       </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>Senior Backend Engineer, SSCS: AI Governance</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t>Remote, India</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr"/>
-      <c r="F40" s="4" t="inlineStr"/>
-      <c r="G40" s="4" t="inlineStr"/>
-      <c r="H40" s="4" t="inlineStr"/>
-      <c r="I40" s="4" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J40" s="5" t="inlineStr">
+      <c r="E41" s="4" t="inlineStr"/>
+      <c r="F41" s="4" t="inlineStr"/>
+      <c r="G41" s="4" t="inlineStr"/>
+      <c r="H41" s="4" t="inlineStr"/>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8480544002</t>
         </is>
       </c>
-      <c r="K40" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>Senior Backend Engineer,  SSCS: Supply Chain</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Remote, India</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr"/>
-      <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr"/>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8480580002</t>
         </is>
       </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>Senior Fullstack Engineer (TypeScript), AI Engineering: Editor Extensions</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="D43" s="4" t="inlineStr">
         <is>
           <t>Remote, APAC; Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US-Southeast</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr"/>
-      <c r="F42" s="4" t="inlineStr"/>
-      <c r="G42" s="4" t="inlineStr"/>
-      <c r="H42" s="4" t="inlineStr"/>
-      <c r="I42" s="4" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J42" s="5" t="inlineStr">
+      <c r="E43" s="4" t="inlineStr"/>
+      <c r="F43" s="4" t="inlineStr"/>
+      <c r="G43" s="4" t="inlineStr"/>
+      <c r="H43" s="4" t="inlineStr"/>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8452278002</t>
         </is>
       </c>
-      <c r="K42" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="K43" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>Staff Backend Engineer, Analytics Instrumentation (Golang)</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Remote, India</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr"/>
-      <c r="F43" s="2" t="inlineStr"/>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr"/>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8508027002</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>Staff Backend Engineer, AST: Composition Analysis</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="D45" s="4" t="inlineStr">
         <is>
           <t>Remote, Australia; Remote, Canada; Remote, India; Remote, Ireland; Remote, Israel; Remote, Japan; Remote, Netherlands; Remote, New Zealand; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr"/>
-      <c r="F44" s="4" t="inlineStr"/>
-      <c r="G44" s="4" t="inlineStr"/>
-      <c r="H44" s="4" t="inlineStr"/>
-      <c r="I44" s="4" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J44" s="5" t="inlineStr">
+      <c r="E45" s="4" t="inlineStr"/>
+      <c r="F45" s="4" t="inlineStr"/>
+      <c r="G45" s="4" t="inlineStr"/>
+      <c r="H45" s="4" t="inlineStr"/>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8478364002</t>
         </is>
       </c>
-      <c r="K44" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="K45" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>Staff Backend Engineer, Developer Experience</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Remote, Canada; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr"/>
-      <c r="F45" s="2" t="inlineStr"/>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr"/>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr"/>
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8490477002</t>
         </is>
       </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>Staff Backend Engineer, Gitlab Delivery: Upgrades</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr">
+      <c r="D47" s="4" t="inlineStr">
         <is>
           <t>Remote, India</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr"/>
-      <c r="F46" s="4" t="inlineStr"/>
-      <c r="G46" s="4" t="inlineStr"/>
-      <c r="H46" s="4" t="inlineStr"/>
-      <c r="I46" s="4" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J46" s="5" t="inlineStr">
+      <c r="E47" s="4" t="inlineStr"/>
+      <c r="F47" s="4" t="inlineStr"/>
+      <c r="G47" s="4" t="inlineStr"/>
+      <c r="H47" s="4" t="inlineStr"/>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8463922002</t>
         </is>
       </c>
-      <c r="K46" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="K47" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>Staff Backend Engineer (Go), Continuous Delivery</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Remote, India</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr"/>
-      <c r="F47" s="2" t="inlineStr"/>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr"/>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8488961002</t>
         </is>
       </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>Staff Backend Engineer (Go), Software Supply Chain Security: Secrets Management</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr">
+      <c r="D49" s="4" t="inlineStr">
         <is>
           <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr"/>
-      <c r="F48" s="4" t="inlineStr"/>
-      <c r="G48" s="4" t="inlineStr"/>
-      <c r="H48" s="4" t="inlineStr"/>
-      <c r="I48" s="4" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J48" s="5" t="inlineStr">
+      <c r="E49" s="4" t="inlineStr"/>
+      <c r="F49" s="4" t="inlineStr"/>
+      <c r="G49" s="4" t="inlineStr"/>
+      <c r="H49" s="4" t="inlineStr"/>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8432235002</t>
         </is>
       </c>
-      <c r="K48" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="K49" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>Staff Backend Engineer, Knowledge Graph (Rust)</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Remote, India</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr"/>
-      <c r="F49" s="2" t="inlineStr"/>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr"/>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8481945002</t>
         </is>
       </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>Staff Backend Engineer,  Software Supply Chain Security</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="D51" s="4" t="inlineStr">
         <is>
           <t>Remote, India</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr"/>
-      <c r="F50" s="4" t="inlineStr"/>
-      <c r="G50" s="4" t="inlineStr"/>
-      <c r="H50" s="4" t="inlineStr"/>
-      <c r="I50" s="4" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J50" s="5" t="inlineStr">
+      <c r="E51" s="4" t="inlineStr"/>
+      <c r="F51" s="4" t="inlineStr"/>
+      <c r="G51" s="4" t="inlineStr"/>
+      <c r="H51" s="4" t="inlineStr"/>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8480559002</t>
         </is>
       </c>
-      <c r="K50" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="K51" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>Staff Backend Engineer, SSCS: AI Governance</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Remote, India</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr"/>
-      <c r="F51" s="2" t="inlineStr"/>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr"/>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr"/>
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8480531002</t>
         </is>
       </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>Staff Backend (Python) Engineer, AI Engineering:Duo Chat</t>
         </is>
       </c>
-      <c r="C52" s="4" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D52" s="4" t="inlineStr">
+      <c r="D53" s="4" t="inlineStr">
         <is>
           <t>Remote, Americas; Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr"/>
-      <c r="F52" s="4" t="inlineStr"/>
-      <c r="G52" s="4" t="inlineStr"/>
-      <c r="H52" s="4" t="inlineStr"/>
-      <c r="I52" s="4" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J52" s="5" t="inlineStr">
+      <c r="E53" s="4" t="inlineStr"/>
+      <c r="F53" s="4" t="inlineStr"/>
+      <c r="G53" s="4" t="inlineStr"/>
+      <c r="H53" s="4" t="inlineStr"/>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8450446002</t>
         </is>
       </c>
-      <c r="K52" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Product Software Engineer</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Dropbox</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>Remote - Poland</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr"/>
-      <c r="F53" s="2" t="inlineStr"/>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr"/>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>https://jobs.dropbox.com/listing/6449719?gh_jid=6449719</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
+      <c r="K53" s="4" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
@@ -2688,2132 +2692,2173 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
+          <t>Senior Full Stack Product Software Engineer</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Dropbox</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Remote - Poland</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr"/>
+      <c r="F54" s="2" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.dropbox.com/listing/6449719?gh_jid=6449719</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>AI Engineer</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>Dry Ground AI</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Brazil, Colombia, Philippines</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>full_time</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Artificial Intelligence</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>api, cloud, fullstack, python, AI/ML, automation, research, CI/CD, TensorFlow, spark, NLP, CMS, Pytorch, REST</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>$40- $60k</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr">
         <is>
           <t>Remotive</t>
         </is>
       </c>
-      <c r="J54" s="3" t="inlineStr">
+      <c r="J55" s="3" t="inlineStr">
         <is>
           <t>https://remotive.com/remote-jobs/artificial-intelligence/ai-engineer-2089958</t>
         </is>
       </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>Senior Independent AI Engineer / Architect</t>
         </is>
       </c>
-      <c r="C55" s="4" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>A.Team</t>
         </is>
       </c>
-      <c r="D55" s="4" t="inlineStr">
+      <c r="D56" s="4" t="inlineStr">
         <is>
           <t>Americas, Europe, Israel</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr">
+      <c r="E56" s="4" t="inlineStr">
         <is>
           <t>contract</t>
         </is>
       </c>
-      <c r="F55" s="4" t="inlineStr">
+      <c r="F56" s="4" t="inlineStr">
         <is>
           <t>Software Development</t>
         </is>
       </c>
-      <c r="G55" s="4" t="inlineStr">
+      <c r="G56" s="4" t="inlineStr">
         <is>
           <t>go, UI/UX, wordpress, chat, apple, testing, catalyst</t>
         </is>
       </c>
-      <c r="H55" s="4" t="inlineStr">
+      <c r="H56" s="4" t="inlineStr">
         <is>
           <t>$120 - $170 /hour</t>
         </is>
       </c>
-      <c r="I55" s="4" t="inlineStr">
+      <c r="I56" s="4" t="inlineStr">
         <is>
           <t>Remotive</t>
         </is>
       </c>
-      <c r="J55" s="5" t="inlineStr">
+      <c r="J56" s="5" t="inlineStr">
         <is>
           <t>https://remotive.com/remote-jobs/software-development/senior-independent-ai-engineer-architect-1919266</t>
         </is>
       </c>
-      <c r="K55" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="K56" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>Senior Independent Software Developer</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>A.Team</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Americas, Europe, Israel</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>contract</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Software Development</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>go, wordpress, chat, apple, testing, catalyst</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>$90 - $150 /hour</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr">
         <is>
           <t>Remotive</t>
         </is>
       </c>
-      <c r="J56" s="3" t="inlineStr">
+      <c r="J57" s="3" t="inlineStr">
         <is>
           <t>https://remotive.com/remote-jobs/software-development/senior-independent-software-developer-1919265</t>
         </is>
       </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
         <is>
           <t>Senior Full-stack React Developer</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
+      <c r="C58" s="4" t="inlineStr">
         <is>
           <t>Lemon.io</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr">
+      <c r="D58" s="4" t="inlineStr">
         <is>
           <t>Americas, Europe, Asia, Oceania</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
+      <c r="E58" s="4" t="inlineStr">
         <is>
           <t>contract</t>
         </is>
       </c>
-      <c r="F57" s="4" t="inlineStr">
+      <c r="F58" s="4" t="inlineStr">
         <is>
           <t>Software Development</t>
         </is>
       </c>
-      <c r="G57" s="4" t="inlineStr">
+      <c r="G58" s="4" t="inlineStr">
         <is>
           <t>.Net, android, AWS, azure, backend, C, C#, C++, data science, fullstack, golang, ios, java, javascript, node.js, php, python, react, react js, ruby/rails, shopify, video, blockchain, AI/ML, react native, rust, unity, spring, data analysis, laravel, solidity, flask, Typescript , angular , GCP, data engineering, Symfony, startup, marketplace, next.js</t>
         </is>
       </c>
-      <c r="H57" s="4" t="inlineStr"/>
-      <c r="I57" s="4" t="inlineStr">
+      <c r="H58" s="4" t="inlineStr"/>
+      <c r="I58" s="4" t="inlineStr">
         <is>
           <t>Remotive</t>
         </is>
       </c>
-      <c r="J57" s="5" t="inlineStr">
+      <c r="J58" s="5" t="inlineStr">
         <is>
           <t>https://remotive.com/remote-jobs/software-development/senior-full-stack-react-developer-2088711</t>
         </is>
       </c>
-      <c r="K57" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>Tech Lead Full-Stack Rails Engineer</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>Mitre Media</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>USA, Canada, USA timezones</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>full_time</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Software Development</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>api, CSS, docker, elasticsearch, fullstack, html, javascript, kubernetes, postgresql, react, ror, ruby/rails, AI/ML, CAD, advertising, Redis, ES6, web applications, MySQL, NLP, fintech, Micro services, github, system architecture</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>$170k - $200k</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr">
         <is>
           <t>Remotive</t>
         </is>
       </c>
-      <c r="J58" s="3" t="inlineStr">
+      <c r="J59" s="3" t="inlineStr">
         <is>
           <t>https://remotive.com/remote-jobs/software-development/tech-lead-full-stack-rails-engineer-2069746</t>
         </is>
       </c>
-      <c r="K58" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>Senior Frontend Developer</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>Sanctuary Computer</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
+      <c r="D60" s="4" t="inlineStr">
         <is>
           <t>LATAM, Asia</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
+      <c r="E60" s="4" t="inlineStr">
         <is>
           <t>contract</t>
         </is>
       </c>
-      <c r="F59" s="4" t="inlineStr">
+      <c r="F60" s="4" t="inlineStr">
         <is>
           <t>Software Development</t>
         </is>
       </c>
-      <c r="G59" s="4" t="inlineStr">
+      <c r="G60" s="4" t="inlineStr">
         <is>
           <t>api, backend, CSS, ecommerce, frontend, fullstack, graphql, postgresql, redux, security, seo, shopify, open source, paas, product management, documentation, mentoring, Typescript , Redis, web applications, cypress, data visualization, firebase, IoT, engineering management, runtime, responsive, prismic, testing, next.js, CMS, jest, REST, web sockets, performance optimization</t>
         </is>
       </c>
-      <c r="H59" s="4" t="inlineStr">
+      <c r="H60" s="4" t="inlineStr">
         <is>
           <t>$80k - $120k</t>
         </is>
       </c>
-      <c r="I59" s="4" t="inlineStr">
+      <c r="I60" s="4" t="inlineStr">
         <is>
           <t>Remotive</t>
         </is>
       </c>
-      <c r="J59" s="5" t="inlineStr">
+      <c r="J60" s="5" t="inlineStr">
         <is>
           <t>https://remotive.com/remote-jobs/software-development/senior-frontend-developer-2088707</t>
         </is>
       </c>
-      <c r="K59" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>Fullstack Developer (US - ET)</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>Chooose</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>full_time</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Software Development</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>api, azure, fullstack, python, react, saas, AI/ML, project management, documentation, Typescript , computer science, diversity, insurance</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr"/>
-      <c r="I60" s="2" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr"/>
+      <c r="I61" s="2" t="inlineStr">
         <is>
           <t>Remotive</t>
         </is>
       </c>
-      <c r="J60" s="3" t="inlineStr">
+      <c r="J61" s="3" t="inlineStr">
         <is>
           <t>https://remotive.com/remote-jobs/software-development/fullstack-developer-us-et-2088706</t>
         </is>
       </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
         <is>
           <t>Machine Learning Manager, Notifications Relevance</t>
         </is>
       </c>
-      <c r="C61" s="4" t="inlineStr">
+      <c r="C62" s="4" t="inlineStr">
         <is>
           <t>Reddit</t>
         </is>
       </c>
-      <c r="D61" s="4" t="inlineStr">
+      <c r="D62" s="4" t="inlineStr">
         <is>
           <t>Remote - United States</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr"/>
-      <c r="F61" s="4" t="inlineStr"/>
-      <c r="G61" s="4" t="inlineStr"/>
-      <c r="H61" s="4" t="inlineStr"/>
-      <c r="I61" s="4" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J61" s="5" t="inlineStr">
+      <c r="E62" s="4" t="inlineStr"/>
+      <c r="F62" s="4" t="inlineStr"/>
+      <c r="G62" s="4" t="inlineStr"/>
+      <c r="H62" s="4" t="inlineStr"/>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J62" s="5" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/reddit/jobs/7846885</t>
         </is>
       </c>
-      <c r="K61" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="K62" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>Senior Staff ML Engineer, Search &amp; Recommendation</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>Reddit</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Remote - United States</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr"/>
-      <c r="F62" s="2" t="inlineStr"/>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr"/>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr"/>
+      <c r="F63" s="2" t="inlineStr"/>
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr"/>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/reddit/jobs/7833622</t>
         </is>
       </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t>Machine Learning Engineer</t>
         </is>
       </c>
-      <c r="C63" s="4" t="inlineStr">
+      <c r="C64" s="4" t="inlineStr">
         <is>
           <t>Twilio</t>
         </is>
       </c>
-      <c r="D63" s="4" t="inlineStr">
+      <c r="D64" s="4" t="inlineStr">
         <is>
           <t>Remote - US</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr"/>
-      <c r="F63" s="4" t="inlineStr"/>
-      <c r="G63" s="4" t="inlineStr"/>
-      <c r="H63" s="4" t="inlineStr"/>
-      <c r="I63" s="4" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J63" s="5" t="inlineStr">
+      <c r="E64" s="4" t="inlineStr"/>
+      <c r="F64" s="4" t="inlineStr"/>
+      <c r="G64" s="4" t="inlineStr"/>
+      <c r="H64" s="4" t="inlineStr"/>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J64" s="5" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/twilio/jobs/7059734</t>
         </is>
       </c>
-      <c r="K63" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="K64" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>Machine Learning Engineer</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>Twilio</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Remote - US</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr"/>
-      <c r="F64" s="2" t="inlineStr"/>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr"/>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr"/>
+      <c r="F65" s="2" t="inlineStr"/>
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr"/>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/twilio/jobs/7702644</t>
         </is>
       </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
         <is>
           <t>Principal Machine Learning &amp; Data Engineer</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
+      <c r="C66" s="4" t="inlineStr">
         <is>
           <t>Twilio</t>
         </is>
       </c>
-      <c r="D65" s="4" t="inlineStr">
+      <c r="D66" s="4" t="inlineStr">
         <is>
           <t>Remote - US</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr"/>
-      <c r="F65" s="4" t="inlineStr"/>
-      <c r="G65" s="4" t="inlineStr"/>
-      <c r="H65" s="4" t="inlineStr"/>
-      <c r="I65" s="4" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J65" s="5" t="inlineStr">
+      <c r="E66" s="4" t="inlineStr"/>
+      <c r="F66" s="4" t="inlineStr"/>
+      <c r="G66" s="4" t="inlineStr"/>
+      <c r="H66" s="4" t="inlineStr"/>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J66" s="5" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/twilio/jobs/7155492</t>
         </is>
       </c>
-      <c r="K65" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="K66" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>Principal, Product Manager - AI / LLM</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
         <is>
           <t>Twilio</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Remote - US</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr"/>
-      <c r="F66" s="2" t="inlineStr"/>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr"/>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr"/>
+      <c r="F67" s="2" t="inlineStr"/>
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr"/>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/twilio/jobs/7619420</t>
         </is>
       </c>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B67" s="4" t="inlineStr">
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
         <is>
           <t>Product Engineer (Backend)</t>
         </is>
       </c>
-      <c r="C67" s="4" t="inlineStr">
+      <c r="C68" s="4" t="inlineStr">
         <is>
           <t>Twilio</t>
         </is>
       </c>
-      <c r="D67" s="4" t="inlineStr">
+      <c r="D68" s="4" t="inlineStr">
         <is>
           <t>Remote - US</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr"/>
-      <c r="F67" s="4" t="inlineStr"/>
-      <c r="G67" s="4" t="inlineStr"/>
-      <c r="H67" s="4" t="inlineStr"/>
-      <c r="I67" s="4" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J67" s="5" t="inlineStr">
+      <c r="E68" s="4" t="inlineStr"/>
+      <c r="F68" s="4" t="inlineStr"/>
+      <c r="G68" s="4" t="inlineStr"/>
+      <c r="H68" s="4" t="inlineStr"/>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J68" s="5" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/twilio/jobs/7671815</t>
         </is>
       </c>
-      <c r="K67" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="K68" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>Senior Manager, Machine Learning</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>Twilio</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Remote - US</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr"/>
-      <c r="F68" s="2" t="inlineStr"/>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr"/>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr"/>
+      <c r="F69" s="2" t="inlineStr"/>
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/twilio/jobs/7066029</t>
         </is>
       </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="inlineStr">
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
         <is>
           <t>Staff Data Scientist</t>
         </is>
       </c>
-      <c r="C69" s="4" t="inlineStr">
+      <c r="C70" s="4" t="inlineStr">
         <is>
           <t>Twilio</t>
         </is>
       </c>
-      <c r="D69" s="4" t="inlineStr">
+      <c r="D70" s="4" t="inlineStr">
         <is>
           <t>Remote - US</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr"/>
-      <c r="F69" s="4" t="inlineStr"/>
-      <c r="G69" s="4" t="inlineStr"/>
-      <c r="H69" s="4" t="inlineStr"/>
-      <c r="I69" s="4" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J69" s="5" t="inlineStr">
+      <c r="E70" s="4" t="inlineStr"/>
+      <c r="F70" s="4" t="inlineStr"/>
+      <c r="G70" s="4" t="inlineStr"/>
+      <c r="H70" s="4" t="inlineStr"/>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J70" s="5" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/twilio/jobs/7821458</t>
         </is>
       </c>
-      <c r="K69" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="K70" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>Staff, Data Scientist (L4) GTM Data Science &amp; Analytics</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>Twilio</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Remote - US</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr"/>
-      <c r="F70" s="2" t="inlineStr"/>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr"/>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr"/>
+      <c r="F71" s="2" t="inlineStr"/>
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr"/>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/twilio/jobs/7851920</t>
         </is>
       </c>
-      <c r="K70" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B71" s="4" t="inlineStr">
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
         <is>
           <t>Staff Machine Learning Engineer</t>
         </is>
       </c>
-      <c r="C71" s="4" t="inlineStr">
+      <c r="C72" s="4" t="inlineStr">
         <is>
           <t>Twilio</t>
         </is>
       </c>
-      <c r="D71" s="4" t="inlineStr">
+      <c r="D72" s="4" t="inlineStr">
         <is>
           <t>Remote - US</t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr"/>
-      <c r="F71" s="4" t="inlineStr"/>
-      <c r="G71" s="4" t="inlineStr"/>
-      <c r="H71" s="4" t="inlineStr"/>
-      <c r="I71" s="4" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J71" s="5" t="inlineStr">
+      <c r="E72" s="4" t="inlineStr"/>
+      <c r="F72" s="4" t="inlineStr"/>
+      <c r="G72" s="4" t="inlineStr"/>
+      <c r="H72" s="4" t="inlineStr"/>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J72" s="5" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/twilio/jobs/7061880</t>
         </is>
       </c>
-      <c r="K71" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="K72" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>Staff Machine Learning Engineer (L4)</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
         <is>
           <t>Twilio</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Remote - India</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr"/>
-      <c r="F72" s="2" t="inlineStr"/>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr"/>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr"/>
+      <c r="F73" s="2" t="inlineStr"/>
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr"/>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/twilio/jobs/7520997</t>
         </is>
       </c>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
         <is>
           <t>Senior Python Developer - Django (m/w/d)</t>
         </is>
       </c>
-      <c r="C73" s="4" t="inlineStr">
+      <c r="C74" s="4" t="inlineStr">
         <is>
           <t>sync.blue® GmbH</t>
         </is>
       </c>
-      <c r="D73" s="4" t="inlineStr">
+      <c r="D74" s="4" t="inlineStr">
         <is>
           <t>Haltern am See</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr">
+      <c r="E74" s="4" t="inlineStr">
         <is>
           <t>berufserfahren</t>
         </is>
       </c>
-      <c r="F73" s="4" t="inlineStr"/>
-      <c r="G73" s="4" t="inlineStr">
+      <c r="F74" s="4" t="inlineStr"/>
+      <c r="G74" s="4" t="inlineStr">
         <is>
           <t>Remote, Software Development</t>
         </is>
       </c>
-      <c r="H73" s="4" t="inlineStr"/>
-      <c r="I73" s="4" t="inlineStr">
+      <c r="H74" s="4" t="inlineStr"/>
+      <c r="I74" s="4" t="inlineStr">
         <is>
           <t>Arbeitnow</t>
         </is>
       </c>
-      <c r="J73" s="5" t="inlineStr">
+      <c r="J74" s="5" t="inlineStr">
         <is>
           <t>https://www.arbeitnow.com/jobs/companies/syncblue-gmbh/senior-python-developer-django-haltern-am-see-16238</t>
         </is>
       </c>
-      <c r="K73" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="K74" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>Freelance Senior AI Product Manager</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
         <is>
           <t>nexamind GmbH</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Freelance, professional / experienced</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr"/>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr"/>
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>Remote, Product Management</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr"/>
-      <c r="I74" s="2" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr"/>
+      <c r="I75" s="2" t="inlineStr">
         <is>
           <t>Arbeitnow</t>
         </is>
       </c>
-      <c r="J74" s="3" t="inlineStr">
+      <c r="J75" s="3" t="inlineStr">
         <is>
           <t>https://www.arbeitnow.com/jobs/companies/nexamind-gmbh/freelance-senior-ai-product-manager-berlin-73613</t>
         </is>
       </c>
-      <c r="K74" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B75" s="4" t="inlineStr">
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
         <is>
           <t>Senior Full-Stack-Entwickler:in React / TypeScript / .NET  100 % Remote, KI-First</t>
         </is>
       </c>
-      <c r="C75" s="4" t="inlineStr">
+      <c r="C76" s="4" t="inlineStr">
         <is>
           <t>yourMAIL GmbH</t>
         </is>
       </c>
-      <c r="D75" s="4" t="inlineStr">
+      <c r="D76" s="4" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr">
+      <c r="E76" s="4" t="inlineStr">
         <is>
           <t>berufserfahren</t>
         </is>
       </c>
-      <c r="F75" s="4" t="inlineStr"/>
-      <c r="G75" s="4" t="inlineStr">
+      <c r="F76" s="4" t="inlineStr"/>
+      <c r="G76" s="4" t="inlineStr">
         <is>
           <t>Remote, Software Development</t>
         </is>
       </c>
-      <c r="H75" s="4" t="inlineStr"/>
-      <c r="I75" s="4" t="inlineStr">
+      <c r="H76" s="4" t="inlineStr"/>
+      <c r="I76" s="4" t="inlineStr">
         <is>
           <t>Arbeitnow</t>
         </is>
       </c>
-      <c r="J75" s="5" t="inlineStr">
+      <c r="J76" s="5" t="inlineStr">
         <is>
           <t>https://www.arbeitnow.com/jobs/companies/yourmail-gmbh/senior-full-stack-entwicklerin-react-typescript-net-100-remote-ki-first-berlin-21152</t>
         </is>
       </c>
-      <c r="K75" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="K76" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>Senior Frontend-Entwickler:in React / TypeScript, 100 % Remote, KI-First</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
         <is>
           <t>yourMAIL GmbH</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>berufserfahren</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr"/>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr"/>
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>Remote, Software Development</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr"/>
-      <c r="I76" s="2" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr"/>
+      <c r="I77" s="2" t="inlineStr">
         <is>
           <t>Arbeitnow</t>
         </is>
       </c>
-      <c r="J76" s="3" t="inlineStr">
+      <c r="J77" s="3" t="inlineStr">
         <is>
           <t>https://www.arbeitnow.com/jobs/companies/yourmail-gmbh/senior-frontend-entwicklerin-react-typescript-100-remote-ki-first-berlin-288218</t>
         </is>
       </c>
-      <c r="K76" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B77" s="4" t="inlineStr">
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
         <is>
           <t>Full-Stack Entwickler (m/w/d) - .NET 100% Remote</t>
         </is>
       </c>
-      <c r="C77" s="4" t="inlineStr">
+      <c r="C78" s="4" t="inlineStr">
         <is>
           <t>FNTIO</t>
         </is>
       </c>
-      <c r="D77" s="4" t="inlineStr">
+      <c r="D78" s="4" t="inlineStr">
         <is>
           <t>Frankfurt am Main</t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr"/>
-      <c r="F77" s="4" t="inlineStr"/>
-      <c r="G77" s="4" t="inlineStr">
+      <c r="E78" s="4" t="inlineStr"/>
+      <c r="F78" s="4" t="inlineStr"/>
+      <c r="G78" s="4" t="inlineStr">
         <is>
           <t>Remote, Consulting, Engineering</t>
         </is>
       </c>
-      <c r="H77" s="4" t="inlineStr"/>
-      <c r="I77" s="4" t="inlineStr">
+      <c r="H78" s="4" t="inlineStr"/>
+      <c r="I78" s="4" t="inlineStr">
         <is>
           <t>Arbeitnow</t>
         </is>
       </c>
-      <c r="J77" s="5" t="inlineStr">
+      <c r="J78" s="5" t="inlineStr">
         <is>
           <t>https://www.arbeitnow.com/jobs/companies/fntio/full-stack-entwickler-net-100-remote-frankfurt-am-main-122380</t>
         </is>
       </c>
-      <c r="K77" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="K78" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>Machine Learning Engineer</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
         <is>
           <t>Phantasma Labs</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr"/>
-      <c r="F78" s="2" t="inlineStr"/>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr"/>
+      <c r="F79" s="2" t="inlineStr"/>
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>Remote, Engineering</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr"/>
-      <c r="I78" s="2" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr"/>
+      <c r="I79" s="2" t="inlineStr">
         <is>
           <t>Arbeitnow</t>
         </is>
       </c>
-      <c r="J78" s="3" t="inlineStr">
+      <c r="J79" s="3" t="inlineStr">
         <is>
           <t>https://www.arbeitnow.com/jobs/companies/phantasma-labs/machine-learning-engineer-berlin-303955</t>
         </is>
       </c>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B79" s="4" t="inlineStr">
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
         <is>
           <t>Technical Data Manager (m/w/d)</t>
         </is>
       </c>
-      <c r="C79" s="4" t="inlineStr">
+      <c r="C80" s="4" t="inlineStr">
         <is>
           <t>BMF Media Information Technology GmbH</t>
         </is>
       </c>
-      <c r="D79" s="4" t="inlineStr">
+      <c r="D80" s="4" t="inlineStr">
         <is>
           <t>Augsburg</t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr">
+      <c r="E80" s="4" t="inlineStr">
         <is>
           <t>berufserfahren</t>
         </is>
       </c>
-      <c r="F79" s="4" t="inlineStr"/>
-      <c r="G79" s="4" t="inlineStr">
+      <c r="F80" s="4" t="inlineStr"/>
+      <c r="G80" s="4" t="inlineStr">
         <is>
           <t>Remote, Technical Documentation</t>
         </is>
       </c>
-      <c r="H79" s="4" t="inlineStr"/>
-      <c r="I79" s="4" t="inlineStr">
+      <c r="H80" s="4" t="inlineStr"/>
+      <c r="I80" s="4" t="inlineStr">
         <is>
           <t>Arbeitnow</t>
         </is>
       </c>
-      <c r="J79" s="5" t="inlineStr">
+      <c r="J80" s="5" t="inlineStr">
         <is>
           <t>https://www.arbeitnow.com/jobs/companies/bmf-media-information-technology-gmbh/technical-data-manager-augsburg-42188</t>
         </is>
       </c>
-      <c r="K79" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="K80" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>Data Integration &amp; API Engineer m/w/d - Bi &amp; Data Automation</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
         <is>
           <t>loyos bi GmbH</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Hamburg</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>berufserfahren</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr"/>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr"/>
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>Remote, Software Development</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr"/>
-      <c r="I80" s="2" t="inlineStr">
+      <c r="H81" s="2" t="inlineStr"/>
+      <c r="I81" s="2" t="inlineStr">
         <is>
           <t>Arbeitnow</t>
         </is>
       </c>
-      <c r="J80" s="3" t="inlineStr">
+      <c r="J81" s="3" t="inlineStr">
         <is>
           <t>https://www.arbeitnow.com/jobs/companies/loyos-bi-gmbh/data-integration-api-engineer-bi-data-automation-hamburg-66228</t>
         </is>
       </c>
-      <c r="K80" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B81" s="4" t="inlineStr">
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
         <is>
           <t>Senior Full Stack Engineer</t>
         </is>
       </c>
-      <c r="C81" s="4" t="inlineStr">
+      <c r="C82" s="4" t="inlineStr">
         <is>
           <t>Coding Partners</t>
         </is>
       </c>
-      <c r="D81" s="4" t="inlineStr">
+      <c r="D82" s="4" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr">
+      <c r="E82" s="4" t="inlineStr">
         <is>
           <t>professional / experienced</t>
         </is>
       </c>
-      <c r="F81" s="4" t="inlineStr"/>
-      <c r="G81" s="4" t="inlineStr">
+      <c r="F82" s="4" t="inlineStr"/>
+      <c r="G82" s="4" t="inlineStr">
         <is>
           <t>Remote, Software Development</t>
         </is>
       </c>
-      <c r="H81" s="4" t="inlineStr"/>
-      <c r="I81" s="4" t="inlineStr">
+      <c r="H82" s="4" t="inlineStr"/>
+      <c r="I82" s="4" t="inlineStr">
         <is>
           <t>Arbeitnow</t>
         </is>
       </c>
-      <c r="J81" s="5" t="inlineStr">
+      <c r="J82" s="5" t="inlineStr">
         <is>
           <t>https://www.arbeitnow.com/jobs/companies/coding-partners/senior-full-stack-engineer-berlin-391720</t>
         </is>
       </c>
-      <c r="K81" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="K82" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>Laravel Developer (m/w/d) - AI-First PropTech</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
         <is>
           <t>Immovara GmbH</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Korntal-Münchingen</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>berufserfahren</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr"/>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr"/>
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>Remote, Software Development</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr"/>
-      <c r="I82" s="2" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr"/>
+      <c r="I83" s="2" t="inlineStr">
         <is>
           <t>Arbeitnow</t>
         </is>
       </c>
-      <c r="J82" s="3" t="inlineStr">
+      <c r="J83" s="3" t="inlineStr">
         <is>
           <t>https://www.arbeitnow.com/jobs/companies/immovara-gmbh/laravel-developer-ai-first-proptech-korntal-munchingen-471269</t>
         </is>
       </c>
-      <c r="K82" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B83" s="4" t="inlineStr">
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
         <is>
           <t>Fullstack Softwareentwickler (m/w/d)</t>
         </is>
       </c>
-      <c r="C83" s="4" t="inlineStr">
+      <c r="C84" s="4" t="inlineStr">
         <is>
           <t>TecFox GmbH</t>
         </is>
       </c>
-      <c r="D83" s="4" t="inlineStr">
+      <c r="D84" s="4" t="inlineStr">
         <is>
           <t>Braunschweig</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr">
+      <c r="E84" s="4" t="inlineStr">
         <is>
           <t>berufserfahren</t>
         </is>
       </c>
-      <c r="F83" s="4" t="inlineStr"/>
-      <c r="G83" s="4" t="inlineStr">
+      <c r="F84" s="4" t="inlineStr"/>
+      <c r="G84" s="4" t="inlineStr">
         <is>
           <t>Remote, Software Development</t>
         </is>
       </c>
-      <c r="H83" s="4" t="inlineStr"/>
-      <c r="I83" s="4" t="inlineStr">
+      <c r="H84" s="4" t="inlineStr"/>
+      <c r="I84" s="4" t="inlineStr">
         <is>
           <t>Arbeitnow</t>
         </is>
       </c>
-      <c r="J83" s="5" t="inlineStr">
+      <c r="J84" s="5" t="inlineStr">
         <is>
           <t>https://www.arbeitnow.com/jobs/companies/tecfox-gmbh/fullstack-softwareentwickler-braunschweig-405178</t>
         </is>
       </c>
-      <c r="K83" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="K84" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>Frontend Softwareentwickler (m/w/d)</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
         <is>
           <t>TecFox GmbH</t>
         </is>
       </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Braunschweig</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>berufserfahren</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr"/>
-      <c r="G84" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr"/>
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>Remote, Software Development</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr"/>
-      <c r="I84" s="2" t="inlineStr">
+      <c r="H85" s="2" t="inlineStr"/>
+      <c r="I85" s="2" t="inlineStr">
         <is>
           <t>Arbeitnow</t>
         </is>
       </c>
-      <c r="J84" s="3" t="inlineStr">
+      <c r="J85" s="3" t="inlineStr">
         <is>
           <t>https://www.arbeitnow.com/jobs/companies/tecfox-gmbh/frontend-softwareentwickler-braunschweig-341792</t>
         </is>
       </c>
-      <c r="K84" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B85" s="4" t="inlineStr">
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
         <is>
           <t>Fullstack-Developer*in (m/w/d) Web &amp; AI Automation</t>
         </is>
       </c>
-      <c r="C85" s="4" t="inlineStr">
+      <c r="C86" s="4" t="inlineStr">
         <is>
           <t>NeoBird Digital</t>
         </is>
       </c>
-      <c r="D85" s="4" t="inlineStr">
+      <c r="D86" s="4" t="inlineStr">
         <is>
           <t>Nuremberg</t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr">
+      <c r="E86" s="4" t="inlineStr">
         <is>
           <t>berufserfahren</t>
         </is>
       </c>
-      <c r="F85" s="4" t="inlineStr"/>
-      <c r="G85" s="4" t="inlineStr">
+      <c r="F86" s="4" t="inlineStr"/>
+      <c r="G86" s="4" t="inlineStr">
         <is>
           <t>Remote, Software Development</t>
         </is>
       </c>
-      <c r="H85" s="4" t="inlineStr"/>
-      <c r="I85" s="4" t="inlineStr">
+      <c r="H86" s="4" t="inlineStr"/>
+      <c r="I86" s="4" t="inlineStr">
         <is>
           <t>Arbeitnow</t>
         </is>
       </c>
-      <c r="J85" s="5" t="inlineStr">
+      <c r="J86" s="5" t="inlineStr">
         <is>
           <t>https://www.arbeitnow.com/jobs/companies/neobird-digital/fullstack-developerin-web-ai-automation-nuremberg-157752</t>
         </is>
       </c>
-      <c r="K85" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="K86" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>Full-Stack Software Engineer / Backend &amp; Frontend - Bootstrapped SaaS Startup (m/w/d) remote in EU</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
         <is>
           <t>DatAds</t>
         </is>
       </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Cologne</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr"/>
-      <c r="F86" s="2" t="inlineStr"/>
-      <c r="G86" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr"/>
+      <c r="F87" s="2" t="inlineStr"/>
+      <c r="G87" s="2" t="inlineStr">
         <is>
           <t>Remote, IT</t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr"/>
-      <c r="I86" s="2" t="inlineStr">
+      <c r="H87" s="2" t="inlineStr"/>
+      <c r="I87" s="2" t="inlineStr">
         <is>
           <t>Arbeitnow</t>
         </is>
       </c>
-      <c r="J86" s="3" t="inlineStr">
+      <c r="J87" s="3" t="inlineStr">
         <is>
           <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-bootstrapped-saas-startup-remote-in-eu-cologne-82307</t>
         </is>
       </c>
-      <c r="K86" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B87" s="4" t="inlineStr">
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
         <is>
           <t>Full-Stack Software Engineer / Rest APIs / Cloud / TailwindCSS / SaaS Startup (m/w/d) remote in EU</t>
         </is>
       </c>
-      <c r="C87" s="4" t="inlineStr">
+      <c r="C88" s="4" t="inlineStr">
         <is>
           <t>DatAds</t>
         </is>
       </c>
-      <c r="D87" s="4" t="inlineStr">
+      <c r="D88" s="4" t="inlineStr">
         <is>
           <t>Cologne</t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr"/>
-      <c r="F87" s="4" t="inlineStr"/>
-      <c r="G87" s="4" t="inlineStr">
+      <c r="E88" s="4" t="inlineStr"/>
+      <c r="F88" s="4" t="inlineStr"/>
+      <c r="G88" s="4" t="inlineStr">
         <is>
           <t>Remote, IT</t>
         </is>
       </c>
-      <c r="H87" s="4" t="inlineStr"/>
-      <c r="I87" s="4" t="inlineStr">
+      <c r="H88" s="4" t="inlineStr"/>
+      <c r="I88" s="4" t="inlineStr">
         <is>
           <t>Arbeitnow</t>
         </is>
       </c>
-      <c r="J87" s="5" t="inlineStr">
+      <c r="J88" s="5" t="inlineStr">
         <is>
           <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-bootstrapped-saas-startup-remote-in-eu-cologne-38634</t>
         </is>
       </c>
-      <c r="K87" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="K88" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>Full-Stack Software Engineer / Node.js / TypeScript / React / Azure - AdTech SaaS Startup (m/w/d) remote</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
         <is>
           <t>DatAds</t>
         </is>
       </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Cologne</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr"/>
-      <c r="F88" s="2" t="inlineStr"/>
-      <c r="G88" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr"/>
+      <c r="F89" s="2" t="inlineStr"/>
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t>Remote, IT</t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr"/>
-      <c r="I88" s="2" t="inlineStr">
+      <c r="H89" s="2" t="inlineStr"/>
+      <c r="I89" s="2" t="inlineStr">
         <is>
           <t>Arbeitnow</t>
         </is>
       </c>
-      <c r="J88" s="3" t="inlineStr">
+      <c r="J89" s="3" t="inlineStr">
         <is>
           <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-adtech-saas-startup-remote-cologne-263746</t>
         </is>
       </c>
-      <c r="K88" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B89" s="4" t="inlineStr">
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
         <is>
           <t>Senior DevOps / Platform Engineer (f/m/x)</t>
         </is>
       </c>
-      <c r="C89" s="4" t="inlineStr">
+      <c r="C90" s="4" t="inlineStr">
         <is>
           <t>MAIA</t>
         </is>
       </c>
-      <c r="D89" s="4" t="inlineStr">
+      <c r="D90" s="4" t="inlineStr">
         <is>
           <t>Leipzig</t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr">
+      <c r="E90" s="4" t="inlineStr">
         <is>
           <t>professional / experienced</t>
         </is>
       </c>
-      <c r="F89" s="4" t="inlineStr"/>
-      <c r="G89" s="4" t="inlineStr">
+      <c r="F90" s="4" t="inlineStr"/>
+      <c r="G90" s="4" t="inlineStr">
         <is>
           <t>Remote, IT</t>
         </is>
       </c>
-      <c r="H89" s="4" t="inlineStr"/>
-      <c r="I89" s="4" t="inlineStr">
+      <c r="H90" s="4" t="inlineStr"/>
+      <c r="I90" s="4" t="inlineStr">
         <is>
           <t>Arbeitnow</t>
         </is>
       </c>
-      <c r="J89" s="5" t="inlineStr">
+      <c r="J90" s="5" t="inlineStr">
         <is>
           <t>https://www.arbeitnow.com/jobs/companies/maia/senior-devops-platform-engineer-leipzig-388068</t>
         </is>
       </c>
-      <c r="K89" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+      <c r="K90" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>Senior Site Reliability Engineer AI Infrastructure</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
         <is>
           <t>Andromeda Cluster</t>
         </is>
       </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr"/>
-      <c r="F90" s="2" t="inlineStr"/>
-      <c r="G90" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr"/>
+      <c r="F91" s="2" t="inlineStr"/>
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t>design, training, technical, software, code, manager, financial, cloud, management, lead, senior, operations, reliability, go, health, engineer, engineering, linux, digital nomad</t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr"/>
-      <c r="I90" s="2" t="inlineStr">
+      <c r="H91" s="2" t="inlineStr"/>
+      <c r="I91" s="2" t="inlineStr">
         <is>
           <t>RemoteOK</t>
         </is>
       </c>
-      <c r="J90" s="3" t="inlineStr">
+      <c r="J91" s="3" t="inlineStr">
         <is>
           <t>https://remoteOK.com/remote-jobs/remote-senior-site-reliability-engineer-ai-infrastructure-andromeda-cluster-1131375</t>
         </is>
       </c>
-      <c r="K90" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="4" t="inlineStr">
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B91" s="4" t="inlineStr">
+      <c r="B92" s="4" t="inlineStr">
         <is>
           <t>Senior Financial Analyst Digital Assets</t>
         </is>
       </c>
-      <c r="C91" s="4" t="inlineStr">
+      <c r="C92" s="4" t="inlineStr">
         <is>
           <t>Exodus Movement Inc.</t>
         </is>
       </c>
-      <c r="D91" s="4" t="inlineStr">
+      <c r="D92" s="4" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr"/>
-      <c r="F91" s="4" t="inlineStr"/>
-      <c r="G91" s="4" t="inlineStr">
+      <c r="E92" s="4" t="inlineStr"/>
+      <c r="F92" s="4" t="inlineStr"/>
+      <c r="G92" s="4" t="inlineStr">
         <is>
           <t>analyst, cryptocurrency, support, financial, investment, finance, senior, non tech</t>
         </is>
       </c>
-      <c r="H91" s="4" t="inlineStr"/>
-      <c r="I91" s="4" t="inlineStr">
+      <c r="H92" s="4" t="inlineStr"/>
+      <c r="I92" s="4" t="inlineStr">
         <is>
           <t>RemoteOK</t>
         </is>
       </c>
-      <c r="J91" s="5" t="inlineStr">
+      <c r="J92" s="5" t="inlineStr">
         <is>
           <t>https://remoteOK.com/remote-jobs/remote-senior-financial-analyst-digital-assets-exodus-movement-inc-1131374</t>
         </is>
       </c>
-      <c r="K91" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+      <c r="K92" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>Front End Full Stack Developer</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
         <is>
           <t>Honor Foods</t>
         </is>
       </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Philadelphia, PA</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr"/>
-      <c r="F92" s="2" t="inlineStr"/>
-      <c r="G92" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr"/>
+      <c r="F93" s="2" t="inlineStr"/>
+      <c r="G93" s="2" t="inlineStr">
         <is>
           <t>developer, front-end, ui, code, web, operational, backend, digital nomad</t>
         </is>
       </c>
-      <c r="H92" s="2" t="inlineStr"/>
-      <c r="I92" s="2" t="inlineStr">
+      <c r="H93" s="2" t="inlineStr"/>
+      <c r="I93" s="2" t="inlineStr">
         <is>
           <t>RemoteOK</t>
         </is>
       </c>
-      <c r="J92" s="3" t="inlineStr">
+      <c r="J93" s="3" t="inlineStr">
         <is>
           <t>https://remoteOK.com/remote-jobs/remote-front-end-full-stack-developer-honor-foods-1131370</t>
         </is>
       </c>
-      <c r="K92" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="4" t="inlineStr">
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B93" s="4" t="inlineStr">
+      <c r="B94" s="4" t="inlineStr">
         <is>
           <t>Wing Assistant: Full-Stack Developer</t>
         </is>
       </c>
-      <c r="C93" s="4" t="inlineStr"/>
-      <c r="D93" s="4" t="inlineStr">
+      <c r="C94" s="4" t="inlineStr"/>
+      <c r="D94" s="4" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="E93" s="4" t="inlineStr"/>
-      <c r="F93" s="4" t="inlineStr"/>
-      <c r="G93" s="4" t="inlineStr"/>
-      <c r="H93" s="4" t="inlineStr"/>
-      <c r="I93" s="4" t="inlineStr">
+      <c r="E94" s="4" t="inlineStr"/>
+      <c r="F94" s="4" t="inlineStr"/>
+      <c r="G94" s="4" t="inlineStr"/>
+      <c r="H94" s="4" t="inlineStr"/>
+      <c r="I94" s="4" t="inlineStr">
         <is>
           <t>WeWorkRemotely</t>
         </is>
       </c>
-      <c r="J93" s="5" t="inlineStr">
+      <c r="J94" s="5" t="inlineStr">
         <is>
           <t>https://weworkremotely.com/remote-jobs/wing-assistant-full-stack-developer</t>
         </is>
       </c>
-      <c r="K93" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+      <c r="K94" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>Qventus: Product Designer</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr"/>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr"/>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr"/>
-      <c r="F94" s="2" t="inlineStr"/>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr"/>
-      <c r="I94" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr"/>
+      <c r="F95" s="2" t="inlineStr"/>
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr"/>
+      <c r="I95" s="2" t="inlineStr">
         <is>
           <t>WeWorkRemotely</t>
         </is>
       </c>
-      <c r="J94" s="3" t="inlineStr">
+      <c r="J95" s="3" t="inlineStr">
         <is>
           <t>https://weworkremotely.com/remote-jobs/qventus-product-designer</t>
         </is>
       </c>
-      <c r="K94" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="4" t="inlineStr">
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B95" s="4" t="inlineStr">
+      <c r="B96" s="4" t="inlineStr">
         <is>
           <t>Socure: Senior Product Marketing Manager</t>
         </is>
       </c>
-      <c r="C95" s="4" t="inlineStr"/>
-      <c r="D95" s="4" t="inlineStr">
+      <c r="C96" s="4" t="inlineStr"/>
+      <c r="D96" s="4" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="E95" s="4" t="inlineStr"/>
-      <c r="F95" s="4" t="inlineStr"/>
-      <c r="G95" s="4" t="inlineStr"/>
-      <c r="H95" s="4" t="inlineStr"/>
-      <c r="I95" s="4" t="inlineStr">
+      <c r="E96" s="4" t="inlineStr"/>
+      <c r="F96" s="4" t="inlineStr"/>
+      <c r="G96" s="4" t="inlineStr"/>
+      <c r="H96" s="4" t="inlineStr"/>
+      <c r="I96" s="4" t="inlineStr">
         <is>
           <t>WeWorkRemotely</t>
         </is>
       </c>
-      <c r="J95" s="5" t="inlineStr">
+      <c r="J96" s="5" t="inlineStr">
         <is>
           <t>https://weworkremotely.com/remote-jobs/socure-senior-product-marketing-manager</t>
         </is>
       </c>
-      <c r="K95" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+      <c r="K96" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>Blueprint: Product Designer</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr"/>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr"/>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr"/>
-      <c r="F96" s="2" t="inlineStr"/>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr"/>
-      <c r="I96" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr"/>
+      <c r="F97" s="2" t="inlineStr"/>
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr"/>
+      <c r="I97" s="2" t="inlineStr">
         <is>
           <t>WeWorkRemotely</t>
         </is>
       </c>
-      <c r="J96" s="3" t="inlineStr">
+      <c r="J97" s="3" t="inlineStr">
         <is>
           <t>https://weworkremotely.com/remote-jobs/blueprint-product-designer</t>
         </is>
       </c>
-      <c r="K96" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B97" s="4" t="inlineStr">
+      <c r="B98" s="4" t="inlineStr">
         <is>
           <t>Interop Labs: Product Marketing Manager</t>
         </is>
       </c>
-      <c r="C97" s="4" t="inlineStr"/>
-      <c r="D97" s="4" t="inlineStr">
+      <c r="C98" s="4" t="inlineStr"/>
+      <c r="D98" s="4" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr"/>
-      <c r="F97" s="4" t="inlineStr"/>
-      <c r="G97" s="4" t="inlineStr"/>
-      <c r="H97" s="4" t="inlineStr"/>
-      <c r="I97" s="4" t="inlineStr">
+      <c r="E98" s="4" t="inlineStr"/>
+      <c r="F98" s="4" t="inlineStr"/>
+      <c r="G98" s="4" t="inlineStr"/>
+      <c r="H98" s="4" t="inlineStr"/>
+      <c r="I98" s="4" t="inlineStr">
         <is>
           <t>WeWorkRemotely</t>
         </is>
       </c>
-      <c r="J97" s="5" t="inlineStr">
+      <c r="J98" s="5" t="inlineStr">
         <is>
           <t>https://weworkremotely.com/remote-jobs/interop-labs-product-marketing-manager</t>
         </is>
       </c>
-      <c r="K97" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+      <c r="K98" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>Full Stack Engineer, Link</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
+      <c r="C99" s="2" t="inlineStr">
         <is>
           <t>Stripe</t>
         </is>
       </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Toronto, Remote in Canada</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr"/>
-      <c r="F98" s="2" t="inlineStr"/>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr"/>
-      <c r="I98" s="2" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J98" s="3" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr"/>
+      <c r="F99" s="2" t="inlineStr"/>
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr"/>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
         <is>
           <t>https://stripe.com/jobs/search?gh_jid=6447175</t>
         </is>
       </c>
-      <c r="K98" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="4" t="inlineStr">
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B99" s="4" t="inlineStr">
+      <c r="B100" s="4" t="inlineStr">
         <is>
           <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
-      <c r="C99" s="4" t="inlineStr">
+      <c r="C100" s="4" t="inlineStr">
         <is>
           <t>Reddit</t>
         </is>
       </c>
-      <c r="D99" s="4" t="inlineStr">
+      <c r="D100" s="4" t="inlineStr">
         <is>
           <t>Remote - Ontario, Canada</t>
         </is>
       </c>
-      <c r="E99" s="4" t="inlineStr"/>
-      <c r="F99" s="4" t="inlineStr"/>
-      <c r="G99" s="4" t="inlineStr"/>
-      <c r="H99" s="4" t="inlineStr"/>
-      <c r="I99" s="4" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J99" s="5" t="inlineStr">
+      <c r="E100" s="4" t="inlineStr"/>
+      <c r="F100" s="4" t="inlineStr"/>
+      <c r="G100" s="4" t="inlineStr"/>
+      <c r="H100" s="4" t="inlineStr"/>
+      <c r="I100" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J100" s="5" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/reddit/jobs/6960833</t>
         </is>
       </c>
-      <c r="K99" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+      <c r="K100" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
+      <c r="C101" s="2" t="inlineStr">
         <is>
           <t>Reddit</t>
         </is>
       </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Remote - United States</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr"/>
-      <c r="F100" s="2" t="inlineStr"/>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr"/>
-      <c r="I100" s="2" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J100" s="3" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr"/>
+      <c r="F101" s="2" t="inlineStr"/>
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr"/>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/reddit/jobs/6960831</t>
         </is>
       </c>
-      <c r="K100" s="2" t="inlineStr">
+      <c r="K101" s="2" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
@@ -4822,57 +4867,53 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId48"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/remote_jobs.xlsx
+++ b/remote_jobs.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K101"/>
+  <dimension ref="A1:K103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -523,29 +523,33 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Fullstack Developer (m/w/d) REMOTE //  UX / Python / Vue.js</t>
+          <t>AI Developer (Claude + AWS)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Pont Connects e.K.</t>
+          <t>Datavent</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Düsseldorf</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr"/>
+          <t>Hamburg</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Remote, IT</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -556,146 +560,154 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
+          <t>https://www.arbeitnow.com/jobs/companies/datavent/ai-developer-claude-aws-hamburg-22354</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Python Software Engineer, Backend &amp; APIs - Remote</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>dexter health</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Cologne</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr"/>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Software Development</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/python-software-engineer-backend-apis-remote-cologne-284750</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Fullstack Developer (m/w/d) REMOTE //  UX / Python / Vue.js</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Pont Connects e.K.</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Düsseldorf</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Remote, IT</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>https://www.arbeitnow.com/jobs/companies/pont-connects-ek/fullstack-developer-remote-ux-python-vuejs-dusseldorf-371903</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2026-05-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Lemon.io</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Americas, Europe, Asia, Oceania</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>full_time</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Devops</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>.Net, android, AWS, azure, C, C#, C++, data science, golang, ios, java, javascript, kubernetes, node.js, php, python, react, ruby/rails, shopify, sql, video, blockchain, AI/ML, automation, react native, rust, unity, spring, data analysis, laravel, solidity, flask, Typescript , terraform, angular , GCP, data engineering, Symfony, startup, marketplace, next.js</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Remotive</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>https://remotive.com/remote-jobs/devops/senior-devops-engineer-2090002</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>M&amp;A Research Analyst</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>EquiMatch GmbH</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Mergers &amp; Acquisitions</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J4" s="5" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/equimatch-gmbh/ma-research-analyst-berlin-498635</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Xsolla: Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr"/>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Lemon.io</t>
+        </is>
+      </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
+          <t>Americas, Europe, Asia, Oceania</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>full_time</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Devops</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>.Net, android, AWS, azure, C, C#, C++, data science, golang, ios, java, javascript, kubernetes, node.js, php, python, react, ruby/rails, shopify, sql, video, blockchain, AI/ML, automation, react native, rust, unity, spring, data analysis, laravel, solidity, flask, Typescript , terraform, angular , GCP, data engineering, Symfony, startup, marketplace, next.js</t>
+        </is>
+      </c>
       <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Remotive</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/xsolla-full-stack-developer</t>
+          <t>https://remotive.com/remote-jobs/devops/senior-devops-engineer-2090002</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -707,32 +719,44 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Dropbox: Staff Fullstack Product Software Engineer, Dash</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr"/>
+          <t>M&amp;A Research Analyst</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>EquiMatch GmbH</t>
+        </is>
+      </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr"/>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
       <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Mergers &amp; Acquisitions</t>
+        </is>
+      </c>
       <c r="H6" s="4" t="inlineStr"/>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/dropbox-staff-fullstack-product-software-engineer-dash</t>
+          <t>https://www.arbeitnow.com/jobs/companies/equimatch-gmbh/ma-research-analyst-berlin-498635</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
@@ -749,17 +773,13 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, Ranking and Personalization</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Reddit</t>
-        </is>
-      </c>
+          <t>Xsolla: Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr"/>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -768,115 +788,95 @@
       <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>https://weworkremotely.com/remote-jobs/xsolla-full-stack-developer</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Dropbox: Staff Fullstack Product Software Engineer, Dash</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>WeWorkRemotely</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>https://weworkremotely.com/remote-jobs/dropbox-staff-fullstack-product-software-engineer-dash</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Staff Machine Learning Engineer, Ranking and Personalization</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
           <t>https://job-boards.greenhouse.io/reddit/jobs/7848689</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>2026-05-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Senior Rust Consultant / Engineer (m/w/d)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Hackstack GmbH</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>berufserfahren</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Remote, Consulting, Engineering</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/hackstack-gmbh/senior-rust-consultant-engineer-munich-451602</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer - Remote</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>dexter health</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Cologne</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Development</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr"/>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/applied-ai-engineer-remote-cologne-2870</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -888,28 +888,28 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Python Backend Engineer - Remote</t>
+          <t>Senior Rust Consultant / Engineer (m/w/d)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>dexter health</t>
+          <t>Hackstack GmbH</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Cologne</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>professional / experienced</t>
+          <t>berufserfahren</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Remote, Development</t>
+          <t>Remote, Consulting, Engineering</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
@@ -920,7 +920,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/python-backend-engineer-remote-cologne-34228</t>
+          <t>https://www.arbeitnow.com/jobs/companies/hackstack-gmbh/senior-rust-consultant-engineer-munich-451602</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>AI Engineer (LLM Products) - Remote</t>
+          <t>Applied AI Engineer - Remote</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/ai-engineer-llm-products-remote-cologne-236027</t>
+          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/applied-ai-engineer-remote-cologne-2870</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Backend Python Engineer (APIs, Databases &amp; Cloud) - Remote</t>
+          <t>Python Backend Engineer - Remote</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/backend-python-engineer-apis-databases-cloud-remote-cologne-274767</t>
+          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/python-backend-engineer-remote-cologne-34228</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1030,32 +1030,44 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Toptal: QA Automation Engineer</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr"/>
+          <t>AI Engineer (LLM Products) - Remote</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>dexter health</t>
+        </is>
+      </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr"/>
+          <t>Cologne</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
       <c r="F13" s="4" t="inlineStr"/>
-      <c r="G13" s="4" t="inlineStr"/>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Development</t>
+        </is>
+      </c>
       <c r="H13" s="4" t="inlineStr"/>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/toptal-qa-automation-engineer-1</t>
+          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/ai-engineer-llm-products-remote-cologne-236027</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
@@ -1067,32 +1079,44 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Opensea: Staff Product Designer</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr"/>
+          <t>Backend Python Engineer (APIs, Databases &amp; Cloud) - Remote</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>dexter health</t>
+        </is>
+      </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr"/>
+          <t>Cologne</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
       <c r="F14" s="2" t="inlineStr"/>
-      <c r="G14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Remote, Development</t>
+        </is>
+      </c>
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/opensea-staff-product-designer</t>
+          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/backend-python-engineer-apis-databases-cloud-remote-cologne-274767</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1109,7 +1133,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Mutt Data: Devops</t>
+          <t>Toptal: QA Automation Engineer</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr"/>
@@ -1129,7 +1153,7 @@
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/mutt-data-devops</t>
+          <t>https://weworkremotely.com/remote-jobs/toptal-qa-automation-engineer-1</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
@@ -1146,7 +1170,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Holywater: Full-Stack Developer</t>
+          <t>Opensea: Staff Product Designer</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr"/>
@@ -1166,7 +1190,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/holywater-full-stack-developer</t>
+          <t>https://weworkremotely.com/remote-jobs/opensea-staff-product-designer</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1183,7 +1207,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Qventus: DevOps Engineer</t>
+          <t>Mutt Data: Devops</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr"/>
@@ -1203,7 +1227,7 @@
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/qventus-devops-engineer</t>
+          <t>https://weworkremotely.com/remote-jobs/mutt-data-devops</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
@@ -1220,7 +1244,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Visualis: Senior Full Stack Developer</t>
+          <t>Holywater: Full-Stack Developer</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr"/>
@@ -1240,7 +1264,7 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/visualis-senior-full-stack-developer</t>
+          <t>https://weworkremotely.com/remote-jobs/holywater-full-stack-developer</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1257,17 +1281,13 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>GitLab</t>
-        </is>
-      </c>
+          <t>Qventus: DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr"/>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Remote, Bangalore</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
@@ -1276,12 +1296,12 @@
       <c r="H19" s="4" t="inlineStr"/>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8517564002</t>
+          <t>https://weworkremotely.com/remote-jobs/qventus-devops-engineer</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
@@ -1298,17 +1318,13 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Backend Engineer, Analytics Instrumentation (Golang)</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>GitLab</t>
-        </is>
-      </c>
+          <t>Visualis: Senior Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr"/>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -1317,12 +1333,12 @@
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481922002</t>
+          <t>https://weworkremotely.com/remote-jobs/visualis-senior-full-stack-developer</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1339,7 +1355,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Backend Engineer, Analytics Instrumentation (Golang)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1349,7 +1365,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, Bangalore</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr"/>
@@ -1363,7 +1379,7 @@
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481929002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8517564002</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
@@ -1380,7 +1396,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Backend Engineer, Knowledge Graph (Rust)</t>
+          <t>Backend Engineer, Analytics Instrumentation (Golang)</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1390,7 +1406,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, US</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr"/>
@@ -1404,7 +1420,7 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8437754002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481922002</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1421,7 +1437,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Backend Engineer, Knowledge Graph (Rust)</t>
+          <t>Backend Engineer, Analytics Instrumentation (Golang)</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -1445,7 +1461,7 @@
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481958002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481929002</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
@@ -1462,7 +1478,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Intermediate Backend Engineer (C), Tenant Scale: Git</t>
+          <t>Backend Engineer, Knowledge Graph (Rust)</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1472,7 +1488,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, Canada; Remote, US</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
@@ -1486,7 +1502,7 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8497793002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8437754002</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1503,7 +1519,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Intermediate Backend Engineer, Gitlab Delivery: Upgrades</t>
+          <t>Backend Engineer, Knowledge Graph (Rust)</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1527,7 +1543,7 @@
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8463951002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481958002</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
@@ -1544,7 +1560,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Intermediate Backend Engineer, SRM: Security Platform Management</t>
+          <t>Intermediate Backend Engineer (C), Tenant Scale: Git</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1554,7 +1570,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
@@ -1568,7 +1584,7 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8443325002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8497793002</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -1585,7 +1601,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Intermediate Backend Engineer, SSCS: AI Governance</t>
+          <t>Intermediate Backend Engineer, Gitlab Delivery: Upgrades</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1609,7 +1625,7 @@
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480551002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8463951002</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
@@ -1626,7 +1642,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Intermediate Backend Engineer,  SSCS: Supply Chain</t>
+          <t>Intermediate Backend Engineer, SRM: Security Platform Management</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1636,7 +1652,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
@@ -1650,7 +1666,7 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480565002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8443325002</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -1667,7 +1683,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Intermediate Backend Engineer, SSCS: AI Governance</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1677,7 +1693,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Remote, EMEA</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr"/>
@@ -1691,7 +1707,7 @@
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8464072002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480551002</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
@@ -1708,7 +1724,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (AI), Pipeline Execution</t>
+          <t>Intermediate Backend Engineer,  SSCS: Supply Chain</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1718,7 +1734,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US-Southeast</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
@@ -1732,7 +1748,7 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8514945002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480565002</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -1749,7 +1765,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Analytics Instrumentation (Golang)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -1759,7 +1775,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, US</t>
+          <t>Remote, EMEA</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr"/>
@@ -1773,7 +1789,7 @@
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8451512002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8464072002</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
@@ -1790,7 +1806,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (C), Tenant Scale: Git</t>
+          <t>Senior Backend Engineer (AI), Pipeline Execution</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1800,7 +1816,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US-Southeast</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr"/>
@@ -1814,7 +1830,7 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8497791002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8514945002</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -1831,7 +1847,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Gitlab Delivery: Runway (Platform Engineering)</t>
+          <t>Senior Backend Engineer, Analytics Instrumentation (Golang)</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -1841,7 +1857,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Remote, Australia; Remote, India; Remote, Ireland; Remote, Japan; Remote, Netherlands; Remote, Singapore; Remote, United Kingdom</t>
+          <t>Remote, Canada; Remote, US</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr"/>
@@ -1855,7 +1871,7 @@
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8324132002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8451512002</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
@@ -1872,7 +1888,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Gitlab Delivery: Upgrades</t>
+          <t>Senior Backend Engineer (C), Tenant Scale: Git</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -1896,7 +1912,7 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8463933002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8497791002</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -1913,7 +1929,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer(Go), Continuous Delivery</t>
+          <t>Senior Backend Engineer, Gitlab Delivery: Runway (Platform Engineering)</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -1923,7 +1939,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, Australia; Remote, India; Remote, Ireland; Remote, Japan; Remote, Netherlands; Remote, Singapore; Remote, United Kingdom</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr"/>
@@ -1937,7 +1953,7 @@
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8488966002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8324132002</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
@@ -1954,7 +1970,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer(Golang),Software Supply Chain Security: Auth Infrastructure</t>
+          <t>Senior Backend Engineer, Gitlab Delivery: Upgrades</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -1964,7 +1980,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Remote, Americas; Remote, APAC; Remote, Canada</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr"/>
@@ -1978,7 +1994,7 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8157520002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8463933002</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -1995,7 +2011,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (RoR), AST: Secret Detection</t>
+          <t>Senior Backend Engineer(Go), Continuous Delivery</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -2005,7 +2021,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr"/>
@@ -2019,7 +2035,7 @@
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8432262002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8488966002</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
@@ -2036,7 +2052,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (RoR/Go), SSCS: Pipeline Security</t>
+          <t>Senior Backend Engineer(Golang),Software Supply Chain Security: Auth Infrastructure</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2046,7 +2062,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
+          <t>Remote, Americas; Remote, APAC; Remote, Canada</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr"/>
@@ -2060,7 +2076,7 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8432221002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8157520002</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -2077,7 +2093,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (RoR), SSCS: Authorization</t>
+          <t>Senior Backend Engineer (RoR), AST: Secret Detection</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -2087,7 +2103,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
+          <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr"/>
@@ -2101,7 +2117,7 @@
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8457315002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8432262002</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
@@ -2118,7 +2134,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby or Golang), Tenant Scale; Cells Infrastructure</t>
+          <t>Senior Backend Engineer (RoR/Go), SSCS: Pipeline Security</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2128,7 +2144,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Remote, APAC; Remote, Canada; Remote, EMEA; Remote, US</t>
+          <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
@@ -2142,7 +2158,7 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8437148002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8432221002</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -2159,7 +2175,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, SSCS: AI Governance</t>
+          <t>Senior Backend Engineer (RoR), SSCS: Authorization</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -2169,7 +2185,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr"/>
@@ -2183,7 +2199,7 @@
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480544002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8457315002</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
@@ -2200,7 +2216,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer,  SSCS: Supply Chain</t>
+          <t>Senior Backend Engineer (Ruby or Golang), Tenant Scale; Cells Infrastructure</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2210,7 +2226,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, APAC; Remote, Canada; Remote, EMEA; Remote, US</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr"/>
@@ -2224,7 +2240,7 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480580002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8437148002</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -2241,7 +2257,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Senior Fullstack Engineer (TypeScript), AI Engineering: Editor Extensions</t>
+          <t>Senior Backend Engineer, SSCS: AI Governance</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -2251,7 +2267,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Remote, APAC; Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US-Southeast</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr"/>
@@ -2265,7 +2281,7 @@
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8452278002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480544002</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
@@ -2282,7 +2298,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer, Analytics Instrumentation (Golang)</t>
+          <t>Senior Backend Engineer,  SSCS: Supply Chain</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2306,7 +2322,7 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8508027002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480580002</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -2323,7 +2339,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer, AST: Composition Analysis</t>
+          <t>Senior Fullstack Engineer (TypeScript), AI Engineering: Editor Extensions</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -2333,7 +2349,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Remote, Australia; Remote, Canada; Remote, India; Remote, Ireland; Remote, Israel; Remote, Japan; Remote, Netherlands; Remote, New Zealand; Remote, United Kingdom; Remote, US</t>
+          <t>Remote, APAC; Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US-Southeast</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr"/>
@@ -2347,7 +2363,7 @@
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8478364002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8452278002</t>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr">
@@ -2364,7 +2380,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer, Developer Experience</t>
+          <t>Staff Backend Engineer, Analytics Instrumentation (Golang)</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2374,7 +2390,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, United Kingdom; Remote, US</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
@@ -2388,7 +2404,7 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8490477002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8508027002</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -2405,7 +2421,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer, Gitlab Delivery: Upgrades</t>
+          <t>Staff Backend Engineer, AST: Composition Analysis</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -2415,7 +2431,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, Australia; Remote, Canada; Remote, India; Remote, Ireland; Remote, Israel; Remote, Japan; Remote, Netherlands; Remote, New Zealand; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr"/>
@@ -2429,7 +2445,7 @@
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8463922002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8478364002</t>
         </is>
       </c>
       <c r="K47" s="4" t="inlineStr">
@@ -2446,7 +2462,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer (Go), Continuous Delivery</t>
+          <t>Staff Backend Engineer, Developer Experience</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2456,7 +2472,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, Canada; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr"/>
@@ -2470,7 +2486,7 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8488961002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8490477002</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -2487,7 +2503,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer (Go), Software Supply Chain Security: Secrets Management</t>
+          <t>Staff Backend Engineer, Gitlab Delivery: Upgrades</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -2497,7 +2513,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr"/>
@@ -2511,7 +2527,7 @@
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8432235002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8463922002</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr">
@@ -2528,7 +2544,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer, Knowledge Graph (Rust)</t>
+          <t>Staff Backend Engineer (Go), Continuous Delivery</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2552,7 +2568,7 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481945002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8488961002</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -2569,7 +2585,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer,  Software Supply Chain Security</t>
+          <t>Staff Backend Engineer (Go), Software Supply Chain Security: Secrets Management</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -2579,7 +2595,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr"/>
@@ -2593,7 +2609,7 @@
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480559002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8432235002</t>
         </is>
       </c>
       <c r="K51" s="4" t="inlineStr">
@@ -2610,7 +2626,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer, SSCS: AI Governance</t>
+          <t>Staff Backend Engineer, Knowledge Graph (Rust)</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -2634,7 +2650,7 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480531002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481945002</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -2651,7 +2667,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Staff Backend (Python) Engineer, AI Engineering:Duo Chat</t>
+          <t>Staff Backend Engineer,  Software Supply Chain Security</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -2661,7 +2677,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Remote, Americas; Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr"/>
@@ -2675,7 +2691,7 @@
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8450446002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480559002</t>
         </is>
       </c>
       <c r="K53" s="4" t="inlineStr">
@@ -2692,17 +2708,17 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Senior Full Stack Product Software Engineer</t>
+          <t>Staff Backend Engineer, SSCS: AI Governance</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Dropbox</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Remote - Poland</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr"/>
@@ -2716,126 +2732,94 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480531002</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>Staff Backend (Python) Engineer, AI Engineering:Duo Chat</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>GitLab</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Americas; Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr"/>
+      <c r="F55" s="4" t="inlineStr"/>
+      <c r="G55" s="4" t="inlineStr"/>
+      <c r="H55" s="4" t="inlineStr"/>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8450446002</t>
+        </is>
+      </c>
+      <c r="K55" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Product Software Engineer</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Dropbox</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Remote - Poland</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr"/>
+      <c r="F56" s="2" t="inlineStr"/>
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
           <t>https://jobs.dropbox.com/listing/6449719?gh_jid=6449719</t>
         </is>
       </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Dry Ground AI</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>Brazil, Colombia, Philippines</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>full_time</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>api, cloud, fullstack, python, AI/ML, automation, research, CI/CD, TensorFlow, spark, NLP, CMS, Pytorch, REST</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>$40- $60k</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>Remotive</t>
-        </is>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>https://remotive.com/remote-jobs/artificial-intelligence/ai-engineer-2089958</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>Senior Independent AI Engineer / Architect</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>A.Team</t>
-        </is>
-      </c>
-      <c r="D56" s="4" t="inlineStr">
-        <is>
-          <t>Americas, Europe, Israel</t>
-        </is>
-      </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>contract</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>Software Development</t>
-        </is>
-      </c>
-      <c r="G56" s="4" t="inlineStr">
-        <is>
-          <t>go, UI/UX, wordpress, chat, apple, testing, catalyst</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="inlineStr">
-        <is>
-          <t>$120 - $170 /hour</t>
-        </is>
-      </c>
-      <c r="I56" s="4" t="inlineStr">
-        <is>
-          <t>Remotive</t>
-        </is>
-      </c>
-      <c r="J56" s="5" t="inlineStr">
-        <is>
-          <t>https://remotive.com/remote-jobs/software-development/senior-independent-ai-engineer-architect-1919266</t>
-        </is>
-      </c>
-      <c r="K56" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2847,37 +2831,37 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Senior Independent Software Developer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>A.Team</t>
+          <t>Dry Ground AI</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Americas, Europe, Israel</t>
+          <t>Brazil, Colombia, Philippines</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>contract</t>
+          <t>full_time</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Software Development</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>go, wordpress, chat, apple, testing, catalyst</t>
+          <t>api, cloud, fullstack, python, AI/ML, automation, research, CI/CD, TensorFlow, spark, NLP, CMS, Pytorch, REST</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>$90 - $150 /hour</t>
+          <t>$40- $60k</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -2887,7 +2871,7 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>https://remotive.com/remote-jobs/software-development/senior-independent-software-developer-1919265</t>
+          <t>https://remotive.com/remote-jobs/artificial-intelligence/ai-engineer-2089958</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -2904,17 +2888,17 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Senior Full-stack React Developer</t>
+          <t>Senior Independent AI Engineer / Architect</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Lemon.io</t>
+          <t>A.Team</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Americas, Europe, Asia, Oceania</t>
+          <t>Americas, Europe, Israel</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
@@ -2929,10 +2913,14 @@
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>.Net, android, AWS, azure, backend, C, C#, C++, data science, fullstack, golang, ios, java, javascript, node.js, php, python, react, react js, ruby/rails, shopify, video, blockchain, AI/ML, react native, rust, unity, spring, data analysis, laravel, solidity, flask, Typescript , angular , GCP, data engineering, Symfony, startup, marketplace, next.js</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="inlineStr"/>
+          <t>go, UI/UX, wordpress, chat, apple, testing, catalyst</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>$120 - $170 /hour</t>
+        </is>
+      </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
           <t>Remotive</t>
@@ -2940,7 +2928,7 @@
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>https://remotive.com/remote-jobs/software-development/senior-full-stack-react-developer-2088711</t>
+          <t>https://remotive.com/remote-jobs/software-development/senior-independent-ai-engineer-architect-1919266</t>
         </is>
       </c>
       <c r="K58" s="4" t="inlineStr">
@@ -2957,22 +2945,22 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Tech Lead Full-Stack Rails Engineer</t>
+          <t>Senior Independent Software Developer</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Mitre Media</t>
+          <t>A.Team</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>USA, Canada, USA timezones</t>
+          <t>Americas, Europe, Israel</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>full_time</t>
+          <t>contract</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -2982,12 +2970,12 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>api, CSS, docker, elasticsearch, fullstack, html, javascript, kubernetes, postgresql, react, ror, ruby/rails, AI/ML, CAD, advertising, Redis, ES6, web applications, MySQL, NLP, fintech, Micro services, github, system architecture</t>
+          <t>go, wordpress, chat, apple, testing, catalyst</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>$170k - $200k</t>
+          <t>$90 - $150 /hour</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -2997,7 +2985,7 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>https://remotive.com/remote-jobs/software-development/tech-lead-full-stack-rails-engineer-2069746</t>
+          <t>https://remotive.com/remote-jobs/software-development/senior-independent-software-developer-1919265</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -3014,17 +3002,17 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Senior Frontend Developer</t>
+          <t>Senior Full-stack React Developer</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Sanctuary Computer</t>
+          <t>Lemon.io</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>LATAM, Asia</t>
+          <t>Americas, Europe, Asia, Oceania</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
@@ -3039,14 +3027,10 @@
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>api, backend, CSS, ecommerce, frontend, fullstack, graphql, postgresql, redux, security, seo, shopify, open source, paas, product management, documentation, mentoring, Typescript , Redis, web applications, cypress, data visualization, firebase, IoT, engineering management, runtime, responsive, prismic, testing, next.js, CMS, jest, REST, web sockets, performance optimization</t>
-        </is>
-      </c>
-      <c r="H60" s="4" t="inlineStr">
-        <is>
-          <t>$80k - $120k</t>
-        </is>
-      </c>
+          <t>.Net, android, AWS, azure, backend, C, C#, C++, data science, fullstack, golang, ios, java, javascript, node.js, php, python, react, react js, ruby/rails, shopify, video, blockchain, AI/ML, react native, rust, unity, spring, data analysis, laravel, solidity, flask, Typescript , angular , GCP, data engineering, Symfony, startup, marketplace, next.js</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr"/>
       <c r="I60" s="4" t="inlineStr">
         <is>
           <t>Remotive</t>
@@ -3054,7 +3038,7 @@
       </c>
       <c r="J60" s="5" t="inlineStr">
         <is>
-          <t>https://remotive.com/remote-jobs/software-development/senior-frontend-developer-2088707</t>
+          <t>https://remotive.com/remote-jobs/software-development/senior-full-stack-react-developer-2088711</t>
         </is>
       </c>
       <c r="K60" s="4" t="inlineStr">
@@ -3071,17 +3055,17 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Fullstack Developer (US - ET)</t>
+          <t>Tech Lead Full-Stack Rails Engineer</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Chooose</t>
+          <t>Mitre Media</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>USA, Canada, USA timezones</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -3096,10 +3080,14 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>api, azure, fullstack, python, react, saas, AI/ML, project management, documentation, Typescript , computer science, diversity, insurance</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr"/>
+          <t>api, CSS, docker, elasticsearch, fullstack, html, javascript, kubernetes, postgresql, react, ror, ruby/rails, AI/ML, CAD, advertising, Redis, ES6, web applications, MySQL, NLP, fintech, Micro services, github, system architecture</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>$170k - $200k</t>
+        </is>
+      </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
           <t>Remotive</t>
@@ -3107,7 +3095,7 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>https://remotive.com/remote-jobs/software-development/fullstack-developer-us-et-2088706</t>
+          <t>https://remotive.com/remote-jobs/software-development/tech-lead-full-stack-rails-engineer-2069746</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -3124,31 +3112,47 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning Manager, Notifications Relevance</t>
+          <t>Senior Frontend Developer</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Sanctuary Computer</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
-        </is>
-      </c>
-      <c r="E62" s="4" t="inlineStr"/>
-      <c r="F62" s="4" t="inlineStr"/>
-      <c r="G62" s="4" t="inlineStr"/>
-      <c r="H62" s="4" t="inlineStr"/>
+          <t>LATAM, Asia</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>contract</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>Software Development</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>api, backend, CSS, ecommerce, frontend, fullstack, graphql, postgresql, redux, security, seo, shopify, open source, paas, product management, documentation, mentoring, Typescript , Redis, web applications, cypress, data visualization, firebase, IoT, engineering management, runtime, responsive, prismic, testing, next.js, CMS, jest, REST, web sockets, performance optimization</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>$80k - $120k</t>
+        </is>
+      </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>Remotive</t>
         </is>
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7846885</t>
+          <t>https://remotive.com/remote-jobs/software-development/senior-frontend-developer-2088707</t>
         </is>
       </c>
       <c r="K62" s="4" t="inlineStr">
@@ -3165,31 +3169,43 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Senior Staff ML Engineer, Search &amp; Recommendation</t>
+          <t>Fullstack Developer (US - ET)</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Chooose</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr"/>
-      <c r="F63" s="2" t="inlineStr"/>
-      <c r="G63" s="2" t="inlineStr"/>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>full_time</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>Software Development</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>api, azure, fullstack, python, react, saas, AI/ML, project management, documentation, Typescript , computer science, diversity, insurance</t>
+        </is>
+      </c>
       <c r="H63" s="2" t="inlineStr"/>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>Remotive</t>
         </is>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7833622</t>
+          <t>https://remotive.com/remote-jobs/software-development/fullstack-developer-us-et-2088706</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -3206,17 +3222,17 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Machine Learning Manager, Notifications Relevance</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Remote - US</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr"/>
@@ -3230,7 +3246,7 @@
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7059734</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7846885</t>
         </is>
       </c>
       <c r="K64" s="4" t="inlineStr">
@@ -3247,17 +3263,17 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Staff ML Engineer, Search &amp; Recommendation</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Remote - US</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr"/>
@@ -3271,7 +3287,7 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7702644</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7833622</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -3288,7 +3304,7 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Principal Machine Learning &amp; Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -3312,7 +3328,7 @@
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7155492</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7059734</t>
         </is>
       </c>
       <c r="K66" s="4" t="inlineStr">
@@ -3329,7 +3345,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Principal, Product Manager - AI / LLM</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -3353,7 +3369,7 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7619420</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7702644</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -3370,7 +3386,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Product Engineer (Backend)</t>
+          <t>Principal Machine Learning &amp; Data Engineer</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -3394,7 +3410,7 @@
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7671815</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7155492</t>
         </is>
       </c>
       <c r="K68" s="4" t="inlineStr">
@@ -3411,7 +3427,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Senior Manager, Machine Learning</t>
+          <t>Principal, Product Manager - AI / LLM</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -3435,7 +3451,7 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7066029</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7619420</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -3452,7 +3468,7 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Staff Data Scientist</t>
+          <t>Product Engineer (Backend)</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -3476,7 +3492,7 @@
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7821458</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7671815</t>
         </is>
       </c>
       <c r="K70" s="4" t="inlineStr">
@@ -3493,7 +3509,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Staff, Data Scientist (L4) GTM Data Science &amp; Analytics</t>
+          <t>Senior Manager, Machine Learning</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -3517,7 +3533,7 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7851920</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7066029</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -3534,7 +3550,7 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer</t>
+          <t>Staff Data Scientist</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -3558,7 +3574,7 @@
       </c>
       <c r="J72" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7061880</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7821458</t>
         </is>
       </c>
       <c r="K72" s="4" t="inlineStr">
@@ -3575,7 +3591,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer (L4)</t>
+          <t>Staff, Data Scientist (L4) GTM Data Science &amp; Analytics</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -3585,7 +3601,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Remote - India</t>
+          <t>Remote - US</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr"/>
@@ -3599,7 +3615,7 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7520997</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7851920</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -3616,39 +3632,31 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Senior Python Developer - Django (m/w/d)</t>
+          <t>Staff Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>sync.blue® GmbH</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>Haltern am See</t>
-        </is>
-      </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>berufserfahren</t>
-        </is>
-      </c>
+          <t>Remote - US</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr"/>
       <c r="F74" s="4" t="inlineStr"/>
-      <c r="G74" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Software Development</t>
-        </is>
-      </c>
+      <c r="G74" s="4" t="inlineStr"/>
       <c r="H74" s="4" t="inlineStr"/>
       <c r="I74" s="4" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J74" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/syncblue-gmbh/senior-python-developer-django-haltern-am-see-16238</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7061880</t>
         </is>
       </c>
       <c r="K74" s="4" t="inlineStr">
@@ -3665,39 +3673,31 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Freelance Senior AI Product Manager</t>
+          <t>Staff Machine Learning Engineer (L4)</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>nexamind GmbH</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>Freelance, professional / experienced</t>
-        </is>
-      </c>
+          <t>Remote - India</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr"/>
       <c r="F75" s="2" t="inlineStr"/>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t>Remote, Product Management</t>
-        </is>
-      </c>
+      <c r="G75" s="2" t="inlineStr"/>
       <c r="H75" s="2" t="inlineStr"/>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/nexamind-gmbh/freelance-senior-ai-product-manager-berlin-73613</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7520997</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -3714,17 +3714,17 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Senior Full-Stack-Entwickler:in React / TypeScript / .NET  100 % Remote, KI-First</t>
+          <t>Senior Python Developer - Django (m/w/d)</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>yourMAIL GmbH</t>
+          <t>sync.blue® GmbH</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Haltern am See</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="J76" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/yourmail-gmbh/senior-full-stack-entwicklerin-react-typescript-net-100-remote-ki-first-berlin-21152</t>
+          <t>https://www.arbeitnow.com/jobs/companies/syncblue-gmbh/senior-python-developer-django-haltern-am-see-16238</t>
         </is>
       </c>
       <c r="K76" s="4" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Senior Frontend-Entwickler:in React / TypeScript, 100 % Remote, KI-First</t>
+          <t>Freelance Senior AI Product Manager</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>yourMAIL GmbH</t>
+          <t>nexamind GmbH</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -3778,13 +3778,13 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>berufserfahren</t>
+          <t>Freelance, professional / experienced</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Remote, Software Development</t>
+          <t>Remote, Product Management</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr"/>
@@ -3795,7 +3795,7 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/yourmail-gmbh/senior-frontend-entwicklerin-react-typescript-100-remote-ki-first-berlin-288218</t>
+          <t>https://www.arbeitnow.com/jobs/companies/nexamind-gmbh/freelance-senior-ai-product-manager-berlin-73613</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -3812,24 +3812,28 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Full-Stack Entwickler (m/w/d) - .NET 100% Remote</t>
+          <t>Senior Full-Stack-Entwickler:in React / TypeScript / .NET  100 % Remote, KI-First</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>FNTIO</t>
+          <t>yourMAIL GmbH</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>Frankfurt am Main</t>
-        </is>
-      </c>
-      <c r="E78" s="4" t="inlineStr"/>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
       <c r="F78" s="4" t="inlineStr"/>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>Remote, Consulting, Engineering</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr"/>
@@ -3840,7 +3844,7 @@
       </c>
       <c r="J78" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/fntio/full-stack-entwickler-net-100-remote-frankfurt-am-main-122380</t>
+          <t>https://www.arbeitnow.com/jobs/companies/yourmail-gmbh/senior-full-stack-entwicklerin-react-typescript-net-100-remote-ki-first-berlin-21152</t>
         </is>
       </c>
       <c r="K78" s="4" t="inlineStr">
@@ -3857,12 +3861,12 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Frontend-Entwickler:in React / TypeScript, 100 % Remote, KI-First</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Phantasma Labs</t>
+          <t>yourMAIL GmbH</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -3870,11 +3874,15 @@
           <t>Berlin</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr"/>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
       <c r="F79" s="2" t="inlineStr"/>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Remote, Engineering</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr"/>
@@ -3885,7 +3893,7 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/phantasma-labs/machine-learning-engineer-berlin-303955</t>
+          <t>https://www.arbeitnow.com/jobs/companies/yourmail-gmbh/senior-frontend-entwicklerin-react-typescript-100-remote-ki-first-berlin-288218</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -3902,28 +3910,24 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Technical Data Manager (m/w/d)</t>
+          <t>Full-Stack Entwickler (m/w/d) - .NET 100% Remote</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>BMF Media Information Technology GmbH</t>
+          <t>FNTIO</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>Augsburg</t>
-        </is>
-      </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>berufserfahren</t>
-        </is>
-      </c>
+          <t>Frankfurt am Main</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr"/>
       <c r="F80" s="4" t="inlineStr"/>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>Remote, Technical Documentation</t>
+          <t>Remote, Consulting, Engineering</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr"/>
@@ -3934,7 +3938,7 @@
       </c>
       <c r="J80" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/bmf-media-information-technology-gmbh/technical-data-manager-augsburg-42188</t>
+          <t>https://www.arbeitnow.com/jobs/companies/fntio/full-stack-entwickler-net-100-remote-frankfurt-am-main-122380</t>
         </is>
       </c>
       <c r="K80" s="4" t="inlineStr">
@@ -3951,28 +3955,24 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Data Integration &amp; API Engineer m/w/d - Bi &amp; Data Automation</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>loyos bi GmbH</t>
+          <t>Phantasma Labs</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Hamburg</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>berufserfahren</t>
-        </is>
-      </c>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr"/>
       <c r="F81" s="2" t="inlineStr"/>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Remote, Software Development</t>
+          <t>Remote, Engineering</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr"/>
@@ -3983,7 +3983,7 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/loyos-bi-gmbh/data-integration-api-engineer-bi-data-automation-hamburg-66228</t>
+          <t>https://www.arbeitnow.com/jobs/companies/phantasma-labs/machine-learning-engineer-berlin-303955</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -4000,28 +4000,28 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Technical Data Manager (m/w/d)</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Coding Partners</t>
+          <t>BMF Media Information Technology GmbH</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>professional / experienced</t>
+          <t>berufserfahren</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr"/>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>Remote, Software Development</t>
+          <t>Remote, Technical Documentation</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr"/>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="J82" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/coding-partners/senior-full-stack-engineer-berlin-391720</t>
+          <t>https://www.arbeitnow.com/jobs/companies/bmf-media-information-technology-gmbh/technical-data-manager-augsburg-42188</t>
         </is>
       </c>
       <c r="K82" s="4" t="inlineStr">
@@ -4049,17 +4049,17 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Laravel Developer (m/w/d) - AI-First PropTech</t>
+          <t>Data Integration &amp; API Engineer m/w/d - Bi &amp; Data Automation</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Immovara GmbH</t>
+          <t>loyos bi GmbH</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Korntal-Münchingen</t>
+          <t>Hamburg</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/immovara-gmbh/laravel-developer-ai-first-proptech-korntal-munchingen-471269</t>
+          <t>https://www.arbeitnow.com/jobs/companies/loyos-bi-gmbh/data-integration-api-engineer-bi-data-automation-hamburg-66228</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -4098,22 +4098,22 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Fullstack Softwareentwickler (m/w/d)</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>TecFox GmbH</t>
+          <t>Coding Partners</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Braunschweig</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>berufserfahren</t>
+          <t>professional / experienced</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr"/>
@@ -4130,7 +4130,7 @@
       </c>
       <c r="J84" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/tecfox-gmbh/fullstack-softwareentwickler-braunschweig-405178</t>
+          <t>https://www.arbeitnow.com/jobs/companies/coding-partners/senior-full-stack-engineer-berlin-391720</t>
         </is>
       </c>
       <c r="K84" s="4" t="inlineStr">
@@ -4147,17 +4147,17 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Frontend Softwareentwickler (m/w/d)</t>
+          <t>Laravel Developer (m/w/d) - AI-First PropTech</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>TecFox GmbH</t>
+          <t>Immovara GmbH</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Braunschweig</t>
+          <t>Korntal-Münchingen</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/tecfox-gmbh/frontend-softwareentwickler-braunschweig-341792</t>
+          <t>https://www.arbeitnow.com/jobs/companies/immovara-gmbh/laravel-developer-ai-first-proptech-korntal-munchingen-471269</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -4196,17 +4196,17 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Fullstack-Developer*in (m/w/d) Web &amp; AI Automation</t>
+          <t>Fullstack Softwareentwickler (m/w/d)</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>NeoBird Digital</t>
+          <t>TecFox GmbH</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Nuremberg</t>
+          <t>Braunschweig</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="J86" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/neobird-digital/fullstack-developerin-web-ai-automation-nuremberg-157752</t>
+          <t>https://www.arbeitnow.com/jobs/companies/tecfox-gmbh/fullstack-softwareentwickler-braunschweig-405178</t>
         </is>
       </c>
       <c r="K86" s="4" t="inlineStr">
@@ -4245,24 +4245,28 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer / Backend &amp; Frontend - Bootstrapped SaaS Startup (m/w/d) remote in EU</t>
+          <t>Frontend Softwareentwickler (m/w/d)</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>DatAds</t>
+          <t>TecFox GmbH</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Cologne</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr"/>
+          <t>Braunschweig</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
       <c r="F87" s="2" t="inlineStr"/>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Remote, IT</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr"/>
@@ -4273,7 +4277,7 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-bootstrapped-saas-startup-remote-in-eu-cologne-82307</t>
+          <t>https://www.arbeitnow.com/jobs/companies/tecfox-gmbh/frontend-softwareentwickler-braunschweig-341792</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -4290,24 +4294,28 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer / Rest APIs / Cloud / TailwindCSS / SaaS Startup (m/w/d) remote in EU</t>
+          <t>Fullstack-Developer*in (m/w/d) Web &amp; AI Automation</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>DatAds</t>
+          <t>NeoBird Digital</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>Cologne</t>
-        </is>
-      </c>
-      <c r="E88" s="4" t="inlineStr"/>
+          <t>Nuremberg</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
       <c r="F88" s="4" t="inlineStr"/>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>Remote, IT</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr"/>
@@ -4318,7 +4326,7 @@
       </c>
       <c r="J88" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-bootstrapped-saas-startup-remote-in-eu-cologne-38634</t>
+          <t>https://www.arbeitnow.com/jobs/companies/neobird-digital/fullstack-developerin-web-ai-automation-nuremberg-157752</t>
         </is>
       </c>
       <c r="K88" s="4" t="inlineStr">
@@ -4335,7 +4343,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer / Node.js / TypeScript / React / Azure - AdTech SaaS Startup (m/w/d) remote</t>
+          <t>Full-Stack Software Engineer / Backend &amp; Frontend - Bootstrapped SaaS Startup (m/w/d) remote in EU</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -4363,7 +4371,7 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-adtech-saas-startup-remote-cologne-263746</t>
+          <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-bootstrapped-saas-startup-remote-in-eu-cologne-82307</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -4380,24 +4388,20 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Senior DevOps / Platform Engineer (f/m/x)</t>
+          <t>Full-Stack Software Engineer / Rest APIs / Cloud / TailwindCSS / SaaS Startup (m/w/d) remote in EU</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>MAIA</t>
+          <t>DatAds</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>Leipzig</t>
-        </is>
-      </c>
-      <c r="E90" s="4" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
+          <t>Cologne</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr"/>
       <c r="F90" s="4" t="inlineStr"/>
       <c r="G90" s="4" t="inlineStr">
         <is>
@@ -4412,7 +4416,7 @@
       </c>
       <c r="J90" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/maia/senior-devops-platform-engineer-leipzig-388068</t>
+          <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-bootstrapped-saas-startup-remote-in-eu-cologne-38634</t>
         </is>
       </c>
       <c r="K90" s="4" t="inlineStr">
@@ -4424,40 +4428,40 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer AI Infrastructure</t>
+          <t>Full-Stack Software Engineer / Node.js / TypeScript / React / Azure - AdTech SaaS Startup (m/w/d) remote</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Andromeda Cluster</t>
+          <t>DatAds</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Cologne</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr"/>
       <c r="F91" s="2" t="inlineStr"/>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>design, training, technical, software, code, manager, financial, cloud, management, lead, senior, operations, reliability, go, health, engineer, engineering, linux, digital nomad</t>
+          <t>Remote, IT</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr"/>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-senior-site-reliability-engineer-ai-infrastructure-andromeda-cluster-1131375</t>
+          <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-adtech-saas-startup-remote-cologne-263746</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -4469,40 +4473,44 @@
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Senior Financial Analyst Digital Assets</t>
+          <t>Senior DevOps / Platform Engineer (f/m/x)</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>Exodus Movement Inc.</t>
+          <t>MAIA</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E92" s="4" t="inlineStr"/>
+          <t>Leipzig</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
       <c r="F92" s="4" t="inlineStr"/>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>analyst, cryptocurrency, support, financial, investment, finance, senior, non tech</t>
+          <t>Remote, IT</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr"/>
       <c r="I92" s="4" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J92" s="5" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-senior-financial-analyst-digital-assets-exodus-movement-inc-1131374</t>
+          <t>https://www.arbeitnow.com/jobs/companies/maia/senior-devops-platform-engineer-leipzig-388068</t>
         </is>
       </c>
       <c r="K92" s="4" t="inlineStr">
@@ -4519,24 +4527,24 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Front End Full Stack Developer</t>
+          <t>Senior Site Reliability Engineer AI Infrastructure</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Honor Foods</t>
+          <t>Andromeda Cluster</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Philadelphia, PA</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr"/>
       <c r="F93" s="2" t="inlineStr"/>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>developer, front-end, ui, code, web, operational, backend, digital nomad</t>
+          <t>design, training, technical, software, code, manager, financial, cloud, management, lead, senior, operations, reliability, go, health, engineer, engineering, linux, digital nomad</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr"/>
@@ -4547,7 +4555,7 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-front-end-full-stack-developer-honor-foods-1131370</t>
+          <t>https://remoteOK.com/remote-jobs/remote-senior-site-reliability-engineer-ai-infrastructure-andromeda-cluster-1131375</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -4564,10 +4572,14 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Wing Assistant: Full-Stack Developer</t>
-        </is>
-      </c>
-      <c r="C94" s="4" t="inlineStr"/>
+          <t>Senior Financial Analyst Digital Assets</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>Exodus Movement Inc.</t>
+        </is>
+      </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
           <t>Remote</t>
@@ -4575,16 +4587,20 @@
       </c>
       <c r="E94" s="4" t="inlineStr"/>
       <c r="F94" s="4" t="inlineStr"/>
-      <c r="G94" s="4" t="inlineStr"/>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t>analyst, cryptocurrency, support, financial, investment, finance, senior, non tech</t>
+        </is>
+      </c>
       <c r="H94" s="4" t="inlineStr"/>
       <c r="I94" s="4" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J94" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/wing-assistant-full-stack-developer</t>
+          <t>https://remoteOK.com/remote-jobs/remote-senior-financial-analyst-digital-assets-exodus-movement-inc-1131374</t>
         </is>
       </c>
       <c r="K94" s="4" t="inlineStr">
@@ -4601,27 +4617,35 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Qventus: Product Designer</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr"/>
+          <t>Front End Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Honor Foods</t>
+        </is>
+      </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Philadelphia, PA</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr"/>
       <c r="F95" s="2" t="inlineStr"/>
-      <c r="G95" s="2" t="inlineStr"/>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>developer, front-end, ui, code, web, operational, backend, digital nomad</t>
+        </is>
+      </c>
       <c r="H95" s="2" t="inlineStr"/>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/qventus-product-designer</t>
+          <t>https://remoteOK.com/remote-jobs/remote-front-end-full-stack-developer-honor-foods-1131370</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -4638,7 +4662,7 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Socure: Senior Product Marketing Manager</t>
+          <t>Wing Assistant: Full-Stack Developer</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr"/>
@@ -4658,7 +4682,7 @@
       </c>
       <c r="J96" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/socure-senior-product-marketing-manager</t>
+          <t>https://weworkremotely.com/remote-jobs/wing-assistant-full-stack-developer</t>
         </is>
       </c>
       <c r="K96" s="4" t="inlineStr">
@@ -4675,7 +4699,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Blueprint: Product Designer</t>
+          <t>Qventus: Product Designer</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr"/>
@@ -4695,7 +4719,7 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/blueprint-product-designer</t>
+          <t>https://weworkremotely.com/remote-jobs/qventus-product-designer</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -4712,7 +4736,7 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Interop Labs: Product Marketing Manager</t>
+          <t>Socure: Senior Product Marketing Manager</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr"/>
@@ -4732,7 +4756,7 @@
       </c>
       <c r="J98" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/interop-labs-product-marketing-manager</t>
+          <t>https://weworkremotely.com/remote-jobs/socure-senior-product-marketing-manager</t>
         </is>
       </c>
       <c r="K98" s="4" t="inlineStr">
@@ -4749,17 +4773,13 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Link</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
+          <t>Blueprint: Product Designer</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr"/>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Toronto, Remote in Canada</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr"/>
@@ -4768,12 +4788,12 @@
       <c r="H99" s="2" t="inlineStr"/>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=6447175</t>
+          <t>https://weworkremotely.com/remote-jobs/blueprint-product-designer</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -4790,17 +4810,13 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="C100" s="4" t="inlineStr">
-        <is>
-          <t>Reddit</t>
-        </is>
-      </c>
+          <t>Interop Labs: Product Marketing Manager</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr"/>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Remote - Ontario, Canada</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr"/>
@@ -4809,12 +4825,12 @@
       <c r="H100" s="4" t="inlineStr"/>
       <c r="I100" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J100" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/6960833</t>
+          <t>https://weworkremotely.com/remote-jobs/interop-labs-product-marketing-manager</t>
         </is>
       </c>
       <c r="K100" s="4" t="inlineStr">
@@ -4831,17 +4847,17 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Full Stack Engineer, Link</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Toronto, Remote in Canada</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr"/>
@@ -4855,10 +4871,92 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
+          <t>https://stripe.com/jobs/search?gh_jid=6447175</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>Remote - Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr"/>
+      <c r="F102" s="4" t="inlineStr"/>
+      <c r="G102" s="4" t="inlineStr"/>
+      <c r="H102" s="4" t="inlineStr"/>
+      <c r="I102" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J102" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/6960833</t>
+        </is>
+      </c>
+      <c r="K102" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr"/>
+      <c r="F103" s="2" t="inlineStr"/>
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr"/>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
           <t>https://job-boards.greenhouse.io/reddit/jobs/6960831</t>
         </is>
       </c>
-      <c r="K101" s="2" t="inlineStr">
+      <c r="K103" s="2" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
@@ -4867,53 +4965,54 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId49"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/remote_jobs.xlsx
+++ b/remote_jobs.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K103"/>
+  <dimension ref="A1:K120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -523,33 +523,33 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>AI Developer (Claude + AWS)</t>
+          <t>Werkstudent:in KI Marketing (m/w/d)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Datavent</t>
+          <t>laria.ai</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Hamburg</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>professional / experienced</t>
+          <t>Working student, berufseinstieg</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Remote, Software Development</t>
+          <t>Remote, Online Marketing</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -560,39 +560,39 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/datavent/ai-developer-claude-aws-hamburg-22354</t>
+          <t>https://www.arbeitnow.com/jobs/companies/lariaai/werkstudentin-ki-marketing-berlin-9847</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Python Software Engineer, Backend &amp; APIs - Remote</t>
+          <t>Laravel Developer (m/w/d) - AI-First PropTech</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>dexter health</t>
+          <t>Immovara GmbH</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Cologne</t>
+          <t>Korntal-Münchingen</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>professional / experienced</t>
+          <t>berufserfahren</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr"/>
@@ -609,537 +609,485 @@
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/python-software-engineer-backend-apis-remote-cologne-284750</t>
+          <t>https://www.arbeitnow.com/jobs/companies/immovara-gmbh/laravel-developer-ai-first-proptech-korntal-munchingen-239743</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Fullstack Developer (m/w/d) REMOTE //  UX / Python / Vue.js</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Pont Connects e.K.</t>
-        </is>
-      </c>
+          <t>Machine Learning (ML) Engineer - Applied</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Düsseldorf</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Remote, IT</t>
+          <t>machine learning, artificial intelligence, python, cplusplus, startup</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>WorkingNomads</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/pont-connects-ek/fullstack-developer-remote-ux-python-vuejs-dusseldorf-371903</t>
+          <t>https://www.workingnomads.com/job/go/1578553/</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Lemon.io</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Americas, Europe, Asia, Oceania</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>full_time</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Devops</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>.Net, android, AWS, azure, C, C#, C++, data science, golang, ios, java, javascript, kubernetes, node.js, php, python, react, ruby/rails, shopify, sql, video, blockchain, AI/ML, automation, react native, rust, unity, spring, data analysis, laravel, solidity, flask, Typescript , terraform, angular , GCP, data engineering, Symfony, startup, marketplace, next.js</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Remotive</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>https://remotive.com/remote-jobs/devops/senior-devops-engineer-2090002</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Backend Engineer, AI Security</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>New York, San Francisco, Seattle, or Remote (US/Canada)</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=7826765</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>M&amp;A Research Analyst</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>EquiMatch GmbH</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Mergers &amp; Acquisitions</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/equimatch-gmbh/ma-research-analyst-berlin-498635</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Backend Engineer, Core Tech, Canada</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, CAN-Remote</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=6567253</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Xsolla: Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr"/>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>WeWorkRemotely</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>https://weworkremotely.com/remote-jobs/xsolla-full-stack-developer</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Backend Engineer, Core Technology</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>US-Remote, Chicago</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr"/>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=6042172</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Dropbox: Staff Fullstack Product Software Engineer, Dash</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr"/>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr"/>
-      <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr"/>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>WeWorkRemotely</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>https://weworkremotely.com/remote-jobs/dropbox-staff-fullstack-product-software-engineer-dash</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Backend Engineer, Developer Experience &amp; Product Platform</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Toronto Canada, San Francisco, Remote in US, Remote in Canada</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=7292520</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Staff Machine Learning Engineer, Ranking and Personalization</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Reddit</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Remote - United States</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7848689</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Commercial Counsel, Crypto</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>New York City, Seattle, San Francisco, Chicago, Atlanta, US-Remote</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr"/>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=7392188</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Senior Rust Consultant / Engineer (m/w/d)</t>
+          <t>Fullstack Engineer, Privy</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Hackstack GmbH</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>berufserfahren</t>
-        </is>
-      </c>
+          <t xml:space="preserve">NYC-Privy, US-Remote </t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Remote, Consulting, Engineering</t>
-        </is>
-      </c>
+      <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/hackstack-gmbh/senior-rust-consultant-engineer-munich-451602</t>
+          <t>https://stripe.com/jobs/search?gh_jid=7091959</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Applied AI Engineer - Remote</t>
+          <t>Machine Learning Engineer, Stripe Assistant</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>dexter health</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Cologne</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
+          <t>Seattle; San Francisco; New York City; Remote</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr"/>
       <c r="F11" s="4" t="inlineStr"/>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Development</t>
-        </is>
-      </c>
+      <c r="G11" s="4" t="inlineStr"/>
       <c r="H11" s="4" t="inlineStr"/>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/applied-ai-engineer-remote-cologne-2870</t>
+          <t>https://stripe.com/jobs/search?gh_jid=7629052</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Python Backend Engineer - Remote</t>
+          <t>Machine Learning Manager, Feed Relevance</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>dexter health</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Cologne</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Remote, Development</t>
-        </is>
-      </c>
+      <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/python-backend-engineer-remote-cologne-34228</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7802495</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>AI Engineer (LLM Products) - Remote</t>
+          <t>Senior Machine Learning Engineer, GenAI Security</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>dexter health</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Cologne</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr"/>
       <c r="F13" s="4" t="inlineStr"/>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Development</t>
-        </is>
-      </c>
+      <c r="G13" s="4" t="inlineStr"/>
       <c r="H13" s="4" t="inlineStr"/>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/ai-engineer-llm-products-remote-cologne-236027</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7891887</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Backend Python Engineer (APIs, Databases &amp; Cloud) - Remote</t>
+          <t>Senior Staff Machine Learning Engineer, Feed Relevance</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>dexter health</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Cologne</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr"/>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Remote, Development</t>
-        </is>
-      </c>
+      <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/backend-python-engineer-apis-databases-cloud-remote-cologne-274767</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7791994</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Toptal: QA Automation Engineer</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr"/>
+          <t>Senior Staff Machine Learning Engineer, ML Understanding</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr"/>
@@ -1148,35 +1096,39 @@
       <c r="H15" s="4" t="inlineStr"/>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/toptal-qa-automation-engineer-1</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7847148</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Opensea: Staff Product Designer</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr"/>
+          <t>Staff Machine Learning Engineer, Ads Measurement Modeling</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -1185,35 +1137,39 @@
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/opensea-staff-product-designer</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7890096</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Mutt Data: Devops</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr"/>
+          <t>Staff Machine Learning Engineer, AI Serving</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr"/>
@@ -1222,35 +1178,39 @@
       <c r="H17" s="4" t="inlineStr"/>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/mutt-data-devops</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7886459</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Holywater: Full-Stack Developer</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr"/>
+          <t>Senior Software Engineer (L3) - Full Stack</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote - US</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
@@ -1259,236 +1219,280 @@
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/holywater-full-stack-developer</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7738955</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Qventus: DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr"/>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="4" t="inlineStr"/>
-      <c r="G19" s="4" t="inlineStr"/>
-      <c r="H19" s="4" t="inlineStr"/>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>WeWorkRemotely</t>
-        </is>
-      </c>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>https://weworkremotely.com/remote-jobs/qventus-devops-engineer</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>AI Developer (Claude + AWS)</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Datavent</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Hamburg</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Remote, Software Development</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/datavent/ai-developer-claude-aws-hamburg-22354</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Visualis: Senior Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr"/>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr"/>
-      <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr"/>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>WeWorkRemotely</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>https://weworkremotely.com/remote-jobs/visualis-senior-full-stack-developer</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Python Software Engineer, Backend &amp; APIs - Remote</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>dexter health</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Cologne</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr"/>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Software Development</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr"/>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/python-software-engineer-backend-apis-remote-cologne-284750</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>GitLab</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Bangalore</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr"/>
-      <c r="F21" s="4" t="inlineStr"/>
-      <c r="G21" s="4" t="inlineStr"/>
-      <c r="H21" s="4" t="inlineStr"/>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8517564002</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Fullstack Developer (m/w/d) REMOTE //  UX / Python / Vue.js</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Pont Connects e.K.</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Düsseldorf</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Remote, IT</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/pont-connects-ek/fullstack-developer-remote-ux-python-vuejs-dusseldorf-371903</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Backend Engineer, Analytics Instrumentation (Golang)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>GitLab</t>
+          <t>Lemon.io</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Remote, India</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr"/>
-      <c r="F22" s="2" t="inlineStr"/>
-      <c r="G22" s="2" t="inlineStr"/>
+          <t>Americas, Europe, Asia, Oceania</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>full_time</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Devops</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>.Net, android, AWS, azure, C, C#, C++, data science, golang, ios, java, javascript, kubernetes, node.js, php, python, react, ruby/rails, shopify, sql, video, blockchain, AI/ML, automation, react native, rust, unity, spring, data analysis, laravel, solidity, flask, Typescript , terraform, angular , GCP, data engineering, Symfony, startup, marketplace, next.js</t>
+        </is>
+      </c>
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>Remotive</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481922002</t>
+          <t>https://remotive.com/remote-jobs/devops/senior-devops-engineer-2090002</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Backend Engineer, Analytics Instrumentation (Golang)</t>
+          <t>M&amp;A Research Analyst</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>GitLab</t>
+          <t>EquiMatch GmbH</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Remote, India</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr"/>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
       <c r="F23" s="4" t="inlineStr"/>
-      <c r="G23" s="4" t="inlineStr"/>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Mergers &amp; Acquisitions</t>
+        </is>
+      </c>
       <c r="H23" s="4" t="inlineStr"/>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481929002</t>
+          <t>https://www.arbeitnow.com/jobs/companies/equimatch-gmbh/ma-research-analyst-berlin-498635</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Backend Engineer, Knowledge Graph (Rust)</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>GitLab</t>
-        </is>
-      </c>
+          <t>Xsolla: Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr"/>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, US</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
@@ -1497,39 +1501,35 @@
       <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8437754002</t>
+          <t>https://weworkremotely.com/remote-jobs/xsolla-full-stack-developer</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Backend Engineer, Knowledge Graph (Rust)</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>GitLab</t>
-        </is>
-      </c>
+          <t>Dropbox: Staff Fullstack Product Software Engineer, Dash</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr"/>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr"/>
@@ -1538,39 +1538,39 @@
       <c r="H25" s="4" t="inlineStr"/>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481958002</t>
+          <t>https://weworkremotely.com/remote-jobs/dropbox-staff-fullstack-product-software-engineer-dash</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Intermediate Backend Engineer (C), Tenant Scale: Git</t>
+          <t>Staff Machine Learning Engineer, Ranking and Personalization</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>GitLab</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
@@ -1584,1240 +1584,1256 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7848689</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Senior Rust Consultant / Engineer (m/w/d)</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Hackstack GmbH</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Remote, Consulting, Engineering</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/hackstack-gmbh/senior-rust-consultant-engineer-munich-451602</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>dexter health</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Cologne</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr"/>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Development</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr"/>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/applied-ai-engineer-remote-cologne-2870</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Python Backend Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>dexter health</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Cologne</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Remote, Development</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/python-backend-engineer-remote-cologne-34228</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>AI Engineer (LLM Products) - Remote</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>dexter health</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Cologne</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr"/>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Development</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr"/>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/ai-engineer-llm-products-remote-cologne-236027</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Backend Python Engineer (APIs, Databases &amp; Cloud) - Remote</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>dexter health</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Cologne</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Remote, Development</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/backend-python-engineer-apis-databases-cloud-remote-cologne-274767</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Toptal: QA Automation Engineer</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr"/>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr"/>
+      <c r="G32" s="4" t="inlineStr"/>
+      <c r="H32" s="4" t="inlineStr"/>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>WeWorkRemotely</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>https://weworkremotely.com/remote-jobs/toptal-qa-automation-engineer-1</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Opensea: Staff Product Designer</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr"/>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>WeWorkRemotely</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>https://weworkremotely.com/remote-jobs/opensea-staff-product-designer</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Mutt Data: Devops</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr"/>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr"/>
+      <c r="F34" s="4" t="inlineStr"/>
+      <c r="G34" s="4" t="inlineStr"/>
+      <c r="H34" s="4" t="inlineStr"/>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>WeWorkRemotely</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>https://weworkremotely.com/remote-jobs/mutt-data-devops</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Holywater: Full-Stack Developer</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr"/>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>WeWorkRemotely</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>https://weworkremotely.com/remote-jobs/holywater-full-stack-developer</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Qventus: DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr"/>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr"/>
+      <c r="F36" s="4" t="inlineStr"/>
+      <c r="G36" s="4" t="inlineStr"/>
+      <c r="H36" s="4" t="inlineStr"/>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>WeWorkRemotely</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>https://weworkremotely.com/remote-jobs/qventus-devops-engineer</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Visualis: Senior Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr"/>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr"/>
+      <c r="F37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>WeWorkRemotely</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>https://weworkremotely.com/remote-jobs/visualis-senior-full-stack-developer</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>GitLab</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Bangalore</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr"/>
+      <c r="F38" s="4" t="inlineStr"/>
+      <c r="G38" s="4" t="inlineStr"/>
+      <c r="H38" s="4" t="inlineStr"/>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8517564002</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Backend Engineer, Analytics Instrumentation (Golang)</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>GitLab</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Remote, India</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481922002</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Backend Engineer, Analytics Instrumentation (Golang)</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>GitLab</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>Remote, India</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr"/>
+      <c r="F40" s="4" t="inlineStr"/>
+      <c r="G40" s="4" t="inlineStr"/>
+      <c r="H40" s="4" t="inlineStr"/>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481929002</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Backend Engineer, Knowledge Graph (Rust)</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>GitLab</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Remote, Canada; Remote, US</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8437754002</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Backend Engineer, Knowledge Graph (Rust)</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>GitLab</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>Remote, India</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr"/>
+      <c r="F42" s="4" t="inlineStr"/>
+      <c r="G42" s="4" t="inlineStr"/>
+      <c r="H42" s="4" t="inlineStr"/>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481958002</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Intermediate Backend Engineer (C), Tenant Scale: Git</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>GitLab</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Remote, India</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr"/>
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr"/>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8497793002</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="K43" s="2" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>Intermediate Backend Engineer, Gitlab Delivery: Upgrades</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D44" s="4" t="inlineStr">
         <is>
           <t>Remote, India</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr"/>
-      <c r="F27" s="4" t="inlineStr"/>
-      <c r="G27" s="4" t="inlineStr"/>
-      <c r="H27" s="4" t="inlineStr"/>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
+      <c r="E44" s="4" t="inlineStr"/>
+      <c r="F44" s="4" t="inlineStr"/>
+      <c r="G44" s="4" t="inlineStr"/>
+      <c r="H44" s="4" t="inlineStr"/>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8463951002</t>
         </is>
       </c>
-      <c r="K27" s="4" t="inlineStr">
+      <c r="K44" s="4" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>Intermediate Backend Engineer, SRM: Security Platform Management</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr"/>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr"/>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr"/>
+      <c r="F45" s="2" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr"/>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8443325002</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="K45" s="2" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>Intermediate Backend Engineer, SSCS: AI Governance</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D46" s="4" t="inlineStr">
         <is>
           <t>Remote, India</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr"/>
-      <c r="F29" s="4" t="inlineStr"/>
-      <c r="G29" s="4" t="inlineStr"/>
-      <c r="H29" s="4" t="inlineStr"/>
-      <c r="I29" s="4" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J29" s="5" t="inlineStr">
+      <c r="E46" s="4" t="inlineStr"/>
+      <c r="F46" s="4" t="inlineStr"/>
+      <c r="G46" s="4" t="inlineStr"/>
+      <c r="H46" s="4" t="inlineStr"/>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8480551002</t>
         </is>
       </c>
-      <c r="K29" s="4" t="inlineStr">
+      <c r="K46" s="4" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>Intermediate Backend Engineer,  SSCS: Supply Chain</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Remote, India</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr"/>
+      <c r="F47" s="2" t="inlineStr"/>
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8480565002</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="K47" s="2" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>Senior AI Engineer</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D48" s="4" t="inlineStr">
         <is>
           <t>Remote, EMEA</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr"/>
-      <c r="F31" s="4" t="inlineStr"/>
-      <c r="G31" s="4" t="inlineStr"/>
-      <c r="H31" s="4" t="inlineStr"/>
-      <c r="I31" s="4" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J31" s="5" t="inlineStr">
+      <c r="E48" s="4" t="inlineStr"/>
+      <c r="F48" s="4" t="inlineStr"/>
+      <c r="G48" s="4" t="inlineStr"/>
+      <c r="H48" s="4" t="inlineStr"/>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8464072002</t>
         </is>
       </c>
-      <c r="K31" s="4" t="inlineStr">
+      <c r="K48" s="4" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>Senior Backend Engineer (AI), Pipeline Execution</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US-Southeast</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr"/>
-      <c r="F32" s="2" t="inlineStr"/>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr"/>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr"/>
+      <c r="F49" s="2" t="inlineStr"/>
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8514945002</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="K49" s="2" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>Senior Backend Engineer, Analytics Instrumentation (Golang)</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D50" s="4" t="inlineStr">
         <is>
           <t>Remote, Canada; Remote, US</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr"/>
-      <c r="F33" s="4" t="inlineStr"/>
-      <c r="G33" s="4" t="inlineStr"/>
-      <c r="H33" s="4" t="inlineStr"/>
-      <c r="I33" s="4" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J33" s="5" t="inlineStr">
+      <c r="E50" s="4" t="inlineStr"/>
+      <c r="F50" s="4" t="inlineStr"/>
+      <c r="G50" s="4" t="inlineStr"/>
+      <c r="H50" s="4" t="inlineStr"/>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8451512002</t>
         </is>
       </c>
-      <c r="K33" s="4" t="inlineStr">
+      <c r="K50" s="4" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>Senior Backend Engineer (C), Tenant Scale: Git</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Remote, India</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr"/>
-      <c r="F34" s="2" t="inlineStr"/>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr"/>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8497791002</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="K51" s="2" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>Senior Backend Engineer, Gitlab Delivery: Runway (Platform Engineering)</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D52" s="4" t="inlineStr">
         <is>
           <t>Remote, Australia; Remote, India; Remote, Ireland; Remote, Japan; Remote, Netherlands; Remote, Singapore; Remote, United Kingdom</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr"/>
-      <c r="F35" s="4" t="inlineStr"/>
-      <c r="G35" s="4" t="inlineStr"/>
-      <c r="H35" s="4" t="inlineStr"/>
-      <c r="I35" s="4" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J35" s="5" t="inlineStr">
+      <c r="E52" s="4" t="inlineStr"/>
+      <c r="F52" s="4" t="inlineStr"/>
+      <c r="G52" s="4" t="inlineStr"/>
+      <c r="H52" s="4" t="inlineStr"/>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8324132002</t>
         </is>
       </c>
-      <c r="K35" s="4" t="inlineStr">
+      <c r="K52" s="4" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>Senior Backend Engineer, Gitlab Delivery: Upgrades</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Remote, India</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="2" t="inlineStr"/>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr"/>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr"/>
+      <c r="F53" s="2" t="inlineStr"/>
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr"/>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8463933002</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="K53" s="2" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>Senior Backend Engineer(Go), Continuous Delivery</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D54" s="4" t="inlineStr">
         <is>
           <t>Remote, India</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr"/>
-      <c r="F37" s="4" t="inlineStr"/>
-      <c r="G37" s="4" t="inlineStr"/>
-      <c r="H37" s="4" t="inlineStr"/>
-      <c r="I37" s="4" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J37" s="5" t="inlineStr">
+      <c r="E54" s="4" t="inlineStr"/>
+      <c r="F54" s="4" t="inlineStr"/>
+      <c r="G54" s="4" t="inlineStr"/>
+      <c r="H54" s="4" t="inlineStr"/>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8488966002</t>
         </is>
       </c>
-      <c r="K37" s="4" t="inlineStr">
+      <c r="K54" s="4" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>Senior Backend Engineer(Golang),Software Supply Chain Security: Auth Infrastructure</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Remote, Americas; Remote, APAC; Remote, Canada</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr"/>
-      <c r="F38" s="2" t="inlineStr"/>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr"/>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr"/>
+      <c r="F55" s="2" t="inlineStr"/>
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8157520002</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="K55" s="2" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>Senior Backend Engineer (RoR), AST: Secret Detection</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="D56" s="4" t="inlineStr">
         <is>
           <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr"/>
-      <c r="F39" s="4" t="inlineStr"/>
-      <c r="G39" s="4" t="inlineStr"/>
-      <c r="H39" s="4" t="inlineStr"/>
-      <c r="I39" s="4" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J39" s="5" t="inlineStr">
+      <c r="E56" s="4" t="inlineStr"/>
+      <c r="F56" s="4" t="inlineStr"/>
+      <c r="G56" s="4" t="inlineStr"/>
+      <c r="H56" s="4" t="inlineStr"/>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8432262002</t>
         </is>
       </c>
-      <c r="K39" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer (RoR/Go), SSCS: Pipeline Security</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>GitLab</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr"/>
-      <c r="F40" s="2" t="inlineStr"/>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr"/>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8432221002</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer (RoR), SSCS: Authorization</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>GitLab</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr"/>
-      <c r="F41" s="4" t="inlineStr"/>
-      <c r="G41" s="4" t="inlineStr"/>
-      <c r="H41" s="4" t="inlineStr"/>
-      <c r="I41" s="4" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J41" s="5" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8457315002</t>
-        </is>
-      </c>
-      <c r="K41" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer (Ruby or Golang), Tenant Scale; Cells Infrastructure</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>GitLab</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Remote, APAC; Remote, Canada; Remote, EMEA; Remote, US</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8437148002</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer, SSCS: AI Governance</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>GitLab</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>Remote, India</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="inlineStr"/>
-      <c r="F43" s="4" t="inlineStr"/>
-      <c r="G43" s="4" t="inlineStr"/>
-      <c r="H43" s="4" t="inlineStr"/>
-      <c r="I43" s="4" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J43" s="5" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480544002</t>
-        </is>
-      </c>
-      <c r="K43" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer,  SSCS: Supply Chain</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>GitLab</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>Remote, India</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr"/>
-      <c r="F44" s="2" t="inlineStr"/>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr"/>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480580002</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>Senior Fullstack Engineer (TypeScript), AI Engineering: Editor Extensions</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>GitLab</t>
-        </is>
-      </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>Remote, APAC; Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US-Southeast</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr"/>
-      <c r="F45" s="4" t="inlineStr"/>
-      <c r="G45" s="4" t="inlineStr"/>
-      <c r="H45" s="4" t="inlineStr"/>
-      <c r="I45" s="4" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J45" s="5" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8452278002</t>
-        </is>
-      </c>
-      <c r="K45" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>Staff Backend Engineer, Analytics Instrumentation (Golang)</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>GitLab</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>Remote, India</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr"/>
-      <c r="F46" s="2" t="inlineStr"/>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr"/>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8508027002</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>Staff Backend Engineer, AST: Composition Analysis</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>GitLab</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Australia; Remote, Canada; Remote, India; Remote, Ireland; Remote, Israel; Remote, Japan; Remote, Netherlands; Remote, New Zealand; Remote, United Kingdom; Remote, US</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr"/>
-      <c r="F47" s="4" t="inlineStr"/>
-      <c r="G47" s="4" t="inlineStr"/>
-      <c r="H47" s="4" t="inlineStr"/>
-      <c r="I47" s="4" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J47" s="5" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8478364002</t>
-        </is>
-      </c>
-      <c r="K47" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Staff Backend Engineer, Developer Experience</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>GitLab</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>Remote, Canada; Remote, United Kingdom; Remote, US</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr"/>
-      <c r="F48" s="2" t="inlineStr"/>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr"/>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8490477002</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>Staff Backend Engineer, Gitlab Delivery: Upgrades</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>GitLab</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr">
-        <is>
-          <t>Remote, India</t>
-        </is>
-      </c>
-      <c r="E49" s="4" t="inlineStr"/>
-      <c r="F49" s="4" t="inlineStr"/>
-      <c r="G49" s="4" t="inlineStr"/>
-      <c r="H49" s="4" t="inlineStr"/>
-      <c r="I49" s="4" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J49" s="5" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8463922002</t>
-        </is>
-      </c>
-      <c r="K49" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>Staff Backend Engineer (Go), Continuous Delivery</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>GitLab</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>Remote, India</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr"/>
-      <c r="F50" s="2" t="inlineStr"/>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr"/>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8488961002</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>Staff Backend Engineer (Go), Software Supply Chain Security: Secrets Management</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>GitLab</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="inlineStr"/>
-      <c r="F51" s="4" t="inlineStr"/>
-      <c r="G51" s="4" t="inlineStr"/>
-      <c r="H51" s="4" t="inlineStr"/>
-      <c r="I51" s="4" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J51" s="5" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8432235002</t>
-        </is>
-      </c>
-      <c r="K51" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>Staff Backend Engineer, Knowledge Graph (Rust)</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>GitLab</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>Remote, India</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr"/>
-      <c r="F52" s="2" t="inlineStr"/>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr"/>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481945002</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>Staff Backend Engineer,  Software Supply Chain Security</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>GitLab</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>Remote, India</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="inlineStr"/>
-      <c r="F53" s="4" t="inlineStr"/>
-      <c r="G53" s="4" t="inlineStr"/>
-      <c r="H53" s="4" t="inlineStr"/>
-      <c r="I53" s="4" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J53" s="5" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480559002</t>
-        </is>
-      </c>
-      <c r="K53" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>Staff Backend Engineer, SSCS: AI Governance</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>GitLab</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>Remote, India</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr"/>
-      <c r="F54" s="2" t="inlineStr"/>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr"/>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480531002</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>Staff Backend (Python) Engineer, AI Engineering:Duo Chat</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>GitLab</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Americas; Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr"/>
-      <c r="F55" s="4" t="inlineStr"/>
-      <c r="G55" s="4" t="inlineStr"/>
-      <c r="H55" s="4" t="inlineStr"/>
-      <c r="I55" s="4" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J55" s="5" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8450446002</t>
-        </is>
-      </c>
-      <c r="K55" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Product Software Engineer</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Dropbox</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>Remote - Poland</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr"/>
-      <c r="F56" s="2" t="inlineStr"/>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr"/>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>https://jobs.dropbox.com/listing/6449719?gh_jid=6449719</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
+      <c r="K56" s="4" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
@@ -2831,52 +2847,36 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Backend Engineer (RoR/Go), SSCS: Pipeline Security</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Dry Ground AI</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Brazil, Colombia, Philippines</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>full_time</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>api, cloud, fullstack, python, AI/ML, automation, research, CI/CD, TensorFlow, spark, NLP, CMS, Pytorch, REST</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>$40- $60k</t>
-        </is>
-      </c>
+          <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr"/>
+      <c r="F57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr"/>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>Remotive</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>https://remotive.com/remote-jobs/artificial-intelligence/ai-engineer-2089958</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8432221002</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2888,52 +2888,36 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Senior Independent AI Engineer / Architect</t>
+          <t>Senior Backend Engineer (RoR), SSCS: Authorization</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>A.Team</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Americas, Europe, Israel</t>
-        </is>
-      </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>contract</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>Software Development</t>
-        </is>
-      </c>
-      <c r="G58" s="4" t="inlineStr">
-        <is>
-          <t>go, UI/UX, wordpress, chat, apple, testing, catalyst</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>$120 - $170 /hour</t>
-        </is>
-      </c>
+          <t>Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr"/>
+      <c r="F58" s="4" t="inlineStr"/>
+      <c r="G58" s="4" t="inlineStr"/>
+      <c r="H58" s="4" t="inlineStr"/>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t>Remotive</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>https://remotive.com/remote-jobs/software-development/senior-independent-ai-engineer-architect-1919266</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8457315002</t>
         </is>
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2945,52 +2929,36 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Senior Independent Software Developer</t>
+          <t>Senior Backend Engineer (Ruby or Golang), Tenant Scale; Cells Infrastructure</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>A.Team</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Americas, Europe, Israel</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>contract</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>Software Development</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>go, wordpress, chat, apple, testing, catalyst</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>$90 - $150 /hour</t>
-        </is>
-      </c>
+          <t>Remote, APAC; Remote, Canada; Remote, EMEA; Remote, US</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr"/>
+      <c r="F59" s="2" t="inlineStr"/>
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr"/>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>Remotive</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>https://remotive.com/remote-jobs/software-development/senior-independent-software-developer-1919265</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8437148002</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3002,48 +2970,36 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Senior Full-stack React Developer</t>
+          <t>Senior Backend Engineer, SSCS: AI Governance</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Lemon.io</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Americas, Europe, Asia, Oceania</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>contract</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>Software Development</t>
-        </is>
-      </c>
-      <c r="G60" s="4" t="inlineStr">
-        <is>
-          <t>.Net, android, AWS, azure, backend, C, C#, C++, data science, fullstack, golang, ios, java, javascript, node.js, php, python, react, react js, ruby/rails, shopify, video, blockchain, AI/ML, react native, rust, unity, spring, data analysis, laravel, solidity, flask, Typescript , angular , GCP, data engineering, Symfony, startup, marketplace, next.js</t>
-        </is>
-      </c>
+          <t>Remote, India</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr"/>
+      <c r="F60" s="4" t="inlineStr"/>
+      <c r="G60" s="4" t="inlineStr"/>
       <c r="H60" s="4" t="inlineStr"/>
       <c r="I60" s="4" t="inlineStr">
         <is>
-          <t>Remotive</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J60" s="5" t="inlineStr">
         <is>
-          <t>https://remotive.com/remote-jobs/software-development/senior-full-stack-react-developer-2088711</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480544002</t>
         </is>
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3055,52 +3011,36 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Tech Lead Full-Stack Rails Engineer</t>
+          <t>Senior Backend Engineer,  SSCS: Supply Chain</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Mitre Media</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>USA, Canada, USA timezones</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>full_time</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>Software Development</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>api, CSS, docker, elasticsearch, fullstack, html, javascript, kubernetes, postgresql, react, ror, ruby/rails, AI/ML, CAD, advertising, Redis, ES6, web applications, MySQL, NLP, fintech, Micro services, github, system architecture</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>$170k - $200k</t>
-        </is>
-      </c>
+          <t>Remote, India</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr"/>
+      <c r="F61" s="2" t="inlineStr"/>
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr"/>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>Remotive</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>https://remotive.com/remote-jobs/software-development/tech-lead-full-stack-rails-engineer-2069746</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480580002</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3112,52 +3052,36 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Senior Frontend Developer</t>
+          <t>Senior Fullstack Engineer (TypeScript), AI Engineering: Editor Extensions</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Sanctuary Computer</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>LATAM, Asia</t>
-        </is>
-      </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>contract</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>Software Development</t>
-        </is>
-      </c>
-      <c r="G62" s="4" t="inlineStr">
-        <is>
-          <t>api, backend, CSS, ecommerce, frontend, fullstack, graphql, postgresql, redux, security, seo, shopify, open source, paas, product management, documentation, mentoring, Typescript , Redis, web applications, cypress, data visualization, firebase, IoT, engineering management, runtime, responsive, prismic, testing, next.js, CMS, jest, REST, web sockets, performance optimization</t>
-        </is>
-      </c>
-      <c r="H62" s="4" t="inlineStr">
-        <is>
-          <t>$80k - $120k</t>
-        </is>
-      </c>
+          <t>Remote, APAC; Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US-Southeast</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr"/>
+      <c r="F62" s="4" t="inlineStr"/>
+      <c r="G62" s="4" t="inlineStr"/>
+      <c r="H62" s="4" t="inlineStr"/>
       <c r="I62" s="4" t="inlineStr">
         <is>
-          <t>Remotive</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
-          <t>https://remotive.com/remote-jobs/software-development/senior-frontend-developer-2088707</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8452278002</t>
         </is>
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3169,48 +3093,36 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Fullstack Developer (US - ET)</t>
+          <t>Staff Backend Engineer, Analytics Instrumentation (Golang)</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Chooose</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>full_time</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>Software Development</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>api, azure, fullstack, python, react, saas, AI/ML, project management, documentation, Typescript , computer science, diversity, insurance</t>
-        </is>
-      </c>
+          <t>Remote, India</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr"/>
+      <c r="F63" s="2" t="inlineStr"/>
+      <c r="G63" s="2" t="inlineStr"/>
       <c r="H63" s="2" t="inlineStr"/>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>Remotive</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>https://remotive.com/remote-jobs/software-development/fullstack-developer-us-et-2088706</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8508027002</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3222,17 +3134,17 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning Manager, Notifications Relevance</t>
+          <t>Staff Backend Engineer, AST: Composition Analysis</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Remote, Australia; Remote, Canada; Remote, India; Remote, Ireland; Remote, Israel; Remote, Japan; Remote, Netherlands; Remote, New Zealand; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr"/>
@@ -3246,12 +3158,12 @@
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7846885</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8478364002</t>
         </is>
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3263,17 +3175,17 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Senior Staff ML Engineer, Search &amp; Recommendation</t>
+          <t>Staff Backend Engineer, Developer Experience</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Remote, Canada; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr"/>
@@ -3287,12 +3199,12 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7833622</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8490477002</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3304,17 +3216,17 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Staff Backend Engineer, Gitlab Delivery: Upgrades</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Remote - US</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr"/>
@@ -3328,12 +3240,12 @@
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7059734</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8463922002</t>
         </is>
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3345,17 +3257,17 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Staff Backend Engineer (Go), Continuous Delivery</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Remote - US</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr"/>
@@ -3369,12 +3281,12 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7702644</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8488961002</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3386,17 +3298,17 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Principal Machine Learning &amp; Data Engineer</t>
+          <t>Staff Backend Engineer (Go), Software Supply Chain Security: Secrets Management</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Remote - US</t>
+          <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr"/>
@@ -3410,12 +3322,12 @@
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7155492</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8432235002</t>
         </is>
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3427,17 +3339,17 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Principal, Product Manager - AI / LLM</t>
+          <t>Staff Backend Engineer, Knowledge Graph (Rust)</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Remote - US</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr"/>
@@ -3451,12 +3363,12 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7619420</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481945002</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3468,17 +3380,17 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Product Engineer (Backend)</t>
+          <t>Staff Backend Engineer,  Software Supply Chain Security</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Remote - US</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr"/>
@@ -3492,12 +3404,12 @@
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7671815</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480559002</t>
         </is>
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3509,17 +3421,17 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Senior Manager, Machine Learning</t>
+          <t>Staff Backend Engineer, SSCS: AI Governance</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Remote - US</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr"/>
@@ -3533,12 +3445,12 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7066029</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480531002</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3550,17 +3462,17 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Staff Data Scientist</t>
+          <t>Staff Backend (Python) Engineer, AI Engineering:Duo Chat</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Remote - US</t>
+          <t>Remote, Americas; Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr"/>
@@ -3574,12 +3486,12 @@
       </c>
       <c r="J72" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7821458</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8450446002</t>
         </is>
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3591,17 +3503,17 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Staff, Data Scientist (L4) GTM Data Science &amp; Analytics</t>
+          <t>Senior Full Stack Product Software Engineer</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Dropbox</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Remote - US</t>
+          <t>Remote - Poland</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr"/>
@@ -3615,1348 +3527,2149 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>https://jobs.dropbox.com/listing/6449719?gh_jid=6449719</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Dry Ground AI</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Brazil, Colombia, Philippines</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>full_time</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>api, cloud, fullstack, python, AI/ML, automation, research, CI/CD, TensorFlow, spark, NLP, CMS, Pytorch, REST</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>$40- $60k</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>Remotive</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/artificial-intelligence/ai-engineer-2089958</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>Senior Independent AI Engineer / Architect</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>A.Team</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>Americas, Europe, Israel</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>contract</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>Software Development</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>go, UI/UX, wordpress, chat, apple, testing, catalyst</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>$120 - $170 /hour</t>
+        </is>
+      </c>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>Remotive</t>
+        </is>
+      </c>
+      <c r="J75" s="5" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/software-development/senior-independent-ai-engineer-architect-1919266</t>
+        </is>
+      </c>
+      <c r="K75" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Senior Independent Software Developer</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>A.Team</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Americas, Europe, Israel</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>contract</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Software Development</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>go, wordpress, chat, apple, testing, catalyst</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>$90 - $150 /hour</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>Remotive</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/software-development/senior-independent-software-developer-1919265</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>Senior Full-stack React Developer</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>Lemon.io</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>Americas, Europe, Asia, Oceania</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>contract</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>Software Development</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t>.Net, android, AWS, azure, backend, C, C#, C++, data science, fullstack, golang, ios, java, javascript, node.js, php, python, react, react js, ruby/rails, shopify, video, blockchain, AI/ML, react native, rust, unity, spring, data analysis, laravel, solidity, flask, Typescript , angular , GCP, data engineering, Symfony, startup, marketplace, next.js</t>
+        </is>
+      </c>
+      <c r="H77" s="4" t="inlineStr"/>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t>Remotive</t>
+        </is>
+      </c>
+      <c r="J77" s="5" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/software-development/senior-full-stack-react-developer-2088711</t>
+        </is>
+      </c>
+      <c r="K77" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Tech Lead Full-Stack Rails Engineer</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Mitre Media</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>USA, Canada, USA timezones</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>full_time</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Software Development</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>api, CSS, docker, elasticsearch, fullstack, html, javascript, kubernetes, postgresql, react, ror, ruby/rails, AI/ML, CAD, advertising, Redis, ES6, web applications, MySQL, NLP, fintech, Micro services, github, system architecture</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>$170k - $200k</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>Remotive</t>
+        </is>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/software-development/tech-lead-full-stack-rails-engineer-2069746</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>Senior Frontend Developer</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>Sanctuary Computer</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>LATAM, Asia</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>contract</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>Software Development</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>api, backend, CSS, ecommerce, frontend, fullstack, graphql, postgresql, redux, security, seo, shopify, open source, paas, product management, documentation, mentoring, Typescript , Redis, web applications, cypress, data visualization, firebase, IoT, engineering management, runtime, responsive, prismic, testing, next.js, CMS, jest, REST, web sockets, performance optimization</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>$80k - $120k</t>
+        </is>
+      </c>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>Remotive</t>
+        </is>
+      </c>
+      <c r="J79" s="5" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/software-development/senior-frontend-developer-2088707</t>
+        </is>
+      </c>
+      <c r="K79" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Fullstack Developer (US - ET)</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Chooose</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>full_time</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>Software Development</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>api, azure, fullstack, python, react, saas, AI/ML, project management, documentation, Typescript , computer science, diversity, insurance</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr"/>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>Remotive</t>
+        </is>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/software-development/fullstack-developer-us-et-2088706</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>Machine Learning Manager, Notifications Relevance</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr"/>
+      <c r="F81" s="4" t="inlineStr"/>
+      <c r="G81" s="4" t="inlineStr"/>
+      <c r="H81" s="4" t="inlineStr"/>
+      <c r="I81" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J81" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7846885</t>
+        </is>
+      </c>
+      <c r="K81" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Senior Staff ML Engineer, Search &amp; Recommendation</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr"/>
+      <c r="F82" s="2" t="inlineStr"/>
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr"/>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7833622</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>Remote - US</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr"/>
+      <c r="F83" s="4" t="inlineStr"/>
+      <c r="G83" s="4" t="inlineStr"/>
+      <c r="H83" s="4" t="inlineStr"/>
+      <c r="I83" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J83" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7059734</t>
+        </is>
+      </c>
+      <c r="K83" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Remote - US</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr"/>
+      <c r="F84" s="2" t="inlineStr"/>
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7702644</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>Principal Machine Learning &amp; Data Engineer</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>Remote - US</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr"/>
+      <c r="F85" s="4" t="inlineStr"/>
+      <c r="G85" s="4" t="inlineStr"/>
+      <c r="H85" s="4" t="inlineStr"/>
+      <c r="I85" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J85" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7155492</t>
+        </is>
+      </c>
+      <c r="K85" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Principal, Product Manager - AI / LLM</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Remote - US</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr"/>
+      <c r="F86" s="2" t="inlineStr"/>
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr"/>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7619420</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>Product Engineer (Backend)</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>Remote - US</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr"/>
+      <c r="F87" s="4" t="inlineStr"/>
+      <c r="G87" s="4" t="inlineStr"/>
+      <c r="H87" s="4" t="inlineStr"/>
+      <c r="I87" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J87" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7671815</t>
+        </is>
+      </c>
+      <c r="K87" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Senior Manager, Machine Learning</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Remote - US</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr"/>
+      <c r="F88" s="2" t="inlineStr"/>
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr"/>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7066029</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>Staff Data Scientist</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>Remote - US</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr"/>
+      <c r="F89" s="4" t="inlineStr"/>
+      <c r="G89" s="4" t="inlineStr"/>
+      <c r="H89" s="4" t="inlineStr"/>
+      <c r="I89" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J89" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7821458</t>
+        </is>
+      </c>
+      <c r="K89" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Staff, Data Scientist (L4) GTM Data Science &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Remote - US</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr"/>
+      <c r="F90" s="2" t="inlineStr"/>
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr"/>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
           <t>https://job-boards.greenhouse.io/twilio/jobs/7851920</t>
         </is>
       </c>
-      <c r="K73" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B74" s="4" t="inlineStr">
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
         <is>
           <t>Staff Machine Learning Engineer</t>
         </is>
       </c>
-      <c r="C74" s="4" t="inlineStr">
+      <c r="C91" s="4" t="inlineStr">
         <is>
           <t>Twilio</t>
         </is>
       </c>
-      <c r="D74" s="4" t="inlineStr">
+      <c r="D91" s="4" t="inlineStr">
         <is>
           <t>Remote - US</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr"/>
-      <c r="F74" s="4" t="inlineStr"/>
-      <c r="G74" s="4" t="inlineStr"/>
-      <c r="H74" s="4" t="inlineStr"/>
-      <c r="I74" s="4" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J74" s="5" t="inlineStr">
+      <c r="E91" s="4" t="inlineStr"/>
+      <c r="F91" s="4" t="inlineStr"/>
+      <c r="G91" s="4" t="inlineStr"/>
+      <c r="H91" s="4" t="inlineStr"/>
+      <c r="I91" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J91" s="5" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/twilio/jobs/7061880</t>
         </is>
       </c>
-      <c r="K74" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="K91" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>Staff Machine Learning Engineer (L4)</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
         <is>
           <t>Twilio</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Remote - India</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr"/>
-      <c r="F75" s="2" t="inlineStr"/>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr"/>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr"/>
+      <c r="F92" s="2" t="inlineStr"/>
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr"/>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/twilio/jobs/7520997</t>
         </is>
       </c>
-      <c r="K75" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B76" s="4" t="inlineStr">
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
         <is>
           <t>Senior Python Developer - Django (m/w/d)</t>
         </is>
       </c>
-      <c r="C76" s="4" t="inlineStr">
+      <c r="C93" s="4" t="inlineStr">
         <is>
           <t>sync.blue® GmbH</t>
         </is>
       </c>
-      <c r="D76" s="4" t="inlineStr">
+      <c r="D93" s="4" t="inlineStr">
         <is>
           <t>Haltern am See</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr">
+      <c r="E93" s="4" t="inlineStr">
         <is>
           <t>berufserfahren</t>
         </is>
       </c>
-      <c r="F76" s="4" t="inlineStr"/>
-      <c r="G76" s="4" t="inlineStr">
+      <c r="F93" s="4" t="inlineStr"/>
+      <c r="G93" s="4" t="inlineStr">
         <is>
           <t>Remote, Software Development</t>
         </is>
       </c>
-      <c r="H76" s="4" t="inlineStr"/>
-      <c r="I76" s="4" t="inlineStr">
+      <c r="H93" s="4" t="inlineStr"/>
+      <c r="I93" s="4" t="inlineStr">
         <is>
           <t>Arbeitnow</t>
         </is>
       </c>
-      <c r="J76" s="5" t="inlineStr">
+      <c r="J93" s="5" t="inlineStr">
         <is>
           <t>https://www.arbeitnow.com/jobs/companies/syncblue-gmbh/senior-python-developer-django-haltern-am-see-16238</t>
         </is>
       </c>
-      <c r="K76" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="K93" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>Freelance Senior AI Product Manager</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
         <is>
           <t>nexamind GmbH</t>
         </is>
       </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>Freelance, professional / experienced</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr"/>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr"/>
+      <c r="G94" s="2" t="inlineStr">
         <is>
           <t>Remote, Product Management</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr"/>
-      <c r="I77" s="2" t="inlineStr">
+      <c r="H94" s="2" t="inlineStr"/>
+      <c r="I94" s="2" t="inlineStr">
         <is>
           <t>Arbeitnow</t>
         </is>
       </c>
-      <c r="J77" s="3" t="inlineStr">
+      <c r="J94" s="3" t="inlineStr">
         <is>
           <t>https://www.arbeitnow.com/jobs/companies/nexamind-gmbh/freelance-senior-ai-product-manager-berlin-73613</t>
         </is>
       </c>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B78" s="4" t="inlineStr">
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
         <is>
           <t>Senior Full-Stack-Entwickler:in React / TypeScript / .NET  100 % Remote, KI-First</t>
         </is>
       </c>
-      <c r="C78" s="4" t="inlineStr">
+      <c r="C95" s="4" t="inlineStr">
         <is>
           <t>yourMAIL GmbH</t>
         </is>
       </c>
-      <c r="D78" s="4" t="inlineStr">
+      <c r="D95" s="4" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr">
+      <c r="E95" s="4" t="inlineStr">
         <is>
           <t>berufserfahren</t>
         </is>
       </c>
-      <c r="F78" s="4" t="inlineStr"/>
-      <c r="G78" s="4" t="inlineStr">
+      <c r="F95" s="4" t="inlineStr"/>
+      <c r="G95" s="4" t="inlineStr">
         <is>
           <t>Remote, Software Development</t>
         </is>
       </c>
-      <c r="H78" s="4" t="inlineStr"/>
-      <c r="I78" s="4" t="inlineStr">
+      <c r="H95" s="4" t="inlineStr"/>
+      <c r="I95" s="4" t="inlineStr">
         <is>
           <t>Arbeitnow</t>
         </is>
       </c>
-      <c r="J78" s="5" t="inlineStr">
+      <c r="J95" s="5" t="inlineStr">
         <is>
           <t>https://www.arbeitnow.com/jobs/companies/yourmail-gmbh/senior-full-stack-entwicklerin-react-typescript-net-100-remote-ki-first-berlin-21152</t>
         </is>
       </c>
-      <c r="K78" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="K95" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>Senior Frontend-Entwickler:in React / TypeScript, 100 % Remote, KI-First</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
         <is>
           <t>yourMAIL GmbH</t>
         </is>
       </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>berufserfahren</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr"/>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr"/>
+      <c r="G96" s="2" t="inlineStr">
         <is>
           <t>Remote, Software Development</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr"/>
-      <c r="I79" s="2" t="inlineStr">
+      <c r="H96" s="2" t="inlineStr"/>
+      <c r="I96" s="2" t="inlineStr">
         <is>
           <t>Arbeitnow</t>
         </is>
       </c>
-      <c r="J79" s="3" t="inlineStr">
+      <c r="J96" s="3" t="inlineStr">
         <is>
           <t>https://www.arbeitnow.com/jobs/companies/yourmail-gmbh/senior-frontend-entwicklerin-react-typescript-100-remote-ki-first-berlin-288218</t>
         </is>
       </c>
-      <c r="K79" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B80" s="4" t="inlineStr">
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
         <is>
           <t>Full-Stack Entwickler (m/w/d) - .NET 100% Remote</t>
         </is>
       </c>
-      <c r="C80" s="4" t="inlineStr">
+      <c r="C97" s="4" t="inlineStr">
         <is>
           <t>FNTIO</t>
         </is>
       </c>
-      <c r="D80" s="4" t="inlineStr">
+      <c r="D97" s="4" t="inlineStr">
         <is>
           <t>Frankfurt am Main</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr"/>
-      <c r="F80" s="4" t="inlineStr"/>
-      <c r="G80" s="4" t="inlineStr">
+      <c r="E97" s="4" t="inlineStr"/>
+      <c r="F97" s="4" t="inlineStr"/>
+      <c r="G97" s="4" t="inlineStr">
         <is>
           <t>Remote, Consulting, Engineering</t>
         </is>
       </c>
-      <c r="H80" s="4" t="inlineStr"/>
-      <c r="I80" s="4" t="inlineStr">
+      <c r="H97" s="4" t="inlineStr"/>
+      <c r="I97" s="4" t="inlineStr">
         <is>
           <t>Arbeitnow</t>
         </is>
       </c>
-      <c r="J80" s="5" t="inlineStr">
+      <c r="J97" s="5" t="inlineStr">
         <is>
           <t>https://www.arbeitnow.com/jobs/companies/fntio/full-stack-entwickler-net-100-remote-frankfurt-am-main-122380</t>
         </is>
       </c>
-      <c r="K80" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="K97" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>Machine Learning Engineer</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
         <is>
           <t>Phantasma Labs</t>
         </is>
       </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr"/>
-      <c r="F81" s="2" t="inlineStr"/>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr"/>
+      <c r="F98" s="2" t="inlineStr"/>
+      <c r="G98" s="2" t="inlineStr">
         <is>
           <t>Remote, Engineering</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr"/>
-      <c r="I81" s="2" t="inlineStr">
+      <c r="H98" s="2" t="inlineStr"/>
+      <c r="I98" s="2" t="inlineStr">
         <is>
           <t>Arbeitnow</t>
         </is>
       </c>
-      <c r="J81" s="3" t="inlineStr">
+      <c r="J98" s="3" t="inlineStr">
         <is>
           <t>https://www.arbeitnow.com/jobs/companies/phantasma-labs/machine-learning-engineer-berlin-303955</t>
         </is>
       </c>
-      <c r="K81" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B82" s="4" t="inlineStr">
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
         <is>
           <t>Technical Data Manager (m/w/d)</t>
         </is>
       </c>
-      <c r="C82" s="4" t="inlineStr">
+      <c r="C99" s="4" t="inlineStr">
         <is>
           <t>BMF Media Information Technology GmbH</t>
         </is>
       </c>
-      <c r="D82" s="4" t="inlineStr">
+      <c r="D99" s="4" t="inlineStr">
         <is>
           <t>Augsburg</t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr">
+      <c r="E99" s="4" t="inlineStr">
         <is>
           <t>berufserfahren</t>
         </is>
       </c>
-      <c r="F82" s="4" t="inlineStr"/>
-      <c r="G82" s="4" t="inlineStr">
+      <c r="F99" s="4" t="inlineStr"/>
+      <c r="G99" s="4" t="inlineStr">
         <is>
           <t>Remote, Technical Documentation</t>
         </is>
       </c>
-      <c r="H82" s="4" t="inlineStr"/>
-      <c r="I82" s="4" t="inlineStr">
+      <c r="H99" s="4" t="inlineStr"/>
+      <c r="I99" s="4" t="inlineStr">
         <is>
           <t>Arbeitnow</t>
         </is>
       </c>
-      <c r="J82" s="5" t="inlineStr">
+      <c r="J99" s="5" t="inlineStr">
         <is>
           <t>https://www.arbeitnow.com/jobs/companies/bmf-media-information-technology-gmbh/technical-data-manager-augsburg-42188</t>
         </is>
       </c>
-      <c r="K82" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="K99" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>Data Integration &amp; API Engineer m/w/d - Bi &amp; Data Automation</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
         <is>
           <t>loyos bi GmbH</t>
         </is>
       </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Hamburg</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>berufserfahren</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr"/>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr"/>
+      <c r="G100" s="2" t="inlineStr">
         <is>
           <t>Remote, Software Development</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr"/>
-      <c r="I83" s="2" t="inlineStr">
+      <c r="H100" s="2" t="inlineStr"/>
+      <c r="I100" s="2" t="inlineStr">
         <is>
           <t>Arbeitnow</t>
         </is>
       </c>
-      <c r="J83" s="3" t="inlineStr">
+      <c r="J100" s="3" t="inlineStr">
         <is>
           <t>https://www.arbeitnow.com/jobs/companies/loyos-bi-gmbh/data-integration-api-engineer-bi-data-automation-hamburg-66228</t>
         </is>
       </c>
-      <c r="K83" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B84" s="4" t="inlineStr">
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
         <is>
           <t>Senior Full Stack Engineer</t>
         </is>
       </c>
-      <c r="C84" s="4" t="inlineStr">
+      <c r="C101" s="4" t="inlineStr">
         <is>
           <t>Coding Partners</t>
         </is>
       </c>
-      <c r="D84" s="4" t="inlineStr">
+      <c r="D101" s="4" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr">
+      <c r="E101" s="4" t="inlineStr">
         <is>
           <t>professional / experienced</t>
         </is>
       </c>
-      <c r="F84" s="4" t="inlineStr"/>
-      <c r="G84" s="4" t="inlineStr">
+      <c r="F101" s="4" t="inlineStr"/>
+      <c r="G101" s="4" t="inlineStr">
         <is>
           <t>Remote, Software Development</t>
         </is>
       </c>
-      <c r="H84" s="4" t="inlineStr"/>
-      <c r="I84" s="4" t="inlineStr">
+      <c r="H101" s="4" t="inlineStr"/>
+      <c r="I101" s="4" t="inlineStr">
         <is>
           <t>Arbeitnow</t>
         </is>
       </c>
-      <c r="J84" s="5" t="inlineStr">
+      <c r="J101" s="5" t="inlineStr">
         <is>
           <t>https://www.arbeitnow.com/jobs/companies/coding-partners/senior-full-stack-engineer-berlin-391720</t>
         </is>
       </c>
-      <c r="K84" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="K101" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>Laravel Developer (m/w/d) - AI-First PropTech</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
         <is>
           <t>Immovara GmbH</t>
         </is>
       </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Korntal-Münchingen</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>berufserfahren</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr"/>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr"/>
+      <c r="G102" s="2" t="inlineStr">
         <is>
           <t>Remote, Software Development</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr"/>
-      <c r="I85" s="2" t="inlineStr">
+      <c r="H102" s="2" t="inlineStr"/>
+      <c r="I102" s="2" t="inlineStr">
         <is>
           <t>Arbeitnow</t>
         </is>
       </c>
-      <c r="J85" s="3" t="inlineStr">
+      <c r="J102" s="3" t="inlineStr">
         <is>
           <t>https://www.arbeitnow.com/jobs/companies/immovara-gmbh/laravel-developer-ai-first-proptech-korntal-munchingen-471269</t>
         </is>
       </c>
-      <c r="K85" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B86" s="4" t="inlineStr">
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
         <is>
           <t>Fullstack Softwareentwickler (m/w/d)</t>
         </is>
       </c>
-      <c r="C86" s="4" t="inlineStr">
+      <c r="C103" s="4" t="inlineStr">
         <is>
           <t>TecFox GmbH</t>
         </is>
       </c>
-      <c r="D86" s="4" t="inlineStr">
+      <c r="D103" s="4" t="inlineStr">
         <is>
           <t>Braunschweig</t>
         </is>
       </c>
-      <c r="E86" s="4" t="inlineStr">
+      <c r="E103" s="4" t="inlineStr">
         <is>
           <t>berufserfahren</t>
         </is>
       </c>
-      <c r="F86" s="4" t="inlineStr"/>
-      <c r="G86" s="4" t="inlineStr">
+      <c r="F103" s="4" t="inlineStr"/>
+      <c r="G103" s="4" t="inlineStr">
         <is>
           <t>Remote, Software Development</t>
         </is>
       </c>
-      <c r="H86" s="4" t="inlineStr"/>
-      <c r="I86" s="4" t="inlineStr">
+      <c r="H103" s="4" t="inlineStr"/>
+      <c r="I103" s="4" t="inlineStr">
         <is>
           <t>Arbeitnow</t>
         </is>
       </c>
-      <c r="J86" s="5" t="inlineStr">
+      <c r="J103" s="5" t="inlineStr">
         <is>
           <t>https://www.arbeitnow.com/jobs/companies/tecfox-gmbh/fullstack-softwareentwickler-braunschweig-405178</t>
         </is>
       </c>
-      <c r="K86" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="K103" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>Frontend Softwareentwickler (m/w/d)</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
+      <c r="C104" s="2" t="inlineStr">
         <is>
           <t>TecFox GmbH</t>
         </is>
       </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Braunschweig</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>berufserfahren</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr"/>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr"/>
+      <c r="G104" s="2" t="inlineStr">
         <is>
           <t>Remote, Software Development</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr"/>
-      <c r="I87" s="2" t="inlineStr">
+      <c r="H104" s="2" t="inlineStr"/>
+      <c r="I104" s="2" t="inlineStr">
         <is>
           <t>Arbeitnow</t>
         </is>
       </c>
-      <c r="J87" s="3" t="inlineStr">
+      <c r="J104" s="3" t="inlineStr">
         <is>
           <t>https://www.arbeitnow.com/jobs/companies/tecfox-gmbh/frontend-softwareentwickler-braunschweig-341792</t>
         </is>
       </c>
-      <c r="K87" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B88" s="4" t="inlineStr">
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
         <is>
           <t>Fullstack-Developer*in (m/w/d) Web &amp; AI Automation</t>
         </is>
       </c>
-      <c r="C88" s="4" t="inlineStr">
+      <c r="C105" s="4" t="inlineStr">
         <is>
           <t>NeoBird Digital</t>
         </is>
       </c>
-      <c r="D88" s="4" t="inlineStr">
+      <c r="D105" s="4" t="inlineStr">
         <is>
           <t>Nuremberg</t>
         </is>
       </c>
-      <c r="E88" s="4" t="inlineStr">
+      <c r="E105" s="4" t="inlineStr">
         <is>
           <t>berufserfahren</t>
         </is>
       </c>
-      <c r="F88" s="4" t="inlineStr"/>
-      <c r="G88" s="4" t="inlineStr">
+      <c r="F105" s="4" t="inlineStr"/>
+      <c r="G105" s="4" t="inlineStr">
         <is>
           <t>Remote, Software Development</t>
         </is>
       </c>
-      <c r="H88" s="4" t="inlineStr"/>
-      <c r="I88" s="4" t="inlineStr">
+      <c r="H105" s="4" t="inlineStr"/>
+      <c r="I105" s="4" t="inlineStr">
         <is>
           <t>Arbeitnow</t>
         </is>
       </c>
-      <c r="J88" s="5" t="inlineStr">
+      <c r="J105" s="5" t="inlineStr">
         <is>
           <t>https://www.arbeitnow.com/jobs/companies/neobird-digital/fullstack-developerin-web-ai-automation-nuremberg-157752</t>
         </is>
       </c>
-      <c r="K88" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="K105" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>Full-Stack Software Engineer / Backend &amp; Frontend - Bootstrapped SaaS Startup (m/w/d) remote in EU</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
+      <c r="C106" s="2" t="inlineStr">
         <is>
           <t>DatAds</t>
         </is>
       </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Cologne</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr"/>
-      <c r="F89" s="2" t="inlineStr"/>
-      <c r="G89" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr"/>
+      <c r="F106" s="2" t="inlineStr"/>
+      <c r="G106" s="2" t="inlineStr">
         <is>
           <t>Remote, IT</t>
         </is>
       </c>
-      <c r="H89" s="2" t="inlineStr"/>
-      <c r="I89" s="2" t="inlineStr">
+      <c r="H106" s="2" t="inlineStr"/>
+      <c r="I106" s="2" t="inlineStr">
         <is>
           <t>Arbeitnow</t>
         </is>
       </c>
-      <c r="J89" s="3" t="inlineStr">
+      <c r="J106" s="3" t="inlineStr">
         <is>
           <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-bootstrapped-saas-startup-remote-in-eu-cologne-82307</t>
         </is>
       </c>
-      <c r="K89" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B90" s="4" t="inlineStr">
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
         <is>
           <t>Full-Stack Software Engineer / Rest APIs / Cloud / TailwindCSS / SaaS Startup (m/w/d) remote in EU</t>
         </is>
       </c>
-      <c r="C90" s="4" t="inlineStr">
+      <c r="C107" s="4" t="inlineStr">
         <is>
           <t>DatAds</t>
         </is>
       </c>
-      <c r="D90" s="4" t="inlineStr">
+      <c r="D107" s="4" t="inlineStr">
         <is>
           <t>Cologne</t>
         </is>
       </c>
-      <c r="E90" s="4" t="inlineStr"/>
-      <c r="F90" s="4" t="inlineStr"/>
-      <c r="G90" s="4" t="inlineStr">
+      <c r="E107" s="4" t="inlineStr"/>
+      <c r="F107" s="4" t="inlineStr"/>
+      <c r="G107" s="4" t="inlineStr">
         <is>
           <t>Remote, IT</t>
         </is>
       </c>
-      <c r="H90" s="4" t="inlineStr"/>
-      <c r="I90" s="4" t="inlineStr">
+      <c r="H107" s="4" t="inlineStr"/>
+      <c r="I107" s="4" t="inlineStr">
         <is>
           <t>Arbeitnow</t>
         </is>
       </c>
-      <c r="J90" s="5" t="inlineStr">
+      <c r="J107" s="5" t="inlineStr">
         <is>
           <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-bootstrapped-saas-startup-remote-in-eu-cologne-38634</t>
         </is>
       </c>
-      <c r="K90" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="K107" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>Full-Stack Software Engineer / Node.js / TypeScript / React / Azure - AdTech SaaS Startup (m/w/d) remote</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
+      <c r="C108" s="2" t="inlineStr">
         <is>
           <t>DatAds</t>
         </is>
       </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Cologne</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr"/>
-      <c r="F91" s="2" t="inlineStr"/>
-      <c r="G91" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr"/>
+      <c r="F108" s="2" t="inlineStr"/>
+      <c r="G108" s="2" t="inlineStr">
         <is>
           <t>Remote, IT</t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr"/>
-      <c r="I91" s="2" t="inlineStr">
+      <c r="H108" s="2" t="inlineStr"/>
+      <c r="I108" s="2" t="inlineStr">
         <is>
           <t>Arbeitnow</t>
         </is>
       </c>
-      <c r="J91" s="3" t="inlineStr">
+      <c r="J108" s="3" t="inlineStr">
         <is>
           <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-adtech-saas-startup-remote-cologne-263746</t>
         </is>
       </c>
-      <c r="K91" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B92" s="4" t="inlineStr">
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
         <is>
           <t>Senior DevOps / Platform Engineer (f/m/x)</t>
         </is>
       </c>
-      <c r="C92" s="4" t="inlineStr">
+      <c r="C109" s="4" t="inlineStr">
         <is>
           <t>MAIA</t>
         </is>
       </c>
-      <c r="D92" s="4" t="inlineStr">
+      <c r="D109" s="4" t="inlineStr">
         <is>
           <t>Leipzig</t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr">
+      <c r="E109" s="4" t="inlineStr">
         <is>
           <t>professional / experienced</t>
         </is>
       </c>
-      <c r="F92" s="4" t="inlineStr"/>
-      <c r="G92" s="4" t="inlineStr">
+      <c r="F109" s="4" t="inlineStr"/>
+      <c r="G109" s="4" t="inlineStr">
         <is>
           <t>Remote, IT</t>
         </is>
       </c>
-      <c r="H92" s="4" t="inlineStr"/>
-      <c r="I92" s="4" t="inlineStr">
+      <c r="H109" s="4" t="inlineStr"/>
+      <c r="I109" s="4" t="inlineStr">
         <is>
           <t>Arbeitnow</t>
         </is>
       </c>
-      <c r="J92" s="5" t="inlineStr">
+      <c r="J109" s="5" t="inlineStr">
         <is>
           <t>https://www.arbeitnow.com/jobs/companies/maia/senior-devops-platform-engineer-leipzig-388068</t>
         </is>
       </c>
-      <c r="K92" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+      <c r="K109" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>Senior Site Reliability Engineer AI Infrastructure</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
+      <c r="C110" s="2" t="inlineStr">
         <is>
           <t>Andromeda Cluster</t>
         </is>
       </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr"/>
-      <c r="F93" s="2" t="inlineStr"/>
-      <c r="G93" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr"/>
+      <c r="F110" s="2" t="inlineStr"/>
+      <c r="G110" s="2" t="inlineStr">
         <is>
           <t>design, training, technical, software, code, manager, financial, cloud, management, lead, senior, operations, reliability, go, health, engineer, engineering, linux, digital nomad</t>
         </is>
       </c>
-      <c r="H93" s="2" t="inlineStr"/>
-      <c r="I93" s="2" t="inlineStr">
+      <c r="H110" s="2" t="inlineStr"/>
+      <c r="I110" s="2" t="inlineStr">
         <is>
           <t>RemoteOK</t>
         </is>
       </c>
-      <c r="J93" s="3" t="inlineStr">
+      <c r="J110" s="3" t="inlineStr">
         <is>
           <t>https://remoteOK.com/remote-jobs/remote-senior-site-reliability-engineer-ai-infrastructure-andromeda-cluster-1131375</t>
         </is>
       </c>
-      <c r="K93" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="4" t="inlineStr">
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B94" s="4" t="inlineStr">
+      <c r="B111" s="4" t="inlineStr">
         <is>
           <t>Senior Financial Analyst Digital Assets</t>
         </is>
       </c>
-      <c r="C94" s="4" t="inlineStr">
+      <c r="C111" s="4" t="inlineStr">
         <is>
           <t>Exodus Movement Inc.</t>
         </is>
       </c>
-      <c r="D94" s="4" t="inlineStr">
+      <c r="D111" s="4" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="E94" s="4" t="inlineStr"/>
-      <c r="F94" s="4" t="inlineStr"/>
-      <c r="G94" s="4" t="inlineStr">
+      <c r="E111" s="4" t="inlineStr"/>
+      <c r="F111" s="4" t="inlineStr"/>
+      <c r="G111" s="4" t="inlineStr">
         <is>
           <t>analyst, cryptocurrency, support, financial, investment, finance, senior, non tech</t>
         </is>
       </c>
-      <c r="H94" s="4" t="inlineStr"/>
-      <c r="I94" s="4" t="inlineStr">
+      <c r="H111" s="4" t="inlineStr"/>
+      <c r="I111" s="4" t="inlineStr">
         <is>
           <t>RemoteOK</t>
         </is>
       </c>
-      <c r="J94" s="5" t="inlineStr">
+      <c r="J111" s="5" t="inlineStr">
         <is>
           <t>https://remoteOK.com/remote-jobs/remote-senior-financial-analyst-digital-assets-exodus-movement-inc-1131374</t>
         </is>
       </c>
-      <c r="K94" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+      <c r="K111" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>Front End Full Stack Developer</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
+      <c r="C112" s="2" t="inlineStr">
         <is>
           <t>Honor Foods</t>
         </is>
       </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Philadelphia, PA</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr"/>
-      <c r="F95" s="2" t="inlineStr"/>
-      <c r="G95" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr"/>
+      <c r="F112" s="2" t="inlineStr"/>
+      <c r="G112" s="2" t="inlineStr">
         <is>
           <t>developer, front-end, ui, code, web, operational, backend, digital nomad</t>
         </is>
       </c>
-      <c r="H95" s="2" t="inlineStr"/>
-      <c r="I95" s="2" t="inlineStr">
+      <c r="H112" s="2" t="inlineStr"/>
+      <c r="I112" s="2" t="inlineStr">
         <is>
           <t>RemoteOK</t>
         </is>
       </c>
-      <c r="J95" s="3" t="inlineStr">
+      <c r="J112" s="3" t="inlineStr">
         <is>
           <t>https://remoteOK.com/remote-jobs/remote-front-end-full-stack-developer-honor-foods-1131370</t>
         </is>
       </c>
-      <c r="K95" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="4" t="inlineStr">
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B96" s="4" t="inlineStr">
+      <c r="B113" s="4" t="inlineStr">
         <is>
           <t>Wing Assistant: Full-Stack Developer</t>
         </is>
       </c>
-      <c r="C96" s="4" t="inlineStr"/>
-      <c r="D96" s="4" t="inlineStr">
+      <c r="C113" s="4" t="inlineStr"/>
+      <c r="D113" s="4" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="E96" s="4" t="inlineStr"/>
-      <c r="F96" s="4" t="inlineStr"/>
-      <c r="G96" s="4" t="inlineStr"/>
-      <c r="H96" s="4" t="inlineStr"/>
-      <c r="I96" s="4" t="inlineStr">
+      <c r="E113" s="4" t="inlineStr"/>
+      <c r="F113" s="4" t="inlineStr"/>
+      <c r="G113" s="4" t="inlineStr"/>
+      <c r="H113" s="4" t="inlineStr"/>
+      <c r="I113" s="4" t="inlineStr">
         <is>
           <t>WeWorkRemotely</t>
         </is>
       </c>
-      <c r="J96" s="5" t="inlineStr">
+      <c r="J113" s="5" t="inlineStr">
         <is>
           <t>https://weworkremotely.com/remote-jobs/wing-assistant-full-stack-developer</t>
         </is>
       </c>
-      <c r="K96" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+      <c r="K113" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>Qventus: Product Designer</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr"/>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="C114" s="2" t="inlineStr"/>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr"/>
-      <c r="F97" s="2" t="inlineStr"/>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr"/>
-      <c r="I97" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr"/>
+      <c r="F114" s="2" t="inlineStr"/>
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr"/>
+      <c r="I114" s="2" t="inlineStr">
         <is>
           <t>WeWorkRemotely</t>
         </is>
       </c>
-      <c r="J97" s="3" t="inlineStr">
+      <c r="J114" s="3" t="inlineStr">
         <is>
           <t>https://weworkremotely.com/remote-jobs/qventus-product-designer</t>
         </is>
       </c>
-      <c r="K97" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="4" t="inlineStr">
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B98" s="4" t="inlineStr">
+      <c r="B115" s="4" t="inlineStr">
         <is>
           <t>Socure: Senior Product Marketing Manager</t>
         </is>
       </c>
-      <c r="C98" s="4" t="inlineStr"/>
-      <c r="D98" s="4" t="inlineStr">
+      <c r="C115" s="4" t="inlineStr"/>
+      <c r="D115" s="4" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="E98" s="4" t="inlineStr"/>
-      <c r="F98" s="4" t="inlineStr"/>
-      <c r="G98" s="4" t="inlineStr"/>
-      <c r="H98" s="4" t="inlineStr"/>
-      <c r="I98" s="4" t="inlineStr">
+      <c r="E115" s="4" t="inlineStr"/>
+      <c r="F115" s="4" t="inlineStr"/>
+      <c r="G115" s="4" t="inlineStr"/>
+      <c r="H115" s="4" t="inlineStr"/>
+      <c r="I115" s="4" t="inlineStr">
         <is>
           <t>WeWorkRemotely</t>
         </is>
       </c>
-      <c r="J98" s="5" t="inlineStr">
+      <c r="J115" s="5" t="inlineStr">
         <is>
           <t>https://weworkremotely.com/remote-jobs/socure-senior-product-marketing-manager</t>
         </is>
       </c>
-      <c r="K98" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+      <c r="K115" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>Blueprint: Product Designer</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr"/>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="C116" s="2" t="inlineStr"/>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr"/>
-      <c r="F99" s="2" t="inlineStr"/>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr"/>
-      <c r="I99" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr"/>
+      <c r="F116" s="2" t="inlineStr"/>
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr"/>
+      <c r="I116" s="2" t="inlineStr">
         <is>
           <t>WeWorkRemotely</t>
         </is>
       </c>
-      <c r="J99" s="3" t="inlineStr">
+      <c r="J116" s="3" t="inlineStr">
         <is>
           <t>https://weworkremotely.com/remote-jobs/blueprint-product-designer</t>
         </is>
       </c>
-      <c r="K99" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="4" t="inlineStr">
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B100" s="4" t="inlineStr">
+      <c r="B117" s="4" t="inlineStr">
         <is>
           <t>Interop Labs: Product Marketing Manager</t>
         </is>
       </c>
-      <c r="C100" s="4" t="inlineStr"/>
-      <c r="D100" s="4" t="inlineStr">
+      <c r="C117" s="4" t="inlineStr"/>
+      <c r="D117" s="4" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="E100" s="4" t="inlineStr"/>
-      <c r="F100" s="4" t="inlineStr"/>
-      <c r="G100" s="4" t="inlineStr"/>
-      <c r="H100" s="4" t="inlineStr"/>
-      <c r="I100" s="4" t="inlineStr">
+      <c r="E117" s="4" t="inlineStr"/>
+      <c r="F117" s="4" t="inlineStr"/>
+      <c r="G117" s="4" t="inlineStr"/>
+      <c r="H117" s="4" t="inlineStr"/>
+      <c r="I117" s="4" t="inlineStr">
         <is>
           <t>WeWorkRemotely</t>
         </is>
       </c>
-      <c r="J100" s="5" t="inlineStr">
+      <c r="J117" s="5" t="inlineStr">
         <is>
           <t>https://weworkremotely.com/remote-jobs/interop-labs-product-marketing-manager</t>
         </is>
       </c>
-      <c r="K100" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+      <c r="K117" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>Full Stack Engineer, Link</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
+      <c r="C118" s="2" t="inlineStr">
         <is>
           <t>Stripe</t>
         </is>
       </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Toronto, Remote in Canada</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr"/>
-      <c r="F101" s="2" t="inlineStr"/>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr"/>
-      <c r="I101" s="2" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J101" s="3" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr"/>
+      <c r="F118" s="2" t="inlineStr"/>
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr"/>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
         <is>
           <t>https://stripe.com/jobs/search?gh_jid=6447175</t>
         </is>
       </c>
-      <c r="K101" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="4" t="inlineStr">
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B102" s="4" t="inlineStr">
+      <c r="B119" s="4" t="inlineStr">
         <is>
           <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
-      <c r="C102" s="4" t="inlineStr">
+      <c r="C119" s="4" t="inlineStr">
         <is>
           <t>Reddit</t>
         </is>
       </c>
-      <c r="D102" s="4" t="inlineStr">
+      <c r="D119" s="4" t="inlineStr">
         <is>
           <t>Remote - Ontario, Canada</t>
         </is>
       </c>
-      <c r="E102" s="4" t="inlineStr"/>
-      <c r="F102" s="4" t="inlineStr"/>
-      <c r="G102" s="4" t="inlineStr"/>
-      <c r="H102" s="4" t="inlineStr"/>
-      <c r="I102" s="4" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J102" s="5" t="inlineStr">
+      <c r="E119" s="4" t="inlineStr"/>
+      <c r="F119" s="4" t="inlineStr"/>
+      <c r="G119" s="4" t="inlineStr"/>
+      <c r="H119" s="4" t="inlineStr"/>
+      <c r="I119" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J119" s="5" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/reddit/jobs/6960833</t>
         </is>
       </c>
-      <c r="K102" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+      <c r="K119" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
         <is>
           <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
+      <c r="C120" s="2" t="inlineStr">
         <is>
           <t>Reddit</t>
         </is>
       </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Remote - United States</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr"/>
-      <c r="F103" s="2" t="inlineStr"/>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr"/>
-      <c r="I103" s="2" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J103" s="3" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr"/>
+      <c r="F120" s="2" t="inlineStr"/>
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr"/>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J120" s="3" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/reddit/jobs/6960831</t>
         </is>
       </c>
-      <c r="K103" s="2" t="inlineStr">
+      <c r="K120" s="2" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
@@ -4966,53 +5679,68 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId64"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/remote_jobs.xlsx
+++ b/remote_jobs.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K185"/>
+  <dimension ref="A1:K193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -523,22 +523,22 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Sidebase Open-Source Contributor &amp; Senior TS Dev (f/m/d)</t>
+          <t>Senior Cloud Software Engineer (TypeScript &amp; AWS) (m/w/d)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Sidestream</t>
+          <t>vOffice Software</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Cologne</t>
+          <t>Hamburg</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -556,37 +556,41 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/sidestream/sidebase-open-source-contributor-senior-ts-dev-cologne-317648</t>
+          <t>https://www.arbeitnow.com/jobs/companies/voffice-software/senior-cloud-software-engineer-typescript-aws-hamburg-431856</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Senior Typescript Developer (f/m/d)</t>
+          <t>Senior Backend Engineer RoR (all identities)</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Sidestream</t>
+          <t>Caspar Health</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Cologne</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr"/>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
       <c r="F3" s="4" t="inlineStr"/>
       <c r="G3" s="4" t="inlineStr">
         <is>
@@ -601,41 +605,45 @@
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/sidestream/senior-typescript-developer-cologne-220463</t>
+          <t>https://www.arbeitnow.com/jobs/companies/caspar-health/senior-backend-engineer-ror-all-identities-berlin-7147</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Senior AI-Engineer / Agent-Architekt (m/w/d)</t>
+          <t>Python Software Engineer - Machine Learning Systems (m/f/d)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Neurawork GmbH &amp; Co. KG</t>
+          <t>CUJU</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Ampfing</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr"/>
+          <t>Frankenthal</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Remote, IT</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -646,34 +654,34 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/neurawork-gmbh-co-kg/senior-ai-engineer-agent-architekt-ampfing-390691</t>
+          <t>https://www.arbeitnow.com/jobs/companies/cuju/python-software-engineer-machine-learning-systems-frankenthal-183273</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Senior AI Consultant / Machine Learning Engineer (m/w/d) Public Sector | &gt;90% REMOTE</t>
+          <t>AI Algorithm Developer Medical Imaging (m/w/d)</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Bridgency HR Management GbR</t>
+          <t>citema systems GmbH</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Usingen</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -684,7 +692,7 @@
       <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>Remote, Consulting, Engineering</t>
+          <t>Remote, IT</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
@@ -695,12 +703,12 @@
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/bridgency-hr-management-gbr/senior-ai-consultant-machine-learning-engineer-public-sector-90-remote-usingen-94077</t>
+          <t>https://www.arbeitnow.com/jobs/companies/citema-systems-gmbh/ai-algorithm-developer-medical-imaging-munich-91573</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -712,73 +720,69 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Werkstudent (m/w/d) Frontend Development &amp; KI-Integration (20h/Woche)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>MEvents Cross Media GmbH</t>
+          <t>Civitech</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>hilfstätigkeit / student</t>
-        </is>
-      </c>
+          <t>Austin, TX or Remote</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Remote, Software Development</t>
+          <t>python, support, code, cloud, analytics, engineer, engineering, full-time</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/mevents-cross-media-gmbh/werkstudent-frontend-development-ki-integration-20h-woche-berlin-378282</t>
+          <t>https://remoteOK.com/remote-jobs/remote-analytics-engineer-civitech-1131512</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Tech Lead</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Valon Mortgage</t>
+          <t>Zensurance</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Toronto, ON</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr"/>
       <c r="F7" s="4" t="inlineStr"/>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>design, saas, python, architect, technical, support, cloud, strategy, management, senior, operations, operational, analytics, reliability, go, engineer, engineering, digital nomad</t>
+          <t>design, system, front-end, back-end, security, training, full-stack, docker, technical, support, software, testing, test, growth, code, web, scrum, devops, javascript, education, strategy, management, lead, senior, health, engineering, digital nomad</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
@@ -789,24 +793,24 @@
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-senior-data-engineer-valon-mortgage-1131504</t>
+          <t>https://remoteOK.com/remote-jobs/remote-tech-lead-zensurance-1131509</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Senior AI Agent Architect / AI Automation Architect</t>
+          <t>Senior Full-stack Symfony Developer</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
@@ -819,7 +823,7 @@
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>artificial intelligence, python, machine learning, engineer, communication</t>
+          <t>symfony, php, javascript, vuejs</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
@@ -830,416 +834,416 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>https://www.workingnomads.com/job/go/1587815/</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Senior Staff Machine Learning Engineer, Feed Relevance</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr"/>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7908786</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Sidebase Open-Source Contributor &amp; Senior TS Dev (f/m/d)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Sidestream</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Cologne</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Remote, Software Development</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/sidestream/sidebase-open-source-contributor-senior-ts-dev-cologne-317648</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Senior Typescript Developer (f/m/d)</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Sidestream</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Cologne</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr"/>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Software Development</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/sidestream/senior-typescript-developer-cologne-220463</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Senior AI-Engineer / Agent-Architekt (m/w/d)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Neurawork GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Ampfing</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Remote, IT</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/neurawork-gmbh-co-kg/senior-ai-engineer-agent-architekt-ampfing-390691</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Senior AI Consultant / Machine Learning Engineer (m/w/d) Public Sector | &gt;90% REMOTE</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Bridgency HR Management GbR</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Usingen</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr"/>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Consulting, Engineering</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr"/>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/bridgency-hr-management-gbr/senior-ai-consultant-machine-learning-engineer-public-sector-90-remote-usingen-94077</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Werkstudent (m/w/d) Frontend Development &amp; KI-Integration (20h/Woche)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>MEvents Cross Media GmbH</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>hilfstätigkeit / student</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Remote, Software Development</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/mevents-cross-media-gmbh/werkstudent-frontend-development-ki-integration-20h-woche-berlin-378282</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Valon Mortgage</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>design, saas, python, architect, technical, support, cloud, strategy, management, senior, operations, operational, analytics, reliability, go, engineer, engineering, digital nomad</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr"/>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-senior-data-engineer-valon-mortgage-1131504</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Senior AI Agent Architect / AI Automation Architect</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>artificial intelligence, python, machine learning, engineer, communication</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>WorkingNomads</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
           <t>https://www.workingnomads.com/job/go/1585195/</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>2026-05-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Weiterbildung: Data Science &amp; Business Analytics (IHK) (m/w/d) - Remote</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>DataSmart Point GmbH</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Apprenticeship</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Remote, Data Scientist</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/datasmart-point-gmbh/weiterbildung-data-science-business-analytics-ihk-remote-berlin-23738</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Karrierestart in Data &amp; AI - IHK Data Analyst (m/w/d) - 100 % Online</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>DataSmart Point GmbH</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>Apprenticeship</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr"/>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Data Scientist</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr"/>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/datasmart-point-gmbh/karrierestart-in-data-ai-ihk-data-analyst-100-online-berlin-138911</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Rockstardevelopers: Senior Fullstack Entwickler (m/w/d) mit Projekterfahrung Deutsche Bahn oder DB Systel</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Rockstardevelopers GmbH</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Stuttgart</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>berufserfahren</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>Remote, Software Development</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/rockstardevelopers-gmbh/rockstardevelopers-senior-fullstack-entwickler-mit-projekterfahrung-deutsche-bahn-oder-db-systel-stuttgart-354361</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Full-Stack AI Engineer (Computer Vision &amp; Back-end Focus)</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>StellDirVor GmbH</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr"/>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Software Development</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr"/>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/stelldirvor-gmbh/full-stack-ai-engineer-computer-vision-back-end-focus-munich-122395</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Prove</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="2" t="inlineStr"/>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>software, security, senior, engineer, engineering</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>RemoteOK</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>https://remoteOK.com/remote-jobs/remote-senior-software-engineer-prove-1131482</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Akuity</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr"/>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>saas, developer, software, code, devops, senior, engineer, engineering, backend, digital nomad</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr"/>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>RemoteOK</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>https://remoteOK.com/remote-jobs/remote-senior-backend-engineer-akuity-1131479</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Medical Affairs Solutions Manager UK</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Sorcero</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>manager, growth, operations, biotech</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>RemoteOK</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>https://remoteOK.com/remote-jobs/remote-medical-affairs-solutions-manager-uk-sorcero-1131475</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Dropbox</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Remote - Canada: Select locations</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr"/>
-      <c r="G16" s="4" t="inlineStr"/>
-      <c r="H16" s="4" t="inlineStr"/>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>https://jobs.dropbox.com/listing/7762007?gh_jid=7762007</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Weiterbildung: Data Science &amp; Business Analytics (IHK) (m/w/d) - Remote</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Dropbox</t>
+          <t>DataSmart Point GmbH</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Remote - US: Select locations</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr"/>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Apprenticeship</t>
+        </is>
+      </c>
       <c r="F17" s="2" t="inlineStr"/>
-      <c r="G17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Remote, Data Scientist</t>
+        </is>
+      </c>
       <c r="H17" s="2" t="inlineStr"/>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7762004?gh_jid=7762004</t>
+          <t>https://www.arbeitnow.com/jobs/companies/datasmart-point-gmbh/weiterbildung-data-science-business-analytics-ihk-remote-berlin-23738</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1251,36 +1255,44 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Karrierestart in Data &amp; AI - IHK Data Analyst (m/w/d) - 100 % Online</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Dropbox</t>
+          <t>DataSmart Point GmbH</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Remote - Mexico</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr"/>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Apprenticeship</t>
+        </is>
+      </c>
       <c r="F18" s="4" t="inlineStr"/>
-      <c r="G18" s="4" t="inlineStr"/>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Data Scientist</t>
+        </is>
+      </c>
       <c r="H18" s="4" t="inlineStr"/>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7762009?gh_jid=7762009</t>
+          <t>https://www.arbeitnow.com/jobs/companies/datasmart-point-gmbh/karrierestart-in-data-ai-ihk-data-analyst-100-online-berlin-138911</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
@@ -1292,36 +1304,44 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Frontend Product Software Engineer, Web DX</t>
+          <t>Rockstardevelopers: Senior Fullstack Entwickler (m/w/d) mit Projekterfahrung Deutsche Bahn oder DB Systel</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Dropbox</t>
+          <t>Rockstardevelopers GmbH</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Remote - Mexico</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr"/>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
       <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Remote, Software Development</t>
+        </is>
+      </c>
       <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7580431?gh_jid=7580431</t>
+          <t>https://www.arbeitnow.com/jobs/companies/rockstardevelopers-gmbh/rockstardevelopers-senior-fullstack-entwickler-mit-projekterfahrung-deutsche-bahn-oder-db-systel-stuttgart-354361</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1333,36 +1353,40 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer, Dash Experiences</t>
+          <t>Full-Stack AI Engineer (Computer Vision &amp; Back-end Focus)</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Dropbox</t>
+          <t>StellDirVor GmbH</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Remote - US: Select locations</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr"/>
       <c r="F20" s="4" t="inlineStr"/>
-      <c r="G20" s="4" t="inlineStr"/>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Software Development</t>
+        </is>
+      </c>
       <c r="H20" s="4" t="inlineStr"/>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7569140?gh_jid=7569140</t>
+          <t>https://www.arbeitnow.com/jobs/companies/stelldirvor-gmbh/full-stack-ai-engineer-computer-vision-back-end-focus-munich-122395</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
@@ -1379,31 +1403,35 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer, Dash Experiences</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Dropbox</t>
+          <t>Prove</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Remote - Mexico</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>software, security, senior, engineer, engineering</t>
+        </is>
+      </c>
       <c r="H21" s="2" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7569145?gh_jid=7569145</t>
+          <t>https://remoteOK.com/remote-jobs/remote-senior-software-engineer-prove-1131482</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1420,31 +1448,35 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Product Software Engineer, Payments</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Dropbox</t>
+          <t>Akuity</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Remote - Poland</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr"/>
       <c r="F22" s="4" t="inlineStr"/>
-      <c r="G22" s="4" t="inlineStr"/>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>saas, developer, software, code, devops, senior, engineer, engineering, backend, digital nomad</t>
+        </is>
+      </c>
       <c r="H22" s="4" t="inlineStr"/>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7812915?gh_jid=7812915</t>
+          <t>https://remoteOK.com/remote-jobs/remote-senior-backend-engineer-akuity-1131479</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
@@ -1461,31 +1493,35 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, AI Products</t>
+          <t>Medical Affairs Solutions Manager UK</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Dropbox</t>
+          <t>Sorcero</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Remote - Canada: Select locations</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="2" t="inlineStr"/>
-      <c r="G23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>manager, growth, operations, biotech</t>
+        </is>
+      </c>
       <c r="H23" s="2" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7789389?gh_jid=7789389</t>
+          <t>https://remoteOK.com/remote-jobs/remote-medical-affairs-solutions-manager-uk-sorcero-1131475</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1502,7 +1538,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, AI Products</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1526,7 +1562,7 @@
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7729764?gh_jid=7729764</t>
+          <t>https://jobs.dropbox.com/listing/7762007?gh_jid=7762007</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
@@ -1543,7 +1579,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, AI Products</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1567,7 +1603,7 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7729761?gh_jid=7729761</t>
+          <t>https://jobs.dropbox.com/listing/7762004?gh_jid=7762004</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1584,7 +1620,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, AI Products</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1594,7 +1630,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Remote - US: Select locations</t>
+          <t>Remote - Mexico</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr"/>
@@ -1608,7 +1644,7 @@
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7789386?gh_jid=7789386</t>
+          <t>https://jobs.dropbox.com/listing/7762009?gh_jid=7762009</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
@@ -1625,7 +1661,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Dash Agentic AI</t>
+          <t>Frontend Product Software Engineer, Web DX</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1635,7 +1671,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Remote - Canada: Select locations</t>
+          <t>Remote - Mexico</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr"/>
@@ -1649,7 +1685,7 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7644890?gh_jid=7644890</t>
+          <t>https://jobs.dropbox.com/listing/7580431?gh_jid=7580431</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1666,7 +1702,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Dash Agentic AI</t>
+          <t>Full Stack Software Engineer, Dash Experiences</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -1676,7 +1712,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Remote - US: All locations</t>
+          <t>Remote - US: Select locations</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr"/>
@@ -1690,7 +1726,7 @@
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7644886?gh_jid=7644886</t>
+          <t>https://jobs.dropbox.com/listing/7569140?gh_jid=7569140</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
@@ -1707,7 +1743,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Staff Backend Product Software Engineer, Commerce Platform</t>
+          <t>Full Stack Software Engineer, Dash Experiences</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1731,7 +1767,7 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7759733?gh_jid=7759733</t>
+          <t>https://jobs.dropbox.com/listing/7569145?gh_jid=7569145</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1748,7 +1784,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Staff Backend Product Software Engineer, Commerce Platform</t>
+          <t>Senior Backend Product Software Engineer, Payments</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -1758,7 +1794,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Remote - US: Select locations</t>
+          <t>Remote - Poland</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr"/>
@@ -1772,7 +1808,7 @@
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7759728?gh_jid=7759728</t>
+          <t>https://jobs.dropbox.com/listing/7812915?gh_jid=7812915</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
@@ -1789,7 +1825,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Staff Backend Product Software Engineer, Commerce Platform</t>
+          <t>Senior Data Scientist, AI Products</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1813,7 +1849,7 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7759731?gh_jid=7759731</t>
+          <t>https://jobs.dropbox.com/listing/7789389?gh_jid=7789389</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1830,7 +1866,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Staff Backend Product Software Engineer, Core</t>
+          <t>Senior Data Scientist, AI Products</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -1840,7 +1876,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Remote - US: Select locations</t>
+          <t>Remote - Canada: Select locations</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr"/>
@@ -1854,7 +1890,7 @@
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7421121?gh_jid=7421121</t>
+          <t>https://jobs.dropbox.com/listing/7729764?gh_jid=7729764</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
@@ -1871,7 +1907,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Staff Backend Product Software Engineer, Core</t>
+          <t>Senior Data Scientist, AI Products</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1881,7 +1917,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Remote - Canada: Select locations</t>
+          <t>Remote - US: Select locations</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
@@ -1895,7 +1931,7 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7421124?gh_jid=7421124</t>
+          <t>https://jobs.dropbox.com/listing/7729761?gh_jid=7729761</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -1912,7 +1948,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Staff Fullstack Product Software Engineer, Dash</t>
+          <t>Senior Data Scientist, AI Products</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -1922,7 +1958,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Remote - Canada: Select locations</t>
+          <t>Remote - US: Select locations</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr"/>
@@ -1936,7 +1972,7 @@
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7551548?gh_jid=7551548</t>
+          <t>https://jobs.dropbox.com/listing/7789386?gh_jid=7789386</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
@@ -1953,7 +1989,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Staff Fullstack Product Software Engineer, Dash</t>
+          <t>Senior Machine Learning Engineer, Dash Agentic AI</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -1963,7 +1999,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Remote - US: Select locations</t>
+          <t>Remote - Canada: Select locations</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr"/>
@@ -1977,7 +2013,7 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7551545?gh_jid=7551545</t>
+          <t>https://jobs.dropbox.com/listing/7644890?gh_jid=7644890</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -1994,7 +2030,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Staff Full Stack Software Engineer, Churn</t>
+          <t>Senior Machine Learning Engineer, Dash Agentic AI</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -2004,7 +2040,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Remote - Poland</t>
+          <t>Remote - US: All locations</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr"/>
@@ -2018,7 +2054,7 @@
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7421131?gh_jid=7421131</t>
+          <t>https://jobs.dropbox.com/listing/7644886?gh_jid=7644886</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
@@ -2035,7 +2071,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Staff Fullstack Software Engineer, Growth Monetization</t>
+          <t>Staff Backend Product Software Engineer, Commerce Platform</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2045,7 +2081,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Remote - US: Select locations</t>
+          <t>Remote - Mexico</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr"/>
@@ -2059,7 +2095,7 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7421150?gh_jid=7421150</t>
+          <t>https://jobs.dropbox.com/listing/7759733?gh_jid=7759733</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2076,7 +2112,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Staff Fullstack Software Engineer, Growth Monetization</t>
+          <t>Staff Backend Product Software Engineer, Commerce Platform</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -2086,7 +2122,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Remote - Canada: Select locations</t>
+          <t>Remote - US: Select locations</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr"/>
@@ -2100,7 +2136,7 @@
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7421153?gh_jid=7421153</t>
+          <t>https://jobs.dropbox.com/listing/7759728?gh_jid=7759728</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
@@ -2117,13 +2153,17 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>WALTER: Senior Fullstack Engineer (Ruby+React)</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr"/>
+          <t>Staff Backend Product Software Engineer, Commerce Platform</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Dropbox</t>
+        </is>
+      </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote - Canada: Select locations</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr"/>
@@ -2132,17 +2172,17 @@
       <c r="H39" s="2" t="inlineStr"/>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/walter-senior-fullstack-engineer-ruby-react</t>
+          <t>https://jobs.dropbox.com/listing/7759731?gh_jid=7759731</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
     </row>
@@ -2154,13 +2194,17 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>WALTER: Full-Stack Engineering Lead</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr"/>
+          <t>Staff Backend Product Software Engineer, Core</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>Dropbox</t>
+        </is>
+      </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote - US: Select locations</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr"/>
@@ -2169,17 +2213,17 @@
       <c r="H40" s="4" t="inlineStr"/>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/walter-full-stack-engineering-lead</t>
+          <t>https://jobs.dropbox.com/listing/7421121?gh_jid=7421121</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
     </row>
@@ -2191,7 +2235,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Frontend Product Software Engineer, Design Systems</t>
+          <t>Staff Backend Product Software Engineer, Core</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2201,7 +2245,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Remote - Mexico</t>
+          <t>Remote - Canada: Select locations</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr"/>
@@ -2215,165 +2259,157 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7862086?gh_jid=7862086</t>
+          <t>https://jobs.dropbox.com/listing/7421124?gh_jid=7421124</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Lead AI Engineer &amp; Technical Architect</t>
+          <t>Staff Fullstack Product Software Engineer, Dash</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Bold Business</t>
+          <t>Dropbox</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>India, Latin America, Philippines</t>
+          <t>Remote - Canada: Select locations</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr"/>
       <c r="F42" s="4" t="inlineStr"/>
-      <c r="G42" s="4" t="inlineStr">
-        <is>
-          <t>architect, technical, lead, engineer</t>
-        </is>
-      </c>
+      <c r="G42" s="4" t="inlineStr"/>
       <c r="H42" s="4" t="inlineStr"/>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-lead-ai-engineer-technical-architect-bold-business-1131461</t>
+          <t>https://jobs.dropbox.com/listing/7551548?gh_jid=7551548</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer Showroom</t>
+          <t>Staff Fullstack Product Software Engineer, Dash</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Higharc</t>
+          <t>Dropbox</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote - US: Select locations</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
       <c r="F43" s="2" t="inlineStr"/>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>software, design, 3d, full-stack, support, ux, manager, api, engineer, engineering, backend, digital nomad</t>
-        </is>
-      </c>
+      <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr"/>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-software-engineer-showroom-higharc-1131457</t>
+          <t>https://jobs.dropbox.com/listing/7551545?gh_jid=7551545</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Protocol Review Specialist</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr"/>
+          <t>Staff Full Stack Software Engineer, Churn</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>Dropbox</t>
+        </is>
+      </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote - Poland</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr"/>
       <c r="F44" s="4" t="inlineStr"/>
-      <c r="G44" s="4" t="inlineStr">
-        <is>
-          <t>communication, phone, english</t>
-        </is>
-      </c>
+      <c r="G44" s="4" t="inlineStr"/>
       <c r="H44" s="4" t="inlineStr"/>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>WorkingNomads</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>https://www.workingnomads.com/job/go/1580747/</t>
+          <t>https://jobs.dropbox.com/listing/7421131?gh_jid=7421131</t>
         </is>
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Staff AI Engineer - Notebooks</t>
+          <t>Staff Fullstack Software Engineer, Growth Monetization</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Datadog</t>
+          <t>Dropbox</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Portugal, Remote</t>
+          <t>Remote - US: Select locations</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -2387,34 +2423,34 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>https://careers.datadoghq.com/detail/7627445/?gh_jid=7627445</t>
+          <t>https://jobs.dropbox.com/listing/7421150?gh_jid=7421150</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Staff AI Engineer - Notebooks</t>
+          <t>Staff Fullstack Software Engineer, Growth Monetization</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Datadog</t>
+          <t>Dropbox</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>France, Remote; Germany, Remote; Ireland, Remote; Italy, Remote; Spain, Remote; Switzerland, Remote</t>
+          <t>Remote - Canada: Select locations</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr"/>
@@ -2428,34 +2464,30 @@
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>https://careers.datadoghq.com/detail/7627429/?gh_jid=7627429</t>
+          <t>https://jobs.dropbox.com/listing/7421153?gh_jid=7421153</t>
         </is>
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Ads Conversion Modeling, Machine Learning Engineering Manager</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>Reddit</t>
-        </is>
-      </c>
+          <t>WALTER: Senior Fullstack Engineer (Ruby+React)</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr"/>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr"/>
@@ -2464,12 +2496,12 @@
       <c r="H47" s="2" t="inlineStr"/>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7792848</t>
+          <t>https://weworkremotely.com/remote-jobs/walter-senior-fullstack-engineer-ruby-react</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -2481,22 +2513,18 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Data Scientist, Ads</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>Reddit</t>
-        </is>
-      </c>
+          <t>WALTER: Full-Stack Engineering Lead</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr"/>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Remote - British Columbia, Canada</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr"/>
@@ -2505,12 +2533,12 @@
       <c r="H48" s="4" t="inlineStr"/>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7607124</t>
+          <t>https://weworkremotely.com/remote-jobs/walter-full-stack-engineering-lead</t>
         </is>
       </c>
       <c r="K48" s="4" t="inlineStr">
@@ -2522,22 +2550,22 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Data Scientist, Ads</t>
+          <t>Frontend Product Software Engineer, Design Systems</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Dropbox</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Remote - Mexico</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr"/>
@@ -2551,7 +2579,7 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/6580815</t>
+          <t>https://jobs.dropbox.com/listing/7862086?gh_jid=7862086</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -2568,31 +2596,35 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Lead AI Engineer &amp; Technical Architect</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Bold Business</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Remote - Ontario, Canada</t>
+          <t>India, Latin America, Philippines</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr"/>
       <c r="F50" s="4" t="inlineStr"/>
-      <c r="G50" s="4" t="inlineStr"/>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>architect, technical, lead, engineer</t>
+        </is>
+      </c>
       <c r="H50" s="4" t="inlineStr"/>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7131934</t>
+          <t>https://remoteOK.com/remote-jobs/remote-lead-ai-engineer-technical-architect-bold-business-1131461</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
@@ -2609,31 +2641,35 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Software Engineer Showroom</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Higharc</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr"/>
       <c r="F51" s="2" t="inlineStr"/>
-      <c r="G51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>software, design, 3d, full-stack, support, ux, manager, api, engineer, engineering, backend, digital nomad</t>
+        </is>
+      </c>
       <c r="H51" s="2" t="inlineStr"/>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7131932</t>
+          <t>https://remoteOK.com/remote-jobs/remote-software-engineer-showroom-higharc-1131457</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -2650,31 +2686,31 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Principal Data Scientist, Ads</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>Reddit</t>
-        </is>
-      </c>
+          <t>Protocol Review Specialist</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr"/>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr"/>
       <c r="F52" s="4" t="inlineStr"/>
-      <c r="G52" s="4" t="inlineStr"/>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>communication, phone, english</t>
+        </is>
+      </c>
       <c r="H52" s="4" t="inlineStr"/>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WorkingNomads</t>
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7330347</t>
+          <t>https://www.workingnomads.com/job/go/1580747/</t>
         </is>
       </c>
       <c r="K52" s="4" t="inlineStr">
@@ -2691,17 +2727,17 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Ads</t>
+          <t>Staff AI Engineer - Notebooks</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Datadog</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Remote - British Columbia, Canada</t>
+          <t>Portugal, Remote</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr"/>
@@ -2715,7 +2751,7 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7607121</t>
+          <t>https://careers.datadoghq.com/detail/7627445/?gh_jid=7627445</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -2732,17 +2768,17 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Ads</t>
+          <t>Staff AI Engineer - Notebooks</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Datadog</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>France, Remote; Germany, Remote; Ireland, Remote; Italy, Remote; Spain, Remote; Switzerland, Remote</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr"/>
@@ -2756,7 +2792,7 @@
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/6042236</t>
+          <t>https://careers.datadoghq.com/detail/7627429/?gh_jid=7627429</t>
         </is>
       </c>
       <c r="K54" s="4" t="inlineStr">
@@ -2773,7 +2809,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Consumer</t>
+          <t>Ads Conversion Modeling, Machine Learning Engineering Manager</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -2797,7 +2833,7 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7275414</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7792848</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -2814,7 +2850,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Senior  Machine Learning Engineer, ML Training Platform</t>
+          <t>Data Scientist, Ads</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -2824,7 +2860,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Remote - British Columbia, Canada</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr"/>
@@ -2838,7 +2874,7 @@
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7074776</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7607124</t>
         </is>
       </c>
       <c r="K56" s="4" t="inlineStr">
@@ -2855,7 +2891,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Systems Engineer</t>
+          <t>Data Scientist, Ads</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -2879,7 +2915,7 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7731772</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/6580815</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -2896,7 +2932,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, GenAI Platform</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -2906,7 +2942,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Remote - Ontario, Canada</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr"/>
@@ -2920,7 +2956,7 @@
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7753480</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7131934</t>
         </is>
       </c>
       <c r="K58" s="4" t="inlineStr">
@@ -2937,7 +2973,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Senior Staff Machine Learning Engineer, GenAI Platform</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -2961,7 +2997,7 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7772274</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7131932</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -2978,7 +3014,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Staff Data Scientist, Ads</t>
+          <t>Principal Data Scientist, Ads</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -2988,7 +3024,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Remote - British Columbia, Canada</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr"/>
@@ -3002,7 +3038,7 @@
       </c>
       <c r="J60" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7721851</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7330347</t>
         </is>
       </c>
       <c r="K60" s="4" t="inlineStr">
@@ -3019,7 +3055,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Staff Data Scientist, Ads</t>
+          <t>Senior Data Scientist, Ads</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3029,7 +3065,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Remote - British Columbia, Canada</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr"/>
@@ -3043,7 +3079,7 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7721787</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7607121</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -3060,7 +3096,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Staff Data Scientist, Consumer</t>
+          <t>Senior Data Scientist, Ads</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -3084,7 +3120,7 @@
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/6745284</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/6042236</t>
         </is>
       </c>
       <c r="K62" s="4" t="inlineStr">
@@ -3101,7 +3137,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Staff Data Scientist, Marketing</t>
+          <t>Senior Data Scientist, Consumer</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3125,7 +3161,7 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7445240</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7275414</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -3142,7 +3178,7 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, Ads Auction (Ads Marketplace Quality)</t>
+          <t>Senior  Machine Learning Engineer, ML Training Platform</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -3166,7 +3202,7 @@
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7181821</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7074776</t>
         </is>
       </c>
       <c r="K64" s="4" t="inlineStr">
@@ -3183,7 +3219,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, Ads Content Understanding</t>
+          <t>Senior Machine Learning Systems Engineer</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3207,7 +3243,7 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7851761</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7731772</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -3224,7 +3260,7 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Systems Engineer</t>
+          <t>Senior Software Engineer, GenAI Platform</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -3248,7 +3284,7 @@
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7731788</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7753480</t>
         </is>
       </c>
       <c r="K66" s="4" t="inlineStr">
@@ -3265,44 +3301,36 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Werkstudent:in KI Marketing (m/w/d)</t>
+          <t>Senior Staff Machine Learning Engineer, GenAI Platform</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>laria.ai</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>Working student, berufseinstieg</t>
-        </is>
-      </c>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr"/>
       <c r="F67" s="2" t="inlineStr"/>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>Remote, Online Marketing</t>
-        </is>
-      </c>
+      <c r="G67" s="2" t="inlineStr"/>
       <c r="H67" s="2" t="inlineStr"/>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/lariaai/werkstudentin-ki-marketing-berlin-9847</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7772274</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -3314,107 +3342,99 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Laravel Developer (m/w/d) - AI-First PropTech</t>
+          <t>Staff Data Scientist, Ads</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Immovara GmbH</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Korntal-Münchingen</t>
-        </is>
-      </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>berufserfahren</t>
-        </is>
-      </c>
+          <t>Remote - British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr"/>
       <c r="F68" s="4" t="inlineStr"/>
-      <c r="G68" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Software Development</t>
-        </is>
-      </c>
+      <c r="G68" s="4" t="inlineStr"/>
       <c r="H68" s="4" t="inlineStr"/>
       <c r="I68" s="4" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/immovara-gmbh/laravel-developer-ai-first-proptech-korntal-munchingen-239743</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7721851</t>
         </is>
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning (ML) Engineer - Applied</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr"/>
+          <t>Staff Data Scientist, Ads</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr"/>
       <c r="F69" s="2" t="inlineStr"/>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>machine learning, artificial intelligence, python, cplusplus, startup</t>
-        </is>
-      </c>
+      <c r="G69" s="2" t="inlineStr"/>
       <c r="H69" s="2" t="inlineStr"/>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>WorkingNomads</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>https://www.workingnomads.com/job/go/1578553/</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7721787</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Backend Engineer, AI Security</t>
+          <t>Staff Data Scientist, Consumer</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>New York, San Francisco, Seattle, or Remote (US/Canada)</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr"/>
@@ -3428,34 +3448,34 @@
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7826765</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/6745284</t>
         </is>
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Backend Engineer, Core Tech, Canada</t>
+          <t>Staff Data Scientist, Marketing</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Toronto, CAN-Remote</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr"/>
@@ -3469,34 +3489,34 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=6567253</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7445240</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Backend Engineer, Core Technology</t>
+          <t>Staff Machine Learning Engineer, Ads Auction (Ads Marketplace Quality)</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>US-Remote, Chicago</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr"/>
@@ -3510,34 +3530,34 @@
       </c>
       <c r="J72" s="5" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=6042172</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7181821</t>
         </is>
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Backend Engineer, Developer Experience &amp; Product Platform</t>
+          <t>Staff Machine Learning Engineer, Ads Content Understanding</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Toronto Canada, San Francisco, Remote in US, Remote in Canada</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr"/>
@@ -3551,34 +3571,34 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7292520</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7851761</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Commercial Counsel, Crypto</t>
+          <t>Staff Machine Learning Systems Engineer</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>New York City, Seattle, San Francisco, Chicago, Atlanta, US-Remote</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr"/>
@@ -3592,48 +3612,56 @@
       </c>
       <c r="J74" s="5" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7392188</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7731788</t>
         </is>
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Fullstack Engineer, Privy</t>
+          <t>Werkstudent:in KI Marketing (m/w/d)</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>laria.ai</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">NYC-Privy, US-Remote </t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr"/>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Working student, berufseinstieg</t>
+        </is>
+      </c>
       <c r="F75" s="2" t="inlineStr"/>
-      <c r="G75" s="2" t="inlineStr"/>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Remote, Online Marketing</t>
+        </is>
+      </c>
       <c r="H75" s="2" t="inlineStr"/>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7091959</t>
+          <t>https://www.arbeitnow.com/jobs/companies/lariaai/werkstudentin-ki-marketing-berlin-9847</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -3645,36 +3673,44 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Stripe Assistant</t>
+          <t>Laravel Developer (m/w/d) - AI-First PropTech</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Immovara GmbH</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Seattle; San Francisco; New York City; Remote</t>
-        </is>
-      </c>
-      <c r="E76" s="4" t="inlineStr"/>
+          <t>Korntal-Münchingen</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
       <c r="F76" s="4" t="inlineStr"/>
-      <c r="G76" s="4" t="inlineStr"/>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Software Development</t>
+        </is>
+      </c>
       <c r="H76" s="4" t="inlineStr"/>
       <c r="I76" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J76" s="5" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7629052</t>
+          <t>https://www.arbeitnow.com/jobs/companies/immovara-gmbh/laravel-developer-ai-first-proptech-korntal-munchingen-239743</t>
         </is>
       </c>
       <c r="K76" s="4" t="inlineStr">
@@ -3691,31 +3727,31 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning Manager, Feed Relevance</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>Reddit</t>
-        </is>
-      </c>
+          <t>Machine Learning (ML) Engineer - Applied</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr"/>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr"/>
       <c r="F77" s="2" t="inlineStr"/>
-      <c r="G77" s="2" t="inlineStr"/>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>machine learning, artificial intelligence, python, cplusplus, startup</t>
+        </is>
+      </c>
       <c r="H77" s="2" t="inlineStr"/>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WorkingNomads</t>
         </is>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7802495</t>
+          <t>https://www.workingnomads.com/job/go/1578553/</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -3732,17 +3768,17 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, GenAI Security</t>
+          <t>Backend Engineer, AI Security</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>New York, San Francisco, Seattle, or Remote (US/Canada)</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr"/>
@@ -3756,7 +3792,7 @@
       </c>
       <c r="J78" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7891887</t>
+          <t>https://stripe.com/jobs/search?gh_jid=7826765</t>
         </is>
       </c>
       <c r="K78" s="4" t="inlineStr">
@@ -3773,17 +3809,17 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Senior Staff Machine Learning Engineer, Feed Relevance</t>
+          <t>Backend Engineer, Core Tech, Canada</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Toronto, CAN-Remote</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr"/>
@@ -3797,7 +3833,7 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7791994</t>
+          <t>https://stripe.com/jobs/search?gh_jid=6567253</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -3814,17 +3850,17 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Senior Staff Machine Learning Engineer, ML Understanding</t>
+          <t>Backend Engineer, Core Technology</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>US-Remote, Chicago</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr"/>
@@ -3838,7 +3874,7 @@
       </c>
       <c r="J80" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7847148</t>
+          <t>https://stripe.com/jobs/search?gh_jid=6042172</t>
         </is>
       </c>
       <c r="K80" s="4" t="inlineStr">
@@ -3855,17 +3891,17 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, Ads Measurement Modeling</t>
+          <t>Backend Engineer, Developer Experience &amp; Product Platform</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Toronto Canada, San Francisco, Remote in US, Remote in Canada</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr"/>
@@ -3879,7 +3915,7 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7890096</t>
+          <t>https://stripe.com/jobs/search?gh_jid=7292520</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -3896,17 +3932,17 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, AI Serving</t>
+          <t>Commercial Counsel, Crypto</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>New York City, Seattle, San Francisco, Chicago, Atlanta, US-Remote</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr"/>
@@ -3920,7 +3956,7 @@
       </c>
       <c r="J82" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7886459</t>
+          <t>https://stripe.com/jobs/search?gh_jid=7392188</t>
         </is>
       </c>
       <c r="K82" s="4" t="inlineStr">
@@ -3937,17 +3973,17 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (L3) - Full Stack</t>
+          <t>Fullstack Engineer, Privy</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Remote - US</t>
+          <t xml:space="preserve">NYC-Privy, US-Remote </t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr"/>
@@ -3961,7 +3997,7 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7738955</t>
+          <t>https://stripe.com/jobs/search?gh_jid=7091959</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -3971,265 +4007,229 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="A84" s="4" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>AI Developer (Claude + AWS)</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Datavent</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>Hamburg</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr"/>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>Remote, Software Development</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr"/>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/datavent/ai-developer-claude-aws-hamburg-22354</t>
-        </is>
-      </c>
-      <c r="K84" s="2" t="inlineStr">
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Stripe Assistant</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>Seattle; San Francisco; New York City; Remote</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr"/>
+      <c r="F84" s="4" t="inlineStr"/>
+      <c r="G84" s="4" t="inlineStr"/>
+      <c r="H84" s="4" t="inlineStr"/>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J84" s="5" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=7629052</t>
+        </is>
+      </c>
+      <c r="K84" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="4" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Machine Learning Manager, Feed Relevance</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr"/>
+      <c r="F85" s="2" t="inlineStr"/>
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr"/>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7802495</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="B85" s="4" t="inlineStr">
-        <is>
-          <t>Python Software Engineer, Backend &amp; APIs - Remote</t>
-        </is>
-      </c>
-      <c r="C85" s="4" t="inlineStr">
-        <is>
-          <t>dexter health</t>
-        </is>
-      </c>
-      <c r="D85" s="4" t="inlineStr">
-        <is>
-          <t>Cologne</t>
-        </is>
-      </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
-      <c r="F85" s="4" t="inlineStr"/>
-      <c r="G85" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Software Development</t>
-        </is>
-      </c>
-      <c r="H85" s="4" t="inlineStr"/>
-      <c r="I85" s="4" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J85" s="5" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/python-software-engineer-backend-apis-remote-cologne-284750</t>
-        </is>
-      </c>
-      <c r="K85" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>Fullstack Developer (m/w/d) REMOTE //  UX / Python / Vue.js</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>Pont Connects e.K.</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>Düsseldorf</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr"/>
-      <c r="F86" s="2" t="inlineStr"/>
-      <c r="G86" s="2" t="inlineStr">
-        <is>
-          <t>Remote, IT</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr"/>
-      <c r="I86" s="2" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/pont-connects-ek/fullstack-developer-remote-ux-python-vuejs-dusseldorf-371903</t>
-        </is>
-      </c>
-      <c r="K86" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-03</t>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer, GenAI Security</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr"/>
+      <c r="F86" s="4" t="inlineStr"/>
+      <c r="G86" s="4" t="inlineStr"/>
+      <c r="H86" s="4" t="inlineStr"/>
+      <c r="I86" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J86" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7891887</t>
+        </is>
+      </c>
+      <c r="K86" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Staff Machine Learning Engineer, Feed Relevance</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Lemon.io</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Americas, Europe, Asia, Oceania</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>full_time</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>Devops</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="inlineStr">
-        <is>
-          <t>.Net, android, AWS, azure, C, C#, C++, data science, golang, ios, java, javascript, kubernetes, node.js, php, python, react, ruby/rails, shopify, sql, video, blockchain, AI/ML, automation, react native, rust, unity, spring, data analysis, laravel, solidity, flask, Typescript , terraform, angular , GCP, data engineering, Symfony, startup, marketplace, next.js</t>
-        </is>
-      </c>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr"/>
+      <c r="F87" s="2" t="inlineStr"/>
+      <c r="G87" s="2" t="inlineStr"/>
       <c r="H87" s="2" t="inlineStr"/>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>Remotive</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>https://remotive.com/remote-jobs/devops/senior-devops-engineer-2090002</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7791994</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-05</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>M&amp;A Research Analyst</t>
+          <t>Senior Staff Machine Learning Engineer, ML Understanding</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>EquiMatch GmbH</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E88" s="4" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr"/>
       <c r="F88" s="4" t="inlineStr"/>
-      <c r="G88" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Mergers &amp; Acquisitions</t>
-        </is>
-      </c>
+      <c r="G88" s="4" t="inlineStr"/>
       <c r="H88" s="4" t="inlineStr"/>
       <c r="I88" s="4" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J88" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/equimatch-gmbh/ma-research-analyst-berlin-498635</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7847148</t>
         </is>
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-05</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Xsolla: Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr"/>
+          <t>Staff Machine Learning Engineer, Ads Measurement Modeling</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr"/>
@@ -4238,35 +4238,39 @@
       <c r="H89" s="2" t="inlineStr"/>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/xsolla-full-stack-developer</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7890096</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-05</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Dropbox: Staff Fullstack Product Software Engineer, Dash</t>
-        </is>
-      </c>
-      <c r="C90" s="4" t="inlineStr"/>
+          <t>Staff Machine Learning Engineer, AI Serving</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr"/>
@@ -4275,39 +4279,39 @@
       <c r="H90" s="4" t="inlineStr"/>
       <c r="I90" s="4" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J90" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/dropbox-staff-fullstack-product-software-engineer-dash</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7886459</t>
         </is>
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-05</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, Ranking and Personalization</t>
+          <t>Senior Software Engineer (L3) - Full Stack</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Remote - US</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr"/>
@@ -4321,45 +4325,45 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7848689</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7738955</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-05</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Senior Rust Consultant / Engineer (m/w/d)</t>
+          <t>AI Developer (Claude + AWS)</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Hackstack GmbH</t>
+          <t>Datavent</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Hamburg</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>berufserfahren</t>
+          <t>professional / experienced</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr"/>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Remote, Consulting, Engineering</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr"/>
@@ -4370,24 +4374,24 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/hackstack-gmbh/senior-rust-consultant-engineer-munich-451602</t>
+          <t>https://www.arbeitnow.com/jobs/companies/datavent/ai-developer-claude-aws-hamburg-22354</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Applied AI Engineer - Remote</t>
+          <t>Python Software Engineer, Backend &amp; APIs - Remote</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -4408,7 +4412,7 @@
       <c r="F93" s="4" t="inlineStr"/>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>Remote, Development</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr"/>
@@ -4419,45 +4423,41 @@
       </c>
       <c r="J93" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/applied-ai-engineer-remote-cologne-2870</t>
+          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/python-software-engineer-backend-apis-remote-cologne-284750</t>
         </is>
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Python Backend Engineer - Remote</t>
+          <t>Fullstack Developer (m/w/d) REMOTE //  UX / Python / Vue.js</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>dexter health</t>
+          <t>Pont Connects e.K.</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Cologne</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
+          <t>Düsseldorf</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr"/>
       <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Remote, Development</t>
+          <t>Remote, IT</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr"/>
@@ -4468,253 +4468,273 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/python-backend-engineer-remote-cologne-34228</t>
+          <t>https://www.arbeitnow.com/jobs/companies/pont-connects-ek/fullstack-developer-remote-ux-python-vuejs-dusseldorf-371903</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Lemon.io</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Americas, Europe, Asia, Oceania</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>full_time</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>Devops</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>.Net, android, AWS, azure, C, C#, C++, data science, golang, ios, java, javascript, kubernetes, node.js, php, python, react, ruby/rails, shopify, sql, video, blockchain, AI/ML, automation, react native, rust, unity, spring, data analysis, laravel, solidity, flask, Typescript , terraform, angular , GCP, data engineering, Symfony, startup, marketplace, next.js</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr"/>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>Remotive</t>
+        </is>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/devops/senior-devops-engineer-2090002</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>M&amp;A Research Analyst</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>EquiMatch GmbH</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr"/>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Mergers &amp; Acquisitions</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="inlineStr"/>
+      <c r="I96" s="4" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J96" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/equimatch-gmbh/ma-research-analyst-berlin-498635</t>
+        </is>
+      </c>
+      <c r="K96" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
           <t>2026-05-01</t>
         </is>
       </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="4" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Xsolla: Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr"/>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr"/>
+      <c r="F97" s="2" t="inlineStr"/>
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr"/>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>WeWorkRemotely</t>
+        </is>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>https://weworkremotely.com/remote-jobs/xsolla-full-stack-developer</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="B95" s="4" t="inlineStr">
-        <is>
-          <t>AI Engineer (LLM Products) - Remote</t>
-        </is>
-      </c>
-      <c r="C95" s="4" t="inlineStr">
-        <is>
-          <t>dexter health</t>
-        </is>
-      </c>
-      <c r="D95" s="4" t="inlineStr">
-        <is>
-          <t>Cologne</t>
-        </is>
-      </c>
-      <c r="E95" s="4" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
-      <c r="F95" s="4" t="inlineStr"/>
-      <c r="G95" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Development</t>
-        </is>
-      </c>
-      <c r="H95" s="4" t="inlineStr"/>
-      <c r="I95" s="4" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J95" s="5" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/ai-engineer-llm-products-remote-cologne-236027</t>
-        </is>
-      </c>
-      <c r="K95" s="4" t="inlineStr">
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>Dropbox: Staff Fullstack Product Software Engineer, Dash</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr"/>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr"/>
+      <c r="F98" s="4" t="inlineStr"/>
+      <c r="G98" s="4" t="inlineStr"/>
+      <c r="H98" s="4" t="inlineStr"/>
+      <c r="I98" s="4" t="inlineStr">
+        <is>
+          <t>WeWorkRemotely</t>
+        </is>
+      </c>
+      <c r="J98" s="5" t="inlineStr">
+        <is>
+          <t>https://weworkremotely.com/remote-jobs/dropbox-staff-fullstack-product-software-engineer-dash</t>
+        </is>
+      </c>
+      <c r="K98" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>Backend Python Engineer (APIs, Databases &amp; Cloud) - Remote</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>dexter health</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>Cologne</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
-      <c r="F96" s="2" t="inlineStr"/>
-      <c r="G96" s="2" t="inlineStr">
-        <is>
-          <t>Remote, Development</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr"/>
-      <c r="I96" s="2" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/backend-python-engineer-apis-databases-cloud-remote-cologne-274767</t>
-        </is>
-      </c>
-      <c r="K96" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B97" s="4" t="inlineStr">
-        <is>
-          <t>Toptal: QA Automation Engineer</t>
-        </is>
-      </c>
-      <c r="C97" s="4" t="inlineStr"/>
-      <c r="D97" s="4" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E97" s="4" t="inlineStr"/>
-      <c r="F97" s="4" t="inlineStr"/>
-      <c r="G97" s="4" t="inlineStr"/>
-      <c r="H97" s="4" t="inlineStr"/>
-      <c r="I97" s="4" t="inlineStr">
-        <is>
-          <t>WeWorkRemotely</t>
-        </is>
-      </c>
-      <c r="J97" s="5" t="inlineStr">
-        <is>
-          <t>https://weworkremotely.com/remote-jobs/toptal-qa-automation-engineer-1</t>
-        </is>
-      </c>
-      <c r="K97" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>Opensea: Staff Product Designer</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr"/>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr"/>
-      <c r="F98" s="2" t="inlineStr"/>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr"/>
-      <c r="I98" s="2" t="inlineStr">
-        <is>
-          <t>WeWorkRemotely</t>
-        </is>
-      </c>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>https://weworkremotely.com/remote-jobs/opensea-staff-product-designer</t>
-        </is>
-      </c>
-      <c r="K98" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B99" s="4" t="inlineStr">
-        <is>
-          <t>Mutt Data: Devops</t>
-        </is>
-      </c>
-      <c r="C99" s="4" t="inlineStr"/>
-      <c r="D99" s="4" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E99" s="4" t="inlineStr"/>
-      <c r="F99" s="4" t="inlineStr"/>
-      <c r="G99" s="4" t="inlineStr"/>
-      <c r="H99" s="4" t="inlineStr"/>
-      <c r="I99" s="4" t="inlineStr">
-        <is>
-          <t>WeWorkRemotely</t>
-        </is>
-      </c>
-      <c r="J99" s="5" t="inlineStr">
-        <is>
-          <t>https://weworkremotely.com/remote-jobs/mutt-data-devops</t>
-        </is>
-      </c>
-      <c r="K99" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Staff Machine Learning Engineer, Ranking and Personalization</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr"/>
+      <c r="F99" s="2" t="inlineStr"/>
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr"/>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7848689</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Holywater: Full-Stack Developer</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr"/>
+          <t>Senior Rust Consultant / Engineer (m/w/d)</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Hackstack GmbH</t>
+        </is>
+      </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr"/>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
       <c r="F100" s="2" t="inlineStr"/>
-      <c r="G100" s="2" t="inlineStr"/>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>Remote, Consulting, Engineering</t>
+        </is>
+      </c>
       <c r="H100" s="2" t="inlineStr"/>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/holywater-full-stack-developer</t>
+          <t>https://www.arbeitnow.com/jobs/companies/hackstack-gmbh/senior-rust-consultant-engineer-munich-451602</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -4726,32 +4746,44 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Qventus: DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="C101" s="4" t="inlineStr"/>
+          <t>Applied AI Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>dexter health</t>
+        </is>
+      </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E101" s="4" t="inlineStr"/>
+          <t>Cologne</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
       <c r="F101" s="4" t="inlineStr"/>
-      <c r="G101" s="4" t="inlineStr"/>
+      <c r="G101" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Development</t>
+        </is>
+      </c>
       <c r="H101" s="4" t="inlineStr"/>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J101" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/qventus-devops-engineer</t>
+          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/applied-ai-engineer-remote-cologne-2870</t>
         </is>
       </c>
       <c r="K101" s="4" t="inlineStr">
@@ -4763,32 +4795,44 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Visualis: Senior Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr"/>
+          <t>Python Backend Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>dexter health</t>
+        </is>
+      </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr"/>
+          <t>Cologne</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
       <c r="F102" s="2" t="inlineStr"/>
-      <c r="G102" s="2" t="inlineStr"/>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>Remote, Development</t>
+        </is>
+      </c>
       <c r="H102" s="2" t="inlineStr"/>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/visualis-senior-full-stack-developer</t>
+          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/python-backend-engineer-remote-cologne-34228</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -4800,36 +4844,44 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>AI Engineer (LLM Products) - Remote</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>GitLab</t>
+          <t>dexter health</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Remote, Bangalore</t>
-        </is>
-      </c>
-      <c r="E103" s="4" t="inlineStr"/>
+          <t>Cologne</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
       <c r="F103" s="4" t="inlineStr"/>
-      <c r="G103" s="4" t="inlineStr"/>
+      <c r="G103" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Development</t>
+        </is>
+      </c>
       <c r="H103" s="4" t="inlineStr"/>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J103" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8517564002</t>
+          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/ai-engineer-llm-products-remote-cologne-236027</t>
         </is>
       </c>
       <c r="K103" s="4" t="inlineStr">
@@ -4841,36 +4893,44 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Backend Engineer, Analytics Instrumentation (Golang)</t>
+          <t>Backend Python Engineer (APIs, Databases &amp; Cloud) - Remote</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>GitLab</t>
+          <t>dexter health</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Remote, India</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr"/>
+          <t>Cologne</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
       <c r="F104" s="2" t="inlineStr"/>
-      <c r="G104" s="2" t="inlineStr"/>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>Remote, Development</t>
+        </is>
+      </c>
       <c r="H104" s="2" t="inlineStr"/>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481922002</t>
+          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/backend-python-engineer-apis-databases-cloud-remote-cologne-274767</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -4887,17 +4947,13 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Backend Engineer, Analytics Instrumentation (Golang)</t>
-        </is>
-      </c>
-      <c r="C105" s="4" t="inlineStr">
-        <is>
-          <t>GitLab</t>
-        </is>
-      </c>
+          <t>Toptal: QA Automation Engineer</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr"/>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr"/>
@@ -4906,12 +4962,12 @@
       <c r="H105" s="4" t="inlineStr"/>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J105" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481929002</t>
+          <t>https://weworkremotely.com/remote-jobs/toptal-qa-automation-engineer-1</t>
         </is>
       </c>
       <c r="K105" s="4" t="inlineStr">
@@ -4928,17 +4984,13 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Backend Engineer, Knowledge Graph (Rust)</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>GitLab</t>
-        </is>
-      </c>
+          <t>Opensea: Staff Product Designer</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr"/>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, US</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr"/>
@@ -4947,12 +4999,12 @@
       <c r="H106" s="2" t="inlineStr"/>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8437754002</t>
+          <t>https://weworkremotely.com/remote-jobs/opensea-staff-product-designer</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -4969,17 +5021,13 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Backend Engineer, Knowledge Graph (Rust)</t>
-        </is>
-      </c>
-      <c r="C107" s="4" t="inlineStr">
-        <is>
-          <t>GitLab</t>
-        </is>
-      </c>
+          <t>Mutt Data: Devops</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr"/>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr"/>
@@ -4988,12 +5036,12 @@
       <c r="H107" s="4" t="inlineStr"/>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J107" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481958002</t>
+          <t>https://weworkremotely.com/remote-jobs/mutt-data-devops</t>
         </is>
       </c>
       <c r="K107" s="4" t="inlineStr">
@@ -5010,17 +5058,13 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Intermediate Backend Engineer (C), Tenant Scale: Git</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>GitLab</t>
-        </is>
-      </c>
+          <t>Holywater: Full-Stack Developer</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr"/>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr"/>
@@ -5029,12 +5073,12 @@
       <c r="H108" s="2" t="inlineStr"/>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8497793002</t>
+          <t>https://weworkremotely.com/remote-jobs/holywater-full-stack-developer</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -5051,17 +5095,13 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Intermediate Backend Engineer, Gitlab Delivery: Upgrades</t>
-        </is>
-      </c>
-      <c r="C109" s="4" t="inlineStr">
-        <is>
-          <t>GitLab</t>
-        </is>
-      </c>
+          <t>Qventus: DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr"/>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr"/>
@@ -5070,12 +5110,12 @@
       <c r="H109" s="4" t="inlineStr"/>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J109" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8463951002</t>
+          <t>https://weworkremotely.com/remote-jobs/qventus-devops-engineer</t>
         </is>
       </c>
       <c r="K109" s="4" t="inlineStr">
@@ -5092,14 +5132,10 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Intermediate Backend Engineer, SRM: Security Platform Management</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>GitLab</t>
-        </is>
-      </c>
+          <t>Visualis: Senior Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr"/>
       <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Remote</t>
@@ -5111,12 +5147,12 @@
       <c r="H110" s="2" t="inlineStr"/>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8443325002</t>
+          <t>https://weworkremotely.com/remote-jobs/visualis-senior-full-stack-developer</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -5133,7 +5169,7 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Intermediate Backend Engineer, SSCS: AI Governance</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
@@ -5143,7 +5179,7 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, Bangalore</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr"/>
@@ -5157,7 +5193,7 @@
       </c>
       <c r="J111" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480551002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8517564002</t>
         </is>
       </c>
       <c r="K111" s="4" t="inlineStr">
@@ -5174,7 +5210,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Intermediate Backend Engineer,  SSCS: Supply Chain</t>
+          <t>Backend Engineer, Analytics Instrumentation (Golang)</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -5198,7 +5234,7 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480565002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481922002</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -5215,7 +5251,7 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Backend Engineer, Analytics Instrumentation (Golang)</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
@@ -5225,7 +5261,7 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Remote, EMEA</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr"/>
@@ -5239,7 +5275,7 @@
       </c>
       <c r="J113" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8464072002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481929002</t>
         </is>
       </c>
       <c r="K113" s="4" t="inlineStr">
@@ -5256,7 +5292,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (AI), Pipeline Execution</t>
+          <t>Backend Engineer, Knowledge Graph (Rust)</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -5266,7 +5302,7 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US-Southeast</t>
+          <t>Remote, Canada; Remote, US</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr"/>
@@ -5280,7 +5316,7 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8514945002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8437754002</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -5297,7 +5333,7 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Analytics Instrumentation (Golang)</t>
+          <t>Backend Engineer, Knowledge Graph (Rust)</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
@@ -5307,7 +5343,7 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, US</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr"/>
@@ -5321,7 +5357,7 @@
       </c>
       <c r="J115" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8451512002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481958002</t>
         </is>
       </c>
       <c r="K115" s="4" t="inlineStr">
@@ -5338,7 +5374,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (C), Tenant Scale: Git</t>
+          <t>Intermediate Backend Engineer (C), Tenant Scale: Git</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -5362,7 +5398,7 @@
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8497791002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8497793002</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -5379,7 +5415,7 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Gitlab Delivery: Runway (Platform Engineering)</t>
+          <t>Intermediate Backend Engineer, Gitlab Delivery: Upgrades</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
@@ -5389,7 +5425,7 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Remote, Australia; Remote, India; Remote, Ireland; Remote, Japan; Remote, Netherlands; Remote, Singapore; Remote, United Kingdom</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr"/>
@@ -5403,7 +5439,7 @@
       </c>
       <c r="J117" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8324132002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8463951002</t>
         </is>
       </c>
       <c r="K117" s="4" t="inlineStr">
@@ -5420,7 +5456,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Gitlab Delivery: Upgrades</t>
+          <t>Intermediate Backend Engineer, SRM: Security Platform Management</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -5430,7 +5466,7 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr"/>
@@ -5444,7 +5480,7 @@
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8463933002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8443325002</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -5461,7 +5497,7 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer(Go), Continuous Delivery</t>
+          <t>Intermediate Backend Engineer, SSCS: AI Governance</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
@@ -5485,7 +5521,7 @@
       </c>
       <c r="J119" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8488966002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480551002</t>
         </is>
       </c>
       <c r="K119" s="4" t="inlineStr">
@@ -5502,7 +5538,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer(Golang),Software Supply Chain Security: Auth Infrastructure</t>
+          <t>Intermediate Backend Engineer,  SSCS: Supply Chain</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -5512,7 +5548,7 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Remote, Americas; Remote, APAC; Remote, Canada</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr"/>
@@ -5526,7 +5562,7 @@
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8157520002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480565002</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -5543,7 +5579,7 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (RoR), AST: Secret Detection</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
@@ -5553,7 +5589,7 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
+          <t>Remote, EMEA</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr"/>
@@ -5567,7 +5603,7 @@
       </c>
       <c r="J121" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8432262002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8464072002</t>
         </is>
       </c>
       <c r="K121" s="4" t="inlineStr">
@@ -5584,7 +5620,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (RoR/Go), SSCS: Pipeline Security</t>
+          <t>Senior Backend Engineer (AI), Pipeline Execution</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -5594,7 +5630,7 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
+          <t>Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US-Southeast</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr"/>
@@ -5608,7 +5644,7 @@
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8432221002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8514945002</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -5625,7 +5661,7 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (RoR), SSCS: Authorization</t>
+          <t>Senior Backend Engineer, Analytics Instrumentation (Golang)</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
@@ -5635,7 +5671,7 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
+          <t>Remote, Canada; Remote, US</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr"/>
@@ -5649,7 +5685,7 @@
       </c>
       <c r="J123" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8457315002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8451512002</t>
         </is>
       </c>
       <c r="K123" s="4" t="inlineStr">
@@ -5666,7 +5702,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby or Golang), Tenant Scale; Cells Infrastructure</t>
+          <t>Senior Backend Engineer (C), Tenant Scale: Git</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -5676,7 +5712,7 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Remote, APAC; Remote, Canada; Remote, EMEA; Remote, US</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr"/>
@@ -5690,7 +5726,7 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8437148002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8497791002</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -5707,7 +5743,7 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, SSCS: AI Governance</t>
+          <t>Senior Backend Engineer, Gitlab Delivery: Runway (Platform Engineering)</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
@@ -5717,7 +5753,7 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, Australia; Remote, India; Remote, Ireland; Remote, Japan; Remote, Netherlands; Remote, Singapore; Remote, United Kingdom</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr"/>
@@ -5731,7 +5767,7 @@
       </c>
       <c r="J125" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480544002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8324132002</t>
         </is>
       </c>
       <c r="K125" s="4" t="inlineStr">
@@ -5748,7 +5784,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer,  SSCS: Supply Chain</t>
+          <t>Senior Backend Engineer, Gitlab Delivery: Upgrades</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -5772,7 +5808,7 @@
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480580002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8463933002</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -5789,7 +5825,7 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>Senior Fullstack Engineer (TypeScript), AI Engineering: Editor Extensions</t>
+          <t>Senior Backend Engineer(Go), Continuous Delivery</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
@@ -5799,7 +5835,7 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Remote, APAC; Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US-Southeast</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr"/>
@@ -5813,7 +5849,7 @@
       </c>
       <c r="J127" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8452278002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8488966002</t>
         </is>
       </c>
       <c r="K127" s="4" t="inlineStr">
@@ -5830,7 +5866,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer, Analytics Instrumentation (Golang)</t>
+          <t>Senior Backend Engineer(Golang),Software Supply Chain Security: Auth Infrastructure</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -5840,7 +5876,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, Americas; Remote, APAC; Remote, Canada</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr"/>
@@ -5854,7 +5890,7 @@
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8508027002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8157520002</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -5871,7 +5907,7 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer, AST: Composition Analysis</t>
+          <t>Senior Backend Engineer (RoR), AST: Secret Detection</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
@@ -5881,7 +5917,7 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Remote, Australia; Remote, Canada; Remote, India; Remote, Ireland; Remote, Israel; Remote, Japan; Remote, Netherlands; Remote, New Zealand; Remote, United Kingdom; Remote, US</t>
+          <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr"/>
@@ -5895,7 +5931,7 @@
       </c>
       <c r="J129" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8478364002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8432262002</t>
         </is>
       </c>
       <c r="K129" s="4" t="inlineStr">
@@ -5912,7 +5948,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer, Developer Experience</t>
+          <t>Senior Backend Engineer (RoR/Go), SSCS: Pipeline Security</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -5922,7 +5958,7 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, United Kingdom; Remote, US</t>
+          <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr"/>
@@ -5936,7 +5972,7 @@
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8490477002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8432221002</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
@@ -5953,7 +5989,7 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer, Gitlab Delivery: Upgrades</t>
+          <t>Senior Backend Engineer (RoR), SSCS: Authorization</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
@@ -5963,7 +5999,7 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr"/>
@@ -5977,7 +6013,7 @@
       </c>
       <c r="J131" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8463922002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8457315002</t>
         </is>
       </c>
       <c r="K131" s="4" t="inlineStr">
@@ -5994,7 +6030,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer (Go), Continuous Delivery</t>
+          <t>Senior Backend Engineer (Ruby or Golang), Tenant Scale; Cells Infrastructure</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -6004,7 +6040,7 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, APAC; Remote, Canada; Remote, EMEA; Remote, US</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr"/>
@@ -6018,7 +6054,7 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8488961002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8437148002</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -6035,7 +6071,7 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer (Go), Software Supply Chain Security: Secrets Management</t>
+          <t>Senior Backend Engineer, SSCS: AI Governance</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
@@ -6045,7 +6081,7 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr"/>
@@ -6059,7 +6095,7 @@
       </c>
       <c r="J133" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8432235002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480544002</t>
         </is>
       </c>
       <c r="K133" s="4" t="inlineStr">
@@ -6076,7 +6112,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer, Knowledge Graph (Rust)</t>
+          <t>Senior Backend Engineer,  SSCS: Supply Chain</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -6100,7 +6136,7 @@
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481945002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480580002</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
@@ -6117,7 +6153,7 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer,  Software Supply Chain Security</t>
+          <t>Senior Fullstack Engineer (TypeScript), AI Engineering: Editor Extensions</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
@@ -6127,7 +6163,7 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, APAC; Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US-Southeast</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr"/>
@@ -6141,7 +6177,7 @@
       </c>
       <c r="J135" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480559002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8452278002</t>
         </is>
       </c>
       <c r="K135" s="4" t="inlineStr">
@@ -6158,7 +6194,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer, SSCS: AI Governance</t>
+          <t>Staff Backend Engineer, Analytics Instrumentation (Golang)</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -6182,7 +6218,7 @@
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480531002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8508027002</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -6199,7 +6235,7 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Staff Backend (Python) Engineer, AI Engineering:Duo Chat</t>
+          <t>Staff Backend Engineer, AST: Composition Analysis</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
@@ -6209,7 +6245,7 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>Remote, Americas; Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom</t>
+          <t>Remote, Australia; Remote, Canada; Remote, India; Remote, Ireland; Remote, Israel; Remote, Japan; Remote, Netherlands; Remote, New Zealand; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr"/>
@@ -6223,7 +6259,7 @@
       </c>
       <c r="J137" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8450446002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8478364002</t>
         </is>
       </c>
       <c r="K137" s="4" t="inlineStr">
@@ -6240,17 +6276,17 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Senior Full Stack Product Software Engineer</t>
+          <t>Staff Backend Engineer, Developer Experience</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Dropbox</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Remote - Poland</t>
+          <t>Remote, Canada; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr"/>
@@ -6264,444 +6300,340 @@
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8490477002</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>Staff Backend Engineer, Gitlab Delivery: Upgrades</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>GitLab</t>
+        </is>
+      </c>
+      <c r="D139" s="4" t="inlineStr">
+        <is>
+          <t>Remote, India</t>
+        </is>
+      </c>
+      <c r="E139" s="4" t="inlineStr"/>
+      <c r="F139" s="4" t="inlineStr"/>
+      <c r="G139" s="4" t="inlineStr"/>
+      <c r="H139" s="4" t="inlineStr"/>
+      <c r="I139" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J139" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8463922002</t>
+        </is>
+      </c>
+      <c r="K139" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>Staff Backend Engineer (Go), Continuous Delivery</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>GitLab</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Remote, India</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr"/>
+      <c r="F140" s="2" t="inlineStr"/>
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr"/>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8488961002</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>Staff Backend Engineer (Go), Software Supply Chain Security: Secrets Management</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>GitLab</t>
+        </is>
+      </c>
+      <c r="D141" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
+        </is>
+      </c>
+      <c r="E141" s="4" t="inlineStr"/>
+      <c r="F141" s="4" t="inlineStr"/>
+      <c r="G141" s="4" t="inlineStr"/>
+      <c r="H141" s="4" t="inlineStr"/>
+      <c r="I141" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J141" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8432235002</t>
+        </is>
+      </c>
+      <c r="K141" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>Staff Backend Engineer, Knowledge Graph (Rust)</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>GitLab</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Remote, India</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr"/>
+      <c r="F142" s="2" t="inlineStr"/>
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr"/>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J142" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481945002</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t>Staff Backend Engineer,  Software Supply Chain Security</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="inlineStr">
+        <is>
+          <t>GitLab</t>
+        </is>
+      </c>
+      <c r="D143" s="4" t="inlineStr">
+        <is>
+          <t>Remote, India</t>
+        </is>
+      </c>
+      <c r="E143" s="4" t="inlineStr"/>
+      <c r="F143" s="4" t="inlineStr"/>
+      <c r="G143" s="4" t="inlineStr"/>
+      <c r="H143" s="4" t="inlineStr"/>
+      <c r="I143" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J143" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480559002</t>
+        </is>
+      </c>
+      <c r="K143" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>Staff Backend Engineer, SSCS: AI Governance</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>GitLab</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Remote, India</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr"/>
+      <c r="F144" s="2" t="inlineStr"/>
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr"/>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J144" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480531002</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>Staff Backend (Python) Engineer, AI Engineering:Duo Chat</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>GitLab</t>
+        </is>
+      </c>
+      <c r="D145" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Americas; Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom</t>
+        </is>
+      </c>
+      <c r="E145" s="4" t="inlineStr"/>
+      <c r="F145" s="4" t="inlineStr"/>
+      <c r="G145" s="4" t="inlineStr"/>
+      <c r="H145" s="4" t="inlineStr"/>
+      <c r="I145" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J145" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8450446002</t>
+        </is>
+      </c>
+      <c r="K145" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Product Software Engineer</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>Dropbox</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Remote - Poland</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr"/>
+      <c r="F146" s="2" t="inlineStr"/>
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr"/>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J146" s="3" t="inlineStr">
+        <is>
           <t>https://jobs.dropbox.com/listing/6449719?gh_jid=6449719</t>
         </is>
       </c>
-      <c r="K138" s="2" t="inlineStr">
+      <c r="K146" s="2" t="inlineStr">
         <is>
           <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>Dry Ground AI</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
-        <is>
-          <t>Brazil, Colombia, Philippines</t>
-        </is>
-      </c>
-      <c r="E139" s="2" t="inlineStr">
-        <is>
-          <t>full_time</t>
-        </is>
-      </c>
-      <c r="F139" s="2" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence</t>
-        </is>
-      </c>
-      <c r="G139" s="2" t="inlineStr">
-        <is>
-          <t>api, cloud, fullstack, python, AI/ML, automation, research, CI/CD, TensorFlow, spark, NLP, CMS, Pytorch, REST</t>
-        </is>
-      </c>
-      <c r="H139" s="2" t="inlineStr">
-        <is>
-          <t>$40- $60k</t>
-        </is>
-      </c>
-      <c r="I139" s="2" t="inlineStr">
-        <is>
-          <t>Remotive</t>
-        </is>
-      </c>
-      <c r="J139" s="3" t="inlineStr">
-        <is>
-          <t>https://remotive.com/remote-jobs/artificial-intelligence/ai-engineer-2089958</t>
-        </is>
-      </c>
-      <c r="K139" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B140" s="4" t="inlineStr">
-        <is>
-          <t>Senior Independent AI Engineer / Architect</t>
-        </is>
-      </c>
-      <c r="C140" s="4" t="inlineStr">
-        <is>
-          <t>A.Team</t>
-        </is>
-      </c>
-      <c r="D140" s="4" t="inlineStr">
-        <is>
-          <t>Americas, Europe, Israel</t>
-        </is>
-      </c>
-      <c r="E140" s="4" t="inlineStr">
-        <is>
-          <t>contract</t>
-        </is>
-      </c>
-      <c r="F140" s="4" t="inlineStr">
-        <is>
-          <t>Software Development</t>
-        </is>
-      </c>
-      <c r="G140" s="4" t="inlineStr">
-        <is>
-          <t>go, UI/UX, wordpress, chat, apple, testing, catalyst</t>
-        </is>
-      </c>
-      <c r="H140" s="4" t="inlineStr">
-        <is>
-          <t>$120 - $170 /hour</t>
-        </is>
-      </c>
-      <c r="I140" s="4" t="inlineStr">
-        <is>
-          <t>Remotive</t>
-        </is>
-      </c>
-      <c r="J140" s="5" t="inlineStr">
-        <is>
-          <t>https://remotive.com/remote-jobs/software-development/senior-independent-ai-engineer-architect-1919266</t>
-        </is>
-      </c>
-      <c r="K140" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>Senior Independent Software Developer</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>A.Team</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
-        <is>
-          <t>Americas, Europe, Israel</t>
-        </is>
-      </c>
-      <c r="E141" s="2" t="inlineStr">
-        <is>
-          <t>contract</t>
-        </is>
-      </c>
-      <c r="F141" s="2" t="inlineStr">
-        <is>
-          <t>Software Development</t>
-        </is>
-      </c>
-      <c r="G141" s="2" t="inlineStr">
-        <is>
-          <t>go, wordpress, chat, apple, testing, catalyst</t>
-        </is>
-      </c>
-      <c r="H141" s="2" t="inlineStr">
-        <is>
-          <t>$90 - $150 /hour</t>
-        </is>
-      </c>
-      <c r="I141" s="2" t="inlineStr">
-        <is>
-          <t>Remotive</t>
-        </is>
-      </c>
-      <c r="J141" s="3" t="inlineStr">
-        <is>
-          <t>https://remotive.com/remote-jobs/software-development/senior-independent-software-developer-1919265</t>
-        </is>
-      </c>
-      <c r="K141" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B142" s="4" t="inlineStr">
-        <is>
-          <t>Senior Full-stack React Developer</t>
-        </is>
-      </c>
-      <c r="C142" s="4" t="inlineStr">
-        <is>
-          <t>Lemon.io</t>
-        </is>
-      </c>
-      <c r="D142" s="4" t="inlineStr">
-        <is>
-          <t>Americas, Europe, Asia, Oceania</t>
-        </is>
-      </c>
-      <c r="E142" s="4" t="inlineStr">
-        <is>
-          <t>contract</t>
-        </is>
-      </c>
-      <c r="F142" s="4" t="inlineStr">
-        <is>
-          <t>Software Development</t>
-        </is>
-      </c>
-      <c r="G142" s="4" t="inlineStr">
-        <is>
-          <t>.Net, android, AWS, azure, backend, C, C#, C++, data science, fullstack, golang, ios, java, javascript, node.js, php, python, react, react js, ruby/rails, shopify, video, blockchain, AI/ML, react native, rust, unity, spring, data analysis, laravel, solidity, flask, Typescript , angular , GCP, data engineering, Symfony, startup, marketplace, next.js</t>
-        </is>
-      </c>
-      <c r="H142" s="4" t="inlineStr"/>
-      <c r="I142" s="4" t="inlineStr">
-        <is>
-          <t>Remotive</t>
-        </is>
-      </c>
-      <c r="J142" s="5" t="inlineStr">
-        <is>
-          <t>https://remotive.com/remote-jobs/software-development/senior-full-stack-react-developer-2088711</t>
-        </is>
-      </c>
-      <c r="K142" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>Tech Lead Full-Stack Rails Engineer</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>Mitre Media</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
-        <is>
-          <t>USA, Canada, USA timezones</t>
-        </is>
-      </c>
-      <c r="E143" s="2" t="inlineStr">
-        <is>
-          <t>full_time</t>
-        </is>
-      </c>
-      <c r="F143" s="2" t="inlineStr">
-        <is>
-          <t>Software Development</t>
-        </is>
-      </c>
-      <c r="G143" s="2" t="inlineStr">
-        <is>
-          <t>api, CSS, docker, elasticsearch, fullstack, html, javascript, kubernetes, postgresql, react, ror, ruby/rails, AI/ML, CAD, advertising, Redis, ES6, web applications, MySQL, NLP, fintech, Micro services, github, system architecture</t>
-        </is>
-      </c>
-      <c r="H143" s="2" t="inlineStr">
-        <is>
-          <t>$170k - $200k</t>
-        </is>
-      </c>
-      <c r="I143" s="2" t="inlineStr">
-        <is>
-          <t>Remotive</t>
-        </is>
-      </c>
-      <c r="J143" s="3" t="inlineStr">
-        <is>
-          <t>https://remotive.com/remote-jobs/software-development/tech-lead-full-stack-rails-engineer-2069746</t>
-        </is>
-      </c>
-      <c r="K143" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B144" s="4" t="inlineStr">
-        <is>
-          <t>Senior Frontend Developer</t>
-        </is>
-      </c>
-      <c r="C144" s="4" t="inlineStr">
-        <is>
-          <t>Sanctuary Computer</t>
-        </is>
-      </c>
-      <c r="D144" s="4" t="inlineStr">
-        <is>
-          <t>LATAM, Asia</t>
-        </is>
-      </c>
-      <c r="E144" s="4" t="inlineStr">
-        <is>
-          <t>contract</t>
-        </is>
-      </c>
-      <c r="F144" s="4" t="inlineStr">
-        <is>
-          <t>Software Development</t>
-        </is>
-      </c>
-      <c r="G144" s="4" t="inlineStr">
-        <is>
-          <t>api, backend, CSS, ecommerce, frontend, fullstack, graphql, postgresql, redux, security, seo, shopify, open source, paas, product management, documentation, mentoring, Typescript , Redis, web applications, cypress, data visualization, firebase, IoT, engineering management, runtime, responsive, prismic, testing, next.js, CMS, jest, REST, web sockets, performance optimization</t>
-        </is>
-      </c>
-      <c r="H144" s="4" t="inlineStr">
-        <is>
-          <t>$80k - $120k</t>
-        </is>
-      </c>
-      <c r="I144" s="4" t="inlineStr">
-        <is>
-          <t>Remotive</t>
-        </is>
-      </c>
-      <c r="J144" s="5" t="inlineStr">
-        <is>
-          <t>https://remotive.com/remote-jobs/software-development/senior-frontend-developer-2088707</t>
-        </is>
-      </c>
-      <c r="K144" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>Fullstack Developer (US - ET)</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>Chooose</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E145" s="2" t="inlineStr">
-        <is>
-          <t>full_time</t>
-        </is>
-      </c>
-      <c r="F145" s="2" t="inlineStr">
-        <is>
-          <t>Software Development</t>
-        </is>
-      </c>
-      <c r="G145" s="2" t="inlineStr">
-        <is>
-          <t>api, azure, fullstack, python, react, saas, AI/ML, project management, documentation, Typescript , computer science, diversity, insurance</t>
-        </is>
-      </c>
-      <c r="H145" s="2" t="inlineStr"/>
-      <c r="I145" s="2" t="inlineStr">
-        <is>
-          <t>Remotive</t>
-        </is>
-      </c>
-      <c r="J145" s="3" t="inlineStr">
-        <is>
-          <t>https://remotive.com/remote-jobs/software-development/fullstack-developer-us-et-2088706</t>
-        </is>
-      </c>
-      <c r="K145" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B146" s="4" t="inlineStr">
-        <is>
-          <t>Machine Learning Manager, Notifications Relevance</t>
-        </is>
-      </c>
-      <c r="C146" s="4" t="inlineStr">
-        <is>
-          <t>Reddit</t>
-        </is>
-      </c>
-      <c r="D146" s="4" t="inlineStr">
-        <is>
-          <t>Remote - United States</t>
-        </is>
-      </c>
-      <c r="E146" s="4" t="inlineStr"/>
-      <c r="F146" s="4" t="inlineStr"/>
-      <c r="G146" s="4" t="inlineStr"/>
-      <c r="H146" s="4" t="inlineStr"/>
-      <c r="I146" s="4" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J146" s="5" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7846885</t>
-        </is>
-      </c>
-      <c r="K146" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6713,31 +6645,47 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Senior Staff ML Engineer, Search &amp; Recommendation</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Dry Ground AI</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
-        </is>
-      </c>
-      <c r="E147" s="2" t="inlineStr"/>
-      <c r="F147" s="2" t="inlineStr"/>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr"/>
+          <t>Brazil, Colombia, Philippines</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>full_time</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>api, cloud, fullstack, python, AI/ML, automation, research, CI/CD, TensorFlow, spark, NLP, CMS, Pytorch, REST</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>$40- $60k</t>
+        </is>
+      </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>Remotive</t>
         </is>
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7833622</t>
+          <t>https://remotive.com/remote-jobs/artificial-intelligence/ai-engineer-2089958</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
@@ -6754,31 +6702,47 @@
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Independent AI Engineer / Architect</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>A.Team</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>Remote - US</t>
-        </is>
-      </c>
-      <c r="E148" s="4" t="inlineStr"/>
-      <c r="F148" s="4" t="inlineStr"/>
-      <c r="G148" s="4" t="inlineStr"/>
-      <c r="H148" s="4" t="inlineStr"/>
+          <t>Americas, Europe, Israel</t>
+        </is>
+      </c>
+      <c r="E148" s="4" t="inlineStr">
+        <is>
+          <t>contract</t>
+        </is>
+      </c>
+      <c r="F148" s="4" t="inlineStr">
+        <is>
+          <t>Software Development</t>
+        </is>
+      </c>
+      <c r="G148" s="4" t="inlineStr">
+        <is>
+          <t>go, UI/UX, wordpress, chat, apple, testing, catalyst</t>
+        </is>
+      </c>
+      <c r="H148" s="4" t="inlineStr">
+        <is>
+          <t>$120 - $170 /hour</t>
+        </is>
+      </c>
       <c r="I148" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>Remotive</t>
         </is>
       </c>
       <c r="J148" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7059734</t>
+          <t>https://remotive.com/remote-jobs/software-development/senior-independent-ai-engineer-architect-1919266</t>
         </is>
       </c>
       <c r="K148" s="4" t="inlineStr">
@@ -6795,31 +6759,47 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Independent Software Developer</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>A.Team</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>Remote - US</t>
-        </is>
-      </c>
-      <c r="E149" s="2" t="inlineStr"/>
-      <c r="F149" s="2" t="inlineStr"/>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr"/>
+          <t>Americas, Europe, Israel</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>contract</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>Software Development</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>go, wordpress, chat, apple, testing, catalyst</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>$90 - $150 /hour</t>
+        </is>
+      </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>Remotive</t>
         </is>
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7702644</t>
+          <t>https://remotive.com/remote-jobs/software-development/senior-independent-software-developer-1919265</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
@@ -6836,31 +6816,43 @@
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>Principal Machine Learning &amp; Data Engineer</t>
+          <t>Senior Full-stack React Developer</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Lemon.io</t>
         </is>
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>Remote - US</t>
-        </is>
-      </c>
-      <c r="E150" s="4" t="inlineStr"/>
-      <c r="F150" s="4" t="inlineStr"/>
-      <c r="G150" s="4" t="inlineStr"/>
+          <t>Americas, Europe, Asia, Oceania</t>
+        </is>
+      </c>
+      <c r="E150" s="4" t="inlineStr">
+        <is>
+          <t>contract</t>
+        </is>
+      </c>
+      <c r="F150" s="4" t="inlineStr">
+        <is>
+          <t>Software Development</t>
+        </is>
+      </c>
+      <c r="G150" s="4" t="inlineStr">
+        <is>
+          <t>.Net, android, AWS, azure, backend, C, C#, C++, data science, fullstack, golang, ios, java, javascript, node.js, php, python, react, react js, ruby/rails, shopify, video, blockchain, AI/ML, react native, rust, unity, spring, data analysis, laravel, solidity, flask, Typescript , angular , GCP, data engineering, Symfony, startup, marketplace, next.js</t>
+        </is>
+      </c>
       <c r="H150" s="4" t="inlineStr"/>
       <c r="I150" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>Remotive</t>
         </is>
       </c>
       <c r="J150" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7155492</t>
+          <t>https://remotive.com/remote-jobs/software-development/senior-full-stack-react-developer-2088711</t>
         </is>
       </c>
       <c r="K150" s="4" t="inlineStr">
@@ -6877,31 +6869,47 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>Principal, Product Manager - AI / LLM</t>
+          <t>Tech Lead Full-Stack Rails Engineer</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Mitre Media</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>Remote - US</t>
-        </is>
-      </c>
-      <c r="E151" s="2" t="inlineStr"/>
-      <c r="F151" s="2" t="inlineStr"/>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr"/>
+          <t>USA, Canada, USA timezones</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>full_time</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>Software Development</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>api, CSS, docker, elasticsearch, fullstack, html, javascript, kubernetes, postgresql, react, ror, ruby/rails, AI/ML, CAD, advertising, Redis, ES6, web applications, MySQL, NLP, fintech, Micro services, github, system architecture</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>$170k - $200k</t>
+        </is>
+      </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>Remotive</t>
         </is>
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7619420</t>
+          <t>https://remotive.com/remote-jobs/software-development/tech-lead-full-stack-rails-engineer-2069746</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
@@ -6918,31 +6926,47 @@
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>Product Engineer (Backend)</t>
+          <t>Senior Frontend Developer</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Sanctuary Computer</t>
         </is>
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>Remote - US</t>
-        </is>
-      </c>
-      <c r="E152" s="4" t="inlineStr"/>
-      <c r="F152" s="4" t="inlineStr"/>
-      <c r="G152" s="4" t="inlineStr"/>
-      <c r="H152" s="4" t="inlineStr"/>
+          <t>LATAM, Asia</t>
+        </is>
+      </c>
+      <c r="E152" s="4" t="inlineStr">
+        <is>
+          <t>contract</t>
+        </is>
+      </c>
+      <c r="F152" s="4" t="inlineStr">
+        <is>
+          <t>Software Development</t>
+        </is>
+      </c>
+      <c r="G152" s="4" t="inlineStr">
+        <is>
+          <t>api, backend, CSS, ecommerce, frontend, fullstack, graphql, postgresql, redux, security, seo, shopify, open source, paas, product management, documentation, mentoring, Typescript , Redis, web applications, cypress, data visualization, firebase, IoT, engineering management, runtime, responsive, prismic, testing, next.js, CMS, jest, REST, web sockets, performance optimization</t>
+        </is>
+      </c>
+      <c r="H152" s="4" t="inlineStr">
+        <is>
+          <t>$80k - $120k</t>
+        </is>
+      </c>
       <c r="I152" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>Remotive</t>
         </is>
       </c>
       <c r="J152" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7671815</t>
+          <t>https://remotive.com/remote-jobs/software-development/senior-frontend-developer-2088707</t>
         </is>
       </c>
       <c r="K152" s="4" t="inlineStr">
@@ -6959,31 +6983,43 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>Senior Manager, Machine Learning</t>
+          <t>Fullstack Developer (US - ET)</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Chooose</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Remote - US</t>
-        </is>
-      </c>
-      <c r="E153" s="2" t="inlineStr"/>
-      <c r="F153" s="2" t="inlineStr"/>
-      <c r="G153" s="2" t="inlineStr"/>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>full_time</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>Software Development</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>api, azure, fullstack, python, react, saas, AI/ML, project management, documentation, Typescript , computer science, diversity, insurance</t>
+        </is>
+      </c>
       <c r="H153" s="2" t="inlineStr"/>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>Remotive</t>
         </is>
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7066029</t>
+          <t>https://remotive.com/remote-jobs/software-development/fullstack-developer-us-et-2088706</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -7000,17 +7036,17 @@
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>Staff Data Scientist</t>
+          <t>Machine Learning Manager, Notifications Relevance</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>Remote - US</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E154" s="4" t="inlineStr"/>
@@ -7024,7 +7060,7 @@
       </c>
       <c r="J154" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7821458</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7846885</t>
         </is>
       </c>
       <c r="K154" s="4" t="inlineStr">
@@ -7041,17 +7077,17 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Staff, Data Scientist (L4) GTM Data Science &amp; Analytics</t>
+          <t>Senior Staff ML Engineer, Search &amp; Recommendation</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Remote - US</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr"/>
@@ -7065,7 +7101,7 @@
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7851920</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7833622</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -7082,7 +7118,7 @@
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
@@ -7106,7 +7142,7 @@
       </c>
       <c r="J156" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7061880</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7059734</t>
         </is>
       </c>
       <c r="K156" s="4" t="inlineStr">
@@ -7123,7 +7159,7 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer (L4)</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -7133,7 +7169,7 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Remote - India</t>
+          <t>Remote - US</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr"/>
@@ -7147,7 +7183,7 @@
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7520997</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7702644</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -7164,39 +7200,31 @@
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>Senior Python Developer - Django (m/w/d)</t>
+          <t>Principal Machine Learning &amp; Data Engineer</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>sync.blue® GmbH</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>Haltern am See</t>
-        </is>
-      </c>
-      <c r="E158" s="4" t="inlineStr">
-        <is>
-          <t>berufserfahren</t>
-        </is>
-      </c>
+          <t>Remote - US</t>
+        </is>
+      </c>
+      <c r="E158" s="4" t="inlineStr"/>
       <c r="F158" s="4" t="inlineStr"/>
-      <c r="G158" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Software Development</t>
-        </is>
-      </c>
+      <c r="G158" s="4" t="inlineStr"/>
       <c r="H158" s="4" t="inlineStr"/>
       <c r="I158" s="4" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J158" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/syncblue-gmbh/senior-python-developer-django-haltern-am-see-16238</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7155492</t>
         </is>
       </c>
       <c r="K158" s="4" t="inlineStr">
@@ -7213,39 +7241,31 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>Freelance Senior AI Product Manager</t>
+          <t>Principal, Product Manager - AI / LLM</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>nexamind GmbH</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E159" s="2" t="inlineStr">
-        <is>
-          <t>Freelance, professional / experienced</t>
-        </is>
-      </c>
+          <t>Remote - US</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr"/>
       <c r="F159" s="2" t="inlineStr"/>
-      <c r="G159" s="2" t="inlineStr">
-        <is>
-          <t>Remote, Product Management</t>
-        </is>
-      </c>
+      <c r="G159" s="2" t="inlineStr"/>
       <c r="H159" s="2" t="inlineStr"/>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/nexamind-gmbh/freelance-senior-ai-product-manager-berlin-73613</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7619420</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
@@ -7262,39 +7282,31 @@
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>Senior Full-Stack-Entwickler:in React / TypeScript / .NET  100 % Remote, KI-First</t>
+          <t>Product Engineer (Backend)</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>yourMAIL GmbH</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E160" s="4" t="inlineStr">
-        <is>
-          <t>berufserfahren</t>
-        </is>
-      </c>
+          <t>Remote - US</t>
+        </is>
+      </c>
+      <c r="E160" s="4" t="inlineStr"/>
       <c r="F160" s="4" t="inlineStr"/>
-      <c r="G160" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Software Development</t>
-        </is>
-      </c>
+      <c r="G160" s="4" t="inlineStr"/>
       <c r="H160" s="4" t="inlineStr"/>
       <c r="I160" s="4" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J160" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/yourmail-gmbh/senior-full-stack-entwicklerin-react-typescript-net-100-remote-ki-first-berlin-21152</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7671815</t>
         </is>
       </c>
       <c r="K160" s="4" t="inlineStr">
@@ -7311,39 +7323,31 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Senior Frontend-Entwickler:in React / TypeScript, 100 % Remote, KI-First</t>
+          <t>Senior Manager, Machine Learning</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>yourMAIL GmbH</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E161" s="2" t="inlineStr">
-        <is>
-          <t>berufserfahren</t>
-        </is>
-      </c>
+          <t>Remote - US</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr"/>
       <c r="F161" s="2" t="inlineStr"/>
-      <c r="G161" s="2" t="inlineStr">
-        <is>
-          <t>Remote, Software Development</t>
-        </is>
-      </c>
+      <c r="G161" s="2" t="inlineStr"/>
       <c r="H161" s="2" t="inlineStr"/>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/yourmail-gmbh/senior-frontend-entwicklerin-react-typescript-100-remote-ki-first-berlin-288218</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7066029</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
@@ -7360,35 +7364,31 @@
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>Full-Stack Entwickler (m/w/d) - .NET 100% Remote</t>
+          <t>Staff Data Scientist</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>FNTIO</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>Frankfurt am Main</t>
+          <t>Remote - US</t>
         </is>
       </c>
       <c r="E162" s="4" t="inlineStr"/>
       <c r="F162" s="4" t="inlineStr"/>
-      <c r="G162" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Consulting, Engineering</t>
-        </is>
-      </c>
+      <c r="G162" s="4" t="inlineStr"/>
       <c r="H162" s="4" t="inlineStr"/>
       <c r="I162" s="4" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J162" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/fntio/full-stack-entwickler-net-100-remote-frankfurt-am-main-122380</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7821458</t>
         </is>
       </c>
       <c r="K162" s="4" t="inlineStr">
@@ -7405,35 +7405,31 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Staff, Data Scientist (L4) GTM Data Science &amp; Analytics</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>Phantasma Labs</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Remote - US</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr"/>
       <c r="F163" s="2" t="inlineStr"/>
-      <c r="G163" s="2" t="inlineStr">
-        <is>
-          <t>Remote, Engineering</t>
-        </is>
-      </c>
+      <c r="G163" s="2" t="inlineStr"/>
       <c r="H163" s="2" t="inlineStr"/>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/phantasma-labs/machine-learning-engineer-berlin-303955</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7851920</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
@@ -7450,39 +7446,31 @@
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>Technical Data Manager (m/w/d)</t>
+          <t>Staff Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>BMF Media Information Technology GmbH</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>Augsburg</t>
-        </is>
-      </c>
-      <c r="E164" s="4" t="inlineStr">
-        <is>
-          <t>berufserfahren</t>
-        </is>
-      </c>
+          <t>Remote - US</t>
+        </is>
+      </c>
+      <c r="E164" s="4" t="inlineStr"/>
       <c r="F164" s="4" t="inlineStr"/>
-      <c r="G164" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Technical Documentation</t>
-        </is>
-      </c>
+      <c r="G164" s="4" t="inlineStr"/>
       <c r="H164" s="4" t="inlineStr"/>
       <c r="I164" s="4" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J164" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/bmf-media-information-technology-gmbh/technical-data-manager-augsburg-42188</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7061880</t>
         </is>
       </c>
       <c r="K164" s="4" t="inlineStr">
@@ -7499,39 +7487,31 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>Data Integration &amp; API Engineer m/w/d - Bi &amp; Data Automation</t>
+          <t>Staff Machine Learning Engineer (L4)</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>loyos bi GmbH</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>Hamburg</t>
-        </is>
-      </c>
-      <c r="E165" s="2" t="inlineStr">
-        <is>
-          <t>berufserfahren</t>
-        </is>
-      </c>
+          <t>Remote - India</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr"/>
       <c r="F165" s="2" t="inlineStr"/>
-      <c r="G165" s="2" t="inlineStr">
-        <is>
-          <t>Remote, Software Development</t>
-        </is>
-      </c>
+      <c r="G165" s="2" t="inlineStr"/>
       <c r="H165" s="2" t="inlineStr"/>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/loyos-bi-gmbh/data-integration-api-engineer-bi-data-automation-hamburg-66228</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7520997</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
@@ -7548,22 +7528,22 @@
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Python Developer - Django (m/w/d)</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>Coding Partners</t>
+          <t>sync.blue® GmbH</t>
         </is>
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Haltern am See</t>
         </is>
       </c>
       <c r="E166" s="4" t="inlineStr">
         <is>
-          <t>professional / experienced</t>
+          <t>berufserfahren</t>
         </is>
       </c>
       <c r="F166" s="4" t="inlineStr"/>
@@ -7580,7 +7560,7 @@
       </c>
       <c r="J166" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/coding-partners/senior-full-stack-engineer-berlin-391720</t>
+          <t>https://www.arbeitnow.com/jobs/companies/syncblue-gmbh/senior-python-developer-django-haltern-am-see-16238</t>
         </is>
       </c>
       <c r="K166" s="4" t="inlineStr">
@@ -7597,28 +7577,28 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>Laravel Developer (m/w/d) - AI-First PropTech</t>
+          <t>Freelance Senior AI Product Manager</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>Immovara GmbH</t>
+          <t>nexamind GmbH</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>Korntal-Münchingen</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>berufserfahren</t>
+          <t>Freelance, professional / experienced</t>
         </is>
       </c>
       <c r="F167" s="2" t="inlineStr"/>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>Remote, Software Development</t>
+          <t>Remote, Product Management</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr"/>
@@ -7629,7 +7609,7 @@
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/immovara-gmbh/laravel-developer-ai-first-proptech-korntal-munchingen-471269</t>
+          <t>https://www.arbeitnow.com/jobs/companies/nexamind-gmbh/freelance-senior-ai-product-manager-berlin-73613</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
@@ -7646,17 +7626,17 @@
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>Fullstack Softwareentwickler (m/w/d)</t>
+          <t>Senior Full-Stack-Entwickler:in React / TypeScript / .NET  100 % Remote, KI-First</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>TecFox GmbH</t>
+          <t>yourMAIL GmbH</t>
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>Braunschweig</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="E168" s="4" t="inlineStr">
@@ -7678,7 +7658,7 @@
       </c>
       <c r="J168" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/tecfox-gmbh/fullstack-softwareentwickler-braunschweig-405178</t>
+          <t>https://www.arbeitnow.com/jobs/companies/yourmail-gmbh/senior-full-stack-entwicklerin-react-typescript-net-100-remote-ki-first-berlin-21152</t>
         </is>
       </c>
       <c r="K168" s="4" t="inlineStr">
@@ -7695,17 +7675,17 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>Frontend Softwareentwickler (m/w/d)</t>
+          <t>Senior Frontend-Entwickler:in React / TypeScript, 100 % Remote, KI-First</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>TecFox GmbH</t>
+          <t>yourMAIL GmbH</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>Braunschweig</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
@@ -7727,7 +7707,7 @@
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/tecfox-gmbh/frontend-softwareentwickler-braunschweig-341792</t>
+          <t>https://www.arbeitnow.com/jobs/companies/yourmail-gmbh/senior-frontend-entwicklerin-react-typescript-100-remote-ki-first-berlin-288218</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
@@ -7744,28 +7724,24 @@
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>Fullstack-Developer*in (m/w/d) Web &amp; AI Automation</t>
+          <t>Full-Stack Entwickler (m/w/d) - .NET 100% Remote</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>NeoBird Digital</t>
+          <t>FNTIO</t>
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>Nuremberg</t>
-        </is>
-      </c>
-      <c r="E170" s="4" t="inlineStr">
-        <is>
-          <t>berufserfahren</t>
-        </is>
-      </c>
+          <t>Frankfurt am Main</t>
+        </is>
+      </c>
+      <c r="E170" s="4" t="inlineStr"/>
       <c r="F170" s="4" t="inlineStr"/>
       <c r="G170" s="4" t="inlineStr">
         <is>
-          <t>Remote, Software Development</t>
+          <t>Remote, Consulting, Engineering</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr"/>
@@ -7776,7 +7752,7 @@
       </c>
       <c r="J170" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/neobird-digital/fullstack-developerin-web-ai-automation-nuremberg-157752</t>
+          <t>https://www.arbeitnow.com/jobs/companies/fntio/full-stack-entwickler-net-100-remote-frankfurt-am-main-122380</t>
         </is>
       </c>
       <c r="K170" s="4" t="inlineStr">
@@ -7793,24 +7769,24 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer / Backend &amp; Frontend - Bootstrapped SaaS Startup (m/w/d) remote in EU</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>DatAds</t>
+          <t>Phantasma Labs</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>Cologne</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr"/>
       <c r="F171" s="2" t="inlineStr"/>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>Remote, IT</t>
+          <t>Remote, Engineering</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr"/>
@@ -7821,7 +7797,7 @@
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-bootstrapped-saas-startup-remote-in-eu-cologne-82307</t>
+          <t>https://www.arbeitnow.com/jobs/companies/phantasma-labs/machine-learning-engineer-berlin-303955</t>
         </is>
       </c>
       <c r="K171" s="2" t="inlineStr">
@@ -7838,24 +7814,28 @@
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer / Rest APIs / Cloud / TailwindCSS / SaaS Startup (m/w/d) remote in EU</t>
+          <t>Technical Data Manager (m/w/d)</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>DatAds</t>
+          <t>BMF Media Information Technology GmbH</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>Cologne</t>
-        </is>
-      </c>
-      <c r="E172" s="4" t="inlineStr"/>
+          <t>Augsburg</t>
+        </is>
+      </c>
+      <c r="E172" s="4" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
       <c r="F172" s="4" t="inlineStr"/>
       <c r="G172" s="4" t="inlineStr">
         <is>
-          <t>Remote, IT</t>
+          <t>Remote, Technical Documentation</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr"/>
@@ -7866,7 +7846,7 @@
       </c>
       <c r="J172" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-bootstrapped-saas-startup-remote-in-eu-cologne-38634</t>
+          <t>https://www.arbeitnow.com/jobs/companies/bmf-media-information-technology-gmbh/technical-data-manager-augsburg-42188</t>
         </is>
       </c>
       <c r="K172" s="4" t="inlineStr">
@@ -7883,24 +7863,28 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer / Node.js / TypeScript / React / Azure - AdTech SaaS Startup (m/w/d) remote</t>
+          <t>Data Integration &amp; API Engineer m/w/d - Bi &amp; Data Automation</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>DatAds</t>
+          <t>loyos bi GmbH</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>Cologne</t>
-        </is>
-      </c>
-      <c r="E173" s="2" t="inlineStr"/>
+          <t>Hamburg</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
       <c r="F173" s="2" t="inlineStr"/>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>Remote, IT</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr"/>
@@ -7911,7 +7895,7 @@
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-adtech-saas-startup-remote-cologne-263746</t>
+          <t>https://www.arbeitnow.com/jobs/companies/loyos-bi-gmbh/data-integration-api-engineer-bi-data-automation-hamburg-66228</t>
         </is>
       </c>
       <c r="K173" s="2" t="inlineStr">
@@ -7928,17 +7912,17 @@
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>Senior DevOps / Platform Engineer (f/m/x)</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>MAIA</t>
+          <t>Coding Partners</t>
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>Leipzig</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="E174" s="4" t="inlineStr">
@@ -7949,7 +7933,7 @@
       <c r="F174" s="4" t="inlineStr"/>
       <c r="G174" s="4" t="inlineStr">
         <is>
-          <t>Remote, IT</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr"/>
@@ -7960,7 +7944,7 @@
       </c>
       <c r="J174" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/maia/senior-devops-platform-engineer-leipzig-388068</t>
+          <t>https://www.arbeitnow.com/jobs/companies/coding-partners/senior-full-stack-engineer-berlin-391720</t>
         </is>
       </c>
       <c r="K174" s="4" t="inlineStr">
@@ -7972,40 +7956,44 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer AI Infrastructure</t>
+          <t>Laravel Developer (m/w/d) - AI-First PropTech</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>Andromeda Cluster</t>
+          <t>Immovara GmbH</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="E175" s="2" t="inlineStr"/>
+          <t>Korntal-Münchingen</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
       <c r="F175" s="2" t="inlineStr"/>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>design, training, technical, software, code, manager, financial, cloud, management, lead, senior, operations, reliability, go, health, engineer, engineering, linux, digital nomad</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr"/>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-senior-site-reliability-engineer-ai-infrastructure-andromeda-cluster-1131375</t>
+          <t>https://www.arbeitnow.com/jobs/companies/immovara-gmbh/laravel-developer-ai-first-proptech-korntal-munchingen-471269</t>
         </is>
       </c>
       <c r="K175" s="2" t="inlineStr">
@@ -8017,40 +8005,44 @@
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>Senior Financial Analyst Digital Assets</t>
+          <t>Fullstack Softwareentwickler (m/w/d)</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>Exodus Movement Inc.</t>
+          <t>TecFox GmbH</t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E176" s="4" t="inlineStr"/>
+          <t>Braunschweig</t>
+        </is>
+      </c>
+      <c r="E176" s="4" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
       <c r="F176" s="4" t="inlineStr"/>
       <c r="G176" s="4" t="inlineStr">
         <is>
-          <t>analyst, cryptocurrency, support, financial, investment, finance, senior, non tech</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr"/>
       <c r="I176" s="4" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J176" s="5" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-senior-financial-analyst-digital-assets-exodus-movement-inc-1131374</t>
+          <t>https://www.arbeitnow.com/jobs/companies/tecfox-gmbh/fullstack-softwareentwickler-braunschweig-405178</t>
         </is>
       </c>
       <c r="K176" s="4" t="inlineStr">
@@ -8062,40 +8054,44 @@
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>Front End Full Stack Developer</t>
+          <t>Frontend Softwareentwickler (m/w/d)</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>Honor Foods</t>
+          <t>TecFox GmbH</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>Philadelphia, PA</t>
-        </is>
-      </c>
-      <c r="E177" s="2" t="inlineStr"/>
+          <t>Braunschweig</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
       <c r="F177" s="2" t="inlineStr"/>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>developer, front-end, ui, code, web, operational, backend, digital nomad</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr"/>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-front-end-full-stack-developer-honor-foods-1131370</t>
+          <t>https://www.arbeitnow.com/jobs/companies/tecfox-gmbh/frontend-softwareentwickler-braunschweig-341792</t>
         </is>
       </c>
       <c r="K177" s="2" t="inlineStr">
@@ -8107,32 +8103,44 @@
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>Wing Assistant: Full-Stack Developer</t>
-        </is>
-      </c>
-      <c r="C178" s="4" t="inlineStr"/>
+          <t>Fullstack-Developer*in (m/w/d) Web &amp; AI Automation</t>
+        </is>
+      </c>
+      <c r="C178" s="4" t="inlineStr">
+        <is>
+          <t>NeoBird Digital</t>
+        </is>
+      </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E178" s="4" t="inlineStr"/>
+          <t>Nuremberg</t>
+        </is>
+      </c>
+      <c r="E178" s="4" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
       <c r="F178" s="4" t="inlineStr"/>
-      <c r="G178" s="4" t="inlineStr"/>
+      <c r="G178" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Software Development</t>
+        </is>
+      </c>
       <c r="H178" s="4" t="inlineStr"/>
       <c r="I178" s="4" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J178" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/wing-assistant-full-stack-developer</t>
+          <t>https://www.arbeitnow.com/jobs/companies/neobird-digital/fullstack-developerin-web-ai-automation-nuremberg-157752</t>
         </is>
       </c>
       <c r="K178" s="4" t="inlineStr">
@@ -8144,32 +8152,40 @@
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>Qventus: Product Designer</t>
-        </is>
-      </c>
-      <c r="C179" s="2" t="inlineStr"/>
+          <t>Full-Stack Software Engineer / Backend &amp; Frontend - Bootstrapped SaaS Startup (m/w/d) remote in EU</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>DatAds</t>
+        </is>
+      </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Cologne</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr"/>
       <c r="F179" s="2" t="inlineStr"/>
-      <c r="G179" s="2" t="inlineStr"/>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>Remote, IT</t>
+        </is>
+      </c>
       <c r="H179" s="2" t="inlineStr"/>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J179" s="3" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/qventus-product-designer</t>
+          <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-bootstrapped-saas-startup-remote-in-eu-cologne-82307</t>
         </is>
       </c>
       <c r="K179" s="2" t="inlineStr">
@@ -8181,32 +8197,40 @@
     <row r="180">
       <c r="A180" s="4" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>Socure: Senior Product Marketing Manager</t>
-        </is>
-      </c>
-      <c r="C180" s="4" t="inlineStr"/>
+          <t>Full-Stack Software Engineer / Rest APIs / Cloud / TailwindCSS / SaaS Startup (m/w/d) remote in EU</t>
+        </is>
+      </c>
+      <c r="C180" s="4" t="inlineStr">
+        <is>
+          <t>DatAds</t>
+        </is>
+      </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Cologne</t>
         </is>
       </c>
       <c r="E180" s="4" t="inlineStr"/>
       <c r="F180" s="4" t="inlineStr"/>
-      <c r="G180" s="4" t="inlineStr"/>
+      <c r="G180" s="4" t="inlineStr">
+        <is>
+          <t>Remote, IT</t>
+        </is>
+      </c>
       <c r="H180" s="4" t="inlineStr"/>
       <c r="I180" s="4" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J180" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/socure-senior-product-marketing-manager</t>
+          <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-bootstrapped-saas-startup-remote-in-eu-cologne-38634</t>
         </is>
       </c>
       <c r="K180" s="4" t="inlineStr">
@@ -8218,32 +8242,40 @@
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>Blueprint: Product Designer</t>
-        </is>
-      </c>
-      <c r="C181" s="2" t="inlineStr"/>
+          <t>Full-Stack Software Engineer / Node.js / TypeScript / React / Azure - AdTech SaaS Startup (m/w/d) remote</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>DatAds</t>
+        </is>
+      </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Cologne</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr"/>
       <c r="F181" s="2" t="inlineStr"/>
-      <c r="G181" s="2" t="inlineStr"/>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>Remote, IT</t>
+        </is>
+      </c>
       <c r="H181" s="2" t="inlineStr"/>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/blueprint-product-designer</t>
+          <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-adtech-saas-startup-remote-cologne-263746</t>
         </is>
       </c>
       <c r="K181" s="2" t="inlineStr">
@@ -8255,32 +8287,44 @@
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>Interop Labs: Product Marketing Manager</t>
-        </is>
-      </c>
-      <c r="C182" s="4" t="inlineStr"/>
+          <t>Senior DevOps / Platform Engineer (f/m/x)</t>
+        </is>
+      </c>
+      <c r="C182" s="4" t="inlineStr">
+        <is>
+          <t>MAIA</t>
+        </is>
+      </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E182" s="4" t="inlineStr"/>
+          <t>Leipzig</t>
+        </is>
+      </c>
+      <c r="E182" s="4" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
       <c r="F182" s="4" t="inlineStr"/>
-      <c r="G182" s="4" t="inlineStr"/>
+      <c r="G182" s="4" t="inlineStr">
+        <is>
+          <t>Remote, IT</t>
+        </is>
+      </c>
       <c r="H182" s="4" t="inlineStr"/>
       <c r="I182" s="4" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J182" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/interop-labs-product-marketing-manager</t>
+          <t>https://www.arbeitnow.com/jobs/companies/maia/senior-devops-platform-engineer-leipzig-388068</t>
         </is>
       </c>
       <c r="K182" s="4" t="inlineStr">
@@ -8297,31 +8341,35 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Link</t>
+          <t>Senior Site Reliability Engineer AI Infrastructure</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Andromeda Cluster</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>Toronto, Remote in Canada</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr"/>
       <c r="F183" s="2" t="inlineStr"/>
-      <c r="G183" s="2" t="inlineStr"/>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>design, training, technical, software, code, manager, financial, cloud, management, lead, senior, operations, reliability, go, health, engineer, engineering, linux, digital nomad</t>
+        </is>
+      </c>
       <c r="H183" s="2" t="inlineStr"/>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J183" s="3" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=6447175</t>
+          <t>https://remoteOK.com/remote-jobs/remote-senior-site-reliability-engineer-ai-infrastructure-andromeda-cluster-1131375</t>
         </is>
       </c>
       <c r="K183" s="2" t="inlineStr">
@@ -8338,31 +8386,35 @@
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Financial Analyst Digital Assets</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Exodus Movement Inc.</t>
         </is>
       </c>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t>Remote - Ontario, Canada</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E184" s="4" t="inlineStr"/>
       <c r="F184" s="4" t="inlineStr"/>
-      <c r="G184" s="4" t="inlineStr"/>
+      <c r="G184" s="4" t="inlineStr">
+        <is>
+          <t>analyst, cryptocurrency, support, financial, investment, finance, senior, non tech</t>
+        </is>
+      </c>
       <c r="H184" s="4" t="inlineStr"/>
       <c r="I184" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J184" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/6960833</t>
+          <t>https://remoteOK.com/remote-jobs/remote-senior-financial-analyst-digital-assets-exodus-movement-inc-1131374</t>
         </is>
       </c>
       <c r="K184" s="4" t="inlineStr">
@@ -8379,34 +8431,346 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Front End Full Stack Developer</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Honor Foods</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Philadelphia, PA</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr"/>
       <c r="F185" s="2" t="inlineStr"/>
-      <c r="G185" s="2" t="inlineStr"/>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>developer, front-end, ui, code, web, operational, backend, digital nomad</t>
+        </is>
+      </c>
       <c r="H185" s="2" t="inlineStr"/>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
+          <t>https://remoteOK.com/remote-jobs/remote-front-end-full-stack-developer-honor-foods-1131370</t>
+        </is>
+      </c>
+      <c r="K185" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B186" s="4" t="inlineStr">
+        <is>
+          <t>Wing Assistant: Full-Stack Developer</t>
+        </is>
+      </c>
+      <c r="C186" s="4" t="inlineStr"/>
+      <c r="D186" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E186" s="4" t="inlineStr"/>
+      <c r="F186" s="4" t="inlineStr"/>
+      <c r="G186" s="4" t="inlineStr"/>
+      <c r="H186" s="4" t="inlineStr"/>
+      <c r="I186" s="4" t="inlineStr">
+        <is>
+          <t>WeWorkRemotely</t>
+        </is>
+      </c>
+      <c r="J186" s="5" t="inlineStr">
+        <is>
+          <t>https://weworkremotely.com/remote-jobs/wing-assistant-full-stack-developer</t>
+        </is>
+      </c>
+      <c r="K186" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>Qventus: Product Designer</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr"/>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr"/>
+      <c r="F187" s="2" t="inlineStr"/>
+      <c r="G187" s="2" t="inlineStr"/>
+      <c r="H187" s="2" t="inlineStr"/>
+      <c r="I187" s="2" t="inlineStr">
+        <is>
+          <t>WeWorkRemotely</t>
+        </is>
+      </c>
+      <c r="J187" s="3" t="inlineStr">
+        <is>
+          <t>https://weworkremotely.com/remote-jobs/qventus-product-designer</t>
+        </is>
+      </c>
+      <c r="K187" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B188" s="4" t="inlineStr">
+        <is>
+          <t>Socure: Senior Product Marketing Manager</t>
+        </is>
+      </c>
+      <c r="C188" s="4" t="inlineStr"/>
+      <c r="D188" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E188" s="4" t="inlineStr"/>
+      <c r="F188" s="4" t="inlineStr"/>
+      <c r="G188" s="4" t="inlineStr"/>
+      <c r="H188" s="4" t="inlineStr"/>
+      <c r="I188" s="4" t="inlineStr">
+        <is>
+          <t>WeWorkRemotely</t>
+        </is>
+      </c>
+      <c r="J188" s="5" t="inlineStr">
+        <is>
+          <t>https://weworkremotely.com/remote-jobs/socure-senior-product-marketing-manager</t>
+        </is>
+      </c>
+      <c r="K188" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>Blueprint: Product Designer</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr"/>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr"/>
+      <c r="F189" s="2" t="inlineStr"/>
+      <c r="G189" s="2" t="inlineStr"/>
+      <c r="H189" s="2" t="inlineStr"/>
+      <c r="I189" s="2" t="inlineStr">
+        <is>
+          <t>WeWorkRemotely</t>
+        </is>
+      </c>
+      <c r="J189" s="3" t="inlineStr">
+        <is>
+          <t>https://weworkremotely.com/remote-jobs/blueprint-product-designer</t>
+        </is>
+      </c>
+      <c r="K189" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B190" s="4" t="inlineStr">
+        <is>
+          <t>Interop Labs: Product Marketing Manager</t>
+        </is>
+      </c>
+      <c r="C190" s="4" t="inlineStr"/>
+      <c r="D190" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E190" s="4" t="inlineStr"/>
+      <c r="F190" s="4" t="inlineStr"/>
+      <c r="G190" s="4" t="inlineStr"/>
+      <c r="H190" s="4" t="inlineStr"/>
+      <c r="I190" s="4" t="inlineStr">
+        <is>
+          <t>WeWorkRemotely</t>
+        </is>
+      </c>
+      <c r="J190" s="5" t="inlineStr">
+        <is>
+          <t>https://weworkremotely.com/remote-jobs/interop-labs-product-marketing-manager</t>
+        </is>
+      </c>
+      <c r="K190" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer, Link</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Remote in Canada</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr"/>
+      <c r="F191" s="2" t="inlineStr"/>
+      <c r="G191" s="2" t="inlineStr"/>
+      <c r="H191" s="2" t="inlineStr"/>
+      <c r="I191" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J191" s="3" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=6447175</t>
+        </is>
+      </c>
+      <c r="K191" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B192" s="4" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="C192" s="4" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="D192" s="4" t="inlineStr">
+        <is>
+          <t>Remote - Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="E192" s="4" t="inlineStr"/>
+      <c r="F192" s="4" t="inlineStr"/>
+      <c r="G192" s="4" t="inlineStr"/>
+      <c r="H192" s="4" t="inlineStr"/>
+      <c r="I192" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J192" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/6960833</t>
+        </is>
+      </c>
+      <c r="K192" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr"/>
+      <c r="F193" s="2" t="inlineStr"/>
+      <c r="G193" s="2" t="inlineStr"/>
+      <c r="H193" s="2" t="inlineStr"/>
+      <c r="I193" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J193" s="3" t="inlineStr">
+        <is>
           <t>https://job-boards.greenhouse.io/reddit/jobs/6960831</t>
         </is>
       </c>
-      <c r="K185" s="2" t="inlineStr">
+      <c r="K193" s="2" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
@@ -8421,53 +8785,54 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId55"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/remote_jobs.xlsx
+++ b/remote_jobs.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K193"/>
+  <dimension ref="A1:K195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -523,29 +523,29 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer (TypeScript &amp; AWS) (m/w/d)</t>
+          <t>Full-Stack Software Engineer / Backend &amp; Frontend - Bootstrapped SaaS Startup (m/w/d) remote in EU</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>vOffice Software</t>
+          <t>DatAds</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Hamburg</t>
+          <t>Cologne</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Remote, Software Development</t>
+          <t>Remote, IT</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -556,12 +556,12 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/voffice-software/senior-cloud-software-engineer-typescript-aws-hamburg-431856</t>
+          <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-bootstrapped-saas-startup-remote-in-eu-cologne-266336</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
@@ -573,44 +573,44 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer RoR (all identities)</t>
+          <t>Asset Administration Operations Specialist</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Caspar Health</t>
+          <t>Forge Global</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
+          <t>Denver</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr"/>
       <c r="F3" s="4" t="inlineStr"/>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>Remote, Software Development</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr"/>
+          <t>travel, financial, operations, non tech</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>$21 - $24</t>
+        </is>
+      </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/caspar-health/senior-backend-engineer-ror-all-identities-berlin-7147</t>
+          <t>https://remoteOK.com/remote-jobs/remote-asset-administration-operations-specialist-forge-global-1131523</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
@@ -622,24 +622,20 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Python Software Engineer - Machine Learning Systems (m/f/d)</t>
+          <t>Senior Cloud Software Engineer (TypeScript &amp; AWS) (m/w/d)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>CUJU</t>
+          <t>vOffice Software</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Frankenthal</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
+          <t>Hamburg</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -654,7 +650,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/cuju/python-software-engineer-machine-learning-systems-frankenthal-183273</t>
+          <t>https://www.arbeitnow.com/jobs/companies/voffice-software/senior-cloud-software-engineer-typescript-aws-hamburg-431856</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -671,28 +667,28 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>AI Algorithm Developer Medical Imaging (m/w/d)</t>
+          <t>Senior Backend Engineer RoR (all identities)</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>citema systems GmbH</t>
+          <t>Caspar Health</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>berufserfahren</t>
+          <t>professional / experienced</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>Remote, IT</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
@@ -703,7 +699,7 @@
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/citema-systems-gmbh/ai-algorithm-developer-medical-imaging-munich-91573</t>
+          <t>https://www.arbeitnow.com/jobs/companies/caspar-health/senior-backend-engineer-ror-all-identities-berlin-7147</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -715,40 +711,44 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Python Software Engineer - Machine Learning Systems (m/f/d)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Civitech</t>
+          <t>CUJU</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Austin, TX or Remote</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr"/>
+          <t>Frankenthal</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>python, support, code, cloud, analytics, engineer, engineering, full-time</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-analytics-engineer-civitech-1131512</t>
+          <t>https://www.arbeitnow.com/jobs/companies/cuju/python-software-engineer-machine-learning-systems-frankenthal-183273</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -760,40 +760,44 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Tech Lead</t>
+          <t>AI Algorithm Developer Medical Imaging (m/w/d)</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Zensurance</t>
+          <t>citema systems GmbH</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Toronto, ON</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr"/>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
       <c r="F7" s="4" t="inlineStr"/>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>design, system, front-end, back-end, security, training, full-stack, docker, technical, support, software, testing, test, growth, code, web, scrum, devops, javascript, education, strategy, management, lead, senior, health, engineering, digital nomad</t>
+          <t>Remote, IT</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-tech-lead-zensurance-1131509</t>
+          <t>https://www.arbeitnow.com/jobs/companies/citema-systems-gmbh/ai-algorithm-developer-medical-imaging-munich-91573</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -810,31 +814,35 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Senior Full-stack Symfony Developer</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr"/>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Civitech</t>
+        </is>
+      </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Austin, TX or Remote</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>symfony, php, javascript, vuejs</t>
+          <t>python, support, code, cloud, analytics, engineer, engineering, full-time</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>WorkingNomads</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>https://www.workingnomads.com/job/go/1587815/</t>
+          <t>https://remoteOK.com/remote-jobs/remote-analytics-engineer-civitech-1131512</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -851,31 +859,35 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Senior Staff Machine Learning Engineer, Feed Relevance</t>
+          <t>Tech Lead</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Zensurance</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Toronto, ON</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr"/>
       <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="4" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>design, system, front-end, back-end, security, training, full-stack, docker, technical, support, software, testing, test, growth, code, web, scrum, devops, javascript, education, strategy, management, lead, senior, health, engineering, digital nomad</t>
+        </is>
+      </c>
       <c r="H9" s="4" t="inlineStr"/>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7908786</t>
+          <t>https://remoteOK.com/remote-jobs/remote-tech-lead-zensurance-1131509</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
@@ -892,40 +904,36 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Sidebase Open-Source Contributor &amp; Senior TS Dev (f/m/d)</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Sidestream</t>
-        </is>
-      </c>
+          <t>Senior Full-stack Symfony Developer</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Cologne</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Remote, Software Development</t>
+          <t>symfony, php, javascript, vuejs</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>WorkingNomads</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/sidestream/sidebase-open-source-contributor-senior-ts-dev-cologne-317648</t>
+          <t>https://www.workingnomads.com/job/go/1587815/</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -937,40 +945,36 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Senior Typescript Developer (f/m/d)</t>
+          <t>Senior Staff Machine Learning Engineer, Feed Relevance</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Sidestream</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Cologne</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr"/>
       <c r="F11" s="4" t="inlineStr"/>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Software Development</t>
-        </is>
-      </c>
+      <c r="G11" s="4" t="inlineStr"/>
       <c r="H11" s="4" t="inlineStr"/>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/sidestream/senior-typescript-developer-cologne-220463</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7908786</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -982,24 +986,24 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Senior AI-Engineer / Agent-Architekt (m/w/d)</t>
+          <t>Sidebase Open-Source Contributor &amp; Senior TS Dev (f/m/d)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Neurawork GmbH &amp; Co. KG</t>
+          <t>Sidestream</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Ampfing</t>
+          <t>Cologne</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Remote, IT</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
@@ -1010,7 +1014,7 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/neurawork-gmbh-co-kg/senior-ai-engineer-agent-architekt-ampfing-390691</t>
+          <t>https://www.arbeitnow.com/jobs/companies/sidestream/sidebase-open-source-contributor-senior-ts-dev-cologne-317648</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1027,28 +1031,24 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Senior AI Consultant / Machine Learning Engineer (m/w/d) Public Sector | &gt;90% REMOTE</t>
+          <t>Senior Typescript Developer (f/m/d)</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Bridgency HR Management GbR</t>
+          <t>Sidestream</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Usingen</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>berufserfahren</t>
-        </is>
-      </c>
+          <t>Cologne</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr"/>
       <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>Remote, Consulting, Engineering</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/bridgency-hr-management-gbr/senior-ai-consultant-machine-learning-engineer-public-sector-90-remote-usingen-94077</t>
+          <t>https://www.arbeitnow.com/jobs/companies/sidestream/senior-typescript-developer-cologne-220463</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
@@ -1076,28 +1076,24 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Werkstudent (m/w/d) Frontend Development &amp; KI-Integration (20h/Woche)</t>
+          <t>Senior AI-Engineer / Agent-Architekt (m/w/d)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>MEvents Cross Media GmbH</t>
+          <t>Neurawork GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>hilfstätigkeit / student</t>
-        </is>
-      </c>
+          <t>Ampfing</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Remote, Software Development</t>
+          <t>Remote, IT</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
@@ -1108,7 +1104,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/mevents-cross-media-gmbh/werkstudent-frontend-development-ki-integration-20h-woche-berlin-378282</t>
+          <t>https://www.arbeitnow.com/jobs/companies/neurawork-gmbh-co-kg/senior-ai-engineer-agent-architekt-ampfing-390691</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1120,40 +1116,44 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Consultant / Machine Learning Engineer (m/w/d) Public Sector | &gt;90% REMOTE</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Valon Mortgage</t>
+          <t>Bridgency HR Management GbR</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr"/>
+          <t>Usingen</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
       <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>design, saas, python, architect, technical, support, cloud, strategy, management, senior, operations, operational, analytics, reliability, go, engineer, engineering, digital nomad</t>
+          <t>Remote, Consulting, Engineering</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-senior-data-engineer-valon-mortgage-1131504</t>
+          <t>https://www.arbeitnow.com/jobs/companies/bridgency-hr-management-gbr/senior-ai-consultant-machine-learning-engineer-public-sector-90-remote-usingen-94077</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
@@ -1165,139 +1165,135 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Senior AI Agent Architect / AI Automation Architect</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr"/>
+          <t>Werkstudent (m/w/d) Frontend Development &amp; KI-Integration (20h/Woche)</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>MEvents Cross Media GmbH</t>
+        </is>
+      </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr"/>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>hilfstätigkeit / student</t>
+        </is>
+      </c>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>artificial intelligence, python, machine learning, engineer, communication</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/mevents-cross-media-gmbh/werkstudent-frontend-development-ki-integration-20h-woche-berlin-378282</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Valon Mortgage</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr"/>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>design, saas, python, architect, technical, support, cloud, strategy, management, senior, operations, operational, analytics, reliability, go, engineer, engineering, digital nomad</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-senior-data-engineer-valon-mortgage-1131504</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Senior AI Agent Architect / AI Automation Architect</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr"/>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>artificial intelligence, python, machine learning, engineer, communication</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
           <t>WorkingNomads</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t>https://www.workingnomads.com/job/go/1585195/</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>2026-05-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Weiterbildung: Data Science &amp; Business Analytics (IHK) (m/w/d) - Remote</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>DataSmart Point GmbH</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Apprenticeship</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr"/>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Remote, Data Scientist</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr"/>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/datasmart-point-gmbh/weiterbildung-data-science-business-analytics-ihk-remote-berlin-23738</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Karrierestart in Data &amp; AI - IHK Data Analyst (m/w/d) - 100 % Online</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>DataSmart Point GmbH</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>Apprenticeship</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr"/>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Data Scientist</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr"/>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/datasmart-point-gmbh/karrierestart-in-data-ai-ihk-data-analyst-100-online-berlin-138911</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
         </is>
       </c>
     </row>
@@ -1309,28 +1305,28 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Rockstardevelopers: Senior Fullstack Entwickler (m/w/d) mit Projekterfahrung Deutsche Bahn oder DB Systel</t>
+          <t>Weiterbildung: Data Science &amp; Business Analytics (IHK) (m/w/d) - Remote</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Rockstardevelopers GmbH</t>
+          <t>DataSmart Point GmbH</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>berufserfahren</t>
+          <t>Apprenticeship</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Remote, Software Development</t>
+          <t>Remote, Data Scientist</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr"/>
@@ -1341,7 +1337,7 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/rockstardevelopers-gmbh/rockstardevelopers-senior-fullstack-entwickler-mit-projekterfahrung-deutsche-bahn-oder-db-systel-stuttgart-354361</t>
+          <t>https://www.arbeitnow.com/jobs/companies/datasmart-point-gmbh/weiterbildung-data-science-business-analytics-ihk-remote-berlin-23738</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1358,24 +1354,28 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Full-Stack AI Engineer (Computer Vision &amp; Back-end Focus)</t>
+          <t>Karrierestart in Data &amp; AI - IHK Data Analyst (m/w/d) - 100 % Online</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>StellDirVor GmbH</t>
+          <t>DataSmart Point GmbH</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr"/>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Apprenticeship</t>
+        </is>
+      </c>
       <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>Remote, Software Development</t>
+          <t>Remote, Data Scientist</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr"/>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/stelldirvor-gmbh/full-stack-ai-engineer-computer-vision-back-end-focus-munich-122395</t>
+          <t>https://www.arbeitnow.com/jobs/companies/datasmart-point-gmbh/karrierestart-in-data-ai-ihk-data-analyst-100-online-berlin-138911</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
@@ -1398,40 +1398,44 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Rockstardevelopers: Senior Fullstack Entwickler (m/w/d) mit Projekterfahrung Deutsche Bahn oder DB Systel</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Prove</t>
+          <t>Rockstardevelopers GmbH</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr"/>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>software, security, senior, engineer, engineering</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-senior-software-engineer-prove-1131482</t>
+          <t>https://www.arbeitnow.com/jobs/companies/rockstardevelopers-gmbh/rockstardevelopers-senior-fullstack-entwickler-mit-projekterfahrung-deutsche-bahn-oder-db-systel-stuttgart-354361</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1443,40 +1447,40 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Full-Stack AI Engineer (Computer Vision &amp; Back-end Focus)</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Akuity</t>
+          <t>StellDirVor GmbH</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr"/>
       <c r="F22" s="4" t="inlineStr"/>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>saas, developer, software, code, devops, senior, engineer, engineering, backend, digital nomad</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr"/>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-senior-backend-engineer-akuity-1131479</t>
+          <t>https://www.arbeitnow.com/jobs/companies/stelldirvor-gmbh/full-stack-ai-engineer-computer-vision-back-end-focus-munich-122395</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
@@ -1493,24 +1497,24 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Medical Affairs Solutions Manager UK</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Sorcero</t>
+          <t>Prove</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>manager, growth, operations, biotech</t>
+          <t>software, security, senior, engineer, engineering</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr"/>
@@ -1521,7 +1525,7 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-medical-affairs-solutions-manager-uk-sorcero-1131475</t>
+          <t>https://remoteOK.com/remote-jobs/remote-senior-software-engineer-prove-1131482</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1538,31 +1542,35 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Dropbox</t>
+          <t>Akuity</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Remote - Canada: Select locations</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr"/>
       <c r="F24" s="4" t="inlineStr"/>
-      <c r="G24" s="4" t="inlineStr"/>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>saas, developer, software, code, devops, senior, engineer, engineering, backend, digital nomad</t>
+        </is>
+      </c>
       <c r="H24" s="4" t="inlineStr"/>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7762007?gh_jid=7762007</t>
+          <t>https://remoteOK.com/remote-jobs/remote-senior-backend-engineer-akuity-1131479</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
@@ -1579,31 +1587,35 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Medical Affairs Solutions Manager UK</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Dropbox</t>
+          <t>Sorcero</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Remote - US: Select locations</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>manager, growth, operations, biotech</t>
+        </is>
+      </c>
       <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7762004?gh_jid=7762004</t>
+          <t>https://remoteOK.com/remote-jobs/remote-medical-affairs-solutions-manager-uk-sorcero-1131475</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1630,7 +1642,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Remote - Mexico</t>
+          <t>Remote - Canada: Select locations</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr"/>
@@ -1644,7 +1656,7 @@
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7762009?gh_jid=7762009</t>
+          <t>https://jobs.dropbox.com/listing/7762007?gh_jid=7762007</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
@@ -1661,7 +1673,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Frontend Product Software Engineer, Web DX</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1671,7 +1683,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Remote - Mexico</t>
+          <t>Remote - US: Select locations</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr"/>
@@ -1685,7 +1697,7 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7580431?gh_jid=7580431</t>
+          <t>https://jobs.dropbox.com/listing/7762004?gh_jid=7762004</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1702,7 +1714,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer, Dash Experiences</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -1712,7 +1724,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Remote - US: Select locations</t>
+          <t>Remote - Mexico</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr"/>
@@ -1726,7 +1738,7 @@
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7569140?gh_jid=7569140</t>
+          <t>https://jobs.dropbox.com/listing/7762009?gh_jid=7762009</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
@@ -1743,7 +1755,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer, Dash Experiences</t>
+          <t>Frontend Product Software Engineer, Web DX</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1767,7 +1779,7 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7569145?gh_jid=7569145</t>
+          <t>https://jobs.dropbox.com/listing/7580431?gh_jid=7580431</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1784,7 +1796,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Product Software Engineer, Payments</t>
+          <t>Full Stack Software Engineer, Dash Experiences</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -1794,7 +1806,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Remote - Poland</t>
+          <t>Remote - US: Select locations</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr"/>
@@ -1808,7 +1820,7 @@
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7812915?gh_jid=7812915</t>
+          <t>https://jobs.dropbox.com/listing/7569140?gh_jid=7569140</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
@@ -1825,7 +1837,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, AI Products</t>
+          <t>Full Stack Software Engineer, Dash Experiences</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1835,7 +1847,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Remote - Canada: Select locations</t>
+          <t>Remote - Mexico</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
@@ -1849,7 +1861,7 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7789389?gh_jid=7789389</t>
+          <t>https://jobs.dropbox.com/listing/7569145?gh_jid=7569145</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1866,7 +1878,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, AI Products</t>
+          <t>Senior Backend Product Software Engineer, Payments</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -1876,7 +1888,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Remote - Canada: Select locations</t>
+          <t>Remote - Poland</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr"/>
@@ -1890,7 +1902,7 @@
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7729764?gh_jid=7729764</t>
+          <t>https://jobs.dropbox.com/listing/7812915?gh_jid=7812915</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
@@ -1917,7 +1929,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Remote - US: Select locations</t>
+          <t>Remote - Canada: Select locations</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
@@ -1931,7 +1943,7 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7729761?gh_jid=7729761</t>
+          <t>https://jobs.dropbox.com/listing/7789389?gh_jid=7789389</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -1958,7 +1970,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Remote - US: Select locations</t>
+          <t>Remote - Canada: Select locations</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr"/>
@@ -1972,7 +1984,7 @@
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7789386?gh_jid=7789386</t>
+          <t>https://jobs.dropbox.com/listing/7729764?gh_jid=7729764</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
@@ -1989,7 +2001,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Dash Agentic AI</t>
+          <t>Senior Data Scientist, AI Products</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -1999,7 +2011,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Remote - Canada: Select locations</t>
+          <t>Remote - US: Select locations</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr"/>
@@ -2013,7 +2025,7 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7644890?gh_jid=7644890</t>
+          <t>https://jobs.dropbox.com/listing/7729761?gh_jid=7729761</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2030,7 +2042,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Dash Agentic AI</t>
+          <t>Senior Data Scientist, AI Products</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -2040,7 +2052,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Remote - US: All locations</t>
+          <t>Remote - US: Select locations</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr"/>
@@ -2054,7 +2066,7 @@
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7644886?gh_jid=7644886</t>
+          <t>https://jobs.dropbox.com/listing/7789386?gh_jid=7789386</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
@@ -2071,7 +2083,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Staff Backend Product Software Engineer, Commerce Platform</t>
+          <t>Senior Machine Learning Engineer, Dash Agentic AI</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2081,7 +2093,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Remote - Mexico</t>
+          <t>Remote - Canada: Select locations</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr"/>
@@ -2095,7 +2107,7 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7759733?gh_jid=7759733</t>
+          <t>https://jobs.dropbox.com/listing/7644890?gh_jid=7644890</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2112,7 +2124,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Staff Backend Product Software Engineer, Commerce Platform</t>
+          <t>Senior Machine Learning Engineer, Dash Agentic AI</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -2122,7 +2134,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Remote - US: Select locations</t>
+          <t>Remote - US: All locations</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr"/>
@@ -2136,7 +2148,7 @@
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7759728?gh_jid=7759728</t>
+          <t>https://jobs.dropbox.com/listing/7644886?gh_jid=7644886</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
@@ -2163,7 +2175,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Remote - Canada: Select locations</t>
+          <t>Remote - Mexico</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr"/>
@@ -2177,7 +2189,7 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7759731?gh_jid=7759731</t>
+          <t>https://jobs.dropbox.com/listing/7759733?gh_jid=7759733</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2194,7 +2206,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Staff Backend Product Software Engineer, Core</t>
+          <t>Staff Backend Product Software Engineer, Commerce Platform</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -2218,7 +2230,7 @@
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7421121?gh_jid=7421121</t>
+          <t>https://jobs.dropbox.com/listing/7759728?gh_jid=7759728</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
@@ -2235,7 +2247,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Staff Backend Product Software Engineer, Core</t>
+          <t>Staff Backend Product Software Engineer, Commerce Platform</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2259,7 +2271,7 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7421124?gh_jid=7421124</t>
+          <t>https://jobs.dropbox.com/listing/7759731?gh_jid=7759731</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -2276,7 +2288,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Staff Fullstack Product Software Engineer, Dash</t>
+          <t>Staff Backend Product Software Engineer, Core</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -2286,7 +2298,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Remote - Canada: Select locations</t>
+          <t>Remote - US: Select locations</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr"/>
@@ -2300,7 +2312,7 @@
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7551548?gh_jid=7551548</t>
+          <t>https://jobs.dropbox.com/listing/7421121?gh_jid=7421121</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
@@ -2317,7 +2329,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Staff Fullstack Product Software Engineer, Dash</t>
+          <t>Staff Backend Product Software Engineer, Core</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2327,7 +2339,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Remote - US: Select locations</t>
+          <t>Remote - Canada: Select locations</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
@@ -2341,7 +2353,7 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7551545?gh_jid=7551545</t>
+          <t>https://jobs.dropbox.com/listing/7421124?gh_jid=7421124</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -2358,7 +2370,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Staff Full Stack Software Engineer, Churn</t>
+          <t>Staff Fullstack Product Software Engineer, Dash</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -2368,7 +2380,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Remote - Poland</t>
+          <t>Remote - Canada: Select locations</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr"/>
@@ -2382,7 +2394,7 @@
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7421131?gh_jid=7421131</t>
+          <t>https://jobs.dropbox.com/listing/7551548?gh_jid=7551548</t>
         </is>
       </c>
       <c r="K44" s="4" t="inlineStr">
@@ -2399,7 +2411,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Staff Fullstack Software Engineer, Growth Monetization</t>
+          <t>Staff Fullstack Product Software Engineer, Dash</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2423,7 +2435,7 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7421150?gh_jid=7421150</t>
+          <t>https://jobs.dropbox.com/listing/7551545?gh_jid=7551545</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -2440,7 +2452,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Staff Fullstack Software Engineer, Growth Monetization</t>
+          <t>Staff Full Stack Software Engineer, Churn</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -2450,7 +2462,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Remote - Canada: Select locations</t>
+          <t>Remote - Poland</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr"/>
@@ -2464,7 +2476,7 @@
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7421153?gh_jid=7421153</t>
+          <t>https://jobs.dropbox.com/listing/7421131?gh_jid=7421131</t>
         </is>
       </c>
       <c r="K46" s="4" t="inlineStr">
@@ -2481,13 +2493,17 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>WALTER: Senior Fullstack Engineer (Ruby+React)</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr"/>
+          <t>Staff Fullstack Software Engineer, Growth Monetization</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Dropbox</t>
+        </is>
+      </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote - US: Select locations</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr"/>
@@ -2496,17 +2512,17 @@
       <c r="H47" s="2" t="inlineStr"/>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/walter-senior-fullstack-engineer-ruby-react</t>
+          <t>https://jobs.dropbox.com/listing/7421150?gh_jid=7421150</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
     </row>
@@ -2518,13 +2534,17 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>WALTER: Full-Stack Engineering Lead</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr"/>
+          <t>Staff Fullstack Software Engineer, Growth Monetization</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>Dropbox</t>
+        </is>
+      </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote - Canada: Select locations</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr"/>
@@ -2533,17 +2553,17 @@
       <c r="H48" s="4" t="inlineStr"/>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/walter-full-stack-engineering-lead</t>
+          <t>https://jobs.dropbox.com/listing/7421153?gh_jid=7421153</t>
         </is>
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
     </row>
@@ -2555,17 +2575,13 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Frontend Product Software Engineer, Design Systems</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>Dropbox</t>
-        </is>
-      </c>
+          <t>WALTER: Senior Fullstack Engineer (Ruby+React)</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr"/>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Remote - Mexico</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr"/>
@@ -2574,12 +2590,12 @@
       <c r="H49" s="2" t="inlineStr"/>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7862086?gh_jid=7862086</t>
+          <t>https://weworkremotely.com/remote-jobs/walter-senior-fullstack-engineer-ruby-react</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -2591,40 +2607,32 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Lead AI Engineer &amp; Technical Architect</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>Bold Business</t>
-        </is>
-      </c>
+          <t>WALTER: Full-Stack Engineering Lead</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr"/>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>India, Latin America, Philippines</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr"/>
       <c r="F50" s="4" t="inlineStr"/>
-      <c r="G50" s="4" t="inlineStr">
-        <is>
-          <t>architect, technical, lead, engineer</t>
-        </is>
-      </c>
+      <c r="G50" s="4" t="inlineStr"/>
       <c r="H50" s="4" t="inlineStr"/>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-lead-ai-engineer-technical-architect-bold-business-1131461</t>
+          <t>https://weworkremotely.com/remote-jobs/walter-full-stack-engineering-lead</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
@@ -2636,40 +2644,36 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer Showroom</t>
+          <t>Frontend Product Software Engineer, Design Systems</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Higharc</t>
+          <t>Dropbox</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote - Mexico</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr"/>
       <c r="F51" s="2" t="inlineStr"/>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>software, design, 3d, full-stack, support, ux, manager, api, engineer, engineering, backend, digital nomad</t>
-        </is>
-      </c>
+      <c r="G51" s="2" t="inlineStr"/>
       <c r="H51" s="2" t="inlineStr"/>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-software-engineer-showroom-higharc-1131457</t>
+          <t>https://jobs.dropbox.com/listing/7862086?gh_jid=7862086</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -2686,31 +2690,35 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Protocol Review Specialist</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr"/>
+          <t>Lead AI Engineer &amp; Technical Architect</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>Bold Business</t>
+        </is>
+      </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>India, Latin America, Philippines</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr"/>
       <c r="F52" s="4" t="inlineStr"/>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>communication, phone, english</t>
+          <t>architect, technical, lead, engineer</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr"/>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>WorkingNomads</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>https://www.workingnomads.com/job/go/1580747/</t>
+          <t>https://remoteOK.com/remote-jobs/remote-lead-ai-engineer-technical-architect-bold-business-1131461</t>
         </is>
       </c>
       <c r="K52" s="4" t="inlineStr">
@@ -2727,31 +2735,35 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Staff AI Engineer - Notebooks</t>
+          <t>Software Engineer Showroom</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Datadog</t>
+          <t>Higharc</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Portugal, Remote</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr"/>
       <c r="F53" s="2" t="inlineStr"/>
-      <c r="G53" s="2" t="inlineStr"/>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>software, design, 3d, full-stack, support, ux, manager, api, engineer, engineering, backend, digital nomad</t>
+        </is>
+      </c>
       <c r="H53" s="2" t="inlineStr"/>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>https://careers.datadoghq.com/detail/7627445/?gh_jid=7627445</t>
+          <t>https://remoteOK.com/remote-jobs/remote-software-engineer-showroom-higharc-1131457</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -2768,31 +2780,31 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Staff AI Engineer - Notebooks</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>Datadog</t>
-        </is>
-      </c>
+          <t>Protocol Review Specialist</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr"/>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>France, Remote; Germany, Remote; Ireland, Remote; Italy, Remote; Spain, Remote; Switzerland, Remote</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr"/>
       <c r="F54" s="4" t="inlineStr"/>
-      <c r="G54" s="4" t="inlineStr"/>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>communication, phone, english</t>
+        </is>
+      </c>
       <c r="H54" s="4" t="inlineStr"/>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WorkingNomads</t>
         </is>
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>https://careers.datadoghq.com/detail/7627429/?gh_jid=7627429</t>
+          <t>https://www.workingnomads.com/job/go/1580747/</t>
         </is>
       </c>
       <c r="K54" s="4" t="inlineStr">
@@ -2809,17 +2821,17 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Ads Conversion Modeling, Machine Learning Engineering Manager</t>
+          <t>Staff AI Engineer - Notebooks</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Datadog</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Portugal, Remote</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr"/>
@@ -2833,7 +2845,7 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7792848</t>
+          <t>https://careers.datadoghq.com/detail/7627445/?gh_jid=7627445</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -2850,17 +2862,17 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Data Scientist, Ads</t>
+          <t>Staff AI Engineer - Notebooks</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Datadog</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Remote - British Columbia, Canada</t>
+          <t>France, Remote; Germany, Remote; Ireland, Remote; Italy, Remote; Spain, Remote; Switzerland, Remote</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr"/>
@@ -2874,7 +2886,7 @@
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7607124</t>
+          <t>https://careers.datadoghq.com/detail/7627429/?gh_jid=7627429</t>
         </is>
       </c>
       <c r="K56" s="4" t="inlineStr">
@@ -2891,7 +2903,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Data Scientist, Ads</t>
+          <t>Ads Conversion Modeling, Machine Learning Engineering Manager</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -2915,7 +2927,7 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/6580815</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7792848</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -2932,7 +2944,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Scientist, Ads</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -2942,7 +2954,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Remote - Ontario, Canada</t>
+          <t>Remote - British Columbia, Canada</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr"/>
@@ -2956,7 +2968,7 @@
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7131934</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7607124</t>
         </is>
       </c>
       <c r="K58" s="4" t="inlineStr">
@@ -2973,7 +2985,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Scientist, Ads</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -2997,7 +3009,7 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7131932</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/6580815</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -3014,7 +3026,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Principal Data Scientist, Ads</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -3024,7 +3036,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Remote - Ontario, Canada</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr"/>
@@ -3038,7 +3050,7 @@
       </c>
       <c r="J60" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7330347</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7131934</t>
         </is>
       </c>
       <c r="K60" s="4" t="inlineStr">
@@ -3055,7 +3067,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Ads</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3065,7 +3077,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Remote - British Columbia, Canada</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr"/>
@@ -3079,7 +3091,7 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7607121</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7131932</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -3096,7 +3108,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Ads</t>
+          <t>Principal Data Scientist, Ads</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -3120,7 +3132,7 @@
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/6042236</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7330347</t>
         </is>
       </c>
       <c r="K62" s="4" t="inlineStr">
@@ -3137,7 +3149,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Consumer</t>
+          <t>Senior Data Scientist, Ads</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3147,7 +3159,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Remote - British Columbia, Canada</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr"/>
@@ -3161,7 +3173,7 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7275414</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7607121</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -3178,7 +3190,7 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Senior  Machine Learning Engineer, ML Training Platform</t>
+          <t>Senior Data Scientist, Ads</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -3202,7 +3214,7 @@
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7074776</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/6042236</t>
         </is>
       </c>
       <c r="K64" s="4" t="inlineStr">
@@ -3219,7 +3231,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Systems Engineer</t>
+          <t>Senior Data Scientist, Consumer</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3243,7 +3255,7 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7731772</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7275414</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -3260,7 +3272,7 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, GenAI Platform</t>
+          <t>Senior  Machine Learning Engineer, ML Training Platform</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -3284,7 +3296,7 @@
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7753480</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7074776</t>
         </is>
       </c>
       <c r="K66" s="4" t="inlineStr">
@@ -3301,7 +3313,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Senior Staff Machine Learning Engineer, GenAI Platform</t>
+          <t>Senior Machine Learning Systems Engineer</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -3325,7 +3337,7 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7772274</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7731772</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -3342,7 +3354,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Staff Data Scientist, Ads</t>
+          <t>Senior Software Engineer, GenAI Platform</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -3352,7 +3364,7 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Remote - British Columbia, Canada</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr"/>
@@ -3366,7 +3378,7 @@
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7721851</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7753480</t>
         </is>
       </c>
       <c r="K68" s="4" t="inlineStr">
@@ -3383,7 +3395,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Staff Data Scientist, Ads</t>
+          <t>Senior Staff Machine Learning Engineer, GenAI Platform</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -3407,7 +3419,7 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7721787</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7772274</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -3424,7 +3436,7 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Staff Data Scientist, Consumer</t>
+          <t>Staff Data Scientist, Ads</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -3434,7 +3446,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Remote - British Columbia, Canada</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr"/>
@@ -3448,7 +3460,7 @@
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/6745284</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7721851</t>
         </is>
       </c>
       <c r="K70" s="4" t="inlineStr">
@@ -3465,7 +3477,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Staff Data Scientist, Marketing</t>
+          <t>Staff Data Scientist, Ads</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -3489,7 +3501,7 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7445240</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7721787</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -3506,7 +3518,7 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, Ads Auction (Ads Marketplace Quality)</t>
+          <t>Staff Data Scientist, Consumer</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -3530,7 +3542,7 @@
       </c>
       <c r="J72" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7181821</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/6745284</t>
         </is>
       </c>
       <c r="K72" s="4" t="inlineStr">
@@ -3547,7 +3559,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, Ads Content Understanding</t>
+          <t>Staff Data Scientist, Marketing</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -3571,7 +3583,7 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7851761</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7445240</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -3588,7 +3600,7 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Systems Engineer</t>
+          <t>Staff Machine Learning Engineer, Ads Auction (Ads Marketplace Quality)</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -3612,7 +3624,7 @@
       </c>
       <c r="J74" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7731788</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7181821</t>
         </is>
       </c>
       <c r="K74" s="4" t="inlineStr">
@@ -3629,44 +3641,36 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Werkstudent:in KI Marketing (m/w/d)</t>
+          <t>Staff Machine Learning Engineer, Ads Content Understanding</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>laria.ai</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>Working student, berufseinstieg</t>
-        </is>
-      </c>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr"/>
       <c r="F75" s="2" t="inlineStr"/>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t>Remote, Online Marketing</t>
-        </is>
-      </c>
+      <c r="G75" s="2" t="inlineStr"/>
       <c r="H75" s="2" t="inlineStr"/>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/lariaai/werkstudentin-ki-marketing-berlin-9847</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7851761</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -3678,80 +3682,80 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Laravel Developer (m/w/d) - AI-First PropTech</t>
+          <t>Staff Machine Learning Systems Engineer</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Immovara GmbH</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Korntal-Münchingen</t>
-        </is>
-      </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>berufserfahren</t>
-        </is>
-      </c>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr"/>
       <c r="F76" s="4" t="inlineStr"/>
-      <c r="G76" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Software Development</t>
-        </is>
-      </c>
+      <c r="G76" s="4" t="inlineStr"/>
       <c r="H76" s="4" t="inlineStr"/>
       <c r="I76" s="4" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J76" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/immovara-gmbh/laravel-developer-ai-first-proptech-korntal-munchingen-239743</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7731788</t>
         </is>
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning (ML) Engineer - Applied</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr"/>
+          <t>Werkstudent:in KI Marketing (m/w/d)</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>laria.ai</t>
+        </is>
+      </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr"/>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Working student, berufseinstieg</t>
+        </is>
+      </c>
       <c r="F77" s="2" t="inlineStr"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>machine learning, artificial intelligence, python, cplusplus, startup</t>
+          <t>Remote, Online Marketing</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr"/>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>WorkingNomads</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>https://www.workingnomads.com/job/go/1578553/</t>
+          <t>https://www.arbeitnow.com/jobs/companies/lariaai/werkstudentin-ki-marketing-berlin-9847</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -3763,36 +3767,44 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Backend Engineer, AI Security</t>
+          <t>Laravel Developer (m/w/d) - AI-First PropTech</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Immovara GmbH</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>New York, San Francisco, Seattle, or Remote (US/Canada)</t>
-        </is>
-      </c>
-      <c r="E78" s="4" t="inlineStr"/>
+          <t>Korntal-Münchingen</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
       <c r="F78" s="4" t="inlineStr"/>
-      <c r="G78" s="4" t="inlineStr"/>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Software Development</t>
+        </is>
+      </c>
       <c r="H78" s="4" t="inlineStr"/>
       <c r="I78" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J78" s="5" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7826765</t>
+          <t>https://www.arbeitnow.com/jobs/companies/immovara-gmbh/laravel-developer-ai-first-proptech-korntal-munchingen-239743</t>
         </is>
       </c>
       <c r="K78" s="4" t="inlineStr">
@@ -3809,31 +3821,31 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Backend Engineer, Core Tech, Canada</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
+          <t>Machine Learning (ML) Engineer - Applied</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr"/>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Toronto, CAN-Remote</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr"/>
       <c r="F79" s="2" t="inlineStr"/>
-      <c r="G79" s="2" t="inlineStr"/>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>machine learning, artificial intelligence, python, cplusplus, startup</t>
+        </is>
+      </c>
       <c r="H79" s="2" t="inlineStr"/>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WorkingNomads</t>
         </is>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=6567253</t>
+          <t>https://www.workingnomads.com/job/go/1578553/</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -3850,7 +3862,7 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Backend Engineer, Core Technology</t>
+          <t>Backend Engineer, AI Security</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
@@ -3860,7 +3872,7 @@
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>US-Remote, Chicago</t>
+          <t>New York, San Francisco, Seattle, or Remote (US/Canada)</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr"/>
@@ -3874,7 +3886,7 @@
       </c>
       <c r="J80" s="5" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=6042172</t>
+          <t>https://stripe.com/jobs/search?gh_jid=7826765</t>
         </is>
       </c>
       <c r="K80" s="4" t="inlineStr">
@@ -3891,7 +3903,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Backend Engineer, Developer Experience &amp; Product Platform</t>
+          <t>Backend Engineer, Core Tech, Canada</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -3901,7 +3913,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Toronto Canada, San Francisco, Remote in US, Remote in Canada</t>
+          <t>Toronto, CAN-Remote</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr"/>
@@ -3915,7 +3927,7 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7292520</t>
+          <t>https://stripe.com/jobs/search?gh_jid=6567253</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -3932,7 +3944,7 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Commercial Counsel, Crypto</t>
+          <t>Backend Engineer, Core Technology</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -3942,7 +3954,7 @@
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>New York City, Seattle, San Francisco, Chicago, Atlanta, US-Remote</t>
+          <t>US-Remote, Chicago</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr"/>
@@ -3956,7 +3968,7 @@
       </c>
       <c r="J82" s="5" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7392188</t>
+          <t>https://stripe.com/jobs/search?gh_jid=6042172</t>
         </is>
       </c>
       <c r="K82" s="4" t="inlineStr">
@@ -3973,7 +3985,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Fullstack Engineer, Privy</t>
+          <t>Backend Engineer, Developer Experience &amp; Product Platform</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -3983,7 +3995,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">NYC-Privy, US-Remote </t>
+          <t>Toronto Canada, San Francisco, Remote in US, Remote in Canada</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr"/>
@@ -3997,7 +4009,7 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7091959</t>
+          <t>https://stripe.com/jobs/search?gh_jid=7292520</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -4014,7 +4026,7 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Stripe Assistant</t>
+          <t>Commercial Counsel, Crypto</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -4024,7 +4036,7 @@
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Seattle; San Francisco; New York City; Remote</t>
+          <t>New York City, Seattle, San Francisco, Chicago, Atlanta, US-Remote</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr"/>
@@ -4038,7 +4050,7 @@
       </c>
       <c r="J84" s="5" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7629052</t>
+          <t>https://stripe.com/jobs/search?gh_jid=7392188</t>
         </is>
       </c>
       <c r="K84" s="4" t="inlineStr">
@@ -4055,17 +4067,17 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning Manager, Feed Relevance</t>
+          <t>Fullstack Engineer, Privy</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t xml:space="preserve">NYC-Privy, US-Remote </t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr"/>
@@ -4079,7 +4091,7 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7802495</t>
+          <t>https://stripe.com/jobs/search?gh_jid=7091959</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -4096,17 +4108,17 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, GenAI Security</t>
+          <t>Machine Learning Engineer, Stripe Assistant</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Seattle; San Francisco; New York City; Remote</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr"/>
@@ -4120,7 +4132,7 @@
       </c>
       <c r="J86" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7891887</t>
+          <t>https://stripe.com/jobs/search?gh_jid=7629052</t>
         </is>
       </c>
       <c r="K86" s="4" t="inlineStr">
@@ -4137,7 +4149,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Senior Staff Machine Learning Engineer, Feed Relevance</t>
+          <t>Machine Learning Manager, Feed Relevance</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -4161,7 +4173,7 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7791994</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7802495</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -4178,7 +4190,7 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Senior Staff Machine Learning Engineer, ML Understanding</t>
+          <t>Senior Machine Learning Engineer, GenAI Security</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
@@ -4202,7 +4214,7 @@
       </c>
       <c r="J88" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7847148</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7891887</t>
         </is>
       </c>
       <c r="K88" s="4" t="inlineStr">
@@ -4219,7 +4231,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, Ads Measurement Modeling</t>
+          <t>Senior Staff Machine Learning Engineer, Feed Relevance</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -4243,7 +4255,7 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7890096</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7791994</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -4260,7 +4272,7 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, AI Serving</t>
+          <t>Senior Staff Machine Learning Engineer, ML Understanding</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
@@ -4284,7 +4296,7 @@
       </c>
       <c r="J90" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7886459</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7847148</t>
         </is>
       </c>
       <c r="K90" s="4" t="inlineStr">
@@ -4301,17 +4313,17 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (L3) - Full Stack</t>
+          <t>Staff Machine Learning Engineer, Ads Measurement Modeling</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Remote - US</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr"/>
@@ -4325,139 +4337,127 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7890096</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>Staff Machine Learning Engineer, AI Serving</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr"/>
+      <c r="F92" s="4" t="inlineStr"/>
+      <c r="G92" s="4" t="inlineStr"/>
+      <c r="H92" s="4" t="inlineStr"/>
+      <c r="I92" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J92" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7886459</t>
+        </is>
+      </c>
+      <c r="K92" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (L3) - Full Stack</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Remote - US</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr"/>
+      <c r="F93" s="2" t="inlineStr"/>
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr"/>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
           <t>https://job-boards.greenhouse.io/twilio/jobs/7738955</t>
         </is>
       </c>
-      <c r="K91" s="2" t="inlineStr">
+      <c r="K93" s="2" t="inlineStr">
         <is>
           <t>2026-05-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>AI Developer (Claude + AWS)</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>Datavent</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>Hamburg</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr"/>
-      <c r="G92" s="2" t="inlineStr">
-        <is>
-          <t>Remote, Software Development</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr"/>
-      <c r="I92" s="2" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J92" s="3" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/datavent/ai-developer-claude-aws-hamburg-22354</t>
-        </is>
-      </c>
-      <c r="K92" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="B93" s="4" t="inlineStr">
-        <is>
-          <t>Python Software Engineer, Backend &amp; APIs - Remote</t>
-        </is>
-      </c>
-      <c r="C93" s="4" t="inlineStr">
-        <is>
-          <t>dexter health</t>
-        </is>
-      </c>
-      <c r="D93" s="4" t="inlineStr">
-        <is>
-          <t>Cologne</t>
-        </is>
-      </c>
-      <c r="E93" s="4" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
-      <c r="F93" s="4" t="inlineStr"/>
-      <c r="G93" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Software Development</t>
-        </is>
-      </c>
-      <c r="H93" s="4" t="inlineStr"/>
-      <c r="I93" s="4" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J93" s="5" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/python-software-engineer-backend-apis-remote-cologne-284750</t>
-        </is>
-      </c>
-      <c r="K93" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Fullstack Developer (m/w/d) REMOTE //  UX / Python / Vue.js</t>
+          <t>AI Developer (Claude + AWS)</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Pont Connects e.K.</t>
+          <t>Datavent</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Düsseldorf</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr"/>
+          <t>Hamburg</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
       <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Remote, IT</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr"/>
@@ -4468,146 +4468,154 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
+          <t>https://www.arbeitnow.com/jobs/companies/datavent/ai-developer-claude-aws-hamburg-22354</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>Python Software Engineer, Backend &amp; APIs - Remote</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>dexter health</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>Cologne</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr"/>
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Software Development</t>
+        </is>
+      </c>
+      <c r="H95" s="4" t="inlineStr"/>
+      <c r="I95" s="4" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J95" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/python-software-engineer-backend-apis-remote-cologne-284750</t>
+        </is>
+      </c>
+      <c r="K95" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Fullstack Developer (m/w/d) REMOTE //  UX / Python / Vue.js</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Pont Connects e.K.</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Düsseldorf</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr"/>
+      <c r="F96" s="2" t="inlineStr"/>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>Remote, IT</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr"/>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
           <t>https://www.arbeitnow.com/jobs/companies/pont-connects-ek/fullstack-developer-remote-ux-python-vuejs-dusseldorf-371903</t>
         </is>
       </c>
-      <c r="K94" s="2" t="inlineStr">
+      <c r="K96" s="2" t="inlineStr">
         <is>
           <t>2026-05-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>Lemon.io</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>Americas, Europe, Asia, Oceania</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>full_time</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>Devops</t>
-        </is>
-      </c>
-      <c r="G95" s="2" t="inlineStr">
-        <is>
-          <t>.Net, android, AWS, azure, C, C#, C++, data science, golang, ios, java, javascript, kubernetes, node.js, php, python, react, ruby/rails, shopify, sql, video, blockchain, AI/ML, automation, react native, rust, unity, spring, data analysis, laravel, solidity, flask, Typescript , terraform, angular , GCP, data engineering, Symfony, startup, marketplace, next.js</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr"/>
-      <c r="I95" s="2" t="inlineStr">
-        <is>
-          <t>Remotive</t>
-        </is>
-      </c>
-      <c r="J95" s="3" t="inlineStr">
-        <is>
-          <t>https://remotive.com/remote-jobs/devops/senior-devops-engineer-2090002</t>
-        </is>
-      </c>
-      <c r="K95" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="B96" s="4" t="inlineStr">
-        <is>
-          <t>M&amp;A Research Analyst</t>
-        </is>
-      </c>
-      <c r="C96" s="4" t="inlineStr">
-        <is>
-          <t>EquiMatch GmbH</t>
-        </is>
-      </c>
-      <c r="D96" s="4" t="inlineStr">
-        <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E96" s="4" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
-      <c r="F96" s="4" t="inlineStr"/>
-      <c r="G96" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Mergers &amp; Acquisitions</t>
-        </is>
-      </c>
-      <c r="H96" s="4" t="inlineStr"/>
-      <c r="I96" s="4" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J96" s="5" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/equimatch-gmbh/ma-research-analyst-berlin-498635</t>
-        </is>
-      </c>
-      <c r="K96" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Xsolla: Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr"/>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Lemon.io</t>
+        </is>
+      </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr"/>
-      <c r="F97" s="2" t="inlineStr"/>
-      <c r="G97" s="2" t="inlineStr"/>
+          <t>Americas, Europe, Asia, Oceania</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>full_time</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>Devops</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>.Net, android, AWS, azure, C, C#, C++, data science, golang, ios, java, javascript, kubernetes, node.js, php, python, react, ruby/rails, shopify, sql, video, blockchain, AI/ML, automation, react native, rust, unity, spring, data analysis, laravel, solidity, flask, Typescript , terraform, angular , GCP, data engineering, Symfony, startup, marketplace, next.js</t>
+        </is>
+      </c>
       <c r="H97" s="2" t="inlineStr"/>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Remotive</t>
         </is>
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/xsolla-full-stack-developer</t>
+          <t>https://remotive.com/remote-jobs/devops/senior-devops-engineer-2090002</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -4619,32 +4627,44 @@
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Dropbox: Staff Fullstack Product Software Engineer, Dash</t>
-        </is>
-      </c>
-      <c r="C98" s="4" t="inlineStr"/>
+          <t>M&amp;A Research Analyst</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>EquiMatch GmbH</t>
+        </is>
+      </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E98" s="4" t="inlineStr"/>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
       <c r="F98" s="4" t="inlineStr"/>
-      <c r="G98" s="4" t="inlineStr"/>
+      <c r="G98" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Mergers &amp; Acquisitions</t>
+        </is>
+      </c>
       <c r="H98" s="4" t="inlineStr"/>
       <c r="I98" s="4" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J98" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/dropbox-staff-fullstack-product-software-engineer-dash</t>
+          <t>https://www.arbeitnow.com/jobs/companies/equimatch-gmbh/ma-research-analyst-berlin-498635</t>
         </is>
       </c>
       <c r="K98" s="4" t="inlineStr">
@@ -4661,17 +4681,13 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, Ranking and Personalization</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>Reddit</t>
-        </is>
-      </c>
+          <t>Xsolla: Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr"/>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr"/>
@@ -4680,115 +4696,95 @@
       <c r="H99" s="2" t="inlineStr"/>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
+          <t>https://weworkremotely.com/remote-jobs/xsolla-full-stack-developer</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>Dropbox: Staff Fullstack Product Software Engineer, Dash</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr"/>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr"/>
+      <c r="F100" s="4" t="inlineStr"/>
+      <c r="G100" s="4" t="inlineStr"/>
+      <c r="H100" s="4" t="inlineStr"/>
+      <c r="I100" s="4" t="inlineStr">
+        <is>
+          <t>WeWorkRemotely</t>
+        </is>
+      </c>
+      <c r="J100" s="5" t="inlineStr">
+        <is>
+          <t>https://weworkremotely.com/remote-jobs/dropbox-staff-fullstack-product-software-engineer-dash</t>
+        </is>
+      </c>
+      <c r="K100" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Staff Machine Learning Engineer, Ranking and Personalization</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr"/>
+      <c r="F101" s="2" t="inlineStr"/>
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr"/>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
           <t>https://job-boards.greenhouse.io/reddit/jobs/7848689</t>
         </is>
       </c>
-      <c r="K99" s="2" t="inlineStr">
+      <c r="K101" s="2" t="inlineStr">
         <is>
           <t>2026-05-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>Senior Rust Consultant / Engineer (m/w/d)</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>Hackstack GmbH</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>berufserfahren</t>
-        </is>
-      </c>
-      <c r="F100" s="2" t="inlineStr"/>
-      <c r="G100" s="2" t="inlineStr">
-        <is>
-          <t>Remote, Consulting, Engineering</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="inlineStr"/>
-      <c r="I100" s="2" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J100" s="3" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/hackstack-gmbh/senior-rust-consultant-engineer-munich-451602</t>
-        </is>
-      </c>
-      <c r="K100" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="B101" s="4" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer - Remote</t>
-        </is>
-      </c>
-      <c r="C101" s="4" t="inlineStr">
-        <is>
-          <t>dexter health</t>
-        </is>
-      </c>
-      <c r="D101" s="4" t="inlineStr">
-        <is>
-          <t>Cologne</t>
-        </is>
-      </c>
-      <c r="E101" s="4" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
-      <c r="F101" s="4" t="inlineStr"/>
-      <c r="G101" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Development</t>
-        </is>
-      </c>
-      <c r="H101" s="4" t="inlineStr"/>
-      <c r="I101" s="4" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J101" s="5" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/applied-ai-engineer-remote-cologne-2870</t>
-        </is>
-      </c>
-      <c r="K101" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4800,28 +4796,28 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Python Backend Engineer - Remote</t>
+          <t>Senior Rust Consultant / Engineer (m/w/d)</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>dexter health</t>
+          <t>Hackstack GmbH</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Cologne</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>professional / experienced</t>
+          <t>berufserfahren</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr"/>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Remote, Development</t>
+          <t>Remote, Consulting, Engineering</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr"/>
@@ -4832,7 +4828,7 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/python-backend-engineer-remote-cologne-34228</t>
+          <t>https://www.arbeitnow.com/jobs/companies/hackstack-gmbh/senior-rust-consultant-engineer-munich-451602</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -4849,7 +4845,7 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>AI Engineer (LLM Products) - Remote</t>
+          <t>Applied AI Engineer - Remote</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
@@ -4881,7 +4877,7 @@
       </c>
       <c r="J103" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/ai-engineer-llm-products-remote-cologne-236027</t>
+          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/applied-ai-engineer-remote-cologne-2870</t>
         </is>
       </c>
       <c r="K103" s="4" t="inlineStr">
@@ -4898,7 +4894,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Backend Python Engineer (APIs, Databases &amp; Cloud) - Remote</t>
+          <t>Python Backend Engineer - Remote</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -4930,7 +4926,7 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/backend-python-engineer-apis-databases-cloud-remote-cologne-274767</t>
+          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/python-backend-engineer-remote-cologne-34228</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -4942,32 +4938,44 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Toptal: QA Automation Engineer</t>
-        </is>
-      </c>
-      <c r="C105" s="4" t="inlineStr"/>
+          <t>AI Engineer (LLM Products) - Remote</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>dexter health</t>
+        </is>
+      </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E105" s="4" t="inlineStr"/>
+          <t>Cologne</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
       <c r="F105" s="4" t="inlineStr"/>
-      <c r="G105" s="4" t="inlineStr"/>
+      <c r="G105" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Development</t>
+        </is>
+      </c>
       <c r="H105" s="4" t="inlineStr"/>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J105" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/toptal-qa-automation-engineer-1</t>
+          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/ai-engineer-llm-products-remote-cologne-236027</t>
         </is>
       </c>
       <c r="K105" s="4" t="inlineStr">
@@ -4979,32 +4987,44 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Opensea: Staff Product Designer</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr"/>
+          <t>Backend Python Engineer (APIs, Databases &amp; Cloud) - Remote</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>dexter health</t>
+        </is>
+      </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr"/>
+          <t>Cologne</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
       <c r="F106" s="2" t="inlineStr"/>
-      <c r="G106" s="2" t="inlineStr"/>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>Remote, Development</t>
+        </is>
+      </c>
       <c r="H106" s="2" t="inlineStr"/>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/opensea-staff-product-designer</t>
+          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/backend-python-engineer-apis-databases-cloud-remote-cologne-274767</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -5021,7 +5041,7 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Mutt Data: Devops</t>
+          <t>Toptal: QA Automation Engineer</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr"/>
@@ -5041,7 +5061,7 @@
       </c>
       <c r="J107" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/mutt-data-devops</t>
+          <t>https://weworkremotely.com/remote-jobs/toptal-qa-automation-engineer-1</t>
         </is>
       </c>
       <c r="K107" s="4" t="inlineStr">
@@ -5058,7 +5078,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Holywater: Full-Stack Developer</t>
+          <t>Opensea: Staff Product Designer</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr"/>
@@ -5078,7 +5098,7 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/holywater-full-stack-developer</t>
+          <t>https://weworkremotely.com/remote-jobs/opensea-staff-product-designer</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -5095,7 +5115,7 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Qventus: DevOps Engineer</t>
+          <t>Mutt Data: Devops</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr"/>
@@ -5115,7 +5135,7 @@
       </c>
       <c r="J109" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/qventus-devops-engineer</t>
+          <t>https://weworkremotely.com/remote-jobs/mutt-data-devops</t>
         </is>
       </c>
       <c r="K109" s="4" t="inlineStr">
@@ -5132,7 +5152,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Visualis: Senior Full Stack Developer</t>
+          <t>Holywater: Full-Stack Developer</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr"/>
@@ -5152,7 +5172,7 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/visualis-senior-full-stack-developer</t>
+          <t>https://weworkremotely.com/remote-jobs/holywater-full-stack-developer</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -5169,17 +5189,13 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="C111" s="4" t="inlineStr">
-        <is>
-          <t>GitLab</t>
-        </is>
-      </c>
+          <t>Qventus: DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr"/>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Remote, Bangalore</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr"/>
@@ -5188,12 +5204,12 @@
       <c r="H111" s="4" t="inlineStr"/>
       <c r="I111" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J111" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8517564002</t>
+          <t>https://weworkremotely.com/remote-jobs/qventus-devops-engineer</t>
         </is>
       </c>
       <c r="K111" s="4" t="inlineStr">
@@ -5210,17 +5226,13 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Backend Engineer, Analytics Instrumentation (Golang)</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>GitLab</t>
-        </is>
-      </c>
+          <t>Visualis: Senior Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr"/>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr"/>
@@ -5229,12 +5241,12 @@
       <c r="H112" s="2" t="inlineStr"/>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481922002</t>
+          <t>https://weworkremotely.com/remote-jobs/visualis-senior-full-stack-developer</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -5251,7 +5263,7 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Backend Engineer, Analytics Instrumentation (Golang)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
@@ -5261,7 +5273,7 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, Bangalore</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr"/>
@@ -5275,7 +5287,7 @@
       </c>
       <c r="J113" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481929002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8517564002</t>
         </is>
       </c>
       <c r="K113" s="4" t="inlineStr">
@@ -5292,7 +5304,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Backend Engineer, Knowledge Graph (Rust)</t>
+          <t>Backend Engineer, Analytics Instrumentation (Golang)</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -5302,7 +5314,7 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, US</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr"/>
@@ -5316,7 +5328,7 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8437754002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481922002</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -5333,7 +5345,7 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Backend Engineer, Knowledge Graph (Rust)</t>
+          <t>Backend Engineer, Analytics Instrumentation (Golang)</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
@@ -5357,7 +5369,7 @@
       </c>
       <c r="J115" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481958002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481929002</t>
         </is>
       </c>
       <c r="K115" s="4" t="inlineStr">
@@ -5374,7 +5386,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Intermediate Backend Engineer (C), Tenant Scale: Git</t>
+          <t>Backend Engineer, Knowledge Graph (Rust)</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -5384,7 +5396,7 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, Canada; Remote, US</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr"/>
@@ -5398,7 +5410,7 @@
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8497793002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8437754002</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -5415,7 +5427,7 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Intermediate Backend Engineer, Gitlab Delivery: Upgrades</t>
+          <t>Backend Engineer, Knowledge Graph (Rust)</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
@@ -5439,7 +5451,7 @@
       </c>
       <c r="J117" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8463951002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481958002</t>
         </is>
       </c>
       <c r="K117" s="4" t="inlineStr">
@@ -5456,7 +5468,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Intermediate Backend Engineer, SRM: Security Platform Management</t>
+          <t>Intermediate Backend Engineer (C), Tenant Scale: Git</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -5466,7 +5478,7 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr"/>
@@ -5480,7 +5492,7 @@
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8443325002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8497793002</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -5497,7 +5509,7 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>Intermediate Backend Engineer, SSCS: AI Governance</t>
+          <t>Intermediate Backend Engineer, Gitlab Delivery: Upgrades</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
@@ -5521,7 +5533,7 @@
       </c>
       <c r="J119" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480551002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8463951002</t>
         </is>
       </c>
       <c r="K119" s="4" t="inlineStr">
@@ -5538,7 +5550,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Intermediate Backend Engineer,  SSCS: Supply Chain</t>
+          <t>Intermediate Backend Engineer, SRM: Security Platform Management</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -5548,7 +5560,7 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr"/>
@@ -5562,7 +5574,7 @@
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480565002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8443325002</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -5579,7 +5591,7 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Intermediate Backend Engineer, SSCS: AI Governance</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
@@ -5589,7 +5601,7 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Remote, EMEA</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr"/>
@@ -5603,7 +5615,7 @@
       </c>
       <c r="J121" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8464072002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480551002</t>
         </is>
       </c>
       <c r="K121" s="4" t="inlineStr">
@@ -5620,7 +5632,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (AI), Pipeline Execution</t>
+          <t>Intermediate Backend Engineer,  SSCS: Supply Chain</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -5630,7 +5642,7 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US-Southeast</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr"/>
@@ -5644,7 +5656,7 @@
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8514945002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480565002</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -5661,7 +5673,7 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Analytics Instrumentation (Golang)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
@@ -5671,7 +5683,7 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, US</t>
+          <t>Remote, EMEA</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr"/>
@@ -5685,7 +5697,7 @@
       </c>
       <c r="J123" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8451512002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8464072002</t>
         </is>
       </c>
       <c r="K123" s="4" t="inlineStr">
@@ -5702,7 +5714,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (C), Tenant Scale: Git</t>
+          <t>Senior Backend Engineer (AI), Pipeline Execution</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -5712,7 +5724,7 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US-Southeast</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr"/>
@@ -5726,7 +5738,7 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8497791002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8514945002</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -5743,7 +5755,7 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Gitlab Delivery: Runway (Platform Engineering)</t>
+          <t>Senior Backend Engineer, Analytics Instrumentation (Golang)</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
@@ -5753,7 +5765,7 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Remote, Australia; Remote, India; Remote, Ireland; Remote, Japan; Remote, Netherlands; Remote, Singapore; Remote, United Kingdom</t>
+          <t>Remote, Canada; Remote, US</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr"/>
@@ -5767,7 +5779,7 @@
       </c>
       <c r="J125" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8324132002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8451512002</t>
         </is>
       </c>
       <c r="K125" s="4" t="inlineStr">
@@ -5784,7 +5796,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Gitlab Delivery: Upgrades</t>
+          <t>Senior Backend Engineer (C), Tenant Scale: Git</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -5808,7 +5820,7 @@
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8463933002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8497791002</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -5825,7 +5837,7 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer(Go), Continuous Delivery</t>
+          <t>Senior Backend Engineer, Gitlab Delivery: Runway (Platform Engineering)</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
@@ -5835,7 +5847,7 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, Australia; Remote, India; Remote, Ireland; Remote, Japan; Remote, Netherlands; Remote, Singapore; Remote, United Kingdom</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr"/>
@@ -5849,7 +5861,7 @@
       </c>
       <c r="J127" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8488966002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8324132002</t>
         </is>
       </c>
       <c r="K127" s="4" t="inlineStr">
@@ -5866,7 +5878,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer(Golang),Software Supply Chain Security: Auth Infrastructure</t>
+          <t>Senior Backend Engineer, Gitlab Delivery: Upgrades</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -5876,7 +5888,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Remote, Americas; Remote, APAC; Remote, Canada</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr"/>
@@ -5890,7 +5902,7 @@
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8157520002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8463933002</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -5907,7 +5919,7 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (RoR), AST: Secret Detection</t>
+          <t>Senior Backend Engineer(Go), Continuous Delivery</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
@@ -5917,7 +5929,7 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr"/>
@@ -5931,7 +5943,7 @@
       </c>
       <c r="J129" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8432262002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8488966002</t>
         </is>
       </c>
       <c r="K129" s="4" t="inlineStr">
@@ -5948,7 +5960,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (RoR/Go), SSCS: Pipeline Security</t>
+          <t>Senior Backend Engineer(Golang),Software Supply Chain Security: Auth Infrastructure</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -5958,7 +5970,7 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
+          <t>Remote, Americas; Remote, APAC; Remote, Canada</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr"/>
@@ -5972,7 +5984,7 @@
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8432221002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8157520002</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
@@ -5989,7 +6001,7 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (RoR), SSCS: Authorization</t>
+          <t>Senior Backend Engineer (RoR), AST: Secret Detection</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
@@ -5999,7 +6011,7 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
+          <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr"/>
@@ -6013,7 +6025,7 @@
       </c>
       <c r="J131" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8457315002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8432262002</t>
         </is>
       </c>
       <c r="K131" s="4" t="inlineStr">
@@ -6030,7 +6042,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby or Golang), Tenant Scale; Cells Infrastructure</t>
+          <t>Senior Backend Engineer (RoR/Go), SSCS: Pipeline Security</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -6040,7 +6052,7 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Remote, APAC; Remote, Canada; Remote, EMEA; Remote, US</t>
+          <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr"/>
@@ -6054,7 +6066,7 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8437148002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8432221002</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -6071,7 +6083,7 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, SSCS: AI Governance</t>
+          <t>Senior Backend Engineer (RoR), SSCS: Authorization</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
@@ -6081,7 +6093,7 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr"/>
@@ -6095,7 +6107,7 @@
       </c>
       <c r="J133" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480544002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8457315002</t>
         </is>
       </c>
       <c r="K133" s="4" t="inlineStr">
@@ -6112,7 +6124,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer,  SSCS: Supply Chain</t>
+          <t>Senior Backend Engineer (Ruby or Golang), Tenant Scale; Cells Infrastructure</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -6122,7 +6134,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, APAC; Remote, Canada; Remote, EMEA; Remote, US</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr"/>
@@ -6136,7 +6148,7 @@
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480580002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8437148002</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
@@ -6153,7 +6165,7 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Senior Fullstack Engineer (TypeScript), AI Engineering: Editor Extensions</t>
+          <t>Senior Backend Engineer, SSCS: AI Governance</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
@@ -6163,7 +6175,7 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Remote, APAC; Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US-Southeast</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr"/>
@@ -6177,7 +6189,7 @@
       </c>
       <c r="J135" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8452278002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480544002</t>
         </is>
       </c>
       <c r="K135" s="4" t="inlineStr">
@@ -6194,7 +6206,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer, Analytics Instrumentation (Golang)</t>
+          <t>Senior Backend Engineer,  SSCS: Supply Chain</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -6218,7 +6230,7 @@
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8508027002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480580002</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -6235,7 +6247,7 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer, AST: Composition Analysis</t>
+          <t>Senior Fullstack Engineer (TypeScript), AI Engineering: Editor Extensions</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
@@ -6245,7 +6257,7 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>Remote, Australia; Remote, Canada; Remote, India; Remote, Ireland; Remote, Israel; Remote, Japan; Remote, Netherlands; Remote, New Zealand; Remote, United Kingdom; Remote, US</t>
+          <t>Remote, APAC; Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US-Southeast</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr"/>
@@ -6259,7 +6271,7 @@
       </c>
       <c r="J137" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8478364002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8452278002</t>
         </is>
       </c>
       <c r="K137" s="4" t="inlineStr">
@@ -6276,7 +6288,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer, Developer Experience</t>
+          <t>Staff Backend Engineer, Analytics Instrumentation (Golang)</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -6286,7 +6298,7 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, United Kingdom; Remote, US</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr"/>
@@ -6300,7 +6312,7 @@
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8490477002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8508027002</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
@@ -6317,7 +6329,7 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer, Gitlab Delivery: Upgrades</t>
+          <t>Staff Backend Engineer, AST: Composition Analysis</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
@@ -6327,7 +6339,7 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, Australia; Remote, Canada; Remote, India; Remote, Ireland; Remote, Israel; Remote, Japan; Remote, Netherlands; Remote, New Zealand; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr"/>
@@ -6341,7 +6353,7 @@
       </c>
       <c r="J139" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8463922002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8478364002</t>
         </is>
       </c>
       <c r="K139" s="4" t="inlineStr">
@@ -6358,7 +6370,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer (Go), Continuous Delivery</t>
+          <t>Staff Backend Engineer, Developer Experience</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -6368,7 +6380,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, Canada; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr"/>
@@ -6382,7 +6394,7 @@
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8488961002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8490477002</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -6399,7 +6411,7 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer (Go), Software Supply Chain Security: Secrets Management</t>
+          <t>Staff Backend Engineer, Gitlab Delivery: Upgrades</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
@@ -6409,7 +6421,7 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr"/>
@@ -6423,7 +6435,7 @@
       </c>
       <c r="J141" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8432235002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8463922002</t>
         </is>
       </c>
       <c r="K141" s="4" t="inlineStr">
@@ -6440,7 +6452,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer, Knowledge Graph (Rust)</t>
+          <t>Staff Backend Engineer (Go), Continuous Delivery</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -6464,7 +6476,7 @@
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481945002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8488961002</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -6481,7 +6493,7 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer,  Software Supply Chain Security</t>
+          <t>Staff Backend Engineer (Go), Software Supply Chain Security: Secrets Management</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
@@ -6491,7 +6503,7 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr"/>
@@ -6505,7 +6517,7 @@
       </c>
       <c r="J143" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480559002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8432235002</t>
         </is>
       </c>
       <c r="K143" s="4" t="inlineStr">
@@ -6522,7 +6534,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer, SSCS: AI Governance</t>
+          <t>Staff Backend Engineer, Knowledge Graph (Rust)</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -6546,7 +6558,7 @@
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480531002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481945002</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -6563,7 +6575,7 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Staff Backend (Python) Engineer, AI Engineering:Duo Chat</t>
+          <t>Staff Backend Engineer,  Software Supply Chain Security</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
@@ -6573,7 +6585,7 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>Remote, Americas; Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr"/>
@@ -6587,7 +6599,7 @@
       </c>
       <c r="J145" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8450446002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480559002</t>
         </is>
       </c>
       <c r="K145" s="4" t="inlineStr">
@@ -6604,17 +6616,17 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Senior Full Stack Product Software Engineer</t>
+          <t>Staff Backend Engineer, SSCS: AI Governance</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Dropbox</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Remote - Poland</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr"/>
@@ -6628,126 +6640,94 @@
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480531002</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t>Staff Backend (Python) Engineer, AI Engineering:Duo Chat</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="inlineStr">
+        <is>
+          <t>GitLab</t>
+        </is>
+      </c>
+      <c r="D147" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Americas; Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom</t>
+        </is>
+      </c>
+      <c r="E147" s="4" t="inlineStr"/>
+      <c r="F147" s="4" t="inlineStr"/>
+      <c r="G147" s="4" t="inlineStr"/>
+      <c r="H147" s="4" t="inlineStr"/>
+      <c r="I147" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J147" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8450446002</t>
+        </is>
+      </c>
+      <c r="K147" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Product Software Engineer</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Dropbox</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Remote - Poland</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr"/>
+      <c r="F148" s="2" t="inlineStr"/>
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr"/>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J148" s="3" t="inlineStr">
+        <is>
           <t>https://jobs.dropbox.com/listing/6449719?gh_jid=6449719</t>
         </is>
       </c>
-      <c r="K146" s="2" t="inlineStr">
+      <c r="K148" s="2" t="inlineStr">
         <is>
           <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>Dry Ground AI</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
-        <is>
-          <t>Brazil, Colombia, Philippines</t>
-        </is>
-      </c>
-      <c r="E147" s="2" t="inlineStr">
-        <is>
-          <t>full_time</t>
-        </is>
-      </c>
-      <c r="F147" s="2" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence</t>
-        </is>
-      </c>
-      <c r="G147" s="2" t="inlineStr">
-        <is>
-          <t>api, cloud, fullstack, python, AI/ML, automation, research, CI/CD, TensorFlow, spark, NLP, CMS, Pytorch, REST</t>
-        </is>
-      </c>
-      <c r="H147" s="2" t="inlineStr">
-        <is>
-          <t>$40- $60k</t>
-        </is>
-      </c>
-      <c r="I147" s="2" t="inlineStr">
-        <is>
-          <t>Remotive</t>
-        </is>
-      </c>
-      <c r="J147" s="3" t="inlineStr">
-        <is>
-          <t>https://remotive.com/remote-jobs/artificial-intelligence/ai-engineer-2089958</t>
-        </is>
-      </c>
-      <c r="K147" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B148" s="4" t="inlineStr">
-        <is>
-          <t>Senior Independent AI Engineer / Architect</t>
-        </is>
-      </c>
-      <c r="C148" s="4" t="inlineStr">
-        <is>
-          <t>A.Team</t>
-        </is>
-      </c>
-      <c r="D148" s="4" t="inlineStr">
-        <is>
-          <t>Americas, Europe, Israel</t>
-        </is>
-      </c>
-      <c r="E148" s="4" t="inlineStr">
-        <is>
-          <t>contract</t>
-        </is>
-      </c>
-      <c r="F148" s="4" t="inlineStr">
-        <is>
-          <t>Software Development</t>
-        </is>
-      </c>
-      <c r="G148" s="4" t="inlineStr">
-        <is>
-          <t>go, UI/UX, wordpress, chat, apple, testing, catalyst</t>
-        </is>
-      </c>
-      <c r="H148" s="4" t="inlineStr">
-        <is>
-          <t>$120 - $170 /hour</t>
-        </is>
-      </c>
-      <c r="I148" s="4" t="inlineStr">
-        <is>
-          <t>Remotive</t>
-        </is>
-      </c>
-      <c r="J148" s="5" t="inlineStr">
-        <is>
-          <t>https://remotive.com/remote-jobs/software-development/senior-independent-ai-engineer-architect-1919266</t>
-        </is>
-      </c>
-      <c r="K148" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6759,37 +6739,37 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Senior Independent Software Developer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>A.Team</t>
+          <t>Dry Ground AI</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>Americas, Europe, Israel</t>
+          <t>Brazil, Colombia, Philippines</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>contract</t>
+          <t>full_time</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>Software Development</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>go, wordpress, chat, apple, testing, catalyst</t>
+          <t>api, cloud, fullstack, python, AI/ML, automation, research, CI/CD, TensorFlow, spark, NLP, CMS, Pytorch, REST</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>$90 - $150 /hour</t>
+          <t>$40- $60k</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr">
@@ -6799,7 +6779,7 @@
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
-          <t>https://remotive.com/remote-jobs/software-development/senior-independent-software-developer-1919265</t>
+          <t>https://remotive.com/remote-jobs/artificial-intelligence/ai-engineer-2089958</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
@@ -6816,17 +6796,17 @@
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>Senior Full-stack React Developer</t>
+          <t>Senior Independent AI Engineer / Architect</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>Lemon.io</t>
+          <t>A.Team</t>
         </is>
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>Americas, Europe, Asia, Oceania</t>
+          <t>Americas, Europe, Israel</t>
         </is>
       </c>
       <c r="E150" s="4" t="inlineStr">
@@ -6841,10 +6821,14 @@
       </c>
       <c r="G150" s="4" t="inlineStr">
         <is>
-          <t>.Net, android, AWS, azure, backend, C, C#, C++, data science, fullstack, golang, ios, java, javascript, node.js, php, python, react, react js, ruby/rails, shopify, video, blockchain, AI/ML, react native, rust, unity, spring, data analysis, laravel, solidity, flask, Typescript , angular , GCP, data engineering, Symfony, startup, marketplace, next.js</t>
-        </is>
-      </c>
-      <c r="H150" s="4" t="inlineStr"/>
+          <t>go, UI/UX, wordpress, chat, apple, testing, catalyst</t>
+        </is>
+      </c>
+      <c r="H150" s="4" t="inlineStr">
+        <is>
+          <t>$120 - $170 /hour</t>
+        </is>
+      </c>
       <c r="I150" s="4" t="inlineStr">
         <is>
           <t>Remotive</t>
@@ -6852,7 +6836,7 @@
       </c>
       <c r="J150" s="5" t="inlineStr">
         <is>
-          <t>https://remotive.com/remote-jobs/software-development/senior-full-stack-react-developer-2088711</t>
+          <t>https://remotive.com/remote-jobs/software-development/senior-independent-ai-engineer-architect-1919266</t>
         </is>
       </c>
       <c r="K150" s="4" t="inlineStr">
@@ -6869,22 +6853,22 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>Tech Lead Full-Stack Rails Engineer</t>
+          <t>Senior Independent Software Developer</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Mitre Media</t>
+          <t>A.Team</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>USA, Canada, USA timezones</t>
+          <t>Americas, Europe, Israel</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>full_time</t>
+          <t>contract</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
@@ -6894,12 +6878,12 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>api, CSS, docker, elasticsearch, fullstack, html, javascript, kubernetes, postgresql, react, ror, ruby/rails, AI/ML, CAD, advertising, Redis, ES6, web applications, MySQL, NLP, fintech, Micro services, github, system architecture</t>
+          <t>go, wordpress, chat, apple, testing, catalyst</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>$170k - $200k</t>
+          <t>$90 - $150 /hour</t>
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr">
@@ -6909,7 +6893,7 @@
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
-          <t>https://remotive.com/remote-jobs/software-development/tech-lead-full-stack-rails-engineer-2069746</t>
+          <t>https://remotive.com/remote-jobs/software-development/senior-independent-software-developer-1919265</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
@@ -6926,17 +6910,17 @@
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>Senior Frontend Developer</t>
+          <t>Senior Full-stack React Developer</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>Sanctuary Computer</t>
+          <t>Lemon.io</t>
         </is>
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>LATAM, Asia</t>
+          <t>Americas, Europe, Asia, Oceania</t>
         </is>
       </c>
       <c r="E152" s="4" t="inlineStr">
@@ -6951,14 +6935,10 @@
       </c>
       <c r="G152" s="4" t="inlineStr">
         <is>
-          <t>api, backend, CSS, ecommerce, frontend, fullstack, graphql, postgresql, redux, security, seo, shopify, open source, paas, product management, documentation, mentoring, Typescript , Redis, web applications, cypress, data visualization, firebase, IoT, engineering management, runtime, responsive, prismic, testing, next.js, CMS, jest, REST, web sockets, performance optimization</t>
-        </is>
-      </c>
-      <c r="H152" s="4" t="inlineStr">
-        <is>
-          <t>$80k - $120k</t>
-        </is>
-      </c>
+          <t>.Net, android, AWS, azure, backend, C, C#, C++, data science, fullstack, golang, ios, java, javascript, node.js, php, python, react, react js, ruby/rails, shopify, video, blockchain, AI/ML, react native, rust, unity, spring, data analysis, laravel, solidity, flask, Typescript , angular , GCP, data engineering, Symfony, startup, marketplace, next.js</t>
+        </is>
+      </c>
+      <c r="H152" s="4" t="inlineStr"/>
       <c r="I152" s="4" t="inlineStr">
         <is>
           <t>Remotive</t>
@@ -6966,7 +6946,7 @@
       </c>
       <c r="J152" s="5" t="inlineStr">
         <is>
-          <t>https://remotive.com/remote-jobs/software-development/senior-frontend-developer-2088707</t>
+          <t>https://remotive.com/remote-jobs/software-development/senior-full-stack-react-developer-2088711</t>
         </is>
       </c>
       <c r="K152" s="4" t="inlineStr">
@@ -6983,17 +6963,17 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>Fullstack Developer (US - ET)</t>
+          <t>Tech Lead Full-Stack Rails Engineer</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>Chooose</t>
+          <t>Mitre Media</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>USA, Canada, USA timezones</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
@@ -7008,10 +6988,14 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>api, azure, fullstack, python, react, saas, AI/ML, project management, documentation, Typescript , computer science, diversity, insurance</t>
-        </is>
-      </c>
-      <c r="H153" s="2" t="inlineStr"/>
+          <t>api, CSS, docker, elasticsearch, fullstack, html, javascript, kubernetes, postgresql, react, ror, ruby/rails, AI/ML, CAD, advertising, Redis, ES6, web applications, MySQL, NLP, fintech, Micro services, github, system architecture</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>$170k - $200k</t>
+        </is>
+      </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
           <t>Remotive</t>
@@ -7019,7 +7003,7 @@
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
-          <t>https://remotive.com/remote-jobs/software-development/fullstack-developer-us-et-2088706</t>
+          <t>https://remotive.com/remote-jobs/software-development/tech-lead-full-stack-rails-engineer-2069746</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -7036,31 +7020,47 @@
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning Manager, Notifications Relevance</t>
+          <t>Senior Frontend Developer</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Sanctuary Computer</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
-        </is>
-      </c>
-      <c r="E154" s="4" t="inlineStr"/>
-      <c r="F154" s="4" t="inlineStr"/>
-      <c r="G154" s="4" t="inlineStr"/>
-      <c r="H154" s="4" t="inlineStr"/>
+          <t>LATAM, Asia</t>
+        </is>
+      </c>
+      <c r="E154" s="4" t="inlineStr">
+        <is>
+          <t>contract</t>
+        </is>
+      </c>
+      <c r="F154" s="4" t="inlineStr">
+        <is>
+          <t>Software Development</t>
+        </is>
+      </c>
+      <c r="G154" s="4" t="inlineStr">
+        <is>
+          <t>api, backend, CSS, ecommerce, frontend, fullstack, graphql, postgresql, redux, security, seo, shopify, open source, paas, product management, documentation, mentoring, Typescript , Redis, web applications, cypress, data visualization, firebase, IoT, engineering management, runtime, responsive, prismic, testing, next.js, CMS, jest, REST, web sockets, performance optimization</t>
+        </is>
+      </c>
+      <c r="H154" s="4" t="inlineStr">
+        <is>
+          <t>$80k - $120k</t>
+        </is>
+      </c>
       <c r="I154" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>Remotive</t>
         </is>
       </c>
       <c r="J154" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7846885</t>
+          <t>https://remotive.com/remote-jobs/software-development/senior-frontend-developer-2088707</t>
         </is>
       </c>
       <c r="K154" s="4" t="inlineStr">
@@ -7077,31 +7077,43 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Senior Staff ML Engineer, Search &amp; Recommendation</t>
+          <t>Fullstack Developer (US - ET)</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Chooose</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
-        </is>
-      </c>
-      <c r="E155" s="2" t="inlineStr"/>
-      <c r="F155" s="2" t="inlineStr"/>
-      <c r="G155" s="2" t="inlineStr"/>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>full_time</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>Software Development</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>api, azure, fullstack, python, react, saas, AI/ML, project management, documentation, Typescript , computer science, diversity, insurance</t>
+        </is>
+      </c>
       <c r="H155" s="2" t="inlineStr"/>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>Remotive</t>
         </is>
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7833622</t>
+          <t>https://remotive.com/remote-jobs/software-development/fullstack-developer-us-et-2088706</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -7118,17 +7130,17 @@
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Machine Learning Manager, Notifications Relevance</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>Remote - US</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E156" s="4" t="inlineStr"/>
@@ -7142,7 +7154,7 @@
       </c>
       <c r="J156" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7059734</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7846885</t>
         </is>
       </c>
       <c r="K156" s="4" t="inlineStr">
@@ -7159,17 +7171,17 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Staff ML Engineer, Search &amp; Recommendation</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Remote - US</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr"/>
@@ -7183,7 +7195,7 @@
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7702644</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7833622</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -7200,7 +7212,7 @@
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>Principal Machine Learning &amp; Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
@@ -7224,7 +7236,7 @@
       </c>
       <c r="J158" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7155492</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7059734</t>
         </is>
       </c>
       <c r="K158" s="4" t="inlineStr">
@@ -7241,7 +7253,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>Principal, Product Manager - AI / LLM</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -7265,7 +7277,7 @@
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7619420</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7702644</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
@@ -7282,7 +7294,7 @@
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>Product Engineer (Backend)</t>
+          <t>Principal Machine Learning &amp; Data Engineer</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
@@ -7306,7 +7318,7 @@
       </c>
       <c r="J160" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7671815</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7155492</t>
         </is>
       </c>
       <c r="K160" s="4" t="inlineStr">
@@ -7323,7 +7335,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Senior Manager, Machine Learning</t>
+          <t>Principal, Product Manager - AI / LLM</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -7347,7 +7359,7 @@
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7066029</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7619420</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
@@ -7364,7 +7376,7 @@
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>Staff Data Scientist</t>
+          <t>Product Engineer (Backend)</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
@@ -7388,7 +7400,7 @@
       </c>
       <c r="J162" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7821458</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7671815</t>
         </is>
       </c>
       <c r="K162" s="4" t="inlineStr">
@@ -7405,7 +7417,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>Staff, Data Scientist (L4) GTM Data Science &amp; Analytics</t>
+          <t>Senior Manager, Machine Learning</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -7429,7 +7441,7 @@
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7851920</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7066029</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
@@ -7446,7 +7458,7 @@
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer</t>
+          <t>Staff Data Scientist</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
@@ -7470,7 +7482,7 @@
       </c>
       <c r="J164" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7061880</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7821458</t>
         </is>
       </c>
       <c r="K164" s="4" t="inlineStr">
@@ -7487,7 +7499,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer (L4)</t>
+          <t>Staff, Data Scientist (L4) GTM Data Science &amp; Analytics</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -7497,7 +7509,7 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>Remote - India</t>
+          <t>Remote - US</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr"/>
@@ -7511,7 +7523,7 @@
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7520997</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7851920</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
@@ -7528,39 +7540,31 @@
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>Senior Python Developer - Django (m/w/d)</t>
+          <t>Staff Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>sync.blue® GmbH</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>Haltern am See</t>
-        </is>
-      </c>
-      <c r="E166" s="4" t="inlineStr">
-        <is>
-          <t>berufserfahren</t>
-        </is>
-      </c>
+          <t>Remote - US</t>
+        </is>
+      </c>
+      <c r="E166" s="4" t="inlineStr"/>
       <c r="F166" s="4" t="inlineStr"/>
-      <c r="G166" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Software Development</t>
-        </is>
-      </c>
+      <c r="G166" s="4" t="inlineStr"/>
       <c r="H166" s="4" t="inlineStr"/>
       <c r="I166" s="4" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J166" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/syncblue-gmbh/senior-python-developer-django-haltern-am-see-16238</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7061880</t>
         </is>
       </c>
       <c r="K166" s="4" t="inlineStr">
@@ -7577,39 +7581,31 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>Freelance Senior AI Product Manager</t>
+          <t>Staff Machine Learning Engineer (L4)</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>nexamind GmbH</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E167" s="2" t="inlineStr">
-        <is>
-          <t>Freelance, professional / experienced</t>
-        </is>
-      </c>
+          <t>Remote - India</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr"/>
       <c r="F167" s="2" t="inlineStr"/>
-      <c r="G167" s="2" t="inlineStr">
-        <is>
-          <t>Remote, Product Management</t>
-        </is>
-      </c>
+      <c r="G167" s="2" t="inlineStr"/>
       <c r="H167" s="2" t="inlineStr"/>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/nexamind-gmbh/freelance-senior-ai-product-manager-berlin-73613</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7520997</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
@@ -7626,17 +7622,17 @@
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>Senior Full-Stack-Entwickler:in React / TypeScript / .NET  100 % Remote, KI-First</t>
+          <t>Senior Python Developer - Django (m/w/d)</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>yourMAIL GmbH</t>
+          <t>sync.blue® GmbH</t>
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Haltern am See</t>
         </is>
       </c>
       <c r="E168" s="4" t="inlineStr">
@@ -7658,7 +7654,7 @@
       </c>
       <c r="J168" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/yourmail-gmbh/senior-full-stack-entwicklerin-react-typescript-net-100-remote-ki-first-berlin-21152</t>
+          <t>https://www.arbeitnow.com/jobs/companies/syncblue-gmbh/senior-python-developer-django-haltern-am-see-16238</t>
         </is>
       </c>
       <c r="K168" s="4" t="inlineStr">
@@ -7675,12 +7671,12 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>Senior Frontend-Entwickler:in React / TypeScript, 100 % Remote, KI-First</t>
+          <t>Freelance Senior AI Product Manager</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>yourMAIL GmbH</t>
+          <t>nexamind GmbH</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
@@ -7690,13 +7686,13 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>berufserfahren</t>
+          <t>Freelance, professional / experienced</t>
         </is>
       </c>
       <c r="F169" s="2" t="inlineStr"/>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>Remote, Software Development</t>
+          <t>Remote, Product Management</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr"/>
@@ -7707,7 +7703,7 @@
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/yourmail-gmbh/senior-frontend-entwicklerin-react-typescript-100-remote-ki-first-berlin-288218</t>
+          <t>https://www.arbeitnow.com/jobs/companies/nexamind-gmbh/freelance-senior-ai-product-manager-berlin-73613</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
@@ -7724,24 +7720,28 @@
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>Full-Stack Entwickler (m/w/d) - .NET 100% Remote</t>
+          <t>Senior Full-Stack-Entwickler:in React / TypeScript / .NET  100 % Remote, KI-First</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>FNTIO</t>
+          <t>yourMAIL GmbH</t>
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>Frankfurt am Main</t>
-        </is>
-      </c>
-      <c r="E170" s="4" t="inlineStr"/>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="E170" s="4" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
       <c r="F170" s="4" t="inlineStr"/>
       <c r="G170" s="4" t="inlineStr">
         <is>
-          <t>Remote, Consulting, Engineering</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr"/>
@@ -7752,7 +7752,7 @@
       </c>
       <c r="J170" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/fntio/full-stack-entwickler-net-100-remote-frankfurt-am-main-122380</t>
+          <t>https://www.arbeitnow.com/jobs/companies/yourmail-gmbh/senior-full-stack-entwicklerin-react-typescript-net-100-remote-ki-first-berlin-21152</t>
         </is>
       </c>
       <c r="K170" s="4" t="inlineStr">
@@ -7769,12 +7769,12 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Frontend-Entwickler:in React / TypeScript, 100 % Remote, KI-First</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>Phantasma Labs</t>
+          <t>yourMAIL GmbH</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
@@ -7782,11 +7782,15 @@
           <t>Berlin</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr"/>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
       <c r="F171" s="2" t="inlineStr"/>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>Remote, Engineering</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr"/>
@@ -7797,7 +7801,7 @@
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/phantasma-labs/machine-learning-engineer-berlin-303955</t>
+          <t>https://www.arbeitnow.com/jobs/companies/yourmail-gmbh/senior-frontend-entwicklerin-react-typescript-100-remote-ki-first-berlin-288218</t>
         </is>
       </c>
       <c r="K171" s="2" t="inlineStr">
@@ -7814,28 +7818,24 @@
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>Technical Data Manager (m/w/d)</t>
+          <t>Full-Stack Entwickler (m/w/d) - .NET 100% Remote</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>BMF Media Information Technology GmbH</t>
+          <t>FNTIO</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>Augsburg</t>
-        </is>
-      </c>
-      <c r="E172" s="4" t="inlineStr">
-        <is>
-          <t>berufserfahren</t>
-        </is>
-      </c>
+          <t>Frankfurt am Main</t>
+        </is>
+      </c>
+      <c r="E172" s="4" t="inlineStr"/>
       <c r="F172" s="4" t="inlineStr"/>
       <c r="G172" s="4" t="inlineStr">
         <is>
-          <t>Remote, Technical Documentation</t>
+          <t>Remote, Consulting, Engineering</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr"/>
@@ -7846,7 +7846,7 @@
       </c>
       <c r="J172" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/bmf-media-information-technology-gmbh/technical-data-manager-augsburg-42188</t>
+          <t>https://www.arbeitnow.com/jobs/companies/fntio/full-stack-entwickler-net-100-remote-frankfurt-am-main-122380</t>
         </is>
       </c>
       <c r="K172" s="4" t="inlineStr">
@@ -7863,28 +7863,24 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>Data Integration &amp; API Engineer m/w/d - Bi &amp; Data Automation</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>loyos bi GmbH</t>
+          <t>Phantasma Labs</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>Hamburg</t>
-        </is>
-      </c>
-      <c r="E173" s="2" t="inlineStr">
-        <is>
-          <t>berufserfahren</t>
-        </is>
-      </c>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr"/>
       <c r="F173" s="2" t="inlineStr"/>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>Remote, Software Development</t>
+          <t>Remote, Engineering</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr"/>
@@ -7895,7 +7891,7 @@
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/loyos-bi-gmbh/data-integration-api-engineer-bi-data-automation-hamburg-66228</t>
+          <t>https://www.arbeitnow.com/jobs/companies/phantasma-labs/machine-learning-engineer-berlin-303955</t>
         </is>
       </c>
       <c r="K173" s="2" t="inlineStr">
@@ -7912,28 +7908,28 @@
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Technical Data Manager (m/w/d)</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>Coding Partners</t>
+          <t>BMF Media Information Technology GmbH</t>
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="E174" s="4" t="inlineStr">
         <is>
-          <t>professional / experienced</t>
+          <t>berufserfahren</t>
         </is>
       </c>
       <c r="F174" s="4" t="inlineStr"/>
       <c r="G174" s="4" t="inlineStr">
         <is>
-          <t>Remote, Software Development</t>
+          <t>Remote, Technical Documentation</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr"/>
@@ -7944,7 +7940,7 @@
       </c>
       <c r="J174" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/coding-partners/senior-full-stack-engineer-berlin-391720</t>
+          <t>https://www.arbeitnow.com/jobs/companies/bmf-media-information-technology-gmbh/technical-data-manager-augsburg-42188</t>
         </is>
       </c>
       <c r="K174" s="4" t="inlineStr">
@@ -7961,17 +7957,17 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>Laravel Developer (m/w/d) - AI-First PropTech</t>
+          <t>Data Integration &amp; API Engineer m/w/d - Bi &amp; Data Automation</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>Immovara GmbH</t>
+          <t>loyos bi GmbH</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>Korntal-Münchingen</t>
+          <t>Hamburg</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
@@ -7993,7 +7989,7 @@
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/immovara-gmbh/laravel-developer-ai-first-proptech-korntal-munchingen-471269</t>
+          <t>https://www.arbeitnow.com/jobs/companies/loyos-bi-gmbh/data-integration-api-engineer-bi-data-automation-hamburg-66228</t>
         </is>
       </c>
       <c r="K175" s="2" t="inlineStr">
@@ -8010,22 +8006,22 @@
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>Fullstack Softwareentwickler (m/w/d)</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>TecFox GmbH</t>
+          <t>Coding Partners</t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>Braunschweig</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="E176" s="4" t="inlineStr">
         <is>
-          <t>berufserfahren</t>
+          <t>professional / experienced</t>
         </is>
       </c>
       <c r="F176" s="4" t="inlineStr"/>
@@ -8042,7 +8038,7 @@
       </c>
       <c r="J176" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/tecfox-gmbh/fullstack-softwareentwickler-braunschweig-405178</t>
+          <t>https://www.arbeitnow.com/jobs/companies/coding-partners/senior-full-stack-engineer-berlin-391720</t>
         </is>
       </c>
       <c r="K176" s="4" t="inlineStr">
@@ -8059,17 +8055,17 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>Frontend Softwareentwickler (m/w/d)</t>
+          <t>Laravel Developer (m/w/d) - AI-First PropTech</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>TecFox GmbH</t>
+          <t>Immovara GmbH</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>Braunschweig</t>
+          <t>Korntal-Münchingen</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
@@ -8091,7 +8087,7 @@
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/tecfox-gmbh/frontend-softwareentwickler-braunschweig-341792</t>
+          <t>https://www.arbeitnow.com/jobs/companies/immovara-gmbh/laravel-developer-ai-first-proptech-korntal-munchingen-471269</t>
         </is>
       </c>
       <c r="K177" s="2" t="inlineStr">
@@ -8108,17 +8104,17 @@
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>Fullstack-Developer*in (m/w/d) Web &amp; AI Automation</t>
+          <t>Fullstack Softwareentwickler (m/w/d)</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>NeoBird Digital</t>
+          <t>TecFox GmbH</t>
         </is>
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>Nuremberg</t>
+          <t>Braunschweig</t>
         </is>
       </c>
       <c r="E178" s="4" t="inlineStr">
@@ -8140,7 +8136,7 @@
       </c>
       <c r="J178" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/neobird-digital/fullstack-developerin-web-ai-automation-nuremberg-157752</t>
+          <t>https://www.arbeitnow.com/jobs/companies/tecfox-gmbh/fullstack-softwareentwickler-braunschweig-405178</t>
         </is>
       </c>
       <c r="K178" s="4" t="inlineStr">
@@ -8157,24 +8153,28 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer / Backend &amp; Frontend - Bootstrapped SaaS Startup (m/w/d) remote in EU</t>
+          <t>Frontend Softwareentwickler (m/w/d)</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>DatAds</t>
+          <t>TecFox GmbH</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>Cologne</t>
-        </is>
-      </c>
-      <c r="E179" s="2" t="inlineStr"/>
+          <t>Braunschweig</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
       <c r="F179" s="2" t="inlineStr"/>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>Remote, IT</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr"/>
@@ -8185,7 +8185,7 @@
       </c>
       <c r="J179" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-bootstrapped-saas-startup-remote-in-eu-cologne-82307</t>
+          <t>https://www.arbeitnow.com/jobs/companies/tecfox-gmbh/frontend-softwareentwickler-braunschweig-341792</t>
         </is>
       </c>
       <c r="K179" s="2" t="inlineStr">
@@ -8202,24 +8202,28 @@
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer / Rest APIs / Cloud / TailwindCSS / SaaS Startup (m/w/d) remote in EU</t>
+          <t>Fullstack-Developer*in (m/w/d) Web &amp; AI Automation</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>DatAds</t>
+          <t>NeoBird Digital</t>
         </is>
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>Cologne</t>
-        </is>
-      </c>
-      <c r="E180" s="4" t="inlineStr"/>
+          <t>Nuremberg</t>
+        </is>
+      </c>
+      <c r="E180" s="4" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
       <c r="F180" s="4" t="inlineStr"/>
       <c r="G180" s="4" t="inlineStr">
         <is>
-          <t>Remote, IT</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H180" s="4" t="inlineStr"/>
@@ -8230,7 +8234,7 @@
       </c>
       <c r="J180" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-bootstrapped-saas-startup-remote-in-eu-cologne-38634</t>
+          <t>https://www.arbeitnow.com/jobs/companies/neobird-digital/fullstack-developerin-web-ai-automation-nuremberg-157752</t>
         </is>
       </c>
       <c r="K180" s="4" t="inlineStr">
@@ -8247,7 +8251,7 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer / Node.js / TypeScript / React / Azure - AdTech SaaS Startup (m/w/d) remote</t>
+          <t>Full-Stack Software Engineer / Backend &amp; Frontend - Bootstrapped SaaS Startup (m/w/d) remote in EU</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
@@ -8275,7 +8279,7 @@
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-adtech-saas-startup-remote-cologne-263746</t>
+          <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-bootstrapped-saas-startup-remote-in-eu-cologne-82307</t>
         </is>
       </c>
       <c r="K181" s="2" t="inlineStr">
@@ -8292,24 +8296,20 @@
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>Senior DevOps / Platform Engineer (f/m/x)</t>
+          <t>Full-Stack Software Engineer / Rest APIs / Cloud / TailwindCSS / SaaS Startup (m/w/d) remote in EU</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>MAIA</t>
+          <t>DatAds</t>
         </is>
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>Leipzig</t>
-        </is>
-      </c>
-      <c r="E182" s="4" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
+          <t>Cologne</t>
+        </is>
+      </c>
+      <c r="E182" s="4" t="inlineStr"/>
       <c r="F182" s="4" t="inlineStr"/>
       <c r="G182" s="4" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
       </c>
       <c r="J182" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/maia/senior-devops-platform-engineer-leipzig-388068</t>
+          <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-bootstrapped-saas-startup-remote-in-eu-cologne-38634</t>
         </is>
       </c>
       <c r="K182" s="4" t="inlineStr">
@@ -8336,40 +8336,40 @@
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer AI Infrastructure</t>
+          <t>Full-Stack Software Engineer / Node.js / TypeScript / React / Azure - AdTech SaaS Startup (m/w/d) remote</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>Andromeda Cluster</t>
+          <t>DatAds</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Cologne</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr"/>
       <c r="F183" s="2" t="inlineStr"/>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>design, training, technical, software, code, manager, financial, cloud, management, lead, senior, operations, reliability, go, health, engineer, engineering, linux, digital nomad</t>
+          <t>Remote, IT</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr"/>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J183" s="3" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-senior-site-reliability-engineer-ai-infrastructure-andromeda-cluster-1131375</t>
+          <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-adtech-saas-startup-remote-cologne-263746</t>
         </is>
       </c>
       <c r="K183" s="2" t="inlineStr">
@@ -8381,40 +8381,44 @@
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>Senior Financial Analyst Digital Assets</t>
+          <t>Senior DevOps / Platform Engineer (f/m/x)</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>Exodus Movement Inc.</t>
+          <t>MAIA</t>
         </is>
       </c>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E184" s="4" t="inlineStr"/>
+          <t>Leipzig</t>
+        </is>
+      </c>
+      <c r="E184" s="4" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
       <c r="F184" s="4" t="inlineStr"/>
       <c r="G184" s="4" t="inlineStr">
         <is>
-          <t>analyst, cryptocurrency, support, financial, investment, finance, senior, non tech</t>
+          <t>Remote, IT</t>
         </is>
       </c>
       <c r="H184" s="4" t="inlineStr"/>
       <c r="I184" s="4" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J184" s="5" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-senior-financial-analyst-digital-assets-exodus-movement-inc-1131374</t>
+          <t>https://www.arbeitnow.com/jobs/companies/maia/senior-devops-platform-engineer-leipzig-388068</t>
         </is>
       </c>
       <c r="K184" s="4" t="inlineStr">
@@ -8431,24 +8435,24 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>Front End Full Stack Developer</t>
+          <t>Senior Site Reliability Engineer AI Infrastructure</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>Honor Foods</t>
+          <t>Andromeda Cluster</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>Philadelphia, PA</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr"/>
       <c r="F185" s="2" t="inlineStr"/>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>developer, front-end, ui, code, web, operational, backend, digital nomad</t>
+          <t>design, training, technical, software, code, manager, financial, cloud, management, lead, senior, operations, reliability, go, health, engineer, engineering, linux, digital nomad</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr"/>
@@ -8459,7 +8463,7 @@
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-front-end-full-stack-developer-honor-foods-1131370</t>
+          <t>https://remoteOK.com/remote-jobs/remote-senior-site-reliability-engineer-ai-infrastructure-andromeda-cluster-1131375</t>
         </is>
       </c>
       <c r="K185" s="2" t="inlineStr">
@@ -8476,10 +8480,14 @@
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>Wing Assistant: Full-Stack Developer</t>
-        </is>
-      </c>
-      <c r="C186" s="4" t="inlineStr"/>
+          <t>Senior Financial Analyst Digital Assets</t>
+        </is>
+      </c>
+      <c r="C186" s="4" t="inlineStr">
+        <is>
+          <t>Exodus Movement Inc.</t>
+        </is>
+      </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
           <t>Remote</t>
@@ -8487,16 +8495,20 @@
       </c>
       <c r="E186" s="4" t="inlineStr"/>
       <c r="F186" s="4" t="inlineStr"/>
-      <c r="G186" s="4" t="inlineStr"/>
+      <c r="G186" s="4" t="inlineStr">
+        <is>
+          <t>analyst, cryptocurrency, support, financial, investment, finance, senior, non tech</t>
+        </is>
+      </c>
       <c r="H186" s="4" t="inlineStr"/>
       <c r="I186" s="4" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J186" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/wing-assistant-full-stack-developer</t>
+          <t>https://remoteOK.com/remote-jobs/remote-senior-financial-analyst-digital-assets-exodus-movement-inc-1131374</t>
         </is>
       </c>
       <c r="K186" s="4" t="inlineStr">
@@ -8513,27 +8525,35 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>Qventus: Product Designer</t>
-        </is>
-      </c>
-      <c r="C187" s="2" t="inlineStr"/>
+          <t>Front End Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>Honor Foods</t>
+        </is>
+      </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Philadelphia, PA</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr"/>
       <c r="F187" s="2" t="inlineStr"/>
-      <c r="G187" s="2" t="inlineStr"/>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>developer, front-end, ui, code, web, operational, backend, digital nomad</t>
+        </is>
+      </c>
       <c r="H187" s="2" t="inlineStr"/>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/qventus-product-designer</t>
+          <t>https://remoteOK.com/remote-jobs/remote-front-end-full-stack-developer-honor-foods-1131370</t>
         </is>
       </c>
       <c r="K187" s="2" t="inlineStr">
@@ -8550,7 +8570,7 @@
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>Socure: Senior Product Marketing Manager</t>
+          <t>Wing Assistant: Full-Stack Developer</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr"/>
@@ -8570,7 +8590,7 @@
       </c>
       <c r="J188" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/socure-senior-product-marketing-manager</t>
+          <t>https://weworkremotely.com/remote-jobs/wing-assistant-full-stack-developer</t>
         </is>
       </c>
       <c r="K188" s="4" t="inlineStr">
@@ -8587,7 +8607,7 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>Blueprint: Product Designer</t>
+          <t>Qventus: Product Designer</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr"/>
@@ -8607,7 +8627,7 @@
       </c>
       <c r="J189" s="3" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/blueprint-product-designer</t>
+          <t>https://weworkremotely.com/remote-jobs/qventus-product-designer</t>
         </is>
       </c>
       <c r="K189" s="2" t="inlineStr">
@@ -8624,7 +8644,7 @@
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>Interop Labs: Product Marketing Manager</t>
+          <t>Socure: Senior Product Marketing Manager</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr"/>
@@ -8644,7 +8664,7 @@
       </c>
       <c r="J190" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/interop-labs-product-marketing-manager</t>
+          <t>https://weworkremotely.com/remote-jobs/socure-senior-product-marketing-manager</t>
         </is>
       </c>
       <c r="K190" s="4" t="inlineStr">
@@ -8661,17 +8681,13 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Link</t>
-        </is>
-      </c>
-      <c r="C191" s="2" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
+          <t>Blueprint: Product Designer</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr"/>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>Toronto, Remote in Canada</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr"/>
@@ -8680,12 +8696,12 @@
       <c r="H191" s="2" t="inlineStr"/>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J191" s="3" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=6447175</t>
+          <t>https://weworkremotely.com/remote-jobs/blueprint-product-designer</t>
         </is>
       </c>
       <c r="K191" s="2" t="inlineStr">
@@ -8702,17 +8718,13 @@
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="C192" s="4" t="inlineStr">
-        <is>
-          <t>Reddit</t>
-        </is>
-      </c>
+          <t>Interop Labs: Product Marketing Manager</t>
+        </is>
+      </c>
+      <c r="C192" s="4" t="inlineStr"/>
       <c r="D192" s="4" t="inlineStr">
         <is>
-          <t>Remote - Ontario, Canada</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E192" s="4" t="inlineStr"/>
@@ -8721,12 +8733,12 @@
       <c r="H192" s="4" t="inlineStr"/>
       <c r="I192" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J192" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/6960833</t>
+          <t>https://weworkremotely.com/remote-jobs/interop-labs-product-marketing-manager</t>
         </is>
       </c>
       <c r="K192" s="4" t="inlineStr">
@@ -8743,17 +8755,17 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Full Stack Engineer, Link</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Toronto, Remote in Canada</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr"/>
@@ -8767,10 +8779,92 @@
       </c>
       <c r="J193" s="3" t="inlineStr">
         <is>
+          <t>https://stripe.com/jobs/search?gh_jid=6447175</t>
+        </is>
+      </c>
+      <c r="K193" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B194" s="4" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="C194" s="4" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="D194" s="4" t="inlineStr">
+        <is>
+          <t>Remote - Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="E194" s="4" t="inlineStr"/>
+      <c r="F194" s="4" t="inlineStr"/>
+      <c r="G194" s="4" t="inlineStr"/>
+      <c r="H194" s="4" t="inlineStr"/>
+      <c r="I194" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J194" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/6960833</t>
+        </is>
+      </c>
+      <c r="K194" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr"/>
+      <c r="F195" s="2" t="inlineStr"/>
+      <c r="G195" s="2" t="inlineStr"/>
+      <c r="H195" s="2" t="inlineStr"/>
+      <c r="I195" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J195" s="3" t="inlineStr">
+        <is>
           <t>https://job-boards.greenhouse.io/reddit/jobs/6960831</t>
         </is>
       </c>
-      <c r="K193" s="2" t="inlineStr">
+      <c r="K195" s="2" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
@@ -8780,59 +8874,53 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId49"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/remote_jobs.xlsx
+++ b/remote_jobs.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K195"/>
+  <dimension ref="A1:K197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -523,29 +523,33 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer / Backend &amp; Frontend - Bootstrapped SaaS Startup (m/w/d) remote in EU</t>
+          <t>Senior Sofrware Engineer - Full Stack</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>DatAds</t>
+          <t>Parto Group GmbH</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Cologne</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr"/>
+          <t>Hamburg</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Remote, IT</t>
+          <t>Remote, Engineering</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -556,90 +560,90 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-bootstrapped-saas-startup-remote-in-eu-cologne-266336</t>
+          <t>https://www.arbeitnow.com/jobs/companies/parto-group-gmbh/senior-sofrware-engineer-full-stack-hamburg-207489</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Asset Administration Operations Specialist</t>
+          <t>Senior Full Stack Engineer (Product Ownership &amp; Operations)</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Forge Global</t>
+          <t>Yoffix</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Denver</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr"/>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Contract, professional / experienced</t>
+        </is>
+      </c>
       <c r="F3" s="4" t="inlineStr"/>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>travel, financial, operations, non tech</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>$21 - $24</t>
-        </is>
-      </c>
+          <t>Remote, Software Development</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr"/>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-asset-administration-operations-specialist-forge-global-1131523</t>
+          <t>https://www.arbeitnow.com/jobs/companies/yoffix/senior-full-stack-engineer-product-ownership-operations-berlin-437578</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer (TypeScript &amp; AWS) (m/w/d)</t>
+          <t>Full-Stack Software Engineer / Backend &amp; Frontend - Bootstrapped SaaS Startup (m/w/d) remote in EU</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>vOffice Software</t>
+          <t>DatAds</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Hamburg</t>
+          <t>Cologne</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Remote, Software Development</t>
+          <t>Remote, IT</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -650,12 +654,12 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/voffice-software/senior-cloud-software-engineer-typescript-aws-hamburg-431856</t>
+          <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-bootstrapped-saas-startup-remote-in-eu-cologne-266336</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
@@ -667,44 +671,44 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer RoR (all identities)</t>
+          <t>Asset Administration Operations Specialist</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Caspar Health</t>
+          <t>Forge Global</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
+          <t>Denver</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr"/>
       <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>Remote, Software Development</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr"/>
+          <t>travel, financial, operations, non tech</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>$21 - $24</t>
+        </is>
+      </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/caspar-health/senior-backend-engineer-ror-all-identities-berlin-7147</t>
+          <t>https://remoteOK.com/remote-jobs/remote-asset-administration-operations-specialist-forge-global-1131523</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
@@ -716,24 +720,20 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Python Software Engineer - Machine Learning Systems (m/f/d)</t>
+          <t>Senior Cloud Software Engineer (TypeScript &amp; AWS) (m/w/d)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>CUJU</t>
+          <t>vOffice Software</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Frankenthal</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
+          <t>Hamburg</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/cuju/python-software-engineer-machine-learning-systems-frankenthal-183273</t>
+          <t>https://www.arbeitnow.com/jobs/companies/voffice-software/senior-cloud-software-engineer-typescript-aws-hamburg-431856</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -765,28 +765,28 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>AI Algorithm Developer Medical Imaging (m/w/d)</t>
+          <t>Senior Backend Engineer RoR (all identities)</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>citema systems GmbH</t>
+          <t>Caspar Health</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>berufserfahren</t>
+          <t>professional / experienced</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr"/>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>Remote, IT</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
@@ -797,7 +797,7 @@
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/citema-systems-gmbh/ai-algorithm-developer-medical-imaging-munich-91573</t>
+          <t>https://www.arbeitnow.com/jobs/companies/caspar-health/senior-backend-engineer-ror-all-identities-berlin-7147</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -809,40 +809,44 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Python Software Engineer - Machine Learning Systems (m/f/d)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Civitech</t>
+          <t>CUJU</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Austin, TX or Remote</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr"/>
+          <t>Frankenthal</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>python, support, code, cloud, analytics, engineer, engineering, full-time</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-analytics-engineer-civitech-1131512</t>
+          <t>https://www.arbeitnow.com/jobs/companies/cuju/python-software-engineer-machine-learning-systems-frankenthal-183273</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -854,40 +858,44 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Tech Lead</t>
+          <t>AI Algorithm Developer Medical Imaging (m/w/d)</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Zensurance</t>
+          <t>citema systems GmbH</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Toronto, ON</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr"/>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
       <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>design, system, front-end, back-end, security, training, full-stack, docker, technical, support, software, testing, test, growth, code, web, scrum, devops, javascript, education, strategy, management, lead, senior, health, engineering, digital nomad</t>
+          <t>Remote, IT</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr"/>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-tech-lead-zensurance-1131509</t>
+          <t>https://www.arbeitnow.com/jobs/companies/citema-systems-gmbh/ai-algorithm-developer-medical-imaging-munich-91573</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
@@ -904,31 +912,35 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Senior Full-stack Symfony Developer</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr"/>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Civitech</t>
+        </is>
+      </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Austin, TX or Remote</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>symfony, php, javascript, vuejs</t>
+          <t>python, support, code, cloud, analytics, engineer, engineering, full-time</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>WorkingNomads</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>https://www.workingnomads.com/job/go/1587815/</t>
+          <t>https://remoteOK.com/remote-jobs/remote-analytics-engineer-civitech-1131512</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -945,31 +957,35 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Senior Staff Machine Learning Engineer, Feed Relevance</t>
+          <t>Tech Lead</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Zensurance</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Toronto, ON</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr"/>
       <c r="F11" s="4" t="inlineStr"/>
-      <c r="G11" s="4" t="inlineStr"/>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>design, system, front-end, back-end, security, training, full-stack, docker, technical, support, software, testing, test, growth, code, web, scrum, devops, javascript, education, strategy, management, lead, senior, health, engineering, digital nomad</t>
+        </is>
+      </c>
       <c r="H11" s="4" t="inlineStr"/>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7908786</t>
+          <t>https://remoteOK.com/remote-jobs/remote-tech-lead-zensurance-1131509</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
@@ -986,40 +1002,36 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Sidebase Open-Source Contributor &amp; Senior TS Dev (f/m/d)</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Sidestream</t>
-        </is>
-      </c>
+          <t>Senior Full-stack Symfony Developer</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Cologne</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Remote, Software Development</t>
+          <t>symfony, php, javascript, vuejs</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>WorkingNomads</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/sidestream/sidebase-open-source-contributor-senior-ts-dev-cologne-317648</t>
+          <t>https://www.workingnomads.com/job/go/1587815/</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -1031,40 +1043,36 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Senior Typescript Developer (f/m/d)</t>
+          <t>Senior Staff Machine Learning Engineer, Feed Relevance</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Sidestream</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Cologne</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr"/>
       <c r="F13" s="4" t="inlineStr"/>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Software Development</t>
-        </is>
-      </c>
+      <c r="G13" s="4" t="inlineStr"/>
       <c r="H13" s="4" t="inlineStr"/>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/sidestream/senior-typescript-developer-cologne-220463</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7908786</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -1076,24 +1084,24 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Senior AI-Engineer / Agent-Architekt (m/w/d)</t>
+          <t>Sidebase Open-Source Contributor &amp; Senior TS Dev (f/m/d)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Neurawork GmbH &amp; Co. KG</t>
+          <t>Sidestream</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Ampfing</t>
+          <t>Cologne</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Remote, IT</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
@@ -1104,7 +1112,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/neurawork-gmbh-co-kg/senior-ai-engineer-agent-architekt-ampfing-390691</t>
+          <t>https://www.arbeitnow.com/jobs/companies/sidestream/sidebase-open-source-contributor-senior-ts-dev-cologne-317648</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1121,28 +1129,24 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Senior AI Consultant / Machine Learning Engineer (m/w/d) Public Sector | &gt;90% REMOTE</t>
+          <t>Senior Typescript Developer (f/m/d)</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Bridgency HR Management GbR</t>
+          <t>Sidestream</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Usingen</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>berufserfahren</t>
-        </is>
-      </c>
+          <t>Cologne</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr"/>
       <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>Remote, Consulting, Engineering</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
@@ -1153,7 +1157,7 @@
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/bridgency-hr-management-gbr/senior-ai-consultant-machine-learning-engineer-public-sector-90-remote-usingen-94077</t>
+          <t>https://www.arbeitnow.com/jobs/companies/sidestream/senior-typescript-developer-cologne-220463</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
@@ -1170,28 +1174,24 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Werkstudent (m/w/d) Frontend Development &amp; KI-Integration (20h/Woche)</t>
+          <t>Senior AI-Engineer / Agent-Architekt (m/w/d)</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>MEvents Cross Media GmbH</t>
+          <t>Neurawork GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>hilfstätigkeit / student</t>
-        </is>
-      </c>
+          <t>Ampfing</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Remote, Software Development</t>
+          <t>Remote, IT</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/mevents-cross-media-gmbh/werkstudent-frontend-development-ki-integration-20h-woche-berlin-378282</t>
+          <t>https://www.arbeitnow.com/jobs/companies/neurawork-gmbh-co-kg/senior-ai-engineer-agent-architekt-ampfing-390691</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1214,40 +1214,44 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Consultant / Machine Learning Engineer (m/w/d) Public Sector | &gt;90% REMOTE</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Valon Mortgage</t>
+          <t>Bridgency HR Management GbR</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr"/>
+          <t>Usingen</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
       <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>design, saas, python, architect, technical, support, cloud, strategy, management, senior, operations, operational, analytics, reliability, go, engineer, engineering, digital nomad</t>
+          <t>Remote, Consulting, Engineering</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-senior-data-engineer-valon-mortgage-1131504</t>
+          <t>https://www.arbeitnow.com/jobs/companies/bridgency-hr-management-gbr/senior-ai-consultant-machine-learning-engineer-public-sector-90-remote-usingen-94077</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
@@ -1259,139 +1263,135 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Senior AI Agent Architect / AI Automation Architect</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr"/>
+          <t>Werkstudent (m/w/d) Frontend Development &amp; KI-Integration (20h/Woche)</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>MEvents Cross Media GmbH</t>
+        </is>
+      </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr"/>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>hilfstätigkeit / student</t>
+        </is>
+      </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>artificial intelligence, python, machine learning, engineer, communication</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr">
         <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/mevents-cross-media-gmbh/werkstudent-frontend-development-ki-integration-20h-woche-berlin-378282</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Valon Mortgage</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr"/>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>design, saas, python, architect, technical, support, cloud, strategy, management, senior, operations, operational, analytics, reliability, go, engineer, engineering, digital nomad</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr"/>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-senior-data-engineer-valon-mortgage-1131504</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Senior AI Agent Architect / AI Automation Architect</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>artificial intelligence, python, machine learning, engineer, communication</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
           <t>WorkingNomads</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>https://www.workingnomads.com/job/go/1585195/</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>2026-05-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Weiterbildung: Data Science &amp; Business Analytics (IHK) (m/w/d) - Remote</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>DataSmart Point GmbH</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Apprenticeship</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>Remote, Data Scientist</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr"/>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/datasmart-point-gmbh/weiterbildung-data-science-business-analytics-ihk-remote-berlin-23738</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Karrierestart in Data &amp; AI - IHK Data Analyst (m/w/d) - 100 % Online</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>DataSmart Point GmbH</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>Apprenticeship</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr"/>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Data Scientist</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr"/>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J20" s="5" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/datasmart-point-gmbh/karrierestart-in-data-ai-ihk-data-analyst-100-online-berlin-138911</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
         </is>
       </c>
     </row>
@@ -1403,28 +1403,28 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Rockstardevelopers: Senior Fullstack Entwickler (m/w/d) mit Projekterfahrung Deutsche Bahn oder DB Systel</t>
+          <t>Weiterbildung: Data Science &amp; Business Analytics (IHK) (m/w/d) - Remote</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Rockstardevelopers GmbH</t>
+          <t>DataSmart Point GmbH</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>berufserfahren</t>
+          <t>Apprenticeship</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Remote, Software Development</t>
+          <t>Remote, Data Scientist</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr"/>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/rockstardevelopers-gmbh/rockstardevelopers-senior-fullstack-entwickler-mit-projekterfahrung-deutsche-bahn-oder-db-systel-stuttgart-354361</t>
+          <t>https://www.arbeitnow.com/jobs/companies/datasmart-point-gmbh/weiterbildung-data-science-business-analytics-ihk-remote-berlin-23738</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1452,24 +1452,28 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Full-Stack AI Engineer (Computer Vision &amp; Back-end Focus)</t>
+          <t>Karrierestart in Data &amp; AI - IHK Data Analyst (m/w/d) - 100 % Online</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>StellDirVor GmbH</t>
+          <t>DataSmart Point GmbH</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr"/>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Apprenticeship</t>
+        </is>
+      </c>
       <c r="F22" s="4" t="inlineStr"/>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>Remote, Software Development</t>
+          <t>Remote, Data Scientist</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr"/>
@@ -1480,7 +1484,7 @@
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/stelldirvor-gmbh/full-stack-ai-engineer-computer-vision-back-end-focus-munich-122395</t>
+          <t>https://www.arbeitnow.com/jobs/companies/datasmart-point-gmbh/karrierestart-in-data-ai-ihk-data-analyst-100-online-berlin-138911</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
@@ -1492,40 +1496,44 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Rockstardevelopers: Senior Fullstack Entwickler (m/w/d) mit Projekterfahrung Deutsche Bahn oder DB Systel</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Prove</t>
+          <t>Rockstardevelopers GmbH</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr"/>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>software, security, senior, engineer, engineering</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-senior-software-engineer-prove-1131482</t>
+          <t>https://www.arbeitnow.com/jobs/companies/rockstardevelopers-gmbh/rockstardevelopers-senior-fullstack-entwickler-mit-projekterfahrung-deutsche-bahn-oder-db-systel-stuttgart-354361</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1537,40 +1545,40 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Full-Stack AI Engineer (Computer Vision &amp; Back-end Focus)</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Akuity</t>
+          <t>StellDirVor GmbH</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr"/>
       <c r="F24" s="4" t="inlineStr"/>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>saas, developer, software, code, devops, senior, engineer, engineering, backend, digital nomad</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-senior-backend-engineer-akuity-1131479</t>
+          <t>https://www.arbeitnow.com/jobs/companies/stelldirvor-gmbh/full-stack-ai-engineer-computer-vision-back-end-focus-munich-122395</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
@@ -1587,24 +1595,24 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Medical Affairs Solutions Manager UK</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Sorcero</t>
+          <t>Prove</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>manager, growth, operations, biotech</t>
+          <t>software, security, senior, engineer, engineering</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr"/>
@@ -1615,7 +1623,7 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-medical-affairs-solutions-manager-uk-sorcero-1131475</t>
+          <t>https://remoteOK.com/remote-jobs/remote-senior-software-engineer-prove-1131482</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1632,31 +1640,35 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Dropbox</t>
+          <t>Akuity</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Remote - Canada: Select locations</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr"/>
       <c r="F26" s="4" t="inlineStr"/>
-      <c r="G26" s="4" t="inlineStr"/>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>saas, developer, software, code, devops, senior, engineer, engineering, backend, digital nomad</t>
+        </is>
+      </c>
       <c r="H26" s="4" t="inlineStr"/>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7762007?gh_jid=7762007</t>
+          <t>https://remoteOK.com/remote-jobs/remote-senior-backend-engineer-akuity-1131479</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
@@ -1673,31 +1685,35 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Medical Affairs Solutions Manager UK</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Dropbox</t>
+          <t>Sorcero</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Remote - US: Select locations</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr"/>
       <c r="F27" s="2" t="inlineStr"/>
-      <c r="G27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>manager, growth, operations, biotech</t>
+        </is>
+      </c>
       <c r="H27" s="2" t="inlineStr"/>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7762004?gh_jid=7762004</t>
+          <t>https://remoteOK.com/remote-jobs/remote-medical-affairs-solutions-manager-uk-sorcero-1131475</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1724,7 +1740,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Remote - Mexico</t>
+          <t>Remote - Canada: Select locations</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr"/>
@@ -1738,7 +1754,7 @@
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7762009?gh_jid=7762009</t>
+          <t>https://jobs.dropbox.com/listing/7762007?gh_jid=7762007</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
@@ -1755,7 +1771,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Frontend Product Software Engineer, Web DX</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1765,7 +1781,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Remote - Mexico</t>
+          <t>Remote - US: Select locations</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr"/>
@@ -1779,7 +1795,7 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7580431?gh_jid=7580431</t>
+          <t>https://jobs.dropbox.com/listing/7762004?gh_jid=7762004</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1796,7 +1812,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer, Dash Experiences</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -1806,7 +1822,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Remote - US: Select locations</t>
+          <t>Remote - Mexico</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr"/>
@@ -1820,7 +1836,7 @@
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7569140?gh_jid=7569140</t>
+          <t>https://jobs.dropbox.com/listing/7762009?gh_jid=7762009</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
@@ -1837,7 +1853,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer, Dash Experiences</t>
+          <t>Frontend Product Software Engineer, Web DX</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1861,7 +1877,7 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7569145?gh_jid=7569145</t>
+          <t>https://jobs.dropbox.com/listing/7580431?gh_jid=7580431</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1878,7 +1894,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Product Software Engineer, Payments</t>
+          <t>Full Stack Software Engineer, Dash Experiences</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -1888,7 +1904,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Remote - Poland</t>
+          <t>Remote - US: Select locations</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr"/>
@@ -1902,7 +1918,7 @@
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7812915?gh_jid=7812915</t>
+          <t>https://jobs.dropbox.com/listing/7569140?gh_jid=7569140</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
@@ -1919,7 +1935,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, AI Products</t>
+          <t>Full Stack Software Engineer, Dash Experiences</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1929,7 +1945,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Remote - Canada: Select locations</t>
+          <t>Remote - Mexico</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
@@ -1943,7 +1959,7 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7789389?gh_jid=7789389</t>
+          <t>https://jobs.dropbox.com/listing/7569145?gh_jid=7569145</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -1960,7 +1976,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, AI Products</t>
+          <t>Senior Backend Product Software Engineer, Payments</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -1970,7 +1986,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Remote - Canada: Select locations</t>
+          <t>Remote - Poland</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr"/>
@@ -1984,7 +2000,7 @@
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7729764?gh_jid=7729764</t>
+          <t>https://jobs.dropbox.com/listing/7812915?gh_jid=7812915</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
@@ -2011,7 +2027,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Remote - US: Select locations</t>
+          <t>Remote - Canada: Select locations</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr"/>
@@ -2025,7 +2041,7 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7729761?gh_jid=7729761</t>
+          <t>https://jobs.dropbox.com/listing/7789389?gh_jid=7789389</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2052,7 +2068,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Remote - US: Select locations</t>
+          <t>Remote - Canada: Select locations</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr"/>
@@ -2066,7 +2082,7 @@
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7789386?gh_jid=7789386</t>
+          <t>https://jobs.dropbox.com/listing/7729764?gh_jid=7729764</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
@@ -2083,7 +2099,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Dash Agentic AI</t>
+          <t>Senior Data Scientist, AI Products</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2093,7 +2109,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Remote - Canada: Select locations</t>
+          <t>Remote - US: Select locations</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr"/>
@@ -2107,7 +2123,7 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7644890?gh_jid=7644890</t>
+          <t>https://jobs.dropbox.com/listing/7729761?gh_jid=7729761</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2124,7 +2140,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Dash Agentic AI</t>
+          <t>Senior Data Scientist, AI Products</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -2134,7 +2150,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Remote - US: All locations</t>
+          <t>Remote - US: Select locations</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr"/>
@@ -2148,7 +2164,7 @@
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7644886?gh_jid=7644886</t>
+          <t>https://jobs.dropbox.com/listing/7789386?gh_jid=7789386</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
@@ -2165,7 +2181,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Staff Backend Product Software Engineer, Commerce Platform</t>
+          <t>Senior Machine Learning Engineer, Dash Agentic AI</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2175,7 +2191,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Remote - Mexico</t>
+          <t>Remote - Canada: Select locations</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr"/>
@@ -2189,7 +2205,7 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7759733?gh_jid=7759733</t>
+          <t>https://jobs.dropbox.com/listing/7644890?gh_jid=7644890</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2206,7 +2222,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Staff Backend Product Software Engineer, Commerce Platform</t>
+          <t>Senior Machine Learning Engineer, Dash Agentic AI</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -2216,7 +2232,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Remote - US: Select locations</t>
+          <t>Remote - US: All locations</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr"/>
@@ -2230,7 +2246,7 @@
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7759728?gh_jid=7759728</t>
+          <t>https://jobs.dropbox.com/listing/7644886?gh_jid=7644886</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
@@ -2257,7 +2273,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Remote - Canada: Select locations</t>
+          <t>Remote - Mexico</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr"/>
@@ -2271,7 +2287,7 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7759731?gh_jid=7759731</t>
+          <t>https://jobs.dropbox.com/listing/7759733?gh_jid=7759733</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -2288,7 +2304,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Staff Backend Product Software Engineer, Core</t>
+          <t>Staff Backend Product Software Engineer, Commerce Platform</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -2312,7 +2328,7 @@
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7421121?gh_jid=7421121</t>
+          <t>https://jobs.dropbox.com/listing/7759728?gh_jid=7759728</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
@@ -2329,7 +2345,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Staff Backend Product Software Engineer, Core</t>
+          <t>Staff Backend Product Software Engineer, Commerce Platform</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2353,7 +2369,7 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7421124?gh_jid=7421124</t>
+          <t>https://jobs.dropbox.com/listing/7759731?gh_jid=7759731</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -2370,7 +2386,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Staff Fullstack Product Software Engineer, Dash</t>
+          <t>Staff Backend Product Software Engineer, Core</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -2380,7 +2396,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Remote - Canada: Select locations</t>
+          <t>Remote - US: Select locations</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr"/>
@@ -2394,7 +2410,7 @@
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7551548?gh_jid=7551548</t>
+          <t>https://jobs.dropbox.com/listing/7421121?gh_jid=7421121</t>
         </is>
       </c>
       <c r="K44" s="4" t="inlineStr">
@@ -2411,7 +2427,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Staff Fullstack Product Software Engineer, Dash</t>
+          <t>Staff Backend Product Software Engineer, Core</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2421,7 +2437,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Remote - US: Select locations</t>
+          <t>Remote - Canada: Select locations</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -2435,7 +2451,7 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7551545?gh_jid=7551545</t>
+          <t>https://jobs.dropbox.com/listing/7421124?gh_jid=7421124</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -2452,7 +2468,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Staff Full Stack Software Engineer, Churn</t>
+          <t>Staff Fullstack Product Software Engineer, Dash</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -2462,7 +2478,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Remote - Poland</t>
+          <t>Remote - Canada: Select locations</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr"/>
@@ -2476,7 +2492,7 @@
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7421131?gh_jid=7421131</t>
+          <t>https://jobs.dropbox.com/listing/7551548?gh_jid=7551548</t>
         </is>
       </c>
       <c r="K46" s="4" t="inlineStr">
@@ -2493,7 +2509,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Staff Fullstack Software Engineer, Growth Monetization</t>
+          <t>Staff Fullstack Product Software Engineer, Dash</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2517,7 +2533,7 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7421150?gh_jid=7421150</t>
+          <t>https://jobs.dropbox.com/listing/7551545?gh_jid=7551545</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -2534,7 +2550,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Staff Fullstack Software Engineer, Growth Monetization</t>
+          <t>Staff Full Stack Software Engineer, Churn</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -2544,7 +2560,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Remote - Canada: Select locations</t>
+          <t>Remote - Poland</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr"/>
@@ -2558,7 +2574,7 @@
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7421153?gh_jid=7421153</t>
+          <t>https://jobs.dropbox.com/listing/7421131?gh_jid=7421131</t>
         </is>
       </c>
       <c r="K48" s="4" t="inlineStr">
@@ -2575,13 +2591,17 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>WALTER: Senior Fullstack Engineer (Ruby+React)</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr"/>
+          <t>Staff Fullstack Software Engineer, Growth Monetization</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Dropbox</t>
+        </is>
+      </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote - US: Select locations</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr"/>
@@ -2590,17 +2610,17 @@
       <c r="H49" s="2" t="inlineStr"/>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/walter-senior-fullstack-engineer-ruby-react</t>
+          <t>https://jobs.dropbox.com/listing/7421150?gh_jid=7421150</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
     </row>
@@ -2612,13 +2632,17 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>WALTER: Full-Stack Engineering Lead</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr"/>
+          <t>Staff Fullstack Software Engineer, Growth Monetization</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Dropbox</t>
+        </is>
+      </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote - Canada: Select locations</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr"/>
@@ -2627,17 +2651,17 @@
       <c r="H50" s="4" t="inlineStr"/>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/walter-full-stack-engineering-lead</t>
+          <t>https://jobs.dropbox.com/listing/7421153?gh_jid=7421153</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
     </row>
@@ -2649,17 +2673,13 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Frontend Product Software Engineer, Design Systems</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>Dropbox</t>
-        </is>
-      </c>
+          <t>WALTER: Senior Fullstack Engineer (Ruby+React)</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr"/>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Remote - Mexico</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr"/>
@@ -2668,12 +2688,12 @@
       <c r="H51" s="2" t="inlineStr"/>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7862086?gh_jid=7862086</t>
+          <t>https://weworkremotely.com/remote-jobs/walter-senior-fullstack-engineer-ruby-react</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -2685,40 +2705,32 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Lead AI Engineer &amp; Technical Architect</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>Bold Business</t>
-        </is>
-      </c>
+          <t>WALTER: Full-Stack Engineering Lead</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr"/>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>India, Latin America, Philippines</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr"/>
       <c r="F52" s="4" t="inlineStr"/>
-      <c r="G52" s="4" t="inlineStr">
-        <is>
-          <t>architect, technical, lead, engineer</t>
-        </is>
-      </c>
+      <c r="G52" s="4" t="inlineStr"/>
       <c r="H52" s="4" t="inlineStr"/>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-lead-ai-engineer-technical-architect-bold-business-1131461</t>
+          <t>https://weworkremotely.com/remote-jobs/walter-full-stack-engineering-lead</t>
         </is>
       </c>
       <c r="K52" s="4" t="inlineStr">
@@ -2730,40 +2742,36 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer Showroom</t>
+          <t>Frontend Product Software Engineer, Design Systems</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Higharc</t>
+          <t>Dropbox</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote - Mexico</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr"/>
       <c r="F53" s="2" t="inlineStr"/>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>software, design, 3d, full-stack, support, ux, manager, api, engineer, engineering, backend, digital nomad</t>
-        </is>
-      </c>
+      <c r="G53" s="2" t="inlineStr"/>
       <c r="H53" s="2" t="inlineStr"/>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-software-engineer-showroom-higharc-1131457</t>
+          <t>https://jobs.dropbox.com/listing/7862086?gh_jid=7862086</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -2780,31 +2788,35 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Protocol Review Specialist</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr"/>
+          <t>Lead AI Engineer &amp; Technical Architect</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>Bold Business</t>
+        </is>
+      </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>India, Latin America, Philippines</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr"/>
       <c r="F54" s="4" t="inlineStr"/>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>communication, phone, english</t>
+          <t>architect, technical, lead, engineer</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr"/>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>WorkingNomads</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>https://www.workingnomads.com/job/go/1580747/</t>
+          <t>https://remoteOK.com/remote-jobs/remote-lead-ai-engineer-technical-architect-bold-business-1131461</t>
         </is>
       </c>
       <c r="K54" s="4" t="inlineStr">
@@ -2821,31 +2833,35 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Staff AI Engineer - Notebooks</t>
+          <t>Software Engineer Showroom</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Datadog</t>
+          <t>Higharc</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Portugal, Remote</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="2" t="inlineStr"/>
-      <c r="G55" s="2" t="inlineStr"/>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>software, design, 3d, full-stack, support, ux, manager, api, engineer, engineering, backend, digital nomad</t>
+        </is>
+      </c>
       <c r="H55" s="2" t="inlineStr"/>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>https://careers.datadoghq.com/detail/7627445/?gh_jid=7627445</t>
+          <t>https://remoteOK.com/remote-jobs/remote-software-engineer-showroom-higharc-1131457</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -2862,31 +2878,31 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Staff AI Engineer - Notebooks</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>Datadog</t>
-        </is>
-      </c>
+          <t>Protocol Review Specialist</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr"/>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>France, Remote; Germany, Remote; Ireland, Remote; Italy, Remote; Spain, Remote; Switzerland, Remote</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr"/>
       <c r="F56" s="4" t="inlineStr"/>
-      <c r="G56" s="4" t="inlineStr"/>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>communication, phone, english</t>
+        </is>
+      </c>
       <c r="H56" s="4" t="inlineStr"/>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WorkingNomads</t>
         </is>
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>https://careers.datadoghq.com/detail/7627429/?gh_jid=7627429</t>
+          <t>https://www.workingnomads.com/job/go/1580747/</t>
         </is>
       </c>
       <c r="K56" s="4" t="inlineStr">
@@ -2903,17 +2919,17 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Ads Conversion Modeling, Machine Learning Engineering Manager</t>
+          <t>Staff AI Engineer - Notebooks</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Datadog</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Portugal, Remote</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr"/>
@@ -2927,7 +2943,7 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7792848</t>
+          <t>https://careers.datadoghq.com/detail/7627445/?gh_jid=7627445</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -2944,17 +2960,17 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Data Scientist, Ads</t>
+          <t>Staff AI Engineer - Notebooks</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Datadog</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Remote - British Columbia, Canada</t>
+          <t>France, Remote; Germany, Remote; Ireland, Remote; Italy, Remote; Spain, Remote; Switzerland, Remote</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr"/>
@@ -2968,7 +2984,7 @@
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7607124</t>
+          <t>https://careers.datadoghq.com/detail/7627429/?gh_jid=7627429</t>
         </is>
       </c>
       <c r="K58" s="4" t="inlineStr">
@@ -2985,7 +3001,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Data Scientist, Ads</t>
+          <t>Ads Conversion Modeling, Machine Learning Engineering Manager</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -3009,7 +3025,7 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/6580815</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7792848</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -3026,7 +3042,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Scientist, Ads</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -3036,7 +3052,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Remote - Ontario, Canada</t>
+          <t>Remote - British Columbia, Canada</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr"/>
@@ -3050,7 +3066,7 @@
       </c>
       <c r="J60" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7131934</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7607124</t>
         </is>
       </c>
       <c r="K60" s="4" t="inlineStr">
@@ -3067,7 +3083,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Scientist, Ads</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3091,7 +3107,7 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7131932</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/6580815</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -3108,7 +3124,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Principal Data Scientist, Ads</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -3118,7 +3134,7 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Remote - Ontario, Canada</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr"/>
@@ -3132,7 +3148,7 @@
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7330347</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7131934</t>
         </is>
       </c>
       <c r="K62" s="4" t="inlineStr">
@@ -3149,7 +3165,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Ads</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3159,7 +3175,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Remote - British Columbia, Canada</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr"/>
@@ -3173,7 +3189,7 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7607121</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7131932</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -3190,7 +3206,7 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Ads</t>
+          <t>Principal Data Scientist, Ads</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -3214,7 +3230,7 @@
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/6042236</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7330347</t>
         </is>
       </c>
       <c r="K64" s="4" t="inlineStr">
@@ -3231,7 +3247,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Consumer</t>
+          <t>Senior Data Scientist, Ads</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3241,7 +3257,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Remote - British Columbia, Canada</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr"/>
@@ -3255,7 +3271,7 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7275414</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7607121</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -3272,7 +3288,7 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Senior  Machine Learning Engineer, ML Training Platform</t>
+          <t>Senior Data Scientist, Ads</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -3296,7 +3312,7 @@
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7074776</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/6042236</t>
         </is>
       </c>
       <c r="K66" s="4" t="inlineStr">
@@ -3313,7 +3329,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Systems Engineer</t>
+          <t>Senior Data Scientist, Consumer</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -3337,7 +3353,7 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7731772</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7275414</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -3354,7 +3370,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, GenAI Platform</t>
+          <t>Senior  Machine Learning Engineer, ML Training Platform</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -3378,7 +3394,7 @@
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7753480</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7074776</t>
         </is>
       </c>
       <c r="K68" s="4" t="inlineStr">
@@ -3395,7 +3411,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Senior Staff Machine Learning Engineer, GenAI Platform</t>
+          <t>Senior Machine Learning Systems Engineer</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -3419,7 +3435,7 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7772274</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7731772</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -3436,7 +3452,7 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Staff Data Scientist, Ads</t>
+          <t>Senior Software Engineer, GenAI Platform</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -3446,7 +3462,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Remote - British Columbia, Canada</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr"/>
@@ -3460,7 +3476,7 @@
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7721851</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7753480</t>
         </is>
       </c>
       <c r="K70" s="4" t="inlineStr">
@@ -3477,7 +3493,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Staff Data Scientist, Ads</t>
+          <t>Senior Staff Machine Learning Engineer, GenAI Platform</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -3501,7 +3517,7 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7721787</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7772274</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -3518,7 +3534,7 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Staff Data Scientist, Consumer</t>
+          <t>Staff Data Scientist, Ads</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -3528,7 +3544,7 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Remote - British Columbia, Canada</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr"/>
@@ -3542,7 +3558,7 @@
       </c>
       <c r="J72" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/6745284</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7721851</t>
         </is>
       </c>
       <c r="K72" s="4" t="inlineStr">
@@ -3559,7 +3575,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Staff Data Scientist, Marketing</t>
+          <t>Staff Data Scientist, Ads</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -3583,7 +3599,7 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7445240</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7721787</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -3600,7 +3616,7 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, Ads Auction (Ads Marketplace Quality)</t>
+          <t>Staff Data Scientist, Consumer</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -3624,7 +3640,7 @@
       </c>
       <c r="J74" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7181821</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/6745284</t>
         </is>
       </c>
       <c r="K74" s="4" t="inlineStr">
@@ -3641,7 +3657,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, Ads Content Understanding</t>
+          <t>Staff Data Scientist, Marketing</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -3665,7 +3681,7 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7851761</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7445240</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -3682,7 +3698,7 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Systems Engineer</t>
+          <t>Staff Machine Learning Engineer, Ads Auction (Ads Marketplace Quality)</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
@@ -3706,7 +3722,7 @@
       </c>
       <c r="J76" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7731788</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7181821</t>
         </is>
       </c>
       <c r="K76" s="4" t="inlineStr">
@@ -3723,44 +3739,36 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Werkstudent:in KI Marketing (m/w/d)</t>
+          <t>Staff Machine Learning Engineer, Ads Content Understanding</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>laria.ai</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>Working student, berufseinstieg</t>
-        </is>
-      </c>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr"/>
       <c r="F77" s="2" t="inlineStr"/>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>Remote, Online Marketing</t>
-        </is>
-      </c>
+      <c r="G77" s="2" t="inlineStr"/>
       <c r="H77" s="2" t="inlineStr"/>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/lariaai/werkstudentin-ki-marketing-berlin-9847</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7851761</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -3772,80 +3780,80 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Laravel Developer (m/w/d) - AI-First PropTech</t>
+          <t>Staff Machine Learning Systems Engineer</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>Immovara GmbH</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>Korntal-Münchingen</t>
-        </is>
-      </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>berufserfahren</t>
-        </is>
-      </c>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr"/>
       <c r="F78" s="4" t="inlineStr"/>
-      <c r="G78" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Software Development</t>
-        </is>
-      </c>
+      <c r="G78" s="4" t="inlineStr"/>
       <c r="H78" s="4" t="inlineStr"/>
       <c r="I78" s="4" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J78" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/immovara-gmbh/laravel-developer-ai-first-proptech-korntal-munchingen-239743</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7731788</t>
         </is>
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning (ML) Engineer - Applied</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr"/>
+          <t>Werkstudent:in KI Marketing (m/w/d)</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>laria.ai</t>
+        </is>
+      </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr"/>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Working student, berufseinstieg</t>
+        </is>
+      </c>
       <c r="F79" s="2" t="inlineStr"/>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>machine learning, artificial intelligence, python, cplusplus, startup</t>
+          <t>Remote, Online Marketing</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr"/>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>WorkingNomads</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>https://www.workingnomads.com/job/go/1578553/</t>
+          <t>https://www.arbeitnow.com/jobs/companies/lariaai/werkstudentin-ki-marketing-berlin-9847</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -3857,36 +3865,44 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Backend Engineer, AI Security</t>
+          <t>Laravel Developer (m/w/d) - AI-First PropTech</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Immovara GmbH</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>New York, San Francisco, Seattle, or Remote (US/Canada)</t>
-        </is>
-      </c>
-      <c r="E80" s="4" t="inlineStr"/>
+          <t>Korntal-Münchingen</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
       <c r="F80" s="4" t="inlineStr"/>
-      <c r="G80" s="4" t="inlineStr"/>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Software Development</t>
+        </is>
+      </c>
       <c r="H80" s="4" t="inlineStr"/>
       <c r="I80" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J80" s="5" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7826765</t>
+          <t>https://www.arbeitnow.com/jobs/companies/immovara-gmbh/laravel-developer-ai-first-proptech-korntal-munchingen-239743</t>
         </is>
       </c>
       <c r="K80" s="4" t="inlineStr">
@@ -3903,31 +3919,31 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Backend Engineer, Core Tech, Canada</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
+          <t>Machine Learning (ML) Engineer - Applied</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr"/>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Toronto, CAN-Remote</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr"/>
       <c r="F81" s="2" t="inlineStr"/>
-      <c r="G81" s="2" t="inlineStr"/>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>machine learning, artificial intelligence, python, cplusplus, startup</t>
+        </is>
+      </c>
       <c r="H81" s="2" t="inlineStr"/>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WorkingNomads</t>
         </is>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=6567253</t>
+          <t>https://www.workingnomads.com/job/go/1578553/</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -3944,7 +3960,7 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Backend Engineer, Core Technology</t>
+          <t>Backend Engineer, AI Security</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -3954,7 +3970,7 @@
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>US-Remote, Chicago</t>
+          <t>New York, San Francisco, Seattle, or Remote (US/Canada)</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr"/>
@@ -3968,7 +3984,7 @@
       </c>
       <c r="J82" s="5" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=6042172</t>
+          <t>https://stripe.com/jobs/search?gh_jid=7826765</t>
         </is>
       </c>
       <c r="K82" s="4" t="inlineStr">
@@ -3985,7 +4001,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Backend Engineer, Developer Experience &amp; Product Platform</t>
+          <t>Backend Engineer, Core Tech, Canada</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -3995,7 +4011,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Toronto Canada, San Francisco, Remote in US, Remote in Canada</t>
+          <t>Toronto, CAN-Remote</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr"/>
@@ -4009,7 +4025,7 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7292520</t>
+          <t>https://stripe.com/jobs/search?gh_jid=6567253</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -4026,7 +4042,7 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Commercial Counsel, Crypto</t>
+          <t>Backend Engineer, Core Technology</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -4036,7 +4052,7 @@
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>New York City, Seattle, San Francisco, Chicago, Atlanta, US-Remote</t>
+          <t>US-Remote, Chicago</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr"/>
@@ -4050,7 +4066,7 @@
       </c>
       <c r="J84" s="5" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7392188</t>
+          <t>https://stripe.com/jobs/search?gh_jid=6042172</t>
         </is>
       </c>
       <c r="K84" s="4" t="inlineStr">
@@ -4067,7 +4083,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Fullstack Engineer, Privy</t>
+          <t>Backend Engineer, Developer Experience &amp; Product Platform</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -4077,7 +4093,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">NYC-Privy, US-Remote </t>
+          <t>Toronto Canada, San Francisco, Remote in US, Remote in Canada</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr"/>
@@ -4091,7 +4107,7 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7091959</t>
+          <t>https://stripe.com/jobs/search?gh_jid=7292520</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -4108,7 +4124,7 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Stripe Assistant</t>
+          <t>Commercial Counsel, Crypto</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -4118,7 +4134,7 @@
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Seattle; San Francisco; New York City; Remote</t>
+          <t>New York City, Seattle, San Francisco, Chicago, Atlanta, US-Remote</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr"/>
@@ -4132,7 +4148,7 @@
       </c>
       <c r="J86" s="5" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7629052</t>
+          <t>https://stripe.com/jobs/search?gh_jid=7392188</t>
         </is>
       </c>
       <c r="K86" s="4" t="inlineStr">
@@ -4149,17 +4165,17 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning Manager, Feed Relevance</t>
+          <t>Fullstack Engineer, Privy</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t xml:space="preserve">NYC-Privy, US-Remote </t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr"/>
@@ -4173,7 +4189,7 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7802495</t>
+          <t>https://stripe.com/jobs/search?gh_jid=7091959</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -4190,17 +4206,17 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, GenAI Security</t>
+          <t>Machine Learning Engineer, Stripe Assistant</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Seattle; San Francisco; New York City; Remote</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr"/>
@@ -4214,7 +4230,7 @@
       </c>
       <c r="J88" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7891887</t>
+          <t>https://stripe.com/jobs/search?gh_jid=7629052</t>
         </is>
       </c>
       <c r="K88" s="4" t="inlineStr">
@@ -4231,7 +4247,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Senior Staff Machine Learning Engineer, Feed Relevance</t>
+          <t>Machine Learning Manager, Feed Relevance</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -4255,7 +4271,7 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7791994</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7802495</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -4272,7 +4288,7 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Senior Staff Machine Learning Engineer, ML Understanding</t>
+          <t>Senior Machine Learning Engineer, GenAI Security</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
@@ -4296,7 +4312,7 @@
       </c>
       <c r="J90" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7847148</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7891887</t>
         </is>
       </c>
       <c r="K90" s="4" t="inlineStr">
@@ -4313,7 +4329,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, Ads Measurement Modeling</t>
+          <t>Senior Staff Machine Learning Engineer, Feed Relevance</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -4337,7 +4353,7 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7890096</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7791994</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -4354,7 +4370,7 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, AI Serving</t>
+          <t>Senior Staff Machine Learning Engineer, ML Understanding</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -4378,7 +4394,7 @@
       </c>
       <c r="J92" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7886459</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7847148</t>
         </is>
       </c>
       <c r="K92" s="4" t="inlineStr">
@@ -4395,17 +4411,17 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (L3) - Full Stack</t>
+          <t>Staff Machine Learning Engineer, Ads Measurement Modeling</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Remote - US</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr"/>
@@ -4419,139 +4435,127 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7890096</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>Staff Machine Learning Engineer, AI Serving</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr"/>
+      <c r="F94" s="4" t="inlineStr"/>
+      <c r="G94" s="4" t="inlineStr"/>
+      <c r="H94" s="4" t="inlineStr"/>
+      <c r="I94" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J94" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7886459</t>
+        </is>
+      </c>
+      <c r="K94" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (L3) - Full Stack</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Remote - US</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr"/>
+      <c r="F95" s="2" t="inlineStr"/>
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr"/>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
           <t>https://job-boards.greenhouse.io/twilio/jobs/7738955</t>
         </is>
       </c>
-      <c r="K93" s="2" t="inlineStr">
+      <c r="K95" s="2" t="inlineStr">
         <is>
           <t>2026-05-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>AI Developer (Claude + AWS)</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>Datavent</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>Hamburg</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr"/>
-      <c r="G94" s="2" t="inlineStr">
-        <is>
-          <t>Remote, Software Development</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr"/>
-      <c r="I94" s="2" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J94" s="3" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/datavent/ai-developer-claude-aws-hamburg-22354</t>
-        </is>
-      </c>
-      <c r="K94" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="B95" s="4" t="inlineStr">
-        <is>
-          <t>Python Software Engineer, Backend &amp; APIs - Remote</t>
-        </is>
-      </c>
-      <c r="C95" s="4" t="inlineStr">
-        <is>
-          <t>dexter health</t>
-        </is>
-      </c>
-      <c r="D95" s="4" t="inlineStr">
-        <is>
-          <t>Cologne</t>
-        </is>
-      </c>
-      <c r="E95" s="4" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
-      <c r="F95" s="4" t="inlineStr"/>
-      <c r="G95" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Software Development</t>
-        </is>
-      </c>
-      <c r="H95" s="4" t="inlineStr"/>
-      <c r="I95" s="4" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J95" s="5" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/python-software-engineer-backend-apis-remote-cologne-284750</t>
-        </is>
-      </c>
-      <c r="K95" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Fullstack Developer (m/w/d) REMOTE //  UX / Python / Vue.js</t>
+          <t>AI Developer (Claude + AWS)</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Pont Connects e.K.</t>
+          <t>Datavent</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Düsseldorf</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr"/>
+          <t>Hamburg</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
       <c r="F96" s="2" t="inlineStr"/>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Remote, IT</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr"/>
@@ -4562,146 +4566,154 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
+          <t>https://www.arbeitnow.com/jobs/companies/datavent/ai-developer-claude-aws-hamburg-22354</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>Python Software Engineer, Backend &amp; APIs - Remote</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>dexter health</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>Cologne</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr"/>
+      <c r="G97" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Software Development</t>
+        </is>
+      </c>
+      <c r="H97" s="4" t="inlineStr"/>
+      <c r="I97" s="4" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J97" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/python-software-engineer-backend-apis-remote-cologne-284750</t>
+        </is>
+      </c>
+      <c r="K97" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Fullstack Developer (m/w/d) REMOTE //  UX / Python / Vue.js</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Pont Connects e.K.</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Düsseldorf</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr"/>
+      <c r="F98" s="2" t="inlineStr"/>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>Remote, IT</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr"/>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
           <t>https://www.arbeitnow.com/jobs/companies/pont-connects-ek/fullstack-developer-remote-ux-python-vuejs-dusseldorf-371903</t>
         </is>
       </c>
-      <c r="K96" s="2" t="inlineStr">
+      <c r="K98" s="2" t="inlineStr">
         <is>
           <t>2026-05-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>Lemon.io</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>Americas, Europe, Asia, Oceania</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t>full_time</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>Devops</t>
-        </is>
-      </c>
-      <c r="G97" s="2" t="inlineStr">
-        <is>
-          <t>.Net, android, AWS, azure, C, C#, C++, data science, golang, ios, java, javascript, kubernetes, node.js, php, python, react, ruby/rails, shopify, sql, video, blockchain, AI/ML, automation, react native, rust, unity, spring, data analysis, laravel, solidity, flask, Typescript , terraform, angular , GCP, data engineering, Symfony, startup, marketplace, next.js</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr"/>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>Remotive</t>
-        </is>
-      </c>
-      <c r="J97" s="3" t="inlineStr">
-        <is>
-          <t>https://remotive.com/remote-jobs/devops/senior-devops-engineer-2090002</t>
-        </is>
-      </c>
-      <c r="K97" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="B98" s="4" t="inlineStr">
-        <is>
-          <t>M&amp;A Research Analyst</t>
-        </is>
-      </c>
-      <c r="C98" s="4" t="inlineStr">
-        <is>
-          <t>EquiMatch GmbH</t>
-        </is>
-      </c>
-      <c r="D98" s="4" t="inlineStr">
-        <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E98" s="4" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
-      <c r="F98" s="4" t="inlineStr"/>
-      <c r="G98" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Mergers &amp; Acquisitions</t>
-        </is>
-      </c>
-      <c r="H98" s="4" t="inlineStr"/>
-      <c r="I98" s="4" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J98" s="5" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/equimatch-gmbh/ma-research-analyst-berlin-498635</t>
-        </is>
-      </c>
-      <c r="K98" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Xsolla: Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr"/>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Lemon.io</t>
+        </is>
+      </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr"/>
-      <c r="F99" s="2" t="inlineStr"/>
-      <c r="G99" s="2" t="inlineStr"/>
+          <t>Americas, Europe, Asia, Oceania</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>full_time</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>Devops</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>.Net, android, AWS, azure, C, C#, C++, data science, golang, ios, java, javascript, kubernetes, node.js, php, python, react, ruby/rails, shopify, sql, video, blockchain, AI/ML, automation, react native, rust, unity, spring, data analysis, laravel, solidity, flask, Typescript , terraform, angular , GCP, data engineering, Symfony, startup, marketplace, next.js</t>
+        </is>
+      </c>
       <c r="H99" s="2" t="inlineStr"/>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Remotive</t>
         </is>
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/xsolla-full-stack-developer</t>
+          <t>https://remotive.com/remote-jobs/devops/senior-devops-engineer-2090002</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -4713,32 +4725,44 @@
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>Dropbox: Staff Fullstack Product Software Engineer, Dash</t>
-        </is>
-      </c>
-      <c r="C100" s="4" t="inlineStr"/>
+          <t>M&amp;A Research Analyst</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>EquiMatch GmbH</t>
+        </is>
+      </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E100" s="4" t="inlineStr"/>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
       <c r="F100" s="4" t="inlineStr"/>
-      <c r="G100" s="4" t="inlineStr"/>
+      <c r="G100" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Mergers &amp; Acquisitions</t>
+        </is>
+      </c>
       <c r="H100" s="4" t="inlineStr"/>
       <c r="I100" s="4" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J100" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/dropbox-staff-fullstack-product-software-engineer-dash</t>
+          <t>https://www.arbeitnow.com/jobs/companies/equimatch-gmbh/ma-research-analyst-berlin-498635</t>
         </is>
       </c>
       <c r="K100" s="4" t="inlineStr">
@@ -4755,17 +4779,13 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, Ranking and Personalization</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>Reddit</t>
-        </is>
-      </c>
+          <t>Xsolla: Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr"/>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr"/>
@@ -4774,115 +4794,95 @@
       <c r="H101" s="2" t="inlineStr"/>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
+          <t>https://weworkremotely.com/remote-jobs/xsolla-full-stack-developer</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>Dropbox: Staff Fullstack Product Software Engineer, Dash</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr"/>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr"/>
+      <c r="F102" s="4" t="inlineStr"/>
+      <c r="G102" s="4" t="inlineStr"/>
+      <c r="H102" s="4" t="inlineStr"/>
+      <c r="I102" s="4" t="inlineStr">
+        <is>
+          <t>WeWorkRemotely</t>
+        </is>
+      </c>
+      <c r="J102" s="5" t="inlineStr">
+        <is>
+          <t>https://weworkremotely.com/remote-jobs/dropbox-staff-fullstack-product-software-engineer-dash</t>
+        </is>
+      </c>
+      <c r="K102" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Staff Machine Learning Engineer, Ranking and Personalization</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr"/>
+      <c r="F103" s="2" t="inlineStr"/>
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr"/>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
           <t>https://job-boards.greenhouse.io/reddit/jobs/7848689</t>
         </is>
       </c>
-      <c r="K101" s="2" t="inlineStr">
+      <c r="K103" s="2" t="inlineStr">
         <is>
           <t>2026-05-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>Senior Rust Consultant / Engineer (m/w/d)</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>Hackstack GmbH</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>berufserfahren</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="inlineStr"/>
-      <c r="G102" s="2" t="inlineStr">
-        <is>
-          <t>Remote, Consulting, Engineering</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr"/>
-      <c r="I102" s="2" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J102" s="3" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/hackstack-gmbh/senior-rust-consultant-engineer-munich-451602</t>
-        </is>
-      </c>
-      <c r="K102" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="B103" s="4" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer - Remote</t>
-        </is>
-      </c>
-      <c r="C103" s="4" t="inlineStr">
-        <is>
-          <t>dexter health</t>
-        </is>
-      </c>
-      <c r="D103" s="4" t="inlineStr">
-        <is>
-          <t>Cologne</t>
-        </is>
-      </c>
-      <c r="E103" s="4" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
-      <c r="F103" s="4" t="inlineStr"/>
-      <c r="G103" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Development</t>
-        </is>
-      </c>
-      <c r="H103" s="4" t="inlineStr"/>
-      <c r="I103" s="4" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J103" s="5" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/applied-ai-engineer-remote-cologne-2870</t>
-        </is>
-      </c>
-      <c r="K103" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4894,28 +4894,28 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Python Backend Engineer - Remote</t>
+          <t>Senior Rust Consultant / Engineer (m/w/d)</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>dexter health</t>
+          <t>Hackstack GmbH</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Cologne</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>professional / experienced</t>
+          <t>berufserfahren</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr"/>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Remote, Development</t>
+          <t>Remote, Consulting, Engineering</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr"/>
@@ -4926,7 +4926,7 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/python-backend-engineer-remote-cologne-34228</t>
+          <t>https://www.arbeitnow.com/jobs/companies/hackstack-gmbh/senior-rust-consultant-engineer-munich-451602</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>AI Engineer (LLM Products) - Remote</t>
+          <t>Applied AI Engineer - Remote</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="J105" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/ai-engineer-llm-products-remote-cologne-236027</t>
+          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/applied-ai-engineer-remote-cologne-2870</t>
         </is>
       </c>
       <c r="K105" s="4" t="inlineStr">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Backend Python Engineer (APIs, Databases &amp; Cloud) - Remote</t>
+          <t>Python Backend Engineer - Remote</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/backend-python-engineer-apis-databases-cloud-remote-cologne-274767</t>
+          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/python-backend-engineer-remote-cologne-34228</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -5036,32 +5036,44 @@
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Toptal: QA Automation Engineer</t>
-        </is>
-      </c>
-      <c r="C107" s="4" t="inlineStr"/>
+          <t>AI Engineer (LLM Products) - Remote</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>dexter health</t>
+        </is>
+      </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E107" s="4" t="inlineStr"/>
+          <t>Cologne</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
       <c r="F107" s="4" t="inlineStr"/>
-      <c r="G107" s="4" t="inlineStr"/>
+      <c r="G107" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Development</t>
+        </is>
+      </c>
       <c r="H107" s="4" t="inlineStr"/>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J107" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/toptal-qa-automation-engineer-1</t>
+          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/ai-engineer-llm-products-remote-cologne-236027</t>
         </is>
       </c>
       <c r="K107" s="4" t="inlineStr">
@@ -5073,32 +5085,44 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Opensea: Staff Product Designer</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr"/>
+          <t>Backend Python Engineer (APIs, Databases &amp; Cloud) - Remote</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>dexter health</t>
+        </is>
+      </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr"/>
+          <t>Cologne</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
       <c r="F108" s="2" t="inlineStr"/>
-      <c r="G108" s="2" t="inlineStr"/>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>Remote, Development</t>
+        </is>
+      </c>
       <c r="H108" s="2" t="inlineStr"/>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/opensea-staff-product-designer</t>
+          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/backend-python-engineer-apis-databases-cloud-remote-cologne-274767</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -5115,7 +5139,7 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Mutt Data: Devops</t>
+          <t>Toptal: QA Automation Engineer</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr"/>
@@ -5135,7 +5159,7 @@
       </c>
       <c r="J109" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/mutt-data-devops</t>
+          <t>https://weworkremotely.com/remote-jobs/toptal-qa-automation-engineer-1</t>
         </is>
       </c>
       <c r="K109" s="4" t="inlineStr">
@@ -5152,7 +5176,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Holywater: Full-Stack Developer</t>
+          <t>Opensea: Staff Product Designer</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr"/>
@@ -5172,7 +5196,7 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/holywater-full-stack-developer</t>
+          <t>https://weworkremotely.com/remote-jobs/opensea-staff-product-designer</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -5189,7 +5213,7 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Qventus: DevOps Engineer</t>
+          <t>Mutt Data: Devops</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr"/>
@@ -5209,7 +5233,7 @@
       </c>
       <c r="J111" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/qventus-devops-engineer</t>
+          <t>https://weworkremotely.com/remote-jobs/mutt-data-devops</t>
         </is>
       </c>
       <c r="K111" s="4" t="inlineStr">
@@ -5226,7 +5250,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Visualis: Senior Full Stack Developer</t>
+          <t>Holywater: Full-Stack Developer</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr"/>
@@ -5246,7 +5270,7 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/visualis-senior-full-stack-developer</t>
+          <t>https://weworkremotely.com/remote-jobs/holywater-full-stack-developer</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -5263,17 +5287,13 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="C113" s="4" t="inlineStr">
-        <is>
-          <t>GitLab</t>
-        </is>
-      </c>
+          <t>Qventus: DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr"/>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Remote, Bangalore</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr"/>
@@ -5282,12 +5302,12 @@
       <c r="H113" s="4" t="inlineStr"/>
       <c r="I113" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J113" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8517564002</t>
+          <t>https://weworkremotely.com/remote-jobs/qventus-devops-engineer</t>
         </is>
       </c>
       <c r="K113" s="4" t="inlineStr">
@@ -5304,17 +5324,13 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Backend Engineer, Analytics Instrumentation (Golang)</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>GitLab</t>
-        </is>
-      </c>
+          <t>Visualis: Senior Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr"/>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr"/>
@@ -5323,12 +5339,12 @@
       <c r="H114" s="2" t="inlineStr"/>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481922002</t>
+          <t>https://weworkremotely.com/remote-jobs/visualis-senior-full-stack-developer</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -5345,7 +5361,7 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Backend Engineer, Analytics Instrumentation (Golang)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
@@ -5355,7 +5371,7 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, Bangalore</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr"/>
@@ -5369,7 +5385,7 @@
       </c>
       <c r="J115" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481929002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8517564002</t>
         </is>
       </c>
       <c r="K115" s="4" t="inlineStr">
@@ -5386,7 +5402,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Backend Engineer, Knowledge Graph (Rust)</t>
+          <t>Backend Engineer, Analytics Instrumentation (Golang)</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -5396,7 +5412,7 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, US</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr"/>
@@ -5410,7 +5426,7 @@
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8437754002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481922002</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -5427,7 +5443,7 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Backend Engineer, Knowledge Graph (Rust)</t>
+          <t>Backend Engineer, Analytics Instrumentation (Golang)</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
@@ -5451,7 +5467,7 @@
       </c>
       <c r="J117" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481958002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481929002</t>
         </is>
       </c>
       <c r="K117" s="4" t="inlineStr">
@@ -5468,7 +5484,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Intermediate Backend Engineer (C), Tenant Scale: Git</t>
+          <t>Backend Engineer, Knowledge Graph (Rust)</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -5478,7 +5494,7 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, Canada; Remote, US</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr"/>
@@ -5492,7 +5508,7 @@
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8497793002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8437754002</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -5509,7 +5525,7 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>Intermediate Backend Engineer, Gitlab Delivery: Upgrades</t>
+          <t>Backend Engineer, Knowledge Graph (Rust)</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
@@ -5533,7 +5549,7 @@
       </c>
       <c r="J119" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8463951002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481958002</t>
         </is>
       </c>
       <c r="K119" s="4" t="inlineStr">
@@ -5550,7 +5566,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Intermediate Backend Engineer, SRM: Security Platform Management</t>
+          <t>Intermediate Backend Engineer (C), Tenant Scale: Git</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -5560,7 +5576,7 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr"/>
@@ -5574,7 +5590,7 @@
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8443325002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8497793002</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -5591,7 +5607,7 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>Intermediate Backend Engineer, SSCS: AI Governance</t>
+          <t>Intermediate Backend Engineer, Gitlab Delivery: Upgrades</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
@@ -5615,7 +5631,7 @@
       </c>
       <c r="J121" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480551002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8463951002</t>
         </is>
       </c>
       <c r="K121" s="4" t="inlineStr">
@@ -5632,7 +5648,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Intermediate Backend Engineer,  SSCS: Supply Chain</t>
+          <t>Intermediate Backend Engineer, SRM: Security Platform Management</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -5642,7 +5658,7 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr"/>
@@ -5656,7 +5672,7 @@
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480565002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8443325002</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -5673,7 +5689,7 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Intermediate Backend Engineer, SSCS: AI Governance</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
@@ -5683,7 +5699,7 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Remote, EMEA</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr"/>
@@ -5697,7 +5713,7 @@
       </c>
       <c r="J123" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8464072002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480551002</t>
         </is>
       </c>
       <c r="K123" s="4" t="inlineStr">
@@ -5714,7 +5730,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (AI), Pipeline Execution</t>
+          <t>Intermediate Backend Engineer,  SSCS: Supply Chain</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -5724,7 +5740,7 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US-Southeast</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr"/>
@@ -5738,7 +5754,7 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8514945002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480565002</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -5755,7 +5771,7 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Analytics Instrumentation (Golang)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
@@ -5765,7 +5781,7 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, US</t>
+          <t>Remote, EMEA</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr"/>
@@ -5779,7 +5795,7 @@
       </c>
       <c r="J125" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8451512002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8464072002</t>
         </is>
       </c>
       <c r="K125" s="4" t="inlineStr">
@@ -5796,7 +5812,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (C), Tenant Scale: Git</t>
+          <t>Senior Backend Engineer (AI), Pipeline Execution</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -5806,7 +5822,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US-Southeast</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr"/>
@@ -5820,7 +5836,7 @@
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8497791002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8514945002</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -5837,7 +5853,7 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Gitlab Delivery: Runway (Platform Engineering)</t>
+          <t>Senior Backend Engineer, Analytics Instrumentation (Golang)</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
@@ -5847,7 +5863,7 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Remote, Australia; Remote, India; Remote, Ireland; Remote, Japan; Remote, Netherlands; Remote, Singapore; Remote, United Kingdom</t>
+          <t>Remote, Canada; Remote, US</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr"/>
@@ -5861,7 +5877,7 @@
       </c>
       <c r="J127" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8324132002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8451512002</t>
         </is>
       </c>
       <c r="K127" s="4" t="inlineStr">
@@ -5878,7 +5894,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Gitlab Delivery: Upgrades</t>
+          <t>Senior Backend Engineer (C), Tenant Scale: Git</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -5902,7 +5918,7 @@
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8463933002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8497791002</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -5919,7 +5935,7 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer(Go), Continuous Delivery</t>
+          <t>Senior Backend Engineer, Gitlab Delivery: Runway (Platform Engineering)</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
@@ -5929,7 +5945,7 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, Australia; Remote, India; Remote, Ireland; Remote, Japan; Remote, Netherlands; Remote, Singapore; Remote, United Kingdom</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr"/>
@@ -5943,7 +5959,7 @@
       </c>
       <c r="J129" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8488966002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8324132002</t>
         </is>
       </c>
       <c r="K129" s="4" t="inlineStr">
@@ -5960,7 +5976,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer(Golang),Software Supply Chain Security: Auth Infrastructure</t>
+          <t>Senior Backend Engineer, Gitlab Delivery: Upgrades</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -5970,7 +5986,7 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Remote, Americas; Remote, APAC; Remote, Canada</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr"/>
@@ -5984,7 +6000,7 @@
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8157520002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8463933002</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
@@ -6001,7 +6017,7 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (RoR), AST: Secret Detection</t>
+          <t>Senior Backend Engineer(Go), Continuous Delivery</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
@@ -6011,7 +6027,7 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr"/>
@@ -6025,7 +6041,7 @@
       </c>
       <c r="J131" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8432262002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8488966002</t>
         </is>
       </c>
       <c r="K131" s="4" t="inlineStr">
@@ -6042,7 +6058,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (RoR/Go), SSCS: Pipeline Security</t>
+          <t>Senior Backend Engineer(Golang),Software Supply Chain Security: Auth Infrastructure</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -6052,7 +6068,7 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
+          <t>Remote, Americas; Remote, APAC; Remote, Canada</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr"/>
@@ -6066,7 +6082,7 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8432221002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8157520002</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -6083,7 +6099,7 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (RoR), SSCS: Authorization</t>
+          <t>Senior Backend Engineer (RoR), AST: Secret Detection</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
@@ -6093,7 +6109,7 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
+          <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr"/>
@@ -6107,7 +6123,7 @@
       </c>
       <c r="J133" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8457315002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8432262002</t>
         </is>
       </c>
       <c r="K133" s="4" t="inlineStr">
@@ -6124,7 +6140,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby or Golang), Tenant Scale; Cells Infrastructure</t>
+          <t>Senior Backend Engineer (RoR/Go), SSCS: Pipeline Security</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -6134,7 +6150,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Remote, APAC; Remote, Canada; Remote, EMEA; Remote, US</t>
+          <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr"/>
@@ -6148,7 +6164,7 @@
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8437148002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8432221002</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
@@ -6165,7 +6181,7 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, SSCS: AI Governance</t>
+          <t>Senior Backend Engineer (RoR), SSCS: Authorization</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
@@ -6175,7 +6191,7 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr"/>
@@ -6189,7 +6205,7 @@
       </c>
       <c r="J135" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480544002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8457315002</t>
         </is>
       </c>
       <c r="K135" s="4" t="inlineStr">
@@ -6206,7 +6222,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer,  SSCS: Supply Chain</t>
+          <t>Senior Backend Engineer (Ruby or Golang), Tenant Scale; Cells Infrastructure</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -6216,7 +6232,7 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, APAC; Remote, Canada; Remote, EMEA; Remote, US</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr"/>
@@ -6230,7 +6246,7 @@
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480580002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8437148002</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -6247,7 +6263,7 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Senior Fullstack Engineer (TypeScript), AI Engineering: Editor Extensions</t>
+          <t>Senior Backend Engineer, SSCS: AI Governance</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
@@ -6257,7 +6273,7 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>Remote, APAC; Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US-Southeast</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr"/>
@@ -6271,7 +6287,7 @@
       </c>
       <c r="J137" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8452278002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480544002</t>
         </is>
       </c>
       <c r="K137" s="4" t="inlineStr">
@@ -6288,7 +6304,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer, Analytics Instrumentation (Golang)</t>
+          <t>Senior Backend Engineer,  SSCS: Supply Chain</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -6312,7 +6328,7 @@
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8508027002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480580002</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
@@ -6329,7 +6345,7 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer, AST: Composition Analysis</t>
+          <t>Senior Fullstack Engineer (TypeScript), AI Engineering: Editor Extensions</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
@@ -6339,7 +6355,7 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Remote, Australia; Remote, Canada; Remote, India; Remote, Ireland; Remote, Israel; Remote, Japan; Remote, Netherlands; Remote, New Zealand; Remote, United Kingdom; Remote, US</t>
+          <t>Remote, APAC; Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US-Southeast</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr"/>
@@ -6353,7 +6369,7 @@
       </c>
       <c r="J139" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8478364002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8452278002</t>
         </is>
       </c>
       <c r="K139" s="4" t="inlineStr">
@@ -6370,7 +6386,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer, Developer Experience</t>
+          <t>Staff Backend Engineer, Analytics Instrumentation (Golang)</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -6380,7 +6396,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, United Kingdom; Remote, US</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr"/>
@@ -6394,7 +6410,7 @@
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8490477002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8508027002</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -6411,7 +6427,7 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer, Gitlab Delivery: Upgrades</t>
+          <t>Staff Backend Engineer, AST: Composition Analysis</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
@@ -6421,7 +6437,7 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, Australia; Remote, Canada; Remote, India; Remote, Ireland; Remote, Israel; Remote, Japan; Remote, Netherlands; Remote, New Zealand; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr"/>
@@ -6435,7 +6451,7 @@
       </c>
       <c r="J141" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8463922002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8478364002</t>
         </is>
       </c>
       <c r="K141" s="4" t="inlineStr">
@@ -6452,7 +6468,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer (Go), Continuous Delivery</t>
+          <t>Staff Backend Engineer, Developer Experience</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -6462,7 +6478,7 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, Canada; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr"/>
@@ -6476,7 +6492,7 @@
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8488961002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8490477002</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -6493,7 +6509,7 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer (Go), Software Supply Chain Security: Secrets Management</t>
+          <t>Staff Backend Engineer, Gitlab Delivery: Upgrades</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
@@ -6503,7 +6519,7 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr"/>
@@ -6517,7 +6533,7 @@
       </c>
       <c r="J143" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8432235002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8463922002</t>
         </is>
       </c>
       <c r="K143" s="4" t="inlineStr">
@@ -6534,7 +6550,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer, Knowledge Graph (Rust)</t>
+          <t>Staff Backend Engineer (Go), Continuous Delivery</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -6558,7 +6574,7 @@
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481945002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8488961002</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -6575,7 +6591,7 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer,  Software Supply Chain Security</t>
+          <t>Staff Backend Engineer (Go), Software Supply Chain Security: Secrets Management</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
@@ -6585,7 +6601,7 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr"/>
@@ -6599,7 +6615,7 @@
       </c>
       <c r="J145" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480559002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8432235002</t>
         </is>
       </c>
       <c r="K145" s="4" t="inlineStr">
@@ -6616,7 +6632,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer, SSCS: AI Governance</t>
+          <t>Staff Backend Engineer, Knowledge Graph (Rust)</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -6640,7 +6656,7 @@
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480531002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481945002</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -6657,7 +6673,7 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>Staff Backend (Python) Engineer, AI Engineering:Duo Chat</t>
+          <t>Staff Backend Engineer,  Software Supply Chain Security</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
@@ -6667,7 +6683,7 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>Remote, Americas; Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr"/>
@@ -6681,7 +6697,7 @@
       </c>
       <c r="J147" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8450446002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480559002</t>
         </is>
       </c>
       <c r="K147" s="4" t="inlineStr">
@@ -6698,17 +6714,17 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Senior Full Stack Product Software Engineer</t>
+          <t>Staff Backend Engineer, SSCS: AI Governance</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Dropbox</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Remote - Poland</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr"/>
@@ -6722,126 +6738,94 @@
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480531002</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t>Staff Backend (Python) Engineer, AI Engineering:Duo Chat</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>GitLab</t>
+        </is>
+      </c>
+      <c r="D149" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Americas; Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom</t>
+        </is>
+      </c>
+      <c r="E149" s="4" t="inlineStr"/>
+      <c r="F149" s="4" t="inlineStr"/>
+      <c r="G149" s="4" t="inlineStr"/>
+      <c r="H149" s="4" t="inlineStr"/>
+      <c r="I149" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J149" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8450446002</t>
+        </is>
+      </c>
+      <c r="K149" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Product Software Engineer</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>Dropbox</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Remote - Poland</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr"/>
+      <c r="F150" s="2" t="inlineStr"/>
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr"/>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J150" s="3" t="inlineStr">
+        <is>
           <t>https://jobs.dropbox.com/listing/6449719?gh_jid=6449719</t>
         </is>
       </c>
-      <c r="K148" s="2" t="inlineStr">
+      <c r="K150" s="2" t="inlineStr">
         <is>
           <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>Dry Ground AI</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
-        <is>
-          <t>Brazil, Colombia, Philippines</t>
-        </is>
-      </c>
-      <c r="E149" s="2" t="inlineStr">
-        <is>
-          <t>full_time</t>
-        </is>
-      </c>
-      <c r="F149" s="2" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence</t>
-        </is>
-      </c>
-      <c r="G149" s="2" t="inlineStr">
-        <is>
-          <t>api, cloud, fullstack, python, AI/ML, automation, research, CI/CD, TensorFlow, spark, NLP, CMS, Pytorch, REST</t>
-        </is>
-      </c>
-      <c r="H149" s="2" t="inlineStr">
-        <is>
-          <t>$40- $60k</t>
-        </is>
-      </c>
-      <c r="I149" s="2" t="inlineStr">
-        <is>
-          <t>Remotive</t>
-        </is>
-      </c>
-      <c r="J149" s="3" t="inlineStr">
-        <is>
-          <t>https://remotive.com/remote-jobs/artificial-intelligence/ai-engineer-2089958</t>
-        </is>
-      </c>
-      <c r="K149" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B150" s="4" t="inlineStr">
-        <is>
-          <t>Senior Independent AI Engineer / Architect</t>
-        </is>
-      </c>
-      <c r="C150" s="4" t="inlineStr">
-        <is>
-          <t>A.Team</t>
-        </is>
-      </c>
-      <c r="D150" s="4" t="inlineStr">
-        <is>
-          <t>Americas, Europe, Israel</t>
-        </is>
-      </c>
-      <c r="E150" s="4" t="inlineStr">
-        <is>
-          <t>contract</t>
-        </is>
-      </c>
-      <c r="F150" s="4" t="inlineStr">
-        <is>
-          <t>Software Development</t>
-        </is>
-      </c>
-      <c r="G150" s="4" t="inlineStr">
-        <is>
-          <t>go, UI/UX, wordpress, chat, apple, testing, catalyst</t>
-        </is>
-      </c>
-      <c r="H150" s="4" t="inlineStr">
-        <is>
-          <t>$120 - $170 /hour</t>
-        </is>
-      </c>
-      <c r="I150" s="4" t="inlineStr">
-        <is>
-          <t>Remotive</t>
-        </is>
-      </c>
-      <c r="J150" s="5" t="inlineStr">
-        <is>
-          <t>https://remotive.com/remote-jobs/software-development/senior-independent-ai-engineer-architect-1919266</t>
-        </is>
-      </c>
-      <c r="K150" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6853,37 +6837,37 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>Senior Independent Software Developer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>A.Team</t>
+          <t>Dry Ground AI</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>Americas, Europe, Israel</t>
+          <t>Brazil, Colombia, Philippines</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>contract</t>
+          <t>full_time</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>Software Development</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>go, wordpress, chat, apple, testing, catalyst</t>
+          <t>api, cloud, fullstack, python, AI/ML, automation, research, CI/CD, TensorFlow, spark, NLP, CMS, Pytorch, REST</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>$90 - $150 /hour</t>
+          <t>$40- $60k</t>
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr">
@@ -6893,7 +6877,7 @@
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
-          <t>https://remotive.com/remote-jobs/software-development/senior-independent-software-developer-1919265</t>
+          <t>https://remotive.com/remote-jobs/artificial-intelligence/ai-engineer-2089958</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
@@ -6910,17 +6894,17 @@
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>Senior Full-stack React Developer</t>
+          <t>Senior Independent AI Engineer / Architect</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>Lemon.io</t>
+          <t>A.Team</t>
         </is>
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>Americas, Europe, Asia, Oceania</t>
+          <t>Americas, Europe, Israel</t>
         </is>
       </c>
       <c r="E152" s="4" t="inlineStr">
@@ -6935,10 +6919,14 @@
       </c>
       <c r="G152" s="4" t="inlineStr">
         <is>
-          <t>.Net, android, AWS, azure, backend, C, C#, C++, data science, fullstack, golang, ios, java, javascript, node.js, php, python, react, react js, ruby/rails, shopify, video, blockchain, AI/ML, react native, rust, unity, spring, data analysis, laravel, solidity, flask, Typescript , angular , GCP, data engineering, Symfony, startup, marketplace, next.js</t>
-        </is>
-      </c>
-      <c r="H152" s="4" t="inlineStr"/>
+          <t>go, UI/UX, wordpress, chat, apple, testing, catalyst</t>
+        </is>
+      </c>
+      <c r="H152" s="4" t="inlineStr">
+        <is>
+          <t>$120 - $170 /hour</t>
+        </is>
+      </c>
       <c r="I152" s="4" t="inlineStr">
         <is>
           <t>Remotive</t>
@@ -6946,7 +6934,7 @@
       </c>
       <c r="J152" s="5" t="inlineStr">
         <is>
-          <t>https://remotive.com/remote-jobs/software-development/senior-full-stack-react-developer-2088711</t>
+          <t>https://remotive.com/remote-jobs/software-development/senior-independent-ai-engineer-architect-1919266</t>
         </is>
       </c>
       <c r="K152" s="4" t="inlineStr">
@@ -6963,22 +6951,22 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>Tech Lead Full-Stack Rails Engineer</t>
+          <t>Senior Independent Software Developer</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>Mitre Media</t>
+          <t>A.Team</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>USA, Canada, USA timezones</t>
+          <t>Americas, Europe, Israel</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>full_time</t>
+          <t>contract</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
@@ -6988,12 +6976,12 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>api, CSS, docker, elasticsearch, fullstack, html, javascript, kubernetes, postgresql, react, ror, ruby/rails, AI/ML, CAD, advertising, Redis, ES6, web applications, MySQL, NLP, fintech, Micro services, github, system architecture</t>
+          <t>go, wordpress, chat, apple, testing, catalyst</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>$170k - $200k</t>
+          <t>$90 - $150 /hour</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr">
@@ -7003,7 +6991,7 @@
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
-          <t>https://remotive.com/remote-jobs/software-development/tech-lead-full-stack-rails-engineer-2069746</t>
+          <t>https://remotive.com/remote-jobs/software-development/senior-independent-software-developer-1919265</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -7020,17 +7008,17 @@
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>Senior Frontend Developer</t>
+          <t>Senior Full-stack React Developer</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>Sanctuary Computer</t>
+          <t>Lemon.io</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>LATAM, Asia</t>
+          <t>Americas, Europe, Asia, Oceania</t>
         </is>
       </c>
       <c r="E154" s="4" t="inlineStr">
@@ -7045,14 +7033,10 @@
       </c>
       <c r="G154" s="4" t="inlineStr">
         <is>
-          <t>api, backend, CSS, ecommerce, frontend, fullstack, graphql, postgresql, redux, security, seo, shopify, open source, paas, product management, documentation, mentoring, Typescript , Redis, web applications, cypress, data visualization, firebase, IoT, engineering management, runtime, responsive, prismic, testing, next.js, CMS, jest, REST, web sockets, performance optimization</t>
-        </is>
-      </c>
-      <c r="H154" s="4" t="inlineStr">
-        <is>
-          <t>$80k - $120k</t>
-        </is>
-      </c>
+          <t>.Net, android, AWS, azure, backend, C, C#, C++, data science, fullstack, golang, ios, java, javascript, node.js, php, python, react, react js, ruby/rails, shopify, video, blockchain, AI/ML, react native, rust, unity, spring, data analysis, laravel, solidity, flask, Typescript , angular , GCP, data engineering, Symfony, startup, marketplace, next.js</t>
+        </is>
+      </c>
+      <c r="H154" s="4" t="inlineStr"/>
       <c r="I154" s="4" t="inlineStr">
         <is>
           <t>Remotive</t>
@@ -7060,7 +7044,7 @@
       </c>
       <c r="J154" s="5" t="inlineStr">
         <is>
-          <t>https://remotive.com/remote-jobs/software-development/senior-frontend-developer-2088707</t>
+          <t>https://remotive.com/remote-jobs/software-development/senior-full-stack-react-developer-2088711</t>
         </is>
       </c>
       <c r="K154" s="4" t="inlineStr">
@@ -7077,17 +7061,17 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Fullstack Developer (US - ET)</t>
+          <t>Tech Lead Full-Stack Rails Engineer</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>Chooose</t>
+          <t>Mitre Media</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>USA, Canada, USA timezones</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
@@ -7102,10 +7086,14 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>api, azure, fullstack, python, react, saas, AI/ML, project management, documentation, Typescript , computer science, diversity, insurance</t>
-        </is>
-      </c>
-      <c r="H155" s="2" t="inlineStr"/>
+          <t>api, CSS, docker, elasticsearch, fullstack, html, javascript, kubernetes, postgresql, react, ror, ruby/rails, AI/ML, CAD, advertising, Redis, ES6, web applications, MySQL, NLP, fintech, Micro services, github, system architecture</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>$170k - $200k</t>
+        </is>
+      </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
           <t>Remotive</t>
@@ -7113,7 +7101,7 @@
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
-          <t>https://remotive.com/remote-jobs/software-development/fullstack-developer-us-et-2088706</t>
+          <t>https://remotive.com/remote-jobs/software-development/tech-lead-full-stack-rails-engineer-2069746</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -7130,31 +7118,47 @@
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning Manager, Notifications Relevance</t>
+          <t>Senior Frontend Developer</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Sanctuary Computer</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
-        </is>
-      </c>
-      <c r="E156" s="4" t="inlineStr"/>
-      <c r="F156" s="4" t="inlineStr"/>
-      <c r="G156" s="4" t="inlineStr"/>
-      <c r="H156" s="4" t="inlineStr"/>
+          <t>LATAM, Asia</t>
+        </is>
+      </c>
+      <c r="E156" s="4" t="inlineStr">
+        <is>
+          <t>contract</t>
+        </is>
+      </c>
+      <c r="F156" s="4" t="inlineStr">
+        <is>
+          <t>Software Development</t>
+        </is>
+      </c>
+      <c r="G156" s="4" t="inlineStr">
+        <is>
+          <t>api, backend, CSS, ecommerce, frontend, fullstack, graphql, postgresql, redux, security, seo, shopify, open source, paas, product management, documentation, mentoring, Typescript , Redis, web applications, cypress, data visualization, firebase, IoT, engineering management, runtime, responsive, prismic, testing, next.js, CMS, jest, REST, web sockets, performance optimization</t>
+        </is>
+      </c>
+      <c r="H156" s="4" t="inlineStr">
+        <is>
+          <t>$80k - $120k</t>
+        </is>
+      </c>
       <c r="I156" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>Remotive</t>
         </is>
       </c>
       <c r="J156" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7846885</t>
+          <t>https://remotive.com/remote-jobs/software-development/senior-frontend-developer-2088707</t>
         </is>
       </c>
       <c r="K156" s="4" t="inlineStr">
@@ -7171,31 +7175,43 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>Senior Staff ML Engineer, Search &amp; Recommendation</t>
+          <t>Fullstack Developer (US - ET)</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Chooose</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
-        </is>
-      </c>
-      <c r="E157" s="2" t="inlineStr"/>
-      <c r="F157" s="2" t="inlineStr"/>
-      <c r="G157" s="2" t="inlineStr"/>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>full_time</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>Software Development</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>api, azure, fullstack, python, react, saas, AI/ML, project management, documentation, Typescript , computer science, diversity, insurance</t>
+        </is>
+      </c>
       <c r="H157" s="2" t="inlineStr"/>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>Remotive</t>
         </is>
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7833622</t>
+          <t>https://remotive.com/remote-jobs/software-development/fullstack-developer-us-et-2088706</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -7212,17 +7228,17 @@
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Machine Learning Manager, Notifications Relevance</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>Remote - US</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E158" s="4" t="inlineStr"/>
@@ -7236,7 +7252,7 @@
       </c>
       <c r="J158" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7059734</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7846885</t>
         </is>
       </c>
       <c r="K158" s="4" t="inlineStr">
@@ -7253,17 +7269,17 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Staff ML Engineer, Search &amp; Recommendation</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>Remote - US</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr"/>
@@ -7277,7 +7293,7 @@
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7702644</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7833622</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
@@ -7294,7 +7310,7 @@
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>Principal Machine Learning &amp; Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
@@ -7318,7 +7334,7 @@
       </c>
       <c r="J160" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7155492</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7059734</t>
         </is>
       </c>
       <c r="K160" s="4" t="inlineStr">
@@ -7335,7 +7351,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Principal, Product Manager - AI / LLM</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -7359,7 +7375,7 @@
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7619420</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7702644</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
@@ -7376,7 +7392,7 @@
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>Product Engineer (Backend)</t>
+          <t>Principal Machine Learning &amp; Data Engineer</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
@@ -7400,7 +7416,7 @@
       </c>
       <c r="J162" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7671815</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7155492</t>
         </is>
       </c>
       <c r="K162" s="4" t="inlineStr">
@@ -7417,7 +7433,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>Senior Manager, Machine Learning</t>
+          <t>Principal, Product Manager - AI / LLM</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -7441,7 +7457,7 @@
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7066029</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7619420</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
@@ -7458,7 +7474,7 @@
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>Staff Data Scientist</t>
+          <t>Product Engineer (Backend)</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
@@ -7482,7 +7498,7 @@
       </c>
       <c r="J164" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7821458</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7671815</t>
         </is>
       </c>
       <c r="K164" s="4" t="inlineStr">
@@ -7499,7 +7515,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>Staff, Data Scientist (L4) GTM Data Science &amp; Analytics</t>
+          <t>Senior Manager, Machine Learning</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -7523,7 +7539,7 @@
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7851920</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7066029</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
@@ -7540,7 +7556,7 @@
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer</t>
+          <t>Staff Data Scientist</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
@@ -7564,7 +7580,7 @@
       </c>
       <c r="J166" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7061880</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7821458</t>
         </is>
       </c>
       <c r="K166" s="4" t="inlineStr">
@@ -7581,7 +7597,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer (L4)</t>
+          <t>Staff, Data Scientist (L4) GTM Data Science &amp; Analytics</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -7591,7 +7607,7 @@
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>Remote - India</t>
+          <t>Remote - US</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr"/>
@@ -7605,7 +7621,7 @@
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7520997</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7851920</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
@@ -7622,39 +7638,31 @@
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>Senior Python Developer - Django (m/w/d)</t>
+          <t>Staff Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>sync.blue® GmbH</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>Haltern am See</t>
-        </is>
-      </c>
-      <c r="E168" s="4" t="inlineStr">
-        <is>
-          <t>berufserfahren</t>
-        </is>
-      </c>
+          <t>Remote - US</t>
+        </is>
+      </c>
+      <c r="E168" s="4" t="inlineStr"/>
       <c r="F168" s="4" t="inlineStr"/>
-      <c r="G168" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Software Development</t>
-        </is>
-      </c>
+      <c r="G168" s="4" t="inlineStr"/>
       <c r="H168" s="4" t="inlineStr"/>
       <c r="I168" s="4" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J168" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/syncblue-gmbh/senior-python-developer-django-haltern-am-see-16238</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7061880</t>
         </is>
       </c>
       <c r="K168" s="4" t="inlineStr">
@@ -7671,39 +7679,31 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>Freelance Senior AI Product Manager</t>
+          <t>Staff Machine Learning Engineer (L4)</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>nexamind GmbH</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E169" s="2" t="inlineStr">
-        <is>
-          <t>Freelance, professional / experienced</t>
-        </is>
-      </c>
+          <t>Remote - India</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr"/>
       <c r="F169" s="2" t="inlineStr"/>
-      <c r="G169" s="2" t="inlineStr">
-        <is>
-          <t>Remote, Product Management</t>
-        </is>
-      </c>
+      <c r="G169" s="2" t="inlineStr"/>
       <c r="H169" s="2" t="inlineStr"/>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/nexamind-gmbh/freelance-senior-ai-product-manager-berlin-73613</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7520997</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
@@ -7720,17 +7720,17 @@
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>Senior Full-Stack-Entwickler:in React / TypeScript / .NET  100 % Remote, KI-First</t>
+          <t>Senior Python Developer - Django (m/w/d)</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>yourMAIL GmbH</t>
+          <t>sync.blue® GmbH</t>
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Haltern am See</t>
         </is>
       </c>
       <c r="E170" s="4" t="inlineStr">
@@ -7752,7 +7752,7 @@
       </c>
       <c r="J170" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/yourmail-gmbh/senior-full-stack-entwicklerin-react-typescript-net-100-remote-ki-first-berlin-21152</t>
+          <t>https://www.arbeitnow.com/jobs/companies/syncblue-gmbh/senior-python-developer-django-haltern-am-see-16238</t>
         </is>
       </c>
       <c r="K170" s="4" t="inlineStr">
@@ -7769,12 +7769,12 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>Senior Frontend-Entwickler:in React / TypeScript, 100 % Remote, KI-First</t>
+          <t>Freelance Senior AI Product Manager</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>yourMAIL GmbH</t>
+          <t>nexamind GmbH</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
@@ -7784,13 +7784,13 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>berufserfahren</t>
+          <t>Freelance, professional / experienced</t>
         </is>
       </c>
       <c r="F171" s="2" t="inlineStr"/>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>Remote, Software Development</t>
+          <t>Remote, Product Management</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr"/>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/yourmail-gmbh/senior-frontend-entwicklerin-react-typescript-100-remote-ki-first-berlin-288218</t>
+          <t>https://www.arbeitnow.com/jobs/companies/nexamind-gmbh/freelance-senior-ai-product-manager-berlin-73613</t>
         </is>
       </c>
       <c r="K171" s="2" t="inlineStr">
@@ -7818,24 +7818,28 @@
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>Full-Stack Entwickler (m/w/d) - .NET 100% Remote</t>
+          <t>Senior Full-Stack-Entwickler:in React / TypeScript / .NET  100 % Remote, KI-First</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>FNTIO</t>
+          <t>yourMAIL GmbH</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>Frankfurt am Main</t>
-        </is>
-      </c>
-      <c r="E172" s="4" t="inlineStr"/>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="E172" s="4" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
       <c r="F172" s="4" t="inlineStr"/>
       <c r="G172" s="4" t="inlineStr">
         <is>
-          <t>Remote, Consulting, Engineering</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr"/>
@@ -7846,7 +7850,7 @@
       </c>
       <c r="J172" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/fntio/full-stack-entwickler-net-100-remote-frankfurt-am-main-122380</t>
+          <t>https://www.arbeitnow.com/jobs/companies/yourmail-gmbh/senior-full-stack-entwicklerin-react-typescript-net-100-remote-ki-first-berlin-21152</t>
         </is>
       </c>
       <c r="K172" s="4" t="inlineStr">
@@ -7863,12 +7867,12 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Frontend-Entwickler:in React / TypeScript, 100 % Remote, KI-First</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>Phantasma Labs</t>
+          <t>yourMAIL GmbH</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
@@ -7876,11 +7880,15 @@
           <t>Berlin</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr"/>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
       <c r="F173" s="2" t="inlineStr"/>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>Remote, Engineering</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr"/>
@@ -7891,7 +7899,7 @@
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/phantasma-labs/machine-learning-engineer-berlin-303955</t>
+          <t>https://www.arbeitnow.com/jobs/companies/yourmail-gmbh/senior-frontend-entwicklerin-react-typescript-100-remote-ki-first-berlin-288218</t>
         </is>
       </c>
       <c r="K173" s="2" t="inlineStr">
@@ -7908,28 +7916,24 @@
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>Technical Data Manager (m/w/d)</t>
+          <t>Full-Stack Entwickler (m/w/d) - .NET 100% Remote</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>BMF Media Information Technology GmbH</t>
+          <t>FNTIO</t>
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>Augsburg</t>
-        </is>
-      </c>
-      <c r="E174" s="4" t="inlineStr">
-        <is>
-          <t>berufserfahren</t>
-        </is>
-      </c>
+          <t>Frankfurt am Main</t>
+        </is>
+      </c>
+      <c r="E174" s="4" t="inlineStr"/>
       <c r="F174" s="4" t="inlineStr"/>
       <c r="G174" s="4" t="inlineStr">
         <is>
-          <t>Remote, Technical Documentation</t>
+          <t>Remote, Consulting, Engineering</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr"/>
@@ -7940,7 +7944,7 @@
       </c>
       <c r="J174" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/bmf-media-information-technology-gmbh/technical-data-manager-augsburg-42188</t>
+          <t>https://www.arbeitnow.com/jobs/companies/fntio/full-stack-entwickler-net-100-remote-frankfurt-am-main-122380</t>
         </is>
       </c>
       <c r="K174" s="4" t="inlineStr">
@@ -7957,28 +7961,24 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>Data Integration &amp; API Engineer m/w/d - Bi &amp; Data Automation</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>loyos bi GmbH</t>
+          <t>Phantasma Labs</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>Hamburg</t>
-        </is>
-      </c>
-      <c r="E175" s="2" t="inlineStr">
-        <is>
-          <t>berufserfahren</t>
-        </is>
-      </c>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr"/>
       <c r="F175" s="2" t="inlineStr"/>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>Remote, Software Development</t>
+          <t>Remote, Engineering</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr"/>
@@ -7989,7 +7989,7 @@
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/loyos-bi-gmbh/data-integration-api-engineer-bi-data-automation-hamburg-66228</t>
+          <t>https://www.arbeitnow.com/jobs/companies/phantasma-labs/machine-learning-engineer-berlin-303955</t>
         </is>
       </c>
       <c r="K175" s="2" t="inlineStr">
@@ -8006,28 +8006,28 @@
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Technical Data Manager (m/w/d)</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>Coding Partners</t>
+          <t>BMF Media Information Technology GmbH</t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="E176" s="4" t="inlineStr">
         <is>
-          <t>professional / experienced</t>
+          <t>berufserfahren</t>
         </is>
       </c>
       <c r="F176" s="4" t="inlineStr"/>
       <c r="G176" s="4" t="inlineStr">
         <is>
-          <t>Remote, Software Development</t>
+          <t>Remote, Technical Documentation</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr"/>
@@ -8038,7 +8038,7 @@
       </c>
       <c r="J176" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/coding-partners/senior-full-stack-engineer-berlin-391720</t>
+          <t>https://www.arbeitnow.com/jobs/companies/bmf-media-information-technology-gmbh/technical-data-manager-augsburg-42188</t>
         </is>
       </c>
       <c r="K176" s="4" t="inlineStr">
@@ -8055,17 +8055,17 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>Laravel Developer (m/w/d) - AI-First PropTech</t>
+          <t>Data Integration &amp; API Engineer m/w/d - Bi &amp; Data Automation</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>Immovara GmbH</t>
+          <t>loyos bi GmbH</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>Korntal-Münchingen</t>
+          <t>Hamburg</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
@@ -8087,7 +8087,7 @@
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/immovara-gmbh/laravel-developer-ai-first-proptech-korntal-munchingen-471269</t>
+          <t>https://www.arbeitnow.com/jobs/companies/loyos-bi-gmbh/data-integration-api-engineer-bi-data-automation-hamburg-66228</t>
         </is>
       </c>
       <c r="K177" s="2" t="inlineStr">
@@ -8104,22 +8104,22 @@
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>Fullstack Softwareentwickler (m/w/d)</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>TecFox GmbH</t>
+          <t>Coding Partners</t>
         </is>
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>Braunschweig</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="E178" s="4" t="inlineStr">
         <is>
-          <t>berufserfahren</t>
+          <t>professional / experienced</t>
         </is>
       </c>
       <c r="F178" s="4" t="inlineStr"/>
@@ -8136,7 +8136,7 @@
       </c>
       <c r="J178" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/tecfox-gmbh/fullstack-softwareentwickler-braunschweig-405178</t>
+          <t>https://www.arbeitnow.com/jobs/companies/coding-partners/senior-full-stack-engineer-berlin-391720</t>
         </is>
       </c>
       <c r="K178" s="4" t="inlineStr">
@@ -8153,17 +8153,17 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>Frontend Softwareentwickler (m/w/d)</t>
+          <t>Laravel Developer (m/w/d) - AI-First PropTech</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>TecFox GmbH</t>
+          <t>Immovara GmbH</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>Braunschweig</t>
+          <t>Korntal-Münchingen</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
@@ -8185,7 +8185,7 @@
       </c>
       <c r="J179" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/tecfox-gmbh/frontend-softwareentwickler-braunschweig-341792</t>
+          <t>https://www.arbeitnow.com/jobs/companies/immovara-gmbh/laravel-developer-ai-first-proptech-korntal-munchingen-471269</t>
         </is>
       </c>
       <c r="K179" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>Fullstack-Developer*in (m/w/d) Web &amp; AI Automation</t>
+          <t>Fullstack Softwareentwickler (m/w/d)</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>NeoBird Digital</t>
+          <t>TecFox GmbH</t>
         </is>
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>Nuremberg</t>
+          <t>Braunschweig</t>
         </is>
       </c>
       <c r="E180" s="4" t="inlineStr">
@@ -8234,7 +8234,7 @@
       </c>
       <c r="J180" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/neobird-digital/fullstack-developerin-web-ai-automation-nuremberg-157752</t>
+          <t>https://www.arbeitnow.com/jobs/companies/tecfox-gmbh/fullstack-softwareentwickler-braunschweig-405178</t>
         </is>
       </c>
       <c r="K180" s="4" t="inlineStr">
@@ -8251,24 +8251,28 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer / Backend &amp; Frontend - Bootstrapped SaaS Startup (m/w/d) remote in EU</t>
+          <t>Frontend Softwareentwickler (m/w/d)</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>DatAds</t>
+          <t>TecFox GmbH</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>Cologne</t>
-        </is>
-      </c>
-      <c r="E181" s="2" t="inlineStr"/>
+          <t>Braunschweig</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
       <c r="F181" s="2" t="inlineStr"/>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>Remote, IT</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr"/>
@@ -8279,7 +8283,7 @@
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-bootstrapped-saas-startup-remote-in-eu-cologne-82307</t>
+          <t>https://www.arbeitnow.com/jobs/companies/tecfox-gmbh/frontend-softwareentwickler-braunschweig-341792</t>
         </is>
       </c>
       <c r="K181" s="2" t="inlineStr">
@@ -8296,24 +8300,28 @@
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer / Rest APIs / Cloud / TailwindCSS / SaaS Startup (m/w/d) remote in EU</t>
+          <t>Fullstack-Developer*in (m/w/d) Web &amp; AI Automation</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>DatAds</t>
+          <t>NeoBird Digital</t>
         </is>
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>Cologne</t>
-        </is>
-      </c>
-      <c r="E182" s="4" t="inlineStr"/>
+          <t>Nuremberg</t>
+        </is>
+      </c>
+      <c r="E182" s="4" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
       <c r="F182" s="4" t="inlineStr"/>
       <c r="G182" s="4" t="inlineStr">
         <is>
-          <t>Remote, IT</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H182" s="4" t="inlineStr"/>
@@ -8324,7 +8332,7 @@
       </c>
       <c r="J182" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-bootstrapped-saas-startup-remote-in-eu-cologne-38634</t>
+          <t>https://www.arbeitnow.com/jobs/companies/neobird-digital/fullstack-developerin-web-ai-automation-nuremberg-157752</t>
         </is>
       </c>
       <c r="K182" s="4" t="inlineStr">
@@ -8341,7 +8349,7 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer / Node.js / TypeScript / React / Azure - AdTech SaaS Startup (m/w/d) remote</t>
+          <t>Full-Stack Software Engineer / Backend &amp; Frontend - Bootstrapped SaaS Startup (m/w/d) remote in EU</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
@@ -8369,7 +8377,7 @@
       </c>
       <c r="J183" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-adtech-saas-startup-remote-cologne-263746</t>
+          <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-bootstrapped-saas-startup-remote-in-eu-cologne-82307</t>
         </is>
       </c>
       <c r="K183" s="2" t="inlineStr">
@@ -8386,24 +8394,20 @@
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>Senior DevOps / Platform Engineer (f/m/x)</t>
+          <t>Full-Stack Software Engineer / Rest APIs / Cloud / TailwindCSS / SaaS Startup (m/w/d) remote in EU</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>MAIA</t>
+          <t>DatAds</t>
         </is>
       </c>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t>Leipzig</t>
-        </is>
-      </c>
-      <c r="E184" s="4" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
+          <t>Cologne</t>
+        </is>
+      </c>
+      <c r="E184" s="4" t="inlineStr"/>
       <c r="F184" s="4" t="inlineStr"/>
       <c r="G184" s="4" t="inlineStr">
         <is>
@@ -8418,7 +8422,7 @@
       </c>
       <c r="J184" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/maia/senior-devops-platform-engineer-leipzig-388068</t>
+          <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-bootstrapped-saas-startup-remote-in-eu-cologne-38634</t>
         </is>
       </c>
       <c r="K184" s="4" t="inlineStr">
@@ -8430,40 +8434,40 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer AI Infrastructure</t>
+          <t>Full-Stack Software Engineer / Node.js / TypeScript / React / Azure - AdTech SaaS Startup (m/w/d) remote</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>Andromeda Cluster</t>
+          <t>DatAds</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Cologne</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr"/>
       <c r="F185" s="2" t="inlineStr"/>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>design, training, technical, software, code, manager, financial, cloud, management, lead, senior, operations, reliability, go, health, engineer, engineering, linux, digital nomad</t>
+          <t>Remote, IT</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr"/>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-senior-site-reliability-engineer-ai-infrastructure-andromeda-cluster-1131375</t>
+          <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-adtech-saas-startup-remote-cologne-263746</t>
         </is>
       </c>
       <c r="K185" s="2" t="inlineStr">
@@ -8475,40 +8479,44 @@
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>Senior Financial Analyst Digital Assets</t>
+          <t>Senior DevOps / Platform Engineer (f/m/x)</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>Exodus Movement Inc.</t>
+          <t>MAIA</t>
         </is>
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E186" s="4" t="inlineStr"/>
+          <t>Leipzig</t>
+        </is>
+      </c>
+      <c r="E186" s="4" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
       <c r="F186" s="4" t="inlineStr"/>
       <c r="G186" s="4" t="inlineStr">
         <is>
-          <t>analyst, cryptocurrency, support, financial, investment, finance, senior, non tech</t>
+          <t>Remote, IT</t>
         </is>
       </c>
       <c r="H186" s="4" t="inlineStr"/>
       <c r="I186" s="4" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J186" s="5" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-senior-financial-analyst-digital-assets-exodus-movement-inc-1131374</t>
+          <t>https://www.arbeitnow.com/jobs/companies/maia/senior-devops-platform-engineer-leipzig-388068</t>
         </is>
       </c>
       <c r="K186" s="4" t="inlineStr">
@@ -8525,24 +8533,24 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>Front End Full Stack Developer</t>
+          <t>Senior Site Reliability Engineer AI Infrastructure</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>Honor Foods</t>
+          <t>Andromeda Cluster</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>Philadelphia, PA</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr"/>
       <c r="F187" s="2" t="inlineStr"/>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>developer, front-end, ui, code, web, operational, backend, digital nomad</t>
+          <t>design, training, technical, software, code, manager, financial, cloud, management, lead, senior, operations, reliability, go, health, engineer, engineering, linux, digital nomad</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr"/>
@@ -8553,7 +8561,7 @@
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-front-end-full-stack-developer-honor-foods-1131370</t>
+          <t>https://remoteOK.com/remote-jobs/remote-senior-site-reliability-engineer-ai-infrastructure-andromeda-cluster-1131375</t>
         </is>
       </c>
       <c r="K187" s="2" t="inlineStr">
@@ -8570,10 +8578,14 @@
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>Wing Assistant: Full-Stack Developer</t>
-        </is>
-      </c>
-      <c r="C188" s="4" t="inlineStr"/>
+          <t>Senior Financial Analyst Digital Assets</t>
+        </is>
+      </c>
+      <c r="C188" s="4" t="inlineStr">
+        <is>
+          <t>Exodus Movement Inc.</t>
+        </is>
+      </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
           <t>Remote</t>
@@ -8581,16 +8593,20 @@
       </c>
       <c r="E188" s="4" t="inlineStr"/>
       <c r="F188" s="4" t="inlineStr"/>
-      <c r="G188" s="4" t="inlineStr"/>
+      <c r="G188" s="4" t="inlineStr">
+        <is>
+          <t>analyst, cryptocurrency, support, financial, investment, finance, senior, non tech</t>
+        </is>
+      </c>
       <c r="H188" s="4" t="inlineStr"/>
       <c r="I188" s="4" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J188" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/wing-assistant-full-stack-developer</t>
+          <t>https://remoteOK.com/remote-jobs/remote-senior-financial-analyst-digital-assets-exodus-movement-inc-1131374</t>
         </is>
       </c>
       <c r="K188" s="4" t="inlineStr">
@@ -8607,27 +8623,35 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>Qventus: Product Designer</t>
-        </is>
-      </c>
-      <c r="C189" s="2" t="inlineStr"/>
+          <t>Front End Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>Honor Foods</t>
+        </is>
+      </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Philadelphia, PA</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr"/>
       <c r="F189" s="2" t="inlineStr"/>
-      <c r="G189" s="2" t="inlineStr"/>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>developer, front-end, ui, code, web, operational, backend, digital nomad</t>
+        </is>
+      </c>
       <c r="H189" s="2" t="inlineStr"/>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J189" s="3" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/qventus-product-designer</t>
+          <t>https://remoteOK.com/remote-jobs/remote-front-end-full-stack-developer-honor-foods-1131370</t>
         </is>
       </c>
       <c r="K189" s="2" t="inlineStr">
@@ -8644,7 +8668,7 @@
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>Socure: Senior Product Marketing Manager</t>
+          <t>Wing Assistant: Full-Stack Developer</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr"/>
@@ -8664,7 +8688,7 @@
       </c>
       <c r="J190" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/socure-senior-product-marketing-manager</t>
+          <t>https://weworkremotely.com/remote-jobs/wing-assistant-full-stack-developer</t>
         </is>
       </c>
       <c r="K190" s="4" t="inlineStr">
@@ -8681,7 +8705,7 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>Blueprint: Product Designer</t>
+          <t>Qventus: Product Designer</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr"/>
@@ -8701,7 +8725,7 @@
       </c>
       <c r="J191" s="3" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/blueprint-product-designer</t>
+          <t>https://weworkremotely.com/remote-jobs/qventus-product-designer</t>
         </is>
       </c>
       <c r="K191" s="2" t="inlineStr">
@@ -8718,7 +8742,7 @@
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>Interop Labs: Product Marketing Manager</t>
+          <t>Socure: Senior Product Marketing Manager</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr"/>
@@ -8738,7 +8762,7 @@
       </c>
       <c r="J192" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/interop-labs-product-marketing-manager</t>
+          <t>https://weworkremotely.com/remote-jobs/socure-senior-product-marketing-manager</t>
         </is>
       </c>
       <c r="K192" s="4" t="inlineStr">
@@ -8755,17 +8779,13 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Link</t>
-        </is>
-      </c>
-      <c r="C193" s="2" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
+          <t>Blueprint: Product Designer</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr"/>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>Toronto, Remote in Canada</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr"/>
@@ -8774,12 +8794,12 @@
       <c r="H193" s="2" t="inlineStr"/>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J193" s="3" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=6447175</t>
+          <t>https://weworkremotely.com/remote-jobs/blueprint-product-designer</t>
         </is>
       </c>
       <c r="K193" s="2" t="inlineStr">
@@ -8796,17 +8816,13 @@
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="C194" s="4" t="inlineStr">
-        <is>
-          <t>Reddit</t>
-        </is>
-      </c>
+          <t>Interop Labs: Product Marketing Manager</t>
+        </is>
+      </c>
+      <c r="C194" s="4" t="inlineStr"/>
       <c r="D194" s="4" t="inlineStr">
         <is>
-          <t>Remote - Ontario, Canada</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E194" s="4" t="inlineStr"/>
@@ -8815,12 +8831,12 @@
       <c r="H194" s="4" t="inlineStr"/>
       <c r="I194" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J194" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/6960833</t>
+          <t>https://weworkremotely.com/remote-jobs/interop-labs-product-marketing-manager</t>
         </is>
       </c>
       <c r="K194" s="4" t="inlineStr">
@@ -8837,17 +8853,17 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Full Stack Engineer, Link</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Toronto, Remote in Canada</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr"/>
@@ -8861,10 +8877,92 @@
       </c>
       <c r="J195" s="3" t="inlineStr">
         <is>
+          <t>https://stripe.com/jobs/search?gh_jid=6447175</t>
+        </is>
+      </c>
+      <c r="K195" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B196" s="4" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="C196" s="4" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="D196" s="4" t="inlineStr">
+        <is>
+          <t>Remote - Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="E196" s="4" t="inlineStr"/>
+      <c r="F196" s="4" t="inlineStr"/>
+      <c r="G196" s="4" t="inlineStr"/>
+      <c r="H196" s="4" t="inlineStr"/>
+      <c r="I196" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J196" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/6960833</t>
+        </is>
+      </c>
+      <c r="K196" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr"/>
+      <c r="F197" s="2" t="inlineStr"/>
+      <c r="G197" s="2" t="inlineStr"/>
+      <c r="H197" s="2" t="inlineStr"/>
+      <c r="I197" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J197" s="3" t="inlineStr">
+        <is>
           <t>https://job-boards.greenhouse.io/reddit/jobs/6960831</t>
         </is>
       </c>
-      <c r="K195" s="2" t="inlineStr">
+      <c r="K197" s="2" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>

--- a/remote_jobs.xlsx
+++ b/remote_jobs.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K197"/>
+  <dimension ref="A1:K199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -523,33 +523,29 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Senior Sofrware Engineer - Full Stack</t>
+          <t>Senior Frontend Developer:in (Angular)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Parto Group GmbH</t>
+          <t>Wintama IT Solutions GmbH</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Hamburg</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
+          <t>Grünwald</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Remote, Engineering</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -560,12 +556,12 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/parto-group-gmbh/senior-sofrware-engineer-full-stack-hamburg-207489</t>
+          <t>https://www.arbeitnow.com/jobs/companies/wintama-it-solutions-gmbh/senior-frontend-developerin-angular-grunwald-41193</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
     </row>
@@ -577,73 +573,73 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Product Ownership &amp; Operations)</t>
+          <t>Tooling Engineer</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Yoffix</t>
+          <t>Unikraft</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Contract, professional / experienced</t>
-        </is>
-      </c>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr"/>
       <c r="F3" s="4" t="inlineStr"/>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>Remote, Software Development</t>
+          <t>golang, cloud, engineer</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr"/>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/yoffix/senior-full-stack-engineer-product-ownership-operations-berlin-437578</t>
+          <t>https://remoteOK.com/remote-jobs/remote-tooling-engineer-unikraft-1131540</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer / Backend &amp; Frontend - Bootstrapped SaaS Startup (m/w/d) remote in EU</t>
+          <t>Senior Sofrware Engineer - Full Stack</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>DatAds</t>
+          <t>Parto Group GmbH</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Cologne</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr"/>
+          <t>Hamburg</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Remote, IT</t>
+          <t>Remote, Engineering</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -654,90 +650,90 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-bootstrapped-saas-startup-remote-in-eu-cologne-266336</t>
+          <t>https://www.arbeitnow.com/jobs/companies/parto-group-gmbh/senior-sofrware-engineer-full-stack-hamburg-207489</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Asset Administration Operations Specialist</t>
+          <t>Senior Full Stack Engineer (Product Ownership &amp; Operations)</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Forge Global</t>
+          <t>Yoffix</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Denver</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr"/>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Contract, professional / experienced</t>
+        </is>
+      </c>
       <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>travel, financial, operations, non tech</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>$21 - $24</t>
-        </is>
-      </c>
+          <t>Remote, Software Development</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr"/>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-asset-administration-operations-specialist-forge-global-1131523</t>
+          <t>https://www.arbeitnow.com/jobs/companies/yoffix/senior-full-stack-engineer-product-ownership-operations-berlin-437578</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer (TypeScript &amp; AWS) (m/w/d)</t>
+          <t>Full-Stack Software Engineer / Backend &amp; Frontend - Bootstrapped SaaS Startup (m/w/d) remote in EU</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>vOffice Software</t>
+          <t>DatAds</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Hamburg</t>
+          <t>Cologne</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Remote, Software Development</t>
+          <t>Remote, IT</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -748,12 +744,12 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/voffice-software/senior-cloud-software-engineer-typescript-aws-hamburg-431856</t>
+          <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-bootstrapped-saas-startup-remote-in-eu-cologne-266336</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
@@ -765,44 +761,44 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer RoR (all identities)</t>
+          <t>Asset Administration Operations Specialist</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Caspar Health</t>
+          <t>Forge Global</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
+          <t>Denver</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr"/>
       <c r="F7" s="4" t="inlineStr"/>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>Remote, Software Development</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr"/>
+          <t>travel, financial, operations, non tech</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>$21 - $24</t>
+        </is>
+      </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/caspar-health/senior-backend-engineer-ror-all-identities-berlin-7147</t>
+          <t>https://remoteOK.com/remote-jobs/remote-asset-administration-operations-specialist-forge-global-1131523</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
@@ -814,24 +810,20 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Python Software Engineer - Machine Learning Systems (m/f/d)</t>
+          <t>Senior Cloud Software Engineer (TypeScript &amp; AWS) (m/w/d)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>CUJU</t>
+          <t>vOffice Software</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Frankenthal</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
+          <t>Hamburg</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -846,7 +838,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/cuju/python-software-engineer-machine-learning-systems-frankenthal-183273</t>
+          <t>https://www.arbeitnow.com/jobs/companies/voffice-software/senior-cloud-software-engineer-typescript-aws-hamburg-431856</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -863,28 +855,28 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>AI Algorithm Developer Medical Imaging (m/w/d)</t>
+          <t>Senior Backend Engineer RoR (all identities)</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>citema systems GmbH</t>
+          <t>Caspar Health</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>berufserfahren</t>
+          <t>professional / experienced</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>Remote, IT</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr"/>
@@ -895,7 +887,7 @@
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/citema-systems-gmbh/ai-algorithm-developer-medical-imaging-munich-91573</t>
+          <t>https://www.arbeitnow.com/jobs/companies/caspar-health/senior-backend-engineer-ror-all-identities-berlin-7147</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
@@ -907,40 +899,44 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Python Software Engineer - Machine Learning Systems (m/f/d)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Civitech</t>
+          <t>CUJU</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Austin, TX or Remote</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr"/>
+          <t>Frankenthal</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>python, support, code, cloud, analytics, engineer, engineering, full-time</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-analytics-engineer-civitech-1131512</t>
+          <t>https://www.arbeitnow.com/jobs/companies/cuju/python-software-engineer-machine-learning-systems-frankenthal-183273</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -952,40 +948,44 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Tech Lead</t>
+          <t>AI Algorithm Developer Medical Imaging (m/w/d)</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Zensurance</t>
+          <t>citema systems GmbH</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Toronto, ON</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr"/>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
       <c r="F11" s="4" t="inlineStr"/>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>design, system, front-end, back-end, security, training, full-stack, docker, technical, support, software, testing, test, growth, code, web, scrum, devops, javascript, education, strategy, management, lead, senior, health, engineering, digital nomad</t>
+          <t>Remote, IT</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-tech-lead-zensurance-1131509</t>
+          <t>https://www.arbeitnow.com/jobs/companies/citema-systems-gmbh/ai-algorithm-developer-medical-imaging-munich-91573</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
@@ -1002,31 +1002,35 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Senior Full-stack Symfony Developer</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr"/>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Civitech</t>
+        </is>
+      </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Austin, TX or Remote</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>symfony, php, javascript, vuejs</t>
+          <t>python, support, code, cloud, analytics, engineer, engineering, full-time</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>WorkingNomads</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>https://www.workingnomads.com/job/go/1587815/</t>
+          <t>https://remoteOK.com/remote-jobs/remote-analytics-engineer-civitech-1131512</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1043,31 +1047,35 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Senior Staff Machine Learning Engineer, Feed Relevance</t>
+          <t>Tech Lead</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Zensurance</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Toronto, ON</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr"/>
       <c r="F13" s="4" t="inlineStr"/>
-      <c r="G13" s="4" t="inlineStr"/>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>design, system, front-end, back-end, security, training, full-stack, docker, technical, support, software, testing, test, growth, code, web, scrum, devops, javascript, education, strategy, management, lead, senior, health, engineering, digital nomad</t>
+        </is>
+      </c>
       <c r="H13" s="4" t="inlineStr"/>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7908786</t>
+          <t>https://remoteOK.com/remote-jobs/remote-tech-lead-zensurance-1131509</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
@@ -1084,40 +1092,36 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Sidebase Open-Source Contributor &amp; Senior TS Dev (f/m/d)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Sidestream</t>
-        </is>
-      </c>
+          <t>Senior Full-stack Symfony Developer</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Cologne</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Remote, Software Development</t>
+          <t>symfony, php, javascript, vuejs</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>WorkingNomads</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/sidestream/sidebase-open-source-contributor-senior-ts-dev-cologne-317648</t>
+          <t>https://www.workingnomads.com/job/go/1587815/</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -1129,40 +1133,36 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Senior Typescript Developer (f/m/d)</t>
+          <t>Senior Staff Machine Learning Engineer, Feed Relevance</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Sidestream</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Cologne</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr"/>
       <c r="F15" s="4" t="inlineStr"/>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Software Development</t>
-        </is>
-      </c>
+      <c r="G15" s="4" t="inlineStr"/>
       <c r="H15" s="4" t="inlineStr"/>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/sidestream/senior-typescript-developer-cologne-220463</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7908786</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -1174,24 +1174,24 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Senior AI-Engineer / Agent-Architekt (m/w/d)</t>
+          <t>Sidebase Open-Source Contributor &amp; Senior TS Dev (f/m/d)</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Neurawork GmbH &amp; Co. KG</t>
+          <t>Sidestream</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Ampfing</t>
+          <t>Cologne</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Remote, IT</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/neurawork-gmbh-co-kg/senior-ai-engineer-agent-architekt-ampfing-390691</t>
+          <t>https://www.arbeitnow.com/jobs/companies/sidestream/sidebase-open-source-contributor-senior-ts-dev-cologne-317648</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1219,28 +1219,24 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Senior AI Consultant / Machine Learning Engineer (m/w/d) Public Sector | &gt;90% REMOTE</t>
+          <t>Senior Typescript Developer (f/m/d)</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Bridgency HR Management GbR</t>
+          <t>Sidestream</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Usingen</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>berufserfahren</t>
-        </is>
-      </c>
+          <t>Cologne</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr"/>
       <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>Remote, Consulting, Engineering</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
@@ -1251,7 +1247,7 @@
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/bridgency-hr-management-gbr/senior-ai-consultant-machine-learning-engineer-public-sector-90-remote-usingen-94077</t>
+          <t>https://www.arbeitnow.com/jobs/companies/sidestream/senior-typescript-developer-cologne-220463</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
@@ -1268,28 +1264,24 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Werkstudent (m/w/d) Frontend Development &amp; KI-Integration (20h/Woche)</t>
+          <t>Senior AI-Engineer / Agent-Architekt (m/w/d)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>MEvents Cross Media GmbH</t>
+          <t>Neurawork GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>hilfstätigkeit / student</t>
-        </is>
-      </c>
+          <t>Ampfing</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Remote, Software Development</t>
+          <t>Remote, IT</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
@@ -1300,7 +1292,7 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/mevents-cross-media-gmbh/werkstudent-frontend-development-ki-integration-20h-woche-berlin-378282</t>
+          <t>https://www.arbeitnow.com/jobs/companies/neurawork-gmbh-co-kg/senior-ai-engineer-agent-architekt-ampfing-390691</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1312,40 +1304,44 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Consultant / Machine Learning Engineer (m/w/d) Public Sector | &gt;90% REMOTE</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Valon Mortgage</t>
+          <t>Bridgency HR Management GbR</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr"/>
+          <t>Usingen</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
       <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>design, saas, python, architect, technical, support, cloud, strategy, management, senior, operations, operational, analytics, reliability, go, engineer, engineering, digital nomad</t>
+          <t>Remote, Consulting, Engineering</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-senior-data-engineer-valon-mortgage-1131504</t>
+          <t>https://www.arbeitnow.com/jobs/companies/bridgency-hr-management-gbr/senior-ai-consultant-machine-learning-engineer-public-sector-90-remote-usingen-94077</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
@@ -1357,139 +1353,135 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Senior AI Agent Architect / AI Automation Architect</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr"/>
+          <t>Werkstudent (m/w/d) Frontend Development &amp; KI-Integration (20h/Woche)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>MEvents Cross Media GmbH</t>
+        </is>
+      </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr"/>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>hilfstätigkeit / student</t>
+        </is>
+      </c>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>artificial intelligence, python, machine learning, engineer, communication</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/mevents-cross-media-gmbh/werkstudent-frontend-development-ki-integration-20h-woche-berlin-378282</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Valon Mortgage</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>design, saas, python, architect, technical, support, cloud, strategy, management, senior, operations, operational, analytics, reliability, go, engineer, engineering, digital nomad</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-senior-data-engineer-valon-mortgage-1131504</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Senior AI Agent Architect / AI Automation Architect</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr"/>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>artificial intelligence, python, machine learning, engineer, communication</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
           <t>WorkingNomads</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>https://www.workingnomads.com/job/go/1585195/</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>2026-05-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Weiterbildung: Data Science &amp; Business Analytics (IHK) (m/w/d) - Remote</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>DataSmart Point GmbH</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Apprenticeship</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>Remote, Data Scientist</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/datasmart-point-gmbh/weiterbildung-data-science-business-analytics-ihk-remote-berlin-23738</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Karrierestart in Data &amp; AI - IHK Data Analyst (m/w/d) - 100 % Online</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>DataSmart Point GmbH</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>Apprenticeship</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr"/>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Data Scientist</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr"/>
-      <c r="I22" s="4" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J22" s="5" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/datasmart-point-gmbh/karrierestart-in-data-ai-ihk-data-analyst-100-online-berlin-138911</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
         </is>
       </c>
     </row>
@@ -1501,28 +1493,28 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Rockstardevelopers: Senior Fullstack Entwickler (m/w/d) mit Projekterfahrung Deutsche Bahn oder DB Systel</t>
+          <t>Weiterbildung: Data Science &amp; Business Analytics (IHK) (m/w/d) - Remote</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Rockstardevelopers GmbH</t>
+          <t>DataSmart Point GmbH</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>berufserfahren</t>
+          <t>Apprenticeship</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Remote, Software Development</t>
+          <t>Remote, Data Scientist</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr"/>
@@ -1533,7 +1525,7 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/rockstardevelopers-gmbh/rockstardevelopers-senior-fullstack-entwickler-mit-projekterfahrung-deutsche-bahn-oder-db-systel-stuttgart-354361</t>
+          <t>https://www.arbeitnow.com/jobs/companies/datasmart-point-gmbh/weiterbildung-data-science-business-analytics-ihk-remote-berlin-23738</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1550,24 +1542,28 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Full-Stack AI Engineer (Computer Vision &amp; Back-end Focus)</t>
+          <t>Karrierestart in Data &amp; AI - IHK Data Analyst (m/w/d) - 100 % Online</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>StellDirVor GmbH</t>
+          <t>DataSmart Point GmbH</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr"/>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Apprenticeship</t>
+        </is>
+      </c>
       <c r="F24" s="4" t="inlineStr"/>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>Remote, Software Development</t>
+          <t>Remote, Data Scientist</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
@@ -1578,7 +1574,7 @@
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/stelldirvor-gmbh/full-stack-ai-engineer-computer-vision-back-end-focus-munich-122395</t>
+          <t>https://www.arbeitnow.com/jobs/companies/datasmart-point-gmbh/karrierestart-in-data-ai-ihk-data-analyst-100-online-berlin-138911</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
@@ -1590,40 +1586,44 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Rockstardevelopers: Senior Fullstack Entwickler (m/w/d) mit Projekterfahrung Deutsche Bahn oder DB Systel</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Prove</t>
+          <t>Rockstardevelopers GmbH</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr"/>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>software, security, senior, engineer, engineering</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-senior-software-engineer-prove-1131482</t>
+          <t>https://www.arbeitnow.com/jobs/companies/rockstardevelopers-gmbh/rockstardevelopers-senior-fullstack-entwickler-mit-projekterfahrung-deutsche-bahn-oder-db-systel-stuttgart-354361</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1635,40 +1635,40 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Full-Stack AI Engineer (Computer Vision &amp; Back-end Focus)</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Akuity</t>
+          <t>StellDirVor GmbH</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr"/>
       <c r="F26" s="4" t="inlineStr"/>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>saas, developer, software, code, devops, senior, engineer, engineering, backend, digital nomad</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-senior-backend-engineer-akuity-1131479</t>
+          <t>https://www.arbeitnow.com/jobs/companies/stelldirvor-gmbh/full-stack-ai-engineer-computer-vision-back-end-focus-munich-122395</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
@@ -1685,24 +1685,24 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Medical Affairs Solutions Manager UK</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Sorcero</t>
+          <t>Prove</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr"/>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>manager, growth, operations, biotech</t>
+          <t>software, security, senior, engineer, engineering</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr"/>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-medical-affairs-solutions-manager-uk-sorcero-1131475</t>
+          <t>https://remoteOK.com/remote-jobs/remote-senior-software-engineer-prove-1131482</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1730,31 +1730,35 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Dropbox</t>
+          <t>Akuity</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Remote - Canada: Select locations</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr"/>
       <c r="F28" s="4" t="inlineStr"/>
-      <c r="G28" s="4" t="inlineStr"/>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>saas, developer, software, code, devops, senior, engineer, engineering, backend, digital nomad</t>
+        </is>
+      </c>
       <c r="H28" s="4" t="inlineStr"/>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7762007?gh_jid=7762007</t>
+          <t>https://remoteOK.com/remote-jobs/remote-senior-backend-engineer-akuity-1131479</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
@@ -1771,31 +1775,35 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Medical Affairs Solutions Manager UK</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Dropbox</t>
+          <t>Sorcero</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Remote - US: Select locations</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>manager, growth, operations, biotech</t>
+        </is>
+      </c>
       <c r="H29" s="2" t="inlineStr"/>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7762004?gh_jid=7762004</t>
+          <t>https://remoteOK.com/remote-jobs/remote-medical-affairs-solutions-manager-uk-sorcero-1131475</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1822,7 +1830,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Remote - Mexico</t>
+          <t>Remote - Canada: Select locations</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr"/>
@@ -1836,7 +1844,7 @@
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7762009?gh_jid=7762009</t>
+          <t>https://jobs.dropbox.com/listing/7762007?gh_jid=7762007</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
@@ -1853,7 +1861,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Frontend Product Software Engineer, Web DX</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1863,7 +1871,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Remote - Mexico</t>
+          <t>Remote - US: Select locations</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
@@ -1877,7 +1885,7 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7580431?gh_jid=7580431</t>
+          <t>https://jobs.dropbox.com/listing/7762004?gh_jid=7762004</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1894,7 +1902,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer, Dash Experiences</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -1904,7 +1912,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Remote - US: Select locations</t>
+          <t>Remote - Mexico</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr"/>
@@ -1918,7 +1926,7 @@
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7569140?gh_jid=7569140</t>
+          <t>https://jobs.dropbox.com/listing/7762009?gh_jid=7762009</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
@@ -1935,7 +1943,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer, Dash Experiences</t>
+          <t>Frontend Product Software Engineer, Web DX</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1959,7 +1967,7 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7569145?gh_jid=7569145</t>
+          <t>https://jobs.dropbox.com/listing/7580431?gh_jid=7580431</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -1976,7 +1984,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Product Software Engineer, Payments</t>
+          <t>Full Stack Software Engineer, Dash Experiences</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -1986,7 +1994,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Remote - Poland</t>
+          <t>Remote - US: Select locations</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr"/>
@@ -2000,7 +2008,7 @@
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7812915?gh_jid=7812915</t>
+          <t>https://jobs.dropbox.com/listing/7569140?gh_jid=7569140</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
@@ -2017,7 +2025,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, AI Products</t>
+          <t>Full Stack Software Engineer, Dash Experiences</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2027,7 +2035,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Remote - Canada: Select locations</t>
+          <t>Remote - Mexico</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr"/>
@@ -2041,7 +2049,7 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7789389?gh_jid=7789389</t>
+          <t>https://jobs.dropbox.com/listing/7569145?gh_jid=7569145</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2058,7 +2066,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, AI Products</t>
+          <t>Senior Backend Product Software Engineer, Payments</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -2068,7 +2076,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Remote - Canada: Select locations</t>
+          <t>Remote - Poland</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr"/>
@@ -2082,7 +2090,7 @@
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7729764?gh_jid=7729764</t>
+          <t>https://jobs.dropbox.com/listing/7812915?gh_jid=7812915</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
@@ -2109,7 +2117,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Remote - US: Select locations</t>
+          <t>Remote - Canada: Select locations</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr"/>
@@ -2123,7 +2131,7 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7729761?gh_jid=7729761</t>
+          <t>https://jobs.dropbox.com/listing/7789389?gh_jid=7789389</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2150,7 +2158,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Remote - US: Select locations</t>
+          <t>Remote - Canada: Select locations</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr"/>
@@ -2164,7 +2172,7 @@
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7789386?gh_jid=7789386</t>
+          <t>https://jobs.dropbox.com/listing/7729764?gh_jid=7729764</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
@@ -2181,7 +2189,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Dash Agentic AI</t>
+          <t>Senior Data Scientist, AI Products</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2191,7 +2199,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Remote - Canada: Select locations</t>
+          <t>Remote - US: Select locations</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr"/>
@@ -2205,7 +2213,7 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7644890?gh_jid=7644890</t>
+          <t>https://jobs.dropbox.com/listing/7729761?gh_jid=7729761</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2222,7 +2230,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Dash Agentic AI</t>
+          <t>Senior Data Scientist, AI Products</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -2232,7 +2240,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Remote - US: All locations</t>
+          <t>Remote - US: Select locations</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr"/>
@@ -2246,7 +2254,7 @@
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7644886?gh_jid=7644886</t>
+          <t>https://jobs.dropbox.com/listing/7789386?gh_jid=7789386</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
@@ -2263,7 +2271,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Staff Backend Product Software Engineer, Commerce Platform</t>
+          <t>Senior Machine Learning Engineer, Dash Agentic AI</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2273,7 +2281,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Remote - Mexico</t>
+          <t>Remote - Canada: Select locations</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr"/>
@@ -2287,7 +2295,7 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7759733?gh_jid=7759733</t>
+          <t>https://jobs.dropbox.com/listing/7644890?gh_jid=7644890</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -2304,7 +2312,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Staff Backend Product Software Engineer, Commerce Platform</t>
+          <t>Senior Machine Learning Engineer, Dash Agentic AI</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -2314,7 +2322,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Remote - US: Select locations</t>
+          <t>Remote - US: All locations</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr"/>
@@ -2328,7 +2336,7 @@
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7759728?gh_jid=7759728</t>
+          <t>https://jobs.dropbox.com/listing/7644886?gh_jid=7644886</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
@@ -2355,7 +2363,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Remote - Canada: Select locations</t>
+          <t>Remote - Mexico</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
@@ -2369,7 +2377,7 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7759731?gh_jid=7759731</t>
+          <t>https://jobs.dropbox.com/listing/7759733?gh_jid=7759733</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -2386,7 +2394,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Staff Backend Product Software Engineer, Core</t>
+          <t>Staff Backend Product Software Engineer, Commerce Platform</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -2410,7 +2418,7 @@
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7421121?gh_jid=7421121</t>
+          <t>https://jobs.dropbox.com/listing/7759728?gh_jid=7759728</t>
         </is>
       </c>
       <c r="K44" s="4" t="inlineStr">
@@ -2427,7 +2435,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Staff Backend Product Software Engineer, Core</t>
+          <t>Staff Backend Product Software Engineer, Commerce Platform</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2451,7 +2459,7 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7421124?gh_jid=7421124</t>
+          <t>https://jobs.dropbox.com/listing/7759731?gh_jid=7759731</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -2468,7 +2476,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Staff Fullstack Product Software Engineer, Dash</t>
+          <t>Staff Backend Product Software Engineer, Core</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -2478,7 +2486,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Remote - Canada: Select locations</t>
+          <t>Remote - US: Select locations</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr"/>
@@ -2492,7 +2500,7 @@
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7551548?gh_jid=7551548</t>
+          <t>https://jobs.dropbox.com/listing/7421121?gh_jid=7421121</t>
         </is>
       </c>
       <c r="K46" s="4" t="inlineStr">
@@ -2509,7 +2517,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Staff Fullstack Product Software Engineer, Dash</t>
+          <t>Staff Backend Product Software Engineer, Core</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2519,7 +2527,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Remote - US: Select locations</t>
+          <t>Remote - Canada: Select locations</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr"/>
@@ -2533,7 +2541,7 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7551545?gh_jid=7551545</t>
+          <t>https://jobs.dropbox.com/listing/7421124?gh_jid=7421124</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -2550,7 +2558,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Staff Full Stack Software Engineer, Churn</t>
+          <t>Staff Fullstack Product Software Engineer, Dash</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -2560,7 +2568,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Remote - Poland</t>
+          <t>Remote - Canada: Select locations</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr"/>
@@ -2574,7 +2582,7 @@
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7421131?gh_jid=7421131</t>
+          <t>https://jobs.dropbox.com/listing/7551548?gh_jid=7551548</t>
         </is>
       </c>
       <c r="K48" s="4" t="inlineStr">
@@ -2591,7 +2599,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Staff Fullstack Software Engineer, Growth Monetization</t>
+          <t>Staff Fullstack Product Software Engineer, Dash</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2615,7 +2623,7 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7421150?gh_jid=7421150</t>
+          <t>https://jobs.dropbox.com/listing/7551545?gh_jid=7551545</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -2632,7 +2640,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Staff Fullstack Software Engineer, Growth Monetization</t>
+          <t>Staff Full Stack Software Engineer, Churn</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -2642,7 +2650,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Remote - Canada: Select locations</t>
+          <t>Remote - Poland</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr"/>
@@ -2656,7 +2664,7 @@
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7421153?gh_jid=7421153</t>
+          <t>https://jobs.dropbox.com/listing/7421131?gh_jid=7421131</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
@@ -2673,13 +2681,17 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>WALTER: Senior Fullstack Engineer (Ruby+React)</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr"/>
+          <t>Staff Fullstack Software Engineer, Growth Monetization</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Dropbox</t>
+        </is>
+      </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote - US: Select locations</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr"/>
@@ -2688,17 +2700,17 @@
       <c r="H51" s="2" t="inlineStr"/>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/walter-senior-fullstack-engineer-ruby-react</t>
+          <t>https://jobs.dropbox.com/listing/7421150?gh_jid=7421150</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
     </row>
@@ -2710,13 +2722,17 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>WALTER: Full-Stack Engineering Lead</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr"/>
+          <t>Staff Fullstack Software Engineer, Growth Monetization</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>Dropbox</t>
+        </is>
+      </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote - Canada: Select locations</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr"/>
@@ -2725,17 +2741,17 @@
       <c r="H52" s="4" t="inlineStr"/>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/walter-full-stack-engineering-lead</t>
+          <t>https://jobs.dropbox.com/listing/7421153?gh_jid=7421153</t>
         </is>
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
     </row>
@@ -2747,17 +2763,13 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Frontend Product Software Engineer, Design Systems</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Dropbox</t>
-        </is>
-      </c>
+          <t>WALTER: Senior Fullstack Engineer (Ruby+React)</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr"/>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Remote - Mexico</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr"/>
@@ -2766,12 +2778,12 @@
       <c r="H53" s="2" t="inlineStr"/>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7862086?gh_jid=7862086</t>
+          <t>https://weworkremotely.com/remote-jobs/walter-senior-fullstack-engineer-ruby-react</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -2783,40 +2795,32 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Lead AI Engineer &amp; Technical Architect</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>Bold Business</t>
-        </is>
-      </c>
+          <t>WALTER: Full-Stack Engineering Lead</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr"/>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>India, Latin America, Philippines</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr"/>
       <c r="F54" s="4" t="inlineStr"/>
-      <c r="G54" s="4" t="inlineStr">
-        <is>
-          <t>architect, technical, lead, engineer</t>
-        </is>
-      </c>
+      <c r="G54" s="4" t="inlineStr"/>
       <c r="H54" s="4" t="inlineStr"/>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-lead-ai-engineer-technical-architect-bold-business-1131461</t>
+          <t>https://weworkremotely.com/remote-jobs/walter-full-stack-engineering-lead</t>
         </is>
       </c>
       <c r="K54" s="4" t="inlineStr">
@@ -2828,40 +2832,36 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer Showroom</t>
+          <t>Frontend Product Software Engineer, Design Systems</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Higharc</t>
+          <t>Dropbox</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote - Mexico</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="2" t="inlineStr"/>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>software, design, 3d, full-stack, support, ux, manager, api, engineer, engineering, backend, digital nomad</t>
-        </is>
-      </c>
+      <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="2" t="inlineStr"/>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-software-engineer-showroom-higharc-1131457</t>
+          <t>https://jobs.dropbox.com/listing/7862086?gh_jid=7862086</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -2878,31 +2878,35 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Protocol Review Specialist</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr"/>
+          <t>Lead AI Engineer &amp; Technical Architect</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>Bold Business</t>
+        </is>
+      </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>India, Latin America, Philippines</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr"/>
       <c r="F56" s="4" t="inlineStr"/>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>communication, phone, english</t>
+          <t>architect, technical, lead, engineer</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr"/>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>WorkingNomads</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>https://www.workingnomads.com/job/go/1580747/</t>
+          <t>https://remoteOK.com/remote-jobs/remote-lead-ai-engineer-technical-architect-bold-business-1131461</t>
         </is>
       </c>
       <c r="K56" s="4" t="inlineStr">
@@ -2919,31 +2923,35 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Staff AI Engineer - Notebooks</t>
+          <t>Software Engineer Showroom</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Datadog</t>
+          <t>Higharc</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Portugal, Remote</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr"/>
       <c r="F57" s="2" t="inlineStr"/>
-      <c r="G57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>software, design, 3d, full-stack, support, ux, manager, api, engineer, engineering, backend, digital nomad</t>
+        </is>
+      </c>
       <c r="H57" s="2" t="inlineStr"/>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>https://careers.datadoghq.com/detail/7627445/?gh_jid=7627445</t>
+          <t>https://remoteOK.com/remote-jobs/remote-software-engineer-showroom-higharc-1131457</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -2960,31 +2968,31 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Staff AI Engineer - Notebooks</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>Datadog</t>
-        </is>
-      </c>
+          <t>Protocol Review Specialist</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr"/>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>France, Remote; Germany, Remote; Ireland, Remote; Italy, Remote; Spain, Remote; Switzerland, Remote</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr"/>
       <c r="F58" s="4" t="inlineStr"/>
-      <c r="G58" s="4" t="inlineStr"/>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>communication, phone, english</t>
+        </is>
+      </c>
       <c r="H58" s="4" t="inlineStr"/>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WorkingNomads</t>
         </is>
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>https://careers.datadoghq.com/detail/7627429/?gh_jid=7627429</t>
+          <t>https://www.workingnomads.com/job/go/1580747/</t>
         </is>
       </c>
       <c r="K58" s="4" t="inlineStr">
@@ -3001,17 +3009,17 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Ads Conversion Modeling, Machine Learning Engineering Manager</t>
+          <t>Staff AI Engineer - Notebooks</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Datadog</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Portugal, Remote</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr"/>
@@ -3025,7 +3033,7 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7792848</t>
+          <t>https://careers.datadoghq.com/detail/7627445/?gh_jid=7627445</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -3042,17 +3050,17 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Data Scientist, Ads</t>
+          <t>Staff AI Engineer - Notebooks</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Datadog</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Remote - British Columbia, Canada</t>
+          <t>France, Remote; Germany, Remote; Ireland, Remote; Italy, Remote; Spain, Remote; Switzerland, Remote</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr"/>
@@ -3066,7 +3074,7 @@
       </c>
       <c r="J60" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7607124</t>
+          <t>https://careers.datadoghq.com/detail/7627429/?gh_jid=7627429</t>
         </is>
       </c>
       <c r="K60" s="4" t="inlineStr">
@@ -3083,7 +3091,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Data Scientist, Ads</t>
+          <t>Ads Conversion Modeling, Machine Learning Engineering Manager</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3107,7 +3115,7 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/6580815</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7792848</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -3124,7 +3132,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Scientist, Ads</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -3134,7 +3142,7 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Remote - Ontario, Canada</t>
+          <t>Remote - British Columbia, Canada</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr"/>
@@ -3148,7 +3156,7 @@
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7131934</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7607124</t>
         </is>
       </c>
       <c r="K62" s="4" t="inlineStr">
@@ -3165,7 +3173,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Scientist, Ads</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3189,7 +3197,7 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7131932</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/6580815</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -3206,7 +3214,7 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Principal Data Scientist, Ads</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -3216,7 +3224,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Remote - Ontario, Canada</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr"/>
@@ -3230,7 +3238,7 @@
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7330347</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7131934</t>
         </is>
       </c>
       <c r="K64" s="4" t="inlineStr">
@@ -3247,7 +3255,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Ads</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3257,7 +3265,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Remote - British Columbia, Canada</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr"/>
@@ -3271,7 +3279,7 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7607121</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7131932</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -3288,7 +3296,7 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Ads</t>
+          <t>Principal Data Scientist, Ads</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -3312,7 +3320,7 @@
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/6042236</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7330347</t>
         </is>
       </c>
       <c r="K66" s="4" t="inlineStr">
@@ -3329,7 +3337,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Consumer</t>
+          <t>Senior Data Scientist, Ads</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -3339,7 +3347,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Remote - British Columbia, Canada</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr"/>
@@ -3353,7 +3361,7 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7275414</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7607121</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -3370,7 +3378,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Senior  Machine Learning Engineer, ML Training Platform</t>
+          <t>Senior Data Scientist, Ads</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -3394,7 +3402,7 @@
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7074776</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/6042236</t>
         </is>
       </c>
       <c r="K68" s="4" t="inlineStr">
@@ -3411,7 +3419,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Systems Engineer</t>
+          <t>Senior Data Scientist, Consumer</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -3435,7 +3443,7 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7731772</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7275414</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -3452,7 +3460,7 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, GenAI Platform</t>
+          <t>Senior  Machine Learning Engineer, ML Training Platform</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -3476,7 +3484,7 @@
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7753480</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7074776</t>
         </is>
       </c>
       <c r="K70" s="4" t="inlineStr">
@@ -3493,7 +3501,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Senior Staff Machine Learning Engineer, GenAI Platform</t>
+          <t>Senior Machine Learning Systems Engineer</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -3517,7 +3525,7 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7772274</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7731772</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -3534,7 +3542,7 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Staff Data Scientist, Ads</t>
+          <t>Senior Software Engineer, GenAI Platform</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -3544,7 +3552,7 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Remote - British Columbia, Canada</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr"/>
@@ -3558,7 +3566,7 @@
       </c>
       <c r="J72" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7721851</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7753480</t>
         </is>
       </c>
       <c r="K72" s="4" t="inlineStr">
@@ -3575,7 +3583,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Staff Data Scientist, Ads</t>
+          <t>Senior Staff Machine Learning Engineer, GenAI Platform</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -3599,7 +3607,7 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7721787</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7772274</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -3616,7 +3624,7 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Staff Data Scientist, Consumer</t>
+          <t>Staff Data Scientist, Ads</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -3626,7 +3634,7 @@
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Remote - British Columbia, Canada</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr"/>
@@ -3640,7 +3648,7 @@
       </c>
       <c r="J74" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/6745284</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7721851</t>
         </is>
       </c>
       <c r="K74" s="4" t="inlineStr">
@@ -3657,7 +3665,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Staff Data Scientist, Marketing</t>
+          <t>Staff Data Scientist, Ads</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -3681,7 +3689,7 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7445240</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7721787</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -3698,7 +3706,7 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, Ads Auction (Ads Marketplace Quality)</t>
+          <t>Staff Data Scientist, Consumer</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
@@ -3722,7 +3730,7 @@
       </c>
       <c r="J76" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7181821</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/6745284</t>
         </is>
       </c>
       <c r="K76" s="4" t="inlineStr">
@@ -3739,7 +3747,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, Ads Content Understanding</t>
+          <t>Staff Data Scientist, Marketing</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -3763,7 +3771,7 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7851761</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7445240</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -3780,7 +3788,7 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Systems Engineer</t>
+          <t>Staff Machine Learning Engineer, Ads Auction (Ads Marketplace Quality)</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -3804,7 +3812,7 @@
       </c>
       <c r="J78" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7731788</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7181821</t>
         </is>
       </c>
       <c r="K78" s="4" t="inlineStr">
@@ -3821,44 +3829,36 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Werkstudent:in KI Marketing (m/w/d)</t>
+          <t>Staff Machine Learning Engineer, Ads Content Understanding</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>laria.ai</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>Working student, berufseinstieg</t>
-        </is>
-      </c>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr"/>
       <c r="F79" s="2" t="inlineStr"/>
-      <c r="G79" s="2" t="inlineStr">
-        <is>
-          <t>Remote, Online Marketing</t>
-        </is>
-      </c>
+      <c r="G79" s="2" t="inlineStr"/>
       <c r="H79" s="2" t="inlineStr"/>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/lariaai/werkstudentin-ki-marketing-berlin-9847</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7851761</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -3870,80 +3870,80 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Laravel Developer (m/w/d) - AI-First PropTech</t>
+          <t>Staff Machine Learning Systems Engineer</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>Immovara GmbH</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>Korntal-Münchingen</t>
-        </is>
-      </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>berufserfahren</t>
-        </is>
-      </c>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr"/>
       <c r="F80" s="4" t="inlineStr"/>
-      <c r="G80" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Software Development</t>
-        </is>
-      </c>
+      <c r="G80" s="4" t="inlineStr"/>
       <c r="H80" s="4" t="inlineStr"/>
       <c r="I80" s="4" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J80" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/immovara-gmbh/laravel-developer-ai-first-proptech-korntal-munchingen-239743</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7731788</t>
         </is>
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning (ML) Engineer - Applied</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr"/>
+          <t>Werkstudent:in KI Marketing (m/w/d)</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>laria.ai</t>
+        </is>
+      </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr"/>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>Working student, berufseinstieg</t>
+        </is>
+      </c>
       <c r="F81" s="2" t="inlineStr"/>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>machine learning, artificial intelligence, python, cplusplus, startup</t>
+          <t>Remote, Online Marketing</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr"/>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>WorkingNomads</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>https://www.workingnomads.com/job/go/1578553/</t>
+          <t>https://www.arbeitnow.com/jobs/companies/lariaai/werkstudentin-ki-marketing-berlin-9847</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -3955,36 +3955,44 @@
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Backend Engineer, AI Security</t>
+          <t>Laravel Developer (m/w/d) - AI-First PropTech</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Immovara GmbH</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>New York, San Francisco, Seattle, or Remote (US/Canada)</t>
-        </is>
-      </c>
-      <c r="E82" s="4" t="inlineStr"/>
+          <t>Korntal-Münchingen</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
       <c r="F82" s="4" t="inlineStr"/>
-      <c r="G82" s="4" t="inlineStr"/>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Software Development</t>
+        </is>
+      </c>
       <c r="H82" s="4" t="inlineStr"/>
       <c r="I82" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J82" s="5" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7826765</t>
+          <t>https://www.arbeitnow.com/jobs/companies/immovara-gmbh/laravel-developer-ai-first-proptech-korntal-munchingen-239743</t>
         </is>
       </c>
       <c r="K82" s="4" t="inlineStr">
@@ -4001,31 +4009,31 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Backend Engineer, Core Tech, Canada</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
+          <t>Machine Learning (ML) Engineer - Applied</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr"/>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Toronto, CAN-Remote</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr"/>
       <c r="F83" s="2" t="inlineStr"/>
-      <c r="G83" s="2" t="inlineStr"/>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>machine learning, artificial intelligence, python, cplusplus, startup</t>
+        </is>
+      </c>
       <c r="H83" s="2" t="inlineStr"/>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WorkingNomads</t>
         </is>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=6567253</t>
+          <t>https://www.workingnomads.com/job/go/1578553/</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -4042,7 +4050,7 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Backend Engineer, Core Technology</t>
+          <t>Backend Engineer, AI Security</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -4052,7 +4060,7 @@
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>US-Remote, Chicago</t>
+          <t>New York, San Francisco, Seattle, or Remote (US/Canada)</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr"/>
@@ -4066,7 +4074,7 @@
       </c>
       <c r="J84" s="5" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=6042172</t>
+          <t>https://stripe.com/jobs/search?gh_jid=7826765</t>
         </is>
       </c>
       <c r="K84" s="4" t="inlineStr">
@@ -4083,7 +4091,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Backend Engineer, Developer Experience &amp; Product Platform</t>
+          <t>Backend Engineer, Core Tech, Canada</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -4093,7 +4101,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Toronto Canada, San Francisco, Remote in US, Remote in Canada</t>
+          <t>Toronto, CAN-Remote</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr"/>
@@ -4107,7 +4115,7 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7292520</t>
+          <t>https://stripe.com/jobs/search?gh_jid=6567253</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -4124,7 +4132,7 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Commercial Counsel, Crypto</t>
+          <t>Backend Engineer, Core Technology</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -4134,7 +4142,7 @@
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>New York City, Seattle, San Francisco, Chicago, Atlanta, US-Remote</t>
+          <t>US-Remote, Chicago</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr"/>
@@ -4148,7 +4156,7 @@
       </c>
       <c r="J86" s="5" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7392188</t>
+          <t>https://stripe.com/jobs/search?gh_jid=6042172</t>
         </is>
       </c>
       <c r="K86" s="4" t="inlineStr">
@@ -4165,7 +4173,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Fullstack Engineer, Privy</t>
+          <t>Backend Engineer, Developer Experience &amp; Product Platform</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -4175,7 +4183,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">NYC-Privy, US-Remote </t>
+          <t>Toronto Canada, San Francisco, Remote in US, Remote in Canada</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr"/>
@@ -4189,7 +4197,7 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7091959</t>
+          <t>https://stripe.com/jobs/search?gh_jid=7292520</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -4206,7 +4214,7 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Stripe Assistant</t>
+          <t>Commercial Counsel, Crypto</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
@@ -4216,7 +4224,7 @@
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>Seattle; San Francisco; New York City; Remote</t>
+          <t>New York City, Seattle, San Francisco, Chicago, Atlanta, US-Remote</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr"/>
@@ -4230,7 +4238,7 @@
       </c>
       <c r="J88" s="5" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7629052</t>
+          <t>https://stripe.com/jobs/search?gh_jid=7392188</t>
         </is>
       </c>
       <c r="K88" s="4" t="inlineStr">
@@ -4247,17 +4255,17 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning Manager, Feed Relevance</t>
+          <t>Fullstack Engineer, Privy</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t xml:space="preserve">NYC-Privy, US-Remote </t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr"/>
@@ -4271,7 +4279,7 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7802495</t>
+          <t>https://stripe.com/jobs/search?gh_jid=7091959</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -4288,17 +4296,17 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, GenAI Security</t>
+          <t>Machine Learning Engineer, Stripe Assistant</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Seattle; San Francisco; New York City; Remote</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr"/>
@@ -4312,7 +4320,7 @@
       </c>
       <c r="J90" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7891887</t>
+          <t>https://stripe.com/jobs/search?gh_jid=7629052</t>
         </is>
       </c>
       <c r="K90" s="4" t="inlineStr">
@@ -4329,7 +4337,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Senior Staff Machine Learning Engineer, Feed Relevance</t>
+          <t>Machine Learning Manager, Feed Relevance</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -4353,7 +4361,7 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7791994</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7802495</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -4370,7 +4378,7 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Senior Staff Machine Learning Engineer, ML Understanding</t>
+          <t>Senior Machine Learning Engineer, GenAI Security</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -4394,7 +4402,7 @@
       </c>
       <c r="J92" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7847148</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7891887</t>
         </is>
       </c>
       <c r="K92" s="4" t="inlineStr">
@@ -4411,7 +4419,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, Ads Measurement Modeling</t>
+          <t>Senior Staff Machine Learning Engineer, Feed Relevance</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -4435,7 +4443,7 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7890096</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7791994</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -4452,7 +4460,7 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, AI Serving</t>
+          <t>Senior Staff Machine Learning Engineer, ML Understanding</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -4476,7 +4484,7 @@
       </c>
       <c r="J94" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7886459</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7847148</t>
         </is>
       </c>
       <c r="K94" s="4" t="inlineStr">
@@ -4493,17 +4501,17 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (L3) - Full Stack</t>
+          <t>Staff Machine Learning Engineer, Ads Measurement Modeling</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Remote - US</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr"/>
@@ -4517,139 +4525,127 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7890096</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>Staff Machine Learning Engineer, AI Serving</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr"/>
+      <c r="F96" s="4" t="inlineStr"/>
+      <c r="G96" s="4" t="inlineStr"/>
+      <c r="H96" s="4" t="inlineStr"/>
+      <c r="I96" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J96" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7886459</t>
+        </is>
+      </c>
+      <c r="K96" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (L3) - Full Stack</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Remote - US</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr"/>
+      <c r="F97" s="2" t="inlineStr"/>
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr"/>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
           <t>https://job-boards.greenhouse.io/twilio/jobs/7738955</t>
         </is>
       </c>
-      <c r="K95" s="2" t="inlineStr">
+      <c r="K97" s="2" t="inlineStr">
         <is>
           <t>2026-05-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>AI Developer (Claude + AWS)</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>Datavent</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>Hamburg</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
-      <c r="F96" s="2" t="inlineStr"/>
-      <c r="G96" s="2" t="inlineStr">
-        <is>
-          <t>Remote, Software Development</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr"/>
-      <c r="I96" s="2" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/datavent/ai-developer-claude-aws-hamburg-22354</t>
-        </is>
-      </c>
-      <c r="K96" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="B97" s="4" t="inlineStr">
-        <is>
-          <t>Python Software Engineer, Backend &amp; APIs - Remote</t>
-        </is>
-      </c>
-      <c r="C97" s="4" t="inlineStr">
-        <is>
-          <t>dexter health</t>
-        </is>
-      </c>
-      <c r="D97" s="4" t="inlineStr">
-        <is>
-          <t>Cologne</t>
-        </is>
-      </c>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
-      <c r="F97" s="4" t="inlineStr"/>
-      <c r="G97" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Software Development</t>
-        </is>
-      </c>
-      <c r="H97" s="4" t="inlineStr"/>
-      <c r="I97" s="4" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J97" s="5" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/python-software-engineer-backend-apis-remote-cologne-284750</t>
-        </is>
-      </c>
-      <c r="K97" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Fullstack Developer (m/w/d) REMOTE //  UX / Python / Vue.js</t>
+          <t>AI Developer (Claude + AWS)</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Pont Connects e.K.</t>
+          <t>Datavent</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Düsseldorf</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr"/>
+          <t>Hamburg</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
       <c r="F98" s="2" t="inlineStr"/>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Remote, IT</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr"/>
@@ -4660,146 +4656,154 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
+          <t>https://www.arbeitnow.com/jobs/companies/datavent/ai-developer-claude-aws-hamburg-22354</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>Python Software Engineer, Backend &amp; APIs - Remote</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>dexter health</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>Cologne</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr"/>
+      <c r="G99" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Software Development</t>
+        </is>
+      </c>
+      <c r="H99" s="4" t="inlineStr"/>
+      <c r="I99" s="4" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J99" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/python-software-engineer-backend-apis-remote-cologne-284750</t>
+        </is>
+      </c>
+      <c r="K99" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Fullstack Developer (m/w/d) REMOTE //  UX / Python / Vue.js</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Pont Connects e.K.</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Düsseldorf</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr"/>
+      <c r="F100" s="2" t="inlineStr"/>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>Remote, IT</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr"/>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
           <t>https://www.arbeitnow.com/jobs/companies/pont-connects-ek/fullstack-developer-remote-ux-python-vuejs-dusseldorf-371903</t>
         </is>
       </c>
-      <c r="K98" s="2" t="inlineStr">
+      <c r="K100" s="2" t="inlineStr">
         <is>
           <t>2026-05-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>Lemon.io</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>Americas, Europe, Asia, Oceania</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>full_time</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>Devops</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>.Net, android, AWS, azure, C, C#, C++, data science, golang, ios, java, javascript, kubernetes, node.js, php, python, react, ruby/rails, shopify, sql, video, blockchain, AI/ML, automation, react native, rust, unity, spring, data analysis, laravel, solidity, flask, Typescript , terraform, angular , GCP, data engineering, Symfony, startup, marketplace, next.js</t>
-        </is>
-      </c>
-      <c r="H99" s="2" t="inlineStr"/>
-      <c r="I99" s="2" t="inlineStr">
-        <is>
-          <t>Remotive</t>
-        </is>
-      </c>
-      <c r="J99" s="3" t="inlineStr">
-        <is>
-          <t>https://remotive.com/remote-jobs/devops/senior-devops-engineer-2090002</t>
-        </is>
-      </c>
-      <c r="K99" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="B100" s="4" t="inlineStr">
-        <is>
-          <t>M&amp;A Research Analyst</t>
-        </is>
-      </c>
-      <c r="C100" s="4" t="inlineStr">
-        <is>
-          <t>EquiMatch GmbH</t>
-        </is>
-      </c>
-      <c r="D100" s="4" t="inlineStr">
-        <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E100" s="4" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
-      <c r="F100" s="4" t="inlineStr"/>
-      <c r="G100" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Mergers &amp; Acquisitions</t>
-        </is>
-      </c>
-      <c r="H100" s="4" t="inlineStr"/>
-      <c r="I100" s="4" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J100" s="5" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/equimatch-gmbh/ma-research-analyst-berlin-498635</t>
-        </is>
-      </c>
-      <c r="K100" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Xsolla: Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr"/>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Lemon.io</t>
+        </is>
+      </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr"/>
-      <c r="F101" s="2" t="inlineStr"/>
-      <c r="G101" s="2" t="inlineStr"/>
+          <t>Americas, Europe, Asia, Oceania</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>full_time</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>Devops</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>.Net, android, AWS, azure, C, C#, C++, data science, golang, ios, java, javascript, kubernetes, node.js, php, python, react, ruby/rails, shopify, sql, video, blockchain, AI/ML, automation, react native, rust, unity, spring, data analysis, laravel, solidity, flask, Typescript , terraform, angular , GCP, data engineering, Symfony, startup, marketplace, next.js</t>
+        </is>
+      </c>
       <c r="H101" s="2" t="inlineStr"/>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Remotive</t>
         </is>
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/xsolla-full-stack-developer</t>
+          <t>https://remotive.com/remote-jobs/devops/senior-devops-engineer-2090002</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -4811,32 +4815,44 @@
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>Dropbox: Staff Fullstack Product Software Engineer, Dash</t>
-        </is>
-      </c>
-      <c r="C102" s="4" t="inlineStr"/>
+          <t>M&amp;A Research Analyst</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>EquiMatch GmbH</t>
+        </is>
+      </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E102" s="4" t="inlineStr"/>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
       <c r="F102" s="4" t="inlineStr"/>
-      <c r="G102" s="4" t="inlineStr"/>
+      <c r="G102" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Mergers &amp; Acquisitions</t>
+        </is>
+      </c>
       <c r="H102" s="4" t="inlineStr"/>
       <c r="I102" s="4" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J102" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/dropbox-staff-fullstack-product-software-engineer-dash</t>
+          <t>https://www.arbeitnow.com/jobs/companies/equimatch-gmbh/ma-research-analyst-berlin-498635</t>
         </is>
       </c>
       <c r="K102" s="4" t="inlineStr">
@@ -4853,17 +4869,13 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, Ranking and Personalization</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>Reddit</t>
-        </is>
-      </c>
+          <t>Xsolla: Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr"/>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr"/>
@@ -4872,115 +4884,95 @@
       <c r="H103" s="2" t="inlineStr"/>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
+          <t>https://weworkremotely.com/remote-jobs/xsolla-full-stack-developer</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>Dropbox: Staff Fullstack Product Software Engineer, Dash</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr"/>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr"/>
+      <c r="F104" s="4" t="inlineStr"/>
+      <c r="G104" s="4" t="inlineStr"/>
+      <c r="H104" s="4" t="inlineStr"/>
+      <c r="I104" s="4" t="inlineStr">
+        <is>
+          <t>WeWorkRemotely</t>
+        </is>
+      </c>
+      <c r="J104" s="5" t="inlineStr">
+        <is>
+          <t>https://weworkremotely.com/remote-jobs/dropbox-staff-fullstack-product-software-engineer-dash</t>
+        </is>
+      </c>
+      <c r="K104" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Staff Machine Learning Engineer, Ranking and Personalization</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr"/>
+      <c r="F105" s="2" t="inlineStr"/>
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr"/>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
           <t>https://job-boards.greenhouse.io/reddit/jobs/7848689</t>
         </is>
       </c>
-      <c r="K103" s="2" t="inlineStr">
+      <c r="K105" s="2" t="inlineStr">
         <is>
           <t>2026-05-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>Senior Rust Consultant / Engineer (m/w/d)</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>Hackstack GmbH</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>berufserfahren</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="inlineStr"/>
-      <c r="G104" s="2" t="inlineStr">
-        <is>
-          <t>Remote, Consulting, Engineering</t>
-        </is>
-      </c>
-      <c r="H104" s="2" t="inlineStr"/>
-      <c r="I104" s="2" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J104" s="3" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/hackstack-gmbh/senior-rust-consultant-engineer-munich-451602</t>
-        </is>
-      </c>
-      <c r="K104" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="B105" s="4" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer - Remote</t>
-        </is>
-      </c>
-      <c r="C105" s="4" t="inlineStr">
-        <is>
-          <t>dexter health</t>
-        </is>
-      </c>
-      <c r="D105" s="4" t="inlineStr">
-        <is>
-          <t>Cologne</t>
-        </is>
-      </c>
-      <c r="E105" s="4" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
-      <c r="F105" s="4" t="inlineStr"/>
-      <c r="G105" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Development</t>
-        </is>
-      </c>
-      <c r="H105" s="4" t="inlineStr"/>
-      <c r="I105" s="4" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J105" s="5" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/applied-ai-engineer-remote-cologne-2870</t>
-        </is>
-      </c>
-      <c r="K105" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4992,28 +4984,28 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Python Backend Engineer - Remote</t>
+          <t>Senior Rust Consultant / Engineer (m/w/d)</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>dexter health</t>
+          <t>Hackstack GmbH</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Cologne</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>professional / experienced</t>
+          <t>berufserfahren</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr"/>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Remote, Development</t>
+          <t>Remote, Consulting, Engineering</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr"/>
@@ -5024,7 +5016,7 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/python-backend-engineer-remote-cologne-34228</t>
+          <t>https://www.arbeitnow.com/jobs/companies/hackstack-gmbh/senior-rust-consultant-engineer-munich-451602</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -5041,7 +5033,7 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>AI Engineer (LLM Products) - Remote</t>
+          <t>Applied AI Engineer - Remote</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
@@ -5073,7 +5065,7 @@
       </c>
       <c r="J107" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/ai-engineer-llm-products-remote-cologne-236027</t>
+          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/applied-ai-engineer-remote-cologne-2870</t>
         </is>
       </c>
       <c r="K107" s="4" t="inlineStr">
@@ -5090,7 +5082,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Backend Python Engineer (APIs, Databases &amp; Cloud) - Remote</t>
+          <t>Python Backend Engineer - Remote</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -5122,7 +5114,7 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/backend-python-engineer-apis-databases-cloud-remote-cologne-274767</t>
+          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/python-backend-engineer-remote-cologne-34228</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -5134,32 +5126,44 @@
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Toptal: QA Automation Engineer</t>
-        </is>
-      </c>
-      <c r="C109" s="4" t="inlineStr"/>
+          <t>AI Engineer (LLM Products) - Remote</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>dexter health</t>
+        </is>
+      </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E109" s="4" t="inlineStr"/>
+          <t>Cologne</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
       <c r="F109" s="4" t="inlineStr"/>
-      <c r="G109" s="4" t="inlineStr"/>
+      <c r="G109" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Development</t>
+        </is>
+      </c>
       <c r="H109" s="4" t="inlineStr"/>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J109" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/toptal-qa-automation-engineer-1</t>
+          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/ai-engineer-llm-products-remote-cologne-236027</t>
         </is>
       </c>
       <c r="K109" s="4" t="inlineStr">
@@ -5171,32 +5175,44 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Opensea: Staff Product Designer</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr"/>
+          <t>Backend Python Engineer (APIs, Databases &amp; Cloud) - Remote</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>dexter health</t>
+        </is>
+      </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr"/>
+          <t>Cologne</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
       <c r="F110" s="2" t="inlineStr"/>
-      <c r="G110" s="2" t="inlineStr"/>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>Remote, Development</t>
+        </is>
+      </c>
       <c r="H110" s="2" t="inlineStr"/>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/opensea-staff-product-designer</t>
+          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/backend-python-engineer-apis-databases-cloud-remote-cologne-274767</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -5213,7 +5229,7 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Mutt Data: Devops</t>
+          <t>Toptal: QA Automation Engineer</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr"/>
@@ -5233,7 +5249,7 @@
       </c>
       <c r="J111" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/mutt-data-devops</t>
+          <t>https://weworkremotely.com/remote-jobs/toptal-qa-automation-engineer-1</t>
         </is>
       </c>
       <c r="K111" s="4" t="inlineStr">
@@ -5250,7 +5266,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Holywater: Full-Stack Developer</t>
+          <t>Opensea: Staff Product Designer</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr"/>
@@ -5270,7 +5286,7 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/holywater-full-stack-developer</t>
+          <t>https://weworkremotely.com/remote-jobs/opensea-staff-product-designer</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -5287,7 +5303,7 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Qventus: DevOps Engineer</t>
+          <t>Mutt Data: Devops</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr"/>
@@ -5307,7 +5323,7 @@
       </c>
       <c r="J113" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/qventus-devops-engineer</t>
+          <t>https://weworkremotely.com/remote-jobs/mutt-data-devops</t>
         </is>
       </c>
       <c r="K113" s="4" t="inlineStr">
@@ -5324,7 +5340,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Visualis: Senior Full Stack Developer</t>
+          <t>Holywater: Full-Stack Developer</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr"/>
@@ -5344,7 +5360,7 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/visualis-senior-full-stack-developer</t>
+          <t>https://weworkremotely.com/remote-jobs/holywater-full-stack-developer</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -5361,17 +5377,13 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="C115" s="4" t="inlineStr">
-        <is>
-          <t>GitLab</t>
-        </is>
-      </c>
+          <t>Qventus: DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr"/>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Remote, Bangalore</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr"/>
@@ -5380,12 +5392,12 @@
       <c r="H115" s="4" t="inlineStr"/>
       <c r="I115" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J115" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8517564002</t>
+          <t>https://weworkremotely.com/remote-jobs/qventus-devops-engineer</t>
         </is>
       </c>
       <c r="K115" s="4" t="inlineStr">
@@ -5402,17 +5414,13 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Backend Engineer, Analytics Instrumentation (Golang)</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>GitLab</t>
-        </is>
-      </c>
+          <t>Visualis: Senior Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr"/>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr"/>
@@ -5421,12 +5429,12 @@
       <c r="H116" s="2" t="inlineStr"/>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481922002</t>
+          <t>https://weworkremotely.com/remote-jobs/visualis-senior-full-stack-developer</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -5443,7 +5451,7 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Backend Engineer, Analytics Instrumentation (Golang)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
@@ -5453,7 +5461,7 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, Bangalore</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr"/>
@@ -5467,7 +5475,7 @@
       </c>
       <c r="J117" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481929002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8517564002</t>
         </is>
       </c>
       <c r="K117" s="4" t="inlineStr">
@@ -5484,7 +5492,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Backend Engineer, Knowledge Graph (Rust)</t>
+          <t>Backend Engineer, Analytics Instrumentation (Golang)</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -5494,7 +5502,7 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, US</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr"/>
@@ -5508,7 +5516,7 @@
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8437754002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481922002</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -5525,7 +5533,7 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>Backend Engineer, Knowledge Graph (Rust)</t>
+          <t>Backend Engineer, Analytics Instrumentation (Golang)</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
@@ -5549,7 +5557,7 @@
       </c>
       <c r="J119" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481958002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481929002</t>
         </is>
       </c>
       <c r="K119" s="4" t="inlineStr">
@@ -5566,7 +5574,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Intermediate Backend Engineer (C), Tenant Scale: Git</t>
+          <t>Backend Engineer, Knowledge Graph (Rust)</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -5576,7 +5584,7 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, Canada; Remote, US</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr"/>
@@ -5590,7 +5598,7 @@
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8497793002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8437754002</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -5607,7 +5615,7 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>Intermediate Backend Engineer, Gitlab Delivery: Upgrades</t>
+          <t>Backend Engineer, Knowledge Graph (Rust)</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
@@ -5631,7 +5639,7 @@
       </c>
       <c r="J121" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8463951002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481958002</t>
         </is>
       </c>
       <c r="K121" s="4" t="inlineStr">
@@ -5648,7 +5656,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Intermediate Backend Engineer, SRM: Security Platform Management</t>
+          <t>Intermediate Backend Engineer (C), Tenant Scale: Git</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -5658,7 +5666,7 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr"/>
@@ -5672,7 +5680,7 @@
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8443325002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8497793002</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -5689,7 +5697,7 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>Intermediate Backend Engineer, SSCS: AI Governance</t>
+          <t>Intermediate Backend Engineer, Gitlab Delivery: Upgrades</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
@@ -5713,7 +5721,7 @@
       </c>
       <c r="J123" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480551002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8463951002</t>
         </is>
       </c>
       <c r="K123" s="4" t="inlineStr">
@@ -5730,7 +5738,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Intermediate Backend Engineer,  SSCS: Supply Chain</t>
+          <t>Intermediate Backend Engineer, SRM: Security Platform Management</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -5740,7 +5748,7 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr"/>
@@ -5754,7 +5762,7 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480565002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8443325002</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -5771,7 +5779,7 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Intermediate Backend Engineer, SSCS: AI Governance</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
@@ -5781,7 +5789,7 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Remote, EMEA</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr"/>
@@ -5795,7 +5803,7 @@
       </c>
       <c r="J125" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8464072002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480551002</t>
         </is>
       </c>
       <c r="K125" s="4" t="inlineStr">
@@ -5812,7 +5820,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (AI), Pipeline Execution</t>
+          <t>Intermediate Backend Engineer,  SSCS: Supply Chain</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -5822,7 +5830,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US-Southeast</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr"/>
@@ -5836,7 +5844,7 @@
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8514945002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480565002</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -5853,7 +5861,7 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Analytics Instrumentation (Golang)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
@@ -5863,7 +5871,7 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, US</t>
+          <t>Remote, EMEA</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr"/>
@@ -5877,7 +5885,7 @@
       </c>
       <c r="J127" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8451512002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8464072002</t>
         </is>
       </c>
       <c r="K127" s="4" t="inlineStr">
@@ -5894,7 +5902,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (C), Tenant Scale: Git</t>
+          <t>Senior Backend Engineer (AI), Pipeline Execution</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -5904,7 +5912,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US-Southeast</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr"/>
@@ -5918,7 +5926,7 @@
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8497791002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8514945002</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -5935,7 +5943,7 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Gitlab Delivery: Runway (Platform Engineering)</t>
+          <t>Senior Backend Engineer, Analytics Instrumentation (Golang)</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
@@ -5945,7 +5953,7 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Remote, Australia; Remote, India; Remote, Ireland; Remote, Japan; Remote, Netherlands; Remote, Singapore; Remote, United Kingdom</t>
+          <t>Remote, Canada; Remote, US</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr"/>
@@ -5959,7 +5967,7 @@
       </c>
       <c r="J129" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8324132002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8451512002</t>
         </is>
       </c>
       <c r="K129" s="4" t="inlineStr">
@@ -5976,7 +5984,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Gitlab Delivery: Upgrades</t>
+          <t>Senior Backend Engineer (C), Tenant Scale: Git</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -6000,7 +6008,7 @@
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8463933002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8497791002</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
@@ -6017,7 +6025,7 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer(Go), Continuous Delivery</t>
+          <t>Senior Backend Engineer, Gitlab Delivery: Runway (Platform Engineering)</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
@@ -6027,7 +6035,7 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, Australia; Remote, India; Remote, Ireland; Remote, Japan; Remote, Netherlands; Remote, Singapore; Remote, United Kingdom</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr"/>
@@ -6041,7 +6049,7 @@
       </c>
       <c r="J131" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8488966002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8324132002</t>
         </is>
       </c>
       <c r="K131" s="4" t="inlineStr">
@@ -6058,7 +6066,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer(Golang),Software Supply Chain Security: Auth Infrastructure</t>
+          <t>Senior Backend Engineer, Gitlab Delivery: Upgrades</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -6068,7 +6076,7 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Remote, Americas; Remote, APAC; Remote, Canada</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr"/>
@@ -6082,7 +6090,7 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8157520002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8463933002</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -6099,7 +6107,7 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (RoR), AST: Secret Detection</t>
+          <t>Senior Backend Engineer(Go), Continuous Delivery</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
@@ -6109,7 +6117,7 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr"/>
@@ -6123,7 +6131,7 @@
       </c>
       <c r="J133" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8432262002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8488966002</t>
         </is>
       </c>
       <c r="K133" s="4" t="inlineStr">
@@ -6140,7 +6148,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (RoR/Go), SSCS: Pipeline Security</t>
+          <t>Senior Backend Engineer(Golang),Software Supply Chain Security: Auth Infrastructure</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -6150,7 +6158,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
+          <t>Remote, Americas; Remote, APAC; Remote, Canada</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr"/>
@@ -6164,7 +6172,7 @@
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8432221002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8157520002</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
@@ -6181,7 +6189,7 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (RoR), SSCS: Authorization</t>
+          <t>Senior Backend Engineer (RoR), AST: Secret Detection</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
@@ -6191,7 +6199,7 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
+          <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr"/>
@@ -6205,7 +6213,7 @@
       </c>
       <c r="J135" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8457315002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8432262002</t>
         </is>
       </c>
       <c r="K135" s="4" t="inlineStr">
@@ -6222,7 +6230,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby or Golang), Tenant Scale; Cells Infrastructure</t>
+          <t>Senior Backend Engineer (RoR/Go), SSCS: Pipeline Security</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -6232,7 +6240,7 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Remote, APAC; Remote, Canada; Remote, EMEA; Remote, US</t>
+          <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr"/>
@@ -6246,7 +6254,7 @@
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8437148002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8432221002</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -6263,7 +6271,7 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, SSCS: AI Governance</t>
+          <t>Senior Backend Engineer (RoR), SSCS: Authorization</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
@@ -6273,7 +6281,7 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr"/>
@@ -6287,7 +6295,7 @@
       </c>
       <c r="J137" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480544002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8457315002</t>
         </is>
       </c>
       <c r="K137" s="4" t="inlineStr">
@@ -6304,7 +6312,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer,  SSCS: Supply Chain</t>
+          <t>Senior Backend Engineer (Ruby or Golang), Tenant Scale; Cells Infrastructure</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -6314,7 +6322,7 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, APAC; Remote, Canada; Remote, EMEA; Remote, US</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr"/>
@@ -6328,7 +6336,7 @@
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480580002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8437148002</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
@@ -6345,7 +6353,7 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Senior Fullstack Engineer (TypeScript), AI Engineering: Editor Extensions</t>
+          <t>Senior Backend Engineer, SSCS: AI Governance</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
@@ -6355,7 +6363,7 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Remote, APAC; Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US-Southeast</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr"/>
@@ -6369,7 +6377,7 @@
       </c>
       <c r="J139" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8452278002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480544002</t>
         </is>
       </c>
       <c r="K139" s="4" t="inlineStr">
@@ -6386,7 +6394,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer, Analytics Instrumentation (Golang)</t>
+          <t>Senior Backend Engineer,  SSCS: Supply Chain</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -6410,7 +6418,7 @@
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8508027002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480580002</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -6427,7 +6435,7 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer, AST: Composition Analysis</t>
+          <t>Senior Fullstack Engineer (TypeScript), AI Engineering: Editor Extensions</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
@@ -6437,7 +6445,7 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>Remote, Australia; Remote, Canada; Remote, India; Remote, Ireland; Remote, Israel; Remote, Japan; Remote, Netherlands; Remote, New Zealand; Remote, United Kingdom; Remote, US</t>
+          <t>Remote, APAC; Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US-Southeast</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr"/>
@@ -6451,7 +6459,7 @@
       </c>
       <c r="J141" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8478364002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8452278002</t>
         </is>
       </c>
       <c r="K141" s="4" t="inlineStr">
@@ -6468,7 +6476,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer, Developer Experience</t>
+          <t>Staff Backend Engineer, Analytics Instrumentation (Golang)</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -6478,7 +6486,7 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, United Kingdom; Remote, US</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr"/>
@@ -6492,7 +6500,7 @@
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8490477002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8508027002</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -6509,7 +6517,7 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer, Gitlab Delivery: Upgrades</t>
+          <t>Staff Backend Engineer, AST: Composition Analysis</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
@@ -6519,7 +6527,7 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, Australia; Remote, Canada; Remote, India; Remote, Ireland; Remote, Israel; Remote, Japan; Remote, Netherlands; Remote, New Zealand; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr"/>
@@ -6533,7 +6541,7 @@
       </c>
       <c r="J143" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8463922002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8478364002</t>
         </is>
       </c>
       <c r="K143" s="4" t="inlineStr">
@@ -6550,7 +6558,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer (Go), Continuous Delivery</t>
+          <t>Staff Backend Engineer, Developer Experience</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -6560,7 +6568,7 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, Canada; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr"/>
@@ -6574,7 +6582,7 @@
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8488961002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8490477002</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -6591,7 +6599,7 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer (Go), Software Supply Chain Security: Secrets Management</t>
+          <t>Staff Backend Engineer, Gitlab Delivery: Upgrades</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
@@ -6601,7 +6609,7 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr"/>
@@ -6615,7 +6623,7 @@
       </c>
       <c r="J145" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8432235002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8463922002</t>
         </is>
       </c>
       <c r="K145" s="4" t="inlineStr">
@@ -6632,7 +6640,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer, Knowledge Graph (Rust)</t>
+          <t>Staff Backend Engineer (Go), Continuous Delivery</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -6656,7 +6664,7 @@
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481945002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8488961002</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -6673,7 +6681,7 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer,  Software Supply Chain Security</t>
+          <t>Staff Backend Engineer (Go), Software Supply Chain Security: Secrets Management</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
@@ -6683,7 +6691,7 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr"/>
@@ -6697,7 +6705,7 @@
       </c>
       <c r="J147" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480559002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8432235002</t>
         </is>
       </c>
       <c r="K147" s="4" t="inlineStr">
@@ -6714,7 +6722,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer, SSCS: AI Governance</t>
+          <t>Staff Backend Engineer, Knowledge Graph (Rust)</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -6738,7 +6746,7 @@
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480531002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481945002</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
@@ -6755,7 +6763,7 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>Staff Backend (Python) Engineer, AI Engineering:Duo Chat</t>
+          <t>Staff Backend Engineer,  Software Supply Chain Security</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
@@ -6765,7 +6773,7 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>Remote, Americas; Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr"/>
@@ -6779,7 +6787,7 @@
       </c>
       <c r="J149" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8450446002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480559002</t>
         </is>
       </c>
       <c r="K149" s="4" t="inlineStr">
@@ -6796,17 +6804,17 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Senior Full Stack Product Software Engineer</t>
+          <t>Staff Backend Engineer, SSCS: AI Governance</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Dropbox</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Remote - Poland</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr"/>
@@ -6820,126 +6828,94 @@
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480531002</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>Staff Backend (Python) Engineer, AI Engineering:Duo Chat</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t>GitLab</t>
+        </is>
+      </c>
+      <c r="D151" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Americas; Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom</t>
+        </is>
+      </c>
+      <c r="E151" s="4" t="inlineStr"/>
+      <c r="F151" s="4" t="inlineStr"/>
+      <c r="G151" s="4" t="inlineStr"/>
+      <c r="H151" s="4" t="inlineStr"/>
+      <c r="I151" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J151" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8450446002</t>
+        </is>
+      </c>
+      <c r="K151" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Product Software Engineer</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Dropbox</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Remote - Poland</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr"/>
+      <c r="F152" s="2" t="inlineStr"/>
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr"/>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J152" s="3" t="inlineStr">
+        <is>
           <t>https://jobs.dropbox.com/listing/6449719?gh_jid=6449719</t>
         </is>
       </c>
-      <c r="K150" s="2" t="inlineStr">
+      <c r="K152" s="2" t="inlineStr">
         <is>
           <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>Dry Ground AI</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
-        <is>
-          <t>Brazil, Colombia, Philippines</t>
-        </is>
-      </c>
-      <c r="E151" s="2" t="inlineStr">
-        <is>
-          <t>full_time</t>
-        </is>
-      </c>
-      <c r="F151" s="2" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence</t>
-        </is>
-      </c>
-      <c r="G151" s="2" t="inlineStr">
-        <is>
-          <t>api, cloud, fullstack, python, AI/ML, automation, research, CI/CD, TensorFlow, spark, NLP, CMS, Pytorch, REST</t>
-        </is>
-      </c>
-      <c r="H151" s="2" t="inlineStr">
-        <is>
-          <t>$40- $60k</t>
-        </is>
-      </c>
-      <c r="I151" s="2" t="inlineStr">
-        <is>
-          <t>Remotive</t>
-        </is>
-      </c>
-      <c r="J151" s="3" t="inlineStr">
-        <is>
-          <t>https://remotive.com/remote-jobs/artificial-intelligence/ai-engineer-2089958</t>
-        </is>
-      </c>
-      <c r="K151" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B152" s="4" t="inlineStr">
-        <is>
-          <t>Senior Independent AI Engineer / Architect</t>
-        </is>
-      </c>
-      <c r="C152" s="4" t="inlineStr">
-        <is>
-          <t>A.Team</t>
-        </is>
-      </c>
-      <c r="D152" s="4" t="inlineStr">
-        <is>
-          <t>Americas, Europe, Israel</t>
-        </is>
-      </c>
-      <c r="E152" s="4" t="inlineStr">
-        <is>
-          <t>contract</t>
-        </is>
-      </c>
-      <c r="F152" s="4" t="inlineStr">
-        <is>
-          <t>Software Development</t>
-        </is>
-      </c>
-      <c r="G152" s="4" t="inlineStr">
-        <is>
-          <t>go, UI/UX, wordpress, chat, apple, testing, catalyst</t>
-        </is>
-      </c>
-      <c r="H152" s="4" t="inlineStr">
-        <is>
-          <t>$120 - $170 /hour</t>
-        </is>
-      </c>
-      <c r="I152" s="4" t="inlineStr">
-        <is>
-          <t>Remotive</t>
-        </is>
-      </c>
-      <c r="J152" s="5" t="inlineStr">
-        <is>
-          <t>https://remotive.com/remote-jobs/software-development/senior-independent-ai-engineer-architect-1919266</t>
-        </is>
-      </c>
-      <c r="K152" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6951,37 +6927,37 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>Senior Independent Software Developer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>A.Team</t>
+          <t>Dry Ground AI</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Americas, Europe, Israel</t>
+          <t>Brazil, Colombia, Philippines</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>contract</t>
+          <t>full_time</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>Software Development</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>go, wordpress, chat, apple, testing, catalyst</t>
+          <t>api, cloud, fullstack, python, AI/ML, automation, research, CI/CD, TensorFlow, spark, NLP, CMS, Pytorch, REST</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>$90 - $150 /hour</t>
+          <t>$40- $60k</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr">
@@ -6991,7 +6967,7 @@
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
-          <t>https://remotive.com/remote-jobs/software-development/senior-independent-software-developer-1919265</t>
+          <t>https://remotive.com/remote-jobs/artificial-intelligence/ai-engineer-2089958</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -7008,17 +6984,17 @@
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>Senior Full-stack React Developer</t>
+          <t>Senior Independent AI Engineer / Architect</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>Lemon.io</t>
+          <t>A.Team</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>Americas, Europe, Asia, Oceania</t>
+          <t>Americas, Europe, Israel</t>
         </is>
       </c>
       <c r="E154" s="4" t="inlineStr">
@@ -7033,10 +7009,14 @@
       </c>
       <c r="G154" s="4" t="inlineStr">
         <is>
-          <t>.Net, android, AWS, azure, backend, C, C#, C++, data science, fullstack, golang, ios, java, javascript, node.js, php, python, react, react js, ruby/rails, shopify, video, blockchain, AI/ML, react native, rust, unity, spring, data analysis, laravel, solidity, flask, Typescript , angular , GCP, data engineering, Symfony, startup, marketplace, next.js</t>
-        </is>
-      </c>
-      <c r="H154" s="4" t="inlineStr"/>
+          <t>go, UI/UX, wordpress, chat, apple, testing, catalyst</t>
+        </is>
+      </c>
+      <c r="H154" s="4" t="inlineStr">
+        <is>
+          <t>$120 - $170 /hour</t>
+        </is>
+      </c>
       <c r="I154" s="4" t="inlineStr">
         <is>
           <t>Remotive</t>
@@ -7044,7 +7024,7 @@
       </c>
       <c r="J154" s="5" t="inlineStr">
         <is>
-          <t>https://remotive.com/remote-jobs/software-development/senior-full-stack-react-developer-2088711</t>
+          <t>https://remotive.com/remote-jobs/software-development/senior-independent-ai-engineer-architect-1919266</t>
         </is>
       </c>
       <c r="K154" s="4" t="inlineStr">
@@ -7061,22 +7041,22 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Tech Lead Full-Stack Rails Engineer</t>
+          <t>Senior Independent Software Developer</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>Mitre Media</t>
+          <t>A.Team</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>USA, Canada, USA timezones</t>
+          <t>Americas, Europe, Israel</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>full_time</t>
+          <t>contract</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
@@ -7086,12 +7066,12 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>api, CSS, docker, elasticsearch, fullstack, html, javascript, kubernetes, postgresql, react, ror, ruby/rails, AI/ML, CAD, advertising, Redis, ES6, web applications, MySQL, NLP, fintech, Micro services, github, system architecture</t>
+          <t>go, wordpress, chat, apple, testing, catalyst</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>$170k - $200k</t>
+          <t>$90 - $150 /hour</t>
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr">
@@ -7101,7 +7081,7 @@
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
-          <t>https://remotive.com/remote-jobs/software-development/tech-lead-full-stack-rails-engineer-2069746</t>
+          <t>https://remotive.com/remote-jobs/software-development/senior-independent-software-developer-1919265</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -7118,17 +7098,17 @@
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>Senior Frontend Developer</t>
+          <t>Senior Full-stack React Developer</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>Sanctuary Computer</t>
+          <t>Lemon.io</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>LATAM, Asia</t>
+          <t>Americas, Europe, Asia, Oceania</t>
         </is>
       </c>
       <c r="E156" s="4" t="inlineStr">
@@ -7143,14 +7123,10 @@
       </c>
       <c r="G156" s="4" t="inlineStr">
         <is>
-          <t>api, backend, CSS, ecommerce, frontend, fullstack, graphql, postgresql, redux, security, seo, shopify, open source, paas, product management, documentation, mentoring, Typescript , Redis, web applications, cypress, data visualization, firebase, IoT, engineering management, runtime, responsive, prismic, testing, next.js, CMS, jest, REST, web sockets, performance optimization</t>
-        </is>
-      </c>
-      <c r="H156" s="4" t="inlineStr">
-        <is>
-          <t>$80k - $120k</t>
-        </is>
-      </c>
+          <t>.Net, android, AWS, azure, backend, C, C#, C++, data science, fullstack, golang, ios, java, javascript, node.js, php, python, react, react js, ruby/rails, shopify, video, blockchain, AI/ML, react native, rust, unity, spring, data analysis, laravel, solidity, flask, Typescript , angular , GCP, data engineering, Symfony, startup, marketplace, next.js</t>
+        </is>
+      </c>
+      <c r="H156" s="4" t="inlineStr"/>
       <c r="I156" s="4" t="inlineStr">
         <is>
           <t>Remotive</t>
@@ -7158,7 +7134,7 @@
       </c>
       <c r="J156" s="5" t="inlineStr">
         <is>
-          <t>https://remotive.com/remote-jobs/software-development/senior-frontend-developer-2088707</t>
+          <t>https://remotive.com/remote-jobs/software-development/senior-full-stack-react-developer-2088711</t>
         </is>
       </c>
       <c r="K156" s="4" t="inlineStr">
@@ -7175,17 +7151,17 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>Fullstack Developer (US - ET)</t>
+          <t>Tech Lead Full-Stack Rails Engineer</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>Chooose</t>
+          <t>Mitre Media</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>USA, Canada, USA timezones</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
@@ -7200,10 +7176,14 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>api, azure, fullstack, python, react, saas, AI/ML, project management, documentation, Typescript , computer science, diversity, insurance</t>
-        </is>
-      </c>
-      <c r="H157" s="2" t="inlineStr"/>
+          <t>api, CSS, docker, elasticsearch, fullstack, html, javascript, kubernetes, postgresql, react, ror, ruby/rails, AI/ML, CAD, advertising, Redis, ES6, web applications, MySQL, NLP, fintech, Micro services, github, system architecture</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>$170k - $200k</t>
+        </is>
+      </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
           <t>Remotive</t>
@@ -7211,7 +7191,7 @@
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
-          <t>https://remotive.com/remote-jobs/software-development/fullstack-developer-us-et-2088706</t>
+          <t>https://remotive.com/remote-jobs/software-development/tech-lead-full-stack-rails-engineer-2069746</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -7228,31 +7208,47 @@
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning Manager, Notifications Relevance</t>
+          <t>Senior Frontend Developer</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Sanctuary Computer</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
-        </is>
-      </c>
-      <c r="E158" s="4" t="inlineStr"/>
-      <c r="F158" s="4" t="inlineStr"/>
-      <c r="G158" s="4" t="inlineStr"/>
-      <c r="H158" s="4" t="inlineStr"/>
+          <t>LATAM, Asia</t>
+        </is>
+      </c>
+      <c r="E158" s="4" t="inlineStr">
+        <is>
+          <t>contract</t>
+        </is>
+      </c>
+      <c r="F158" s="4" t="inlineStr">
+        <is>
+          <t>Software Development</t>
+        </is>
+      </c>
+      <c r="G158" s="4" t="inlineStr">
+        <is>
+          <t>api, backend, CSS, ecommerce, frontend, fullstack, graphql, postgresql, redux, security, seo, shopify, open source, paas, product management, documentation, mentoring, Typescript , Redis, web applications, cypress, data visualization, firebase, IoT, engineering management, runtime, responsive, prismic, testing, next.js, CMS, jest, REST, web sockets, performance optimization</t>
+        </is>
+      </c>
+      <c r="H158" s="4" t="inlineStr">
+        <is>
+          <t>$80k - $120k</t>
+        </is>
+      </c>
       <c r="I158" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>Remotive</t>
         </is>
       </c>
       <c r="J158" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7846885</t>
+          <t>https://remotive.com/remote-jobs/software-development/senior-frontend-developer-2088707</t>
         </is>
       </c>
       <c r="K158" s="4" t="inlineStr">
@@ -7269,31 +7265,43 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>Senior Staff ML Engineer, Search &amp; Recommendation</t>
+          <t>Fullstack Developer (US - ET)</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Chooose</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
-        </is>
-      </c>
-      <c r="E159" s="2" t="inlineStr"/>
-      <c r="F159" s="2" t="inlineStr"/>
-      <c r="G159" s="2" t="inlineStr"/>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>full_time</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>Software Development</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>api, azure, fullstack, python, react, saas, AI/ML, project management, documentation, Typescript , computer science, diversity, insurance</t>
+        </is>
+      </c>
       <c r="H159" s="2" t="inlineStr"/>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>Remotive</t>
         </is>
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7833622</t>
+          <t>https://remotive.com/remote-jobs/software-development/fullstack-developer-us-et-2088706</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
@@ -7310,17 +7318,17 @@
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Machine Learning Manager, Notifications Relevance</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>Remote - US</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E160" s="4" t="inlineStr"/>
@@ -7334,7 +7342,7 @@
       </c>
       <c r="J160" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7059734</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7846885</t>
         </is>
       </c>
       <c r="K160" s="4" t="inlineStr">
@@ -7351,17 +7359,17 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Staff ML Engineer, Search &amp; Recommendation</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>Remote - US</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr"/>
@@ -7375,7 +7383,7 @@
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7702644</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7833622</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
@@ -7392,7 +7400,7 @@
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>Principal Machine Learning &amp; Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
@@ -7416,7 +7424,7 @@
       </c>
       <c r="J162" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7155492</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7059734</t>
         </is>
       </c>
       <c r="K162" s="4" t="inlineStr">
@@ -7433,7 +7441,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>Principal, Product Manager - AI / LLM</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -7457,7 +7465,7 @@
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7619420</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7702644</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
@@ -7474,7 +7482,7 @@
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>Product Engineer (Backend)</t>
+          <t>Principal Machine Learning &amp; Data Engineer</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
@@ -7498,7 +7506,7 @@
       </c>
       <c r="J164" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7671815</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7155492</t>
         </is>
       </c>
       <c r="K164" s="4" t="inlineStr">
@@ -7515,7 +7523,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>Senior Manager, Machine Learning</t>
+          <t>Principal, Product Manager - AI / LLM</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -7539,7 +7547,7 @@
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7066029</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7619420</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
@@ -7556,7 +7564,7 @@
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>Staff Data Scientist</t>
+          <t>Product Engineer (Backend)</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
@@ -7580,7 +7588,7 @@
       </c>
       <c r="J166" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7821458</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7671815</t>
         </is>
       </c>
       <c r="K166" s="4" t="inlineStr">
@@ -7597,7 +7605,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>Staff, Data Scientist (L4) GTM Data Science &amp; Analytics</t>
+          <t>Senior Manager, Machine Learning</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -7621,7 +7629,7 @@
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7851920</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7066029</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
@@ -7638,7 +7646,7 @@
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer</t>
+          <t>Staff Data Scientist</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
@@ -7662,7 +7670,7 @@
       </c>
       <c r="J168" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7061880</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7821458</t>
         </is>
       </c>
       <c r="K168" s="4" t="inlineStr">
@@ -7679,7 +7687,7 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer (L4)</t>
+          <t>Staff, Data Scientist (L4) GTM Data Science &amp; Analytics</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -7689,7 +7697,7 @@
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>Remote - India</t>
+          <t>Remote - US</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr"/>
@@ -7703,7 +7711,7 @@
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7520997</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7851920</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
@@ -7720,39 +7728,31 @@
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>Senior Python Developer - Django (m/w/d)</t>
+          <t>Staff Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>sync.blue® GmbH</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>Haltern am See</t>
-        </is>
-      </c>
-      <c r="E170" s="4" t="inlineStr">
-        <is>
-          <t>berufserfahren</t>
-        </is>
-      </c>
+          <t>Remote - US</t>
+        </is>
+      </c>
+      <c r="E170" s="4" t="inlineStr"/>
       <c r="F170" s="4" t="inlineStr"/>
-      <c r="G170" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Software Development</t>
-        </is>
-      </c>
+      <c r="G170" s="4" t="inlineStr"/>
       <c r="H170" s="4" t="inlineStr"/>
       <c r="I170" s="4" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J170" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/syncblue-gmbh/senior-python-developer-django-haltern-am-see-16238</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7061880</t>
         </is>
       </c>
       <c r="K170" s="4" t="inlineStr">
@@ -7769,39 +7769,31 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>Freelance Senior AI Product Manager</t>
+          <t>Staff Machine Learning Engineer (L4)</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>nexamind GmbH</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E171" s="2" t="inlineStr">
-        <is>
-          <t>Freelance, professional / experienced</t>
-        </is>
-      </c>
+          <t>Remote - India</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr"/>
       <c r="F171" s="2" t="inlineStr"/>
-      <c r="G171" s="2" t="inlineStr">
-        <is>
-          <t>Remote, Product Management</t>
-        </is>
-      </c>
+      <c r="G171" s="2" t="inlineStr"/>
       <c r="H171" s="2" t="inlineStr"/>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/nexamind-gmbh/freelance-senior-ai-product-manager-berlin-73613</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7520997</t>
         </is>
       </c>
       <c r="K171" s="2" t="inlineStr">
@@ -7818,17 +7810,17 @@
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>Senior Full-Stack-Entwickler:in React / TypeScript / .NET  100 % Remote, KI-First</t>
+          <t>Senior Python Developer - Django (m/w/d)</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>yourMAIL GmbH</t>
+          <t>sync.blue® GmbH</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Haltern am See</t>
         </is>
       </c>
       <c r="E172" s="4" t="inlineStr">
@@ -7850,7 +7842,7 @@
       </c>
       <c r="J172" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/yourmail-gmbh/senior-full-stack-entwicklerin-react-typescript-net-100-remote-ki-first-berlin-21152</t>
+          <t>https://www.arbeitnow.com/jobs/companies/syncblue-gmbh/senior-python-developer-django-haltern-am-see-16238</t>
         </is>
       </c>
       <c r="K172" s="4" t="inlineStr">
@@ -7867,12 +7859,12 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>Senior Frontend-Entwickler:in React / TypeScript, 100 % Remote, KI-First</t>
+          <t>Freelance Senior AI Product Manager</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>yourMAIL GmbH</t>
+          <t>nexamind GmbH</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
@@ -7882,13 +7874,13 @@
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>berufserfahren</t>
+          <t>Freelance, professional / experienced</t>
         </is>
       </c>
       <c r="F173" s="2" t="inlineStr"/>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>Remote, Software Development</t>
+          <t>Remote, Product Management</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr"/>
@@ -7899,7 +7891,7 @@
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/yourmail-gmbh/senior-frontend-entwicklerin-react-typescript-100-remote-ki-first-berlin-288218</t>
+          <t>https://www.arbeitnow.com/jobs/companies/nexamind-gmbh/freelance-senior-ai-product-manager-berlin-73613</t>
         </is>
       </c>
       <c r="K173" s="2" t="inlineStr">
@@ -7916,24 +7908,28 @@
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>Full-Stack Entwickler (m/w/d) - .NET 100% Remote</t>
+          <t>Senior Full-Stack-Entwickler:in React / TypeScript / .NET  100 % Remote, KI-First</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>FNTIO</t>
+          <t>yourMAIL GmbH</t>
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>Frankfurt am Main</t>
-        </is>
-      </c>
-      <c r="E174" s="4" t="inlineStr"/>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="E174" s="4" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
       <c r="F174" s="4" t="inlineStr"/>
       <c r="G174" s="4" t="inlineStr">
         <is>
-          <t>Remote, Consulting, Engineering</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr"/>
@@ -7944,7 +7940,7 @@
       </c>
       <c r="J174" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/fntio/full-stack-entwickler-net-100-remote-frankfurt-am-main-122380</t>
+          <t>https://www.arbeitnow.com/jobs/companies/yourmail-gmbh/senior-full-stack-entwicklerin-react-typescript-net-100-remote-ki-first-berlin-21152</t>
         </is>
       </c>
       <c r="K174" s="4" t="inlineStr">
@@ -7961,12 +7957,12 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Frontend-Entwickler:in React / TypeScript, 100 % Remote, KI-First</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>Phantasma Labs</t>
+          <t>yourMAIL GmbH</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
@@ -7974,11 +7970,15 @@
           <t>Berlin</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr"/>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
       <c r="F175" s="2" t="inlineStr"/>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>Remote, Engineering</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr"/>
@@ -7989,7 +7989,7 @@
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/phantasma-labs/machine-learning-engineer-berlin-303955</t>
+          <t>https://www.arbeitnow.com/jobs/companies/yourmail-gmbh/senior-frontend-entwicklerin-react-typescript-100-remote-ki-first-berlin-288218</t>
         </is>
       </c>
       <c r="K175" s="2" t="inlineStr">
@@ -8006,28 +8006,24 @@
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>Technical Data Manager (m/w/d)</t>
+          <t>Full-Stack Entwickler (m/w/d) - .NET 100% Remote</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>BMF Media Information Technology GmbH</t>
+          <t>FNTIO</t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>Augsburg</t>
-        </is>
-      </c>
-      <c r="E176" s="4" t="inlineStr">
-        <is>
-          <t>berufserfahren</t>
-        </is>
-      </c>
+          <t>Frankfurt am Main</t>
+        </is>
+      </c>
+      <c r="E176" s="4" t="inlineStr"/>
       <c r="F176" s="4" t="inlineStr"/>
       <c r="G176" s="4" t="inlineStr">
         <is>
-          <t>Remote, Technical Documentation</t>
+          <t>Remote, Consulting, Engineering</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr"/>
@@ -8038,7 +8034,7 @@
       </c>
       <c r="J176" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/bmf-media-information-technology-gmbh/technical-data-manager-augsburg-42188</t>
+          <t>https://www.arbeitnow.com/jobs/companies/fntio/full-stack-entwickler-net-100-remote-frankfurt-am-main-122380</t>
         </is>
       </c>
       <c r="K176" s="4" t="inlineStr">
@@ -8055,28 +8051,24 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>Data Integration &amp; API Engineer m/w/d - Bi &amp; Data Automation</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>loyos bi GmbH</t>
+          <t>Phantasma Labs</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>Hamburg</t>
-        </is>
-      </c>
-      <c r="E177" s="2" t="inlineStr">
-        <is>
-          <t>berufserfahren</t>
-        </is>
-      </c>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr"/>
       <c r="F177" s="2" t="inlineStr"/>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>Remote, Software Development</t>
+          <t>Remote, Engineering</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr"/>
@@ -8087,7 +8079,7 @@
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/loyos-bi-gmbh/data-integration-api-engineer-bi-data-automation-hamburg-66228</t>
+          <t>https://www.arbeitnow.com/jobs/companies/phantasma-labs/machine-learning-engineer-berlin-303955</t>
         </is>
       </c>
       <c r="K177" s="2" t="inlineStr">
@@ -8104,28 +8096,28 @@
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Technical Data Manager (m/w/d)</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>Coding Partners</t>
+          <t>BMF Media Information Technology GmbH</t>
         </is>
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="E178" s="4" t="inlineStr">
         <is>
-          <t>professional / experienced</t>
+          <t>berufserfahren</t>
         </is>
       </c>
       <c r="F178" s="4" t="inlineStr"/>
       <c r="G178" s="4" t="inlineStr">
         <is>
-          <t>Remote, Software Development</t>
+          <t>Remote, Technical Documentation</t>
         </is>
       </c>
       <c r="H178" s="4" t="inlineStr"/>
@@ -8136,7 +8128,7 @@
       </c>
       <c r="J178" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/coding-partners/senior-full-stack-engineer-berlin-391720</t>
+          <t>https://www.arbeitnow.com/jobs/companies/bmf-media-information-technology-gmbh/technical-data-manager-augsburg-42188</t>
         </is>
       </c>
       <c r="K178" s="4" t="inlineStr">
@@ -8153,17 +8145,17 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>Laravel Developer (m/w/d) - AI-First PropTech</t>
+          <t>Data Integration &amp; API Engineer m/w/d - Bi &amp; Data Automation</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>Immovara GmbH</t>
+          <t>loyos bi GmbH</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>Korntal-Münchingen</t>
+          <t>Hamburg</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
@@ -8185,7 +8177,7 @@
       </c>
       <c r="J179" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/immovara-gmbh/laravel-developer-ai-first-proptech-korntal-munchingen-471269</t>
+          <t>https://www.arbeitnow.com/jobs/companies/loyos-bi-gmbh/data-integration-api-engineer-bi-data-automation-hamburg-66228</t>
         </is>
       </c>
       <c r="K179" s="2" t="inlineStr">
@@ -8202,22 +8194,22 @@
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>Fullstack Softwareentwickler (m/w/d)</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>TecFox GmbH</t>
+          <t>Coding Partners</t>
         </is>
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>Braunschweig</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="E180" s="4" t="inlineStr">
         <is>
-          <t>berufserfahren</t>
+          <t>professional / experienced</t>
         </is>
       </c>
       <c r="F180" s="4" t="inlineStr"/>
@@ -8234,7 +8226,7 @@
       </c>
       <c r="J180" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/tecfox-gmbh/fullstack-softwareentwickler-braunschweig-405178</t>
+          <t>https://www.arbeitnow.com/jobs/companies/coding-partners/senior-full-stack-engineer-berlin-391720</t>
         </is>
       </c>
       <c r="K180" s="4" t="inlineStr">
@@ -8251,17 +8243,17 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>Frontend Softwareentwickler (m/w/d)</t>
+          <t>Laravel Developer (m/w/d) - AI-First PropTech</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>TecFox GmbH</t>
+          <t>Immovara GmbH</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>Braunschweig</t>
+          <t>Korntal-Münchingen</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
@@ -8283,7 +8275,7 @@
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/tecfox-gmbh/frontend-softwareentwickler-braunschweig-341792</t>
+          <t>https://www.arbeitnow.com/jobs/companies/immovara-gmbh/laravel-developer-ai-first-proptech-korntal-munchingen-471269</t>
         </is>
       </c>
       <c r="K181" s="2" t="inlineStr">
@@ -8300,17 +8292,17 @@
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>Fullstack-Developer*in (m/w/d) Web &amp; AI Automation</t>
+          <t>Fullstack Softwareentwickler (m/w/d)</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>NeoBird Digital</t>
+          <t>TecFox GmbH</t>
         </is>
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>Nuremberg</t>
+          <t>Braunschweig</t>
         </is>
       </c>
       <c r="E182" s="4" t="inlineStr">
@@ -8332,7 +8324,7 @@
       </c>
       <c r="J182" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/neobird-digital/fullstack-developerin-web-ai-automation-nuremberg-157752</t>
+          <t>https://www.arbeitnow.com/jobs/companies/tecfox-gmbh/fullstack-softwareentwickler-braunschweig-405178</t>
         </is>
       </c>
       <c r="K182" s="4" t="inlineStr">
@@ -8349,24 +8341,28 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer / Backend &amp; Frontend - Bootstrapped SaaS Startup (m/w/d) remote in EU</t>
+          <t>Frontend Softwareentwickler (m/w/d)</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>DatAds</t>
+          <t>TecFox GmbH</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>Cologne</t>
-        </is>
-      </c>
-      <c r="E183" s="2" t="inlineStr"/>
+          <t>Braunschweig</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
       <c r="F183" s="2" t="inlineStr"/>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>Remote, IT</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr"/>
@@ -8377,7 +8373,7 @@
       </c>
       <c r="J183" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-bootstrapped-saas-startup-remote-in-eu-cologne-82307</t>
+          <t>https://www.arbeitnow.com/jobs/companies/tecfox-gmbh/frontend-softwareentwickler-braunschweig-341792</t>
         </is>
       </c>
       <c r="K183" s="2" t="inlineStr">
@@ -8394,24 +8390,28 @@
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer / Rest APIs / Cloud / TailwindCSS / SaaS Startup (m/w/d) remote in EU</t>
+          <t>Fullstack-Developer*in (m/w/d) Web &amp; AI Automation</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>DatAds</t>
+          <t>NeoBird Digital</t>
         </is>
       </c>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t>Cologne</t>
-        </is>
-      </c>
-      <c r="E184" s="4" t="inlineStr"/>
+          <t>Nuremberg</t>
+        </is>
+      </c>
+      <c r="E184" s="4" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
       <c r="F184" s="4" t="inlineStr"/>
       <c r="G184" s="4" t="inlineStr">
         <is>
-          <t>Remote, IT</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H184" s="4" t="inlineStr"/>
@@ -8422,7 +8422,7 @@
       </c>
       <c r="J184" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-bootstrapped-saas-startup-remote-in-eu-cologne-38634</t>
+          <t>https://www.arbeitnow.com/jobs/companies/neobird-digital/fullstack-developerin-web-ai-automation-nuremberg-157752</t>
         </is>
       </c>
       <c r="K184" s="4" t="inlineStr">
@@ -8439,7 +8439,7 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer / Node.js / TypeScript / React / Azure - AdTech SaaS Startup (m/w/d) remote</t>
+          <t>Full-Stack Software Engineer / Backend &amp; Frontend - Bootstrapped SaaS Startup (m/w/d) remote in EU</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
@@ -8467,7 +8467,7 @@
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-adtech-saas-startup-remote-cologne-263746</t>
+          <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-bootstrapped-saas-startup-remote-in-eu-cologne-82307</t>
         </is>
       </c>
       <c r="K185" s="2" t="inlineStr">
@@ -8484,24 +8484,20 @@
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>Senior DevOps / Platform Engineer (f/m/x)</t>
+          <t>Full-Stack Software Engineer / Rest APIs / Cloud / TailwindCSS / SaaS Startup (m/w/d) remote in EU</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>MAIA</t>
+          <t>DatAds</t>
         </is>
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>Leipzig</t>
-        </is>
-      </c>
-      <c r="E186" s="4" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
+          <t>Cologne</t>
+        </is>
+      </c>
+      <c r="E186" s="4" t="inlineStr"/>
       <c r="F186" s="4" t="inlineStr"/>
       <c r="G186" s="4" t="inlineStr">
         <is>
@@ -8516,7 +8512,7 @@
       </c>
       <c r="J186" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/maia/senior-devops-platform-engineer-leipzig-388068</t>
+          <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-bootstrapped-saas-startup-remote-in-eu-cologne-38634</t>
         </is>
       </c>
       <c r="K186" s="4" t="inlineStr">
@@ -8528,40 +8524,40 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer AI Infrastructure</t>
+          <t>Full-Stack Software Engineer / Node.js / TypeScript / React / Azure - AdTech SaaS Startup (m/w/d) remote</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>Andromeda Cluster</t>
+          <t>DatAds</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Cologne</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr"/>
       <c r="F187" s="2" t="inlineStr"/>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>design, training, technical, software, code, manager, financial, cloud, management, lead, senior, operations, reliability, go, health, engineer, engineering, linux, digital nomad</t>
+          <t>Remote, IT</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr"/>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-senior-site-reliability-engineer-ai-infrastructure-andromeda-cluster-1131375</t>
+          <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-adtech-saas-startup-remote-cologne-263746</t>
         </is>
       </c>
       <c r="K187" s="2" t="inlineStr">
@@ -8573,40 +8569,44 @@
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>Senior Financial Analyst Digital Assets</t>
+          <t>Senior DevOps / Platform Engineer (f/m/x)</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>Exodus Movement Inc.</t>
+          <t>MAIA</t>
         </is>
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E188" s="4" t="inlineStr"/>
+          <t>Leipzig</t>
+        </is>
+      </c>
+      <c r="E188" s="4" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
       <c r="F188" s="4" t="inlineStr"/>
       <c r="G188" s="4" t="inlineStr">
         <is>
-          <t>analyst, cryptocurrency, support, financial, investment, finance, senior, non tech</t>
+          <t>Remote, IT</t>
         </is>
       </c>
       <c r="H188" s="4" t="inlineStr"/>
       <c r="I188" s="4" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J188" s="5" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-senior-financial-analyst-digital-assets-exodus-movement-inc-1131374</t>
+          <t>https://www.arbeitnow.com/jobs/companies/maia/senior-devops-platform-engineer-leipzig-388068</t>
         </is>
       </c>
       <c r="K188" s="4" t="inlineStr">
@@ -8623,24 +8623,24 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>Front End Full Stack Developer</t>
+          <t>Senior Site Reliability Engineer AI Infrastructure</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>Honor Foods</t>
+          <t>Andromeda Cluster</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>Philadelphia, PA</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr"/>
       <c r="F189" s="2" t="inlineStr"/>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>developer, front-end, ui, code, web, operational, backend, digital nomad</t>
+          <t>design, training, technical, software, code, manager, financial, cloud, management, lead, senior, operations, reliability, go, health, engineer, engineering, linux, digital nomad</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr"/>
@@ -8651,7 +8651,7 @@
       </c>
       <c r="J189" s="3" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-front-end-full-stack-developer-honor-foods-1131370</t>
+          <t>https://remoteOK.com/remote-jobs/remote-senior-site-reliability-engineer-ai-infrastructure-andromeda-cluster-1131375</t>
         </is>
       </c>
       <c r="K189" s="2" t="inlineStr">
@@ -8668,10 +8668,14 @@
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>Wing Assistant: Full-Stack Developer</t>
-        </is>
-      </c>
-      <c r="C190" s="4" t="inlineStr"/>
+          <t>Senior Financial Analyst Digital Assets</t>
+        </is>
+      </c>
+      <c r="C190" s="4" t="inlineStr">
+        <is>
+          <t>Exodus Movement Inc.</t>
+        </is>
+      </c>
       <c r="D190" s="4" t="inlineStr">
         <is>
           <t>Remote</t>
@@ -8679,16 +8683,20 @@
       </c>
       <c r="E190" s="4" t="inlineStr"/>
       <c r="F190" s="4" t="inlineStr"/>
-      <c r="G190" s="4" t="inlineStr"/>
+      <c r="G190" s="4" t="inlineStr">
+        <is>
+          <t>analyst, cryptocurrency, support, financial, investment, finance, senior, non tech</t>
+        </is>
+      </c>
       <c r="H190" s="4" t="inlineStr"/>
       <c r="I190" s="4" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J190" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/wing-assistant-full-stack-developer</t>
+          <t>https://remoteOK.com/remote-jobs/remote-senior-financial-analyst-digital-assets-exodus-movement-inc-1131374</t>
         </is>
       </c>
       <c r="K190" s="4" t="inlineStr">
@@ -8705,27 +8713,35 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>Qventus: Product Designer</t>
-        </is>
-      </c>
-      <c r="C191" s="2" t="inlineStr"/>
+          <t>Front End Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>Honor Foods</t>
+        </is>
+      </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Philadelphia, PA</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr"/>
       <c r="F191" s="2" t="inlineStr"/>
-      <c r="G191" s="2" t="inlineStr"/>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>developer, front-end, ui, code, web, operational, backend, digital nomad</t>
+        </is>
+      </c>
       <c r="H191" s="2" t="inlineStr"/>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J191" s="3" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/qventus-product-designer</t>
+          <t>https://remoteOK.com/remote-jobs/remote-front-end-full-stack-developer-honor-foods-1131370</t>
         </is>
       </c>
       <c r="K191" s="2" t="inlineStr">
@@ -8742,7 +8758,7 @@
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>Socure: Senior Product Marketing Manager</t>
+          <t>Wing Assistant: Full-Stack Developer</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr"/>
@@ -8762,7 +8778,7 @@
       </c>
       <c r="J192" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/socure-senior-product-marketing-manager</t>
+          <t>https://weworkremotely.com/remote-jobs/wing-assistant-full-stack-developer</t>
         </is>
       </c>
       <c r="K192" s="4" t="inlineStr">
@@ -8779,7 +8795,7 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>Blueprint: Product Designer</t>
+          <t>Qventus: Product Designer</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr"/>
@@ -8799,7 +8815,7 @@
       </c>
       <c r="J193" s="3" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/blueprint-product-designer</t>
+          <t>https://weworkremotely.com/remote-jobs/qventus-product-designer</t>
         </is>
       </c>
       <c r="K193" s="2" t="inlineStr">
@@ -8816,7 +8832,7 @@
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>Interop Labs: Product Marketing Manager</t>
+          <t>Socure: Senior Product Marketing Manager</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr"/>
@@ -8836,7 +8852,7 @@
       </c>
       <c r="J194" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/interop-labs-product-marketing-manager</t>
+          <t>https://weworkremotely.com/remote-jobs/socure-senior-product-marketing-manager</t>
         </is>
       </c>
       <c r="K194" s="4" t="inlineStr">
@@ -8853,17 +8869,13 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Link</t>
-        </is>
-      </c>
-      <c r="C195" s="2" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
+          <t>Blueprint: Product Designer</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr"/>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>Toronto, Remote in Canada</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr"/>
@@ -8872,12 +8884,12 @@
       <c r="H195" s="2" t="inlineStr"/>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J195" s="3" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=6447175</t>
+          <t>https://weworkremotely.com/remote-jobs/blueprint-product-designer</t>
         </is>
       </c>
       <c r="K195" s="2" t="inlineStr">
@@ -8894,17 +8906,13 @@
       </c>
       <c r="B196" s="4" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="C196" s="4" t="inlineStr">
-        <is>
-          <t>Reddit</t>
-        </is>
-      </c>
+          <t>Interop Labs: Product Marketing Manager</t>
+        </is>
+      </c>
+      <c r="C196" s="4" t="inlineStr"/>
       <c r="D196" s="4" t="inlineStr">
         <is>
-          <t>Remote - Ontario, Canada</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E196" s="4" t="inlineStr"/>
@@ -8913,12 +8921,12 @@
       <c r="H196" s="4" t="inlineStr"/>
       <c r="I196" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J196" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/6960833</t>
+          <t>https://weworkremotely.com/remote-jobs/interop-labs-product-marketing-manager</t>
         </is>
       </c>
       <c r="K196" s="4" t="inlineStr">
@@ -8935,17 +8943,17 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Full Stack Engineer, Link</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Toronto, Remote in Canada</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr"/>
@@ -8959,10 +8967,92 @@
       </c>
       <c r="J197" s="3" t="inlineStr">
         <is>
+          <t>https://stripe.com/jobs/search?gh_jid=6447175</t>
+        </is>
+      </c>
+      <c r="K197" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B198" s="4" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="C198" s="4" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="D198" s="4" t="inlineStr">
+        <is>
+          <t>Remote - Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="E198" s="4" t="inlineStr"/>
+      <c r="F198" s="4" t="inlineStr"/>
+      <c r="G198" s="4" t="inlineStr"/>
+      <c r="H198" s="4" t="inlineStr"/>
+      <c r="I198" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J198" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/6960833</t>
+        </is>
+      </c>
+      <c r="K198" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr"/>
+      <c r="F199" s="2" t="inlineStr"/>
+      <c r="G199" s="2" t="inlineStr"/>
+      <c r="H199" s="2" t="inlineStr"/>
+      <c r="I199" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J199" s="3" t="inlineStr">
+        <is>
           <t>https://job-boards.greenhouse.io/reddit/jobs/6960831</t>
         </is>
       </c>
-      <c r="K197" s="2" t="inlineStr">
+      <c r="K199" s="2" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>

--- a/remote_jobs.xlsx
+++ b/remote_jobs.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K199"/>
+  <dimension ref="A1:K201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -523,123 +523,115 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Senior Frontend Developer:in (Angular)</t>
+          <t>Staff Machine Learning Engineer, Consumer</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Wintama IT Solutions GmbH</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Grünwald</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Remote, Software Development</t>
-        </is>
-      </c>
+      <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/wintama-it-solutions-gmbh/senior-frontend-developerin-angular-grunwald-41193</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7747244</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Tooling Engineer</t>
+          <t>Shopify Developer - Fullstack (m/w/d) in Vollzeit | Remote</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Unikraft</t>
+          <t>we-site GmbH - Shopify Agentur</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hamburg</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr"/>
       <c r="F3" s="4" t="inlineStr"/>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>golang, cloud, engineer</t>
+          <t>Remote, Web Development</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr"/>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-tooling-engineer-unikraft-1131540</t>
+          <t>https://www.arbeitnow.com/jobs/companies/we-site-gmbh-shopify-agentur/shopify-developer-fullstack-in-vollzeit-remote-hamburg-428318</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Senior Sofrware Engineer - Full Stack</t>
+          <t>Senior Frontend Developer:in (Angular)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Parto Group GmbH</t>
+          <t>Wintama IT Solutions GmbH</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Hamburg</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
+          <t>Grünwald</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Remote, Engineering</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -650,12 +642,12 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/parto-group-gmbh/senior-sofrware-engineer-full-stack-hamburg-207489</t>
+          <t>https://www.arbeitnow.com/jobs/companies/wintama-it-solutions-gmbh/senior-frontend-developerin-angular-grunwald-41193</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
     </row>
@@ -667,73 +659,73 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Product Ownership &amp; Operations)</t>
+          <t>Tooling Engineer</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Yoffix</t>
+          <t>Unikraft</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Contract, professional / experienced</t>
-        </is>
-      </c>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr"/>
       <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>Remote, Software Development</t>
+          <t>golang, cloud, engineer</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/yoffix/senior-full-stack-engineer-product-ownership-operations-berlin-437578</t>
+          <t>https://remoteOK.com/remote-jobs/remote-tooling-engineer-unikraft-1131540</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer / Backend &amp; Frontend - Bootstrapped SaaS Startup (m/w/d) remote in EU</t>
+          <t>Senior Sofrware Engineer - Full Stack</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>DatAds</t>
+          <t>Parto Group GmbH</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Cologne</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr"/>
+          <t>Hamburg</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Remote, IT</t>
+          <t>Remote, Engineering</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -744,90 +736,90 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-bootstrapped-saas-startup-remote-in-eu-cologne-266336</t>
+          <t>https://www.arbeitnow.com/jobs/companies/parto-group-gmbh/senior-sofrware-engineer-full-stack-hamburg-207489</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Asset Administration Operations Specialist</t>
+          <t>Senior Full Stack Engineer (Product Ownership &amp; Operations)</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Forge Global</t>
+          <t>Yoffix</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Denver</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr"/>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Contract, professional / experienced</t>
+        </is>
+      </c>
       <c r="F7" s="4" t="inlineStr"/>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>travel, financial, operations, non tech</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>$21 - $24</t>
-        </is>
-      </c>
+          <t>Remote, Software Development</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr"/>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-asset-administration-operations-specialist-forge-global-1131523</t>
+          <t>https://www.arbeitnow.com/jobs/companies/yoffix/senior-full-stack-engineer-product-ownership-operations-berlin-437578</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer (TypeScript &amp; AWS) (m/w/d)</t>
+          <t>Full-Stack Software Engineer / Backend &amp; Frontend - Bootstrapped SaaS Startup (m/w/d) remote in EU</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>vOffice Software</t>
+          <t>DatAds</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Hamburg</t>
+          <t>Cologne</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Remote, Software Development</t>
+          <t>Remote, IT</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
@@ -838,12 +830,12 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/voffice-software/senior-cloud-software-engineer-typescript-aws-hamburg-431856</t>
+          <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-bootstrapped-saas-startup-remote-in-eu-cologne-266336</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
@@ -855,44 +847,44 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer RoR (all identities)</t>
+          <t>Asset Administration Operations Specialist</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Caspar Health</t>
+          <t>Forge Global</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
+          <t>Denver</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
       <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>Remote, Software Development</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr"/>
+          <t>travel, financial, operations, non tech</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>$21 - $24</t>
+        </is>
+      </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/caspar-health/senior-backend-engineer-ror-all-identities-berlin-7147</t>
+          <t>https://remoteOK.com/remote-jobs/remote-asset-administration-operations-specialist-forge-global-1131523</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
@@ -904,24 +896,20 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Python Software Engineer - Machine Learning Systems (m/f/d)</t>
+          <t>Senior Cloud Software Engineer (TypeScript &amp; AWS) (m/w/d)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>CUJU</t>
+          <t>vOffice Software</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Frankenthal</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
+          <t>Hamburg</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
@@ -936,7 +924,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/cuju/python-software-engineer-machine-learning-systems-frankenthal-183273</t>
+          <t>https://www.arbeitnow.com/jobs/companies/voffice-software/senior-cloud-software-engineer-typescript-aws-hamburg-431856</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -953,28 +941,28 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>AI Algorithm Developer Medical Imaging (m/w/d)</t>
+          <t>Senior Backend Engineer RoR (all identities)</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>citema systems GmbH</t>
+          <t>Caspar Health</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>berufserfahren</t>
+          <t>professional / experienced</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr"/>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>Remote, IT</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
@@ -985,7 +973,7 @@
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/citema-systems-gmbh/ai-algorithm-developer-medical-imaging-munich-91573</t>
+          <t>https://www.arbeitnow.com/jobs/companies/caspar-health/senior-backend-engineer-ror-all-identities-berlin-7147</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
@@ -997,40 +985,44 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Python Software Engineer - Machine Learning Systems (m/f/d)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Civitech</t>
+          <t>CUJU</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Austin, TX or Remote</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr"/>
+          <t>Frankenthal</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>python, support, code, cloud, analytics, engineer, engineering, full-time</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-analytics-engineer-civitech-1131512</t>
+          <t>https://www.arbeitnow.com/jobs/companies/cuju/python-software-engineer-machine-learning-systems-frankenthal-183273</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1042,40 +1034,44 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Tech Lead</t>
+          <t>AI Algorithm Developer Medical Imaging (m/w/d)</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Zensurance</t>
+          <t>citema systems GmbH</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Toronto, ON</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr"/>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
       <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>design, system, front-end, back-end, security, training, full-stack, docker, technical, support, software, testing, test, growth, code, web, scrum, devops, javascript, education, strategy, management, lead, senior, health, engineering, digital nomad</t>
+          <t>Remote, IT</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-tech-lead-zensurance-1131509</t>
+          <t>https://www.arbeitnow.com/jobs/companies/citema-systems-gmbh/ai-algorithm-developer-medical-imaging-munich-91573</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
@@ -1092,31 +1088,35 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Senior Full-stack Symfony Developer</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr"/>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Civitech</t>
+        </is>
+      </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Austin, TX or Remote</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>symfony, php, javascript, vuejs</t>
+          <t>python, support, code, cloud, analytics, engineer, engineering, full-time</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>WorkingNomads</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>https://www.workingnomads.com/job/go/1587815/</t>
+          <t>https://remoteOK.com/remote-jobs/remote-analytics-engineer-civitech-1131512</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1133,31 +1133,35 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Senior Staff Machine Learning Engineer, Feed Relevance</t>
+          <t>Tech Lead</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Zensurance</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Toronto, ON</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr"/>
       <c r="F15" s="4" t="inlineStr"/>
-      <c r="G15" s="4" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>design, system, front-end, back-end, security, training, full-stack, docker, technical, support, software, testing, test, growth, code, web, scrum, devops, javascript, education, strategy, management, lead, senior, health, engineering, digital nomad</t>
+        </is>
+      </c>
       <c r="H15" s="4" t="inlineStr"/>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7908786</t>
+          <t>https://remoteOK.com/remote-jobs/remote-tech-lead-zensurance-1131509</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
@@ -1174,40 +1178,36 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Sidebase Open-Source Contributor &amp; Senior TS Dev (f/m/d)</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Sidestream</t>
-        </is>
-      </c>
+          <t>Senior Full-stack Symfony Developer</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Cologne</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Remote, Software Development</t>
+          <t>symfony, php, javascript, vuejs</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>WorkingNomads</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/sidestream/sidebase-open-source-contributor-senior-ts-dev-cologne-317648</t>
+          <t>https://www.workingnomads.com/job/go/1587815/</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -1219,40 +1219,36 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Senior Typescript Developer (f/m/d)</t>
+          <t>Senior Staff Machine Learning Engineer, Feed Relevance</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Sidestream</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Cologne</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr"/>
       <c r="F17" s="4" t="inlineStr"/>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Software Development</t>
-        </is>
-      </c>
+      <c r="G17" s="4" t="inlineStr"/>
       <c r="H17" s="4" t="inlineStr"/>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/sidestream/senior-typescript-developer-cologne-220463</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7908786</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -1264,24 +1260,24 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Senior AI-Engineer / Agent-Architekt (m/w/d)</t>
+          <t>Sidebase Open-Source Contributor &amp; Senior TS Dev (f/m/d)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Neurawork GmbH &amp; Co. KG</t>
+          <t>Sidestream</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Ampfing</t>
+          <t>Cologne</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Remote, IT</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
@@ -1292,7 +1288,7 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/neurawork-gmbh-co-kg/senior-ai-engineer-agent-architekt-ampfing-390691</t>
+          <t>https://www.arbeitnow.com/jobs/companies/sidestream/sidebase-open-source-contributor-senior-ts-dev-cologne-317648</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1309,28 +1305,24 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Senior AI Consultant / Machine Learning Engineer (m/w/d) Public Sector | &gt;90% REMOTE</t>
+          <t>Senior Typescript Developer (f/m/d)</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Bridgency HR Management GbR</t>
+          <t>Sidestream</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Usingen</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>berufserfahren</t>
-        </is>
-      </c>
+          <t>Cologne</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr"/>
       <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>Remote, Consulting, Engineering</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
@@ -1341,7 +1333,7 @@
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/bridgency-hr-management-gbr/senior-ai-consultant-machine-learning-engineer-public-sector-90-remote-usingen-94077</t>
+          <t>https://www.arbeitnow.com/jobs/companies/sidestream/senior-typescript-developer-cologne-220463</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
@@ -1358,28 +1350,24 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Werkstudent (m/w/d) Frontend Development &amp; KI-Integration (20h/Woche)</t>
+          <t>Senior AI-Engineer / Agent-Architekt (m/w/d)</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>MEvents Cross Media GmbH</t>
+          <t>Neurawork GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>hilfstätigkeit / student</t>
-        </is>
-      </c>
+          <t>Ampfing</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Remote, Software Development</t>
+          <t>Remote, IT</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
@@ -1390,7 +1378,7 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/mevents-cross-media-gmbh/werkstudent-frontend-development-ki-integration-20h-woche-berlin-378282</t>
+          <t>https://www.arbeitnow.com/jobs/companies/neurawork-gmbh-co-kg/senior-ai-engineer-agent-architekt-ampfing-390691</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1402,40 +1390,44 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Consultant / Machine Learning Engineer (m/w/d) Public Sector | &gt;90% REMOTE</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Valon Mortgage</t>
+          <t>Bridgency HR Management GbR</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr"/>
+          <t>Usingen</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
       <c r="F21" s="4" t="inlineStr"/>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>design, saas, python, architect, technical, support, cloud, strategy, management, senior, operations, operational, analytics, reliability, go, engineer, engineering, digital nomad</t>
+          <t>Remote, Consulting, Engineering</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-senior-data-engineer-valon-mortgage-1131504</t>
+          <t>https://www.arbeitnow.com/jobs/companies/bridgency-hr-management-gbr/senior-ai-consultant-machine-learning-engineer-public-sector-90-remote-usingen-94077</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
@@ -1447,139 +1439,135 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Senior AI Agent Architect / AI Automation Architect</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr"/>
+          <t>Werkstudent (m/w/d) Frontend Development &amp; KI-Integration (20h/Woche)</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>MEvents Cross Media GmbH</t>
+        </is>
+      </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr"/>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>hilfstätigkeit / student</t>
+        </is>
+      </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>artificial intelligence, python, machine learning, engineer, communication</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/mevents-cross-media-gmbh/werkstudent-frontend-development-ki-integration-20h-woche-berlin-378282</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Valon Mortgage</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr"/>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>design, saas, python, architect, technical, support, cloud, strategy, management, senior, operations, operational, analytics, reliability, go, engineer, engineering, digital nomad</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr"/>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-senior-data-engineer-valon-mortgage-1131504</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Senior AI Agent Architect / AI Automation Architect</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>artificial intelligence, python, machine learning, engineer, communication</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
           <t>WorkingNomads</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="J24" s="3" t="inlineStr">
         <is>
           <t>https://www.workingnomads.com/job/go/1585195/</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>2026-05-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Weiterbildung: Data Science &amp; Business Analytics (IHK) (m/w/d) - Remote</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>DataSmart Point GmbH</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Apprenticeship</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr"/>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>Remote, Data Scientist</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr"/>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/datasmart-point-gmbh/weiterbildung-data-science-business-analytics-ihk-remote-berlin-23738</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Karrierestart in Data &amp; AI - IHK Data Analyst (m/w/d) - 100 % Online</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>DataSmart Point GmbH</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>Apprenticeship</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr"/>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Data Scientist</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr"/>
-      <c r="I24" s="4" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J24" s="5" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/datasmart-point-gmbh/karrierestart-in-data-ai-ihk-data-analyst-100-online-berlin-138911</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
         </is>
       </c>
     </row>
@@ -1591,28 +1579,28 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Rockstardevelopers: Senior Fullstack Entwickler (m/w/d) mit Projekterfahrung Deutsche Bahn oder DB Systel</t>
+          <t>Weiterbildung: Data Science &amp; Business Analytics (IHK) (m/w/d) - Remote</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Rockstardevelopers GmbH</t>
+          <t>DataSmart Point GmbH</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>berufserfahren</t>
+          <t>Apprenticeship</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Remote, Software Development</t>
+          <t>Remote, Data Scientist</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr"/>
@@ -1623,7 +1611,7 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/rockstardevelopers-gmbh/rockstardevelopers-senior-fullstack-entwickler-mit-projekterfahrung-deutsche-bahn-oder-db-systel-stuttgart-354361</t>
+          <t>https://www.arbeitnow.com/jobs/companies/datasmart-point-gmbh/weiterbildung-data-science-business-analytics-ihk-remote-berlin-23738</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1640,24 +1628,28 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Full-Stack AI Engineer (Computer Vision &amp; Back-end Focus)</t>
+          <t>Karrierestart in Data &amp; AI - IHK Data Analyst (m/w/d) - 100 % Online</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>StellDirVor GmbH</t>
+          <t>DataSmart Point GmbH</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr"/>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Apprenticeship</t>
+        </is>
+      </c>
       <c r="F26" s="4" t="inlineStr"/>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>Remote, Software Development</t>
+          <t>Remote, Data Scientist</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
@@ -1668,7 +1660,7 @@
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/stelldirvor-gmbh/full-stack-ai-engineer-computer-vision-back-end-focus-munich-122395</t>
+          <t>https://www.arbeitnow.com/jobs/companies/datasmart-point-gmbh/karrierestart-in-data-ai-ihk-data-analyst-100-online-berlin-138911</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
@@ -1680,40 +1672,44 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Rockstardevelopers: Senior Fullstack Entwickler (m/w/d) mit Projekterfahrung Deutsche Bahn oder DB Systel</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Prove</t>
+          <t>Rockstardevelopers GmbH</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr"/>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>software, security, senior, engineer, engineering</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr"/>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-senior-software-engineer-prove-1131482</t>
+          <t>https://www.arbeitnow.com/jobs/companies/rockstardevelopers-gmbh/rockstardevelopers-senior-fullstack-entwickler-mit-projekterfahrung-deutsche-bahn-oder-db-systel-stuttgart-354361</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1725,40 +1721,40 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Full-Stack AI Engineer (Computer Vision &amp; Back-end Focus)</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Akuity</t>
+          <t>StellDirVor GmbH</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr"/>
       <c r="F28" s="4" t="inlineStr"/>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>saas, developer, software, code, devops, senior, engineer, engineering, backend, digital nomad</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-senior-backend-engineer-akuity-1131479</t>
+          <t>https://www.arbeitnow.com/jobs/companies/stelldirvor-gmbh/full-stack-ai-engineer-computer-vision-back-end-focus-munich-122395</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
@@ -1775,24 +1771,24 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Medical Affairs Solutions Manager UK</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Sorcero</t>
+          <t>Prove</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>manager, growth, operations, biotech</t>
+          <t>software, security, senior, engineer, engineering</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr"/>
@@ -1803,7 +1799,7 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-medical-affairs-solutions-manager-uk-sorcero-1131475</t>
+          <t>https://remoteOK.com/remote-jobs/remote-senior-software-engineer-prove-1131482</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1820,31 +1816,35 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Dropbox</t>
+          <t>Akuity</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Remote - Canada: Select locations</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr"/>
       <c r="F30" s="4" t="inlineStr"/>
-      <c r="G30" s="4" t="inlineStr"/>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>saas, developer, software, code, devops, senior, engineer, engineering, backend, digital nomad</t>
+        </is>
+      </c>
       <c r="H30" s="4" t="inlineStr"/>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7762007?gh_jid=7762007</t>
+          <t>https://remoteOK.com/remote-jobs/remote-senior-backend-engineer-akuity-1131479</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
@@ -1861,31 +1861,35 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Medical Affairs Solutions Manager UK</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Dropbox</t>
+          <t>Sorcero</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Remote - US: Select locations</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="2" t="inlineStr"/>
-      <c r="G31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>manager, growth, operations, biotech</t>
+        </is>
+      </c>
       <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7762004?gh_jid=7762004</t>
+          <t>https://remoteOK.com/remote-jobs/remote-medical-affairs-solutions-manager-uk-sorcero-1131475</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1912,7 +1916,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Remote - Mexico</t>
+          <t>Remote - Canada: Select locations</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr"/>
@@ -1926,7 +1930,7 @@
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7762009?gh_jid=7762009</t>
+          <t>https://jobs.dropbox.com/listing/7762007?gh_jid=7762007</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
@@ -1943,7 +1947,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Frontend Product Software Engineer, Web DX</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1953,7 +1957,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Remote - Mexico</t>
+          <t>Remote - US: Select locations</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
@@ -1967,7 +1971,7 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7580431?gh_jid=7580431</t>
+          <t>https://jobs.dropbox.com/listing/7762004?gh_jid=7762004</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -1984,7 +1988,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer, Dash Experiences</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -1994,7 +1998,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Remote - US: Select locations</t>
+          <t>Remote - Mexico</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr"/>
@@ -2008,7 +2012,7 @@
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7569140?gh_jid=7569140</t>
+          <t>https://jobs.dropbox.com/listing/7762009?gh_jid=7762009</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
@@ -2025,7 +2029,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer, Dash Experiences</t>
+          <t>Frontend Product Software Engineer, Web DX</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2049,7 +2053,7 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7569145?gh_jid=7569145</t>
+          <t>https://jobs.dropbox.com/listing/7580431?gh_jid=7580431</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2066,7 +2070,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Product Software Engineer, Payments</t>
+          <t>Full Stack Software Engineer, Dash Experiences</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -2076,7 +2080,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Remote - Poland</t>
+          <t>Remote - US: Select locations</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr"/>
@@ -2090,7 +2094,7 @@
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7812915?gh_jid=7812915</t>
+          <t>https://jobs.dropbox.com/listing/7569140?gh_jid=7569140</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
@@ -2107,7 +2111,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, AI Products</t>
+          <t>Full Stack Software Engineer, Dash Experiences</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2117,7 +2121,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Remote - Canada: Select locations</t>
+          <t>Remote - Mexico</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr"/>
@@ -2131,7 +2135,7 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7789389?gh_jid=7789389</t>
+          <t>https://jobs.dropbox.com/listing/7569145?gh_jid=7569145</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2148,7 +2152,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, AI Products</t>
+          <t>Senior Backend Product Software Engineer, Payments</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -2158,7 +2162,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Remote - Canada: Select locations</t>
+          <t>Remote - Poland</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr"/>
@@ -2172,7 +2176,7 @@
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7729764?gh_jid=7729764</t>
+          <t>https://jobs.dropbox.com/listing/7812915?gh_jid=7812915</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
@@ -2199,7 +2203,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Remote - US: Select locations</t>
+          <t>Remote - Canada: Select locations</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr"/>
@@ -2213,7 +2217,7 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7729761?gh_jid=7729761</t>
+          <t>https://jobs.dropbox.com/listing/7789389?gh_jid=7789389</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2240,7 +2244,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Remote - US: Select locations</t>
+          <t>Remote - Canada: Select locations</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr"/>
@@ -2254,7 +2258,7 @@
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7789386?gh_jid=7789386</t>
+          <t>https://jobs.dropbox.com/listing/7729764?gh_jid=7729764</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
@@ -2271,7 +2275,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Dash Agentic AI</t>
+          <t>Senior Data Scientist, AI Products</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2281,7 +2285,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Remote - Canada: Select locations</t>
+          <t>Remote - US: Select locations</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr"/>
@@ -2295,7 +2299,7 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7644890?gh_jid=7644890</t>
+          <t>https://jobs.dropbox.com/listing/7729761?gh_jid=7729761</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -2312,7 +2316,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Dash Agentic AI</t>
+          <t>Senior Data Scientist, AI Products</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -2322,7 +2326,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Remote - US: All locations</t>
+          <t>Remote - US: Select locations</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr"/>
@@ -2336,7 +2340,7 @@
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7644886?gh_jid=7644886</t>
+          <t>https://jobs.dropbox.com/listing/7789386?gh_jid=7789386</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
@@ -2353,7 +2357,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Staff Backend Product Software Engineer, Commerce Platform</t>
+          <t>Senior Machine Learning Engineer, Dash Agentic AI</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2363,7 +2367,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Remote - Mexico</t>
+          <t>Remote - Canada: Select locations</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
@@ -2377,7 +2381,7 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7759733?gh_jid=7759733</t>
+          <t>https://jobs.dropbox.com/listing/7644890?gh_jid=7644890</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -2394,7 +2398,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Staff Backend Product Software Engineer, Commerce Platform</t>
+          <t>Senior Machine Learning Engineer, Dash Agentic AI</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -2404,7 +2408,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Remote - US: Select locations</t>
+          <t>Remote - US: All locations</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr"/>
@@ -2418,7 +2422,7 @@
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7759728?gh_jid=7759728</t>
+          <t>https://jobs.dropbox.com/listing/7644886?gh_jid=7644886</t>
         </is>
       </c>
       <c r="K44" s="4" t="inlineStr">
@@ -2445,7 +2449,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Remote - Canada: Select locations</t>
+          <t>Remote - Mexico</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -2459,7 +2463,7 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7759731?gh_jid=7759731</t>
+          <t>https://jobs.dropbox.com/listing/7759733?gh_jid=7759733</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -2476,7 +2480,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Staff Backend Product Software Engineer, Core</t>
+          <t>Staff Backend Product Software Engineer, Commerce Platform</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -2500,7 +2504,7 @@
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7421121?gh_jid=7421121</t>
+          <t>https://jobs.dropbox.com/listing/7759728?gh_jid=7759728</t>
         </is>
       </c>
       <c r="K46" s="4" t="inlineStr">
@@ -2517,7 +2521,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Staff Backend Product Software Engineer, Core</t>
+          <t>Staff Backend Product Software Engineer, Commerce Platform</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2541,7 +2545,7 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7421124?gh_jid=7421124</t>
+          <t>https://jobs.dropbox.com/listing/7759731?gh_jid=7759731</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -2558,7 +2562,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Staff Fullstack Product Software Engineer, Dash</t>
+          <t>Staff Backend Product Software Engineer, Core</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -2568,7 +2572,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Remote - Canada: Select locations</t>
+          <t>Remote - US: Select locations</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr"/>
@@ -2582,7 +2586,7 @@
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7551548?gh_jid=7551548</t>
+          <t>https://jobs.dropbox.com/listing/7421121?gh_jid=7421121</t>
         </is>
       </c>
       <c r="K48" s="4" t="inlineStr">
@@ -2599,7 +2603,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Staff Fullstack Product Software Engineer, Dash</t>
+          <t>Staff Backend Product Software Engineer, Core</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2609,7 +2613,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Remote - US: Select locations</t>
+          <t>Remote - Canada: Select locations</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr"/>
@@ -2623,7 +2627,7 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7551545?gh_jid=7551545</t>
+          <t>https://jobs.dropbox.com/listing/7421124?gh_jid=7421124</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -2640,7 +2644,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Staff Full Stack Software Engineer, Churn</t>
+          <t>Staff Fullstack Product Software Engineer, Dash</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -2650,7 +2654,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Remote - Poland</t>
+          <t>Remote - Canada: Select locations</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr"/>
@@ -2664,7 +2668,7 @@
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7421131?gh_jid=7421131</t>
+          <t>https://jobs.dropbox.com/listing/7551548?gh_jid=7551548</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
@@ -2681,7 +2685,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Staff Fullstack Software Engineer, Growth Monetization</t>
+          <t>Staff Fullstack Product Software Engineer, Dash</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2705,7 +2709,7 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7421150?gh_jid=7421150</t>
+          <t>https://jobs.dropbox.com/listing/7551545?gh_jid=7551545</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -2722,7 +2726,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Staff Fullstack Software Engineer, Growth Monetization</t>
+          <t>Staff Full Stack Software Engineer, Churn</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -2732,7 +2736,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Remote - Canada: Select locations</t>
+          <t>Remote - Poland</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr"/>
@@ -2746,7 +2750,7 @@
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7421153?gh_jid=7421153</t>
+          <t>https://jobs.dropbox.com/listing/7421131?gh_jid=7421131</t>
         </is>
       </c>
       <c r="K52" s="4" t="inlineStr">
@@ -2763,13 +2767,17 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>WALTER: Senior Fullstack Engineer (Ruby+React)</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr"/>
+          <t>Staff Fullstack Software Engineer, Growth Monetization</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Dropbox</t>
+        </is>
+      </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote - US: Select locations</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr"/>
@@ -2778,17 +2786,17 @@
       <c r="H53" s="2" t="inlineStr"/>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/walter-senior-fullstack-engineer-ruby-react</t>
+          <t>https://jobs.dropbox.com/listing/7421150?gh_jid=7421150</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
     </row>
@@ -2800,13 +2808,17 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>WALTER: Full-Stack Engineering Lead</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr"/>
+          <t>Staff Fullstack Software Engineer, Growth Monetization</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>Dropbox</t>
+        </is>
+      </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote - Canada: Select locations</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr"/>
@@ -2815,17 +2827,17 @@
       <c r="H54" s="4" t="inlineStr"/>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/walter-full-stack-engineering-lead</t>
+          <t>https://jobs.dropbox.com/listing/7421153?gh_jid=7421153</t>
         </is>
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
     </row>
@@ -2837,17 +2849,13 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Frontend Product Software Engineer, Design Systems</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Dropbox</t>
-        </is>
-      </c>
+          <t>WALTER: Senior Fullstack Engineer (Ruby+React)</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr"/>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Remote - Mexico</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr"/>
@@ -2856,12 +2864,12 @@
       <c r="H55" s="2" t="inlineStr"/>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7862086?gh_jid=7862086</t>
+          <t>https://weworkremotely.com/remote-jobs/walter-senior-fullstack-engineer-ruby-react</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -2873,40 +2881,32 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Lead AI Engineer &amp; Technical Architect</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>Bold Business</t>
-        </is>
-      </c>
+          <t>WALTER: Full-Stack Engineering Lead</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr"/>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>India, Latin America, Philippines</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr"/>
       <c r="F56" s="4" t="inlineStr"/>
-      <c r="G56" s="4" t="inlineStr">
-        <is>
-          <t>architect, technical, lead, engineer</t>
-        </is>
-      </c>
+      <c r="G56" s="4" t="inlineStr"/>
       <c r="H56" s="4" t="inlineStr"/>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-lead-ai-engineer-technical-architect-bold-business-1131461</t>
+          <t>https://weworkremotely.com/remote-jobs/walter-full-stack-engineering-lead</t>
         </is>
       </c>
       <c r="K56" s="4" t="inlineStr">
@@ -2918,40 +2918,36 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer Showroom</t>
+          <t>Frontend Product Software Engineer, Design Systems</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Higharc</t>
+          <t>Dropbox</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote - Mexico</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr"/>
       <c r="F57" s="2" t="inlineStr"/>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>software, design, 3d, full-stack, support, ux, manager, api, engineer, engineering, backend, digital nomad</t>
-        </is>
-      </c>
+      <c r="G57" s="2" t="inlineStr"/>
       <c r="H57" s="2" t="inlineStr"/>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-software-engineer-showroom-higharc-1131457</t>
+          <t>https://jobs.dropbox.com/listing/7862086?gh_jid=7862086</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -2968,31 +2964,35 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Protocol Review Specialist</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr"/>
+          <t>Lead AI Engineer &amp; Technical Architect</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>Bold Business</t>
+        </is>
+      </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>India, Latin America, Philippines</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr"/>
       <c r="F58" s="4" t="inlineStr"/>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>communication, phone, english</t>
+          <t>architect, technical, lead, engineer</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr"/>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t>WorkingNomads</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>https://www.workingnomads.com/job/go/1580747/</t>
+          <t>https://remoteOK.com/remote-jobs/remote-lead-ai-engineer-technical-architect-bold-business-1131461</t>
         </is>
       </c>
       <c r="K58" s="4" t="inlineStr">
@@ -3009,31 +3009,35 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Staff AI Engineer - Notebooks</t>
+          <t>Software Engineer Showroom</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Datadog</t>
+          <t>Higharc</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Portugal, Remote</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr"/>
       <c r="F59" s="2" t="inlineStr"/>
-      <c r="G59" s="2" t="inlineStr"/>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>software, design, 3d, full-stack, support, ux, manager, api, engineer, engineering, backend, digital nomad</t>
+        </is>
+      </c>
       <c r="H59" s="2" t="inlineStr"/>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>https://careers.datadoghq.com/detail/7627445/?gh_jid=7627445</t>
+          <t>https://remoteOK.com/remote-jobs/remote-software-engineer-showroom-higharc-1131457</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -3050,31 +3054,31 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Staff AI Engineer - Notebooks</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>Datadog</t>
-        </is>
-      </c>
+          <t>Protocol Review Specialist</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr"/>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>France, Remote; Germany, Remote; Ireland, Remote; Italy, Remote; Spain, Remote; Switzerland, Remote</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr"/>
       <c r="F60" s="4" t="inlineStr"/>
-      <c r="G60" s="4" t="inlineStr"/>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>communication, phone, english</t>
+        </is>
+      </c>
       <c r="H60" s="4" t="inlineStr"/>
       <c r="I60" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WorkingNomads</t>
         </is>
       </c>
       <c r="J60" s="5" t="inlineStr">
         <is>
-          <t>https://careers.datadoghq.com/detail/7627429/?gh_jid=7627429</t>
+          <t>https://www.workingnomads.com/job/go/1580747/</t>
         </is>
       </c>
       <c r="K60" s="4" t="inlineStr">
@@ -3091,17 +3095,17 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Ads Conversion Modeling, Machine Learning Engineering Manager</t>
+          <t>Staff AI Engineer - Notebooks</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Datadog</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Portugal, Remote</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr"/>
@@ -3115,7 +3119,7 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7792848</t>
+          <t>https://careers.datadoghq.com/detail/7627445/?gh_jid=7627445</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -3132,17 +3136,17 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Data Scientist, Ads</t>
+          <t>Staff AI Engineer - Notebooks</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Datadog</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Remote - British Columbia, Canada</t>
+          <t>France, Remote; Germany, Remote; Ireland, Remote; Italy, Remote; Spain, Remote; Switzerland, Remote</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr"/>
@@ -3156,7 +3160,7 @@
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7607124</t>
+          <t>https://careers.datadoghq.com/detail/7627429/?gh_jid=7627429</t>
         </is>
       </c>
       <c r="K62" s="4" t="inlineStr">
@@ -3173,7 +3177,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Data Scientist, Ads</t>
+          <t>Ads Conversion Modeling, Machine Learning Engineering Manager</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3197,7 +3201,7 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/6580815</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7792848</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -3214,7 +3218,7 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Scientist, Ads</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -3224,7 +3228,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Remote - Ontario, Canada</t>
+          <t>Remote - British Columbia, Canada</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr"/>
@@ -3238,7 +3242,7 @@
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7131934</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7607124</t>
         </is>
       </c>
       <c r="K64" s="4" t="inlineStr">
@@ -3255,7 +3259,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Scientist, Ads</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3279,7 +3283,7 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7131932</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/6580815</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -3296,7 +3300,7 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Principal Data Scientist, Ads</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -3306,7 +3310,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Remote - Ontario, Canada</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr"/>
@@ -3320,7 +3324,7 @@
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7330347</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7131934</t>
         </is>
       </c>
       <c r="K66" s="4" t="inlineStr">
@@ -3337,7 +3341,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Ads</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -3347,7 +3351,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Remote - British Columbia, Canada</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr"/>
@@ -3361,7 +3365,7 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7607121</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7131932</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -3378,7 +3382,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Ads</t>
+          <t>Principal Data Scientist, Ads</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -3402,7 +3406,7 @@
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/6042236</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7330347</t>
         </is>
       </c>
       <c r="K68" s="4" t="inlineStr">
@@ -3419,7 +3423,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Consumer</t>
+          <t>Senior Data Scientist, Ads</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -3429,7 +3433,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Remote - British Columbia, Canada</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr"/>
@@ -3443,7 +3447,7 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7275414</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7607121</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -3460,7 +3464,7 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Senior  Machine Learning Engineer, ML Training Platform</t>
+          <t>Senior Data Scientist, Ads</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -3484,7 +3488,7 @@
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7074776</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/6042236</t>
         </is>
       </c>
       <c r="K70" s="4" t="inlineStr">
@@ -3501,7 +3505,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Systems Engineer</t>
+          <t>Senior Data Scientist, Consumer</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -3525,7 +3529,7 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7731772</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7275414</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -3542,7 +3546,7 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, GenAI Platform</t>
+          <t>Senior  Machine Learning Engineer, ML Training Platform</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -3566,7 +3570,7 @@
       </c>
       <c r="J72" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7753480</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7074776</t>
         </is>
       </c>
       <c r="K72" s="4" t="inlineStr">
@@ -3583,7 +3587,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Senior Staff Machine Learning Engineer, GenAI Platform</t>
+          <t>Senior Machine Learning Systems Engineer</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -3607,7 +3611,7 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7772274</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7731772</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -3624,7 +3628,7 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Staff Data Scientist, Ads</t>
+          <t>Senior Software Engineer, GenAI Platform</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -3634,7 +3638,7 @@
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>Remote - British Columbia, Canada</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr"/>
@@ -3648,7 +3652,7 @@
       </c>
       <c r="J74" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7721851</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7753480</t>
         </is>
       </c>
       <c r="K74" s="4" t="inlineStr">
@@ -3665,7 +3669,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Staff Data Scientist, Ads</t>
+          <t>Senior Staff Machine Learning Engineer, GenAI Platform</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -3689,7 +3693,7 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7721787</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7772274</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -3706,7 +3710,7 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Staff Data Scientist, Consumer</t>
+          <t>Staff Data Scientist, Ads</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
@@ -3716,7 +3720,7 @@
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Remote - British Columbia, Canada</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr"/>
@@ -3730,7 +3734,7 @@
       </c>
       <c r="J76" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/6745284</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7721851</t>
         </is>
       </c>
       <c r="K76" s="4" t="inlineStr">
@@ -3747,7 +3751,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Staff Data Scientist, Marketing</t>
+          <t>Staff Data Scientist, Ads</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -3771,7 +3775,7 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7445240</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7721787</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -3788,7 +3792,7 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, Ads Auction (Ads Marketplace Quality)</t>
+          <t>Staff Data Scientist, Consumer</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -3812,7 +3816,7 @@
       </c>
       <c r="J78" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7181821</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/6745284</t>
         </is>
       </c>
       <c r="K78" s="4" t="inlineStr">
@@ -3829,7 +3833,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, Ads Content Understanding</t>
+          <t>Staff Data Scientist, Marketing</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -3853,7 +3857,7 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7851761</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7445240</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -3870,7 +3874,7 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Systems Engineer</t>
+          <t>Staff Machine Learning Engineer, Ads Auction (Ads Marketplace Quality)</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
@@ -3894,7 +3898,7 @@
       </c>
       <c r="J80" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7731788</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7181821</t>
         </is>
       </c>
       <c r="K80" s="4" t="inlineStr">
@@ -3911,44 +3915,36 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Werkstudent:in KI Marketing (m/w/d)</t>
+          <t>Staff Machine Learning Engineer, Ads Content Understanding</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>laria.ai</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>Working student, berufseinstieg</t>
-        </is>
-      </c>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr"/>
       <c r="F81" s="2" t="inlineStr"/>
-      <c r="G81" s="2" t="inlineStr">
-        <is>
-          <t>Remote, Online Marketing</t>
-        </is>
-      </c>
+      <c r="G81" s="2" t="inlineStr"/>
       <c r="H81" s="2" t="inlineStr"/>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/lariaai/werkstudentin-ki-marketing-berlin-9847</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7851761</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -3960,80 +3956,80 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Laravel Developer (m/w/d) - AI-First PropTech</t>
+          <t>Staff Machine Learning Systems Engineer</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Immovara GmbH</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>Korntal-Münchingen</t>
-        </is>
-      </c>
-      <c r="E82" s="4" t="inlineStr">
-        <is>
-          <t>berufserfahren</t>
-        </is>
-      </c>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr"/>
       <c r="F82" s="4" t="inlineStr"/>
-      <c r="G82" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Software Development</t>
-        </is>
-      </c>
+      <c r="G82" s="4" t="inlineStr"/>
       <c r="H82" s="4" t="inlineStr"/>
       <c r="I82" s="4" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J82" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/immovara-gmbh/laravel-developer-ai-first-proptech-korntal-munchingen-239743</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7731788</t>
         </is>
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning (ML) Engineer - Applied</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr"/>
+          <t>Werkstudent:in KI Marketing (m/w/d)</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>laria.ai</t>
+        </is>
+      </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr"/>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Working student, berufseinstieg</t>
+        </is>
+      </c>
       <c r="F83" s="2" t="inlineStr"/>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>machine learning, artificial intelligence, python, cplusplus, startup</t>
+          <t>Remote, Online Marketing</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr"/>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>WorkingNomads</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>https://www.workingnomads.com/job/go/1578553/</t>
+          <t>https://www.arbeitnow.com/jobs/companies/lariaai/werkstudentin-ki-marketing-berlin-9847</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -4045,36 +4041,44 @@
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Backend Engineer, AI Security</t>
+          <t>Laravel Developer (m/w/d) - AI-First PropTech</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Immovara GmbH</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>New York, San Francisco, Seattle, or Remote (US/Canada)</t>
-        </is>
-      </c>
-      <c r="E84" s="4" t="inlineStr"/>
+          <t>Korntal-Münchingen</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
       <c r="F84" s="4" t="inlineStr"/>
-      <c r="G84" s="4" t="inlineStr"/>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Software Development</t>
+        </is>
+      </c>
       <c r="H84" s="4" t="inlineStr"/>
       <c r="I84" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J84" s="5" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7826765</t>
+          <t>https://www.arbeitnow.com/jobs/companies/immovara-gmbh/laravel-developer-ai-first-proptech-korntal-munchingen-239743</t>
         </is>
       </c>
       <c r="K84" s="4" t="inlineStr">
@@ -4091,31 +4095,31 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Backend Engineer, Core Tech, Canada</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
+          <t>Machine Learning (ML) Engineer - Applied</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr"/>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Toronto, CAN-Remote</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr"/>
       <c r="F85" s="2" t="inlineStr"/>
-      <c r="G85" s="2" t="inlineStr"/>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>machine learning, artificial intelligence, python, cplusplus, startup</t>
+        </is>
+      </c>
       <c r="H85" s="2" t="inlineStr"/>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WorkingNomads</t>
         </is>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=6567253</t>
+          <t>https://www.workingnomads.com/job/go/1578553/</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -4132,7 +4136,7 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Backend Engineer, Core Technology</t>
+          <t>Backend Engineer, AI Security</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -4142,7 +4146,7 @@
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>US-Remote, Chicago</t>
+          <t>New York, San Francisco, Seattle, or Remote (US/Canada)</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr"/>
@@ -4156,7 +4160,7 @@
       </c>
       <c r="J86" s="5" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=6042172</t>
+          <t>https://stripe.com/jobs/search?gh_jid=7826765</t>
         </is>
       </c>
       <c r="K86" s="4" t="inlineStr">
@@ -4173,7 +4177,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Backend Engineer, Developer Experience &amp; Product Platform</t>
+          <t>Backend Engineer, Core Tech, Canada</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -4183,7 +4187,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Toronto Canada, San Francisco, Remote in US, Remote in Canada</t>
+          <t>Toronto, CAN-Remote</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr"/>
@@ -4197,7 +4201,7 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7292520</t>
+          <t>https://stripe.com/jobs/search?gh_jid=6567253</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -4214,7 +4218,7 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Commercial Counsel, Crypto</t>
+          <t>Backend Engineer, Core Technology</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
@@ -4224,7 +4228,7 @@
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>New York City, Seattle, San Francisco, Chicago, Atlanta, US-Remote</t>
+          <t>US-Remote, Chicago</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr"/>
@@ -4238,7 +4242,7 @@
       </c>
       <c r="J88" s="5" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7392188</t>
+          <t>https://stripe.com/jobs/search?gh_jid=6042172</t>
         </is>
       </c>
       <c r="K88" s="4" t="inlineStr">
@@ -4255,7 +4259,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Fullstack Engineer, Privy</t>
+          <t>Backend Engineer, Developer Experience &amp; Product Platform</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -4265,7 +4269,7 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">NYC-Privy, US-Remote </t>
+          <t>Toronto Canada, San Francisco, Remote in US, Remote in Canada</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr"/>
@@ -4279,7 +4283,7 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7091959</t>
+          <t>https://stripe.com/jobs/search?gh_jid=7292520</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -4296,7 +4300,7 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Stripe Assistant</t>
+          <t>Commercial Counsel, Crypto</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
@@ -4306,7 +4310,7 @@
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>Seattle; San Francisco; New York City; Remote</t>
+          <t>New York City, Seattle, San Francisco, Chicago, Atlanta, US-Remote</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr"/>
@@ -4320,7 +4324,7 @@
       </c>
       <c r="J90" s="5" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7629052</t>
+          <t>https://stripe.com/jobs/search?gh_jid=7392188</t>
         </is>
       </c>
       <c r="K90" s="4" t="inlineStr">
@@ -4337,17 +4341,17 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning Manager, Feed Relevance</t>
+          <t>Fullstack Engineer, Privy</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t xml:space="preserve">NYC-Privy, US-Remote </t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr"/>
@@ -4361,7 +4365,7 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7802495</t>
+          <t>https://stripe.com/jobs/search?gh_jid=7091959</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -4378,17 +4382,17 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, GenAI Security</t>
+          <t>Machine Learning Engineer, Stripe Assistant</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Seattle; San Francisco; New York City; Remote</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr"/>
@@ -4402,7 +4406,7 @@
       </c>
       <c r="J92" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7891887</t>
+          <t>https://stripe.com/jobs/search?gh_jid=7629052</t>
         </is>
       </c>
       <c r="K92" s="4" t="inlineStr">
@@ -4419,7 +4423,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Senior Staff Machine Learning Engineer, Feed Relevance</t>
+          <t>Machine Learning Manager, Feed Relevance</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -4443,7 +4447,7 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7791994</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7802495</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -4460,7 +4464,7 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Senior Staff Machine Learning Engineer, ML Understanding</t>
+          <t>Senior Machine Learning Engineer, GenAI Security</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -4484,7 +4488,7 @@
       </c>
       <c r="J94" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7847148</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7891887</t>
         </is>
       </c>
       <c r="K94" s="4" t="inlineStr">
@@ -4501,7 +4505,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, Ads Measurement Modeling</t>
+          <t>Senior Staff Machine Learning Engineer, Feed Relevance</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -4525,7 +4529,7 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7890096</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7791994</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -4542,7 +4546,7 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, AI Serving</t>
+          <t>Senior Staff Machine Learning Engineer, ML Understanding</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
@@ -4566,7 +4570,7 @@
       </c>
       <c r="J96" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7886459</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7847148</t>
         </is>
       </c>
       <c r="K96" s="4" t="inlineStr">
@@ -4583,17 +4587,17 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (L3) - Full Stack</t>
+          <t>Staff Machine Learning Engineer, Ads Measurement Modeling</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Remote - US</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr"/>
@@ -4607,139 +4611,127 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7890096</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>Staff Machine Learning Engineer, AI Serving</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr"/>
+      <c r="F98" s="4" t="inlineStr"/>
+      <c r="G98" s="4" t="inlineStr"/>
+      <c r="H98" s="4" t="inlineStr"/>
+      <c r="I98" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J98" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7886459</t>
+        </is>
+      </c>
+      <c r="K98" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (L3) - Full Stack</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Remote - US</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr"/>
+      <c r="F99" s="2" t="inlineStr"/>
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr"/>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
           <t>https://job-boards.greenhouse.io/twilio/jobs/7738955</t>
         </is>
       </c>
-      <c r="K97" s="2" t="inlineStr">
+      <c r="K99" s="2" t="inlineStr">
         <is>
           <t>2026-05-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>AI Developer (Claude + AWS)</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>Datavent</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>Hamburg</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
-      <c r="F98" s="2" t="inlineStr"/>
-      <c r="G98" s="2" t="inlineStr">
-        <is>
-          <t>Remote, Software Development</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr"/>
-      <c r="I98" s="2" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/datavent/ai-developer-claude-aws-hamburg-22354</t>
-        </is>
-      </c>
-      <c r="K98" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="B99" s="4" t="inlineStr">
-        <is>
-          <t>Python Software Engineer, Backend &amp; APIs - Remote</t>
-        </is>
-      </c>
-      <c r="C99" s="4" t="inlineStr">
-        <is>
-          <t>dexter health</t>
-        </is>
-      </c>
-      <c r="D99" s="4" t="inlineStr">
-        <is>
-          <t>Cologne</t>
-        </is>
-      </c>
-      <c r="E99" s="4" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
-      <c r="F99" s="4" t="inlineStr"/>
-      <c r="G99" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Software Development</t>
-        </is>
-      </c>
-      <c r="H99" s="4" t="inlineStr"/>
-      <c r="I99" s="4" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J99" s="5" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/python-software-engineer-backend-apis-remote-cologne-284750</t>
-        </is>
-      </c>
-      <c r="K99" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Fullstack Developer (m/w/d) REMOTE //  UX / Python / Vue.js</t>
+          <t>AI Developer (Claude + AWS)</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Pont Connects e.K.</t>
+          <t>Datavent</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Düsseldorf</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr"/>
+          <t>Hamburg</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
       <c r="F100" s="2" t="inlineStr"/>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Remote, IT</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr"/>
@@ -4750,146 +4742,154 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
+          <t>https://www.arbeitnow.com/jobs/companies/datavent/ai-developer-claude-aws-hamburg-22354</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>Python Software Engineer, Backend &amp; APIs - Remote</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>dexter health</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>Cologne</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="inlineStr"/>
+      <c r="G101" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Software Development</t>
+        </is>
+      </c>
+      <c r="H101" s="4" t="inlineStr"/>
+      <c r="I101" s="4" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J101" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/python-software-engineer-backend-apis-remote-cologne-284750</t>
+        </is>
+      </c>
+      <c r="K101" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Fullstack Developer (m/w/d) REMOTE //  UX / Python / Vue.js</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Pont Connects e.K.</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Düsseldorf</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr"/>
+      <c r="F102" s="2" t="inlineStr"/>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>Remote, IT</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr"/>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
           <t>https://www.arbeitnow.com/jobs/companies/pont-connects-ek/fullstack-developer-remote-ux-python-vuejs-dusseldorf-371903</t>
         </is>
       </c>
-      <c r="K100" s="2" t="inlineStr">
+      <c r="K102" s="2" t="inlineStr">
         <is>
           <t>2026-05-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>Lemon.io</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>Americas, Europe, Asia, Oceania</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>full_time</t>
-        </is>
-      </c>
-      <c r="F101" s="2" t="inlineStr">
-        <is>
-          <t>Devops</t>
-        </is>
-      </c>
-      <c r="G101" s="2" t="inlineStr">
-        <is>
-          <t>.Net, android, AWS, azure, C, C#, C++, data science, golang, ios, java, javascript, kubernetes, node.js, php, python, react, ruby/rails, shopify, sql, video, blockchain, AI/ML, automation, react native, rust, unity, spring, data analysis, laravel, solidity, flask, Typescript , terraform, angular , GCP, data engineering, Symfony, startup, marketplace, next.js</t>
-        </is>
-      </c>
-      <c r="H101" s="2" t="inlineStr"/>
-      <c r="I101" s="2" t="inlineStr">
-        <is>
-          <t>Remotive</t>
-        </is>
-      </c>
-      <c r="J101" s="3" t="inlineStr">
-        <is>
-          <t>https://remotive.com/remote-jobs/devops/senior-devops-engineer-2090002</t>
-        </is>
-      </c>
-      <c r="K101" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="B102" s="4" t="inlineStr">
-        <is>
-          <t>M&amp;A Research Analyst</t>
-        </is>
-      </c>
-      <c r="C102" s="4" t="inlineStr">
-        <is>
-          <t>EquiMatch GmbH</t>
-        </is>
-      </c>
-      <c r="D102" s="4" t="inlineStr">
-        <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E102" s="4" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
-      <c r="F102" s="4" t="inlineStr"/>
-      <c r="G102" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Mergers &amp; Acquisitions</t>
-        </is>
-      </c>
-      <c r="H102" s="4" t="inlineStr"/>
-      <c r="I102" s="4" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J102" s="5" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/equimatch-gmbh/ma-research-analyst-berlin-498635</t>
-        </is>
-      </c>
-      <c r="K102" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Xsolla: Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr"/>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Lemon.io</t>
+        </is>
+      </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr"/>
-      <c r="F103" s="2" t="inlineStr"/>
-      <c r="G103" s="2" t="inlineStr"/>
+          <t>Americas, Europe, Asia, Oceania</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>full_time</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>Devops</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>.Net, android, AWS, azure, C, C#, C++, data science, golang, ios, java, javascript, kubernetes, node.js, php, python, react, ruby/rails, shopify, sql, video, blockchain, AI/ML, automation, react native, rust, unity, spring, data analysis, laravel, solidity, flask, Typescript , terraform, angular , GCP, data engineering, Symfony, startup, marketplace, next.js</t>
+        </is>
+      </c>
       <c r="H103" s="2" t="inlineStr"/>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Remotive</t>
         </is>
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/xsolla-full-stack-developer</t>
+          <t>https://remotive.com/remote-jobs/devops/senior-devops-engineer-2090002</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -4901,32 +4901,44 @@
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>Dropbox: Staff Fullstack Product Software Engineer, Dash</t>
-        </is>
-      </c>
-      <c r="C104" s="4" t="inlineStr"/>
+          <t>M&amp;A Research Analyst</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>EquiMatch GmbH</t>
+        </is>
+      </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E104" s="4" t="inlineStr"/>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
       <c r="F104" s="4" t="inlineStr"/>
-      <c r="G104" s="4" t="inlineStr"/>
+      <c r="G104" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Mergers &amp; Acquisitions</t>
+        </is>
+      </c>
       <c r="H104" s="4" t="inlineStr"/>
       <c r="I104" s="4" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J104" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/dropbox-staff-fullstack-product-software-engineer-dash</t>
+          <t>https://www.arbeitnow.com/jobs/companies/equimatch-gmbh/ma-research-analyst-berlin-498635</t>
         </is>
       </c>
       <c r="K104" s="4" t="inlineStr">
@@ -4943,17 +4955,13 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, Ranking and Personalization</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>Reddit</t>
-        </is>
-      </c>
+          <t>Xsolla: Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr"/>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr"/>
@@ -4962,115 +4970,95 @@
       <c r="H105" s="2" t="inlineStr"/>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
+          <t>https://weworkremotely.com/remote-jobs/xsolla-full-stack-developer</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>Dropbox: Staff Fullstack Product Software Engineer, Dash</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr"/>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr"/>
+      <c r="F106" s="4" t="inlineStr"/>
+      <c r="G106" s="4" t="inlineStr"/>
+      <c r="H106" s="4" t="inlineStr"/>
+      <c r="I106" s="4" t="inlineStr">
+        <is>
+          <t>WeWorkRemotely</t>
+        </is>
+      </c>
+      <c r="J106" s="5" t="inlineStr">
+        <is>
+          <t>https://weworkremotely.com/remote-jobs/dropbox-staff-fullstack-product-software-engineer-dash</t>
+        </is>
+      </c>
+      <c r="K106" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Staff Machine Learning Engineer, Ranking and Personalization</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr"/>
+      <c r="F107" s="2" t="inlineStr"/>
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr"/>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
           <t>https://job-boards.greenhouse.io/reddit/jobs/7848689</t>
         </is>
       </c>
-      <c r="K105" s="2" t="inlineStr">
+      <c r="K107" s="2" t="inlineStr">
         <is>
           <t>2026-05-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>Senior Rust Consultant / Engineer (m/w/d)</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>Hackstack GmbH</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>berufserfahren</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="inlineStr"/>
-      <c r="G106" s="2" t="inlineStr">
-        <is>
-          <t>Remote, Consulting, Engineering</t>
-        </is>
-      </c>
-      <c r="H106" s="2" t="inlineStr"/>
-      <c r="I106" s="2" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J106" s="3" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/hackstack-gmbh/senior-rust-consultant-engineer-munich-451602</t>
-        </is>
-      </c>
-      <c r="K106" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="B107" s="4" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer - Remote</t>
-        </is>
-      </c>
-      <c r="C107" s="4" t="inlineStr">
-        <is>
-          <t>dexter health</t>
-        </is>
-      </c>
-      <c r="D107" s="4" t="inlineStr">
-        <is>
-          <t>Cologne</t>
-        </is>
-      </c>
-      <c r="E107" s="4" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
-      <c r="F107" s="4" t="inlineStr"/>
-      <c r="G107" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Development</t>
-        </is>
-      </c>
-      <c r="H107" s="4" t="inlineStr"/>
-      <c r="I107" s="4" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J107" s="5" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/applied-ai-engineer-remote-cologne-2870</t>
-        </is>
-      </c>
-      <c r="K107" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5082,28 +5070,28 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Python Backend Engineer - Remote</t>
+          <t>Senior Rust Consultant / Engineer (m/w/d)</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>dexter health</t>
+          <t>Hackstack GmbH</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Cologne</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>professional / experienced</t>
+          <t>berufserfahren</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr"/>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Remote, Development</t>
+          <t>Remote, Consulting, Engineering</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr"/>
@@ -5114,7 +5102,7 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/python-backend-engineer-remote-cologne-34228</t>
+          <t>https://www.arbeitnow.com/jobs/companies/hackstack-gmbh/senior-rust-consultant-engineer-munich-451602</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -5131,7 +5119,7 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>AI Engineer (LLM Products) - Remote</t>
+          <t>Applied AI Engineer - Remote</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
@@ -5163,7 +5151,7 @@
       </c>
       <c r="J109" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/ai-engineer-llm-products-remote-cologne-236027</t>
+          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/applied-ai-engineer-remote-cologne-2870</t>
         </is>
       </c>
       <c r="K109" s="4" t="inlineStr">
@@ -5180,7 +5168,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Backend Python Engineer (APIs, Databases &amp; Cloud) - Remote</t>
+          <t>Python Backend Engineer - Remote</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -5212,7 +5200,7 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/backend-python-engineer-apis-databases-cloud-remote-cologne-274767</t>
+          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/python-backend-engineer-remote-cologne-34228</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -5224,32 +5212,44 @@
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Toptal: QA Automation Engineer</t>
-        </is>
-      </c>
-      <c r="C111" s="4" t="inlineStr"/>
+          <t>AI Engineer (LLM Products) - Remote</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>dexter health</t>
+        </is>
+      </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E111" s="4" t="inlineStr"/>
+          <t>Cologne</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
       <c r="F111" s="4" t="inlineStr"/>
-      <c r="G111" s="4" t="inlineStr"/>
+      <c r="G111" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Development</t>
+        </is>
+      </c>
       <c r="H111" s="4" t="inlineStr"/>
       <c r="I111" s="4" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J111" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/toptal-qa-automation-engineer-1</t>
+          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/ai-engineer-llm-products-remote-cologne-236027</t>
         </is>
       </c>
       <c r="K111" s="4" t="inlineStr">
@@ -5261,32 +5261,44 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Opensea: Staff Product Designer</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr"/>
+          <t>Backend Python Engineer (APIs, Databases &amp; Cloud) - Remote</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>dexter health</t>
+        </is>
+      </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="inlineStr"/>
+          <t>Cologne</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
       <c r="F112" s="2" t="inlineStr"/>
-      <c r="G112" s="2" t="inlineStr"/>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>Remote, Development</t>
+        </is>
+      </c>
       <c r="H112" s="2" t="inlineStr"/>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/opensea-staff-product-designer</t>
+          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/backend-python-engineer-apis-databases-cloud-remote-cologne-274767</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -5303,7 +5315,7 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Mutt Data: Devops</t>
+          <t>Toptal: QA Automation Engineer</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr"/>
@@ -5323,7 +5335,7 @@
       </c>
       <c r="J113" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/mutt-data-devops</t>
+          <t>https://weworkremotely.com/remote-jobs/toptal-qa-automation-engineer-1</t>
         </is>
       </c>
       <c r="K113" s="4" t="inlineStr">
@@ -5340,7 +5352,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Holywater: Full-Stack Developer</t>
+          <t>Opensea: Staff Product Designer</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr"/>
@@ -5360,7 +5372,7 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/holywater-full-stack-developer</t>
+          <t>https://weworkremotely.com/remote-jobs/opensea-staff-product-designer</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -5377,7 +5389,7 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Qventus: DevOps Engineer</t>
+          <t>Mutt Data: Devops</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr"/>
@@ -5397,7 +5409,7 @@
       </c>
       <c r="J115" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/qventus-devops-engineer</t>
+          <t>https://weworkremotely.com/remote-jobs/mutt-data-devops</t>
         </is>
       </c>
       <c r="K115" s="4" t="inlineStr">
@@ -5414,7 +5426,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Visualis: Senior Full Stack Developer</t>
+          <t>Holywater: Full-Stack Developer</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr"/>
@@ -5434,7 +5446,7 @@
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/visualis-senior-full-stack-developer</t>
+          <t>https://weworkremotely.com/remote-jobs/holywater-full-stack-developer</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -5451,17 +5463,13 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="C117" s="4" t="inlineStr">
-        <is>
-          <t>GitLab</t>
-        </is>
-      </c>
+          <t>Qventus: DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr"/>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Remote, Bangalore</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr"/>
@@ -5470,12 +5478,12 @@
       <c r="H117" s="4" t="inlineStr"/>
       <c r="I117" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J117" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8517564002</t>
+          <t>https://weworkremotely.com/remote-jobs/qventus-devops-engineer</t>
         </is>
       </c>
       <c r="K117" s="4" t="inlineStr">
@@ -5492,17 +5500,13 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Backend Engineer, Analytics Instrumentation (Golang)</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>GitLab</t>
-        </is>
-      </c>
+          <t>Visualis: Senior Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr"/>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr"/>
@@ -5511,12 +5515,12 @@
       <c r="H118" s="2" t="inlineStr"/>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481922002</t>
+          <t>https://weworkremotely.com/remote-jobs/visualis-senior-full-stack-developer</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -5533,7 +5537,7 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>Backend Engineer, Analytics Instrumentation (Golang)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
@@ -5543,7 +5547,7 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, Bangalore</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr"/>
@@ -5557,7 +5561,7 @@
       </c>
       <c r="J119" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481929002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8517564002</t>
         </is>
       </c>
       <c r="K119" s="4" t="inlineStr">
@@ -5574,7 +5578,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Backend Engineer, Knowledge Graph (Rust)</t>
+          <t>Backend Engineer, Analytics Instrumentation (Golang)</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -5584,7 +5588,7 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, US</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr"/>
@@ -5598,7 +5602,7 @@
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8437754002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481922002</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -5615,7 +5619,7 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>Backend Engineer, Knowledge Graph (Rust)</t>
+          <t>Backend Engineer, Analytics Instrumentation (Golang)</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
@@ -5639,7 +5643,7 @@
       </c>
       <c r="J121" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481958002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481929002</t>
         </is>
       </c>
       <c r="K121" s="4" t="inlineStr">
@@ -5656,7 +5660,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Intermediate Backend Engineer (C), Tenant Scale: Git</t>
+          <t>Backend Engineer, Knowledge Graph (Rust)</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -5666,7 +5670,7 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, Canada; Remote, US</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr"/>
@@ -5680,7 +5684,7 @@
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8497793002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8437754002</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -5697,7 +5701,7 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>Intermediate Backend Engineer, Gitlab Delivery: Upgrades</t>
+          <t>Backend Engineer, Knowledge Graph (Rust)</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
@@ -5721,7 +5725,7 @@
       </c>
       <c r="J123" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8463951002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481958002</t>
         </is>
       </c>
       <c r="K123" s="4" t="inlineStr">
@@ -5738,7 +5742,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Intermediate Backend Engineer, SRM: Security Platform Management</t>
+          <t>Intermediate Backend Engineer (C), Tenant Scale: Git</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -5748,7 +5752,7 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr"/>
@@ -5762,7 +5766,7 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8443325002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8497793002</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -5779,7 +5783,7 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>Intermediate Backend Engineer, SSCS: AI Governance</t>
+          <t>Intermediate Backend Engineer, Gitlab Delivery: Upgrades</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
@@ -5803,7 +5807,7 @@
       </c>
       <c r="J125" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480551002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8463951002</t>
         </is>
       </c>
       <c r="K125" s="4" t="inlineStr">
@@ -5820,7 +5824,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Intermediate Backend Engineer,  SSCS: Supply Chain</t>
+          <t>Intermediate Backend Engineer, SRM: Security Platform Management</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -5830,7 +5834,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr"/>
@@ -5844,7 +5848,7 @@
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480565002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8443325002</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -5861,7 +5865,7 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Intermediate Backend Engineer, SSCS: AI Governance</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
@@ -5871,7 +5875,7 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Remote, EMEA</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr"/>
@@ -5885,7 +5889,7 @@
       </c>
       <c r="J127" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8464072002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480551002</t>
         </is>
       </c>
       <c r="K127" s="4" t="inlineStr">
@@ -5902,7 +5906,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (AI), Pipeline Execution</t>
+          <t>Intermediate Backend Engineer,  SSCS: Supply Chain</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -5912,7 +5916,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US-Southeast</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr"/>
@@ -5926,7 +5930,7 @@
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8514945002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480565002</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -5943,7 +5947,7 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Analytics Instrumentation (Golang)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
@@ -5953,7 +5957,7 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, US</t>
+          <t>Remote, EMEA</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr"/>
@@ -5967,7 +5971,7 @@
       </c>
       <c r="J129" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8451512002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8464072002</t>
         </is>
       </c>
       <c r="K129" s="4" t="inlineStr">
@@ -5984,7 +5988,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (C), Tenant Scale: Git</t>
+          <t>Senior Backend Engineer (AI), Pipeline Execution</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -5994,7 +5998,7 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US-Southeast</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr"/>
@@ -6008,7 +6012,7 @@
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8497791002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8514945002</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
@@ -6025,7 +6029,7 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Gitlab Delivery: Runway (Platform Engineering)</t>
+          <t>Senior Backend Engineer, Analytics Instrumentation (Golang)</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
@@ -6035,7 +6039,7 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Remote, Australia; Remote, India; Remote, Ireland; Remote, Japan; Remote, Netherlands; Remote, Singapore; Remote, United Kingdom</t>
+          <t>Remote, Canada; Remote, US</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr"/>
@@ -6049,7 +6053,7 @@
       </c>
       <c r="J131" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8324132002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8451512002</t>
         </is>
       </c>
       <c r="K131" s="4" t="inlineStr">
@@ -6066,7 +6070,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Gitlab Delivery: Upgrades</t>
+          <t>Senior Backend Engineer (C), Tenant Scale: Git</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -6090,7 +6094,7 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8463933002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8497791002</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -6107,7 +6111,7 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer(Go), Continuous Delivery</t>
+          <t>Senior Backend Engineer, Gitlab Delivery: Runway (Platform Engineering)</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
@@ -6117,7 +6121,7 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, Australia; Remote, India; Remote, Ireland; Remote, Japan; Remote, Netherlands; Remote, Singapore; Remote, United Kingdom</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr"/>
@@ -6131,7 +6135,7 @@
       </c>
       <c r="J133" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8488966002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8324132002</t>
         </is>
       </c>
       <c r="K133" s="4" t="inlineStr">
@@ -6148,7 +6152,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer(Golang),Software Supply Chain Security: Auth Infrastructure</t>
+          <t>Senior Backend Engineer, Gitlab Delivery: Upgrades</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -6158,7 +6162,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Remote, Americas; Remote, APAC; Remote, Canada</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr"/>
@@ -6172,7 +6176,7 @@
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8157520002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8463933002</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
@@ -6189,7 +6193,7 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (RoR), AST: Secret Detection</t>
+          <t>Senior Backend Engineer(Go), Continuous Delivery</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
@@ -6199,7 +6203,7 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr"/>
@@ -6213,7 +6217,7 @@
       </c>
       <c r="J135" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8432262002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8488966002</t>
         </is>
       </c>
       <c r="K135" s="4" t="inlineStr">
@@ -6230,7 +6234,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (RoR/Go), SSCS: Pipeline Security</t>
+          <t>Senior Backend Engineer(Golang),Software Supply Chain Security: Auth Infrastructure</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -6240,7 +6244,7 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
+          <t>Remote, Americas; Remote, APAC; Remote, Canada</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr"/>
@@ -6254,7 +6258,7 @@
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8432221002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8157520002</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -6271,7 +6275,7 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (RoR), SSCS: Authorization</t>
+          <t>Senior Backend Engineer (RoR), AST: Secret Detection</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
@@ -6281,7 +6285,7 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
+          <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr"/>
@@ -6295,7 +6299,7 @@
       </c>
       <c r="J137" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8457315002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8432262002</t>
         </is>
       </c>
       <c r="K137" s="4" t="inlineStr">
@@ -6312,7 +6316,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby or Golang), Tenant Scale; Cells Infrastructure</t>
+          <t>Senior Backend Engineer (RoR/Go), SSCS: Pipeline Security</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -6322,7 +6326,7 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Remote, APAC; Remote, Canada; Remote, EMEA; Remote, US</t>
+          <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr"/>
@@ -6336,7 +6340,7 @@
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8437148002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8432221002</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
@@ -6353,7 +6357,7 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, SSCS: AI Governance</t>
+          <t>Senior Backend Engineer (RoR), SSCS: Authorization</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
@@ -6363,7 +6367,7 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr"/>
@@ -6377,7 +6381,7 @@
       </c>
       <c r="J139" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480544002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8457315002</t>
         </is>
       </c>
       <c r="K139" s="4" t="inlineStr">
@@ -6394,7 +6398,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer,  SSCS: Supply Chain</t>
+          <t>Senior Backend Engineer (Ruby or Golang), Tenant Scale; Cells Infrastructure</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -6404,7 +6408,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, APAC; Remote, Canada; Remote, EMEA; Remote, US</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr"/>
@@ -6418,7 +6422,7 @@
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480580002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8437148002</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -6435,7 +6439,7 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Senior Fullstack Engineer (TypeScript), AI Engineering: Editor Extensions</t>
+          <t>Senior Backend Engineer, SSCS: AI Governance</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
@@ -6445,7 +6449,7 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>Remote, APAC; Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US-Southeast</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr"/>
@@ -6459,7 +6463,7 @@
       </c>
       <c r="J141" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8452278002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480544002</t>
         </is>
       </c>
       <c r="K141" s="4" t="inlineStr">
@@ -6476,7 +6480,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer, Analytics Instrumentation (Golang)</t>
+          <t>Senior Backend Engineer,  SSCS: Supply Chain</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -6500,7 +6504,7 @@
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8508027002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480580002</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -6517,7 +6521,7 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer, AST: Composition Analysis</t>
+          <t>Senior Fullstack Engineer (TypeScript), AI Engineering: Editor Extensions</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
@@ -6527,7 +6531,7 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Remote, Australia; Remote, Canada; Remote, India; Remote, Ireland; Remote, Israel; Remote, Japan; Remote, Netherlands; Remote, New Zealand; Remote, United Kingdom; Remote, US</t>
+          <t>Remote, APAC; Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US-Southeast</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr"/>
@@ -6541,7 +6545,7 @@
       </c>
       <c r="J143" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8478364002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8452278002</t>
         </is>
       </c>
       <c r="K143" s="4" t="inlineStr">
@@ -6558,7 +6562,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer, Developer Experience</t>
+          <t>Staff Backend Engineer, Analytics Instrumentation (Golang)</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -6568,7 +6572,7 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, United Kingdom; Remote, US</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr"/>
@@ -6582,7 +6586,7 @@
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8490477002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8508027002</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -6599,7 +6603,7 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer, Gitlab Delivery: Upgrades</t>
+          <t>Staff Backend Engineer, AST: Composition Analysis</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
@@ -6609,7 +6613,7 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, Australia; Remote, Canada; Remote, India; Remote, Ireland; Remote, Israel; Remote, Japan; Remote, Netherlands; Remote, New Zealand; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr"/>
@@ -6623,7 +6627,7 @@
       </c>
       <c r="J145" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8463922002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8478364002</t>
         </is>
       </c>
       <c r="K145" s="4" t="inlineStr">
@@ -6640,7 +6644,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer (Go), Continuous Delivery</t>
+          <t>Staff Backend Engineer, Developer Experience</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -6650,7 +6654,7 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, Canada; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr"/>
@@ -6664,7 +6668,7 @@
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8488961002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8490477002</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -6681,7 +6685,7 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer (Go), Software Supply Chain Security: Secrets Management</t>
+          <t>Staff Backend Engineer, Gitlab Delivery: Upgrades</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
@@ -6691,7 +6695,7 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr"/>
@@ -6705,7 +6709,7 @@
       </c>
       <c r="J147" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8432235002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8463922002</t>
         </is>
       </c>
       <c r="K147" s="4" t="inlineStr">
@@ -6722,7 +6726,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer, Knowledge Graph (Rust)</t>
+          <t>Staff Backend Engineer (Go), Continuous Delivery</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -6746,7 +6750,7 @@
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481945002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8488961002</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
@@ -6763,7 +6767,7 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer,  Software Supply Chain Security</t>
+          <t>Staff Backend Engineer (Go), Software Supply Chain Security: Secrets Management</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
@@ -6773,7 +6777,7 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr"/>
@@ -6787,7 +6791,7 @@
       </c>
       <c r="J149" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480559002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8432235002</t>
         </is>
       </c>
       <c r="K149" s="4" t="inlineStr">
@@ -6804,7 +6808,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer, SSCS: AI Governance</t>
+          <t>Staff Backend Engineer, Knowledge Graph (Rust)</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -6828,7 +6832,7 @@
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480531002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481945002</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -6845,7 +6849,7 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>Staff Backend (Python) Engineer, AI Engineering:Duo Chat</t>
+          <t>Staff Backend Engineer,  Software Supply Chain Security</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
@@ -6855,7 +6859,7 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>Remote, Americas; Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr"/>
@@ -6869,7 +6873,7 @@
       </c>
       <c r="J151" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8450446002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480559002</t>
         </is>
       </c>
       <c r="K151" s="4" t="inlineStr">
@@ -6886,17 +6890,17 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Senior Full Stack Product Software Engineer</t>
+          <t>Staff Backend Engineer, SSCS: AI Governance</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Dropbox</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Remote - Poland</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr"/>
@@ -6910,126 +6914,94 @@
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480531002</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B153" s="4" t="inlineStr">
+        <is>
+          <t>Staff Backend (Python) Engineer, AI Engineering:Duo Chat</t>
+        </is>
+      </c>
+      <c r="C153" s="4" t="inlineStr">
+        <is>
+          <t>GitLab</t>
+        </is>
+      </c>
+      <c r="D153" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Americas; Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom</t>
+        </is>
+      </c>
+      <c r="E153" s="4" t="inlineStr"/>
+      <c r="F153" s="4" t="inlineStr"/>
+      <c r="G153" s="4" t="inlineStr"/>
+      <c r="H153" s="4" t="inlineStr"/>
+      <c r="I153" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J153" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8450446002</t>
+        </is>
+      </c>
+      <c r="K153" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Product Software Engineer</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>Dropbox</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Remote - Poland</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr"/>
+      <c r="F154" s="2" t="inlineStr"/>
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr"/>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
           <t>https://jobs.dropbox.com/listing/6449719?gh_jid=6449719</t>
         </is>
       </c>
-      <c r="K152" s="2" t="inlineStr">
+      <c r="K154" s="2" t="inlineStr">
         <is>
           <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>Dry Ground AI</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
-        <is>
-          <t>Brazil, Colombia, Philippines</t>
-        </is>
-      </c>
-      <c r="E153" s="2" t="inlineStr">
-        <is>
-          <t>full_time</t>
-        </is>
-      </c>
-      <c r="F153" s="2" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence</t>
-        </is>
-      </c>
-      <c r="G153" s="2" t="inlineStr">
-        <is>
-          <t>api, cloud, fullstack, python, AI/ML, automation, research, CI/CD, TensorFlow, spark, NLP, CMS, Pytorch, REST</t>
-        </is>
-      </c>
-      <c r="H153" s="2" t="inlineStr">
-        <is>
-          <t>$40- $60k</t>
-        </is>
-      </c>
-      <c r="I153" s="2" t="inlineStr">
-        <is>
-          <t>Remotive</t>
-        </is>
-      </c>
-      <c r="J153" s="3" t="inlineStr">
-        <is>
-          <t>https://remotive.com/remote-jobs/artificial-intelligence/ai-engineer-2089958</t>
-        </is>
-      </c>
-      <c r="K153" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B154" s="4" t="inlineStr">
-        <is>
-          <t>Senior Independent AI Engineer / Architect</t>
-        </is>
-      </c>
-      <c r="C154" s="4" t="inlineStr">
-        <is>
-          <t>A.Team</t>
-        </is>
-      </c>
-      <c r="D154" s="4" t="inlineStr">
-        <is>
-          <t>Americas, Europe, Israel</t>
-        </is>
-      </c>
-      <c r="E154" s="4" t="inlineStr">
-        <is>
-          <t>contract</t>
-        </is>
-      </c>
-      <c r="F154" s="4" t="inlineStr">
-        <is>
-          <t>Software Development</t>
-        </is>
-      </c>
-      <c r="G154" s="4" t="inlineStr">
-        <is>
-          <t>go, UI/UX, wordpress, chat, apple, testing, catalyst</t>
-        </is>
-      </c>
-      <c r="H154" s="4" t="inlineStr">
-        <is>
-          <t>$120 - $170 /hour</t>
-        </is>
-      </c>
-      <c r="I154" s="4" t="inlineStr">
-        <is>
-          <t>Remotive</t>
-        </is>
-      </c>
-      <c r="J154" s="5" t="inlineStr">
-        <is>
-          <t>https://remotive.com/remote-jobs/software-development/senior-independent-ai-engineer-architect-1919266</t>
-        </is>
-      </c>
-      <c r="K154" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7041,37 +7013,37 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Senior Independent Software Developer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>A.Team</t>
+          <t>Dry Ground AI</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Americas, Europe, Israel</t>
+          <t>Brazil, Colombia, Philippines</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>contract</t>
+          <t>full_time</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>Software Development</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>go, wordpress, chat, apple, testing, catalyst</t>
+          <t>api, cloud, fullstack, python, AI/ML, automation, research, CI/CD, TensorFlow, spark, NLP, CMS, Pytorch, REST</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>$90 - $150 /hour</t>
+          <t>$40- $60k</t>
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr">
@@ -7081,7 +7053,7 @@
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
-          <t>https://remotive.com/remote-jobs/software-development/senior-independent-software-developer-1919265</t>
+          <t>https://remotive.com/remote-jobs/artificial-intelligence/ai-engineer-2089958</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -7098,17 +7070,17 @@
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>Senior Full-stack React Developer</t>
+          <t>Senior Independent AI Engineer / Architect</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>Lemon.io</t>
+          <t>A.Team</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>Americas, Europe, Asia, Oceania</t>
+          <t>Americas, Europe, Israel</t>
         </is>
       </c>
       <c r="E156" s="4" t="inlineStr">
@@ -7123,10 +7095,14 @@
       </c>
       <c r="G156" s="4" t="inlineStr">
         <is>
-          <t>.Net, android, AWS, azure, backend, C, C#, C++, data science, fullstack, golang, ios, java, javascript, node.js, php, python, react, react js, ruby/rails, shopify, video, blockchain, AI/ML, react native, rust, unity, spring, data analysis, laravel, solidity, flask, Typescript , angular , GCP, data engineering, Symfony, startup, marketplace, next.js</t>
-        </is>
-      </c>
-      <c r="H156" s="4" t="inlineStr"/>
+          <t>go, UI/UX, wordpress, chat, apple, testing, catalyst</t>
+        </is>
+      </c>
+      <c r="H156" s="4" t="inlineStr">
+        <is>
+          <t>$120 - $170 /hour</t>
+        </is>
+      </c>
       <c r="I156" s="4" t="inlineStr">
         <is>
           <t>Remotive</t>
@@ -7134,7 +7110,7 @@
       </c>
       <c r="J156" s="5" t="inlineStr">
         <is>
-          <t>https://remotive.com/remote-jobs/software-development/senior-full-stack-react-developer-2088711</t>
+          <t>https://remotive.com/remote-jobs/software-development/senior-independent-ai-engineer-architect-1919266</t>
         </is>
       </c>
       <c r="K156" s="4" t="inlineStr">
@@ -7151,22 +7127,22 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>Tech Lead Full-Stack Rails Engineer</t>
+          <t>Senior Independent Software Developer</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>Mitre Media</t>
+          <t>A.Team</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>USA, Canada, USA timezones</t>
+          <t>Americas, Europe, Israel</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>full_time</t>
+          <t>contract</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
@@ -7176,12 +7152,12 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>api, CSS, docker, elasticsearch, fullstack, html, javascript, kubernetes, postgresql, react, ror, ruby/rails, AI/ML, CAD, advertising, Redis, ES6, web applications, MySQL, NLP, fintech, Micro services, github, system architecture</t>
+          <t>go, wordpress, chat, apple, testing, catalyst</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>$170k - $200k</t>
+          <t>$90 - $150 /hour</t>
         </is>
       </c>
       <c r="I157" s="2" t="inlineStr">
@@ -7191,7 +7167,7 @@
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
-          <t>https://remotive.com/remote-jobs/software-development/tech-lead-full-stack-rails-engineer-2069746</t>
+          <t>https://remotive.com/remote-jobs/software-development/senior-independent-software-developer-1919265</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -7208,17 +7184,17 @@
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>Senior Frontend Developer</t>
+          <t>Senior Full-stack React Developer</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>Sanctuary Computer</t>
+          <t>Lemon.io</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>LATAM, Asia</t>
+          <t>Americas, Europe, Asia, Oceania</t>
         </is>
       </c>
       <c r="E158" s="4" t="inlineStr">
@@ -7233,14 +7209,10 @@
       </c>
       <c r="G158" s="4" t="inlineStr">
         <is>
-          <t>api, backend, CSS, ecommerce, frontend, fullstack, graphql, postgresql, redux, security, seo, shopify, open source, paas, product management, documentation, mentoring, Typescript , Redis, web applications, cypress, data visualization, firebase, IoT, engineering management, runtime, responsive, prismic, testing, next.js, CMS, jest, REST, web sockets, performance optimization</t>
-        </is>
-      </c>
-      <c r="H158" s="4" t="inlineStr">
-        <is>
-          <t>$80k - $120k</t>
-        </is>
-      </c>
+          <t>.Net, android, AWS, azure, backend, C, C#, C++, data science, fullstack, golang, ios, java, javascript, node.js, php, python, react, react js, ruby/rails, shopify, video, blockchain, AI/ML, react native, rust, unity, spring, data analysis, laravel, solidity, flask, Typescript , angular , GCP, data engineering, Symfony, startup, marketplace, next.js</t>
+        </is>
+      </c>
+      <c r="H158" s="4" t="inlineStr"/>
       <c r="I158" s="4" t="inlineStr">
         <is>
           <t>Remotive</t>
@@ -7248,7 +7220,7 @@
       </c>
       <c r="J158" s="5" t="inlineStr">
         <is>
-          <t>https://remotive.com/remote-jobs/software-development/senior-frontend-developer-2088707</t>
+          <t>https://remotive.com/remote-jobs/software-development/senior-full-stack-react-developer-2088711</t>
         </is>
       </c>
       <c r="K158" s="4" t="inlineStr">
@@ -7265,17 +7237,17 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>Fullstack Developer (US - ET)</t>
+          <t>Tech Lead Full-Stack Rails Engineer</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Chooose</t>
+          <t>Mitre Media</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>USA, Canada, USA timezones</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -7290,10 +7262,14 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>api, azure, fullstack, python, react, saas, AI/ML, project management, documentation, Typescript , computer science, diversity, insurance</t>
-        </is>
-      </c>
-      <c r="H159" s="2" t="inlineStr"/>
+          <t>api, CSS, docker, elasticsearch, fullstack, html, javascript, kubernetes, postgresql, react, ror, ruby/rails, AI/ML, CAD, advertising, Redis, ES6, web applications, MySQL, NLP, fintech, Micro services, github, system architecture</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>$170k - $200k</t>
+        </is>
+      </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
           <t>Remotive</t>
@@ -7301,7 +7277,7 @@
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
-          <t>https://remotive.com/remote-jobs/software-development/fullstack-developer-us-et-2088706</t>
+          <t>https://remotive.com/remote-jobs/software-development/tech-lead-full-stack-rails-engineer-2069746</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
@@ -7318,31 +7294,47 @@
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning Manager, Notifications Relevance</t>
+          <t>Senior Frontend Developer</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Sanctuary Computer</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
-        </is>
-      </c>
-      <c r="E160" s="4" t="inlineStr"/>
-      <c r="F160" s="4" t="inlineStr"/>
-      <c r="G160" s="4" t="inlineStr"/>
-      <c r="H160" s="4" t="inlineStr"/>
+          <t>LATAM, Asia</t>
+        </is>
+      </c>
+      <c r="E160" s="4" t="inlineStr">
+        <is>
+          <t>contract</t>
+        </is>
+      </c>
+      <c r="F160" s="4" t="inlineStr">
+        <is>
+          <t>Software Development</t>
+        </is>
+      </c>
+      <c r="G160" s="4" t="inlineStr">
+        <is>
+          <t>api, backend, CSS, ecommerce, frontend, fullstack, graphql, postgresql, redux, security, seo, shopify, open source, paas, product management, documentation, mentoring, Typescript , Redis, web applications, cypress, data visualization, firebase, IoT, engineering management, runtime, responsive, prismic, testing, next.js, CMS, jest, REST, web sockets, performance optimization</t>
+        </is>
+      </c>
+      <c r="H160" s="4" t="inlineStr">
+        <is>
+          <t>$80k - $120k</t>
+        </is>
+      </c>
       <c r="I160" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>Remotive</t>
         </is>
       </c>
       <c r="J160" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7846885</t>
+          <t>https://remotive.com/remote-jobs/software-development/senior-frontend-developer-2088707</t>
         </is>
       </c>
       <c r="K160" s="4" t="inlineStr">
@@ -7359,31 +7351,43 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Senior Staff ML Engineer, Search &amp; Recommendation</t>
+          <t>Fullstack Developer (US - ET)</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Chooose</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
-        </is>
-      </c>
-      <c r="E161" s="2" t="inlineStr"/>
-      <c r="F161" s="2" t="inlineStr"/>
-      <c r="G161" s="2" t="inlineStr"/>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>full_time</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>Software Development</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>api, azure, fullstack, python, react, saas, AI/ML, project management, documentation, Typescript , computer science, diversity, insurance</t>
+        </is>
+      </c>
       <c r="H161" s="2" t="inlineStr"/>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>Remotive</t>
         </is>
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7833622</t>
+          <t>https://remotive.com/remote-jobs/software-development/fullstack-developer-us-et-2088706</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
@@ -7400,17 +7404,17 @@
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Machine Learning Manager, Notifications Relevance</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>Remote - US</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E162" s="4" t="inlineStr"/>
@@ -7424,7 +7428,7 @@
       </c>
       <c r="J162" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7059734</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7846885</t>
         </is>
       </c>
       <c r="K162" s="4" t="inlineStr">
@@ -7441,17 +7445,17 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Staff ML Engineer, Search &amp; Recommendation</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>Remote - US</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr"/>
@@ -7465,7 +7469,7 @@
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7702644</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7833622</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
@@ -7482,7 +7486,7 @@
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>Principal Machine Learning &amp; Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
@@ -7506,7 +7510,7 @@
       </c>
       <c r="J164" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7155492</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7059734</t>
         </is>
       </c>
       <c r="K164" s="4" t="inlineStr">
@@ -7523,7 +7527,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>Principal, Product Manager - AI / LLM</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -7547,7 +7551,7 @@
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7619420</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7702644</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
@@ -7564,7 +7568,7 @@
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>Product Engineer (Backend)</t>
+          <t>Principal Machine Learning &amp; Data Engineer</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
@@ -7588,7 +7592,7 @@
       </c>
       <c r="J166" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7671815</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7155492</t>
         </is>
       </c>
       <c r="K166" s="4" t="inlineStr">
@@ -7605,7 +7609,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>Senior Manager, Machine Learning</t>
+          <t>Principal, Product Manager - AI / LLM</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -7629,7 +7633,7 @@
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7066029</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7619420</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
@@ -7646,7 +7650,7 @@
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>Staff Data Scientist</t>
+          <t>Product Engineer (Backend)</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
@@ -7670,7 +7674,7 @@
       </c>
       <c r="J168" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7821458</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7671815</t>
         </is>
       </c>
       <c r="K168" s="4" t="inlineStr">
@@ -7687,7 +7691,7 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>Staff, Data Scientist (L4) GTM Data Science &amp; Analytics</t>
+          <t>Senior Manager, Machine Learning</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -7711,7 +7715,7 @@
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7851920</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7066029</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
@@ -7728,7 +7732,7 @@
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer</t>
+          <t>Staff Data Scientist</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
@@ -7752,7 +7756,7 @@
       </c>
       <c r="J170" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7061880</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7821458</t>
         </is>
       </c>
       <c r="K170" s="4" t="inlineStr">
@@ -7769,7 +7773,7 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer (L4)</t>
+          <t>Staff, Data Scientist (L4) GTM Data Science &amp; Analytics</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -7779,7 +7783,7 @@
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>Remote - India</t>
+          <t>Remote - US</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr"/>
@@ -7793,7 +7797,7 @@
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7520997</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7851920</t>
         </is>
       </c>
       <c r="K171" s="2" t="inlineStr">
@@ -7810,39 +7814,31 @@
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>Senior Python Developer - Django (m/w/d)</t>
+          <t>Staff Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>sync.blue® GmbH</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>Haltern am See</t>
-        </is>
-      </c>
-      <c r="E172" s="4" t="inlineStr">
-        <is>
-          <t>berufserfahren</t>
-        </is>
-      </c>
+          <t>Remote - US</t>
+        </is>
+      </c>
+      <c r="E172" s="4" t="inlineStr"/>
       <c r="F172" s="4" t="inlineStr"/>
-      <c r="G172" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Software Development</t>
-        </is>
-      </c>
+      <c r="G172" s="4" t="inlineStr"/>
       <c r="H172" s="4" t="inlineStr"/>
       <c r="I172" s="4" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J172" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/syncblue-gmbh/senior-python-developer-django-haltern-am-see-16238</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7061880</t>
         </is>
       </c>
       <c r="K172" s="4" t="inlineStr">
@@ -7859,39 +7855,31 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>Freelance Senior AI Product Manager</t>
+          <t>Staff Machine Learning Engineer (L4)</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>nexamind GmbH</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E173" s="2" t="inlineStr">
-        <is>
-          <t>Freelance, professional / experienced</t>
-        </is>
-      </c>
+          <t>Remote - India</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr"/>
       <c r="F173" s="2" t="inlineStr"/>
-      <c r="G173" s="2" t="inlineStr">
-        <is>
-          <t>Remote, Product Management</t>
-        </is>
-      </c>
+      <c r="G173" s="2" t="inlineStr"/>
       <c r="H173" s="2" t="inlineStr"/>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/nexamind-gmbh/freelance-senior-ai-product-manager-berlin-73613</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7520997</t>
         </is>
       </c>
       <c r="K173" s="2" t="inlineStr">
@@ -7908,17 +7896,17 @@
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>Senior Full-Stack-Entwickler:in React / TypeScript / .NET  100 % Remote, KI-First</t>
+          <t>Senior Python Developer - Django (m/w/d)</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>yourMAIL GmbH</t>
+          <t>sync.blue® GmbH</t>
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Haltern am See</t>
         </is>
       </c>
       <c r="E174" s="4" t="inlineStr">
@@ -7940,7 +7928,7 @@
       </c>
       <c r="J174" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/yourmail-gmbh/senior-full-stack-entwicklerin-react-typescript-net-100-remote-ki-first-berlin-21152</t>
+          <t>https://www.arbeitnow.com/jobs/companies/syncblue-gmbh/senior-python-developer-django-haltern-am-see-16238</t>
         </is>
       </c>
       <c r="K174" s="4" t="inlineStr">
@@ -7957,12 +7945,12 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>Senior Frontend-Entwickler:in React / TypeScript, 100 % Remote, KI-First</t>
+          <t>Freelance Senior AI Product Manager</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>yourMAIL GmbH</t>
+          <t>nexamind GmbH</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
@@ -7972,13 +7960,13 @@
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>berufserfahren</t>
+          <t>Freelance, professional / experienced</t>
         </is>
       </c>
       <c r="F175" s="2" t="inlineStr"/>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>Remote, Software Development</t>
+          <t>Remote, Product Management</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr"/>
@@ -7989,7 +7977,7 @@
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/yourmail-gmbh/senior-frontend-entwicklerin-react-typescript-100-remote-ki-first-berlin-288218</t>
+          <t>https://www.arbeitnow.com/jobs/companies/nexamind-gmbh/freelance-senior-ai-product-manager-berlin-73613</t>
         </is>
       </c>
       <c r="K175" s="2" t="inlineStr">
@@ -8006,24 +7994,28 @@
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>Full-Stack Entwickler (m/w/d) - .NET 100% Remote</t>
+          <t>Senior Full-Stack-Entwickler:in React / TypeScript / .NET  100 % Remote, KI-First</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>FNTIO</t>
+          <t>yourMAIL GmbH</t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>Frankfurt am Main</t>
-        </is>
-      </c>
-      <c r="E176" s="4" t="inlineStr"/>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="E176" s="4" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
       <c r="F176" s="4" t="inlineStr"/>
       <c r="G176" s="4" t="inlineStr">
         <is>
-          <t>Remote, Consulting, Engineering</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr"/>
@@ -8034,7 +8026,7 @@
       </c>
       <c r="J176" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/fntio/full-stack-entwickler-net-100-remote-frankfurt-am-main-122380</t>
+          <t>https://www.arbeitnow.com/jobs/companies/yourmail-gmbh/senior-full-stack-entwicklerin-react-typescript-net-100-remote-ki-first-berlin-21152</t>
         </is>
       </c>
       <c r="K176" s="4" t="inlineStr">
@@ -8051,12 +8043,12 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Frontend-Entwickler:in React / TypeScript, 100 % Remote, KI-First</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>Phantasma Labs</t>
+          <t>yourMAIL GmbH</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
@@ -8064,11 +8056,15 @@
           <t>Berlin</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr"/>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
       <c r="F177" s="2" t="inlineStr"/>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>Remote, Engineering</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr"/>
@@ -8079,7 +8075,7 @@
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/phantasma-labs/machine-learning-engineer-berlin-303955</t>
+          <t>https://www.arbeitnow.com/jobs/companies/yourmail-gmbh/senior-frontend-entwicklerin-react-typescript-100-remote-ki-first-berlin-288218</t>
         </is>
       </c>
       <c r="K177" s="2" t="inlineStr">
@@ -8096,28 +8092,24 @@
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>Technical Data Manager (m/w/d)</t>
+          <t>Full-Stack Entwickler (m/w/d) - .NET 100% Remote</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>BMF Media Information Technology GmbH</t>
+          <t>FNTIO</t>
         </is>
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>Augsburg</t>
-        </is>
-      </c>
-      <c r="E178" s="4" t="inlineStr">
-        <is>
-          <t>berufserfahren</t>
-        </is>
-      </c>
+          <t>Frankfurt am Main</t>
+        </is>
+      </c>
+      <c r="E178" s="4" t="inlineStr"/>
       <c r="F178" s="4" t="inlineStr"/>
       <c r="G178" s="4" t="inlineStr">
         <is>
-          <t>Remote, Technical Documentation</t>
+          <t>Remote, Consulting, Engineering</t>
         </is>
       </c>
       <c r="H178" s="4" t="inlineStr"/>
@@ -8128,7 +8120,7 @@
       </c>
       <c r="J178" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/bmf-media-information-technology-gmbh/technical-data-manager-augsburg-42188</t>
+          <t>https://www.arbeitnow.com/jobs/companies/fntio/full-stack-entwickler-net-100-remote-frankfurt-am-main-122380</t>
         </is>
       </c>
       <c r="K178" s="4" t="inlineStr">
@@ -8145,28 +8137,24 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>Data Integration &amp; API Engineer m/w/d - Bi &amp; Data Automation</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>loyos bi GmbH</t>
+          <t>Phantasma Labs</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>Hamburg</t>
-        </is>
-      </c>
-      <c r="E179" s="2" t="inlineStr">
-        <is>
-          <t>berufserfahren</t>
-        </is>
-      </c>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr"/>
       <c r="F179" s="2" t="inlineStr"/>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>Remote, Software Development</t>
+          <t>Remote, Engineering</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr"/>
@@ -8177,7 +8165,7 @@
       </c>
       <c r="J179" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/loyos-bi-gmbh/data-integration-api-engineer-bi-data-automation-hamburg-66228</t>
+          <t>https://www.arbeitnow.com/jobs/companies/phantasma-labs/machine-learning-engineer-berlin-303955</t>
         </is>
       </c>
       <c r="K179" s="2" t="inlineStr">
@@ -8194,28 +8182,28 @@
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Technical Data Manager (m/w/d)</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>Coding Partners</t>
+          <t>BMF Media Information Technology GmbH</t>
         </is>
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="E180" s="4" t="inlineStr">
         <is>
-          <t>professional / experienced</t>
+          <t>berufserfahren</t>
         </is>
       </c>
       <c r="F180" s="4" t="inlineStr"/>
       <c r="G180" s="4" t="inlineStr">
         <is>
-          <t>Remote, Software Development</t>
+          <t>Remote, Technical Documentation</t>
         </is>
       </c>
       <c r="H180" s="4" t="inlineStr"/>
@@ -8226,7 +8214,7 @@
       </c>
       <c r="J180" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/coding-partners/senior-full-stack-engineer-berlin-391720</t>
+          <t>https://www.arbeitnow.com/jobs/companies/bmf-media-information-technology-gmbh/technical-data-manager-augsburg-42188</t>
         </is>
       </c>
       <c r="K180" s="4" t="inlineStr">
@@ -8243,17 +8231,17 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>Laravel Developer (m/w/d) - AI-First PropTech</t>
+          <t>Data Integration &amp; API Engineer m/w/d - Bi &amp; Data Automation</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>Immovara GmbH</t>
+          <t>loyos bi GmbH</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>Korntal-Münchingen</t>
+          <t>Hamburg</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
@@ -8275,7 +8263,7 @@
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/immovara-gmbh/laravel-developer-ai-first-proptech-korntal-munchingen-471269</t>
+          <t>https://www.arbeitnow.com/jobs/companies/loyos-bi-gmbh/data-integration-api-engineer-bi-data-automation-hamburg-66228</t>
         </is>
       </c>
       <c r="K181" s="2" t="inlineStr">
@@ -8292,22 +8280,22 @@
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>Fullstack Softwareentwickler (m/w/d)</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>TecFox GmbH</t>
+          <t>Coding Partners</t>
         </is>
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>Braunschweig</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="E182" s="4" t="inlineStr">
         <is>
-          <t>berufserfahren</t>
+          <t>professional / experienced</t>
         </is>
       </c>
       <c r="F182" s="4" t="inlineStr"/>
@@ -8324,7 +8312,7 @@
       </c>
       <c r="J182" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/tecfox-gmbh/fullstack-softwareentwickler-braunschweig-405178</t>
+          <t>https://www.arbeitnow.com/jobs/companies/coding-partners/senior-full-stack-engineer-berlin-391720</t>
         </is>
       </c>
       <c r="K182" s="4" t="inlineStr">
@@ -8341,17 +8329,17 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>Frontend Softwareentwickler (m/w/d)</t>
+          <t>Laravel Developer (m/w/d) - AI-First PropTech</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>TecFox GmbH</t>
+          <t>Immovara GmbH</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>Braunschweig</t>
+          <t>Korntal-Münchingen</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
@@ -8373,7 +8361,7 @@
       </c>
       <c r="J183" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/tecfox-gmbh/frontend-softwareentwickler-braunschweig-341792</t>
+          <t>https://www.arbeitnow.com/jobs/companies/immovara-gmbh/laravel-developer-ai-first-proptech-korntal-munchingen-471269</t>
         </is>
       </c>
       <c r="K183" s="2" t="inlineStr">
@@ -8390,17 +8378,17 @@
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>Fullstack-Developer*in (m/w/d) Web &amp; AI Automation</t>
+          <t>Fullstack Softwareentwickler (m/w/d)</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>NeoBird Digital</t>
+          <t>TecFox GmbH</t>
         </is>
       </c>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t>Nuremberg</t>
+          <t>Braunschweig</t>
         </is>
       </c>
       <c r="E184" s="4" t="inlineStr">
@@ -8422,7 +8410,7 @@
       </c>
       <c r="J184" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/neobird-digital/fullstack-developerin-web-ai-automation-nuremberg-157752</t>
+          <t>https://www.arbeitnow.com/jobs/companies/tecfox-gmbh/fullstack-softwareentwickler-braunschweig-405178</t>
         </is>
       </c>
       <c r="K184" s="4" t="inlineStr">
@@ -8439,24 +8427,28 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer / Backend &amp; Frontend - Bootstrapped SaaS Startup (m/w/d) remote in EU</t>
+          <t>Frontend Softwareentwickler (m/w/d)</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>DatAds</t>
+          <t>TecFox GmbH</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>Cologne</t>
-        </is>
-      </c>
-      <c r="E185" s="2" t="inlineStr"/>
+          <t>Braunschweig</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
       <c r="F185" s="2" t="inlineStr"/>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Remote, IT</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr"/>
@@ -8467,7 +8459,7 @@
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-bootstrapped-saas-startup-remote-in-eu-cologne-82307</t>
+          <t>https://www.arbeitnow.com/jobs/companies/tecfox-gmbh/frontend-softwareentwickler-braunschweig-341792</t>
         </is>
       </c>
       <c r="K185" s="2" t="inlineStr">
@@ -8484,24 +8476,28 @@
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer / Rest APIs / Cloud / TailwindCSS / SaaS Startup (m/w/d) remote in EU</t>
+          <t>Fullstack-Developer*in (m/w/d) Web &amp; AI Automation</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>DatAds</t>
+          <t>NeoBird Digital</t>
         </is>
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>Cologne</t>
-        </is>
-      </c>
-      <c r="E186" s="4" t="inlineStr"/>
+          <t>Nuremberg</t>
+        </is>
+      </c>
+      <c r="E186" s="4" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
       <c r="F186" s="4" t="inlineStr"/>
       <c r="G186" s="4" t="inlineStr">
         <is>
-          <t>Remote, IT</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H186" s="4" t="inlineStr"/>
@@ -8512,7 +8508,7 @@
       </c>
       <c r="J186" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-bootstrapped-saas-startup-remote-in-eu-cologne-38634</t>
+          <t>https://www.arbeitnow.com/jobs/companies/neobird-digital/fullstack-developerin-web-ai-automation-nuremberg-157752</t>
         </is>
       </c>
       <c r="K186" s="4" t="inlineStr">
@@ -8529,7 +8525,7 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer / Node.js / TypeScript / React / Azure - AdTech SaaS Startup (m/w/d) remote</t>
+          <t>Full-Stack Software Engineer / Backend &amp; Frontend - Bootstrapped SaaS Startup (m/w/d) remote in EU</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
@@ -8557,7 +8553,7 @@
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-adtech-saas-startup-remote-cologne-263746</t>
+          <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-bootstrapped-saas-startup-remote-in-eu-cologne-82307</t>
         </is>
       </c>
       <c r="K187" s="2" t="inlineStr">
@@ -8574,24 +8570,20 @@
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>Senior DevOps / Platform Engineer (f/m/x)</t>
+          <t>Full-Stack Software Engineer / Rest APIs / Cloud / TailwindCSS / SaaS Startup (m/w/d) remote in EU</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>MAIA</t>
+          <t>DatAds</t>
         </is>
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t>Leipzig</t>
-        </is>
-      </c>
-      <c r="E188" s="4" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
+          <t>Cologne</t>
+        </is>
+      </c>
+      <c r="E188" s="4" t="inlineStr"/>
       <c r="F188" s="4" t="inlineStr"/>
       <c r="G188" s="4" t="inlineStr">
         <is>
@@ -8606,7 +8598,7 @@
       </c>
       <c r="J188" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/maia/senior-devops-platform-engineer-leipzig-388068</t>
+          <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-bootstrapped-saas-startup-remote-in-eu-cologne-38634</t>
         </is>
       </c>
       <c r="K188" s="4" t="inlineStr">
@@ -8618,40 +8610,40 @@
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer AI Infrastructure</t>
+          <t>Full-Stack Software Engineer / Node.js / TypeScript / React / Azure - AdTech SaaS Startup (m/w/d) remote</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>Andromeda Cluster</t>
+          <t>DatAds</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Cologne</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr"/>
       <c r="F189" s="2" t="inlineStr"/>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>design, training, technical, software, code, manager, financial, cloud, management, lead, senior, operations, reliability, go, health, engineer, engineering, linux, digital nomad</t>
+          <t>Remote, IT</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr"/>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J189" s="3" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-senior-site-reliability-engineer-ai-infrastructure-andromeda-cluster-1131375</t>
+          <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-adtech-saas-startup-remote-cologne-263746</t>
         </is>
       </c>
       <c r="K189" s="2" t="inlineStr">
@@ -8663,40 +8655,44 @@
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>Senior Financial Analyst Digital Assets</t>
+          <t>Senior DevOps / Platform Engineer (f/m/x)</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>Exodus Movement Inc.</t>
+          <t>MAIA</t>
         </is>
       </c>
       <c r="D190" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E190" s="4" t="inlineStr"/>
+          <t>Leipzig</t>
+        </is>
+      </c>
+      <c r="E190" s="4" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
       <c r="F190" s="4" t="inlineStr"/>
       <c r="G190" s="4" t="inlineStr">
         <is>
-          <t>analyst, cryptocurrency, support, financial, investment, finance, senior, non tech</t>
+          <t>Remote, IT</t>
         </is>
       </c>
       <c r="H190" s="4" t="inlineStr"/>
       <c r="I190" s="4" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J190" s="5" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-senior-financial-analyst-digital-assets-exodus-movement-inc-1131374</t>
+          <t>https://www.arbeitnow.com/jobs/companies/maia/senior-devops-platform-engineer-leipzig-388068</t>
         </is>
       </c>
       <c r="K190" s="4" t="inlineStr">
@@ -8713,24 +8709,24 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>Front End Full Stack Developer</t>
+          <t>Senior Site Reliability Engineer AI Infrastructure</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>Honor Foods</t>
+          <t>Andromeda Cluster</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>Philadelphia, PA</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr"/>
       <c r="F191" s="2" t="inlineStr"/>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>developer, front-end, ui, code, web, operational, backend, digital nomad</t>
+          <t>design, training, technical, software, code, manager, financial, cloud, management, lead, senior, operations, reliability, go, health, engineer, engineering, linux, digital nomad</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr"/>
@@ -8741,7 +8737,7 @@
       </c>
       <c r="J191" s="3" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-front-end-full-stack-developer-honor-foods-1131370</t>
+          <t>https://remoteOK.com/remote-jobs/remote-senior-site-reliability-engineer-ai-infrastructure-andromeda-cluster-1131375</t>
         </is>
       </c>
       <c r="K191" s="2" t="inlineStr">
@@ -8758,10 +8754,14 @@
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>Wing Assistant: Full-Stack Developer</t>
-        </is>
-      </c>
-      <c r="C192" s="4" t="inlineStr"/>
+          <t>Senior Financial Analyst Digital Assets</t>
+        </is>
+      </c>
+      <c r="C192" s="4" t="inlineStr">
+        <is>
+          <t>Exodus Movement Inc.</t>
+        </is>
+      </c>
       <c r="D192" s="4" t="inlineStr">
         <is>
           <t>Remote</t>
@@ -8769,16 +8769,20 @@
       </c>
       <c r="E192" s="4" t="inlineStr"/>
       <c r="F192" s="4" t="inlineStr"/>
-      <c r="G192" s="4" t="inlineStr"/>
+      <c r="G192" s="4" t="inlineStr">
+        <is>
+          <t>analyst, cryptocurrency, support, financial, investment, finance, senior, non tech</t>
+        </is>
+      </c>
       <c r="H192" s="4" t="inlineStr"/>
       <c r="I192" s="4" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J192" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/wing-assistant-full-stack-developer</t>
+          <t>https://remoteOK.com/remote-jobs/remote-senior-financial-analyst-digital-assets-exodus-movement-inc-1131374</t>
         </is>
       </c>
       <c r="K192" s="4" t="inlineStr">
@@ -8795,27 +8799,35 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>Qventus: Product Designer</t>
-        </is>
-      </c>
-      <c r="C193" s="2" t="inlineStr"/>
+          <t>Front End Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>Honor Foods</t>
+        </is>
+      </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Philadelphia, PA</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr"/>
       <c r="F193" s="2" t="inlineStr"/>
-      <c r="G193" s="2" t="inlineStr"/>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>developer, front-end, ui, code, web, operational, backend, digital nomad</t>
+        </is>
+      </c>
       <c r="H193" s="2" t="inlineStr"/>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J193" s="3" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/qventus-product-designer</t>
+          <t>https://remoteOK.com/remote-jobs/remote-front-end-full-stack-developer-honor-foods-1131370</t>
         </is>
       </c>
       <c r="K193" s="2" t="inlineStr">
@@ -8832,7 +8844,7 @@
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>Socure: Senior Product Marketing Manager</t>
+          <t>Wing Assistant: Full-Stack Developer</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr"/>
@@ -8852,7 +8864,7 @@
       </c>
       <c r="J194" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/socure-senior-product-marketing-manager</t>
+          <t>https://weworkremotely.com/remote-jobs/wing-assistant-full-stack-developer</t>
         </is>
       </c>
       <c r="K194" s="4" t="inlineStr">
@@ -8869,7 +8881,7 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>Blueprint: Product Designer</t>
+          <t>Qventus: Product Designer</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr"/>
@@ -8889,7 +8901,7 @@
       </c>
       <c r="J195" s="3" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/blueprint-product-designer</t>
+          <t>https://weworkremotely.com/remote-jobs/qventus-product-designer</t>
         </is>
       </c>
       <c r="K195" s="2" t="inlineStr">
@@ -8906,7 +8918,7 @@
       </c>
       <c r="B196" s="4" t="inlineStr">
         <is>
-          <t>Interop Labs: Product Marketing Manager</t>
+          <t>Socure: Senior Product Marketing Manager</t>
         </is>
       </c>
       <c r="C196" s="4" t="inlineStr"/>
@@ -8926,7 +8938,7 @@
       </c>
       <c r="J196" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/interop-labs-product-marketing-manager</t>
+          <t>https://weworkremotely.com/remote-jobs/socure-senior-product-marketing-manager</t>
         </is>
       </c>
       <c r="K196" s="4" t="inlineStr">
@@ -8943,17 +8955,13 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Link</t>
-        </is>
-      </c>
-      <c r="C197" s="2" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
+          <t>Blueprint: Product Designer</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr"/>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>Toronto, Remote in Canada</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr"/>
@@ -8962,12 +8970,12 @@
       <c r="H197" s="2" t="inlineStr"/>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J197" s="3" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=6447175</t>
+          <t>https://weworkremotely.com/remote-jobs/blueprint-product-designer</t>
         </is>
       </c>
       <c r="K197" s="2" t="inlineStr">
@@ -8984,17 +8992,13 @@
       </c>
       <c r="B198" s="4" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="C198" s="4" t="inlineStr">
-        <is>
-          <t>Reddit</t>
-        </is>
-      </c>
+          <t>Interop Labs: Product Marketing Manager</t>
+        </is>
+      </c>
+      <c r="C198" s="4" t="inlineStr"/>
       <c r="D198" s="4" t="inlineStr">
         <is>
-          <t>Remote - Ontario, Canada</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E198" s="4" t="inlineStr"/>
@@ -9003,12 +9007,12 @@
       <c r="H198" s="4" t="inlineStr"/>
       <c r="I198" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J198" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/6960833</t>
+          <t>https://weworkremotely.com/remote-jobs/interop-labs-product-marketing-manager</t>
         </is>
       </c>
       <c r="K198" s="4" t="inlineStr">
@@ -9025,17 +9029,17 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Full Stack Engineer, Link</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Toronto, Remote in Canada</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr"/>
@@ -9049,10 +9053,92 @@
       </c>
       <c r="J199" s="3" t="inlineStr">
         <is>
+          <t>https://stripe.com/jobs/search?gh_jid=6447175</t>
+        </is>
+      </c>
+      <c r="K199" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B200" s="4" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="C200" s="4" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="D200" s="4" t="inlineStr">
+        <is>
+          <t>Remote - Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="E200" s="4" t="inlineStr"/>
+      <c r="F200" s="4" t="inlineStr"/>
+      <c r="G200" s="4" t="inlineStr"/>
+      <c r="H200" s="4" t="inlineStr"/>
+      <c r="I200" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J200" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/6960833</t>
+        </is>
+      </c>
+      <c r="K200" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr"/>
+      <c r="F201" s="2" t="inlineStr"/>
+      <c r="G201" s="2" t="inlineStr"/>
+      <c r="H201" s="2" t="inlineStr"/>
+      <c r="I201" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J201" s="3" t="inlineStr">
+        <is>
           <t>https://job-boards.greenhouse.io/reddit/jobs/6960831</t>
         </is>
       </c>
-      <c r="K199" s="2" t="inlineStr">
+      <c r="K201" s="2" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>

--- a/remote_jobs.xlsx
+++ b/remote_jobs.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K201"/>
+  <dimension ref="A1:K207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -523,70 +523,74 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, Consumer</t>
+          <t>Full-Stack Entwickler (m/w/d) - .NET 100% Remote</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>FNTIO</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Frankfurt am Main</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Remote, Consulting, Engineering</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7747244</t>
+          <t>https://www.arbeitnow.com/jobs/companies/fntio/full-stack-entwickler-net-100-remote-frankfurt-am-main-495367</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Shopify Developer - Fullstack (m/w/d) in Vollzeit | Remote</t>
+          <t>Software Engineer (Back-end &amp; Computer Vision)</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>we-site GmbH - Shopify Agentur</t>
+          <t>StellDirVor GmbH</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Hamburg</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr"/>
       <c r="F3" s="4" t="inlineStr"/>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>Remote, Web Development</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr"/>
@@ -597,74 +601,70 @@
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/we-site-gmbh-shopify-agentur/shopify-developer-fullstack-in-vollzeit-remote-hamburg-428318</t>
+          <t>https://www.arbeitnow.com/jobs/companies/stelldirvor-gmbh/software-engineer-back-end-computer-vision-munich-286074</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Senior Frontend Developer:in (Angular)</t>
+          <t>Senior Manager, Machine Learning</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Wintama IT Solutions GmbH</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Grünwald</t>
+          <t>Remote - India</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Remote, Software Development</t>
-        </is>
-      </c>
+      <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/wintama-it-solutions-gmbh/senior-frontend-developerin-angular-grunwald-41193</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7919148</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Tooling Engineer</t>
+          <t>Senior Sales Engineer</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Unikraft</t>
+          <t>Glia</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -676,7 +676,7 @@
       <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>golang, cloud, engineer</t>
+          <t>saas, training, architect, technical, support, software, voice, javascript, financial, serverless, api, management, lead, senior, operational, sales, engineer, backend, executive</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
@@ -687,226 +687,214 @@
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-tooling-engineer-unikraft-1131540</t>
+          <t>https://remoteOK.com/remote-jobs/remote-senior-sales-engineer-glia-1131576</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Senior Sofrware Engineer - Full Stack</t>
+          <t>Engenharia Software Engineer III Golang</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Parto Group GmbH</t>
+          <t>Stone</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Hamburg</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Remote, Engineering</t>
+          <t>software, golang, engineer</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/parto-group-gmbh/senior-sofrware-engineer-full-stack-hamburg-207489</t>
+          <t>https://remoteOK.com/remote-jobs/remote-engenharia-software-engineer-iii-golang-stone-1131575</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Product Ownership &amp; Operations)</t>
+          <t>Senior AI System Software Developer</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Yoffix</t>
+          <t>Wealthsimple Technologies</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Contract, professional / experienced</t>
-        </is>
-      </c>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr"/>
       <c r="F7" s="4" t="inlineStr"/>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>Remote, Software Development</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr"/>
+          <t>system, developer, software, react, redis, frontend, full-stack, technical, support, financial, senior, golang, health, engineering, backend, digital nomad</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>$151200 - $189000</t>
+        </is>
+      </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/yoffix/senior-full-stack-engineer-product-ownership-operations-berlin-437578</t>
+          <t>https://remoteOK.com/remote-jobs/remote-senior-ai-system-software-developer-wealthsimple-technologies-1131572</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer / Backend &amp; Frontend - Bootstrapped SaaS Startup (m/w/d) remote in EU</t>
+          <t>Staff Machine Learning Engineer, Consumer</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>DatAds</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Cologne</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Remote, IT</t>
-        </is>
-      </c>
+      <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-bootstrapped-saas-startup-remote-in-eu-cologne-266336</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7747244</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Asset Administration Operations Specialist</t>
+          <t>Shopify Developer - Fullstack (m/w/d) in Vollzeit | Remote</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Forge Global</t>
+          <t>we-site GmbH - Shopify Agentur</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Hamburg</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr"/>
       <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>travel, financial, operations, non tech</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>$21 - $24</t>
-        </is>
-      </c>
+          <t>Remote, Web Development</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr"/>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-asset-administration-operations-specialist-forge-global-1131523</t>
+          <t>https://www.arbeitnow.com/jobs/companies/we-site-gmbh-shopify-agentur/shopify-developer-fullstack-in-vollzeit-remote-hamburg-428318</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer (TypeScript &amp; AWS) (m/w/d)</t>
+          <t>Senior Frontend Developer:in (Angular)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>vOffice Software</t>
+          <t>Wintama IT Solutions GmbH</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Hamburg</t>
+          <t>Grünwald</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -924,83 +912,79 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/voffice-software/senior-cloud-software-engineer-typescript-aws-hamburg-431856</t>
+          <t>https://www.arbeitnow.com/jobs/companies/wintama-it-solutions-gmbh/senior-frontend-developerin-angular-grunwald-41193</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-12</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer RoR (all identities)</t>
+          <t>Tooling Engineer</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Caspar Health</t>
+          <t>Unikraft</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr"/>
       <c r="F11" s="4" t="inlineStr"/>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>Remote, Software Development</t>
+          <t>golang, cloud, engineer</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/caspar-health/senior-backend-engineer-ror-all-identities-berlin-7147</t>
+          <t>https://remoteOK.com/remote-jobs/remote-tooling-engineer-unikraft-1131540</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-12</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Python Software Engineer - Machine Learning Systems (m/f/d)</t>
+          <t>Senior Sofrware Engineer - Full Stack</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>CUJU</t>
+          <t>Parto Group GmbH</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Frankenthal</t>
+          <t>Hamburg</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1011,7 +995,7 @@
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Remote, Software Development</t>
+          <t>Remote, Engineering</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
@@ -1022,45 +1006,45 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/cuju/python-software-engineer-machine-learning-systems-frankenthal-183273</t>
+          <t>https://www.arbeitnow.com/jobs/companies/parto-group-gmbh/senior-sofrware-engineer-full-stack-hamburg-207489</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>AI Algorithm Developer Medical Imaging (m/w/d)</t>
+          <t>Senior Full Stack Engineer (Product Ownership &amp; Operations)</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>citema systems GmbH</t>
+          <t>Yoffix</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>berufserfahren</t>
+          <t>Contract, professional / experienced</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>Remote, IT</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
@@ -1071,89 +1055,93 @@
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/citema-systems-gmbh/ai-algorithm-developer-medical-imaging-munich-91573</t>
+          <t>https://www.arbeitnow.com/jobs/companies/yoffix/senior-full-stack-engineer-product-ownership-operations-berlin-437578</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Full-Stack Software Engineer / Backend &amp; Frontend - Bootstrapped SaaS Startup (m/w/d) remote in EU</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Civitech</t>
+          <t>DatAds</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Austin, TX or Remote</t>
+          <t>Cologne</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>python, support, code, cloud, analytics, engineer, engineering, full-time</t>
+          <t>Remote, IT</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-analytics-engineer-civitech-1131512</t>
+          <t>https://www.arbeitnow.com/jobs/companies/datads/full-stack-software-engineer-backend-frontend-bootstrapped-saas-startup-remote-in-eu-cologne-266336</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Tech Lead</t>
+          <t>Asset Administration Operations Specialist</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Zensurance</t>
+          <t>Forge Global</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Toronto, ON</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr"/>
       <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>design, system, front-end, back-end, security, training, full-stack, docker, technical, support, software, testing, test, growth, code, web, scrum, devops, javascript, education, strategy, management, lead, senior, health, engineering, digital nomad</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr"/>
+          <t>travel, financial, operations, non tech</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>$21 - $24</t>
+        </is>
+      </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
           <t>RemoteOK</t>
@@ -1161,48 +1149,52 @@
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-tech-lead-zensurance-1131509</t>
+          <t>https://remoteOK.com/remote-jobs/remote-asset-administration-operations-specialist-forge-global-1131523</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Senior Full-stack Symfony Developer</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr"/>
+          <t>Senior Cloud Software Engineer (TypeScript &amp; AWS) (m/w/d)</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>vOffice Software</t>
+        </is>
+      </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hamburg</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>symfony, php, javascript, vuejs</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>WorkingNomads</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>https://www.workingnomads.com/job/go/1587815/</t>
+          <t>https://www.arbeitnow.com/jobs/companies/voffice-software/senior-cloud-software-engineer-typescript-aws-hamburg-431856</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1214,36 +1206,44 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Senior Staff Machine Learning Engineer, Feed Relevance</t>
+          <t>Senior Backend Engineer RoR (all identities)</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Caspar Health</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr"/>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
       <c r="F17" s="4" t="inlineStr"/>
-      <c r="G17" s="4" t="inlineStr"/>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Software Development</t>
+        </is>
+      </c>
       <c r="H17" s="4" t="inlineStr"/>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7908786</t>
+          <t>https://www.arbeitnow.com/jobs/companies/caspar-health/senior-backend-engineer-ror-all-identities-berlin-7147</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
@@ -1255,25 +1255,29 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Sidebase Open-Source Contributor &amp; Senior TS Dev (f/m/d)</t>
+          <t>Python Software Engineer - Machine Learning Systems (m/f/d)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Sidestream</t>
+          <t>CUJU</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Cologne</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr"/>
+          <t>Frankenthal</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
@@ -1288,41 +1292,45 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/sidestream/sidebase-open-source-contributor-senior-ts-dev-cologne-317648</t>
+          <t>https://www.arbeitnow.com/jobs/companies/cuju/python-software-engineer-machine-learning-systems-frankenthal-183273</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Senior Typescript Developer (f/m/d)</t>
+          <t>AI Algorithm Developer Medical Imaging (m/w/d)</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Sidestream</t>
+          <t>citema systems GmbH</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Cologne</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr"/>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
       <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>Remote, Software Development</t>
+          <t>Remote, IT</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
@@ -1333,12 +1341,12 @@
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/sidestream/senior-typescript-developer-cologne-220463</t>
+          <t>https://www.arbeitnow.com/jobs/companies/citema-systems-gmbh/ai-algorithm-developer-medical-imaging-munich-91573</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -1350,40 +1358,40 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Senior AI-Engineer / Agent-Architekt (m/w/d)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Neurawork GmbH &amp; Co. KG</t>
+          <t>Civitech</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Ampfing</t>
+          <t>Austin, TX or Remote</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Remote, IT</t>
+          <t>python, support, code, cloud, analytics, engineer, engineering, full-time</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/neurawork-gmbh-co-kg/senior-ai-engineer-agent-architekt-ampfing-390691</t>
+          <t>https://remoteOK.com/remote-jobs/remote-analytics-engineer-civitech-1131512</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -1395,44 +1403,40 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Senior AI Consultant / Machine Learning Engineer (m/w/d) Public Sector | &gt;90% REMOTE</t>
+          <t>Tech Lead</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Bridgency HR Management GbR</t>
+          <t>Zensurance</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Usingen</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>berufserfahren</t>
-        </is>
-      </c>
+          <t>Toronto, ON</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr"/>
       <c r="F21" s="4" t="inlineStr"/>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>Remote, Consulting, Engineering</t>
+          <t>design, system, front-end, back-end, security, training, full-stack, docker, technical, support, software, testing, test, growth, code, web, scrum, devops, javascript, education, strategy, management, lead, senior, health, engineering, digital nomad</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/bridgency-hr-management-gbr/senior-ai-consultant-machine-learning-engineer-public-sector-90-remote-usingen-94077</t>
+          <t>https://remoteOK.com/remote-jobs/remote-tech-lead-zensurance-1131509</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -1444,452 +1448,440 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Werkstudent (m/w/d) Frontend Development &amp; KI-Integration (20h/Woche)</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>MEvents Cross Media GmbH</t>
-        </is>
-      </c>
+          <t>Senior Full-stack Symfony Developer</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr"/>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>hilfstätigkeit / student</t>
-        </is>
-      </c>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Remote, Software Development</t>
+          <t>symfony, php, javascript, vuejs</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>WorkingNomads</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/mevents-cross-media-gmbh/werkstudent-frontend-development-ki-integration-20h-woche-berlin-378282</t>
+          <t>https://www.workingnomads.com/job/go/1587815/</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Staff Machine Learning Engineer, Feed Relevance</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Valon Mortgage</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr"/>
       <c r="F23" s="4" t="inlineStr"/>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>design, saas, python, architect, technical, support, cloud, strategy, management, senior, operations, operational, analytics, reliability, go, engineer, engineering, digital nomad</t>
-        </is>
-      </c>
+      <c r="G23" s="4" t="inlineStr"/>
       <c r="H23" s="4" t="inlineStr"/>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-senior-data-engineer-valon-mortgage-1131504</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7908786</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Senior AI Agent Architect / AI Automation Architect</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr"/>
+          <t>Sidebase Open-Source Contributor &amp; Senior TS Dev (f/m/d)</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Sidestream</t>
+        </is>
+      </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Cologne</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>artificial intelligence, python, machine learning, engineer, communication</t>
+          <t>Remote, Software Development</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr">
         <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/sidestream/sidebase-open-source-contributor-senior-ts-dev-cologne-317648</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Senior Typescript Developer (f/m/d)</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Sidestream</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Cologne</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr"/>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Software Development</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr"/>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/sidestream/senior-typescript-developer-cologne-220463</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Senior AI-Engineer / Agent-Architekt (m/w/d)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Neurawork GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Ampfing</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Remote, IT</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/neurawork-gmbh-co-kg/senior-ai-engineer-agent-architekt-ampfing-390691</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Senior AI Consultant / Machine Learning Engineer (m/w/d) Public Sector | &gt;90% REMOTE</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Bridgency HR Management GbR</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Usingen</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr"/>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Consulting, Engineering</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr"/>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/bridgency-hr-management-gbr/senior-ai-consultant-machine-learning-engineer-public-sector-90-remote-usingen-94077</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Werkstudent (m/w/d) Frontend Development &amp; KI-Integration (20h/Woche)</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>MEvents Cross Media GmbH</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>hilfstätigkeit / student</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Remote, Software Development</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/mevents-cross-media-gmbh/werkstudent-frontend-development-ki-integration-20h-woche-berlin-378282</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Valon Mortgage</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr"/>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>design, saas, python, architect, technical, support, cloud, strategy, management, senior, operations, operational, analytics, reliability, go, engineer, engineering, digital nomad</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr"/>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-senior-data-engineer-valon-mortgage-1131504</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Senior AI Agent Architect / AI Automation Architect</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>artificial intelligence, python, machine learning, engineer, communication</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
           <t>WorkingNomads</t>
         </is>
       </c>
-      <c r="J24" s="3" t="inlineStr">
+      <c r="J30" s="3" t="inlineStr">
         <is>
           <t>https://www.workingnomads.com/job/go/1585195/</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>2026-05-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Weiterbildung: Data Science &amp; Business Analytics (IHK) (m/w/d) - Remote</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>DataSmart Point GmbH</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Apprenticeship</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>Remote, Data Scientist</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr"/>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/datasmart-point-gmbh/weiterbildung-data-science-business-analytics-ihk-remote-berlin-23738</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Karrierestart in Data &amp; AI - IHK Data Analyst (m/w/d) - 100 % Online</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>DataSmart Point GmbH</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>Apprenticeship</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr"/>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Data Scientist</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr"/>
-      <c r="I26" s="4" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J26" s="5" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/datasmart-point-gmbh/karrierestart-in-data-ai-ihk-data-analyst-100-online-berlin-138911</t>
-        </is>
-      </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Rockstardevelopers: Senior Fullstack Entwickler (m/w/d) mit Projekterfahrung Deutsche Bahn oder DB Systel</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Rockstardevelopers GmbH</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>Stuttgart</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>berufserfahren</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr"/>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>Remote, Software Development</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/rockstardevelopers-gmbh/rockstardevelopers-senior-fullstack-entwickler-mit-projekterfahrung-deutsche-bahn-oder-db-systel-stuttgart-354361</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Full-Stack AI Engineer (Computer Vision &amp; Back-end Focus)</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>StellDirVor GmbH</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr"/>
-      <c r="F28" s="4" t="inlineStr"/>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Software Development</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr"/>
-      <c r="I28" s="4" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J28" s="5" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/stelldirvor-gmbh/full-stack-ai-engineer-computer-vision-back-end-focus-munich-122395</t>
-        </is>
-      </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Prove</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr"/>
-      <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>software, security, senior, engineer, engineering</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr"/>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>RemoteOK</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>https://remoteOK.com/remote-jobs/remote-senior-software-engineer-prove-1131482</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>Akuity</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr"/>
-      <c r="F30" s="4" t="inlineStr"/>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>saas, developer, software, code, devops, senior, engineer, engineering, backend, digital nomad</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr"/>
-      <c r="I30" s="4" t="inlineStr">
-        <is>
-          <t>RemoteOK</t>
-        </is>
-      </c>
-      <c r="J30" s="5" t="inlineStr">
-        <is>
-          <t>https://remoteOK.com/remote-jobs/remote-senior-backend-engineer-akuity-1131479</t>
-        </is>
-      </c>
-      <c r="K30" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Medical Affairs Solutions Manager UK</t>
+          <t>Weiterbildung: Data Science &amp; Business Analytics (IHK) (m/w/d) - Remote</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Sorcero</t>
+          <t>DataSmart Point GmbH</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr"/>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Apprenticeship</t>
+        </is>
+      </c>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>manager, growth, operations, biotech</t>
+          <t>Remote, Data Scientist</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-medical-affairs-solutions-manager-uk-sorcero-1131475</t>
+          <t>https://www.arbeitnow.com/jobs/companies/datasmart-point-gmbh/weiterbildung-data-science-business-analytics-ihk-remote-berlin-23738</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1901,36 +1893,44 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Karrierestart in Data &amp; AI - IHK Data Analyst (m/w/d) - 100 % Online</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Dropbox</t>
+          <t>DataSmart Point GmbH</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Remote - Canada: Select locations</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr"/>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>Apprenticeship</t>
+        </is>
+      </c>
       <c r="F32" s="4" t="inlineStr"/>
-      <c r="G32" s="4" t="inlineStr"/>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Data Scientist</t>
+        </is>
+      </c>
       <c r="H32" s="4" t="inlineStr"/>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7762007?gh_jid=7762007</t>
+          <t>https://www.arbeitnow.com/jobs/companies/datasmart-point-gmbh/karrierestart-in-data-ai-ihk-data-analyst-100-online-berlin-138911</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
@@ -1942,36 +1942,44 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Rockstardevelopers: Senior Fullstack Entwickler (m/w/d) mit Projekterfahrung Deutsche Bahn oder DB Systel</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Dropbox</t>
+          <t>Rockstardevelopers GmbH</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Remote - US: Select locations</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr"/>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
       <c r="F33" s="2" t="inlineStr"/>
-      <c r="G33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Remote, Software Development</t>
+        </is>
+      </c>
       <c r="H33" s="2" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7762004?gh_jid=7762004</t>
+          <t>https://www.arbeitnow.com/jobs/companies/rockstardevelopers-gmbh/rockstardevelopers-senior-fullstack-entwickler-mit-projekterfahrung-deutsche-bahn-oder-db-systel-stuttgart-354361</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -1983,36 +1991,40 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Full-Stack AI Engineer (Computer Vision &amp; Back-end Focus)</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Dropbox</t>
+          <t>StellDirVor GmbH</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Remote - Mexico</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr"/>
       <c r="F34" s="4" t="inlineStr"/>
-      <c r="G34" s="4" t="inlineStr"/>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Software Development</t>
+        </is>
+      </c>
       <c r="H34" s="4" t="inlineStr"/>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7762009?gh_jid=7762009</t>
+          <t>https://www.arbeitnow.com/jobs/companies/stelldirvor-gmbh/full-stack-ai-engineer-computer-vision-back-end-focus-munich-122395</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
@@ -2029,31 +2041,35 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Frontend Product Software Engineer, Web DX</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Dropbox</t>
+          <t>Prove</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Remote - Mexico</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="2" t="inlineStr"/>
-      <c r="G35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>software, security, senior, engineer, engineering</t>
+        </is>
+      </c>
       <c r="H35" s="2" t="inlineStr"/>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7580431?gh_jid=7580431</t>
+          <t>https://remoteOK.com/remote-jobs/remote-senior-software-engineer-prove-1131482</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2070,31 +2086,35 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer, Dash Experiences</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Dropbox</t>
+          <t>Akuity</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Remote - US: Select locations</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr"/>
       <c r="F36" s="4" t="inlineStr"/>
-      <c r="G36" s="4" t="inlineStr"/>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>saas, developer, software, code, devops, senior, engineer, engineering, backend, digital nomad</t>
+        </is>
+      </c>
       <c r="H36" s="4" t="inlineStr"/>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7569140?gh_jid=7569140</t>
+          <t>https://remoteOK.com/remote-jobs/remote-senior-backend-engineer-akuity-1131479</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
@@ -2111,31 +2131,35 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer, Dash Experiences</t>
+          <t>Medical Affairs Solutions Manager UK</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Dropbox</t>
+          <t>Sorcero</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Remote - Mexico</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="2" t="inlineStr"/>
-      <c r="G37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>manager, growth, operations, biotech</t>
+        </is>
+      </c>
       <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7569145?gh_jid=7569145</t>
+          <t>https://remoteOK.com/remote-jobs/remote-medical-affairs-solutions-manager-uk-sorcero-1131475</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2152,7 +2176,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Product Software Engineer, Payments</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -2162,7 +2186,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Remote - Poland</t>
+          <t>Remote - Canada: Select locations</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr"/>
@@ -2176,7 +2200,7 @@
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7812915?gh_jid=7812915</t>
+          <t>https://jobs.dropbox.com/listing/7762007?gh_jid=7762007</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
@@ -2193,7 +2217,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, AI Products</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2203,7 +2227,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Remote - Canada: Select locations</t>
+          <t>Remote - US: Select locations</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr"/>
@@ -2217,7 +2241,7 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7789389?gh_jid=7789389</t>
+          <t>https://jobs.dropbox.com/listing/7762004?gh_jid=7762004</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2234,7 +2258,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, AI Products</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -2244,7 +2268,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Remote - Canada: Select locations</t>
+          <t>Remote - Mexico</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr"/>
@@ -2258,7 +2282,7 @@
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7729764?gh_jid=7729764</t>
+          <t>https://jobs.dropbox.com/listing/7762009?gh_jid=7762009</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
@@ -2275,7 +2299,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, AI Products</t>
+          <t>Frontend Product Software Engineer, Web DX</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2285,7 +2309,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Remote - US: Select locations</t>
+          <t>Remote - Mexico</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr"/>
@@ -2299,7 +2323,7 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7729761?gh_jid=7729761</t>
+          <t>https://jobs.dropbox.com/listing/7580431?gh_jid=7580431</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -2316,7 +2340,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, AI Products</t>
+          <t>Full Stack Software Engineer, Dash Experiences</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -2340,7 +2364,7 @@
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7789386?gh_jid=7789386</t>
+          <t>https://jobs.dropbox.com/listing/7569140?gh_jid=7569140</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
@@ -2357,7 +2381,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Dash Agentic AI</t>
+          <t>Full Stack Software Engineer, Dash Experiences</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2367,7 +2391,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Remote - Canada: Select locations</t>
+          <t>Remote - Mexico</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
@@ -2381,7 +2405,7 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7644890?gh_jid=7644890</t>
+          <t>https://jobs.dropbox.com/listing/7569145?gh_jid=7569145</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -2398,7 +2422,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Dash Agentic AI</t>
+          <t>Senior Backend Product Software Engineer, Payments</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -2408,7 +2432,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Remote - US: All locations</t>
+          <t>Remote - Poland</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr"/>
@@ -2422,7 +2446,7 @@
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7644886?gh_jid=7644886</t>
+          <t>https://jobs.dropbox.com/listing/7812915?gh_jid=7812915</t>
         </is>
       </c>
       <c r="K44" s="4" t="inlineStr">
@@ -2439,7 +2463,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Staff Backend Product Software Engineer, Commerce Platform</t>
+          <t>Senior Data Scientist, AI Products</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2449,7 +2473,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Remote - Mexico</t>
+          <t>Remote - Canada: Select locations</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -2463,7 +2487,7 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7759733?gh_jid=7759733</t>
+          <t>https://jobs.dropbox.com/listing/7789389?gh_jid=7789389</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -2480,7 +2504,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Staff Backend Product Software Engineer, Commerce Platform</t>
+          <t>Senior Data Scientist, AI Products</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -2490,7 +2514,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Remote - US: Select locations</t>
+          <t>Remote - Canada: Select locations</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr"/>
@@ -2504,7 +2528,7 @@
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7759728?gh_jid=7759728</t>
+          <t>https://jobs.dropbox.com/listing/7729764?gh_jid=7729764</t>
         </is>
       </c>
       <c r="K46" s="4" t="inlineStr">
@@ -2521,7 +2545,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Staff Backend Product Software Engineer, Commerce Platform</t>
+          <t>Senior Data Scientist, AI Products</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2531,7 +2555,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Remote - Canada: Select locations</t>
+          <t>Remote - US: Select locations</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr"/>
@@ -2545,7 +2569,7 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7759731?gh_jid=7759731</t>
+          <t>https://jobs.dropbox.com/listing/7729761?gh_jid=7729761</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -2562,7 +2586,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Staff Backend Product Software Engineer, Core</t>
+          <t>Senior Data Scientist, AI Products</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -2586,7 +2610,7 @@
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7421121?gh_jid=7421121</t>
+          <t>https://jobs.dropbox.com/listing/7789386?gh_jid=7789386</t>
         </is>
       </c>
       <c r="K48" s="4" t="inlineStr">
@@ -2603,7 +2627,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Staff Backend Product Software Engineer, Core</t>
+          <t>Senior Machine Learning Engineer, Dash Agentic AI</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2627,7 +2651,7 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7421124?gh_jid=7421124</t>
+          <t>https://jobs.dropbox.com/listing/7644890?gh_jid=7644890</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -2644,7 +2668,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Staff Fullstack Product Software Engineer, Dash</t>
+          <t>Senior Machine Learning Engineer, Dash Agentic AI</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -2654,7 +2678,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Remote - Canada: Select locations</t>
+          <t>Remote - US: All locations</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr"/>
@@ -2668,7 +2692,7 @@
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7551548?gh_jid=7551548</t>
+          <t>https://jobs.dropbox.com/listing/7644886?gh_jid=7644886</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
@@ -2685,7 +2709,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Staff Fullstack Product Software Engineer, Dash</t>
+          <t>Staff Backend Product Software Engineer, Commerce Platform</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2695,7 +2719,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Remote - US: Select locations</t>
+          <t>Remote - Mexico</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr"/>
@@ -2709,7 +2733,7 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7551545?gh_jid=7551545</t>
+          <t>https://jobs.dropbox.com/listing/7759733?gh_jid=7759733</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -2726,7 +2750,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Staff Full Stack Software Engineer, Churn</t>
+          <t>Staff Backend Product Software Engineer, Commerce Platform</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -2736,7 +2760,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Remote - Poland</t>
+          <t>Remote - US: Select locations</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr"/>
@@ -2750,7 +2774,7 @@
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7421131?gh_jid=7421131</t>
+          <t>https://jobs.dropbox.com/listing/7759728?gh_jid=7759728</t>
         </is>
       </c>
       <c r="K52" s="4" t="inlineStr">
@@ -2767,7 +2791,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Staff Fullstack Software Engineer, Growth Monetization</t>
+          <t>Staff Backend Product Software Engineer, Commerce Platform</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -2777,7 +2801,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Remote - US: Select locations</t>
+          <t>Remote - Canada: Select locations</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr"/>
@@ -2791,7 +2815,7 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7421150?gh_jid=7421150</t>
+          <t>https://jobs.dropbox.com/listing/7759731?gh_jid=7759731</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -2808,7 +2832,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Staff Fullstack Software Engineer, Growth Monetization</t>
+          <t>Staff Backend Product Software Engineer, Core</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -2818,7 +2842,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Remote - Canada: Select locations</t>
+          <t>Remote - US: Select locations</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr"/>
@@ -2832,7 +2856,7 @@
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7421153?gh_jid=7421153</t>
+          <t>https://jobs.dropbox.com/listing/7421121?gh_jid=7421121</t>
         </is>
       </c>
       <c r="K54" s="4" t="inlineStr">
@@ -2849,13 +2873,17 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>WALTER: Senior Fullstack Engineer (Ruby+React)</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr"/>
+          <t>Staff Backend Product Software Engineer, Core</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Dropbox</t>
+        </is>
+      </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote - Canada: Select locations</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr"/>
@@ -2864,17 +2892,17 @@
       <c r="H55" s="2" t="inlineStr"/>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/walter-senior-fullstack-engineer-ruby-react</t>
+          <t>https://jobs.dropbox.com/listing/7421124?gh_jid=7421124</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
     </row>
@@ -2886,13 +2914,17 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>WALTER: Full-Stack Engineering Lead</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr"/>
+          <t>Staff Fullstack Product Software Engineer, Dash</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>Dropbox</t>
+        </is>
+      </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote - Canada: Select locations</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr"/>
@@ -2901,17 +2933,17 @@
       <c r="H56" s="4" t="inlineStr"/>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/walter-full-stack-engineering-lead</t>
+          <t>https://jobs.dropbox.com/listing/7551548?gh_jid=7551548</t>
         </is>
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2955,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Frontend Product Software Engineer, Design Systems</t>
+          <t>Staff Fullstack Product Software Engineer, Dash</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -2933,7 +2965,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Remote - Mexico</t>
+          <t>Remote - US: Select locations</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr"/>
@@ -2947,165 +2979,153 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/7862086?gh_jid=7862086</t>
+          <t>https://jobs.dropbox.com/listing/7551545?gh_jid=7551545</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Lead AI Engineer &amp; Technical Architect</t>
+          <t>Staff Full Stack Software Engineer, Churn</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Bold Business</t>
+          <t>Dropbox</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>India, Latin America, Philippines</t>
+          <t>Remote - Poland</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr"/>
       <c r="F58" s="4" t="inlineStr"/>
-      <c r="G58" s="4" t="inlineStr">
-        <is>
-          <t>architect, technical, lead, engineer</t>
-        </is>
-      </c>
+      <c r="G58" s="4" t="inlineStr"/>
       <c r="H58" s="4" t="inlineStr"/>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-lead-ai-engineer-technical-architect-bold-business-1131461</t>
+          <t>https://jobs.dropbox.com/listing/7421131?gh_jid=7421131</t>
         </is>
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer Showroom</t>
+          <t>Staff Fullstack Software Engineer, Growth Monetization</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Higharc</t>
+          <t>Dropbox</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote - US: Select locations</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr"/>
       <c r="F59" s="2" t="inlineStr"/>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>software, design, 3d, full-stack, support, ux, manager, api, engineer, engineering, backend, digital nomad</t>
-        </is>
-      </c>
+      <c r="G59" s="2" t="inlineStr"/>
       <c r="H59" s="2" t="inlineStr"/>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>RemoteOK</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-software-engineer-showroom-higharc-1131457</t>
+          <t>https://jobs.dropbox.com/listing/7421150?gh_jid=7421150</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Protocol Review Specialist</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr"/>
+          <t>Staff Fullstack Software Engineer, Growth Monetization</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>Dropbox</t>
+        </is>
+      </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote - Canada: Select locations</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr"/>
       <c r="F60" s="4" t="inlineStr"/>
-      <c r="G60" s="4" t="inlineStr">
-        <is>
-          <t>communication, phone, english</t>
-        </is>
-      </c>
+      <c r="G60" s="4" t="inlineStr"/>
       <c r="H60" s="4" t="inlineStr"/>
       <c r="I60" s="4" t="inlineStr">
         <is>
-          <t>WorkingNomads</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J60" s="5" t="inlineStr">
         <is>
-          <t>https://www.workingnomads.com/job/go/1580747/</t>
+          <t>https://jobs.dropbox.com/listing/7421153?gh_jid=7421153</t>
         </is>
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Staff AI Engineer - Notebooks</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>Datadog</t>
-        </is>
-      </c>
+          <t>WALTER: Senior Fullstack Engineer (Ruby+React)</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr"/>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Portugal, Remote</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr"/>
@@ -3114,12 +3134,12 @@
       <c r="H61" s="2" t="inlineStr"/>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>https://careers.datadoghq.com/detail/7627445/?gh_jid=7627445</t>
+          <t>https://weworkremotely.com/remote-jobs/walter-senior-fullstack-engineer-ruby-react</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -3131,22 +3151,18 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Staff AI Engineer - Notebooks</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>Datadog</t>
-        </is>
-      </c>
+          <t>WALTER: Full-Stack Engineering Lead</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr"/>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>France, Remote; Germany, Remote; Ireland, Remote; Italy, Remote; Spain, Remote; Switzerland, Remote</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr"/>
@@ -3155,12 +3171,12 @@
       <c r="H62" s="4" t="inlineStr"/>
       <c r="I62" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
-          <t>https://careers.datadoghq.com/detail/7627429/?gh_jid=7627429</t>
+          <t>https://weworkremotely.com/remote-jobs/walter-full-stack-engineering-lead</t>
         </is>
       </c>
       <c r="K62" s="4" t="inlineStr">
@@ -3172,22 +3188,22 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Ads Conversion Modeling, Machine Learning Engineering Manager</t>
+          <t>Frontend Product Software Engineer, Design Systems</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Dropbox</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Remote - Mexico</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr"/>
@@ -3201,7 +3217,7 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7792848</t>
+          <t>https://jobs.dropbox.com/listing/7862086?gh_jid=7862086</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -3218,31 +3234,35 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Data Scientist, Ads</t>
+          <t>Lead AI Engineer &amp; Technical Architect</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Bold Business</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Remote - British Columbia, Canada</t>
+          <t>India, Latin America, Philippines</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr"/>
       <c r="F64" s="4" t="inlineStr"/>
-      <c r="G64" s="4" t="inlineStr"/>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>architect, technical, lead, engineer</t>
+        </is>
+      </c>
       <c r="H64" s="4" t="inlineStr"/>
       <c r="I64" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7607124</t>
+          <t>https://remoteOK.com/remote-jobs/remote-lead-ai-engineer-technical-architect-bold-business-1131461</t>
         </is>
       </c>
       <c r="K64" s="4" t="inlineStr">
@@ -3259,31 +3279,35 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Data Scientist, Ads</t>
+          <t>Software Engineer Showroom</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Higharc</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr"/>
       <c r="F65" s="2" t="inlineStr"/>
-      <c r="G65" s="2" t="inlineStr"/>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>software, design, 3d, full-stack, support, ux, manager, api, engineer, engineering, backend, digital nomad</t>
+        </is>
+      </c>
       <c r="H65" s="2" t="inlineStr"/>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>RemoteOK</t>
         </is>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/6580815</t>
+          <t>https://remoteOK.com/remote-jobs/remote-software-engineer-showroom-higharc-1131457</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -3300,31 +3324,31 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="C66" s="4" t="inlineStr">
-        <is>
-          <t>Reddit</t>
-        </is>
-      </c>
+          <t>Protocol Review Specialist</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr"/>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Remote - Ontario, Canada</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr"/>
       <c r="F66" s="4" t="inlineStr"/>
-      <c r="G66" s="4" t="inlineStr"/>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>communication, phone, english</t>
+        </is>
+      </c>
       <c r="H66" s="4" t="inlineStr"/>
       <c r="I66" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WorkingNomads</t>
         </is>
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7131934</t>
+          <t>https://www.workingnomads.com/job/go/1580747/</t>
         </is>
       </c>
       <c r="K66" s="4" t="inlineStr">
@@ -3341,17 +3365,17 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Staff AI Engineer - Notebooks</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Datadog</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Portugal, Remote</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr"/>
@@ -3365,7 +3389,7 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7131932</t>
+          <t>https://careers.datadoghq.com/detail/7627445/?gh_jid=7627445</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -3382,17 +3406,17 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Principal Data Scientist, Ads</t>
+          <t>Staff AI Engineer - Notebooks</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Datadog</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>France, Remote; Germany, Remote; Ireland, Remote; Italy, Remote; Spain, Remote; Switzerland, Remote</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr"/>
@@ -3406,7 +3430,7 @@
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7330347</t>
+          <t>https://careers.datadoghq.com/detail/7627429/?gh_jid=7627429</t>
         </is>
       </c>
       <c r="K68" s="4" t="inlineStr">
@@ -3423,7 +3447,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Ads</t>
+          <t>Ads Conversion Modeling, Machine Learning Engineering Manager</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -3433,7 +3457,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Remote - British Columbia, Canada</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr"/>
@@ -3447,7 +3471,7 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7607121</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7792848</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -3464,7 +3488,7 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Ads</t>
+          <t>Data Scientist, Ads</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -3474,7 +3498,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Remote - British Columbia, Canada</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr"/>
@@ -3488,7 +3512,7 @@
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/6042236</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7607124</t>
         </is>
       </c>
       <c r="K70" s="4" t="inlineStr">
@@ -3505,7 +3529,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Consumer</t>
+          <t>Data Scientist, Ads</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -3529,7 +3553,7 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7275414</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/6580815</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -3546,7 +3570,7 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Senior  Machine Learning Engineer, ML Training Platform</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -3556,7 +3580,7 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Remote - Ontario, Canada</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr"/>
@@ -3570,7 +3594,7 @@
       </c>
       <c r="J72" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7074776</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7131934</t>
         </is>
       </c>
       <c r="K72" s="4" t="inlineStr">
@@ -3587,7 +3611,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Systems Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -3611,7 +3635,7 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7731772</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7131932</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -3628,7 +3652,7 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, GenAI Platform</t>
+          <t>Principal Data Scientist, Ads</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -3652,7 +3676,7 @@
       </c>
       <c r="J74" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7753480</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7330347</t>
         </is>
       </c>
       <c r="K74" s="4" t="inlineStr">
@@ -3669,7 +3693,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Senior Staff Machine Learning Engineer, GenAI Platform</t>
+          <t>Senior Data Scientist, Ads</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -3679,7 +3703,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Remote - British Columbia, Canada</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr"/>
@@ -3693,7 +3717,7 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7772274</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7607121</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -3710,7 +3734,7 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Staff Data Scientist, Ads</t>
+          <t>Senior Data Scientist, Ads</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
@@ -3720,7 +3744,7 @@
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Remote - British Columbia, Canada</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr"/>
@@ -3734,7 +3758,7 @@
       </c>
       <c r="J76" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7721851</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/6042236</t>
         </is>
       </c>
       <c r="K76" s="4" t="inlineStr">
@@ -3751,7 +3775,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Staff Data Scientist, Ads</t>
+          <t>Senior Data Scientist, Consumer</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -3775,7 +3799,7 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7721787</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7275414</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -3792,7 +3816,7 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Staff Data Scientist, Consumer</t>
+          <t>Senior  Machine Learning Engineer, ML Training Platform</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -3816,7 +3840,7 @@
       </c>
       <c r="J78" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/6745284</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7074776</t>
         </is>
       </c>
       <c r="K78" s="4" t="inlineStr">
@@ -3833,7 +3857,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Staff Data Scientist, Marketing</t>
+          <t>Senior Machine Learning Systems Engineer</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -3857,7 +3881,7 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7445240</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7731772</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -3874,7 +3898,7 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, Ads Auction (Ads Marketplace Quality)</t>
+          <t>Senior Software Engineer, GenAI Platform</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
@@ -3898,7 +3922,7 @@
       </c>
       <c r="J80" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7181821</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7753480</t>
         </is>
       </c>
       <c r="K80" s="4" t="inlineStr">
@@ -3915,7 +3939,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, Ads Content Understanding</t>
+          <t>Senior Staff Machine Learning Engineer, GenAI Platform</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -3939,7 +3963,7 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7851761</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7772274</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -3956,7 +3980,7 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Systems Engineer</t>
+          <t>Staff Data Scientist, Ads</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -3966,7 +3990,7 @@
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Remote - British Columbia, Canada</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr"/>
@@ -3980,7 +4004,7 @@
       </c>
       <c r="J82" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7731788</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7721851</t>
         </is>
       </c>
       <c r="K82" s="4" t="inlineStr">
@@ -3997,44 +4021,36 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Werkstudent:in KI Marketing (m/w/d)</t>
+          <t>Staff Data Scientist, Ads</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>laria.ai</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>Working student, berufseinstieg</t>
-        </is>
-      </c>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr"/>
       <c r="F83" s="2" t="inlineStr"/>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>Remote, Online Marketing</t>
-        </is>
-      </c>
+      <c r="G83" s="2" t="inlineStr"/>
       <c r="H83" s="2" t="inlineStr"/>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/lariaai/werkstudentin-ki-marketing-berlin-9847</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7721787</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -4046,107 +4062,99 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Laravel Developer (m/w/d) - AI-First PropTech</t>
+          <t>Staff Data Scientist, Consumer</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>Immovara GmbH</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Korntal-Münchingen</t>
-        </is>
-      </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>berufserfahren</t>
-        </is>
-      </c>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr"/>
       <c r="F84" s="4" t="inlineStr"/>
-      <c r="G84" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Software Development</t>
-        </is>
-      </c>
+      <c r="G84" s="4" t="inlineStr"/>
       <c r="H84" s="4" t="inlineStr"/>
       <c r="I84" s="4" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J84" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/immovara-gmbh/laravel-developer-ai-first-proptech-korntal-munchingen-239743</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/6745284</t>
         </is>
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning (ML) Engineer - Applied</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr"/>
+          <t>Staff Data Scientist, Marketing</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr"/>
       <c r="F85" s="2" t="inlineStr"/>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>machine learning, artificial intelligence, python, cplusplus, startup</t>
-        </is>
-      </c>
+      <c r="G85" s="2" t="inlineStr"/>
       <c r="H85" s="2" t="inlineStr"/>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>WorkingNomads</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>https://www.workingnomads.com/job/go/1578553/</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7445240</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Backend Engineer, AI Security</t>
+          <t>Staff Machine Learning Engineer, Ads Auction (Ads Marketplace Quality)</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>New York, San Francisco, Seattle, or Remote (US/Canada)</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr"/>
@@ -4160,34 +4168,34 @@
       </c>
       <c r="J86" s="5" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7826765</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7181821</t>
         </is>
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Backend Engineer, Core Tech, Canada</t>
+          <t>Staff Machine Learning Engineer, Ads Content Understanding</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Toronto, CAN-Remote</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr"/>
@@ -4201,34 +4209,34 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=6567253</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7851761</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Backend Engineer, Core Technology</t>
+          <t>Staff Machine Learning Systems Engineer</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>US-Remote, Chicago</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr"/>
@@ -4242,48 +4250,56 @@
       </c>
       <c r="J88" s="5" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=6042172</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7731788</t>
         </is>
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Backend Engineer, Developer Experience &amp; Product Platform</t>
+          <t>Werkstudent:in KI Marketing (m/w/d)</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>laria.ai</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Toronto Canada, San Francisco, Remote in US, Remote in Canada</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr"/>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Working student, berufseinstieg</t>
+        </is>
+      </c>
       <c r="F89" s="2" t="inlineStr"/>
-      <c r="G89" s="2" t="inlineStr"/>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>Remote, Online Marketing</t>
+        </is>
+      </c>
       <c r="H89" s="2" t="inlineStr"/>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7292520</t>
+          <t>https://www.arbeitnow.com/jobs/companies/lariaai/werkstudentin-ki-marketing-berlin-9847</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -4295,36 +4311,44 @@
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Commercial Counsel, Crypto</t>
+          <t>Laravel Developer (m/w/d) - AI-First PropTech</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Immovara GmbH</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>New York City, Seattle, San Francisco, Chicago, Atlanta, US-Remote</t>
-        </is>
-      </c>
-      <c r="E90" s="4" t="inlineStr"/>
+          <t>Korntal-Münchingen</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
       <c r="F90" s="4" t="inlineStr"/>
-      <c r="G90" s="4" t="inlineStr"/>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Software Development</t>
+        </is>
+      </c>
       <c r="H90" s="4" t="inlineStr"/>
       <c r="I90" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J90" s="5" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7392188</t>
+          <t>https://www.arbeitnow.com/jobs/companies/immovara-gmbh/laravel-developer-ai-first-proptech-korntal-munchingen-239743</t>
         </is>
       </c>
       <c r="K90" s="4" t="inlineStr">
@@ -4341,31 +4365,31 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Fullstack Engineer, Privy</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
+          <t>Machine Learning (ML) Engineer - Applied</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr"/>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">NYC-Privy, US-Remote </t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr"/>
       <c r="F91" s="2" t="inlineStr"/>
-      <c r="G91" s="2" t="inlineStr"/>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>machine learning, artificial intelligence, python, cplusplus, startup</t>
+        </is>
+      </c>
       <c r="H91" s="2" t="inlineStr"/>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WorkingNomads</t>
         </is>
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7091959</t>
+          <t>https://www.workingnomads.com/job/go/1578553/</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -4382,7 +4406,7 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Stripe Assistant</t>
+          <t>Backend Engineer, AI Security</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -4392,7 +4416,7 @@
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>Seattle; San Francisco; New York City; Remote</t>
+          <t>New York, San Francisco, Seattle, or Remote (US/Canada)</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr"/>
@@ -4406,7 +4430,7 @@
       </c>
       <c r="J92" s="5" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7629052</t>
+          <t>https://stripe.com/jobs/search?gh_jid=7826765</t>
         </is>
       </c>
       <c r="K92" s="4" t="inlineStr">
@@ -4423,17 +4447,17 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning Manager, Feed Relevance</t>
+          <t>Backend Engineer, Core Tech, Canada</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Toronto, CAN-Remote</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr"/>
@@ -4447,7 +4471,7 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7802495</t>
+          <t>https://stripe.com/jobs/search?gh_jid=6567253</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -4464,17 +4488,17 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, GenAI Security</t>
+          <t>Backend Engineer, Core Technology</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>US-Remote, Chicago</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr"/>
@@ -4488,7 +4512,7 @@
       </c>
       <c r="J94" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7891887</t>
+          <t>https://stripe.com/jobs/search?gh_jid=6042172</t>
         </is>
       </c>
       <c r="K94" s="4" t="inlineStr">
@@ -4505,17 +4529,17 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Senior Staff Machine Learning Engineer, Feed Relevance</t>
+          <t>Backend Engineer, Developer Experience &amp; Product Platform</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Toronto Canada, San Francisco, Remote in US, Remote in Canada</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr"/>
@@ -4529,7 +4553,7 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7791994</t>
+          <t>https://stripe.com/jobs/search?gh_jid=7292520</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -4546,17 +4570,17 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Senior Staff Machine Learning Engineer, ML Understanding</t>
+          <t>Commercial Counsel, Crypto</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>New York City, Seattle, San Francisco, Chicago, Atlanta, US-Remote</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr"/>
@@ -4570,7 +4594,7 @@
       </c>
       <c r="J96" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7847148</t>
+          <t>https://stripe.com/jobs/search?gh_jid=7392188</t>
         </is>
       </c>
       <c r="K96" s="4" t="inlineStr">
@@ -4587,17 +4611,17 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, Ads Measurement Modeling</t>
+          <t>Fullstack Engineer, Privy</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t xml:space="preserve">NYC-Privy, US-Remote </t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr"/>
@@ -4611,7 +4635,7 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7890096</t>
+          <t>https://stripe.com/jobs/search?gh_jid=7091959</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -4628,17 +4652,17 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, AI Serving</t>
+          <t>Machine Learning Engineer, Stripe Assistant</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Seattle; San Francisco; New York City; Remote</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr"/>
@@ -4652,7 +4676,7 @@
       </c>
       <c r="J98" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7886459</t>
+          <t>https://stripe.com/jobs/search?gh_jid=7629052</t>
         </is>
       </c>
       <c r="K98" s="4" t="inlineStr">
@@ -4669,17 +4693,17 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (L3) - Full Stack</t>
+          <t>Machine Learning Manager, Feed Relevance</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Remote - US</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr"/>
@@ -4693,7 +4717,7 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7738955</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7802495</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -4703,265 +4727,229 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+      <c r="A100" s="4" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>AI Developer (Claude + AWS)</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>Datavent</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>Hamburg</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
-      <c r="F100" s="2" t="inlineStr"/>
-      <c r="G100" s="2" t="inlineStr">
-        <is>
-          <t>Remote, Software Development</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="inlineStr"/>
-      <c r="I100" s="2" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J100" s="3" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/datavent/ai-developer-claude-aws-hamburg-22354</t>
-        </is>
-      </c>
-      <c r="K100" s="2" t="inlineStr">
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer, GenAI Security</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr"/>
+      <c r="F100" s="4" t="inlineStr"/>
+      <c r="G100" s="4" t="inlineStr"/>
+      <c r="H100" s="4" t="inlineStr"/>
+      <c r="I100" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J100" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7891887</t>
+        </is>
+      </c>
+      <c r="K100" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="4" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Senior Staff Machine Learning Engineer, Feed Relevance</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr"/>
+      <c r="F101" s="2" t="inlineStr"/>
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr"/>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7791994</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="B101" s="4" t="inlineStr">
-        <is>
-          <t>Python Software Engineer, Backend &amp; APIs - Remote</t>
-        </is>
-      </c>
-      <c r="C101" s="4" t="inlineStr">
-        <is>
-          <t>dexter health</t>
-        </is>
-      </c>
-      <c r="D101" s="4" t="inlineStr">
-        <is>
-          <t>Cologne</t>
-        </is>
-      </c>
-      <c r="E101" s="4" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
-      <c r="F101" s="4" t="inlineStr"/>
-      <c r="G101" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Software Development</t>
-        </is>
-      </c>
-      <c r="H101" s="4" t="inlineStr"/>
-      <c r="I101" s="4" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J101" s="5" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/python-software-engineer-backend-apis-remote-cologne-284750</t>
-        </is>
-      </c>
-      <c r="K101" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>Fullstack Developer (m/w/d) REMOTE //  UX / Python / Vue.js</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>Pont Connects e.K.</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>Düsseldorf</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr"/>
-      <c r="F102" s="2" t="inlineStr"/>
-      <c r="G102" s="2" t="inlineStr">
-        <is>
-          <t>Remote, IT</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr"/>
-      <c r="I102" s="2" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J102" s="3" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/pont-connects-ek/fullstack-developer-remote-ux-python-vuejs-dusseldorf-371903</t>
-        </is>
-      </c>
-      <c r="K102" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-03</t>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>Senior Staff Machine Learning Engineer, ML Understanding</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr"/>
+      <c r="F102" s="4" t="inlineStr"/>
+      <c r="G102" s="4" t="inlineStr"/>
+      <c r="H102" s="4" t="inlineStr"/>
+      <c r="I102" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J102" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7847148</t>
+        </is>
+      </c>
+      <c r="K102" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Staff Machine Learning Engineer, Ads Measurement Modeling</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Lemon.io</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Americas, Europe, Asia, Oceania</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
-        <is>
-          <t>full_time</t>
-        </is>
-      </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>Devops</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="inlineStr">
-        <is>
-          <t>.Net, android, AWS, azure, C, C#, C++, data science, golang, ios, java, javascript, kubernetes, node.js, php, python, react, ruby/rails, shopify, sql, video, blockchain, AI/ML, automation, react native, rust, unity, spring, data analysis, laravel, solidity, flask, Typescript , terraform, angular , GCP, data engineering, Symfony, startup, marketplace, next.js</t>
-        </is>
-      </c>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr"/>
+      <c r="F103" s="2" t="inlineStr"/>
+      <c r="G103" s="2" t="inlineStr"/>
       <c r="H103" s="2" t="inlineStr"/>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>Remotive</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
-          <t>https://remotive.com/remote-jobs/devops/senior-devops-engineer-2090002</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7890096</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-05</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>M&amp;A Research Analyst</t>
+          <t>Staff Machine Learning Engineer, AI Serving</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>EquiMatch GmbH</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="E104" s="4" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr"/>
       <c r="F104" s="4" t="inlineStr"/>
-      <c r="G104" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Mergers &amp; Acquisitions</t>
-        </is>
-      </c>
+      <c r="G104" s="4" t="inlineStr"/>
       <c r="H104" s="4" t="inlineStr"/>
       <c r="I104" s="4" t="inlineStr">
         <is>
-          <t>Arbeitnow</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J104" s="5" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/equimatch-gmbh/ma-research-analyst-berlin-498635</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7886459</t>
         </is>
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-05</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Xsolla: Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr"/>
+          <t>Senior Software Engineer (L3) - Full Stack</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote - US</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr"/>
@@ -4970,128 +4958,144 @@
       <c r="H105" s="2" t="inlineStr"/>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/xsolla-full-stack-developer</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7738955</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-05</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="B106" s="4" t="inlineStr">
-        <is>
-          <t>Dropbox: Staff Fullstack Product Software Engineer, Dash</t>
-        </is>
-      </c>
-      <c r="C106" s="4" t="inlineStr"/>
-      <c r="D106" s="4" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E106" s="4" t="inlineStr"/>
-      <c r="F106" s="4" t="inlineStr"/>
-      <c r="G106" s="4" t="inlineStr"/>
-      <c r="H106" s="4" t="inlineStr"/>
-      <c r="I106" s="4" t="inlineStr">
-        <is>
-          <t>WeWorkRemotely</t>
-        </is>
-      </c>
-      <c r="J106" s="5" t="inlineStr">
-        <is>
-          <t>https://weworkremotely.com/remote-jobs/dropbox-staff-fullstack-product-software-engineer-dash</t>
-        </is>
-      </c>
-      <c r="K106" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>AI Developer (Claude + AWS)</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Datavent</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Hamburg</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr"/>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>Remote, Software Development</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr"/>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/datavent/ai-developer-claude-aws-hamburg-22354</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>Staff Machine Learning Engineer, Ranking and Personalization</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>Reddit</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>Remote - United States</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr"/>
-      <c r="F107" s="2" t="inlineStr"/>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr"/>
-      <c r="I107" s="2" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="J107" s="3" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7848689</t>
-        </is>
-      </c>
-      <c r="K107" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>Python Software Engineer, Backend &amp; APIs - Remote</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>dexter health</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>Cologne</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
+      <c r="F107" s="4" t="inlineStr"/>
+      <c r="G107" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Software Development</t>
+        </is>
+      </c>
+      <c r="H107" s="4" t="inlineStr"/>
+      <c r="I107" s="4" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J107" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/python-software-engineer-backend-apis-remote-cologne-284750</t>
+        </is>
+      </c>
+      <c r="K107" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Senior Rust Consultant / Engineer (m/w/d)</t>
+          <t>Fullstack Developer (m/w/d) REMOTE //  UX / Python / Vue.js</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Hackstack GmbH</t>
+          <t>Pont Connects e.K.</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
-        <is>
-          <t>berufserfahren</t>
-        </is>
-      </c>
+          <t>Düsseldorf</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr"/>
       <c r="F108" s="2" t="inlineStr"/>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Remote, Consulting, Engineering</t>
+          <t>Remote, IT</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr"/>
@@ -5102,277 +5106,273 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/hackstack-gmbh/senior-rust-consultant-engineer-munich-451602</t>
+          <t>https://www.arbeitnow.com/jobs/companies/pont-connects-ek/fullstack-developer-remote-ux-python-vuejs-dusseldorf-371903</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Lemon.io</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Americas, Europe, Asia, Oceania</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>full_time</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>Devops</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>.Net, android, AWS, azure, C, C#, C++, data science, golang, ios, java, javascript, kubernetes, node.js, php, python, react, ruby/rails, shopify, sql, video, blockchain, AI/ML, automation, react native, rust, unity, spring, data analysis, laravel, solidity, flask, Typescript , terraform, angular , GCP, data engineering, Symfony, startup, marketplace, next.js</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr"/>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>Remotive</t>
+        </is>
+      </c>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/devops/senior-devops-engineer-2090002</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>M&amp;A Research Analyst</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>EquiMatch GmbH</t>
+        </is>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
+      <c r="F110" s="4" t="inlineStr"/>
+      <c r="G110" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Mergers &amp; Acquisitions</t>
+        </is>
+      </c>
+      <c r="H110" s="4" t="inlineStr"/>
+      <c r="I110" s="4" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="J110" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/equimatch-gmbh/ma-research-analyst-berlin-498635</t>
+        </is>
+      </c>
+      <c r="K110" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
           <t>2026-05-01</t>
         </is>
       </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="4" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Xsolla: Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr"/>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr"/>
+      <c r="F111" s="2" t="inlineStr"/>
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr"/>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>WeWorkRemotely</t>
+        </is>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>https://weworkremotely.com/remote-jobs/xsolla-full-stack-developer</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="B109" s="4" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer - Remote</t>
-        </is>
-      </c>
-      <c r="C109" s="4" t="inlineStr">
-        <is>
-          <t>dexter health</t>
-        </is>
-      </c>
-      <c r="D109" s="4" t="inlineStr">
-        <is>
-          <t>Cologne</t>
-        </is>
-      </c>
-      <c r="E109" s="4" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
-      <c r="F109" s="4" t="inlineStr"/>
-      <c r="G109" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Development</t>
-        </is>
-      </c>
-      <c r="H109" s="4" t="inlineStr"/>
-      <c r="I109" s="4" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J109" s="5" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/applied-ai-engineer-remote-cologne-2870</t>
-        </is>
-      </c>
-      <c r="K109" s="4" t="inlineStr">
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>Dropbox: Staff Fullstack Product Software Engineer, Dash</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr"/>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="inlineStr"/>
+      <c r="F112" s="4" t="inlineStr"/>
+      <c r="G112" s="4" t="inlineStr"/>
+      <c r="H112" s="4" t="inlineStr"/>
+      <c r="I112" s="4" t="inlineStr">
+        <is>
+          <t>WeWorkRemotely</t>
+        </is>
+      </c>
+      <c r="J112" s="5" t="inlineStr">
+        <is>
+          <t>https://weworkremotely.com/remote-jobs/dropbox-staff-fullstack-product-software-engineer-dash</t>
+        </is>
+      </c>
+      <c r="K112" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>Python Backend Engineer - Remote</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>dexter health</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>Cologne</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
-      <c r="F110" s="2" t="inlineStr"/>
-      <c r="G110" s="2" t="inlineStr">
-        <is>
-          <t>Remote, Development</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr"/>
-      <c r="I110" s="2" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J110" s="3" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/python-backend-engineer-remote-cologne-34228</t>
-        </is>
-      </c>
-      <c r="K110" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="B111" s="4" t="inlineStr">
-        <is>
-          <t>AI Engineer (LLM Products) - Remote</t>
-        </is>
-      </c>
-      <c r="C111" s="4" t="inlineStr">
-        <is>
-          <t>dexter health</t>
-        </is>
-      </c>
-      <c r="D111" s="4" t="inlineStr">
-        <is>
-          <t>Cologne</t>
-        </is>
-      </c>
-      <c r="E111" s="4" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
-      <c r="F111" s="4" t="inlineStr"/>
-      <c r="G111" s="4" t="inlineStr">
-        <is>
-          <t>Remote, Development</t>
-        </is>
-      </c>
-      <c r="H111" s="4" t="inlineStr"/>
-      <c r="I111" s="4" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J111" s="5" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/ai-engineer-llm-products-remote-cologne-236027</t>
-        </is>
-      </c>
-      <c r="K111" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>Backend Python Engineer (APIs, Databases &amp; Cloud) - Remote</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>dexter health</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
-        <is>
-          <t>Cologne</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="inlineStr">
-        <is>
-          <t>professional / experienced</t>
-        </is>
-      </c>
-      <c r="F112" s="2" t="inlineStr"/>
-      <c r="G112" s="2" t="inlineStr">
-        <is>
-          <t>Remote, Development</t>
-        </is>
-      </c>
-      <c r="H112" s="2" t="inlineStr"/>
-      <c r="I112" s="2" t="inlineStr">
-        <is>
-          <t>Arbeitnow</t>
-        </is>
-      </c>
-      <c r="J112" s="3" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/backend-python-engineer-apis-databases-cloud-remote-cologne-274767</t>
-        </is>
-      </c>
-      <c r="K112" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B113" s="4" t="inlineStr">
-        <is>
-          <t>Toptal: QA Automation Engineer</t>
-        </is>
-      </c>
-      <c r="C113" s="4" t="inlineStr"/>
-      <c r="D113" s="4" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E113" s="4" t="inlineStr"/>
-      <c r="F113" s="4" t="inlineStr"/>
-      <c r="G113" s="4" t="inlineStr"/>
-      <c r="H113" s="4" t="inlineStr"/>
-      <c r="I113" s="4" t="inlineStr">
-        <is>
-          <t>WeWorkRemotely</t>
-        </is>
-      </c>
-      <c r="J113" s="5" t="inlineStr">
-        <is>
-          <t>https://weworkremotely.com/remote-jobs/toptal-qa-automation-engineer-1</t>
-        </is>
-      </c>
-      <c r="K113" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Staff Machine Learning Engineer, Ranking and Personalization</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr"/>
+      <c r="F113" s="2" t="inlineStr"/>
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr"/>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7848689</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Opensea: Staff Product Designer</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr"/>
+          <t>Senior Rust Consultant / Engineer (m/w/d)</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Hackstack GmbH</t>
+        </is>
+      </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E114" s="2" t="inlineStr"/>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>berufserfahren</t>
+        </is>
+      </c>
       <c r="F114" s="2" t="inlineStr"/>
-      <c r="G114" s="2" t="inlineStr"/>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>Remote, Consulting, Engineering</t>
+        </is>
+      </c>
       <c r="H114" s="2" t="inlineStr"/>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/opensea-staff-product-designer</t>
+          <t>https://www.arbeitnow.com/jobs/companies/hackstack-gmbh/senior-rust-consultant-engineer-munich-451602</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -5384,32 +5384,44 @@
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Mutt Data: Devops</t>
-        </is>
-      </c>
-      <c r="C115" s="4" t="inlineStr"/>
+          <t>Applied AI Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>dexter health</t>
+        </is>
+      </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E115" s="4" t="inlineStr"/>
+          <t>Cologne</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
       <c r="F115" s="4" t="inlineStr"/>
-      <c r="G115" s="4" t="inlineStr"/>
+      <c r="G115" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Development</t>
+        </is>
+      </c>
       <c r="H115" s="4" t="inlineStr"/>
       <c r="I115" s="4" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J115" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/mutt-data-devops</t>
+          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/applied-ai-engineer-remote-cologne-2870</t>
         </is>
       </c>
       <c r="K115" s="4" t="inlineStr">
@@ -5421,32 +5433,44 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Holywater: Full-Stack Developer</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr"/>
+          <t>Python Backend Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>dexter health</t>
+        </is>
+      </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E116" s="2" t="inlineStr"/>
+          <t>Cologne</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
       <c r="F116" s="2" t="inlineStr"/>
-      <c r="G116" s="2" t="inlineStr"/>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>Remote, Development</t>
+        </is>
+      </c>
       <c r="H116" s="2" t="inlineStr"/>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/holywater-full-stack-developer</t>
+          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/python-backend-engineer-remote-cologne-34228</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -5458,32 +5482,44 @@
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Qventus: DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="C117" s="4" t="inlineStr"/>
+          <t>AI Engineer (LLM Products) - Remote</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>dexter health</t>
+        </is>
+      </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E117" s="4" t="inlineStr"/>
+          <t>Cologne</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
       <c r="F117" s="4" t="inlineStr"/>
-      <c r="G117" s="4" t="inlineStr"/>
+      <c r="G117" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Development</t>
+        </is>
+      </c>
       <c r="H117" s="4" t="inlineStr"/>
       <c r="I117" s="4" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J117" s="5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/qventus-devops-engineer</t>
+          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/ai-engineer-llm-products-remote-cologne-236027</t>
         </is>
       </c>
       <c r="K117" s="4" t="inlineStr">
@@ -5495,32 +5531,44 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Visualis: Senior Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr"/>
+          <t>Backend Python Engineer (APIs, Databases &amp; Cloud) - Remote</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>dexter health</t>
+        </is>
+      </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E118" s="2" t="inlineStr"/>
+          <t>Cologne</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>professional / experienced</t>
+        </is>
+      </c>
       <c r="F118" s="2" t="inlineStr"/>
-      <c r="G118" s="2" t="inlineStr"/>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>Remote, Development</t>
+        </is>
+      </c>
       <c r="H118" s="2" t="inlineStr"/>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>WeWorkRemotely</t>
+          <t>Arbeitnow</t>
         </is>
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/visualis-senior-full-stack-developer</t>
+          <t>https://www.arbeitnow.com/jobs/companies/dexter-health/backend-python-engineer-apis-databases-cloud-remote-cologne-274767</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -5537,17 +5585,13 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="C119" s="4" t="inlineStr">
-        <is>
-          <t>GitLab</t>
-        </is>
-      </c>
+          <t>Toptal: QA Automation Engineer</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr"/>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Remote, Bangalore</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr"/>
@@ -5556,12 +5600,12 @@
       <c r="H119" s="4" t="inlineStr"/>
       <c r="I119" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J119" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8517564002</t>
+          <t>https://weworkremotely.com/remote-jobs/toptal-qa-automation-engineer-1</t>
         </is>
       </c>
       <c r="K119" s="4" t="inlineStr">
@@ -5578,17 +5622,13 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Backend Engineer, Analytics Instrumentation (Golang)</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>GitLab</t>
-        </is>
-      </c>
+          <t>Opensea: Staff Product Designer</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr"/>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr"/>
@@ -5597,12 +5637,12 @@
       <c r="H120" s="2" t="inlineStr"/>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481922002</t>
+          <t>https://weworkremotely.com/remote-jobs/opensea-staff-product-designer</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -5619,17 +5659,13 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>Backend Engineer, Analytics Instrumentation (Golang)</t>
-        </is>
-      </c>
-      <c r="C121" s="4" t="inlineStr">
-        <is>
-          <t>GitLab</t>
-        </is>
-      </c>
+          <t>Mutt Data: Devops</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr"/>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr"/>
@@ -5638,12 +5674,12 @@
       <c r="H121" s="4" t="inlineStr"/>
       <c r="I121" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J121" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481929002</t>
+          <t>https://weworkremotely.com/remote-jobs/mutt-data-devops</t>
         </is>
       </c>
       <c r="K121" s="4" t="inlineStr">
@@ -5660,17 +5696,13 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Backend Engineer, Knowledge Graph (Rust)</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>GitLab</t>
-        </is>
-      </c>
+          <t>Holywater: Full-Stack Developer</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr"/>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, US</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr"/>
@@ -5679,12 +5711,12 @@
       <c r="H122" s="2" t="inlineStr"/>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8437754002</t>
+          <t>https://weworkremotely.com/remote-jobs/holywater-full-stack-developer</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -5701,17 +5733,13 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>Backend Engineer, Knowledge Graph (Rust)</t>
-        </is>
-      </c>
-      <c r="C123" s="4" t="inlineStr">
-        <is>
-          <t>GitLab</t>
-        </is>
-      </c>
+          <t>Qventus: DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr"/>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr"/>
@@ -5720,12 +5748,12 @@
       <c r="H123" s="4" t="inlineStr"/>
       <c r="I123" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J123" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481958002</t>
+          <t>https://weworkremotely.com/remote-jobs/qventus-devops-engineer</t>
         </is>
       </c>
       <c r="K123" s="4" t="inlineStr">
@@ -5742,17 +5770,13 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Intermediate Backend Engineer (C), Tenant Scale: Git</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>GitLab</t>
-        </is>
-      </c>
+          <t>Visualis: Senior Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr"/>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr"/>
@@ -5761,12 +5785,12 @@
       <c r="H124" s="2" t="inlineStr"/>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>WeWorkRemotely</t>
         </is>
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8497793002</t>
+          <t>https://weworkremotely.com/remote-jobs/visualis-senior-full-stack-developer</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -5783,7 +5807,7 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>Intermediate Backend Engineer, Gitlab Delivery: Upgrades</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
@@ -5793,7 +5817,7 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, Bangalore</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr"/>
@@ -5807,7 +5831,7 @@
       </c>
       <c r="J125" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8463951002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8517564002</t>
         </is>
       </c>
       <c r="K125" s="4" t="inlineStr">
@@ -5824,7 +5848,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Intermediate Backend Engineer, SRM: Security Platform Management</t>
+          <t>Backend Engineer, Analytics Instrumentation (Golang)</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -5834,7 +5858,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr"/>
@@ -5848,7 +5872,7 @@
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8443325002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481922002</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -5865,7 +5889,7 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>Intermediate Backend Engineer, SSCS: AI Governance</t>
+          <t>Backend Engineer, Analytics Instrumentation (Golang)</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
@@ -5889,7 +5913,7 @@
       </c>
       <c r="J127" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480551002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481929002</t>
         </is>
       </c>
       <c r="K127" s="4" t="inlineStr">
@@ -5906,7 +5930,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Intermediate Backend Engineer,  SSCS: Supply Chain</t>
+          <t>Backend Engineer, Knowledge Graph (Rust)</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -5916,7 +5940,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, Canada; Remote, US</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr"/>
@@ -5930,7 +5954,7 @@
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480565002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8437754002</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -5947,7 +5971,7 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Backend Engineer, Knowledge Graph (Rust)</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
@@ -5957,7 +5981,7 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Remote, EMEA</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr"/>
@@ -5971,7 +5995,7 @@
       </c>
       <c r="J129" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8464072002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481958002</t>
         </is>
       </c>
       <c r="K129" s="4" t="inlineStr">
@@ -5988,7 +6012,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (AI), Pipeline Execution</t>
+          <t>Intermediate Backend Engineer (C), Tenant Scale: Git</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -5998,7 +6022,7 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US-Southeast</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr"/>
@@ -6012,7 +6036,7 @@
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8514945002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8497793002</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
@@ -6029,7 +6053,7 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Analytics Instrumentation (Golang)</t>
+          <t>Intermediate Backend Engineer, Gitlab Delivery: Upgrades</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
@@ -6039,7 +6063,7 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, US</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr"/>
@@ -6053,7 +6077,7 @@
       </c>
       <c r="J131" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8451512002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8463951002</t>
         </is>
       </c>
       <c r="K131" s="4" t="inlineStr">
@@ -6070,7 +6094,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (C), Tenant Scale: Git</t>
+          <t>Intermediate Backend Engineer, SRM: Security Platform Management</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -6080,7 +6104,7 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr"/>
@@ -6094,7 +6118,7 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8497791002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8443325002</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -6111,7 +6135,7 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Gitlab Delivery: Runway (Platform Engineering)</t>
+          <t>Intermediate Backend Engineer, SSCS: AI Governance</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
@@ -6121,7 +6145,7 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Remote, Australia; Remote, India; Remote, Ireland; Remote, Japan; Remote, Netherlands; Remote, Singapore; Remote, United Kingdom</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr"/>
@@ -6135,7 +6159,7 @@
       </c>
       <c r="J133" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8324132002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480551002</t>
         </is>
       </c>
       <c r="K133" s="4" t="inlineStr">
@@ -6152,7 +6176,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Gitlab Delivery: Upgrades</t>
+          <t>Intermediate Backend Engineer,  SSCS: Supply Chain</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -6176,7 +6200,7 @@
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8463933002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480565002</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
@@ -6193,7 +6217,7 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer(Go), Continuous Delivery</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
@@ -6203,7 +6227,7 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, EMEA</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr"/>
@@ -6217,7 +6241,7 @@
       </c>
       <c r="J135" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8488966002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8464072002</t>
         </is>
       </c>
       <c r="K135" s="4" t="inlineStr">
@@ -6234,7 +6258,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer(Golang),Software Supply Chain Security: Auth Infrastructure</t>
+          <t>Senior Backend Engineer (AI), Pipeline Execution</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -6244,7 +6268,7 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Remote, Americas; Remote, APAC; Remote, Canada</t>
+          <t>Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US-Southeast</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr"/>
@@ -6258,7 +6282,7 @@
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8157520002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8514945002</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -6275,7 +6299,7 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (RoR), AST: Secret Detection</t>
+          <t>Senior Backend Engineer, Analytics Instrumentation (Golang)</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
@@ -6285,7 +6309,7 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
+          <t>Remote, Canada; Remote, US</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr"/>
@@ -6299,7 +6323,7 @@
       </c>
       <c r="J137" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8432262002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8451512002</t>
         </is>
       </c>
       <c r="K137" s="4" t="inlineStr">
@@ -6316,7 +6340,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (RoR/Go), SSCS: Pipeline Security</t>
+          <t>Senior Backend Engineer (C), Tenant Scale: Git</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -6326,7 +6350,7 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr"/>
@@ -6340,7 +6364,7 @@
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8432221002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8497791002</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
@@ -6357,7 +6381,7 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (RoR), SSCS: Authorization</t>
+          <t>Senior Backend Engineer, Gitlab Delivery: Runway (Platform Engineering)</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
@@ -6367,7 +6391,7 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
+          <t>Remote, Australia; Remote, India; Remote, Ireland; Remote, Japan; Remote, Netherlands; Remote, Singapore; Remote, United Kingdom</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr"/>
@@ -6381,7 +6405,7 @@
       </c>
       <c r="J139" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8457315002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8324132002</t>
         </is>
       </c>
       <c r="K139" s="4" t="inlineStr">
@@ -6398,7 +6422,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby or Golang), Tenant Scale; Cells Infrastructure</t>
+          <t>Senior Backend Engineer, Gitlab Delivery: Upgrades</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -6408,7 +6432,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Remote, APAC; Remote, Canada; Remote, EMEA; Remote, US</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr"/>
@@ -6422,7 +6446,7 @@
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8437148002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8463933002</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -6439,7 +6463,7 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, SSCS: AI Governance</t>
+          <t>Senior Backend Engineer(Go), Continuous Delivery</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
@@ -6463,7 +6487,7 @@
       </c>
       <c r="J141" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480544002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8488966002</t>
         </is>
       </c>
       <c r="K141" s="4" t="inlineStr">
@@ -6480,7 +6504,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer,  SSCS: Supply Chain</t>
+          <t>Senior Backend Engineer(Golang),Software Supply Chain Security: Auth Infrastructure</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -6490,7 +6514,7 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, Americas; Remote, APAC; Remote, Canada</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr"/>
@@ -6504,7 +6528,7 @@
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480580002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8157520002</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -6521,7 +6545,7 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Senior Fullstack Engineer (TypeScript), AI Engineering: Editor Extensions</t>
+          <t>Senior Backend Engineer (RoR), AST: Secret Detection</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
@@ -6531,7 +6555,7 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Remote, APAC; Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US-Southeast</t>
+          <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr"/>
@@ -6545,7 +6569,7 @@
       </c>
       <c r="J143" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8452278002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8432262002</t>
         </is>
       </c>
       <c r="K143" s="4" t="inlineStr">
@@ -6562,7 +6586,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer, Analytics Instrumentation (Golang)</t>
+          <t>Senior Backend Engineer (RoR/Go), SSCS: Pipeline Security</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -6572,7 +6596,7 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr"/>
@@ -6586,7 +6610,7 @@
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8508027002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8432221002</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -6603,7 +6627,7 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer, AST: Composition Analysis</t>
+          <t>Senior Backend Engineer (RoR), SSCS: Authorization</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
@@ -6613,7 +6637,7 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>Remote, Australia; Remote, Canada; Remote, India; Remote, Ireland; Remote, Israel; Remote, Japan; Remote, Netherlands; Remote, New Zealand; Remote, United Kingdom; Remote, US</t>
+          <t>Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr"/>
@@ -6627,7 +6651,7 @@
       </c>
       <c r="J145" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8478364002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8457315002</t>
         </is>
       </c>
       <c r="K145" s="4" t="inlineStr">
@@ -6644,7 +6668,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer, Developer Experience</t>
+          <t>Senior Backend Engineer (Ruby or Golang), Tenant Scale; Cells Infrastructure</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -6654,7 +6678,7 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, United Kingdom; Remote, US</t>
+          <t>Remote, APAC; Remote, Canada; Remote, EMEA; Remote, US</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr"/>
@@ -6668,7 +6692,7 @@
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8490477002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8437148002</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -6685,7 +6709,7 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer, Gitlab Delivery: Upgrades</t>
+          <t>Senior Backend Engineer, SSCS: AI Governance</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
@@ -6709,7 +6733,7 @@
       </c>
       <c r="J147" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8463922002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480544002</t>
         </is>
       </c>
       <c r="K147" s="4" t="inlineStr">
@@ -6726,7 +6750,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer (Go), Continuous Delivery</t>
+          <t>Senior Backend Engineer,  SSCS: Supply Chain</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -6750,7 +6774,7 @@
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8488961002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480580002</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
@@ -6767,7 +6791,7 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer (Go), Software Supply Chain Security: Secrets Management</t>
+          <t>Senior Fullstack Engineer (TypeScript), AI Engineering: Editor Extensions</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
@@ -6777,7 +6801,7 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
+          <t>Remote, APAC; Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom; Remote, US-Southeast</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr"/>
@@ -6791,7 +6815,7 @@
       </c>
       <c r="J149" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8432235002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8452278002</t>
         </is>
       </c>
       <c r="K149" s="4" t="inlineStr">
@@ -6808,7 +6832,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer, Knowledge Graph (Rust)</t>
+          <t>Staff Backend Engineer, Analytics Instrumentation (Golang)</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -6832,7 +6856,7 @@
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481945002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8508027002</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -6849,7 +6873,7 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer,  Software Supply Chain Security</t>
+          <t>Staff Backend Engineer, AST: Composition Analysis</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
@@ -6859,7 +6883,7 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, Australia; Remote, Canada; Remote, India; Remote, Ireland; Remote, Israel; Remote, Japan; Remote, Netherlands; Remote, New Zealand; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr"/>
@@ -6873,7 +6897,7 @@
       </c>
       <c r="J151" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480559002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8478364002</t>
         </is>
       </c>
       <c r="K151" s="4" t="inlineStr">
@@ -6890,7 +6914,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer, SSCS: AI Governance</t>
+          <t>Staff Backend Engineer, Developer Experience</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -6900,7 +6924,7 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Remote, India</t>
+          <t>Remote, Canada; Remote, United Kingdom; Remote, US</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr"/>
@@ -6914,7 +6938,7 @@
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480531002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8490477002</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
@@ -6931,7 +6955,7 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>Staff Backend (Python) Engineer, AI Engineering:Duo Chat</t>
+          <t>Staff Backend Engineer, Gitlab Delivery: Upgrades</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
@@ -6941,7 +6965,7 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>Remote, Americas; Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr"/>
@@ -6955,7 +6979,7 @@
       </c>
       <c r="J153" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8450446002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8463922002</t>
         </is>
       </c>
       <c r="K153" s="4" t="inlineStr">
@@ -6972,17 +6996,17 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Senior Full Stack Product Software Engineer</t>
+          <t>Staff Backend Engineer (Go), Continuous Delivery</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Dropbox</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Remote - Poland</t>
+          <t>Remote, India</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr"/>
@@ -6996,350 +7020,258 @@
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8488961002</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B155" s="4" t="inlineStr">
+        <is>
+          <t>Staff Backend Engineer (Go), Software Supply Chain Security: Secrets Management</t>
+        </is>
+      </c>
+      <c r="C155" s="4" t="inlineStr">
+        <is>
+          <t>GitLab</t>
+        </is>
+      </c>
+      <c r="D155" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Canada; Remote, Ireland; Remote, Israel; Remote, Netherlands; Remote, United Kingdom; Remote, US</t>
+        </is>
+      </c>
+      <c r="E155" s="4" t="inlineStr"/>
+      <c r="F155" s="4" t="inlineStr"/>
+      <c r="G155" s="4" t="inlineStr"/>
+      <c r="H155" s="4" t="inlineStr"/>
+      <c r="I155" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J155" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8432235002</t>
+        </is>
+      </c>
+      <c r="K155" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>Staff Backend Engineer, Knowledge Graph (Rust)</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>GitLab</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Remote, India</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr"/>
+      <c r="F156" s="2" t="inlineStr"/>
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr"/>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J156" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8481945002</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B157" s="4" t="inlineStr">
+        <is>
+          <t>Staff Backend Engineer,  Software Supply Chain Security</t>
+        </is>
+      </c>
+      <c r="C157" s="4" t="inlineStr">
+        <is>
+          <t>GitLab</t>
+        </is>
+      </c>
+      <c r="D157" s="4" t="inlineStr">
+        <is>
+          <t>Remote, India</t>
+        </is>
+      </c>
+      <c r="E157" s="4" t="inlineStr"/>
+      <c r="F157" s="4" t="inlineStr"/>
+      <c r="G157" s="4" t="inlineStr"/>
+      <c r="H157" s="4" t="inlineStr"/>
+      <c r="I157" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J157" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480559002</t>
+        </is>
+      </c>
+      <c r="K157" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>Staff Backend Engineer, SSCS: AI Governance</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>GitLab</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Remote, India</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr"/>
+      <c r="F158" s="2" t="inlineStr"/>
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr"/>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J158" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8480531002</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B159" s="4" t="inlineStr">
+        <is>
+          <t>Staff Backend (Python) Engineer, AI Engineering:Duo Chat</t>
+        </is>
+      </c>
+      <c r="C159" s="4" t="inlineStr">
+        <is>
+          <t>GitLab</t>
+        </is>
+      </c>
+      <c r="D159" s="4" t="inlineStr">
+        <is>
+          <t>Remote, Americas; Remote, Canada; Remote, Ireland; Remote, Netherlands; Remote, United Kingdom</t>
+        </is>
+      </c>
+      <c r="E159" s="4" t="inlineStr"/>
+      <c r="F159" s="4" t="inlineStr"/>
+      <c r="G159" s="4" t="inlineStr"/>
+      <c r="H159" s="4" t="inlineStr"/>
+      <c r="I159" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J159" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8450446002</t>
+        </is>
+      </c>
+      <c r="K159" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Product Software Engineer</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Dropbox</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Remote - Poland</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr"/>
+      <c r="F160" s="2" t="inlineStr"/>
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr"/>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="J160" s="3" t="inlineStr">
+        <is>
           <t>https://jobs.dropbox.com/listing/6449719?gh_jid=6449719</t>
         </is>
       </c>
-      <c r="K154" s="2" t="inlineStr">
+      <c r="K160" s="2" t="inlineStr">
         <is>
           <t>2026-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>Dry Ground AI</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
-        <is>
-          <t>Brazil, Colombia, Philippines</t>
-        </is>
-      </c>
-      <c r="E155" s="2" t="inlineStr">
-        <is>
-          <t>full_time</t>
-        </is>
-      </c>
-      <c r="F155" s="2" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence</t>
-        </is>
-      </c>
-      <c r="G155" s="2" t="inlineStr">
-        <is>
-          <t>api, cloud, fullstack, python, AI/ML, automation, research, CI/CD, TensorFlow, spark, NLP, CMS, Pytorch, REST</t>
-        </is>
-      </c>
-      <c r="H155" s="2" t="inlineStr">
-        <is>
-          <t>$40- $60k</t>
-        </is>
-      </c>
-      <c r="I155" s="2" t="inlineStr">
-        <is>
-          <t>Remotive</t>
-        </is>
-      </c>
-      <c r="J155" s="3" t="inlineStr">
-        <is>
-          <t>https://remotive.com/remote-jobs/artificial-intelligence/ai-engineer-2089958</t>
-        </is>
-      </c>
-      <c r="K155" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B156" s="4" t="inlineStr">
-        <is>
-          <t>Senior Independent AI Engineer / Architect</t>
-        </is>
-      </c>
-      <c r="C156" s="4" t="inlineStr">
-        <is>
-          <t>A.Team</t>
-        </is>
-      </c>
-      <c r="D156" s="4" t="inlineStr">
-        <is>
-          <t>Americas, Europe, Israel</t>
-        </is>
-      </c>
-      <c r="E156" s="4" t="inlineStr">
-        <is>
-          <t>contract</t>
-        </is>
-      </c>
-      <c r="F156" s="4" t="inlineStr">
-        <is>
-          <t>Software Development</t>
-        </is>
-      </c>
-      <c r="G156" s="4" t="inlineStr">
-        <is>
-          <t>go, UI/UX, wordpress, chat, apple, testing, catalyst</t>
-        </is>
-      </c>
-      <c r="H156" s="4" t="inlineStr">
-        <is>
-          <t>$120 - $170 /hour</t>
-        </is>
-      </c>
-      <c r="I156" s="4" t="inlineStr">
-        <is>
-          <t>Remotive</t>
-        </is>
-      </c>
-      <c r="J156" s="5" t="inlineStr">
-        <is>
-          <t>https://remotive.com/remote-jobs/software-development/senior-independent-ai-engineer-architect-1919266</t>
-        </is>
-      </c>
-      <c r="K156" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>Senior Independent Software Developer</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>A.Team</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
-        <is>
-          <t>Americas, Europe, Israel</t>
-        </is>
-      </c>
-      <c r="E157" s="2" t="inlineStr">
-        <is>
-          <t>contract</t>
-        </is>
-      </c>
-      <c r="F157" s="2" t="inlineStr">
-        <is>
-          <t>Software Development</t>
-        </is>
-      </c>
-      <c r="G157" s="2" t="inlineStr">
-        <is>
-          <t>go, wordpress, chat, apple, testing, catalyst</t>
-        </is>
-      </c>
-      <c r="H157" s="2" t="inlineStr">
-        <is>
-          <t>$90 - $150 /hour</t>
-        </is>
-      </c>
-      <c r="I157" s="2" t="inlineStr">
-        <is>
-          <t>Remotive</t>
-        </is>
-      </c>
-      <c r="J157" s="3" t="inlineStr">
-        <is>
-          <t>https://remotive.com/remote-jobs/software-development/senior-independent-software-developer-1919265</t>
-        </is>
-      </c>
-      <c r="K157" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B158" s="4" t="inlineStr">
-        <is>
-          <t>Senior Full-stack React Developer</t>
-        </is>
-      </c>
-      <c r="C158" s="4" t="inlineStr">
-        <is>
-          <t>Lemon.io</t>
-        </is>
-      </c>
-      <c r="D158" s="4" t="inlineStr">
-        <is>
-          <t>Americas, Europe, Asia, Oceania</t>
-        </is>
-      </c>
-      <c r="E158" s="4" t="inlineStr">
-        <is>
-          <t>contract</t>
-        </is>
-      </c>
-      <c r="F158" s="4" t="inlineStr">
-        <is>
-          <t>Software Development</t>
-        </is>
-      </c>
-      <c r="G158" s="4" t="inlineStr">
-        <is>
-          <t>.Net, android, AWS, azure, backend, C, C#, C++, data science, fullstack, golang, ios, java, javascript, node.js, php, python, react, react js, ruby/rails, shopify, video, blockchain, AI/ML, react native, rust, unity, spring, data analysis, laravel, solidity, flask, Typescript , angular , GCP, data engineering, Symfony, startup, marketplace, next.js</t>
-        </is>
-      </c>
-      <c r="H158" s="4" t="inlineStr"/>
-      <c r="I158" s="4" t="inlineStr">
-        <is>
-          <t>Remotive</t>
-        </is>
-      </c>
-      <c r="J158" s="5" t="inlineStr">
-        <is>
-          <t>https://remotive.com/remote-jobs/software-development/senior-full-stack-react-developer-2088711</t>
-        </is>
-      </c>
-      <c r="K158" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>Tech Lead Full-Stack Rails Engineer</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>Mitre Media</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
-        <is>
-          <t>USA, Canada, USA timezones</t>
-        </is>
-      </c>
-      <c r="E159" s="2" t="inlineStr">
-        <is>
-          <t>full_time</t>
-        </is>
-      </c>
-      <c r="F159" s="2" t="inlineStr">
-        <is>
-          <t>Software Development</t>
-        </is>
-      </c>
-      <c r="G159" s="2" t="inlineStr">
-        <is>
-          <t>api, CSS, docker, elasticsearch, fullstack, html, javascript, kubernetes, postgresql, react, ror, ruby/rails, AI/ML, CAD, advertising, Redis, ES6, web applications, MySQL, NLP, fintech, Micro services, github, system architecture</t>
-        </is>
-      </c>
-      <c r="H159" s="2" t="inlineStr">
-        <is>
-          <t>$170k - $200k</t>
-        </is>
-      </c>
-      <c r="I159" s="2" t="inlineStr">
-        <is>
-          <t>Remotive</t>
-        </is>
-      </c>
-      <c r="J159" s="3" t="inlineStr">
-        <is>
-          <t>https://remotive.com/remote-jobs/software-development/tech-lead-full-stack-rails-engineer-2069746</t>
-        </is>
-      </c>
-      <c r="K159" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B160" s="4" t="inlineStr">
-        <is>
-          <t>Senior Frontend Developer</t>
-        </is>
-      </c>
-      <c r="C160" s="4" t="inlineStr">
-        <is>
-          <t>Sanctuary Computer</t>
-        </is>
-      </c>
-      <c r="D160" s="4" t="inlineStr">
-        <is>
-          <t>LATAM, Asia</t>
-        </is>
-      </c>
-      <c r="E160" s="4" t="inlineStr">
-        <is>
-          <t>contract</t>
-        </is>
-      </c>
-      <c r="F160" s="4" t="inlineStr">
-        <is>
-          <t>Software Development</t>
-        </is>
-      </c>
-      <c r="G160" s="4" t="inlineStr">
-        <is>
-          <t>api, backend, CSS, ecommerce, frontend, fullstack, graphql, postgresql, redux, security, seo, shopify, open source, paas, product management, documentation, mentoring, Typescript , Redis, web applications, cypress, data visualization, firebase, IoT, engineering management, runtime, responsive, prismic, testing, next.js, CMS, jest, REST, web sockets, performance optimization</t>
-        </is>
-      </c>
-      <c r="H160" s="4" t="inlineStr">
-        <is>
-          <t>$80k - $120k</t>
-        </is>
-      </c>
-      <c r="I160" s="4" t="inlineStr">
-        <is>
-          <t>Remotive</t>
-        </is>
-      </c>
-      <c r="J160" s="5" t="inlineStr">
-        <is>
-          <t>https://remotive.com/remote-jobs/software-development/senior-frontend-developer-2088707</t>
-        </is>
-      </c>
-      <c r="K160" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7351,17 +7283,17 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Fullstack Developer (US - ET)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Chooose</t>
+          <t>Dry Ground AI</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Brazil, Colombia, Philippines</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
@@ -7371,15 +7303,19 @@
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>Software Development</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>api, azure, fullstack, python, react, saas, AI/ML, project management, documentation, Typescript , computer science, diversity, insurance</t>
-        </is>
-      </c>
-      <c r="H161" s="2" t="inlineStr"/>
+          <t>api, cloud, fullstack, python, AI/ML, automation, research, CI/CD, TensorFlow, spark, NLP, CMS, Pytorch, REST</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>$40- $60k</t>
+        </is>
+      </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
           <t>Remotive</t>
@@ -7387,7 +7323,7 @@
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
-          <t>https://remotive.com/remote-jobs/software-development/fullstack-developer-us-et-2088706</t>
+          <t>https://remotive.com/remote-jobs/artificial-intelligence/ai-engineer-2089958</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
@@ -7404,31 +7340,47 @@
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning Manager, Notifications Relevance</t>
+          <t>Senior Independent AI Engineer / Architect</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>A.Team</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
-        </is>
-      </c>
-      <c r="E162" s="4" t="inlineStr"/>
-      <c r="F162" s="4" t="inlineStr"/>
-      <c r="G162" s="4" t="inlineStr"/>
-      <c r="H162" s="4" t="inlineStr"/>
+          <t>Americas, Europe, Israel</t>
+        </is>
+      </c>
+      <c r="E162" s="4" t="inlineStr">
+        <is>
+          <t>contract</t>
+        </is>
+      </c>
+      <c r="F162" s="4" t="inlineStr">
+        <is>
+          <t>Software Development</t>
+        </is>
+      </c>
+      <c r="G162" s="4" t="inlineStr">
+        <is>
+          <t>go, UI/UX, wordpress, chat, apple, testing, catalyst</t>
+        </is>
+      </c>
+      <c r="H162" s="4" t="inlineStr">
+        <is>
+          <t>$120 - $170 /hour</t>
+        </is>
+      </c>
       <c r="I162" s="4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>Remotive</t>
         </is>
       </c>
       <c r="J162" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7846885</t>
+          <t>https://remotive.c